--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50 Villain Plan" sheetId="1" r:id="R8f67fb01529745e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rf7ee4ec6ea2c4d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="3" r:id="Rbf4a64d7e6014be8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="4" r:id="R27d6d10b340f4444"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanic Templates" sheetId="5" r:id="R5586d26d1f274e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Summary" sheetId="6" r:id="Rbccb392b13314593"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Audit" sheetId="7" r:id="R79bf5a2307c0450a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50 Villain Plan" sheetId="1" r:id="R276e927aa7834875"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rc9df6acf4aeb4b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="3" r:id="Rc030a180b1394daa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="4" r:id="R93ebc1a983ee405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanic Templates" sheetId="5" r:id="R49f3316edebf4b06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Summary" sheetId="6" r:id="Rda35a6e7f0444502"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Audit" sheetId="7" r:id="R5f342452d088479e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2171,217 +2171,145 @@
       </x:c>
     </x:row>
     <x:row r="15" s="25" customFormat="1" ht="68.0999984741211" customHeight="1">
-      <x:c r="A15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3 - Monsters</x:t>
-        </x:is>
+      <x:c r="A15" s="40" t="str">
+        <x:v>3 - Monsters</x:v>
       </x:c>
       <x:c r="B15" s="40" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reptilla</x:t>
-        </x:is>
+      <x:c r="C15" s="40" t="str">
+        <x:v>Vulcan</x:v>
       </x:c>
       <x:c r="D15" s="40" t="str">
-        <x:v>Conner's Reptiles</x:v>
+        <x:v>Here Comes Trubble</x:v>
       </x:c>
       <x:c r="E15" s="40" t="str">
-        <x:v>Verified</x:v>
-      </x:c>
-      <x:c r="F15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">In code - real/active mode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Playtest City Rampage pops, jackpot lighting, saucer 2 Super, timer reset, and case-file branches</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reptilla</x:t>
-        </x:is>
+        <x:v>Corrected / verified</x:v>
+      </x:c>
+      <x:c r="F15" s="40" t="str">
+        <x:v>In code - real/active mode</x:v>
+      </x:c>
+      <x:c r="G15" s="40" t="str">
+        <x:v>Playtest Vulcan heat/forge rules, gate/upper access, case-file branches, and chapter-fit as Monsters slot.</x:v>
+      </x:c>
+      <x:c r="H15" s="40" t="str">
+        <x:v>vulcan</x:v>
       </x:c>
       <x:c r="I15" s="40" t="str">
-        <x:v>https://marvelanimated.fandom.com/wiki/Reptilla_(Spider-Man_(1967))</x:v>
-      </x:c>
-      <x:c r="J15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Medium mode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pops rampage + jackpot shots</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pops build Rampage and jackpot value. Every 3 pops lights next Rampage Jackpot shot in order: left middle drop, upper middle target, right middle drop, then center web with More JPs.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pops, left middle drop setup, upper center target, right middle drop setup, center web, saucer 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rampage jackpots score current value; Super at saucer 2 equals total collected rampage jackpots.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pop score rises 20K+1K to 50K; jackpot adds 25K/pop to 500K; Super timer is short and reset by pops.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Adds 4th Rampage Jackpot at center web target.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rampage Jackpot awards 2X.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Super timer 10s -&gt; 16s.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10s ball save during Rampage.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shot Assist: first left-bank jackpot leaves all 3 left drops up and any left drop collects it.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="U15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapter 3: rampage/pops and Super Pops bridge.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V15" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">High</x:t>
-        </x:is>
+        <x:v>https://marvel.fandom.com/wiki/Spider-Man_(1967_animated_series)_Season_1_11B</x:v>
+      </x:c>
+      <x:c r="J15" s="40" t="str">
+        <x:v>Compact mode</x:v>
+      </x:c>
+      <x:c r="K15" s="40" t="str">
+        <x:v>Heat / forge</x:v>
+      </x:c>
+      <x:c r="L15" s="40" t="str">
+        <x:v>Build heat at spinner/pops, then forge jackpot at lit target before heat cools.</x:v>
+      </x:c>
+      <x:c r="M15" s="40" t="str">
+        <x:v>Spinner, pops, center target</x:v>
+      </x:c>
+      <x:c r="N15" s="40" t="str">
+        <x:v>Forge/cash heat jackpot.</x:v>
+      </x:c>
+      <x:c r="O15" s="40" t="str">
+        <x:v>Heat cools faster; more heat required.</x:v>
+      </x:c>
+      <x:c r="P15" s="40" t="str">
+        <x:v>+1 extra forge jackpot.</x:v>
+      </x:c>
+      <x:c r="Q15" s="40" t="str">
+        <x:v>+25% forged value.</x:v>
+      </x:c>
+      <x:c r="R15" s="40" t="str">
+        <x:v>+5s heat hold.</x:v>
+      </x:c>
+      <x:c r="S15" s="40" t="str">
+        <x:v>One overheat/drain protected.</x:v>
+      </x:c>
+      <x:c r="T15" s="40" t="str">
+        <x:v>Start with heat meter partly filled.</x:v>
+      </x:c>
+      <x:c r="U15" s="40" t="str">
+        <x:v>Chapter 3: fire/forge monster phase.</x:v>
+      </x:c>
+      <x:c r="V15" s="40" t="str">
+        <x:v>High</x:v>
       </x:c>
       <x:c r="W15" s="40" t="str">
-        <x:v>Reptilla is the intelligent reptile/alligator creature from Conner's Reptiles.</x:v>
+        <x:v>Moved into Monsters chapter; Vulcan appears in Here Comes Trubble as one of Miss Trubble's summoned figures.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="25" customFormat="1" ht="68.0999984741211" customHeight="1">
-      <x:c r="A16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3 - Monsters</x:t>
-        </x:is>
+      <x:c r="A16" s="40" t="str">
+        <x:v>3 - Monsters</x:v>
       </x:c>
       <x:c r="B16" s="40" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mole Man</x:t>
-        </x:is>
+      <x:c r="C16" s="40" t="str">
+        <x:v>Miss Trubble</x:v>
       </x:c>
       <x:c r="D16" s="40" t="str">
-        <x:v>Menace from the Bottom of the World / Spider-Man Battles the Molemen</x:v>
+        <x:v>Here Comes Trubble</x:v>
       </x:c>
       <x:c r="E16" s="40" t="str">
-        <x:v>Verified</x:v>
-      </x:c>
-      <x:c r="F16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">In code - real/active mode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Playtest Find the Mole Man secret-target reveal, early-exit resets, hurry-up, and case-file branches</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">mole_man</x:t>
-        </x:is>
+        <x:v>Corrected / verified</x:v>
+      </x:c>
+      <x:c r="F16" s="40" t="str">
+        <x:v>In code - new/active mode</x:v>
+      </x:c>
+      <x:c r="G16" s="40" t="str">
+        <x:v>Playtest hidden-correct-shot reveal mode; tune reveal timing, wrong-shot limit, and shot pool</x:v>
+      </x:c>
+      <x:c r="H16" s="40" t="str">
+        <x:v>miss_trubble</x:v>
       </x:c>
       <x:c r="I16" s="40" t="str">
-        <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
-      </x:c>
-      <x:c r="J16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Medium mode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Upper reveal -&gt; secret drop target</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enter upper; both banks reset; random secret lower drop target chosen. Upper targets drop non-secret targets while spinner builds value. Only secret remaining starts hurry-up.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Upper targets, upper spinner, both drop banks, bank rubbers</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hit revealed secret target within hurry-up for jackpot.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Early upper exit or bad lower drop before reveal drops remaining targets and forces return upper; final hurry-up pressure.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">+1 extra/bonus hurry-up opportunity later if desired.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mole Man Jackpot 2X.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Secret-target hurry-up 16s -&gt; 24s.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10s ball save.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shot Assist: rubber on secret target's bank scores and drops the secret target programmatically.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="U16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapter 3: hidden underground/search phase.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V16" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">High</x:t>
-        </x:is>
+        <x:v>https://marvel.fandom.com/wiki/Spider-Man_(1967_animated_series)_Season_1_11B</x:v>
+      </x:c>
+      <x:c r="J16" s="40" t="str">
+        <x:v>Medium mode</x:v>
+      </x:c>
+      <x:c r="K16" s="40" t="str">
+        <x:v>Hidden correct shot / reveal</x:v>
+      </x:c>
+      <x:c r="L16" s="40" t="str">
+        <x:v>Each round selects 3 shot groups that look identical. One is correct and two are traps. Spinner briefly reveals correct shot bright green and bad shots dim red. Any selected shot ends the round and selects 3 new shots. Wrong shots add to a tally; 7 wrong shots ends mode.</x:v>
+      </x:c>
+      <x:c r="M16" s="40" t="str">
+        <x:v>Left web, center web, upper spinner, upper targets, drop banks, pops</x:v>
+      </x:c>
+      <x:c r="N16" s="40" t="str">
+        <x:v>Collect jackpots by choosing correct shots before 7 wrong choices.</x:v>
+      </x:c>
+      <x:c r="O16" s="40" t="str">
+        <x:v>Wrong-shot tally creates pressure; later rounds can use harder shot groups.</x:v>
+      </x:c>
+      <x:c r="P16" s="40" t="str">
+        <x:v>Adds 2 extra rounds.</x:v>
+      </x:c>
+      <x:c r="Q16" s="40" t="str">
+        <x:v>Increases jackpot value.</x:v>
+      </x:c>
+      <x:c r="R16" s="40" t="str">
+        <x:v>Spinner reveal lasts 2s instead of 750ms.</x:v>
+      </x:c>
+      <x:c r="S16" s="40" t="str">
+        <x:v>10s ball save at mode start.</x:v>
+      </x:c>
+      <x:c r="T16" s="40" t="str">
+        <x:v>First round: all 3 lit shots count as good/correct shots.</x:v>
+      </x:c>
+      <x:c r="U16" s="40" t="str">
+        <x:v>Chapter 3: Miss Trubble trick/trap reveal phase.</x:v>
+      </x:c>
+      <x:c r="V16" s="40" t="str">
+        <x:v>High</x:v>
       </x:c>
       <x:c r="W16" s="40" t="str">
-        <x:v>Molemen/Mole leader story family verified.</x:v>
+        <x:v>Moved into Monsters chapter; Miss Trubble is the main antagonist of Here Comes Trubble and anchors the Trubble Unleashed mini-wizard.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="25" customFormat="1" ht="68.0999984741211" customHeight="1">
@@ -2492,112 +2420,74 @@
       </x:c>
     </x:row>
     <x:row r="18" s="25" customFormat="1" ht="68.0999984741211" customHeight="1">
-      <x:c r="A18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4 - Crime Wave</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">17</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Miss Trubble</x:t>
-        </x:is>
+      <x:c r="A18" s="40" t="str">
+        <x:v>4 - Crime Wave</x:v>
+      </x:c>
+      <x:c r="B18" s="40" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C18" s="40" t="str">
+        <x:v>Mole Man</x:v>
       </x:c>
       <x:c r="D18" s="40" t="str">
-        <x:v>Here Comes Trubble</x:v>
+        <x:v>Menace from the Bottom of the World / Spider-Man Battles the Molemen</x:v>
       </x:c>
       <x:c r="E18" s="40" t="str">
-        <x:v>Corrected / verified</x:v>
-      </x:c>
-      <x:c r="F18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">In code - new/active mode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Playtest hidden-correct-shot reveal mode; tune reveal timing, wrong-shot limit, and shot pool</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">miss_trubble</x:t>
-        </x:is>
+        <x:v>Verified</x:v>
+      </x:c>
+      <x:c r="F18" s="40" t="str">
+        <x:v>In code - real/active mode</x:v>
+      </x:c>
+      <x:c r="G18" s="40" t="str">
+        <x:v>Playtest Find the Mole Man secret-target reveal, early-exit resets, hurry-up, and case-file branches</x:v>
+      </x:c>
+      <x:c r="H18" s="40" t="str">
+        <x:v>mole_man</x:v>
       </x:c>
       <x:c r="I18" s="40" t="str">
-        <x:v>https://marvel.fandom.com/wiki/Spider-Man_(1967_animated_series)_Season_1_11B</x:v>
-      </x:c>
-      <x:c r="J18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Medium mode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hidden correct shot / reveal</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Each round selects 3 shot groups that look identical. One is correct and two are traps. Spinner briefly reveals correct shot bright green and bad shots dim red. Any selected shot ends the round and selects 3 new shots. Wrong shots add to a tally; 7 wrong shots ends mode.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left web, center web, upper spinner, upper targets, drop banks, pops</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collect jackpots by choosing correct shots before 7 wrong choices.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wrong-shot tally creates pressure; later rounds can use harder shot groups.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Adds 2 extra rounds.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Increases jackpot value.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spinner reveal lasts 2s instead of 750ms.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10s ball save at mode start.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">First round: all 3 lit shots count as good/correct shots.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="U18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapter 4: trick/trap-shot reveal phase.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V18" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">High</x:t>
-        </x:is>
+        <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
+      </x:c>
+      <x:c r="J18" s="40" t="str">
+        <x:v>Medium mode</x:v>
+      </x:c>
+      <x:c r="K18" s="40" t="str">
+        <x:v>Upper reveal -&gt; secret drop target</x:v>
+      </x:c>
+      <x:c r="L18" s="40" t="str">
+        <x:v>Enter upper; both banks reset; random secret lower drop target chosen. Upper targets drop non-secret targets while spinner builds value. Only secret remaining starts hurry-up.</x:v>
+      </x:c>
+      <x:c r="M18" s="40" t="str">
+        <x:v>Upper targets, upper spinner, both drop banks, bank rubbers</x:v>
+      </x:c>
+      <x:c r="N18" s="40" t="str">
+        <x:v>Hit revealed secret target within hurry-up for jackpot.</x:v>
+      </x:c>
+      <x:c r="O18" s="40" t="str">
+        <x:v>Early upper exit or bad lower drop before reveal drops remaining targets and forces return upper; final hurry-up pressure.</x:v>
+      </x:c>
+      <x:c r="P18" s="40" t="str">
+        <x:v>+1 extra/bonus hurry-up opportunity later if desired.</x:v>
+      </x:c>
+      <x:c r="Q18" s="40" t="str">
+        <x:v>Mole Man Jackpot 2X.</x:v>
+      </x:c>
+      <x:c r="R18" s="40" t="str">
+        <x:v>Secret-target hurry-up 16s -&gt; 24s.</x:v>
+      </x:c>
+      <x:c r="S18" s="40" t="str">
+        <x:v>10s ball save.</x:v>
+      </x:c>
+      <x:c r="T18" s="40" t="str">
+        <x:v>Shot Assist: rubber on secret target's bank scores and drops the secret target programmatically.</x:v>
+      </x:c>
+      <x:c r="U18" s="40" t="str">
+        <x:v>Chapter 4: hidden underground/search phase.</x:v>
+      </x:c>
+      <x:c r="V18" s="40" t="str">
+        <x:v>High</x:v>
       </x:c>
       <x:c r="W18" s="40" t="str">
-        <x:v>Miss Trubble is the main antagonist of Here Comes Trubble.</x:v>
+        <x:v>Moved from Monsters into Crime Wave; Molemen/Mole leader story family verified.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="25" customFormat="1" ht="68.0999984741211" customHeight="1">
@@ -3887,110 +3777,74 @@
       </x:c>
     </x:row>
     <x:row r="31" s="25" customFormat="1" ht="68.0999984741211" customHeight="1">
-      <x:c r="A31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6 - Mystic Menace</x:t>
-        </x:is>
+      <x:c r="A31" s="40" t="str">
+        <x:v>6 - Mystic Menace</x:v>
       </x:c>
       <x:c r="B31" s="40" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Vulcan</x:t>
-        </x:is>
+      <x:c r="C31" s="40" t="str">
+        <x:v>Reptilla</x:v>
       </x:c>
       <x:c r="D31" s="40" t="str">
-        <x:v>Here Comes Trubble</x:v>
+        <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="E31" s="40" t="str">
-        <x:v>Corrected / verified</x:v>
-      </x:c>
-      <x:c r="F31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Not in code</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Add placeholder only after confirming episode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">vulcan</x:t>
-        </x:is>
+        <x:v>Verified</x:v>
+      </x:c>
+      <x:c r="F31" s="40" t="str">
+        <x:v>In code - real/active mode</x:v>
+      </x:c>
+      <x:c r="G31" s="40" t="str">
+        <x:v>Playtest City Rampage pops, jackpot lighting, saucer 2 Super, timer reset, and case-file branches</x:v>
+      </x:c>
+      <x:c r="H31" s="40" t="str">
+        <x:v>reptilla</x:v>
       </x:c>
       <x:c r="I31" s="40" t="str">
-        <x:v>https://marvel.fandom.com/wiki/Spider-Man_(1967_animated_series)_Season_1_11B</x:v>
-      </x:c>
-      <x:c r="J31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Compact mode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Heat / forge</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Build heat at spinner/pops, then forge jackpot at lit target before heat cools.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spinner, pops, center target</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Forge/cash heat jackpot.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Heat cools faster; more heat required.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">+1 extra forge jackpot.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">+25% forged value.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">+5s heat hold.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">One overheat/drain protected.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Start with heat meter partly filled.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="U31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapter 6: fire/forge phase.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V31" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Low / verify</x:t>
-        </x:is>
+        <x:v>https://marvelanimated.fandom.com/wiki/Reptilla_(Spider-Man_(1967))</x:v>
+      </x:c>
+      <x:c r="J31" s="40" t="str">
+        <x:v>Medium mode</x:v>
+      </x:c>
+      <x:c r="K31" s="40" t="str">
+        <x:v>Pops rampage + jackpot shots</x:v>
+      </x:c>
+      <x:c r="L31" s="40" t="str">
+        <x:v>Pops build Rampage and jackpot value. Every 3 pops lights next Rampage Jackpot shot in order: left middle drop, upper middle target, right middle drop, then center web with More JPs.</x:v>
+      </x:c>
+      <x:c r="M31" s="40" t="str">
+        <x:v>Pops, left middle drop setup, upper center target, right middle drop setup, center web, saucer 2</x:v>
+      </x:c>
+      <x:c r="N31" s="40" t="str">
+        <x:v>Rampage jackpots score current value; Super at saucer 2 equals total collected rampage jackpots.</x:v>
+      </x:c>
+      <x:c r="O31" s="40" t="str">
+        <x:v>Pop score rises 20K+1K to 50K; jackpot adds 25K/pop to 500K; Super timer is short and reset by pops.</x:v>
+      </x:c>
+      <x:c r="P31" s="40" t="str">
+        <x:v>Adds 4th Rampage Jackpot at center web target.</x:v>
+      </x:c>
+      <x:c r="Q31" s="40" t="str">
+        <x:v>Rampage Jackpot awards 2X.</x:v>
+      </x:c>
+      <x:c r="R31" s="40" t="str">
+        <x:v>Super timer 10s -&gt; 16s.</x:v>
+      </x:c>
+      <x:c r="S31" s="40" t="str">
+        <x:v>10s ball save during Rampage.</x:v>
+      </x:c>
+      <x:c r="T31" s="40" t="str">
+        <x:v>Shot Assist: first left-bank jackpot leaves all 3 left drops up and any left drop collects it.</x:v>
+      </x:c>
+      <x:c r="U31" s="40" t="str">
+        <x:v>Chapter 6: creature/rampage phase.</x:v>
+      </x:c>
+      <x:c r="V31" s="40" t="str">
+        <x:v>High</x:v>
       </x:c>
       <x:c r="W31" s="40" t="str">
-        <x:v>Vulcan appears in Here Comes Trubble as one of Miss Trubble's summoned figures.</x:v>
+        <x:v>Moved out of Monsters into Mystic Menace; Reptilla is the intelligent reptile/alligator creature from Conner's Reptiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" s="25" customFormat="1" ht="68.0999984741211" customHeight="1">
@@ -7740,7 +7594,7 @@
         <x:v>Latest codebase</x:v>
       </x:c>
       <x:c r="B2" s="53" t="str">
-        <x:v>ASM67_2026_06_17c.zip</x:v>
+        <x:v>ASM67_2026_06_18a.zip + 18g chapter swap patch</x:v>
       </x:c>
       <x:c r="C2" s="40"/>
       <x:c r="D2" s="40"/>
@@ -7769,7 +7623,7 @@
         <x:v>Latest workbook update</x:v>
       </x:c>
       <x:c r="B3" s="53" t="str">
-        <x:v>2026-06-17 source verification pass</x:v>
+        <x:v>2026-06-18 chapter roster swap</x:v>
       </x:c>
       <x:c r="C3" s="40"/>
       <x:c r="D3" s="40"/>
@@ -7798,7 +7652,7 @@
         <x:v>Major corrections</x:v>
       </x:c>
       <x:c r="B4" s="53" t="str">
-        <x:v>Centaur/Cerberus/Cyclops/Vulcan -&gt; Here Comes Trubble; Reptilla -&gt; Conner's Reptiles; Doctor Manta -&gt; Phantom from the Depths of Time; Frederick Foswell -&gt; King Pinned; Sky Master -&gt; Criminals in the Clouds.</x:v>
+        <x:v>Monsters now uses Vulcan and Miss Trubble; Reptilla moved to Mystic Menace; Mole Man moved to Crime Wave; Chapter 3 mini-wizard renamed Trubble Unleashed.</x:v>
       </x:c>
       <x:c r="C4" s="40"/>
       <x:c r="D4" s="40"/>
@@ -7827,7 +7681,7 @@
         <x:v>Crime Wave status</x:v>
       </x:c>
       <x:c r="B5" s="53" t="str">
-        <x:v>Enforcers/Ox, Fifth Avenue Phantom, Frederick Foswell, Miss Trubble, Blackwell are designed/coded or in active test flow.</x:v>
+        <x:v>Enforcers/Ox, Mole Man, Fifth Avenue Phantom, Frederick Foswell, Blackwell are designed/coded or in active test flow.</x:v>
       </x:c>
       <x:c r="C5" s="40"/>
       <x:c r="D5" s="40"/>
@@ -7856,7 +7710,7 @@
         <x:v>Monsters status</x:v>
       </x:c>
       <x:c r="B6" s="53" t="str">
-        <x:v>Centaur, Cerberus, Cyclops, Reptilla, Mole Man are designed/coded or in active playtest flow.</x:v>
+        <x:v>Centaur, Cerberus, Cyclops, Vulcan, Miss Trubble are designed/coded or in active playtest flow.</x:v>
       </x:c>
       <x:c r="C6" s="40"/>
       <x:c r="D6" s="40"/>
@@ -7885,7 +7739,7 @@
         <x:v>Backups</x:v>
       </x:c>
       <x:c r="B7" s="53" t="str">
-        <x:v>Miss Trubble backup row marked duplicate/promoted; South Pole Natives and Pod verified as weak/theme/phase candidates.</x:v>
+        <x:v>Miss Trubble promoted to Monsters; Trubble Unleashed becomes the Monsters mini-wizard; Reptilla and Mole Man remain available in later chapters.</x:v>
       </x:c>
       <x:c r="C7" s="40"/>
       <x:c r="D7" s="40"/>
@@ -7943,7 +7797,7 @@
         <x:v>Mini-wizard flow</x:v>
       </x:c>
       <x:c r="B9" s="53" t="str">
-        <x:v>Placeholder mini-wizards use intro -&gt; VUK hold/release -&gt; 2-ball MB -&gt; summary -&gt; chapter advance.</x:v>
+        <x:v>Placeholder mini-wizards use intro -&gt; VUK hold/release -&gt; 2-ball MB -&gt; summary -&gt; chapter advance. Chapter 3 now opens gate for Trubble Unleashed when all 5 Monsters are complete.</x:v>
       </x:c>
       <x:c r="C9" s="40"/>
       <x:c r="D9" s="40"/>
@@ -7972,7 +7826,7 @@
         <x:v>Next work</x:v>
       </x:c>
       <x:c r="B10" s="53" t="str">
-        <x:v>Playtest latest ASM67 build, then finish remaining Chapter 4/5 designs or tune case-file/helper popups.</x:v>
+        <x:v>Playtest latest ASM67 build, then tune Chapter 3 Trubble Unleashed rules and finish remaining Chapter 4/5 designs.</x:v>
       </x:c>
       <x:c r="C10" s="40"/>
       <x:c r="D10" s="40"/>
@@ -12038,25 +11892,17 @@
           <x:t xml:space="preserve">3 - Monsters</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monster Island Breakout</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The monsters escape together.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Centaur, Cerberus, Cyclops, Reptilla, Mole Man</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Placeholder 2-ball mini-wizard flow for now; later customize around monster attacks and area clears.</x:t>
-        </x:is>
+      <x:c r="B4" s="11" t="str">
+        <x:v>Trubble Unleashed</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>Miss Trubble unleashes her mythological monsters together.</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>Centaur, Cerberus, Cyclops, Vulcan, Miss Trubble</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>Placeholder 2-ball mini-wizard flow for now; later customize around Miss Trubble commanding the monster attacks.</x:v>
       </x:c>
       <x:c r="F4" s="11" t="inlineStr">
         <x:is>
@@ -12109,10 +11955,8 @@
           <x:t xml:space="preserve">The Bugle exposes a citywide crime plan.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D5" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enforcers/Ox, Miss Trubble, Phantom, Foswell, Blackwell</x:t>
-        </x:is>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Enforcers/Ox, Mole Man, Phantom, Foswell, Blackwell</x:v>
       </x:c>
       <x:c r="E5" s="11" t="inlineStr">
         <x:is>
@@ -12231,10 +12075,8 @@
           <x:t xml:space="preserve">Magic, mind control, and dimensions overlap.</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fakir rhythm, Kotep relics, Infinata loop, Pardo acts, Vulcan heat</x:t>
-        </x:is>
+      <x:c r="D7" s="11" t="str">
+        <x:v>Fakir rhythm, Kotep relics, Infinata loop, Pardo acts, Reptilla rampage</x:v>
       </x:c>
       <x:c r="E7" s="11" t="inlineStr">
         <x:is>
@@ -15721,16 +15563,16 @@
         <x:v>Latest codebase</x:v>
       </x:c>
       <x:c r="B2" s="53" t="str">
-        <x:v>ASM67_2026_06_17c.zip</x:v>
+        <x:v>ASM67_2026_06_18a.zip + 18g chapter swap patch</x:v>
       </x:c>
       <x:c r="C2" s="53" t="str">
-        <x:v>Workbook audit updated 2026-06-17</x:v>
+        <x:v>Workbook updated 2026-06-18 for chapter roster changes</x:v>
       </x:c>
       <x:c r="D2" s="53" t="str">
-        <x:v>Build future patches from this zip.</x:v>
+        <x:v>Build future patches from the current ASM67_2026_06_18a base plus applied changed-file patches.</x:v>
       </x:c>
       <x:c r="E2" s="53" t="str">
-        <x:v>Confirm local code matches workbook.</x:v>
+        <x:v>Confirm local code has the 18g chapter swap patch applied.</x:v>
       </x:c>
       <x:c r="F2" s="40" t="n"/>
       <x:c r="G2" s="40" t="n"/>
@@ -15756,16 +15598,16 @@
         <x:v>Monsters chapter</x:v>
       </x:c>
       <x:c r="B3" s="77" t="str">
-        <x:v>Centaur/Cerberus/Cyclops/Reptilla/Mole Man designed/coded</x:v>
+        <x:v>Centaur/Cerberus/Cyclops/Vulcan/Miss Trubble designed/coded</x:v>
       </x:c>
       <x:c r="C3" s="77" t="str">
-        <x:v>Centaur/Cyclops/Cerberus are Here Comes Trubble; Reptilla is Conner's Reptiles; Mole Man is Molemen episode family.</x:v>
+        <x:v>Centaur/Cyclops/Cerberus/Vulcan/Miss Trubble are tied to Here Comes Trubble; Miss Trubble anchors the chapter wizard.</x:v>
       </x:c>
       <x:c r="D3" s="77" t="str">
-        <x:v>Keep playtesting lights, bookends, widgets, case file helpers.</x:v>
+        <x:v>Keep playtesting lights, bookends, widgets, case-file helpers, gate/VUK wizard-ready flow.</x:v>
       </x:c>
       <x:c r="E3" s="77" t="str">
-        <x:v>Playtest all five.</x:v>
+        <x:v>Playtest all five and design custom Trubble Unleashed rules.</x:v>
       </x:c>
       <x:c r="F3" s="40" t="n"/>
       <x:c r="G3" s="40" t="n"/>
@@ -15791,10 +15633,10 @@
         <x:v>Crime Wave chapter</x:v>
       </x:c>
       <x:c r="B4" s="53" t="str">
-        <x:v>Enforcers/Ox, Miss Trubble, Fifth Avenue Phantom, Frederick Foswell, Blackwell current</x:v>
+        <x:v>Enforcers/Ox, Mole Man, Fifth Avenue Phantom, Frederick Foswell, Blackwell current</x:v>
       </x:c>
       <x:c r="C4" s="53" t="str">
-        <x:v>Foswell corrected to King Pinned; Enforcers/Ox to Blueprint for Crime; Phantom to Fifth Avenue Phantom/Dark Terrors.</x:v>
+        <x:v>Mole Man moved into Crime Wave; Foswell corrected to King Pinned; Enforcers/Ox to Blueprint for Crime; Phantom to Fifth Avenue Phantom/Dark Terrors.</x:v>
       </x:c>
       <x:c r="D4" s="58" t="str">
         <x:v>Cumulative Crime Wave work should be preserved in latest code.</x:v>
@@ -15861,10 +15703,10 @@
         <x:v>Oddities/backups</x:v>
       </x:c>
       <x:c r="B6" s="53" t="str">
-        <x:v>Some rows are better as phases/themes</x:v>
+        <x:v>Some rows are better as phases/themes; Miss Trubble backup remains duplicate/promoted</x:v>
       </x:c>
       <x:c r="C6" s="53" t="str">
-        <x:v>Pod = Rollarama hazard; South Pole Natives = Neptune's Nose Cone setting; Miss Trubble backup duplicate.</x:v>
+        <x:v>Pod = Rollarama hazard; South Pole Natives = Neptune's Nose Cone setting; Miss Trubble backup duplicate/promoted to Monsters.</x:v>
       </x:c>
       <x:c r="D6" s="58" t="str">
         <x:v>Do not promote weak/theme rows until needed.</x:v>
@@ -18352,25 +18194,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="40" t="str">
-        <x:v>Reptilla</x:v>
+        <x:v>Vulcan</x:v>
       </x:c>
       <x:c r="C15" s="40" t="str">
-        <x:v>Conner's Reptiles</x:v>
+        <x:v>Here Comes Trubble</x:v>
       </x:c>
       <x:c r="D15" s="40" t="str">
-        <x:v>Verified</x:v>
+        <x:v>Corrected / verified</x:v>
       </x:c>
       <x:c r="E15" s="40" t="str">
-        <x:v>https://marvelanimated.fandom.com/wiki/Reptilla_(Spider-Man_(1967))</x:v>
+        <x:v>https://marvel.fandom.com/wiki/Spider-Man_(1967_animated_series)_Season_1_11B</x:v>
       </x:c>
       <x:c r="F15" s="40" t="str">
-        <x:v>Reptilla is the intelligent reptile/alligator creature from Conner's Reptiles.</x:v>
+        <x:v>Moved into Monsters; Vulcan appears in Here Comes Trubble as one of Miss Trubble's summoned figures.</x:v>
       </x:c>
       <x:c r="G15" s="40" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H15" s="40" t="str">
-        <x:v>Verified</x:v>
+        <x:v>Moved</x:v>
       </x:c>
       <x:c r="I15" s="40"/>
       <x:c r="J15" s="40"/>
@@ -18393,25 +18235,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="40" t="str">
-        <x:v>Mole Man</x:v>
+        <x:v>Miss Trubble</x:v>
       </x:c>
       <x:c r="C16" s="40" t="str">
-        <x:v>Menace from the Bottom of the World / Spider-Man Battles the Molemen</x:v>
+        <x:v>Here Comes Trubble</x:v>
       </x:c>
       <x:c r="D16" s="40" t="str">
-        <x:v>Verified</x:v>
+        <x:v>Corrected / verified</x:v>
       </x:c>
       <x:c r="E16" s="40" t="str">
-        <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
+        <x:v>https://marvel.fandom.com/wiki/Spider-Man_(1967_animated_series)_Season_1_11B</x:v>
       </x:c>
       <x:c r="F16" s="40" t="str">
-        <x:v>Molemen/Mole leader story family verified.</x:v>
+        <x:v>Moved into Monsters; Miss Trubble anchors the Trubble Unleashed mini-wizard.</x:v>
       </x:c>
       <x:c r="G16" s="40" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H16" s="40" t="str">
-        <x:v>Verified</x:v>
+        <x:v>Moved</x:v>
       </x:c>
       <x:c r="I16" s="40"/>
       <x:c r="J16" s="40"/>
@@ -18475,25 +18317,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="40" t="str">
-        <x:v>Miss Trubble</x:v>
+        <x:v>Mole Man</x:v>
       </x:c>
       <x:c r="C18" s="40" t="str">
-        <x:v>Here Comes Trubble</x:v>
+        <x:v>Menace from the Bottom of the World / Spider-Man Battles the Molemen</x:v>
       </x:c>
       <x:c r="D18" s="40" t="str">
-        <x:v>Corrected / verified</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="E18" s="40" t="str">
-        <x:v>https://marvel.fandom.com/wiki/Spider-Man_(1967_animated_series)_Season_1_11B</x:v>
+        <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
       </x:c>
       <x:c r="F18" s="40" t="str">
-        <x:v>Miss Trubble is the main antagonist of Here Comes Trubble.</x:v>
+        <x:v>Moved into Crime Wave; Molemen/Mole leader story family verified.</x:v>
       </x:c>
       <x:c r="G18" s="40" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H18" s="40" t="str">
-        <x:v>Corrected</x:v>
+        <x:v>Moved</x:v>
       </x:c>
       <x:c r="I18" s="40"/>
       <x:c r="J18" s="40"/>
@@ -19008,25 +18850,25 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="40" t="str">
-        <x:v>Vulcan</x:v>
+        <x:v>Reptilla</x:v>
       </x:c>
       <x:c r="C31" s="40" t="str">
-        <x:v>Here Comes Trubble</x:v>
+        <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="D31" s="40" t="str">
-        <x:v>Corrected / verified</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="E31" s="40" t="str">
-        <x:v>https://marvel.fandom.com/wiki/Spider-Man_(1967_animated_series)_Season_1_11B</x:v>
+        <x:v>https://marvelanimated.fandom.com/wiki/Reptilla_(Spider-Man_(1967))</x:v>
       </x:c>
       <x:c r="F31" s="40" t="str">
-        <x:v>Vulcan appears in Here Comes Trubble as one of Miss Trubble's summoned figures.</x:v>
+        <x:v>Moved into Mystic Menace; Reptilla is the intelligent reptile/alligator creature from Conner's Reptiles.</x:v>
       </x:c>
       <x:c r="G31" s="40" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H31" s="40" t="str">
-        <x:v>Corrected</x:v>
+        <x:v>Moved</x:v>
       </x:c>
       <x:c r="I31" s="40"/>
       <x:c r="J31" s="40"/>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R620ead94cdbc4de8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R01d47932221b49ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rb8b9b74541014010"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R79432deca8e44e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R5ffc64d6d5a5487d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R0f23334e01be442d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R436c49dfab8e45f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Ra025beeb449d4e48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rabb03f7ed7e04acf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R4e83b5fd9186414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3d0358e813db4d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R30b0596b39c6490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R4d85dc587d3748c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R10ab0a437ec64204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rd2e174fa22e84714"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R3a0fb56df5134868"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rfee91541f7274e1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R0d03cd605e6d49b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R8b813465bd794752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R0b6965da85da45a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4996,16 +4996,16 @@
         <x:v>2-ball MB</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>Chaos multiball: chase solid/flashing windows and saucer/shot opportunities.</x:v>
+        <x:v>Chaos multiball alternates between uncontrolled chaos and a calm saucer-held attack window.</x:v>
       </x:c>
       <x:c r="G7" t="str">
         <x:v>Ends when multiball ends, or when Goblin objectives complete if reached first.</x:v>
       </x:c>
       <x:c r="H7" t="str">
-        <x:v>Chaos multiball; windows alternate between solid/flashing scoring; banks goblin_bonus.</x:v>
+        <x:v>During chaos, STAR, pops, web targets, and drops reduce the Chaos Bonus. A saucer hold calms the mode and lights those shots for Goblin Jackpots. Jackpot starts at 100K, rises 50K per collect to 500K, and each collect also banks the same amount into Chaos Bonus.</x:v>
       </x:c>
       <x:c r="I7" s="31" t="str">
-        <x:v>Improved: persistent flashing/solid shot counts and stabilized bank status.</x:v>
+        <x:v>Redesigned: persistent Chaos Bonus, saucer-controlled calm windows, growing Goblin Jackpot, and no spinner scoring.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -5034,7 +5034,7 @@
         <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpots; spinner boosts multiplier.</x:v>
       </x:c>
       <x:c r="I8" s="31" t="str">
-        <x:v>Improved: persistent arm-lock, web-jackpot, and breakout progress.</x:v>
+        <x:v>Adjusted: spinner flashes when active, arm-release timer resets on new locks, obsolete jackpot widget removed.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -5063,7 +5063,7 @@
         <x:v>Hidden Super/clue mode; wrong shots score smaller and reduce value; clues narrow the target.</x:v>
       </x:c>
       <x:c r="I9" s="31" t="str">
-        <x:v>Improved: persistent remaining-shot count and current Super value.</x:v>
+        <x:v>Adjusted: non-clue shots now post a generic Mysterio callout event; recording still required.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5092,7 +5092,7 @@
         <x:v>Spinner builds Venom; upper exit stages timed drop-bank attack shots.</x:v>
       </x:c>
       <x:c r="I10" s="31" t="str">
-        <x:v>Improved: persistent Venom build, attempt count, exit choice, and staged target status.</x:v>
+        <x:v>Adjusted: exact roof-spinner objective, reusable reminder flag, and delayed Jackpot-to-next-objective pacing.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5121,7 +5121,7 @@
         <x:v>Heat-area multiball; left/right/pops build heat; maxed areas light saucer jackpots and add-a-ball opportunities.</x:v>
       </x:c>
       <x:c r="I11" s="31" t="str">
-        <x:v>Improved: persistent lit-saucer and collected-jackpot totals.</x:v>
+        <x:v>Adjusted: meaningful saucer/jackpot status, ordinary zone-hit scoring, and delayed BALL ADDED message.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3d0358e813db4d56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R30b0596b39c6490c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R4d85dc587d3748c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R10ab0a437ec64204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rd2e174fa22e84714"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R3a0fb56df5134868"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rfee91541f7274e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R0d03cd605e6d49b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R8b813465bd794752"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R0b6965da85da45a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R79263a3263a443b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R7773ea7c09cf46af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R380af374f4364f2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R654be13ca6c148de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rcffbde51bea14878"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Refbee5ac8b594f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R563b89de527e4658"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Ra5f8e8093ef44d59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R6fd19580c7444c7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra805365954c346a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4386,7 +4386,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G2" s="31" t="str">
-        <x:v>Implemented; needs continued playtest/polish.</x:v>
+        <x:v>Implemented; now includes active-area objective reminders, progress status, jackpot guidance, and victory-lap Super guidance.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4478,7 +4478,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4501,7 +4501,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G7" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4524,7 +4524,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G8" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4547,7 +4547,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G9" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4570,7 +4570,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G10" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -4593,7 +4593,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G11" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4616,7 +4616,7 @@
         <x:v>Separate final wizard; Kingpin remains a regular Chapter 4 villain.</x:v>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>Implemented structurally; playtest/polish later.</x:v>
+        <x:v>Implemented structurally; now includes active-area objective reminders, progress status, jackpot guidance, and victory-lap Super guidance.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5945,10 +5945,18 @@
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16"/>
-      <x:c r="B16"/>
-      <x:c r="C16"/>
-      <x:c r="D16"/>
+      <x:c r="A16" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Mode objective reminder and placeholder messaging audit</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Shared reminder flag hardened; wizard modes and placeholder villains now have basic objective/progress guidance.</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Implemented - needs test</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R79263a3263a443b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R7773ea7c09cf46af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R380af374f4364f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R654be13ca6c148de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rcffbde51bea14878"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Refbee5ac8b594f8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R563b89de527e4658"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Ra5f8e8093ef44d59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R6fd19580c7444c7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra805365954c346a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R51afdaf9214b453a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Ra145a9a4939e4052"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R27e4dd8bff4248af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R02d5a188367641c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R971018bbc0484af2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R6dfc2e6d1e264ca8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R4a2b45d84fef436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R9194e9cc56294d13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R10512689410f4419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R104066e9774c4d39"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4386,7 +4386,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G2" s="31" t="str">
-        <x:v>Implemented; now includes active-area objective reminders, progress status, jackpot guidance, and victory-lap Super guidance.</x:v>
+        <x:v>Implemented; needs continued playtest/polish.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4478,7 +4478,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4501,7 +4501,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G7" s="31" t="str">
-        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4524,7 +4524,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G8" s="31" t="str">
-        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4547,7 +4547,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G9" s="31" t="str">
-        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4570,7 +4570,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G10" s="31" t="str">
-        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -4593,7 +4593,7 @@
         <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
       </x:c>
       <x:c r="G11" s="31" t="str">
-        <x:v>Placeholder/simple wizard; now has basic objective reminder, hit/points status, and Jackpot messages; still needs full design.</x:v>
+        <x:v>Placeholder/simple wizard; needs full design.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4616,7 +4616,7 @@
         <x:v>Separate final wizard; Kingpin remains a regular Chapter 4 villain.</x:v>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>Implemented structurally; now includes active-area objective reminders, progress status, jackpot guidance, and victory-lap Super guidance.</x:v>
+        <x:v>Implemented structurally; playtest/polish later.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4996,16 +4996,16 @@
         <x:v>2-ball MB</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>Chaos multiball alternates between uncontrolled chaos and a calm saucer-held attack window.</x:v>
+        <x:v>Chaos multiball: chase solid/flashing windows and saucer/shot opportunities.</x:v>
       </x:c>
       <x:c r="G7" t="str">
         <x:v>Ends when multiball ends, or when Goblin objectives complete if reached first.</x:v>
       </x:c>
       <x:c r="H7" t="str">
-        <x:v>During chaos, STAR, pops, web targets, and drops reduce the Chaos Bonus. A saucer hold calms the mode and lights those shots for Goblin Jackpots. Jackpot starts at 100K, rises 50K per collect to 500K, and each collect also banks the same amount into Chaos Bonus.</x:v>
+        <x:v>Chaos multiball; windows alternate between solid/flashing scoring; banks goblin_bonus.</x:v>
       </x:c>
       <x:c r="I7" s="31" t="str">
-        <x:v>Redesigned: persistent Chaos Bonus, saucer-controlled calm windows, growing Goblin Jackpot, and no spinner scoring.</x:v>
+        <x:v>Improved: persistent flashing/solid shot counts and stabilized bank status.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -5034,7 +5034,7 @@
         <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpots; spinner boosts multiplier.</x:v>
       </x:c>
       <x:c r="I8" s="31" t="str">
-        <x:v>Adjusted: spinner flashes when active, arm-release timer resets on new locks, obsolete jackpot widget removed.</x:v>
+        <x:v>Improved: persistent arm-lock, web-jackpot, and breakout progress.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -5063,7 +5063,7 @@
         <x:v>Hidden Super/clue mode; wrong shots score smaller and reduce value; clues narrow the target.</x:v>
       </x:c>
       <x:c r="I9" s="31" t="str">
-        <x:v>Adjusted: non-clue shots now post a generic Mysterio callout event; recording still required.</x:v>
+        <x:v>Improved: persistent remaining-shot count and current Super value.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5092,7 +5092,7 @@
         <x:v>Spinner builds Venom; upper exit stages timed drop-bank attack shots.</x:v>
       </x:c>
       <x:c r="I10" s="31" t="str">
-        <x:v>Adjusted: exact roof-spinner objective, reusable reminder flag, and delayed Jackpot-to-next-objective pacing.</x:v>
+        <x:v>Improved: persistent Venom build, attempt count, exit choice, and staged target status.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5121,7 +5121,7 @@
         <x:v>Heat-area multiball; left/right/pops build heat; maxed areas light saucer jackpots and add-a-ball opportunities.</x:v>
       </x:c>
       <x:c r="I11" s="31" t="str">
-        <x:v>Adjusted: meaningful saucer/jackpot status, ordinary zone-hit scoring, and delayed BALL ADDED message.</x:v>
+        <x:v>Improved: persistent lit-saucer and collected-jackpot totals.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -5949,12 +5949,26 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>Mode objective reminder and placeholder messaging audit</x:v>
+        <x:v>Mystery instant villain qualification</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Shared reminder flag hardened; wizard modes and placeholder villains now have basic objective/progress guidance.</x:v>
+        <x:v>Mystery award fully qualifies all three villain-start saucers only when no villain/wizard/start flow is active and an unplayed chapter villain remains. Uses sm_objective_spotted on the voice bus.</x:v>
       </x:c>
       <x:c r="D16" t="str">
+        <x:v>Implemented - needs test</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Mystery immediate next villain</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Mystery award shows STARTING NEXT VILLAIN plus the villain name, plays sm_objective_spotted on the voice bus, waits 2 seconds, then starts the first unplayed villain.</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
         <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R51afdaf9214b453a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Ra145a9a4939e4052"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R27e4dd8bff4248af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R02d5a188367641c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R971018bbc0484af2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R6dfc2e6d1e264ca8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R4a2b45d84fef436d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R9194e9cc56294d13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R10512689410f4419"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R104066e9774c4d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R301a2d3c4aa24c18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rb4a9c5d0469040d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R1704807c2d294fe1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R921c5c2296264c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R23c16ff87bf84640"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R1775bfe0b3094214"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R5962fc067a6d4d17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R1e46bd8294614cca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R91331fac76314a80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra229a1d4d12b4b5a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5972,6 +5972,20 @@
         <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Villain music transition-track cleanup</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Reassigned Trubble Unleashed to motorcycle_circus; Fifth Avenue Phantom to waiting; Master Plan to fbi; Ice Monster to the_shadows; Nature Strikes Back to don_and_dewey. Selection/intro/summary tracks remain unchanged.</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Implemented - needs test</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="D2:D16">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R301a2d3c4aa24c18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rb4a9c5d0469040d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R1704807c2d294fe1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R921c5c2296264c81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R23c16ff87bf84640"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R1775bfe0b3094214"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R5962fc067a6d4d17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R1e46bd8294614cca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R91331fac76314a80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra229a1d4d12b4b5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R29f07465886e411d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R64c33406e0884199"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Re9dcdc7410474c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rcfdd75f3c2b04018"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R94bb59b431504d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Red4f86dabe0e440b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R5ee4fc0fe8e74535"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R2830971c099c4da8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Ra2924fee33b147f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rf4c99f4ce9154104"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1571,31 +1571,31 @@
         <x:v>Super Swami</x:v>
       </x:c>
       <x:c r="E25" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F25" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G25" t="str">
-        <x:v>Build-and-cash</x:v>
+        <x:v>Timed / urgency</x:v>
       </x:c>
       <x:c r="H25" t="str">
-        <x:v>Bonus-bank candidate</x:v>
+        <x:v>Area restoration</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>Landmark/objective shots</x:v>
+        <x:v>Six coordinate-based playfield regions</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>super_swami_bonus bank</x:v>
+        <x:v>Increasing restoration jackpots</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>Objective routing / disappearing values</x:v>
+        <x:v>40-second city blackout; 50 seconds with More Time</x:v>
       </x:c>
       <x:c r="L25" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>All 6 areas restored / timer expired / ball end</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>Chapter 5 banked-bonus role; should feel different from Fakir MB.</x:v>
+        <x:v>Simple Mystic Menace timed mode. Shot Assist spots one extra area; Safety Net starts ball save; More Jackpots adds a 500K VUK Blackout Jackpot.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1606,37 +1606,37 @@
         <x:v>Mystic Menace</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>frog_ghosts</x:v>
+        <x:v>infinata</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>Frog Ghosts</x:v>
+        <x:v>Infinata</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F26" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G26" t="str">
-        <x:v>Movement / chaos</x:v>
+        <x:v>Sequential area completion</x:v>
       </x:c>
       <x:c r="H26" t="str">
-        <x:v>Jumping target candidate</x:v>
+        <x:v>Pops, left drops, right drops, webs, upper targets</x:v>
       </x:c>
       <x:c r="I26" t="str">
-        <x:v>Pops + target groups</x:v>
+        <x:v>Rising area awards and timed saucer Super</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>Jumping jackpots / combo values</x:v>
+        <x:v>One green area at a time; 20-second Super timer</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>Moving target pressure</x:v>
+        <x:v>Saucer Super collected / timer expired / ball end</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>Goals or timer / ball end</x:v>
+        <x:v>Three areas required; optional fourth with More Jackpots</x:v>
       </x:c>
       <x:c r="M26" t="str">
-        <x:v>Should be the strange/chaotic movement mode in Mystic Menace.</x:v>
+        <x:v>Case files: 4th area, larger values, 30s Super timer, ball save, first hit awards two areas.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3473,10 +3473,10 @@
         <x:v>Super Swami</x:v>
       </x:c>
       <x:c r="G25" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H25" s="31" t="str">
-        <x:v>Chapter 5 bonus-bank candidate; uses super_swami_bonus naming.</x:v>
+        <x:v>40-second Restore New York mode. GI starts at 404040. Any valid switch in each of six monitor-coordinate regions restores that area permanently. Area awards start at 100K and rise 50K each; More Time gives 50 seconds and Bigger Jackpots starts at 200K.</x:v>
       </x:c>
       <x:c r="I25" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -3499,16 +3499,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="E26" s="31" t="str">
-        <x:v>frog_ghosts</x:v>
+        <x:v>infinata</x:v>
       </x:c>
       <x:c r="F26" s="31" t="str">
-        <x:v>Frog Ghosts</x:v>
+        <x:v>Infinata</x:v>
       </x:c>
       <x:c r="G26" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H26" s="31" t="str">
-        <x:v>Needs full Mystic Menace design.</x:v>
+        <x:v>One green creature area lights at a time. Complete three areas, then collect a timed Super Jackpot at any saucer. More Jackpots adds a fourth optional green area during the Super countdown.</x:v>
       </x:c>
       <x:c r="I26" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -5617,6 +5617,64 @@
         <x:v>Improved: persistent left/right drop progress and live spinner value.</x:v>
       </x:c>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B30" s="31" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="C30" s="31" t="str">
+        <x:v>super_swami</x:v>
+      </x:c>
+      <x:c r="D30" s="31" t="str">
+        <x:v>Super Swami</x:v>
+      </x:c>
+      <x:c r="E30" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F30" s="31" t="str">
+        <x:v>GI dims to 404040; hit any valid switch in each of six physical playfield regions to restore New York.</x:v>
+      </x:c>
+      <x:c r="G30" s="31" t="str">
+        <x:v>Ends when all six areas are restored, the timer expires, or the ball ends. With More Jackpots, a final 500K VUK collect is required.</x:v>
+      </x:c>
+      <x:c r="H30" s="31" t="str">
+        <x:v>Base timer 40s, or 50s with More Time. Area values are 100K–350K, or 200K–450K with Bigger Jackpots. Restored areas stay lit.</x:v>
+      </x:c>
+      <x:c r="I30" s="31" t="str">
+        <x:v>Implemented: live area progress, countdown, restoration messages, case-file helpers, drop resets, and saucer kickouts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B31" s="31" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="C31" s="31" t="str">
+        <x:v>infinata</x:v>
+      </x:c>
+      <x:c r="D31" s="31" t="str">
+        <x:v>Infinata</x:v>
+      </x:c>
+      <x:c r="E31" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F31" s="31" t="str">
+        <x:v>Clear one green creature area at a time. Areas are selected from pops, left drops, right drops, webs, and upper targets.</x:v>
+      </x:c>
+      <x:c r="G31" s="31" t="str">
+        <x:v>After three area completions, all three saucers light for a timed Super. Ends on Super collect, timer expiry, or ball end.</x:v>
+      </x:c>
+      <x:c r="H31" s="31" t="str">
+        <x:v>Area awards are 200K, 300K, 400K; Super is 1M. Bigger Jackpots raises values. More Time extends the Super from 20s to 30s.</x:v>
+      </x:c>
+      <x:c r="I31" s="31" t="str">
+        <x:v>More Jackpots adds a fourth optional green area during the Super countdown. Shot Assist makes the first valid hit award the active and next areas.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R29f07465886e411d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R64c33406e0884199"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Re9dcdc7410474c84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rcfdd75f3c2b04018"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R94bb59b431504d26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Red4f86dabe0e440b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R5ee4fc0fe8e74535"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R2830971c099c4da8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Ra2924fee33b147f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rf4c99f4ce9154104"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra6689fc2c1e54587"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rb4ff5d2bcb8943f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R416818b8ef554d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R4f8eaa3ee7c443e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R1aa7dc55db8146cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Ra069c3f268174b46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R35a5f93c6d08484a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Ra7738754269040c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R7a328d1046504cfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R2d4e645c7d364c5a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4383,7 +4383,7 @@
         <x:v>start_mode_sinister_surge</x:v>
       </x:c>
       <x:c r="F2" s="31" t="str">
-        <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G2" s="31" t="str">
         <x:v>Implemented; needs continued playtest/polish.</x:v>
@@ -4406,7 +4406,7 @@
         <x:v>start_mode_mastermind_trap</x:v>
       </x:c>
       <x:c r="F3" s="31" t="str">
-        <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G3" s="31" t="str">
         <x:v>Implemented; trap objectives and multiball scoring present.</x:v>
@@ -4429,7 +4429,7 @@
         <x:v>start_mode_trubble_unleashed</x:v>
       </x:c>
       <x:c r="F4" s="31" t="str">
-        <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G4" s="31" t="str">
         <x:v>Implemented; staged drops, saucers, VUK add-a-ball and multiball flow present.</x:v>
@@ -4452,7 +4452,7 @@
         <x:v>start_mode_master_plan</x:v>
       </x:c>
       <x:c r="F5" s="31" t="str">
-        <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G5" s="31" t="str">
         <x:v>Implemented; headlines/schemes/Daily Bugle super flow present.</x:v>
@@ -4475,10 +4475,10 @@
         <x:v>start_mode_fifth_dimension_curse</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
-        <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Implemented / needs playtest. Starts 3-ball multiball. Six GI zones stay bright 5s, flicker 3s, then dim independently. VUK jackpots score 500K–1.75M from active zones without clearing them. Upper targets score 100K + 25K per active zone, cycle purple pulse/solid/three flashes, and can award up to three add-a-balls after 3+ zone jackpots. Ends when down to one ball.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4498,7 +4498,7 @@
         <x:v>start_mode_mad_science_meltdown</x:v>
       </x:c>
       <x:c r="F7" s="31" t="str">
-        <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G7" s="31" t="str">
         <x:v>Placeholder/simple wizard; needs full design.</x:v>
@@ -4521,7 +4521,7 @@
         <x:v>start_mode_nature_strikes_back</x:v>
       </x:c>
       <x:c r="F8" s="31" t="str">
-        <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G8" s="31" t="str">
         <x:v>Placeholder/simple wizard; needs full design.</x:v>
@@ -4544,7 +4544,7 @@
         <x:v>start_mode_invasion_from_everywhere</x:v>
       </x:c>
       <x:c r="F9" s="31" t="str">
-        <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G9" s="31" t="str">
         <x:v>Placeholder/simple wizard; needs full design.</x:v>
@@ -4567,7 +4567,7 @@
         <x:v>start_mode_who_is_the_real_villain</x:v>
       </x:c>
       <x:c r="F10" s="31" t="str">
-        <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G10" s="31" t="str">
         <x:v>Placeholder/simple wizard; needs full design.</x:v>
@@ -4590,7 +4590,7 @@
         <x:v>start_mode_time_tossed_showdown</x:v>
       </x:c>
       <x:c r="F11" s="31" t="str">
-        <x:v>Uses chapter case-file total 0–25 for values; active case-file powers are not used.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G11" s="31" t="str">
         <x:v>Placeholder/simple wizard; needs full design.</x:v>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,16 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra6689fc2c1e54587"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rb4ff5d2bcb8943f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R416818b8ef554d3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R4f8eaa3ee7c443e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R1aa7dc55db8146cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Ra069c3f268174b46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R35a5f93c6d08484a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Ra7738754269040c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R7a328d1046504cfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R2d4e645c7d364c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcfb3f8d7777c43cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R35554b42ca7443e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R5cfa94fca5b84015"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Ra408324b33cd4462"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rb49ef4c19cf3431e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R02057c779bcc4c06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R0725a70b63f14561"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rc6f999d0eae245d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R9da81bbcfe2546f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R67e472f7faf94e8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rabd56236baea4926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R7c0a922369b54394"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -68,8 +70,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -106,6 +113,11 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -114,7 +126,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="54">
+  <x:cellXfs count="59">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -238,6 +250,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -477,10 +498,10 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="str">
-        <x:v>Latest codebase</x:v>
+        <x:v>Latest full codebase</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>asm67_2026_07_14_2pm.zip</x:v>
+        <x:v>ASM67_2026_07_23_11am.zip</x:v>
       </x:c>
       <x:c r="C3" s="14"/>
       <x:c r="D3" s="20" t="str">
@@ -495,7 +516,7 @@
         <x:v>Workbook update</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>2026-07-15 — Pardo coded, Lizard case-file behavior reworked, and The Fly Rooftop Swarm coded</x:v>
+        <x:v>2026-07-23 — Mystic Menace completed; Mad Science villains completed; Fifth Dimension Curse implemented; GI and player-variable audits documented</x:v>
       </x:c>
       <x:c r="C4" s="14"/>
       <x:c r="D4" s="10" t="str">
@@ -510,7 +531,7 @@
         <x:v>Chapter structure</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>10 chapters × 5 villains, plus chapter mini-wizards and Final Showdown</x:v>
+        <x:v>10 chapters × 5 villains, plus 10 chapter mini-wizards and Final Showdown</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -525,7 +546,7 @@
         <x:v>Progression model</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>Per-mode _state ints: 0 not played, 1 playing, 2 completed; *_mode_complete means done for progression</x:v>
+        <x:v>Per-mode *_state persists for progression; temporary gameplay state should remain inside each Python mode where possible</x:v>
       </x:c>
       <x:c r="C6" s="14"/>
       <x:c r="D6" s="10" t="str">
@@ -540,7 +561,7 @@
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>First 4 chapters are implemented and in playtest/polish; Fakir, Pardo, and The Fly are coded; Lizard case files reworked; remaining Chapters 5–10 are mostly placeholder/simple modes</x:v>
+        <x:v>Chapters 1–5 villains are implemented. Chapter 6 Mad Science villains are now implemented; Mad Science Meltdown still needs its full wizard design. Chapters 7–10 remain mostly placeholder/simple.</x:v>
       </x:c>
       <x:c r="C7" s="14"/>
       <x:c r="D7" s="10" t="str">
@@ -555,7 +576,7 @@
         <x:v>Recent major changes</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>Custom bonus sequence; chapter-select rescue; Fakir Ruby Heist coded; Pardo Hypnosis Reel coded; The Fly Rooftop Swarm coded; Lizard case-file rework; status/case-file widget fixes</x:v>
+        <x:v>Scarlet Sorcerer, Super Swami, Infinata, Fifth Dimension Curse, Dr. Magneto, Professor Pretoris, and Dr. Von Schlick completed; wizard jackpot Case File bonus standardized; GI/player-variable audits documented; rooftop gate now starts closed and opens immediately when a chapter wizard becomes ready.</x:v>
       </x:c>
       <x:c r="C8" s="14"/>
       <x:c r="D8" s="14"/>
@@ -1530,31 +1551,31 @@
         <x:v>Scarlet Sorcerer</x:v>
       </x:c>
       <x:c r="E24" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F24" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" t="str">
-        <x:v>Sequence / checklist</x:v>
+        <x:v>Sequence / timed reveal</x:v>
       </x:c>
       <x:c r="H24" t="str">
-        <x:v>Spell-chain candidate</x:v>
+        <x:v>Demon checklist</x:v>
       </x:c>
       <x:c r="I24" t="str">
-        <x:v>Upper/lower spell shots</x:v>
+        <x:v>Webs, drops, pops, VUK</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>Spell-chain Super</x:v>
+        <x:v>Rising Demon JPs + Scepter Super</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>Sequence pressure</x:v>
+        <x:v>Four demons appear every 4s; 20s Scepter timer</x:v>
       </x:c>
       <x:c r="L24" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>Super / timer / ball end</x:v>
       </x:c>
       <x:c r="M24" t="str">
-        <x:v>Should avoid hidden-correct-shot logic because Pardo owns that space.</x:v>
+        <x:v>Optional fifth demon with More Jackpots; strong short checklist role.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1583,19 +1604,19 @@
         <x:v>Area restoration</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>Six coordinate-based playfield regions</x:v>
+        <x:v>Six coordinate-based regions</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>Increasing restoration jackpots</x:v>
+        <x:v>Increasing restoration awards</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>40-second city blackout; 50 seconds with More Time</x:v>
+        <x:v>40s blackout / 50s More Time</x:v>
       </x:c>
       <x:c r="L25" t="str">
-        <x:v>All 6 areas restored / timer expired / ball end</x:v>
+        <x:v>Six restored / timer / ball end</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>Simple Mystic Menace timed mode. Shot Assist spots one extra area; Safety Net starts ball save; More Jackpots adds a 500K VUK Blackout Jackpot.</x:v>
+        <x:v>Simple region-restoration role with optional VUK Blackout Jackpot.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1621,22 +1642,22 @@
         <x:v>Sequential area completion</x:v>
       </x:c>
       <x:c r="H26" t="str">
-        <x:v>Pops, left drops, right drops, webs, upper targets</x:v>
+        <x:v>Green corruption areas</x:v>
       </x:c>
       <x:c r="I26" t="str">
-        <x:v>Rising area awards and timed saucer Super</x:v>
+        <x:v>Pops, drops, webs, upper targets, saucers</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>One green area at a time; 20-second Super timer</x:v>
+        <x:v>Rising areas + timed saucer Super</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>Saucer Super collected / timer expired / ball end</x:v>
+        <x:v>One area at a time; 20s Super</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>Three areas required; optional fourth with More Jackpots</x:v>
+        <x:v>Super / timer / ball end</x:v>
       </x:c>
       <x:c r="M26" t="str">
-        <x:v>Case files: 4th area, larger values, 30s Super timer, ball save, first hit awards two areas.</x:v>
+        <x:v>Three required areas; optional fourth with More Jackpots.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1694,31 +1715,31 @@
         <x:v>Dr. Magneto</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F28" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G28" t="str">
-        <x:v>Magnet/control candidate</x:v>
+        <x:v>Rooftop spinner sequence</x:v>
       </x:c>
       <x:c r="H28" t="str">
-        <x:v>Risk/reward choice</x:v>
+        <x:v>Magnetic sweep</x:v>
       </x:c>
       <x:c r="I28" t="str">
-        <x:v>Metal/target banks</x:v>
+        <x:v>Upper spinner + both banks</x:v>
       </x:c>
       <x:c r="J28" t="str">
-        <x:v>Magnetized jackpot build</x:v>
+        <x:v>50K spin + 50K staged drop + Supers</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>Shot pull/control disruption</x:v>
+        <x:v>Seven-stage sweep; 20s final shot</x:v>
       </x:c>
       <x:c r="L28" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>Super / timer / ball end</x:v>
       </x:c>
       <x:c r="M28" t="str">
-        <x:v>Candidate for physical-control/risk-reward mode.</x:v>
+        <x:v>Physical bank staging with retry on early roof exit.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1735,31 +1756,31 @@
         <x:v>Professor Pretoris</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F29" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>Timed creation candidate</x:v>
+        <x:v>Spinner build / timed final</x:v>
       </x:c>
       <x:c r="H29" t="str">
-        <x:v>Build-and-cash</x:v>
+        <x:v>Reactor flood</x:v>
       </x:c>
       <x:c r="I29" t="str">
-        <x:v>Lab shots / saucers</x:v>
+        <x:v>Eight GI bands + webs</x:v>
       </x:c>
       <x:c r="J29" t="str">
-        <x:v>Experiment value / Super</x:v>
+        <x:v>100K bands + timed Supers</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>Timer or escalating hazard</x:v>
+        <x:v>Eight spins; 20s center-web Super</x:v>
       </x:c>
       <x:c r="L29" t="str">
-        <x:v>Goals or timer / ball end</x:v>
+        <x:v>Super / timer / ball end</x:v>
       </x:c>
       <x:c r="M29" t="str">
-        <x:v>Candidate for timed lab experiment to balance Dumpty precision.</x:v>
+        <x:v>Strong theatrical red-to-blue GI progression.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1817,31 +1838,31 @@
         <x:v>Dr. Von Schlick</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" t="str">
-        <x:v>Sequence / gadget candidate</x:v>
+        <x:v>Moving shot / timed Super</x:v>
       </x:c>
       <x:c r="H31" t="str">
-        <x:v>Spinner or drops</x:v>
+        <x:v>Oil Pellet Chase</x:v>
       </x:c>
       <x:c r="I31" t="str">
-        <x:v>Gadget shots</x:v>
+        <x:v>Webs, drops, pops, VUK</x:v>
       </x:c>
       <x:c r="J31" t="str">
-        <x:v>Gadget multipliers</x:v>
+        <x:v>100K/150K pellets + 1M Super</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>Sequence pressure</x:v>
+        <x:v>4s moving shot; five pellets; 20s VUK</x:v>
       </x:c>
       <x:c r="L31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>Super / timer / ball end</x:v>
       </x:c>
       <x:c r="M31" t="str">
-        <x:v>Use as non-reveal, non-precision counterweight in the chapter.</x:v>
+        <x:v>Daily Bugle gate lockout and held-ball eight-band flood finale.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2663,6 +2684,622 @@
       <x:c r="M51" t="str">
         <x:v>Should combine prior chapter skills without becoming a generic checklist.</x:v>
       </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="56" t="str">
+        <x:v>Mode</x:v>
+      </x:c>
+      <x:c r="B1" s="56" t="str">
+        <x:v>Removed Player Vars</x:v>
+      </x:c>
+      <x:c r="C1" s="56" t="str">
+        <x:v>Persistent/Shared Vars Kept</x:v>
+      </x:c>
+      <x:c r="D1" s="56" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="E1" s="56"/>
+      <x:c r="F1" s="56"/>
+      <x:c r="G1" s="56"/>
+      <x:c r="H1" s="56"/>
+      <x:c r="I1" s="56"/>
+      <x:c r="J1" s="56"/>
+      <x:c r="K1" s="56"/>
+      <x:c r="L1" s="56"/>
+      <x:c r="M1" s="56"/>
+      <x:c r="N1" s="56"/>
+      <x:c r="O1" s="56"/>
+      <x:c r="P1" s="56"/>
+      <x:c r="Q1" s="56"/>
+      <x:c r="R1" s="56"/>
+      <x:c r="S1" s="56"/>
+      <x:c r="T1" s="56"/>
+      <x:c r="U1" s="56"/>
+      <x:c r="V1" s="56"/>
+      <x:c r="W1" s="56"/>
+      <x:c r="X1" s="56"/>
+      <x:c r="Y1" s="56"/>
+      <x:c r="Z1" s="56"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="str">
+        <x:v>Diana</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:v>diana_state; active_mode_* summary counters</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
+        <x:v>Temporary arrows, phase, timer, targets, hit counters, Safety Net use, and end bonus moved into Python.</x:v>
+      </x:c>
+      <x:c r="E2" s="14"/>
+      <x:c r="F2" s="14"/>
+      <x:c r="G2" s="14"/>
+      <x:c r="H2" s="14"/>
+      <x:c r="I2" s="14"/>
+      <x:c r="J2" s="14"/>
+      <x:c r="K2" s="14"/>
+      <x:c r="L2" s="14"/>
+      <x:c r="M2" s="14"/>
+      <x:c r="N2" s="14"/>
+      <x:c r="O2" s="14"/>
+      <x:c r="P2" s="14"/>
+      <x:c r="Q2" s="14"/>
+      <x:c r="R2" s="14"/>
+      <x:c r="S2" s="14"/>
+      <x:c r="T2" s="14"/>
+      <x:c r="U2" s="14"/>
+      <x:c r="V2" s="14"/>
+      <x:c r="W2" s="14"/>
+      <x:c r="X2" s="14"/>
+      <x:c r="Y2" s="14"/>
+      <x:c r="Z2" s="14"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>Super Swami</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:v>super_swami_state; super_swami_bonus; active_mode_*</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>Restored count, countdown, and next value moved into Python.</x:v>
+      </x:c>
+      <x:c r="E3" s="14"/>
+      <x:c r="F3" s="14"/>
+      <x:c r="G3" s="14"/>
+      <x:c r="H3" s="14"/>
+      <x:c r="I3" s="14"/>
+      <x:c r="J3" s="14"/>
+      <x:c r="K3" s="14"/>
+      <x:c r="L3" s="14"/>
+      <x:c r="M3" s="14"/>
+      <x:c r="N3" s="14"/>
+      <x:c r="O3" s="14"/>
+      <x:c r="P3" s="14"/>
+      <x:c r="Q3" s="14"/>
+      <x:c r="R3" s="14"/>
+      <x:c r="S3" s="14"/>
+      <x:c r="T3" s="14"/>
+      <x:c r="U3" s="14"/>
+      <x:c r="V3" s="14"/>
+      <x:c r="W3" s="14"/>
+      <x:c r="X3" s="14"/>
+      <x:c r="Y3" s="14"/>
+      <x:c r="Z3" s="14"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:v>fifth_dimension_curse_state; shared mini-wizard/active_mode counters</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>Zones, jackpots, target progress, add-a-ball state, and local Case File bonus moved into Python.</x:v>
+      </x:c>
+      <x:c r="E4" s="14"/>
+      <x:c r="F4" s="14"/>
+      <x:c r="G4" s="14"/>
+      <x:c r="H4" s="14"/>
+      <x:c r="I4" s="14"/>
+      <x:c r="J4" s="14"/>
+      <x:c r="K4" s="14"/>
+      <x:c r="L4" s="14"/>
+      <x:c r="M4" s="14"/>
+      <x:c r="N4" s="14"/>
+      <x:c r="O4" s="14"/>
+      <x:c r="P4" s="14"/>
+      <x:c r="Q4" s="14"/>
+      <x:c r="R4" s="14"/>
+      <x:c r="S4" s="14"/>
+      <x:c r="T4" s="14"/>
+      <x:c r="U4" s="14"/>
+      <x:c r="V4" s="14"/>
+      <x:c r="W4" s="14"/>
+      <x:c r="X4" s="14"/>
+      <x:c r="Y4" s="14"/>
+      <x:c r="Z4" s="14"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>Fakir</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="str">
+        <x:v>fakir_state; active_mode_*</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
+        <x:v>Correct/incorrect counters and obsolete round/value variables removed from global player vars.</x:v>
+      </x:c>
+      <x:c r="E5" s="14"/>
+      <x:c r="F5" s="14"/>
+      <x:c r="G5" s="14"/>
+      <x:c r="H5" s="14"/>
+      <x:c r="I5" s="14"/>
+      <x:c r="J5" s="14"/>
+      <x:c r="K5" s="14"/>
+      <x:c r="L5" s="14"/>
+      <x:c r="M5" s="14"/>
+      <x:c r="N5" s="14"/>
+      <x:c r="O5" s="14"/>
+      <x:c r="P5" s="14"/>
+      <x:c r="Q5" s="14"/>
+      <x:c r="R5" s="14"/>
+      <x:c r="S5" s="14"/>
+      <x:c r="T5" s="14"/>
+      <x:c r="U5" s="14"/>
+      <x:c r="V5" s="14"/>
+      <x:c r="W5" s="14"/>
+      <x:c r="X5" s="14"/>
+      <x:c r="Y5" s="14"/>
+      <x:c r="Z5" s="14"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="56" t="str">
+        <x:v>Chapter</x:v>
+      </x:c>
+      <x:c r="B1" s="56" t="str">
+        <x:v>Villains Coded</x:v>
+      </x:c>
+      <x:c r="C1" s="56" t="str">
+        <x:v>Villains Remaining</x:v>
+      </x:c>
+      <x:c r="D1" s="56" t="str">
+        <x:v>Mini-Wizard</x:v>
+      </x:c>
+      <x:c r="E1" s="56" t="str">
+        <x:v>Wizard Status</x:v>
+      </x:c>
+      <x:c r="F1" s="56"/>
+      <x:c r="G1" s="56"/>
+      <x:c r="H1" s="56"/>
+      <x:c r="I1" s="56"/>
+      <x:c r="J1" s="56"/>
+      <x:c r="K1" s="56"/>
+      <x:c r="L1" s="56"/>
+      <x:c r="M1" s="56"/>
+      <x:c r="N1" s="56"/>
+      <x:c r="O1" s="56"/>
+      <x:c r="P1" s="56"/>
+      <x:c r="Q1" s="56"/>
+      <x:c r="R1" s="56"/>
+      <x:c r="S1" s="56"/>
+      <x:c r="T1" s="56"/>
+      <x:c r="U1" s="56"/>
+      <x:c r="V1" s="56"/>
+      <x:c r="W1" s="56"/>
+      <x:c r="X1" s="56"/>
+      <x:c r="Y1" s="56"/>
+      <x:c r="Z1" s="56"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="str">
+        <x:v>Classic Rogues</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
+        <x:v>Sinister Surge</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="str">
+        <x:v>Implemented / needs playtest</x:v>
+      </x:c>
+      <x:c r="F2" s="14"/>
+      <x:c r="G2" s="14"/>
+      <x:c r="H2" s="14"/>
+      <x:c r="I2" s="14"/>
+      <x:c r="J2" s="14"/>
+      <x:c r="K2" s="14"/>
+      <x:c r="L2" s="14"/>
+      <x:c r="M2" s="14"/>
+      <x:c r="N2" s="14"/>
+      <x:c r="O2" s="14"/>
+      <x:c r="P2" s="14"/>
+      <x:c r="Q2" s="14"/>
+      <x:c r="R2" s="14"/>
+      <x:c r="S2" s="14"/>
+      <x:c r="T2" s="14"/>
+      <x:c r="U2" s="14"/>
+      <x:c r="V2" s="14"/>
+      <x:c r="W2" s="14"/>
+      <x:c r="X2" s="14"/>
+      <x:c r="Y2" s="14"/>
+      <x:c r="Z2" s="14"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>Masked Masterminds</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>Mastermind Trap</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>Implemented / needs playtest</x:v>
+      </x:c>
+      <x:c r="F3" s="14"/>
+      <x:c r="G3" s="14"/>
+      <x:c r="H3" s="14"/>
+      <x:c r="I3" s="14"/>
+      <x:c r="J3" s="14"/>
+      <x:c r="K3" s="14"/>
+      <x:c r="L3" s="14"/>
+      <x:c r="M3" s="14"/>
+      <x:c r="N3" s="14"/>
+      <x:c r="O3" s="14"/>
+      <x:c r="P3" s="14"/>
+      <x:c r="Q3" s="14"/>
+      <x:c r="R3" s="14"/>
+      <x:c r="S3" s="14"/>
+      <x:c r="T3" s="14"/>
+      <x:c r="U3" s="14"/>
+      <x:c r="V3" s="14"/>
+      <x:c r="W3" s="14"/>
+      <x:c r="X3" s="14"/>
+      <x:c r="Y3" s="14"/>
+      <x:c r="Z3" s="14"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14" t="str">
+        <x:v>Trubble's Monsters</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>Trubble Unleashed</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>Implemented / needs playtest</x:v>
+      </x:c>
+      <x:c r="F4" s="14"/>
+      <x:c r="G4" s="14"/>
+      <x:c r="H4" s="14"/>
+      <x:c r="I4" s="14"/>
+      <x:c r="J4" s="14"/>
+      <x:c r="K4" s="14"/>
+      <x:c r="L4" s="14"/>
+      <x:c r="M4" s="14"/>
+      <x:c r="N4" s="14"/>
+      <x:c r="O4" s="14"/>
+      <x:c r="P4" s="14"/>
+      <x:c r="Q4" s="14"/>
+      <x:c r="R4" s="14"/>
+      <x:c r="S4" s="14"/>
+      <x:c r="T4" s="14"/>
+      <x:c r="U4" s="14"/>
+      <x:c r="V4" s="14"/>
+      <x:c r="W4" s="14"/>
+      <x:c r="X4" s="14"/>
+      <x:c r="Y4" s="14"/>
+      <x:c r="Z4" s="14"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>Crime Wave</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
+        <x:v>The Plotter - Master Plan</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="str">
+        <x:v>Implemented / needs playtest</x:v>
+      </x:c>
+      <x:c r="F5" s="14"/>
+      <x:c r="G5" s="14"/>
+      <x:c r="H5" s="14"/>
+      <x:c r="I5" s="14"/>
+      <x:c r="J5" s="14"/>
+      <x:c r="K5" s="14"/>
+      <x:c r="L5" s="14"/>
+      <x:c r="M5" s="14"/>
+      <x:c r="N5" s="14"/>
+      <x:c r="O5" s="14"/>
+      <x:c r="P5" s="14"/>
+      <x:c r="Q5" s="14"/>
+      <x:c r="R5" s="14"/>
+      <x:c r="S5" s="14"/>
+      <x:c r="T5" s="14"/>
+      <x:c r="U5" s="14"/>
+      <x:c r="V5" s="14"/>
+      <x:c r="W5" s="14"/>
+      <x:c r="X5" s="14"/>
+      <x:c r="Y5" s="14"/>
+      <x:c r="Z5" s="14"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>Implemented / needs playtest</x:v>
+      </x:c>
+      <x:c r="F6" s="14"/>
+      <x:c r="G6" s="14"/>
+      <x:c r="H6" s="14"/>
+      <x:c r="I6" s="14"/>
+      <x:c r="J6" s="14"/>
+      <x:c r="K6" s="14"/>
+      <x:c r="L6" s="14"/>
+      <x:c r="M6" s="14"/>
+      <x:c r="N6" s="14"/>
+      <x:c r="O6" s="14"/>
+      <x:c r="P6" s="14"/>
+      <x:c r="Q6" s="14"/>
+      <x:c r="R6" s="14"/>
+      <x:c r="S6" s="14"/>
+      <x:c r="T6" s="14"/>
+      <x:c r="U6" s="14"/>
+      <x:c r="V6" s="14"/>
+      <x:c r="W6" s="14"/>
+      <x:c r="X6" s="14"/>
+      <x:c r="Y6" s="14"/>
+      <x:c r="Z6" s="14"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
+        <x:v>Mad Science Meltdown</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>Placeholder/simple — full design needed</x:v>
+      </x:c>
+      <x:c r="F7" s="14"/>
+      <x:c r="G7" s="14"/>
+      <x:c r="H7" s="14"/>
+      <x:c r="I7" s="14"/>
+      <x:c r="J7" s="14"/>
+      <x:c r="K7" s="14"/>
+      <x:c r="L7" s="14"/>
+      <x:c r="M7" s="14"/>
+      <x:c r="N7" s="14"/>
+      <x:c r="O7" s="14"/>
+      <x:c r="P7" s="14"/>
+      <x:c r="Q7" s="14"/>
+      <x:c r="R7" s="14"/>
+      <x:c r="S7" s="14"/>
+      <x:c r="T7" s="14"/>
+      <x:c r="U7" s="14"/>
+      <x:c r="V7" s="14"/>
+      <x:c r="W7" s="14"/>
+      <x:c r="X7" s="14"/>
+      <x:c r="Y7" s="14"/>
+      <x:c r="Z7" s="14"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>Nature Strikes Back</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>Placeholder/simple</x:v>
+      </x:c>
+      <x:c r="F8" s="14"/>
+      <x:c r="G8" s="14"/>
+      <x:c r="H8" s="14"/>
+      <x:c r="I8" s="14"/>
+      <x:c r="J8" s="14"/>
+      <x:c r="K8" s="14"/>
+      <x:c r="L8" s="14"/>
+      <x:c r="M8" s="14"/>
+      <x:c r="N8" s="14"/>
+      <x:c r="O8" s="14"/>
+      <x:c r="P8" s="14"/>
+      <x:c r="Q8" s="14"/>
+      <x:c r="R8" s="14"/>
+      <x:c r="S8" s="14"/>
+      <x:c r="T8" s="14"/>
+      <x:c r="U8" s="14"/>
+      <x:c r="V8" s="14"/>
+      <x:c r="W8" s="14"/>
+      <x:c r="X8" s="14"/>
+      <x:c r="Y8" s="14"/>
+      <x:c r="Z8" s="14"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
+        <x:v>Invasion from Everywhere</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>Placeholder/simple</x:v>
+      </x:c>
+      <x:c r="F9" s="14"/>
+      <x:c r="G9" s="14"/>
+      <x:c r="H9" s="14"/>
+      <x:c r="I9" s="14"/>
+      <x:c r="J9" s="14"/>
+      <x:c r="K9" s="14"/>
+      <x:c r="L9" s="14"/>
+      <x:c r="M9" s="14"/>
+      <x:c r="N9" s="14"/>
+      <x:c r="O9" s="14"/>
+      <x:c r="P9" s="14"/>
+      <x:c r="Q9" s="14"/>
+      <x:c r="R9" s="14"/>
+      <x:c r="S9" s="14"/>
+      <x:c r="T9" s="14"/>
+      <x:c r="U9" s="14"/>
+      <x:c r="V9" s="14"/>
+      <x:c r="W9" s="14"/>
+      <x:c r="X9" s="14"/>
+      <x:c r="Y9" s="14"/>
+      <x:c r="Z9" s="14"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>Placeholder/simple</x:v>
+      </x:c>
+      <x:c r="F10" s="14"/>
+      <x:c r="G10" s="14"/>
+      <x:c r="H10" s="14"/>
+      <x:c r="I10" s="14"/>
+      <x:c r="J10" s="14"/>
+      <x:c r="K10" s="14"/>
+      <x:c r="L10" s="14"/>
+      <x:c r="M10" s="14"/>
+      <x:c r="N10" s="14"/>
+      <x:c r="O10" s="14"/>
+      <x:c r="P10" s="14"/>
+      <x:c r="Q10" s="14"/>
+      <x:c r="R10" s="14"/>
+      <x:c r="S10" s="14"/>
+      <x:c r="T10" s="14"/>
+      <x:c r="U10" s="14"/>
+      <x:c r="V10" s="14"/>
+      <x:c r="W10" s="14"/>
+      <x:c r="X10" s="14"/>
+      <x:c r="Y10" s="14"/>
+      <x:c r="Z10" s="14"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>Placeholder/simple</x:v>
+      </x:c>
+      <x:c r="F11" s="14"/>
+      <x:c r="G11" s="14"/>
+      <x:c r="H11" s="14"/>
+      <x:c r="I11" s="14"/>
+      <x:c r="J11" s="14"/>
+      <x:c r="K11" s="14"/>
+      <x:c r="L11" s="14"/>
+      <x:c r="M11" s="14"/>
+      <x:c r="N11" s="14"/>
+      <x:c r="O11" s="14"/>
+      <x:c r="P11" s="14"/>
+      <x:c r="Q11" s="14"/>
+      <x:c r="R11" s="14"/>
+      <x:c r="S11" s="14"/>
+      <x:c r="T11" s="14"/>
+      <x:c r="U11" s="14"/>
+      <x:c r="V11" s="14"/>
+      <x:c r="W11" s="14"/>
+      <x:c r="X11" s="14"/>
+      <x:c r="Y11" s="14"/>
+      <x:c r="Z11" s="14"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3441,10 +4078,10 @@
         <x:v>Scarlet Sorcerer</x:v>
       </x:c>
       <x:c r="G24" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H24" s="31" t="str">
-        <x:v>Needs full Mystic Menace design.</x:v>
+        <x:v>Four unique demon shots appear one every 4 seconds and never relight. Demon JPs score 200K–350K; after four demons the gate opens for a 20-second 1M VUK Scepter Super. Case files add an optional fifth demon, larger values, 30 seconds, ball save, or timed Shot Assist.</x:v>
       </x:c>
       <x:c r="I24" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -3476,7 +4113,7 @@
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H25" s="31" t="str">
-        <x:v>40-second Restore New York mode. GI starts at 404040. Any valid switch in each of six monitor-coordinate regions restores that area permanently. Area awards start at 100K and rise 50K each; More Time gives 50 seconds and Bigger Jackpots starts at 200K.</x:v>
+        <x:v>Restore six coordinate-based GI regions before the 40-second timer expires. First-time restoration values rise 100K–350K; Bigger starts at 200K, More Time gives 50 seconds, More Jackpots adds a 500K VUK Blackout Jackpot, Safety Net starts ball save, and Shot Assist spots an extra region.</x:v>
       </x:c>
       <x:c r="I25" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -3508,7 +4145,7 @@
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H26" s="31" t="str">
-        <x:v>One green creature area lights at a time. Complete three areas, then collect a timed Super Jackpot at any saucer. More Jackpots adds a fourth optional green area during the Super countdown.</x:v>
+        <x:v>One green creature area lights at a time from pops, left drops, right drops, webs, and upper targets. Complete three to light all saucers for a 20-second 1M Super. More Jackpots adds a fourth optional area, Bigger raises values, More Time gives 30 seconds, Safety Net adds ball save, and Shot Assist awards the first two areas.</x:v>
       </x:c>
       <x:c r="I26" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -3569,10 +4206,10 @@
         <x:v>Dr. Magneto</x:v>
       </x:c>
       <x:c r="G28" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H28" s="31" t="str">
-        <x:v>Needs full Mad Science design.</x:v>
+        <x:v>Rooftop magnetic sweep: upper entrance resets both banks; each upper spin scores 50K and knocks down the next left-to-right target for another 50K. After seven steps only right drop 5 remains for a timed 1M Super. More Jackpots stages left drop 1 for a 500K Magnetic Flux Super.</x:v>
       </x:c>
       <x:c r="I28" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -3601,10 +4238,10 @@
         <x:v>Professor Pretoris</x:v>
       </x:c>
       <x:c r="G29" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H29" s="31" t="str">
-        <x:v>Needs full Mad Science design.</x:v>
+        <x:v>Reactor Flood: GI starts red in eight horizontal bands. Each web-spinner hit turns the next band blue from bottom to top for 100K. After eight bands, center web lights for a 20-second 1M Super; More Jackpots adds a 10-second left-web Overflow Super.</x:v>
       </x:c>
       <x:c r="I29" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -3665,10 +4302,10 @@
         <x:v>Dr. Von Schlick</x:v>
       </x:c>
       <x:c r="G31" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H31" s="31" t="str">
-        <x:v>Needs full Mad Science design.</x:v>
+        <x:v>Oil Pellet Chase: red GI and one green shot sweep left web, left drops, left pop, center web, right pop, and right drops, reversing every 4 seconds. Five pellets open the gate and light a timed VUK Super; the held-ball finish floods eight GI bands blue before awarding 1M.</x:v>
       </x:c>
       <x:c r="I31" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -4383,7 +5020,7 @@
         <x:v>start_mode_sinister_surge</x:v>
       </x:c>
       <x:c r="F2" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G2" s="31" t="str">
         <x:v>Implemented; needs continued playtest/polish.</x:v>
@@ -4406,7 +5043,7 @@
         <x:v>start_mode_mastermind_trap</x:v>
       </x:c>
       <x:c r="F3" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G3" s="31" t="str">
         <x:v>Implemented; trap objectives and multiball scoring present.</x:v>
@@ -4429,7 +5066,7 @@
         <x:v>start_mode_trubble_unleashed</x:v>
       </x:c>
       <x:c r="F4" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G4" s="31" t="str">
         <x:v>Implemented; staged drops, saucers, VUK add-a-ball and multiball flow present.</x:v>
@@ -4452,7 +5089,7 @@
         <x:v>start_mode_master_plan</x:v>
       </x:c>
       <x:c r="F5" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G5" s="31" t="str">
         <x:v>Implemented; headlines/schemes/Daily Bugle super flow present.</x:v>
@@ -4475,10 +5112,10 @@
         <x:v>start_mode_fifth_dimension_curse</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Implemented / needs playtest. Starts 3-ball multiball. Six GI zones stay bright 5s, flicker 3s, then dim independently. VUK jackpots score 500K–1.75M from active zones without clearing them. Upper targets score 100K + 25K per active zone, cycle purple pulse/solid/three flashes, and can award up to three add-a-balls after 3+ zone jackpots. Ends when down to one ball.</x:v>
+        <x:v>Implemented / needs playtest. Starts 3-ball multiball. Six GI zones stay bright 5s, flicker 3s, then dim independently. VUK jackpots score 500K–1.75M plus the chapter Case File bonus without clearing zones. Upper targets score 100K + 25K per active zone, pulse purple when unhit, turn solid when hit, flash three times on completion, and can award up to three add-a-balls after 3+ zone jackpots. Ends when down to one ball.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4498,7 +5135,7 @@
         <x:v>start_mode_mad_science_meltdown</x:v>
       </x:c>
       <x:c r="F7" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G7" s="31" t="str">
         <x:v>Placeholder/simple wizard; needs full design.</x:v>
@@ -4521,7 +5158,7 @@
         <x:v>start_mode_nature_strikes_back</x:v>
       </x:c>
       <x:c r="F8" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G8" s="31" t="str">
         <x:v>Placeholder/simple wizard; needs full design.</x:v>
@@ -4544,7 +5181,7 @@
         <x:v>start_mode_invasion_from_everywhere</x:v>
       </x:c>
       <x:c r="F9" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G9" s="31" t="str">
         <x:v>Placeholder/simple wizard; needs full design.</x:v>
@@ -4567,7 +5204,7 @@
         <x:v>start_mode_who_is_the_real_villain</x:v>
       </x:c>
       <x:c r="F10" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G10" s="31" t="str">
         <x:v>Placeholder/simple wizard; needs full design.</x:v>
@@ -4590,7 +5227,7 @@
         <x:v>start_mode_time_tossed_showdown</x:v>
       </x:c>
       <x:c r="F11" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, target, spinner, progress, trap-completion, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G11" s="31" t="str">
         <x:v>Placeholder/simple wizard; needs full design.</x:v>
@@ -5617,6 +6254,35 @@
         <x:v>Improved: persistent left/right drop progress and live spinner value.</x:v>
       </x:c>
     </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>scarlet_sorcerer</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Scarlet Sorcerer</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>Destroy four unique demon shots that appear over time; shots never relight.</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>After four demons, collect the timed VUK Scepter Super. Ends on Super, timer expiry, or ball end.</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>Demon JPs 200K–350K; 20-second 1M Super. Bigger gives 300K–450K and 1.5M.</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>More Jackpots adds optional 500K fifth demon; More Time 30s; Safety Net ball save; Shot Assist introduces and destroys the next scheduled demon.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="30">
       <x:c r="A30" s="31" t="n">
         <x:v>5</x:v>
@@ -5634,16 +6300,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F30" s="31" t="str">
-        <x:v>GI dims to 404040; hit any valid switch in each of six physical playfield regions to restore New York.</x:v>
+        <x:v>GI dims to 404040; hit a valid switch in each of six physical playfield regions to restore New York.</x:v>
       </x:c>
       <x:c r="G30" s="31" t="str">
-        <x:v>Ends when all six areas are restored, the timer expires, or the ball ends. With More Jackpots, a final 500K VUK collect is required.</x:v>
+        <x:v>Ends when all six areas are restored, the timer expires, or ball end. More Jackpots adds a final VUK collect.</x:v>
       </x:c>
       <x:c r="H30" s="31" t="str">
-        <x:v>Base timer 40s, or 50s with More Time. Area values are 100K–350K, or 200K–450K with Bigger Jackpots. Restored areas stay lit.</x:v>
+        <x:v>40s base / 50s More Time. Area values 100K–350K, or 200K–450K with Bigger.</x:v>
       </x:c>
       <x:c r="I30" s="31" t="str">
-        <x:v>Implemented: live area progress, countdown, restoration messages, case-file helpers, drop resets, and saucer kickouts.</x:v>
+        <x:v>Restored regions remain lit. Safety Net starts ball save; Shot Assist spots one additional unrestored region.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -5663,17 +6329,115 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F31" s="31" t="str">
-        <x:v>Clear one green creature area at a time. Areas are selected from pops, left drops, right drops, webs, and upper targets.</x:v>
+        <x:v>Clear one green creature area at a time from pops, drops, webs, and upper targets.</x:v>
       </x:c>
       <x:c r="G31" s="31" t="str">
-        <x:v>After three area completions, all three saucers light for a timed Super. Ends on Super collect, timer expiry, or ball end.</x:v>
+        <x:v>After three areas, all saucers light for a timed Super. Ends on collect, timer expiry, or ball end.</x:v>
       </x:c>
       <x:c r="H31" s="31" t="str">
-        <x:v>Area awards are 200K, 300K, 400K; Super is 1M. Bigger Jackpots raises values. More Time extends the Super from 20s to 30s.</x:v>
+        <x:v>Area awards 200K, 300K, 400K; Super 1M. Bigger increases values; More Time makes the Super 30s.</x:v>
       </x:c>
       <x:c r="I31" s="31" t="str">
-        <x:v>More Jackpots adds a fourth optional green area during the Super countdown. Shot Assist makes the first valid hit award the active and next areas.</x:v>
-      </x:c>
+        <x:v>More Jackpots adds an optional fourth area during the Super; Safety Net ball save; Shot Assist awards the active and next areas.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>dr_magneto</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Dr. Magneto</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Reach the roof and spin through left drops 1–3 then right drops 1–4, leaving right drop 5 standing.</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Hit right drop 5 within 20 seconds. Early rooftop exit before staging resets both banks.</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Each spin 50K plus 50K per staged drop; main Super 1M or 1.5M with Bigger.</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>More Jackpots stages left drop 1 for a 500K Flux Super; More Time 30s; Safety Net at main Super; first spin drops two targets with Shot Assist.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>professor_pretoris</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>Professor Pretoris</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>All GI starts red; eight horizontal bands flood blue bottom-to-top, one per web-spinner hit.</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>After all eight are blue, hit center web within 20 seconds. Ends on Super, timer expiry, or ball end.</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>Each converted band 100K. Main Super 1M or 1.5M with Bigger.</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>More Jackpots adds a 10-second 500K left-web Overflow Super; More Time 30s; Safety Net at Super; first spin floods two bands with Shot Assist.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>dr_von_schlick</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>Dr. Von Schlick</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>Follow one green moving shot across left web, left drops, left pop, center web, right pop, and right drops, reversing every 4 seconds.</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>Five pellets open the gate and light the VUK for 20 seconds. VUK starts the held-ball eight-band blue flood and awards 1M at completion.</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>Pellets 100K or 150K with Bigger. Wrong shots score only normal game points.</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>More Jackpots allows two optional pellets after qualification; More Time 30s; Safety Net at Super; Shot Assist makes first pellet count twice. Daily Bugle A+B cannot open the gate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="31"/>
+      <x:c r="B35" s="31"/>
+      <x:c r="C35" s="31"/>
+      <x:c r="D35" s="31"/>
+      <x:c r="E35" s="31"/>
+      <x:c r="F35" s="31"/>
+      <x:c r="G35" s="31"/>
+      <x:c r="H35" s="31"/>
+      <x:c r="I35" s="31"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5775,6 +6539,17 @@
       </x:c>
       <x:c r="C8" s="31" t="str">
         <x:v>Wizard completion uses controlled drain/ball-save rescue to reach shooter lane without ending the ball normally.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="31" t="str">
+        <x:v>Wizard rooftop gate</x:v>
+      </x:c>
+      <x:c r="B9" s="31" t="str">
+        <x:v>The physical rooftop gate is explicitly closed at game start. When chapter_mini_wizard_ready becomes true, villain_progression immediately pulses rooftop_diverter_open; a drop-target hit is not required and qualifying drops are ignored while the wizard is ready.</x:v>
+      </x:c>
+      <x:c r="C9" s="31" t="str">
+        <x:v>Implemented 2026-07-23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5971,7 +6746,7 @@
         <x:v>Update docs for chapter select, wizard transitions, bonus, lighting, ball save, mode behavior.</x:v>
       </x:c>
       <x:c r="D13" s="45" t="str">
-        <x:v>Open</x:v>
+        <x:v>In progress — workbook refreshed through wizard gate behavior on 2026-07-23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="38" customHeight="1">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcfb3f8d7777c43cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R35554b42ca7443e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R5cfa94fca5b84015"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Ra408324b33cd4462"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rb49ef4c19cf3431e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R02057c779bcc4c06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R0725a70b63f14561"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rc6f999d0eae245d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R9da81bbcfe2546f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R67e472f7faf94e8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rabd56236baea4926"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R7c0a922369b54394"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rede25178088c4ca3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R7cc381b0348e4468"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Re537ee9272804efd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R8c14b1da4ffd47a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Ra6f0daa3e4104cab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R4feab012ba7a4482"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R6afeb09425a54dc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R596f224eacad48cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R770924cc95584171"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R812db085eae3427e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rcd15c5b004ef49c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R45c5630ab4ed4acc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -126,7 +126,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="59">
+  <x:cellXfs count="60">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -259,6 +259,9 @@
     <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -490,93 +493,93 @@
       <x:c r="E1" s="38"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="14"/>
-      <x:c r="B2" s="14"/>
+      <x:c r="A2" s="14" t="str">
+        <x:v>Project status</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>Danger Lurks is Chapter 5; former Chapters 5–10 are now Chapters 6–11.</x:v>
+      </x:c>
       <x:c r="C2" s="14"/>
-      <x:c r="D2" s="14"/>
-      <x:c r="E2" s="14"/>
+      <x:c r="D2" s="14" t="str">
+        <x:v>Chapters</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="str">
-        <x:v>Latest full codebase</x:v>
+        <x:v>Chapter structure</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>ASM67_2026_07_23_11am.zip</x:v>
+        <x:v>11 chapters × 5 villains, plus 11 chapter mini-wizards and Final Showdown.</x:v>
       </x:c>
       <x:c r="C3" s="14"/>
       <x:c r="D3" s="20" t="str">
-        <x:v>Metric</x:v>
-      </x:c>
-      <x:c r="E3" s="20" t="str">
-        <x:v>Value</x:v>
+        <x:v>Villain slots</x:v>
+      </x:c>
+      <x:c r="E3" s="20" t="n">
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="str">
-        <x:v>Workbook update</x:v>
+        <x:v>Progression model</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>2026-07-23 — Mystic Menace completed; Mad Science villains completed; Fifth Dimension Curse implemented; GI and player-variable audits documented</x:v>
+        <x:v>Per-mode *_state persists for progression; temporary gameplay values remain in Python or shared display variables.</x:v>
       </x:c>
       <x:c r="C4" s="14"/>
       <x:c r="D4" s="10" t="str">
-        <x:v>Chapters</x:v>
+        <x:v>Mini-wizards</x:v>
       </x:c>
       <x:c r="E4" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="str">
-        <x:v>Chapter structure</x:v>
+        <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>10 chapters × 5 villains, plus 10 chapter mini-wizards and Final Showdown</x:v>
+        <x:v>Danger Lurks has five playable placeholder villain modes, Fiddler Ransom is wired as its persistent bonus, and The Web Tightens is a working placeholder mini-wizard.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
-        <x:v>Villain slots</x:v>
+        <x:v>Final wizard</x:v>
       </x:c>
       <x:c r="E5" s="14" t="n">
-        <x:v>50</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
-        <x:v>Progression model</x:v>
+        <x:v>Chapter 4 structure</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>Per-mode *_state persists for progression; temporary gameplay state should remain inside each Python mode where possible</x:v>
+        <x:v>The Plotter replaces Kingpin as a regular villain. Crime Wave is the new multiball chapter wizard.</x:v>
       </x:c>
       <x:c r="C6" s="14"/>
-      <x:c r="D6" s="10" t="str">
-        <x:v>Mini-wizards</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="D6" s="10"/>
+      <x:c r="E6" s="14"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
-        <x:v>Current focus</x:v>
+        <x:v>Crime Wave rules</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>Chapters 1–5 villains are implemented. Chapter 6 Mad Science villains are now implemented; Mad Science Meltdown still needs its full wizard design. Chapters 7–10 remain mostly placeholder/simple.</x:v>
+        <x:v>Five independently timed villain areas; gate opens at 3+ lit and closes at 1 or 0; upper exits collect jackpots without clearing areas.</x:v>
       </x:c>
       <x:c r="C7" s="14"/>
-      <x:c r="D7" s="10" t="str">
-        <x:v>Final wizard</x:v>
-      </x:c>
-      <x:c r="E7" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="D7" s="10"/>
+      <x:c r="E7" s="14"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
-        <x:v>Recent major changes</x:v>
+        <x:v>Final wizard</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>Scarlet Sorcerer, Super Swami, Infinata, Fifth Dimension Curse, Dr. Magneto, Professor Pretoris, and Dr. Von Schlick completed; wizard jackpot Case File bonus standardized; GI/player-variable audits documented; rooftop gate now starts closed and opens immediately when a chapter wizard becomes ready.</x:v>
+        <x:v>Kingpin is the final wizard identity after all 11 chapter wizards.</x:v>
       </x:c>
       <x:c r="C8" s="14"/>
       <x:c r="D8" s="14"/>
@@ -595,2094 +598,2299 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="str">
+      <x:c r="A1" s="31" t="str">
         <x:v>Chapter #</x:v>
       </x:c>
-      <x:c r="B1" t="str">
+      <x:c r="B1" s="31" t="str">
         <x:v>Chapter</x:v>
       </x:c>
-      <x:c r="C1" t="str">
+      <x:c r="C1" s="31" t="str">
         <x:v>Mode Key</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="D1" s="31" t="str">
         <x:v>Mode Name</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="E1" s="31" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="F1" s="31" t="str">
         <x:v>Number of Balls</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="G1" s="31" t="str">
         <x:v>Primary Type</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="H1" s="31" t="str">
         <x:v>Secondary Type</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="I1" s="31" t="str">
         <x:v>Main Area</x:v>
       </x:c>
-      <x:c r="J1" t="str">
+      <x:c r="J1" s="31" t="str">
         <x:v>Scoring Hook</x:v>
       </x:c>
-      <x:c r="K1" t="str">
+      <x:c r="K1" s="31" t="str">
         <x:v>Risk / Pressure</x:v>
       </x:c>
-      <x:c r="L1" t="str">
+      <x:c r="L1" s="31" t="str">
         <x:v>End Condition</x:v>
       </x:c>
-      <x:c r="M1" t="str">
+      <x:c r="M1" s="31" t="str">
         <x:v>Balance Notes</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
+      <x:c r="A2" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="31" t="str">
         <x:v>Classic Rogues</x:v>
       </x:c>
-      <x:c r="C2" t="str">
+      <x:c r="C2" s="31" t="str">
         <x:v>rhino</x:v>
       </x:c>
-      <x:c r="D2" t="str">
+      <x:c r="D2" s="31" t="str">
         <x:v>Rhino</x:v>
       </x:c>
-      <x:c r="E2" t="str">
+      <x:c r="E2" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F2" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
+      <x:c r="F2" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="31" t="str">
         <x:v>Build-and-cash</x:v>
       </x:c>
-      <x:c r="H2" t="str">
+      <x:c r="H2" s="31" t="str">
         <x:v>Escalation</x:v>
       </x:c>
-      <x:c r="I2" t="str">
+      <x:c r="I2" s="31" t="str">
         <x:v>Pops + B/qualified shots</x:v>
       </x:c>
-      <x:c r="J2" t="str">
+      <x:c r="J2" s="31" t="str">
         <x:v>Growing jackpots</x:v>
       </x:c>
-      <x:c r="K2" t="str">
+      <x:c r="K2" s="31" t="str">
         <x:v>Rage-stage escalation</x:v>
       </x:c>
-      <x:c r="L2" t="str">
+      <x:c r="L2" s="31" t="str">
         <x:v>Goals completed / ball end</x:v>
       </x:c>
-      <x:c r="M2" t="str">
+      <x:c r="M2" s="31" t="str">
         <x:v>Chapter 1 build-and-cash anchor; good contrast with Lizard urgency and Electro sequence.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
+      <x:c r="A3" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B3" s="31" t="str">
         <x:v>Classic Rogues</x:v>
       </x:c>
-      <x:c r="C3" t="str">
+      <x:c r="C3" s="31" t="str">
         <x:v>sandman</x:v>
       </x:c>
-      <x:c r="D3" t="str">
+      <x:c r="D3" s="31" t="str">
         <x:v>Sandman</x:v>
       </x:c>
-      <x:c r="E3" t="str">
+      <x:c r="E3" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G3" t="str">
+      <x:c r="F3" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G3" s="31" t="str">
         <x:v>Precision</x:v>
       </x:c>
-      <x:c r="H3" t="str">
+      <x:c r="H3" s="31" t="str">
         <x:v>Chase / moving target</x:v>
       </x:c>
-      <x:c r="I3" t="str">
+      <x:c r="I3" s="31" t="str">
         <x:v>Right drop bank</x:v>
       </x:c>
-      <x:c r="J3" t="str">
+      <x:c r="J3" s="31" t="str">
         <x:v>Targeted jackpots</x:v>
       </x:c>
-      <x:c r="K3" t="str">
+      <x:c r="K3" s="31" t="str">
         <x:v>Shot accuracy</x:v>
       </x:c>
-      <x:c r="L3" t="str">
+      <x:c r="L3" s="31" t="str">
         <x:v>Goals completed / ball end</x:v>
       </x:c>
-      <x:c r="M3" t="str">
+      <x:c r="M3" s="31" t="str">
         <x:v>Drop-bank precision role; avoids being another broad whole-playfield mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
+      <x:c r="A4" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="31" t="str">
         <x:v>Classic Rogues</x:v>
       </x:c>
-      <x:c r="C4" t="str">
+      <x:c r="C4" s="31" t="str">
         <x:v>vulture</x:v>
       </x:c>
-      <x:c r="D4" t="str">
+      <x:c r="D4" s="31" t="str">
         <x:v>Vulture</x:v>
       </x:c>
-      <x:c r="E4" t="str">
+      <x:c r="E4" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F4" t="str">
+      <x:c r="F4" s="31" t="str">
         <x:v>1; add-a-ball possible</x:v>
       </x:c>
-      <x:c r="G4" t="str">
+      <x:c r="G4" s="31" t="str">
         <x:v>Upper playfield</x:v>
       </x:c>
-      <x:c r="H4" t="str">
+      <x:c r="H4" s="31" t="str">
         <x:v>Spinner build</x:v>
       </x:c>
-      <x:c r="I4" t="str">
+      <x:c r="I4" s="31" t="str">
         <x:v>Upper playfield + spinner</x:v>
       </x:c>
-      <x:c r="J4" t="str">
+      <x:c r="J4" s="31" t="str">
         <x:v>Spinner-scaled value / add-a-ball</x:v>
       </x:c>
-      <x:c r="K4" t="str">
+      <x:c r="K4" s="31" t="str">
         <x:v>Upper control</x:v>
       </x:c>
-      <x:c r="L4" t="str">
+      <x:c r="L4" s="31" t="str">
         <x:v>Goals completed / ball end</x:v>
       </x:c>
-      <x:c r="M4" t="str">
+      <x:c r="M4" s="31" t="str">
         <x:v>Upper-playfield/spinner role for the chapter.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B5" t="str">
+      <x:c r="A5" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="31" t="str">
         <x:v>Classic Rogues</x:v>
       </x:c>
-      <x:c r="C5" t="str">
+      <x:c r="C5" s="31" t="str">
         <x:v>lizard</x:v>
       </x:c>
-      <x:c r="D5" t="str">
+      <x:c r="D5" s="31" t="str">
         <x:v>Lizard</x:v>
       </x:c>
-      <x:c r="E5" t="str">
+      <x:c r="E5" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F5" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G5" t="str">
+      <x:c r="F5" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G5" s="31" t="str">
         <x:v>Timed delivery</x:v>
       </x:c>
-      <x:c r="H5" t="str">
+      <x:c r="H5" s="31" t="str">
         <x:v>Draining value</x:v>
       </x:c>
-      <x:c r="I5" t="str">
+      <x:c r="I5" s="31" t="str">
         <x:v>STAR + web shots</x:v>
       </x:c>
-      <x:c r="J5" t="str">
+      <x:c r="J5" s="31" t="str">
         <x:v>Draining serum value</x:v>
       </x:c>
-      <x:c r="K5" t="str">
+      <x:c r="K5" s="31" t="str">
         <x:v>Value drain / shot routing</x:v>
       </x:c>
-      <x:c r="L5" t="str">
+      <x:c r="L5" s="31" t="str">
         <x:v>Deliveries completed / ball end</x:v>
       </x:c>
-      <x:c r="M5" t="str">
+      <x:c r="M5" s="31" t="str">
         <x:v>Urgency mode; case files now support the core loop instead of bypassing it.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
+      <x:c r="A6" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" s="31" t="str">
         <x:v>Classic Rogues</x:v>
       </x:c>
-      <x:c r="C6" t="str">
+      <x:c r="C6" s="31" t="str">
         <x:v>electro</x:v>
       </x:c>
-      <x:c r="D6" t="str">
+      <x:c r="D6" s="31" t="str">
         <x:v>Electro</x:v>
       </x:c>
-      <x:c r="E6" t="str">
+      <x:c r="E6" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F6" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G6" t="str">
+      <x:c r="F6" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" s="31" t="str">
         <x:v>Sequence</x:v>
       </x:c>
-      <x:c r="H6" t="str">
+      <x:c r="H6" s="31" t="str">
         <x:v>Travelling shot</x:v>
       </x:c>
-      <x:c r="I6" t="str">
+      <x:c r="I6" s="31" t="str">
         <x:v>Whole playfield</x:v>
       </x:c>
-      <x:c r="J6" t="str">
+      <x:c r="J6" s="31" t="str">
         <x:v>Final Super Jackpot</x:v>
       </x:c>
-      <x:c r="K6" t="str">
+      <x:c r="K6" s="31" t="str">
         <x:v>Sequence completion</x:v>
       </x:c>
-      <x:c r="L6" t="str">
+      <x:c r="L6" s="31" t="str">
         <x:v>Final Super collected / ball end</x:v>
       </x:c>
-      <x:c r="M6" t="str">
+      <x:c r="M6" s="31" t="str">
         <x:v>Sequence/follow-the-shot role.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="n">
+      <x:c r="A7" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" t="str">
+      <x:c r="B7" s="31" t="str">
         <x:v>Masked Masterminds</x:v>
       </x:c>
-      <x:c r="C7" t="str">
+      <x:c r="C7" s="31" t="str">
         <x:v>goblin</x:v>
       </x:c>
-      <x:c r="D7" t="str">
+      <x:c r="D7" s="31" t="str">
         <x:v>Green Goblin</x:v>
       </x:c>
-      <x:c r="E7" t="str">
+      <x:c r="E7" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F7" t="str">
+      <x:c r="F7" s="31" t="str">
         <x:v>2-ball MB</x:v>
       </x:c>
-      <x:c r="G7" t="str">
+      <x:c r="G7" s="31" t="str">
         <x:v>Multiball</x:v>
       </x:c>
-      <x:c r="H7" t="str">
+      <x:c r="H7" s="31" t="str">
         <x:v>Chaos windows</x:v>
       </x:c>
-      <x:c r="I7" t="str">
+      <x:c r="I7" s="31" t="str">
         <x:v>Whole playfield + saucers</x:v>
       </x:c>
-      <x:c r="J7" t="str">
+      <x:c r="J7" s="31" t="str">
         <x:v>Windowed jackpots / banked bonus</x:v>
       </x:c>
-      <x:c r="K7" t="str">
+      <x:c r="K7" s="31" t="str">
         <x:v>Multiball drain / timing windows</x:v>
       </x:c>
-      <x:c r="L7" t="str">
+      <x:c r="L7" s="31" t="str">
         <x:v>MB end or goals completed</x:v>
       </x:c>
-      <x:c r="M7" t="str">
+      <x:c r="M7" s="31" t="str">
         <x:v>Chaotic MB role; distinct from Parafino because scoring windows are unstable.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="n">
+      <x:c r="A8" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B8" t="str">
+      <x:c r="B8" s="31" t="str">
         <x:v>Masked Masterminds</x:v>
       </x:c>
-      <x:c r="C8" t="str">
+      <x:c r="C8" s="31" t="str">
         <x:v>doc_ock</x:v>
       </x:c>
-      <x:c r="D8" t="str">
+      <x:c r="D8" s="31" t="str">
         <x:v>Doctor Octopus</x:v>
       </x:c>
-      <x:c r="E8" t="str">
+      <x:c r="E8" s="31" t="str">
         <x:v>Implemented / recent rule update</x:v>
       </x:c>
-      <x:c r="F8" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G8" t="str">
+      <x:c r="F8" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="31" t="str">
         <x:v>Control / lock state</x:v>
       </x:c>
-      <x:c r="H8" t="str">
+      <x:c r="H8" s="31" t="str">
         <x:v>Build-and-cash</x:v>
       </x:c>
-      <x:c r="I8" t="str">
+      <x:c r="I8" s="31" t="str">
         <x:v>Rollovers + left bank + webs</x:v>
       </x:c>
-      <x:c r="J8" t="str">
+      <x:c r="J8" s="31" t="str">
         <x:v>Arm locks and web jackpots</x:v>
       </x:c>
-      <x:c r="K8" t="str">
+      <x:c r="K8" s="31" t="str">
         <x:v>Arms can be freed / state pressure</x:v>
       </x:c>
-      <x:c r="L8" t="str">
+      <x:c r="L8" s="31" t="str">
         <x:v>Goals completed / ball end</x:v>
       </x:c>
-      <x:c r="M8" t="str">
+      <x:c r="M8" s="31" t="str">
         <x:v>State-management mode; good strategic contrast.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="n">
+      <x:c r="A9" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B9" t="str">
+      <x:c r="B9" s="31" t="str">
         <x:v>Masked Masterminds</x:v>
       </x:c>
-      <x:c r="C9" t="str">
+      <x:c r="C9" s="31" t="str">
         <x:v>mysterio</x:v>
       </x:c>
-      <x:c r="D9" t="str">
+      <x:c r="D9" s="31" t="str">
         <x:v>Mysterio</x:v>
       </x:c>
-      <x:c r="E9" t="str">
+      <x:c r="E9" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F9" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G9" t="str">
+      <x:c r="F9" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="31" t="str">
         <x:v>Mystery / reveal</x:v>
       </x:c>
-      <x:c r="H9" t="str">
+      <x:c r="H9" s="31" t="str">
         <x:v>Clue logic</x:v>
       </x:c>
-      <x:c r="I9" t="str">
+      <x:c r="I9" s="31" t="str">
         <x:v>Whole playfield</x:v>
       </x:c>
-      <x:c r="J9" t="str">
+      <x:c r="J9" s="31" t="str">
         <x:v>Hidden Super</x:v>
       </x:c>
-      <x:c r="K9" t="str">
+      <x:c r="K9" s="31" t="str">
         <x:v>Wrong-shot penalty</x:v>
       </x:c>
-      <x:c r="L9" t="str">
+      <x:c r="L9" s="31" t="str">
         <x:v>Hidden Super solved / ball end</x:v>
       </x:c>
-      <x:c r="M9" t="str">
+      <x:c r="M9" s="31" t="str">
         <x:v>Mystery role for the chapter.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="n">
+      <x:c r="A10" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B10" t="str">
+      <x:c r="B10" s="31" t="str">
         <x:v>Masked Masterminds</x:v>
       </x:c>
-      <x:c r="C10" t="str">
+      <x:c r="C10" s="31" t="str">
         <x:v>scorpion</x:v>
       </x:c>
-      <x:c r="D10" t="str">
+      <x:c r="D10" s="31" t="str">
         <x:v>Scorpion</x:v>
       </x:c>
-      <x:c r="E10" t="str">
+      <x:c r="E10" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F10" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G10" t="str">
+      <x:c r="F10" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="31" t="str">
         <x:v>Timed attack</x:v>
       </x:c>
-      <x:c r="H10" t="str">
+      <x:c r="H10" s="31" t="str">
         <x:v>Spinner build</x:v>
       </x:c>
-      <x:c r="I10" t="str">
+      <x:c r="I10" s="31" t="str">
         <x:v>Spinner + drop banks</x:v>
       </x:c>
-      <x:c r="J10" t="str">
+      <x:c r="J10" s="31" t="str">
         <x:v>Venom build into staged attacks</x:v>
       </x:c>
-      <x:c r="K10" t="str">
+      <x:c r="K10" s="31" t="str">
         <x:v>Timed staged shot</x:v>
       </x:c>
-      <x:c r="L10" t="str">
+      <x:c r="L10" s="31" t="str">
         <x:v>Attack sequence complete / ball end</x:v>
       </x:c>
-      <x:c r="M10" t="str">
+      <x:c r="M10" s="31" t="str">
         <x:v>Urgency/drop attack role.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="n">
+      <x:c r="A11" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B11" t="str">
+      <x:c r="B11" s="31" t="str">
         <x:v>Masked Masterminds</x:v>
       </x:c>
-      <x:c r="C11" t="str">
+      <x:c r="C11" s="31" t="str">
         <x:v>parafino</x:v>
       </x:c>
-      <x:c r="D11" t="str">
+      <x:c r="D11" s="31" t="str">
         <x:v>Parafino</x:v>
       </x:c>
-      <x:c r="E11" t="str">
+      <x:c r="E11" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F11" t="str">
+      <x:c r="F11" s="31" t="str">
         <x:v>2-ball MB</x:v>
       </x:c>
-      <x:c r="G11" t="str">
+      <x:c r="G11" s="31" t="str">
         <x:v>Multiball</x:v>
       </x:c>
-      <x:c r="H11" t="str">
+      <x:c r="H11" s="31" t="str">
         <x:v>Area control</x:v>
       </x:c>
-      <x:c r="I11" t="str">
+      <x:c r="I11" s="31" t="str">
         <x:v>Left/right/pops + saucers</x:v>
       </x:c>
-      <x:c r="J11" t="str">
+      <x:c r="J11" s="31" t="str">
         <x:v>Heat-area saucer jackpots</x:v>
       </x:c>
-      <x:c r="K11" t="str">
+      <x:c r="K11" s="31" t="str">
         <x:v>MB drain / area maxing</x:v>
       </x:c>
-      <x:c r="L11" t="str">
+      <x:c r="L11" s="31" t="str">
         <x:v>MB end or goals completed</x:v>
       </x:c>
-      <x:c r="M11" t="str">
+      <x:c r="M11" s="31" t="str">
         <x:v>Second MB, but area-control identity keeps it different from Goblin.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="n">
+      <x:c r="A12" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B12" t="str">
+      <x:c r="B12" s="31" t="str">
         <x:v>Trubble's Monsters</x:v>
       </x:c>
-      <x:c r="C12" t="str">
+      <x:c r="C12" s="31" t="str">
         <x:v>cerberus</x:v>
       </x:c>
-      <x:c r="D12" t="str">
+      <x:c r="D12" s="31" t="str">
         <x:v>Cerberus</x:v>
       </x:c>
-      <x:c r="E12" t="str">
+      <x:c r="E12" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F12" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G12" t="str">
+      <x:c r="F12" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="31" t="str">
         <x:v>Timed matching</x:v>
       </x:c>
-      <x:c r="H12" t="str">
+      <x:c r="H12" s="31" t="str">
         <x:v>Saucer control</x:v>
       </x:c>
-      <x:c r="I12" t="str">
+      <x:c r="I12" s="31" t="str">
         <x:v>Upper targets + saucers</x:v>
       </x:c>
-      <x:c r="J12" t="str">
+      <x:c r="J12" s="31" t="str">
         <x:v>Matching saucer 2X jackpots</x:v>
       </x:c>
-      <x:c r="K12" t="str">
+      <x:c r="K12" s="31" t="str">
         <x:v>Timer expiry</x:v>
       </x:c>
-      <x:c r="L12" t="str">
+      <x:c r="L12" s="31" t="str">
         <x:v>3 saucer JPs / timer / ball end</x:v>
       </x:c>
-      <x:c r="M12" t="str">
+      <x:c r="M12" s="31" t="str">
         <x:v>Timer/matching role.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="n">
+      <x:c r="A13" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B13" t="str">
+      <x:c r="B13" s="31" t="str">
         <x:v>Trubble's Monsters</x:v>
       </x:c>
-      <x:c r="C13" t="str">
+      <x:c r="C13" s="31" t="str">
         <x:v>vulcan</x:v>
       </x:c>
-      <x:c r="D13" t="str">
+      <x:c r="D13" s="31" t="str">
         <x:v>Vulcan</x:v>
       </x:c>
-      <x:c r="E13" t="str">
+      <x:c r="E13" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F13" t="str">
+      <x:c r="F13" s="31" t="str">
         <x:v>2-ball MB; add-a-ball to 3</x:v>
       </x:c>
-      <x:c r="G13" t="str">
+      <x:c r="G13" s="31" t="str">
         <x:v>Multiball</x:v>
       </x:c>
-      <x:c r="H13" t="str">
+      <x:c r="H13" s="31" t="str">
         <x:v>Spinner build</x:v>
       </x:c>
-      <x:c r="I13" t="str">
+      <x:c r="I13" s="31" t="str">
         <x:v>Spinner + right drops + upper targets</x:v>
       </x:c>
-      <x:c r="J13" t="str">
+      <x:c r="J13" s="31" t="str">
         <x:v>Built Vulcan JP / eruption bonus</x:v>
       </x:c>
-      <x:c r="K13" t="str">
+      <x:c r="K13" s="31" t="str">
         <x:v>MB drain + inactivity timeout</x:v>
       </x:c>
-      <x:c r="L13" t="str">
+      <x:c r="L13" s="31" t="str">
         <x:v>MB/inactivity end</x:v>
       </x:c>
-      <x:c r="M13" t="str">
+      <x:c r="M13" s="31" t="str">
         <x:v>Chapter MB role; strongly physical.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="n">
+      <x:c r="A14" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B14" t="str">
+      <x:c r="B14" s="31" t="str">
         <x:v>Trubble's Monsters</x:v>
       </x:c>
-      <x:c r="C14" t="str">
+      <x:c r="C14" s="31" t="str">
         <x:v>diana</x:v>
       </x:c>
-      <x:c r="D14" t="str">
+      <x:c r="D14" s="31" t="str">
         <x:v>Diana</x:v>
       </x:c>
-      <x:c r="E14" t="str">
+      <x:c r="E14" s="31" t="str">
         <x:v>Implemented / needs light-color polish</x:v>
       </x:c>
-      <x:c r="F14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G14" t="str">
+      <x:c r="F14" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="31" t="str">
         <x:v>Timed shot</x:v>
       </x:c>
-      <x:c r="H14" t="str">
+      <x:c r="H14" s="31" t="str">
         <x:v>Post release</x:v>
       </x:c>
-      <x:c r="I14" t="str">
+      <x:c r="I14" s="31" t="str">
         <x:v>Upper/lower transition + right bank</x:v>
       </x:c>
-      <x:c r="J14" t="str">
+      <x:c r="J14" s="31" t="str">
         <x:v>Timed arrow jackpot</x:v>
       </x:c>
-      <x:c r="K14" t="str">
+      <x:c r="K14" s="31" t="str">
         <x:v>Short shot window</x:v>
       </x:c>
-      <x:c r="L14" t="str">
+      <x:c r="L14" s="31" t="str">
         <x:v>Timed objectives / ball end</x:v>
       </x:c>
-      <x:c r="M14" t="str">
+      <x:c r="M14" s="31" t="str">
         <x:v>Timed precision role.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="n">
+      <x:c r="A15" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B15" t="str">
+      <x:c r="B15" s="31" t="str">
         <x:v>Trubble's Monsters</x:v>
       </x:c>
-      <x:c r="C15" t="str">
+      <x:c r="C15" s="31" t="str">
         <x:v>cyclops</x:v>
       </x:c>
-      <x:c r="D15" t="str">
+      <x:c r="D15" s="31" t="str">
         <x:v>Cyclops</x:v>
       </x:c>
-      <x:c r="E15" t="str">
+      <x:c r="E15" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F15" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G15" t="str">
+      <x:c r="F15" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="31" t="str">
         <x:v>Limited flips</x:v>
       </x:c>
-      <x:c r="H15" t="str">
+      <x:c r="H15" s="31" t="str">
         <x:v>Build-to-cash</x:v>
       </x:c>
-      <x:c r="I15" t="str">
+      <x:c r="I15" s="31" t="str">
         <x:v>Drops + center web</x:v>
       </x:c>
-      <x:c r="J15" t="str">
+      <x:c r="J15" s="31" t="str">
         <x:v>Eye value from flips remaining</x:v>
       </x:c>
-      <x:c r="K15" t="str">
+      <x:c r="K15" s="31" t="str">
         <x:v>Flip limit</x:v>
       </x:c>
-      <x:c r="L15" t="str">
+      <x:c r="L15" s="31" t="str">
         <x:v>Eye collected / flips out / ball end</x:v>
       </x:c>
-      <x:c r="M15" t="str">
+      <x:c r="M15" s="31" t="str">
         <x:v>Limited-resource role.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="n">
+      <x:c r="A16" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B16" t="str">
+      <x:c r="B16" s="31" t="str">
         <x:v>Trubble's Monsters</x:v>
       </x:c>
-      <x:c r="C16" t="str">
+      <x:c r="C16" s="31" t="str">
         <x:v>centaur</x:v>
       </x:c>
-      <x:c r="D16" t="str">
+      <x:c r="D16" s="31" t="str">
         <x:v>Centaur</x:v>
       </x:c>
-      <x:c r="E16" t="str">
+      <x:c r="E16" s="31" t="str">
         <x:v>Implemented / needs light-color polish</x:v>
       </x:c>
-      <x:c r="F16" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G16" t="str">
+      <x:c r="F16" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="31" t="str">
         <x:v>Build-and-cash</x:v>
       </x:c>
-      <x:c r="H16" t="str">
+      <x:c r="H16" s="31" t="str">
         <x:v>Roof final</x:v>
       </x:c>
-      <x:c r="I16" t="str">
+      <x:c r="I16" s="31" t="str">
         <x:v>Drops + roof/post + rubber</x:v>
       </x:c>
-      <x:c r="J16" t="str">
+      <x:c r="J16" s="31" t="str">
         <x:v>Built JP into final shot</x:v>
       </x:c>
-      <x:c r="K16" t="str">
+      <x:c r="K16" s="31" t="str">
         <x:v>Final shot pressure</x:v>
       </x:c>
-      <x:c r="L16" t="str">
+      <x:c r="L16" s="31" t="str">
         <x:v>Final phase resolved / ball end</x:v>
       </x:c>
-      <x:c r="M16" t="str">
+      <x:c r="M16" s="31" t="str">
         <x:v>Build-to-final role; rounds out chapter variety.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="n">
+      <x:c r="A17" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B17" t="str">
+      <x:c r="B17" s="31" t="str">
         <x:v>Crime Wave</x:v>
       </x:c>
-      <x:c r="C17" t="str">
-        <x:v>kingpin</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>Kingpin</x:v>
-      </x:c>
-      <x:c r="E17" t="str">
+      <x:c r="C17" s="31" t="str">
+        <x:v>master_plan</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="str">
+        <x:v>The Plotter</x:v>
+      </x:c>
+      <x:c r="E17" s="31" t="str">
+        <x:v>Implemented / simplified</x:v>
+      </x:c>
+      <x:c r="F17" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="31" t="str">
+        <x:v>Build and reveal</x:v>
+      </x:c>
+      <x:c r="H17" s="31" t="str">
+        <x:v>Short sequence</x:v>
+      </x:c>
+      <x:c r="I17" s="31" t="str">
+        <x:v>Pops + spinner + saucers + VUK</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="str">
+        <x:v>Information into scheme jackpots and Super</x:v>
+      </x:c>
+      <x:c r="K17" s="31" t="str">
+        <x:v>Need two information before each reveal</x:v>
+      </x:c>
+      <x:c r="L17" s="31" t="str">
+        <x:v>Three schemes and VUK Super / ball end</x:v>
+      </x:c>
+      <x:c r="M17" s="31" t="str">
+        <x:v>Simplified former wizard code into a compact regular villain mode.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B18" s="31" t="str">
+        <x:v>Crime Wave</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="str">
+        <x:v>fly_brothers</x:v>
+      </x:c>
+      <x:c r="D18" s="31" t="str">
+        <x:v>Fly Brothers</x:v>
+      </x:c>
+      <x:c r="E18" s="31" t="str">
+        <x:v>Implemented / recent gate update</x:v>
+      </x:c>
+      <x:c r="F18" s="31" t="str">
+        <x:v>2-ball MB</x:v>
+      </x:c>
+      <x:c r="G18" s="31" t="str">
+        <x:v>Multiball</x:v>
+      </x:c>
+      <x:c r="H18" s="31" t="str">
+        <x:v>Upper access</x:v>
+      </x:c>
+      <x:c r="I18" s="31" t="str">
+        <x:v>Upper targets + saucers + spinner</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="str">
+        <x:v>Scaled saucer jackpots</x:v>
+      </x:c>
+      <x:c r="K18" s="31" t="str">
+        <x:v>MB drain / upper routing</x:v>
+      </x:c>
+      <x:c r="L18" s="31" t="str">
+        <x:v>MB end or goals completed</x:v>
+      </x:c>
+      <x:c r="M18" s="31" t="str">
+        <x:v>Crime chapter MB role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B19" s="31" t="str">
+        <x:v>Crime Wave</x:v>
+      </x:c>
+      <x:c r="C19" s="31" t="str">
+        <x:v>fifth_avenue_phantom</x:v>
+      </x:c>
+      <x:c r="D19" s="31" t="str">
+        <x:v>Fifth Avenue Phantom</x:v>
+      </x:c>
+      <x:c r="E19" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F17" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G17" t="str">
+      <x:c r="F19" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" s="31" t="str">
+        <x:v>Mystery / reveal</x:v>
+      </x:c>
+      <x:c r="H19" s="31" t="str">
+        <x:v>Timed location</x:v>
+      </x:c>
+      <x:c r="I19" s="31" t="str">
+        <x:v>Right bank + revealed location</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="str">
+        <x:v>Declining revealed-location value</x:v>
+      </x:c>
+      <x:c r="K19" s="31" t="str">
+        <x:v>Reveal window / value decay</x:v>
+      </x:c>
+      <x:c r="L19" s="31" t="str">
+        <x:v>Reveal rounds completed / ball end</x:v>
+      </x:c>
+      <x:c r="M19" s="31" t="str">
+        <x:v>Reveal/urgency role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B20" s="31" t="str">
+        <x:v>Crime Wave</x:v>
+      </x:c>
+      <x:c r="C20" s="31" t="str">
+        <x:v>enforcers</x:v>
+      </x:c>
+      <x:c r="D20" s="31" t="str">
+        <x:v>The Enforcers</x:v>
+      </x:c>
+      <x:c r="E20" s="31" t="str">
+        <x:v>Implemented / needs light-color polish</x:v>
+      </x:c>
+      <x:c r="F20" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G20" s="31" t="str">
         <x:v>Area control</x:v>
       </x:c>
-      <x:c r="H17" t="str">
+      <x:c r="H20" s="31" t="str">
+        <x:v>Super build</x:v>
+      </x:c>
+      <x:c r="I20" s="31" t="str">
+        <x:v>Zones + upper targets + center web</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="str">
+        <x:v>Upper target JPs build OX Super</x:v>
+      </x:c>
+      <x:c r="K20" s="31" t="str">
+        <x:v>Zone completion routing</x:v>
+      </x:c>
+      <x:c r="L20" s="31" t="str">
+        <x:v>Zones + OX Super complete / ball end</x:v>
+      </x:c>
+      <x:c r="M20" s="31" t="str">
+        <x:v>Second area mode, but should feel like team/zone buildup rather than Kingpin boss control.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B21" s="31" t="str">
+        <x:v>Crime Wave</x:v>
+      </x:c>
+      <x:c r="C21" s="31" t="str">
+        <x:v>doctor_cool</x:v>
+      </x:c>
+      <x:c r="D21" s="31" t="str">
+        <x:v>Doctor Cool</x:v>
+      </x:c>
+      <x:c r="E21" s="31" t="str">
+        <x:v>Implemented / needs playtest polish</x:v>
+      </x:c>
+      <x:c r="F21" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="31" t="str">
+        <x:v>Chase / freeze</x:v>
+      </x:c>
+      <x:c r="H21" s="31" t="str">
+        <x:v>Banked bonus</x:v>
+      </x:c>
+      <x:c r="I21" s="31" t="str">
+        <x:v>Drops + STAR + saucers</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="str">
+        <x:v>Frozen-diamond bank / shipment jackpot</x:v>
+      </x:c>
+      <x:c r="K21" s="31" t="str">
+        <x:v>Moving saucer chase and freeze timing</x:v>
+      </x:c>
+      <x:c r="L21" s="31" t="str">
+        <x:v>Required shipments complete / ball end</x:v>
+      </x:c>
+      <x:c r="M21" s="31" t="str">
+        <x:v>Crime Wave risk/reward chase; Doctor Cool smuggles diamonds inside ice.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B22" s="31" t="str">
+        <x:v>Danger Lurks</x:v>
+      </x:c>
+      <x:c r="C22" s="31" t="str">
+        <x:v>harley_clivendon</x:v>
+      </x:c>
+      <x:c r="D22" s="31" t="str">
+        <x:v>Harley Clivendon</x:v>
+      </x:c>
+      <x:c r="E22" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F22" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="31" t="str">
+        <x:v>Hypnosis / reveal</x:v>
+      </x:c>
+      <x:c r="H22" s="31" t="str">
+        <x:v>Hidden-shot control</x:v>
+      </x:c>
+      <x:c r="I22" s="31" t="str">
+        <x:v>Spinner, targets, and changing shots</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="str">
+        <x:v>Idol and scheme jackpots</x:v>
+      </x:c>
+      <x:c r="K22" s="31" t="str">
+        <x:v>Shot confusion / reveal windows</x:v>
+      </x:c>
+      <x:c r="L22" s="31" t="str">
+        <x:v>Goals completed / ball end</x:v>
+      </x:c>
+      <x:c r="M22" s="31" t="str">
+        <x:v>Two-episode antagonist gives the chapter its hypnosis and hidden-scheme role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B23" s="31" t="str">
+        <x:v>Danger Lurks</x:v>
+      </x:c>
+      <x:c r="C23" s="31" t="str">
+        <x:v>conquistador</x:v>
+      </x:c>
+      <x:c r="D23" s="31" t="str">
+        <x:v>The Conquistador</x:v>
+      </x:c>
+      <x:c r="E23" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F23" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" s="31" t="str">
+        <x:v>Treasure hunt / pursuit</x:v>
+      </x:c>
+      <x:c r="H23" s="31" t="str">
+        <x:v>Risk-reward path</x:v>
+      </x:c>
+      <x:c r="I23" s="31" t="str">
+        <x:v>Fort, saucer, upper, and escape shots</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="str">
+        <x:v>Fountain jackpots</x:v>
+      </x:c>
+      <x:c r="K23" s="31" t="str">
+        <x:v>Route and timer pressure</x:v>
+      </x:c>
+      <x:c r="L23" s="31" t="str">
+        <x:v>Goals completed / ball end</x:v>
+      </x:c>
+      <x:c r="M23" s="31" t="str">
+        <x:v>Hidden fort and Fountain of Youth provide the chapter's exploration role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B24" s="31" t="str">
+        <x:v>Danger Lurks</x:v>
+      </x:c>
+      <x:c r="C24" s="31" t="str">
+        <x:v>spider_slayer</x:v>
+      </x:c>
+      <x:c r="D24" s="31" t="str">
+        <x:v>Spider-Slayer</x:v>
+      </x:c>
+      <x:c r="E24" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F24" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" s="31" t="str">
+        <x:v>Machine pursuit</x:v>
+      </x:c>
+      <x:c r="H24" s="31" t="str">
+        <x:v>Tracking target</x:v>
+      </x:c>
+      <x:c r="I24" s="31" t="str">
+        <x:v>Moving playfield shots</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="str">
+        <x:v>Escape and destruction jackpots</x:v>
+      </x:c>
+      <x:c r="K24" s="31" t="str">
+        <x:v>Capture pressure</x:v>
+      </x:c>
+      <x:c r="L24" s="31" t="str">
+        <x:v>Slayer destroyed / ball end</x:v>
+      </x:c>
+      <x:c r="M24" s="31" t="str">
+        <x:v>Jameson-operated robot provides a clear mechanical hunt.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B25" s="31" t="str">
+        <x:v>Danger Lurks</x:v>
+      </x:c>
+      <x:c r="C25" s="31" t="str">
+        <x:v>metal_eating_monster</x:v>
+      </x:c>
+      <x:c r="D25" s="31" t="str">
+        <x:v>Metal-Eating Monster</x:v>
+      </x:c>
+      <x:c r="E25" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F25" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G25" s="31" t="str">
+        <x:v>Area consumption</x:v>
+      </x:c>
+      <x:c r="H25" s="31" t="str">
+        <x:v>Restore disabled areas</x:v>
+      </x:c>
+      <x:c r="I25" s="31" t="str">
+        <x:v>Whole playfield and river finish</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="str">
+        <x:v>Destruction jackpots</x:v>
+      </x:c>
+      <x:c r="K25" s="31" t="str">
+        <x:v>Shrinking safe playfield</x:v>
+      </x:c>
+      <x:c r="L25" s="31" t="str">
+        <x:v>Robot stopped / ball end</x:v>
+      </x:c>
+      <x:c r="M25" s="31" t="str">
+        <x:v>Giant robot creates a distinctive city-destruction mode.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B26" s="31" t="str">
+        <x:v>Danger Lurks</x:v>
+      </x:c>
+      <x:c r="C26" s="31" t="str">
+        <x:v>fiddler</x:v>
+      </x:c>
+      <x:c r="D26" s="31" t="str">
+        <x:v>Fiddler</x:v>
+      </x:c>
+      <x:c r="E26" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F26" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G26" s="31" t="str">
+        <x:v>Music / sequence</x:v>
+      </x:c>
+      <x:c r="H26" s="31" t="str">
+        <x:v>Pitch and ransom build</x:v>
+      </x:c>
+      <x:c r="I26" s="31" t="str">
+        <x:v>Spinner plus ordered shots</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="str">
+        <x:v>Sound-wave jackpots</x:v>
+      </x:c>
+      <x:c r="K26" s="31" t="str">
+        <x:v>Sequence and timer pressure</x:v>
+      </x:c>
+      <x:c r="L26" s="31" t="str">
+        <x:v>Violin silenced / ball end</x:v>
+      </x:c>
+      <x:c r="M26" s="31" t="str">
+        <x:v>Sound-based rules give the chapter a strong audiovisual identity. Persistent fiddler_bonus / FIDDLER RANSOM bank is now structurally implemented.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B27" s="31" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="C27" s="31" t="str">
+        <x:v>pardo</x:v>
+      </x:c>
+      <x:c r="D27" s="31" t="str">
+        <x:v>Pardo</x:v>
+      </x:c>
+      <x:c r="E27" s="31" t="str">
+        <x:v>Implemented / needs playtest polish</x:v>
+      </x:c>
+      <x:c r="F27" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" s="31" t="str">
+        <x:v>Mystery / reveal</x:v>
+      </x:c>
+      <x:c r="H27" s="31" t="str">
+        <x:v>Mistake limit</x:v>
+      </x:c>
+      <x:c r="I27" s="31" t="str">
+        <x:v>Spinner + 3 lit choices</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="str">
+        <x:v>Correct-shot jackpots</x:v>
+      </x:c>
+      <x:c r="K27" s="31" t="str">
+        <x:v>Wrong-shot mistakes</x:v>
+      </x:c>
+      <x:c r="L27" s="31" t="str">
+        <x:v>5 correct / 7 wrong / ball end</x:v>
+      </x:c>
+      <x:c r="M27" s="31" t="str">
+        <x:v>Mystic chapter reveal/mistake-limit role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B28" s="31" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="C28" s="31" t="str">
+        <x:v>fakir</x:v>
+      </x:c>
+      <x:c r="D28" s="31" t="str">
+        <x:v>The Fantastic Fakir</x:v>
+      </x:c>
+      <x:c r="E28" s="31" t="str">
+        <x:v>Implemented / needs playtest polish</x:v>
+      </x:c>
+      <x:c r="F28" s="31" t="str">
+        <x:v>2-ball MB</x:v>
+      </x:c>
+      <x:c r="G28" s="31" t="str">
+        <x:v>Multiball</x:v>
+      </x:c>
+      <x:c r="H28" s="31" t="str">
+        <x:v>Saucer-to-roof</x:v>
+      </x:c>
+      <x:c r="I28" s="31" t="str">
+        <x:v>Saucers + upper targets + spinners</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="str">
+        <x:v>Ruby JPs and Super</x:v>
+      </x:c>
+      <x:c r="K28" s="31" t="str">
+        <x:v>MB drain / timing reveals</x:v>
+      </x:c>
+      <x:c r="L28" s="31" t="str">
+        <x:v>MB end</x:v>
+      </x:c>
+      <x:c r="M28" s="31" t="str">
+        <x:v>Mystic chapter MB role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B29" s="31" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="C29" s="31" t="str">
+        <x:v>scarlet_sorcerer</x:v>
+      </x:c>
+      <x:c r="D29" s="31" t="str">
+        <x:v>Kotep — The Scarlet Sorcerer</x:v>
+      </x:c>
+      <x:c r="E29" s="31" t="str">
+        <x:v>Implemented / needs playtest</x:v>
+      </x:c>
+      <x:c r="F29" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" s="31" t="str">
+        <x:v>Sequence / timed reveal</x:v>
+      </x:c>
+      <x:c r="H29" s="31" t="str">
+        <x:v>Demon checklist</x:v>
+      </x:c>
+      <x:c r="I29" s="31" t="str">
+        <x:v>Webs, drops, pops, VUK</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="str">
+        <x:v>Rising Demon JPs + Scepter Super</x:v>
+      </x:c>
+      <x:c r="K29" s="31" t="str">
+        <x:v>Four demons appear every 4s; 20s Scepter timer</x:v>
+      </x:c>
+      <x:c r="L29" s="31" t="str">
+        <x:v>Super / timer / ball end</x:v>
+      </x:c>
+      <x:c r="M29" s="31" t="str">
+        <x:v>Optional fifth demon with More Jackpots; strong short checklist role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B30" s="31" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="C30" s="31" t="str">
+        <x:v>super_swami</x:v>
+      </x:c>
+      <x:c r="D30" s="31" t="str">
+        <x:v>Super Swami</x:v>
+      </x:c>
+      <x:c r="E30" s="31" t="str">
+        <x:v>Implemented / needs playtest</x:v>
+      </x:c>
+      <x:c r="F30" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G30" s="31" t="str">
+        <x:v>Timed / urgency</x:v>
+      </x:c>
+      <x:c r="H30" s="31" t="str">
+        <x:v>Area restoration</x:v>
+      </x:c>
+      <x:c r="I30" s="31" t="str">
+        <x:v>Six coordinate-based regions</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="str">
+        <x:v>Increasing restoration awards</x:v>
+      </x:c>
+      <x:c r="K30" s="31" t="str">
+        <x:v>40s blackout / 50s More Time</x:v>
+      </x:c>
+      <x:c r="L30" s="31" t="str">
+        <x:v>Six restored / timer / ball end</x:v>
+      </x:c>
+      <x:c r="M30" s="31" t="str">
+        <x:v>Simple region-restoration role with optional VUK Blackout Jackpot.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B31" s="31" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="C31" s="31" t="str">
+        <x:v>infinata</x:v>
+      </x:c>
+      <x:c r="D31" s="31" t="str">
+        <x:v>Infinata</x:v>
+      </x:c>
+      <x:c r="E31" s="31" t="str">
+        <x:v>Implemented / needs playtest</x:v>
+      </x:c>
+      <x:c r="F31" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G31" s="31" t="str">
+        <x:v>Sequential area completion</x:v>
+      </x:c>
+      <x:c r="H31" s="31" t="str">
+        <x:v>Green corruption areas</x:v>
+      </x:c>
+      <x:c r="I31" s="31" t="str">
+        <x:v>Pops, drops, webs, upper targets, saucers</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="str">
+        <x:v>Rising areas + timed saucer Super</x:v>
+      </x:c>
+      <x:c r="K31" s="31" t="str">
+        <x:v>One area at a time; 20s Super</x:v>
+      </x:c>
+      <x:c r="L31" s="31" t="str">
+        <x:v>Super / timer / ball end</x:v>
+      </x:c>
+      <x:c r="M31" s="31" t="str">
+        <x:v>Three required areas; optional fourth with More Jackpots.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B32" s="31" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="C32" s="31" t="str">
+        <x:v>noah_boddy</x:v>
+      </x:c>
+      <x:c r="D32" s="31" t="str">
+        <x:v>Dr. Noah Boddy</x:v>
+      </x:c>
+      <x:c r="E32" s="31" t="str">
+        <x:v>Implemented repurpose / needs polish</x:v>
+      </x:c>
+      <x:c r="F32" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G32" s="31" t="str">
+        <x:v>Mystery / reveal</x:v>
+      </x:c>
+      <x:c r="H32" s="31" t="str">
+        <x:v>Secret shot</x:v>
+      </x:c>
+      <x:c r="I32" s="31" t="str">
+        <x:v>Hidden/revealed shots + saucers</x:v>
+      </x:c>
+      <x:c r="J32" s="31" t="str">
+        <x:v>Secret-shot jackpots</x:v>
+      </x:c>
+      <x:c r="K32" s="31" t="str">
+        <x:v>Hidden info / wrong routing</x:v>
+      </x:c>
+      <x:c r="L32" s="31" t="str">
+        <x:v>Secret objectives solved / ball end</x:v>
+      </x:c>
+      <x:c r="M32" s="31" t="str">
+        <x:v>Mad Science reveal role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B33" s="31" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="C33" s="31" t="str">
+        <x:v>dr_magneto</x:v>
+      </x:c>
+      <x:c r="D33" s="31" t="str">
+        <x:v>Dr. Magneto</x:v>
+      </x:c>
+      <x:c r="E33" s="31" t="str">
+        <x:v>Implemented / needs playtest</x:v>
+      </x:c>
+      <x:c r="F33" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G33" s="31" t="str">
+        <x:v>Rooftop spinner sequence</x:v>
+      </x:c>
+      <x:c r="H33" s="31" t="str">
+        <x:v>Magnetic sweep</x:v>
+      </x:c>
+      <x:c r="I33" s="31" t="str">
+        <x:v>Upper spinner + both banks</x:v>
+      </x:c>
+      <x:c r="J33" s="31" t="str">
+        <x:v>50K spin + 50K staged drop + Supers</x:v>
+      </x:c>
+      <x:c r="K33" s="31" t="str">
+        <x:v>Seven-stage sweep; 20s final shot</x:v>
+      </x:c>
+      <x:c r="L33" s="31" t="str">
+        <x:v>Super / timer / ball end</x:v>
+      </x:c>
+      <x:c r="M33" s="31" t="str">
+        <x:v>Physical bank staging with retry on early roof exit.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B34" s="31" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="C34" s="31" t="str">
+        <x:v>professor_pretoris</x:v>
+      </x:c>
+      <x:c r="D34" s="31" t="str">
+        <x:v>Professor Pretoris</x:v>
+      </x:c>
+      <x:c r="E34" s="31" t="str">
+        <x:v>Implemented / needs playtest</x:v>
+      </x:c>
+      <x:c r="F34" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G34" s="31" t="str">
+        <x:v>Spinner build / timed final</x:v>
+      </x:c>
+      <x:c r="H34" s="31" t="str">
+        <x:v>Reactor flood</x:v>
+      </x:c>
+      <x:c r="I34" s="31" t="str">
+        <x:v>Eight GI bands + webs</x:v>
+      </x:c>
+      <x:c r="J34" s="31" t="str">
+        <x:v>100K bands + timed Supers</x:v>
+      </x:c>
+      <x:c r="K34" s="31" t="str">
+        <x:v>Eight spins; 20s center-web Super</x:v>
+      </x:c>
+      <x:c r="L34" s="31" t="str">
+        <x:v>Super / timer / ball end</x:v>
+      </x:c>
+      <x:c r="M34" s="31" t="str">
+        <x:v>Strong theatrical red-to-blue GI progression.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B35" s="31" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="C35" s="31" t="str">
+        <x:v>doctor_dumpty</x:v>
+      </x:c>
+      <x:c r="D35" s="31" t="str">
+        <x:v>Doctor Dumpty</x:v>
+      </x:c>
+      <x:c r="E35" s="31" t="str">
+        <x:v>Implemented repurpose / needs polish</x:v>
+      </x:c>
+      <x:c r="F35" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G35" s="31" t="str">
+        <x:v>Precision</x:v>
+      </x:c>
+      <x:c r="H35" s="31" t="str">
+        <x:v>Fragile puzzle</x:v>
+      </x:c>
+      <x:c r="I35" s="31" t="str">
+        <x:v>Controlled shots</x:v>
+      </x:c>
+      <x:c r="J35" s="31" t="str">
+        <x:v>Fragile puzzle value</x:v>
+      </x:c>
+      <x:c r="K35" s="31" t="str">
+        <x:v>Mistake/precision penalty</x:v>
+      </x:c>
+      <x:c r="L35" s="31" t="str">
+        <x:v>Puzzle complete / ball end</x:v>
+      </x:c>
+      <x:c r="M35" s="31" t="str">
+        <x:v>Precision/fragile role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B36" s="31" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="C36" s="31" t="str">
+        <x:v>dr_von_schlick</x:v>
+      </x:c>
+      <x:c r="D36" s="31" t="str">
+        <x:v>Dr. Von Schlick</x:v>
+      </x:c>
+      <x:c r="E36" s="31" t="str">
+        <x:v>Implemented / needs playtest</x:v>
+      </x:c>
+      <x:c r="F36" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G36" s="31" t="str">
+        <x:v>Moving shot / timed Super</x:v>
+      </x:c>
+      <x:c r="H36" s="31" t="str">
+        <x:v>Oil Pellet Chase</x:v>
+      </x:c>
+      <x:c r="I36" s="31" t="str">
+        <x:v>Webs, drops, pops, VUK</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="str">
+        <x:v>100K/150K pellets + 1M Super</x:v>
+      </x:c>
+      <x:c r="K36" s="31" t="str">
+        <x:v>4s moving shot; five pellets; 20s VUK</x:v>
+      </x:c>
+      <x:c r="L36" s="31" t="str">
+        <x:v>Super / timer / ball end</x:v>
+      </x:c>
+      <x:c r="M36" s="31" t="str">
+        <x:v>Daily Bugle gate lockout and held-ball eight-band flood finale.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B37" s="31" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="C37" s="31" t="str">
+        <x:v>clive_blotto</x:v>
+      </x:c>
+      <x:c r="D37" s="31" t="str">
+        <x:v>Clive and Blotto</x:v>
+      </x:c>
+      <x:c r="E37" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F37" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G37" s="31" t="str">
+        <x:v>Containment / spreading hazard</x:v>
+      </x:c>
+      <x:c r="H37" s="31" t="str">
+        <x:v>Banked bonus</x:v>
+      </x:c>
+      <x:c r="I37" s="31" t="str">
+        <x:v>Whole playfield / containment shots</x:v>
+      </x:c>
+      <x:c r="J37" s="31" t="str">
+        <x:v>blotto_bonus bank</x:v>
+      </x:c>
+      <x:c r="K37" s="31" t="str">
+        <x:v>Blotto spreads and changes shape</x:v>
+      </x:c>
+      <x:c r="L37" s="31" t="str">
+        <x:v>Goals completed / ball end</x:v>
+      </x:c>
+      <x:c r="M37" s="31" t="str">
+        <x:v>Tar/sludge element; full mode design pending.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B38" s="31" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="C38" s="31" t="str">
+        <x:v>dr_zap</x:v>
+      </x:c>
+      <x:c r="D38" s="31" t="str">
+        <x:v>Doctor Zapp</x:v>
+      </x:c>
+      <x:c r="E38" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F38" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G38" s="31" t="str">
+        <x:v>Electrical machine / timed</x:v>
+      </x:c>
+      <x:c r="H38" s="31" t="str">
+        <x:v>Invention control</x:v>
+      </x:c>
+      <x:c r="I38" s="31" t="str">
+        <x:v>Spinner + lit shots</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="str">
+        <x:v>Zapp/Super value</x:v>
+      </x:c>
+      <x:c r="K38" s="31" t="str">
+        <x:v>Overload timing</x:v>
+      </x:c>
+      <x:c r="L38" s="31" t="str">
+        <x:v>Sequence complete / timer / ball end</x:v>
+      </x:c>
+      <x:c r="M38" s="31" t="str">
+        <x:v>Must stay distinct from Electro by focusing on Caldwell's stolen invention.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B39" s="31" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="C39" s="31" t="str">
+        <x:v>voltan_boomer</x:v>
+      </x:c>
+      <x:c r="D39" s="31" t="str">
+        <x:v>Voltan and Boomer</x:v>
+      </x:c>
+      <x:c r="E39" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F39" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G39" s="31" t="str">
+        <x:v>Storm timing / robbery</x:v>
+      </x:c>
+      <x:c r="H39" s="31" t="str">
+        <x:v>Thunder windows</x:v>
+      </x:c>
+      <x:c r="I39" s="31" t="str">
+        <x:v>Storm shots + target groups</x:v>
+      </x:c>
+      <x:c r="J39" s="31" t="str">
+        <x:v>Thunder/robbery jackpots</x:v>
+      </x:c>
+      <x:c r="K39" s="31" t="str">
+        <x:v>Short storm windows</x:v>
+      </x:c>
+      <x:c r="L39" s="31" t="str">
+        <x:v>Goals completed / ball end</x:v>
+      </x:c>
+      <x:c r="M39" s="31" t="str">
+        <x:v>Thunder Rumble pair kept together; full design pending.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B40" s="31" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="C40" s="31" t="str">
+        <x:v>snowman</x:v>
+      </x:c>
+      <x:c r="D40" s="31" t="str">
+        <x:v>The Snowman</x:v>
+      </x:c>
+      <x:c r="E40" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F40" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G40" s="31" t="str">
+        <x:v>Endurance / melt</x:v>
+      </x:c>
+      <x:c r="H40" s="31" t="str">
+        <x:v>Area control</x:v>
+      </x:c>
+      <x:c r="I40" s="31" t="str">
+        <x:v>Pops / lanes / shots</x:v>
+      </x:c>
+      <x:c r="J40" s="31" t="str">
+        <x:v>Snowballing value</x:v>
+      </x:c>
+      <x:c r="K40" s="31" t="str">
+        <x:v>Escalating snowfall</x:v>
+      </x:c>
+      <x:c r="L40" s="31" t="str">
+        <x:v>Goals or timer / ball end</x:v>
+      </x:c>
+      <x:c r="M40" s="31" t="str">
+        <x:v>Build heat or drain electricity before the Snowman grows.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B41" s="31" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="C41" s="31" t="str">
+        <x:v>plutonians</x:v>
+      </x:c>
+      <x:c r="D41" s="31" t="str">
+        <x:v>The Plutonians</x:v>
+      </x:c>
+      <x:c r="E41" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F41" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G41" s="31" t="str">
+        <x:v>Ice rescue / repair</x:v>
+      </x:c>
+      <x:c r="H41" s="31" t="str">
+        <x:v>Survival / recovery</x:v>
+      </x:c>
+      <x:c r="I41" s="31" t="str">
+        <x:v>Whole playfield</x:v>
+      </x:c>
+      <x:c r="J41" s="31" t="str">
+        <x:v>Frozen jackpots / repair value</x:v>
+      </x:c>
+      <x:c r="K41" s="31" t="str">
+        <x:v>Frozen shots and escape repairs</x:v>
+      </x:c>
+      <x:c r="L41" s="31" t="str">
+        <x:v>Goals completed / ball end</x:v>
+      </x:c>
+      <x:c r="M41" s="31" t="str">
+        <x:v>Canonical identity replaces Ice Monster; story should end by helping them return home.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B42" s="31" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="C42" s="31" t="str">
+        <x:v>dr_manta</x:v>
+      </x:c>
+      <x:c r="D42" s="31" t="str">
+        <x:v>Dr. Manta</x:v>
+      </x:c>
+      <x:c r="E42" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F42" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G42" s="31" t="str">
+        <x:v>Hidden-city control</x:v>
+      </x:c>
+      <x:c r="H42" s="31" t="str">
+        <x:v>Trap / freeze</x:v>
+      </x:c>
+      <x:c r="I42" s="31" t="str">
+        <x:v>Saucers + robotic-creature shots</x:v>
+      </x:c>
+      <x:c r="J42" s="31" t="str">
+        <x:v>Frozen-city jackpots</x:v>
+      </x:c>
+      <x:c r="K42" s="31" t="str">
+        <x:v>Held ball / trap pressure</x:v>
+      </x:c>
+      <x:c r="L42" s="31" t="str">
+        <x:v>Goals or timer / ball end</x:v>
+      </x:c>
+      <x:c r="M42" s="31" t="str">
+        <x:v>Main Phantom from the Depths of Time villain.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B43" s="31" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="C43" s="31" t="str">
+        <x:v>igor</x:v>
+      </x:c>
+      <x:c r="D43" s="31" t="str">
+        <x:v>Igor</x:v>
+      </x:c>
+      <x:c r="E43" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F43" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G43" s="31" t="str">
+        <x:v>Assistant / defenses</x:v>
+      </x:c>
+      <x:c r="H43" s="31" t="str">
+        <x:v>Sequence / precision</x:v>
+      </x:c>
+      <x:c r="I43" s="31" t="str">
+        <x:v>Castle and defense shots</x:v>
+      </x:c>
+      <x:c r="J43" s="31" t="str">
+        <x:v>Assistant combo / Super</x:v>
+      </x:c>
+      <x:c r="K43" s="31" t="str">
+        <x:v>Ordered-shot pressure</x:v>
+      </x:c>
+      <x:c r="L43" s="31" t="str">
+        <x:v>Sequence complete / ball end</x:v>
+      </x:c>
+      <x:c r="M43" s="31" t="str">
+        <x:v>Shares Dr. Manta's episode and remains in the same chapter.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B44" s="31" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="C44" s="31" t="str">
+        <x:v>doctor_atlantean</x:v>
+      </x:c>
+      <x:c r="D44" s="31" t="str">
+        <x:v>Doctor Atlantean</x:v>
+      </x:c>
+      <x:c r="E44" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F44" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G44" s="31" t="str">
+        <x:v>Underwater invasion</x:v>
+      </x:c>
+      <x:c r="H44" s="31" t="str">
+        <x:v>Area control</x:v>
+      </x:c>
+      <x:c r="I44" s="31" t="str">
+        <x:v>Upper/lower Atlantean shots</x:v>
+      </x:c>
+      <x:c r="J44" s="31" t="str">
+        <x:v>Relic/kingdom jackpots</x:v>
+      </x:c>
+      <x:c r="K44" s="31" t="str">
+        <x:v>Dome and sinking pressure</x:v>
+      </x:c>
+      <x:c r="L44" s="31" t="str">
+        <x:v>Goals completed / ball end</x:v>
+      </x:c>
+      <x:c r="M44" s="31" t="str">
+        <x:v>Atlantean lost-world objective role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B45" s="31" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="C45" s="31" t="str">
+        <x:v>devargas</x:v>
+      </x:c>
+      <x:c r="D45" s="31" t="str">
+        <x:v>DeVargas</x:v>
+      </x:c>
+      <x:c r="E45" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F45" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G45" s="31" t="str">
+        <x:v>Hidden city / gold</x:v>
+      </x:c>
+      <x:c r="H45" s="31" t="str">
         <x:v>Build-and-cash</x:v>
       </x:c>
-      <x:c r="I17" t="str">
-        <x:v>Multiple crime areas + DB</x:v>
-      </x:c>
-      <x:c r="J17" t="str">
-        <x:v>Daily Bugle jackpots</x:v>
-      </x:c>
-      <x:c r="K17" t="str">
-        <x:v>Area completion routing</x:v>
-      </x:c>
-      <x:c r="L17" t="str">
-        <x:v>Areas/jackpots cleared / ball end</x:v>
-      </x:c>
-      <x:c r="M17" t="str">
-        <x:v>Area-control boss-style regular villain.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B18" t="str">
-        <x:v>Crime Wave</x:v>
-      </x:c>
-      <x:c r="C18" t="str">
-        <x:v>human_flies</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
-        <x:v>Human Flies</x:v>
-      </x:c>
-      <x:c r="E18" t="str">
-        <x:v>Implemented / recent gate update</x:v>
-      </x:c>
-      <x:c r="F18" t="str">
-        <x:v>2-ball MB</x:v>
-      </x:c>
-      <x:c r="G18" t="str">
-        <x:v>Multiball</x:v>
-      </x:c>
-      <x:c r="H18" t="str">
-        <x:v>Upper access</x:v>
-      </x:c>
-      <x:c r="I18" t="str">
-        <x:v>Upper targets + saucers + spinner</x:v>
-      </x:c>
-      <x:c r="J18" t="str">
-        <x:v>Scaled saucer jackpots</x:v>
-      </x:c>
-      <x:c r="K18" t="str">
-        <x:v>MB drain / upper routing</x:v>
-      </x:c>
-      <x:c r="L18" t="str">
-        <x:v>MB end or goals completed</x:v>
-      </x:c>
-      <x:c r="M18" t="str">
-        <x:v>Crime chapter MB role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B19" t="str">
-        <x:v>Crime Wave</x:v>
-      </x:c>
-      <x:c r="C19" t="str">
-        <x:v>fifth_avenue_phantom</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
-        <x:v>Fifth Avenue Phantom</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
+      <x:c r="I45" s="31" t="str">
+        <x:v>Cloud City and golden-defense shots</x:v>
+      </x:c>
+      <x:c r="J45" s="31" t="str">
+        <x:v>devargas_bonus bank</x:v>
+      </x:c>
+      <x:c r="K45" s="31" t="str">
+        <x:v>Golden eagle / city defenses</x:v>
+      </x:c>
+      <x:c r="L45" s="31" t="str">
+        <x:v>Goals completed / ball end</x:v>
+      </x:c>
+      <x:c r="M45" s="31" t="str">
+        <x:v>Cloud City of Gold gives Chapter 8 its hidden-mountain kingdom role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B46" s="31" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="C46" s="31" t="str">
+        <x:v>molemen</x:v>
+      </x:c>
+      <x:c r="D46" s="31" t="str">
+        <x:v>Molemen</x:v>
+      </x:c>
+      <x:c r="E46" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F46" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G46" s="31" t="str">
+        <x:v>Underground invasion</x:v>
+      </x:c>
+      <x:c r="H46" s="31" t="str">
+        <x:v>Area / survival</x:v>
+      </x:c>
+      <x:c r="I46" s="31" t="str">
+        <x:v>Drops, tunnels, lower playfield</x:v>
+      </x:c>
+      <x:c r="J46" s="31" t="str">
+        <x:v>Underground jackpots</x:v>
+      </x:c>
+      <x:c r="K46" s="31" t="str">
+        <x:v>Escalating underground pressure</x:v>
+      </x:c>
+      <x:c r="L46" s="31" t="str">
+        <x:v>Goals or timer / ball end</x:v>
+      </x:c>
+      <x:c r="M46" s="31" t="str">
+        <x:v>Compact mode name; Mugs Reilly can appear in intro and summaries.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B47" s="31" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="C47" s="31" t="str">
+        <x:v>charles_cameo</x:v>
+      </x:c>
+      <x:c r="D47" s="31" t="str">
+        <x:v>Charles Cameo</x:v>
+      </x:c>
+      <x:c r="E47" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F47" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G47" s="31" t="str">
+        <x:v>Disguise / identity</x:v>
+      </x:c>
+      <x:c r="H47" s="31" t="str">
+        <x:v>Mystery / reveal</x:v>
+      </x:c>
+      <x:c r="I47" s="31" t="str">
+        <x:v>Changing shots</x:v>
+      </x:c>
+      <x:c r="J47" s="31" t="str">
+        <x:v>Impostor jackpots</x:v>
+      </x:c>
+      <x:c r="K47" s="31" t="str">
+        <x:v>Wrong identity penalty</x:v>
+      </x:c>
+      <x:c r="L47" s="31" t="str">
+        <x:v>Goals or mistake limit / ball end</x:v>
+      </x:c>
+      <x:c r="M47" s="31" t="str">
+        <x:v>Chapter identity role; grouped with Brutus.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B48" s="31" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="C48" s="31" t="str">
+        <x:v>brutus</x:v>
+      </x:c>
+      <x:c r="D48" s="31" t="str">
+        <x:v>Brutus</x:v>
+      </x:c>
+      <x:c r="E48" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F48" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G48" s="31" t="str">
+        <x:v>Strength / bash</x:v>
+      </x:c>
+      <x:c r="H48" s="31" t="str">
+        <x:v>Build-and-cash</x:v>
+      </x:c>
+      <x:c r="I48" s="31" t="str">
+        <x:v>Drops / targets</x:v>
+      </x:c>
+      <x:c r="J48" s="31" t="str">
+        <x:v>Bash jackpot build</x:v>
+      </x:c>
+      <x:c r="K48" s="31" t="str">
+        <x:v>Shot volume / bank resets</x:v>
+      </x:c>
+      <x:c r="L48" s="31" t="str">
+        <x:v>Goals completed / ball end</x:v>
+      </x:c>
+      <x:c r="M48" s="31" t="str">
+        <x:v>Direct physical role tied to Charles Cameo's episode.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B49" s="31" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="C49" s="31" t="str">
+        <x:v>desperado</x:v>
+      </x:c>
+      <x:c r="D49" s="31" t="str">
+        <x:v>Desperado</x:v>
+      </x:c>
+      <x:c r="E49" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F49" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G49" s="31" t="str">
+        <x:v>Hypnosis / escape</x:v>
+      </x:c>
+      <x:c r="H49" s="31" t="str">
+        <x:v>Moving or timed shots</x:v>
+      </x:c>
+      <x:c r="I49" s="31" t="str">
+        <x:v>Playfield chase + upper escape</x:v>
+      </x:c>
+      <x:c r="J49" s="31" t="str">
+        <x:v>Desperado jackpots</x:v>
+      </x:c>
+      <x:c r="K49" s="31" t="str">
+        <x:v>Flying-horse escape pressure</x:v>
+      </x:c>
+      <x:c r="L49" s="31" t="str">
+        <x:v>Goals or timer / ball end</x:v>
+      </x:c>
+      <x:c r="M49" s="31" t="str">
+        <x:v>Oddball western villain; full episode-based design pending.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B50" s="31" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="C50" s="31" t="str">
+        <x:v>skymaster</x:v>
+      </x:c>
+      <x:c r="D50" s="31" t="str">
+        <x:v>Skymaster</x:v>
+      </x:c>
+      <x:c r="E50" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
-      <x:c r="F19" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G19" t="str">
-        <x:v>Mystery / reveal</x:v>
-      </x:c>
-      <x:c r="H19" t="str">
-        <x:v>Timed location</x:v>
-      </x:c>
-      <x:c r="I19" t="str">
-        <x:v>Right bank + revealed location</x:v>
-      </x:c>
-      <x:c r="J19" t="str">
-        <x:v>Declining revealed-location value</x:v>
-      </x:c>
-      <x:c r="K19" t="str">
-        <x:v>Reveal window / value decay</x:v>
-      </x:c>
-      <x:c r="L19" t="str">
-        <x:v>Reveal rounds completed / ball end</x:v>
-      </x:c>
-      <x:c r="M19" t="str">
-        <x:v>Reveal/urgency role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B20" t="str">
-        <x:v>Crime Wave</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>enforcers</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>Enforcers / Ox</x:v>
-      </x:c>
-      <x:c r="E20" t="str">
-        <x:v>Implemented / needs light-color polish</x:v>
-      </x:c>
-      <x:c r="F20" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G20" t="str">
-        <x:v>Area control</x:v>
-      </x:c>
-      <x:c r="H20" t="str">
-        <x:v>Super build</x:v>
-      </x:c>
-      <x:c r="I20" t="str">
-        <x:v>Zones + upper targets + center web</x:v>
-      </x:c>
-      <x:c r="J20" t="str">
-        <x:v>Upper target JPs build OX Super</x:v>
-      </x:c>
-      <x:c r="K20" t="str">
-        <x:v>Zone completion routing</x:v>
-      </x:c>
-      <x:c r="L20" t="str">
-        <x:v>Zones + OX Super complete / ball end</x:v>
-      </x:c>
-      <x:c r="M20" t="str">
-        <x:v>Second area mode, but should feel like team/zone buildup rather than Kingpin boss control.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B21" t="str">
-        <x:v>Crime Wave</x:v>
-      </x:c>
-      <x:c r="C21" t="str">
-        <x:v>diamond_smugglers</x:v>
-      </x:c>
-      <x:c r="D21" t="str">
-        <x:v>Diamond Smugglers</x:v>
-      </x:c>
-      <x:c r="E21" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
-      </x:c>
-      <x:c r="F21" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G21" t="str">
-        <x:v>Chase / freeze</x:v>
-      </x:c>
-      <x:c r="H21" t="str">
+      <x:c r="F50" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G50" s="31" t="str">
+        <x:v>Limited flips</x:v>
+      </x:c>
+      <x:c r="H50" s="31" t="str">
+        <x:v>Blimp assault</x:v>
+      </x:c>
+      <x:c r="I50" s="31" t="str">
+        <x:v>Saucers + upper targets</x:v>
+      </x:c>
+      <x:c r="J50" s="31" t="str">
+        <x:v>Flips-left Super</x:v>
+      </x:c>
+      <x:c r="K50" s="31" t="str">
+        <x:v>Flip limit</x:v>
+      </x:c>
+      <x:c r="L50" s="31" t="str">
+        <x:v>3 roof clears / ball end</x:v>
+      </x:c>
+      <x:c r="M50" s="31" t="str">
+        <x:v>The Fly's working limited-flip rules rethemed as an attack on Skymaster's blimp.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B51" s="31" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="C51" s="31" t="str">
+        <x:v>swamp_reptiles</x:v>
+      </x:c>
+      <x:c r="D51" s="31" t="str">
+        <x:v>Swamp Reptiles</x:v>
+      </x:c>
+      <x:c r="E51" s="31" t="str">
+        <x:v>Implemented repurpose / needs polish</x:v>
+      </x:c>
+      <x:c r="F51" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G51" s="31" t="str">
         <x:v>Banked bonus</x:v>
       </x:c>
-      <x:c r="I21" t="str">
-        <x:v>Drops + STAR + saucers</x:v>
-      </x:c>
-      <x:c r="J21" t="str">
-        <x:v>Diamond bonus bank / chase value</x:v>
-      </x:c>
-      <x:c r="K21" t="str">
-        <x:v>Chase timing / freeze decisions</x:v>
-      </x:c>
-      <x:c r="L21" t="str">
-        <x:v>Diamond objectives complete / ball end</x:v>
-      </x:c>
-      <x:c r="M21" t="str">
-        <x:v>Risk/reward chase/freeze role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B22" t="str">
-        <x:v>Mystic Menace</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>pardo</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>Pardo</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
-      </x:c>
-      <x:c r="F22" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G22" t="str">
-        <x:v>Mystery / reveal</x:v>
-      </x:c>
-      <x:c r="H22" t="str">
-        <x:v>Mistake limit</x:v>
-      </x:c>
-      <x:c r="I22" t="str">
-        <x:v>Spinner + 3 lit choices</x:v>
-      </x:c>
-      <x:c r="J22" t="str">
-        <x:v>Correct-shot jackpots</x:v>
-      </x:c>
-      <x:c r="K22" t="str">
-        <x:v>Wrong-shot mistakes</x:v>
-      </x:c>
-      <x:c r="L22" t="str">
-        <x:v>5 correct / 7 wrong / ball end</x:v>
-      </x:c>
-      <x:c r="M22" t="str">
-        <x:v>Mystic chapter reveal/mistake-limit role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B23" t="str">
-        <x:v>Mystic Menace</x:v>
-      </x:c>
-      <x:c r="C23" t="str">
-        <x:v>fakir</x:v>
-      </x:c>
-      <x:c r="D23" t="str">
-        <x:v>The Fakir</x:v>
-      </x:c>
-      <x:c r="E23" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
-      </x:c>
-      <x:c r="F23" t="str">
-        <x:v>2-ball MB</x:v>
-      </x:c>
-      <x:c r="G23" t="str">
-        <x:v>Multiball</x:v>
-      </x:c>
-      <x:c r="H23" t="str">
-        <x:v>Saucer-to-roof</x:v>
-      </x:c>
-      <x:c r="I23" t="str">
-        <x:v>Saucers + upper targets + spinners</x:v>
-      </x:c>
-      <x:c r="J23" t="str">
-        <x:v>Ruby JPs and Super</x:v>
-      </x:c>
-      <x:c r="K23" t="str">
-        <x:v>MB drain / timing reveals</x:v>
-      </x:c>
-      <x:c r="L23" t="str">
-        <x:v>MB end</x:v>
-      </x:c>
-      <x:c r="M23" t="str">
-        <x:v>Mystic chapter MB role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B24" t="str">
-        <x:v>Mystic Menace</x:v>
-      </x:c>
-      <x:c r="C24" t="str">
-        <x:v>scarlet_sorcerer</x:v>
-      </x:c>
-      <x:c r="D24" t="str">
-        <x:v>Scarlet Sorcerer</x:v>
-      </x:c>
-      <x:c r="E24" t="str">
-        <x:v>Implemented / needs playtest</x:v>
-      </x:c>
-      <x:c r="F24" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G24" t="str">
-        <x:v>Sequence / timed reveal</x:v>
-      </x:c>
-      <x:c r="H24" t="str">
-        <x:v>Demon checklist</x:v>
-      </x:c>
-      <x:c r="I24" t="str">
-        <x:v>Webs, drops, pops, VUK</x:v>
-      </x:c>
-      <x:c r="J24" t="str">
-        <x:v>Rising Demon JPs + Scepter Super</x:v>
-      </x:c>
-      <x:c r="K24" t="str">
-        <x:v>Four demons appear every 4s; 20s Scepter timer</x:v>
-      </x:c>
-      <x:c r="L24" t="str">
-        <x:v>Super / timer / ball end</x:v>
-      </x:c>
-      <x:c r="M24" t="str">
-        <x:v>Optional fifth demon with More Jackpots; strong short checklist role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B25" t="str">
-        <x:v>Mystic Menace</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>super_swami</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>Super Swami</x:v>
-      </x:c>
-      <x:c r="E25" t="str">
-        <x:v>Implemented / needs playtest</x:v>
-      </x:c>
-      <x:c r="F25" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G25" t="str">
-        <x:v>Timed / urgency</x:v>
-      </x:c>
-      <x:c r="H25" t="str">
-        <x:v>Area restoration</x:v>
-      </x:c>
-      <x:c r="I25" t="str">
-        <x:v>Six coordinate-based regions</x:v>
-      </x:c>
-      <x:c r="J25" t="str">
-        <x:v>Increasing restoration awards</x:v>
-      </x:c>
-      <x:c r="K25" t="str">
-        <x:v>40s blackout / 50s More Time</x:v>
-      </x:c>
-      <x:c r="L25" t="str">
-        <x:v>Six restored / timer / ball end</x:v>
-      </x:c>
-      <x:c r="M25" t="str">
-        <x:v>Simple region-restoration role with optional VUK Blackout Jackpot.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B26" t="str">
-        <x:v>Mystic Menace</x:v>
-      </x:c>
-      <x:c r="C26" t="str">
-        <x:v>infinata</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
-        <x:v>Infinata</x:v>
-      </x:c>
-      <x:c r="E26" t="str">
-        <x:v>Implemented / needs playtest</x:v>
-      </x:c>
-      <x:c r="F26" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G26" t="str">
-        <x:v>Sequential area completion</x:v>
-      </x:c>
-      <x:c r="H26" t="str">
-        <x:v>Green corruption areas</x:v>
-      </x:c>
-      <x:c r="I26" t="str">
-        <x:v>Pops, drops, webs, upper targets, saucers</x:v>
-      </x:c>
-      <x:c r="J26" t="str">
-        <x:v>Rising areas + timed saucer Super</x:v>
-      </x:c>
-      <x:c r="K26" t="str">
-        <x:v>One area at a time; 20s Super</x:v>
-      </x:c>
-      <x:c r="L26" t="str">
-        <x:v>Super / timer / ball end</x:v>
-      </x:c>
-      <x:c r="M26" t="str">
-        <x:v>Three required areas; optional fourth with More Jackpots.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B27" t="str">
-        <x:v>Mad Science</x:v>
-      </x:c>
-      <x:c r="C27" t="str">
-        <x:v>noah_boddy</x:v>
-      </x:c>
-      <x:c r="D27" t="str">
-        <x:v>Dr. Noah Boddy</x:v>
-      </x:c>
-      <x:c r="E27" t="str">
+      <x:c r="H51" s="31" t="str">
+        <x:v>Area hazard</x:v>
+      </x:c>
+      <x:c r="I51" s="31" t="str">
+        <x:v>Swamp shots</x:v>
+      </x:c>
+      <x:c r="J51" s="31" t="str">
+        <x:v>swamp_bonus bank</x:v>
+      </x:c>
+      <x:c r="K51" s="31" t="str">
+        <x:v>Escalating swamp pressure</x:v>
+      </x:c>
+      <x:c r="L51" s="31" t="str">
+        <x:v>Goals completed / ball end</x:v>
+      </x:c>
+      <x:c r="M51" s="31" t="str">
+        <x:v>Chapter bonus-bank/hazard role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B52" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C52" s="31" t="str">
+        <x:v>sir_galahad</x:v>
+      </x:c>
+      <x:c r="D52" s="31" t="str">
+        <x:v>Sir Galahad</x:v>
+      </x:c>
+      <x:c r="E52" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F52" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G52" s="31" t="str">
+        <x:v>Medieval time shift</x:v>
+      </x:c>
+      <x:c r="H52" s="31" t="str">
+        <x:v>Timed duel / sequence</x:v>
+      </x:c>
+      <x:c r="I52" s="31" t="str">
+        <x:v>Changing knight and castle shots</x:v>
+      </x:c>
+      <x:c r="J52" s="31" t="str">
+        <x:v>Duel jackpots</x:v>
+      </x:c>
+      <x:c r="K52" s="31" t="str">
+        <x:v>Short combat windows</x:v>
+      </x:c>
+      <x:c r="L52" s="31" t="str">
+        <x:v>Goals or timer / ball end</x:v>
+      </x:c>
+      <x:c r="M52" s="31" t="str">
+        <x:v>Knight Must Fall gives the finale a medieval displacement role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B53" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C53" s="31" t="str">
+        <x:v>master_vine</x:v>
+      </x:c>
+      <x:c r="D53" s="31" t="str">
+        <x:v>Master Vine</x:v>
+      </x:c>
+      <x:c r="E53" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F53" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G53" s="31" t="str">
+        <x:v>Spreading control</x:v>
+      </x:c>
+      <x:c r="H53" s="31" t="str">
+        <x:v>Hold / lock shots</x:v>
+      </x:c>
+      <x:c r="I53" s="31" t="str">
+        <x:v>Targets + lanes</x:v>
+      </x:c>
+      <x:c r="J53" s="31" t="str">
+        <x:v>Vine spread/cut jackpots</x:v>
+      </x:c>
+      <x:c r="K53" s="31" t="str">
+        <x:v>Spreading hazard</x:v>
+      </x:c>
+      <x:c r="L53" s="31" t="str">
+        <x:v>Goals or spread limit / ball end</x:v>
+      </x:c>
+      <x:c r="M53" s="31" t="str">
+        <x:v>Prehistoric Forbidden City and giant-vine role.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B54" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C54" s="31" t="str">
+        <x:v>master_technician</x:v>
+      </x:c>
+      <x:c r="D54" s="31" t="str">
+        <x:v>Master Technician</x:v>
+      </x:c>
+      <x:c r="E54" s="31" t="str">
         <x:v>Implemented repurpose / needs polish</x:v>
       </x:c>
-      <x:c r="F27" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G27" t="str">
-        <x:v>Mystery / reveal</x:v>
-      </x:c>
-      <x:c r="H27" t="str">
-        <x:v>Secret shot</x:v>
-      </x:c>
-      <x:c r="I27" t="str">
-        <x:v>Hidden/revealed shots + saucers</x:v>
-      </x:c>
-      <x:c r="J27" t="str">
-        <x:v>Secret-shot jackpots</x:v>
-      </x:c>
-      <x:c r="K27" t="str">
-        <x:v>Hidden info / wrong routing</x:v>
-      </x:c>
-      <x:c r="L27" t="str">
-        <x:v>Secret objectives solved / ball end</x:v>
-      </x:c>
-      <x:c r="M27" t="str">
-        <x:v>Mad Science reveal role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B28" t="str">
-        <x:v>Mad Science</x:v>
-      </x:c>
-      <x:c r="C28" t="str">
-        <x:v>dr_magneto</x:v>
-      </x:c>
-      <x:c r="D28" t="str">
-        <x:v>Dr. Magneto</x:v>
-      </x:c>
-      <x:c r="E28" t="str">
-        <x:v>Implemented / needs playtest</x:v>
-      </x:c>
-      <x:c r="F28" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G28" t="str">
-        <x:v>Rooftop spinner sequence</x:v>
-      </x:c>
-      <x:c r="H28" t="str">
-        <x:v>Magnetic sweep</x:v>
-      </x:c>
-      <x:c r="I28" t="str">
-        <x:v>Upper spinner + both banks</x:v>
-      </x:c>
-      <x:c r="J28" t="str">
-        <x:v>50K spin + 50K staged drop + Supers</x:v>
-      </x:c>
-      <x:c r="K28" t="str">
-        <x:v>Seven-stage sweep; 20s final shot</x:v>
-      </x:c>
-      <x:c r="L28" t="str">
-        <x:v>Super / timer / ball end</x:v>
-      </x:c>
-      <x:c r="M28" t="str">
-        <x:v>Physical bank staging with retry on early roof exit.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B29" t="str">
-        <x:v>Mad Science</x:v>
-      </x:c>
-      <x:c r="C29" t="str">
-        <x:v>professor_pretoris</x:v>
-      </x:c>
-      <x:c r="D29" t="str">
-        <x:v>Professor Pretoris</x:v>
-      </x:c>
-      <x:c r="E29" t="str">
-        <x:v>Implemented / needs playtest</x:v>
-      </x:c>
-      <x:c r="F29" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G29" t="str">
-        <x:v>Spinner build / timed final</x:v>
-      </x:c>
-      <x:c r="H29" t="str">
-        <x:v>Reactor flood</x:v>
-      </x:c>
-      <x:c r="I29" t="str">
-        <x:v>Eight GI bands + webs</x:v>
-      </x:c>
-      <x:c r="J29" t="str">
-        <x:v>100K bands + timed Supers</x:v>
-      </x:c>
-      <x:c r="K29" t="str">
-        <x:v>Eight spins; 20s center-web Super</x:v>
-      </x:c>
-      <x:c r="L29" t="str">
-        <x:v>Super / timer / ball end</x:v>
-      </x:c>
-      <x:c r="M29" t="str">
-        <x:v>Strong theatrical red-to-blue GI progression.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B30" t="str">
-        <x:v>Mad Science</x:v>
-      </x:c>
-      <x:c r="C30" t="str">
-        <x:v>doctor_dumpty</x:v>
-      </x:c>
-      <x:c r="D30" t="str">
-        <x:v>Doctor Dumpty</x:v>
-      </x:c>
-      <x:c r="E30" t="str">
-        <x:v>Implemented repurpose / needs polish</x:v>
-      </x:c>
-      <x:c r="F30" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G30" t="str">
-        <x:v>Precision</x:v>
-      </x:c>
-      <x:c r="H30" t="str">
-        <x:v>Fragile puzzle</x:v>
-      </x:c>
-      <x:c r="I30" t="str">
-        <x:v>Controlled shots</x:v>
-      </x:c>
-      <x:c r="J30" t="str">
-        <x:v>Fragile puzzle value</x:v>
-      </x:c>
-      <x:c r="K30" t="str">
-        <x:v>Mistake/precision penalty</x:v>
-      </x:c>
-      <x:c r="L30" t="str">
-        <x:v>Puzzle complete / ball end</x:v>
-      </x:c>
-      <x:c r="M30" t="str">
-        <x:v>Precision/fragile role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B31" t="str">
-        <x:v>Mad Science</x:v>
-      </x:c>
-      <x:c r="C31" t="str">
-        <x:v>dr_von_schlick</x:v>
-      </x:c>
-      <x:c r="D31" t="str">
-        <x:v>Dr. Von Schlick</x:v>
-      </x:c>
-      <x:c r="E31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
-      </x:c>
-      <x:c r="F31" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G31" t="str">
-        <x:v>Moving shot / timed Super</x:v>
-      </x:c>
-      <x:c r="H31" t="str">
-        <x:v>Oil Pellet Chase</x:v>
-      </x:c>
-      <x:c r="I31" t="str">
-        <x:v>Webs, drops, pops, VUK</x:v>
-      </x:c>
-      <x:c r="J31" t="str">
-        <x:v>100K/150K pellets + 1M Super</x:v>
-      </x:c>
-      <x:c r="K31" t="str">
-        <x:v>4s moving shot; five pellets; 20s VUK</x:v>
-      </x:c>
-      <x:c r="L31" t="str">
-        <x:v>Super / timer / ball end</x:v>
-      </x:c>
-      <x:c r="M31" t="str">
-        <x:v>Daily Bugle gate lockout and held-ball eight-band flood finale.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B32" t="str">
-        <x:v>Elemental Chaos</x:v>
-      </x:c>
-      <x:c r="C32" t="str">
-        <x:v>radiation_specialist</x:v>
-      </x:c>
-      <x:c r="D32" t="str">
-        <x:v>Radiation Specialist</x:v>
-      </x:c>
-      <x:c r="E32" t="str">
+      <x:c r="F54" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G54" s="31" t="str">
+        <x:v>Build-and-cash</x:v>
+      </x:c>
+      <x:c r="H54" s="31" t="str">
+        <x:v>Spinner value</x:v>
+      </x:c>
+      <x:c r="I54" s="31" t="str">
+        <x:v>Drops + spinner</x:v>
+      </x:c>
+      <x:c r="J54" s="31" t="str">
+        <x:v>Drops determine spinner value</x:v>
+      </x:c>
+      <x:c r="K54" s="31" t="str">
+        <x:v>Shot choice / cashout timing</x:v>
+      </x:c>
+      <x:c r="L54" s="31" t="str">
+        <x:v>Goals completed / ball end</x:v>
+      </x:c>
+      <x:c r="M54" s="31" t="str">
+        <x:v>Working Meteor-style mechanic retained; Manhattan-lifting story provides the final-chapter scale.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B55" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C55" s="31" t="str">
+        <x:v>spider_men</x:v>
+      </x:c>
+      <x:c r="D55" s="31" t="str">
+        <x:v>The Spider-Men</x:v>
+      </x:c>
+      <x:c r="E55" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
-      <x:c r="F32" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G32" t="str">
-        <x:v>Build-and-cash</x:v>
-      </x:c>
-      <x:c r="H32" t="str">
-        <x:v>Banked bonus</x:v>
-      </x:c>
-      <x:c r="I32" t="str">
-        <x:v>Radiation shots / drops</x:v>
-      </x:c>
-      <x:c r="J32" t="str">
-        <x:v>radiation_bonus bank</x:v>
-      </x:c>
-      <x:c r="K32" t="str">
-        <x:v>Escalating hazard</x:v>
-      </x:c>
-      <x:c r="L32" t="str">
+      <x:c r="F55" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G55" s="31" t="str">
+        <x:v>Identity / alien doubles</x:v>
+      </x:c>
+      <x:c r="H55" s="31" t="str">
+        <x:v>Mystery / precision</x:v>
+      </x:c>
+      <x:c r="I55" s="31" t="str">
+        <x:v>Changing Spider-Man shots</x:v>
+      </x:c>
+      <x:c r="J55" s="31" t="str">
+        <x:v>Identity jackpots / Super</x:v>
+      </x:c>
+      <x:c r="K55" s="31" t="str">
+        <x:v>Wrong-identity pressure</x:v>
+      </x:c>
+      <x:c r="L55" s="31" t="str">
+        <x:v>Goals or mistake limit / ball end</x:v>
+      </x:c>
+      <x:c r="M55" s="31" t="str">
+        <x:v>Home episode role; should resolve the alien encounter rather than treat them as conventional villains.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B56" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C56" s="31" t="str">
+        <x:v>von_rantenraven</x:v>
+      </x:c>
+      <x:c r="D56" s="31" t="str">
+        <x:v>Baron Von Rantenraven</x:v>
+      </x:c>
+      <x:c r="E56" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="F56" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G56" s="31" t="str">
+        <x:v>Aerial invasion</x:v>
+      </x:c>
+      <x:c r="H56" s="31" t="str">
+        <x:v>Whole-playfield assault</x:v>
+      </x:c>
+      <x:c r="I56" s="31" t="str">
+        <x:v>Air-raid, paralysis, and upper shots</x:v>
+      </x:c>
+      <x:c r="J56" s="31" t="str">
+        <x:v>Sky Harbor jackpots</x:v>
+      </x:c>
+      <x:c r="K56" s="31" t="str">
+        <x:v>Escalating invasion pressure</x:v>
+      </x:c>
+      <x:c r="L56" s="31" t="str">
         <x:v>Goals completed / ball end</x:v>
       </x:c>
-      <x:c r="M32" t="str">
-        <x:v>Chapter 7 banked-bonus role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B33" t="str">
-        <x:v>Elemental Chaos</x:v>
-      </x:c>
-      <x:c r="C33" t="str">
-        <x:v>dr_zap</x:v>
-      </x:c>
-      <x:c r="D33" t="str">
-        <x:v>Dr. Zap</x:v>
-      </x:c>
-      <x:c r="E33" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F33" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G33" t="str">
-        <x:v>Timed</x:v>
-      </x:c>
-      <x:c r="H33" t="str">
-        <x:v>Travelling spark variant</x:v>
-      </x:c>
-      <x:c r="I33" t="str">
-        <x:v>Spinner + lit shots</x:v>
-      </x:c>
-      <x:c r="J33" t="str">
-        <x:v>Zap/Super value</x:v>
-      </x:c>
-      <x:c r="K33" t="str">
-        <x:v>Timer / spark movement</x:v>
-      </x:c>
-      <x:c r="L33" t="str">
-        <x:v>Sequence complete / timer / ball end</x:v>
-      </x:c>
-      <x:c r="M33" t="str">
-        <x:v>Could reuse Electro-style language but needs distinct rules.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B34" t="str">
-        <x:v>Elemental Chaos</x:v>
-      </x:c>
-      <x:c r="C34" t="str">
-        <x:v>doctor_cool</x:v>
-      </x:c>
-      <x:c r="D34" t="str">
-        <x:v>Doctor Cool</x:v>
-      </x:c>
-      <x:c r="E34" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F34" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G34" t="str">
-        <x:v>Freeze / control</x:v>
-      </x:c>
-      <x:c r="H34" t="str">
-        <x:v>Risk/reward</x:v>
-      </x:c>
-      <x:c r="I34" t="str">
-        <x:v>Saucers / target freezes</x:v>
-      </x:c>
-      <x:c r="J34" t="str">
-        <x:v>Frozen jackpot values</x:v>
-      </x:c>
-      <x:c r="K34" t="str">
-        <x:v>Choice to freeze vs build</x:v>
-      </x:c>
-      <x:c r="L34" t="str">
-        <x:v>Goals completed / ball end</x:v>
-      </x:c>
-      <x:c r="M34" t="str">
-        <x:v>Good place for freeze timers and value control.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B35" t="str">
-        <x:v>Elemental Chaos</x:v>
-      </x:c>
-      <x:c r="C35" t="str">
-        <x:v>snowman</x:v>
-      </x:c>
-      <x:c r="D35" t="str">
-        <x:v>The Snowman</x:v>
-      </x:c>
-      <x:c r="E35" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F35" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G35" t="str">
-        <x:v>Endurance / survival</x:v>
-      </x:c>
-      <x:c r="H35" t="str">
-        <x:v>Area control</x:v>
-      </x:c>
-      <x:c r="I35" t="str">
-        <x:v>Pops / lanes / shots</x:v>
-      </x:c>
-      <x:c r="J35" t="str">
-        <x:v>Snowballing value</x:v>
-      </x:c>
-      <x:c r="K35" t="str">
-        <x:v>Escalating difficulty</x:v>
-      </x:c>
-      <x:c r="L35" t="str">
-        <x:v>Goals or timer / ball end</x:v>
-      </x:c>
-      <x:c r="M35" t="str">
-        <x:v>Candidate for slow-building pressure mode.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B36" t="str">
-        <x:v>Elemental Chaos</x:v>
-      </x:c>
-      <x:c r="C36" t="str">
-        <x:v>ice_monster</x:v>
-      </x:c>
-      <x:c r="D36" t="str">
-        <x:v>The Ice Monster</x:v>
-      </x:c>
-      <x:c r="E36" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F36" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G36" t="str">
-        <x:v>Multiball candidate</x:v>
-      </x:c>
-      <x:c r="H36" t="str">
-        <x:v>Survival</x:v>
-      </x:c>
-      <x:c r="I36" t="str">
-        <x:v>Whole playfield</x:v>
-      </x:c>
-      <x:c r="J36" t="str">
-        <x:v>Monster JPs / add-a-ball</x:v>
-      </x:c>
-      <x:c r="K36" t="str">
-        <x:v>MB drain / frozen shots</x:v>
-      </x:c>
-      <x:c r="L36" t="str">
-        <x:v>MB end or goals completed</x:v>
-      </x:c>
-      <x:c r="M36" t="str">
-        <x:v>Elemental chapter likely needs one MB here.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B37" t="str">
-        <x:v>Lost Worlds</x:v>
-      </x:c>
-      <x:c r="C37" t="str">
-        <x:v>dr_manta</x:v>
-      </x:c>
-      <x:c r="D37" t="str">
-        <x:v>Dr. Manta</x:v>
-      </x:c>
-      <x:c r="E37" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F37" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G37" t="str">
-        <x:v>Trap / saucer control</x:v>
-      </x:c>
-      <x:c r="H37" t="str">
-        <x:v>Timed</x:v>
-      </x:c>
-      <x:c r="I37" t="str">
-        <x:v>Saucers + underwater shots</x:v>
-      </x:c>
-      <x:c r="J37" t="str">
-        <x:v>Trap jackpots</x:v>
-      </x:c>
-      <x:c r="K37" t="str">
-        <x:v>Held ball / timer pressure</x:v>
-      </x:c>
-      <x:c r="L37" t="str">
-        <x:v>Goals or timer / ball end</x:v>
-      </x:c>
-      <x:c r="M37" t="str">
-        <x:v>Underwater/saucer trap candidate.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B38" t="str">
-        <x:v>Lost Worlds</x:v>
-      </x:c>
-      <x:c r="C38" t="str">
-        <x:v>doctor_atlantean</x:v>
-      </x:c>
-      <x:c r="D38" t="str">
-        <x:v>Doctor Atlantean</x:v>
-      </x:c>
-      <x:c r="E38" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F38" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G38" t="str">
-        <x:v>Sequence / checklist</x:v>
-      </x:c>
-      <x:c r="H38" t="str">
-        <x:v>Area control</x:v>
-      </x:c>
-      <x:c r="I38" t="str">
-        <x:v>Upper/lower Atlantean shots</x:v>
-      </x:c>
-      <x:c r="J38" t="str">
-        <x:v>Relic/kingdom jackpots</x:v>
-      </x:c>
-      <x:c r="K38" t="str">
-        <x:v>Shot routing</x:v>
-      </x:c>
-      <x:c r="L38" t="str">
-        <x:v>Goals completed / ball end</x:v>
-      </x:c>
-      <x:c r="M38" t="str">
-        <x:v>Lost-world objective/checklist role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B39" t="str">
-        <x:v>Lost Worlds</x:v>
-      </x:c>
-      <x:c r="C39" t="str">
-        <x:v>sky_master</x:v>
-      </x:c>
-      <x:c r="D39" t="str">
-        <x:v>Sky Master</x:v>
-      </x:c>
-      <x:c r="E39" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F39" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G39" t="str">
-        <x:v>Timed aerial attack</x:v>
-      </x:c>
-      <x:c r="H39" t="str">
-        <x:v>Upper playfield</x:v>
-      </x:c>
-      <x:c r="I39" t="str">
-        <x:v>Upper / spinner / lanes</x:v>
-      </x:c>
-      <x:c r="J39" t="str">
-        <x:v>Air-raid jackpots</x:v>
-      </x:c>
-      <x:c r="K39" t="str">
-        <x:v>Timer / shot windows</x:v>
-      </x:c>
-      <x:c r="L39" t="str">
-        <x:v>Goals or timer / ball end</x:v>
-      </x:c>
-      <x:c r="M39" t="str">
-        <x:v>Use upper/air theme without duplicating The Fly's limited flips.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B40" t="str">
-        <x:v>Lost Worlds</x:v>
-      </x:c>
-      <x:c r="C40" t="str">
-        <x:v>plutonians</x:v>
-      </x:c>
-      <x:c r="D40" t="str">
-        <x:v>The Plutonians</x:v>
-      </x:c>
-      <x:c r="E40" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F40" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G40" t="str">
-        <x:v>Build-and-cash</x:v>
-      </x:c>
-      <x:c r="H40" t="str">
-        <x:v>Banked bonus</x:v>
-      </x:c>
-      <x:c r="I40" t="str">
-        <x:v>Space/alien shots</x:v>
-      </x:c>
-      <x:c r="J40" t="str">
-        <x:v>plutonians_bonus bank</x:v>
-      </x:c>
-      <x:c r="K40" t="str">
-        <x:v>Escalating invasion</x:v>
-      </x:c>
-      <x:c r="L40" t="str">
-        <x:v>Goals completed / ball end</x:v>
-      </x:c>
-      <x:c r="M40" t="str">
-        <x:v>Chapter 8 banked-bonus role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B41" t="str">
-        <x:v>Lost Worlds</x:v>
-      </x:c>
-      <x:c r="C41" t="str">
-        <x:v>antarcticans</x:v>
-      </x:c>
-      <x:c r="D41" t="str">
-        <x:v>The Antarcticans</x:v>
-      </x:c>
-      <x:c r="E41" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F41" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G41" t="str">
-        <x:v>Freeze / reveal</x:v>
-      </x:c>
-      <x:c r="H41" t="str">
-        <x:v>Precision</x:v>
-      </x:c>
-      <x:c r="I41" t="str">
-        <x:v>Frozen lanes / target groups</x:v>
-      </x:c>
-      <x:c r="J41" t="str">
-        <x:v>Frozen jackpot / thaw bonus</x:v>
-      </x:c>
-      <x:c r="K41" t="str">
-        <x:v>Blocked/frozen shots</x:v>
-      </x:c>
-      <x:c r="L41" t="str">
-        <x:v>Goals or timer / ball end</x:v>
-      </x:c>
-      <x:c r="M41" t="str">
-        <x:v>Good freeze/reveal role distinct from Doctor Cool if scoped to Lost Worlds.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B42" t="str">
-        <x:v>Savage Oddities</x:v>
-      </x:c>
-      <x:c r="C42" t="str">
-        <x:v>charles_cameo</x:v>
-      </x:c>
-      <x:c r="D42" t="str">
-        <x:v>Charles Cameo</x:v>
-      </x:c>
-      <x:c r="E42" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F42" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G42" t="str">
-        <x:v>Disguise / identity candidate</x:v>
-      </x:c>
-      <x:c r="H42" t="str">
-        <x:v>Mystery / reveal</x:v>
-      </x:c>
-      <x:c r="I42" t="str">
-        <x:v>Changing shots</x:v>
-      </x:c>
-      <x:c r="J42" t="str">
-        <x:v>Impostor jackpots</x:v>
-      </x:c>
-      <x:c r="K42" t="str">
-        <x:v>Wrong identity penalty</x:v>
-      </x:c>
-      <x:c r="L42" t="str">
-        <x:v>Goals or mistake limit / ball end</x:v>
-      </x:c>
-      <x:c r="M42" t="str">
-        <x:v>Could be chapter's mystery/identity role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B43" t="str">
-        <x:v>Savage Oddities</x:v>
-      </x:c>
-      <x:c r="C43" t="str">
-        <x:v>brutus</x:v>
-      </x:c>
-      <x:c r="D43" t="str">
-        <x:v>Brutus</x:v>
-      </x:c>
-      <x:c r="E43" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F43" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G43" t="str">
-        <x:v>Strength / bash</x:v>
-      </x:c>
-      <x:c r="H43" t="str">
-        <x:v>Build-and-cash</x:v>
-      </x:c>
-      <x:c r="I43" t="str">
-        <x:v>Drops / targets</x:v>
-      </x:c>
-      <x:c r="J43" t="str">
-        <x:v>Bash jackpot build</x:v>
-      </x:c>
-      <x:c r="K43" t="str">
-        <x:v>Shot volume / bank resets</x:v>
-      </x:c>
-      <x:c r="L43" t="str">
-        <x:v>Goals completed / ball end</x:v>
-      </x:c>
-      <x:c r="M43" t="str">
-        <x:v>Straight physical bash role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B44" t="str">
-        <x:v>Savage Oddities</x:v>
-      </x:c>
-      <x:c r="C44" t="str">
-        <x:v>eigor</x:v>
-      </x:c>
-      <x:c r="D44" t="str">
-        <x:v>Eigor</x:v>
-      </x:c>
-      <x:c r="E44" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F44" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G44" t="str">
-        <x:v>Sequence / helper candidate</x:v>
-      </x:c>
-      <x:c r="H44" t="str">
-        <x:v>Precision</x:v>
-      </x:c>
-      <x:c r="I44" t="str">
-        <x:v>Specific shot order</x:v>
-      </x:c>
-      <x:c r="J44" t="str">
-        <x:v>Assistant combo/Super</x:v>
-      </x:c>
-      <x:c r="K44" t="str">
-        <x:v>Order pressure</x:v>
-      </x:c>
-      <x:c r="L44" t="str">
-        <x:v>Sequence complete / ball end</x:v>
-      </x:c>
-      <x:c r="M44" t="str">
-        <x:v>Could be ordered-shot precision role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B45" t="str">
-        <x:v>Savage Oddities</x:v>
-      </x:c>
-      <x:c r="C45" t="str">
-        <x:v>the_fly</x:v>
-      </x:c>
-      <x:c r="D45" t="str">
-        <x:v>The Fly</x:v>
-      </x:c>
-      <x:c r="E45" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
-      </x:c>
-      <x:c r="F45" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G45" t="str">
-        <x:v>Limited flips</x:v>
-      </x:c>
-      <x:c r="H45" t="str">
-        <x:v>Roof access loop</x:v>
-      </x:c>
-      <x:c r="I45" t="str">
-        <x:v>Saucers + upper targets</x:v>
-      </x:c>
-      <x:c r="J45" t="str">
-        <x:v>Flips-left Super</x:v>
-      </x:c>
-      <x:c r="K45" t="str">
-        <x:v>Flip limit</x:v>
-      </x:c>
-      <x:c r="L45" t="str">
-        <x:v>3 roof clears / ball end</x:v>
-      </x:c>
-      <x:c r="M45" t="str">
-        <x:v>Chapter limited-resource/roof role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B46" t="str">
-        <x:v>Savage Oddities</x:v>
-      </x:c>
-      <x:c r="C46" t="str">
-        <x:v>swamp_reptiles</x:v>
-      </x:c>
-      <x:c r="D46" t="str">
-        <x:v>Swamp Reptiles</x:v>
-      </x:c>
-      <x:c r="E46" t="str">
-        <x:v>Implemented repurpose / needs polish</x:v>
-      </x:c>
-      <x:c r="F46" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G46" t="str">
-        <x:v>Banked bonus</x:v>
-      </x:c>
-      <x:c r="H46" t="str">
-        <x:v>Area hazard</x:v>
-      </x:c>
-      <x:c r="I46" t="str">
-        <x:v>Swamp shots</x:v>
-      </x:c>
-      <x:c r="J46" t="str">
-        <x:v>swamp_bonus bank</x:v>
-      </x:c>
-      <x:c r="K46" t="str">
-        <x:v>Escalating swamp pressure</x:v>
-      </x:c>
-      <x:c r="L46" t="str">
-        <x:v>Goals completed / ball end</x:v>
-      </x:c>
-      <x:c r="M46" t="str">
-        <x:v>Chapter bonus-bank/hazard role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B47" t="str">
-        <x:v>Dimensional Finale</x:v>
-      </x:c>
-      <x:c r="C47" t="str">
-        <x:v>phantom_from_depths_of_time</x:v>
-      </x:c>
-      <x:c r="D47" t="str">
-        <x:v>Phantom from the Depths of Time</x:v>
-      </x:c>
-      <x:c r="E47" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F47" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G47" t="str">
-        <x:v>Timed / history shift</x:v>
-      </x:c>
-      <x:c r="H47" t="str">
-        <x:v>Mystery / reveal</x:v>
-      </x:c>
-      <x:c r="I47" t="str">
-        <x:v>Changing era shots</x:v>
-      </x:c>
-      <x:c r="J47" t="str">
-        <x:v>Time-window jackpots</x:v>
-      </x:c>
-      <x:c r="K47" t="str">
-        <x:v>Timer / shifting shots</x:v>
-      </x:c>
-      <x:c r="L47" t="str">
-        <x:v>Goals or timer / ball end</x:v>
-      </x:c>
-      <x:c r="M47" t="str">
-        <x:v>Final chapter timed-shift role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B48" t="str">
-        <x:v>Dimensional Finale</x:v>
-      </x:c>
-      <x:c r="C48" t="str">
-        <x:v>master_vine</x:v>
-      </x:c>
-      <x:c r="D48" t="str">
-        <x:v>Master Vine</x:v>
-      </x:c>
-      <x:c r="E48" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F48" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G48" t="str">
-        <x:v>Spreading control</x:v>
-      </x:c>
-      <x:c r="H48" t="str">
-        <x:v>Hold / lock shots</x:v>
-      </x:c>
-      <x:c r="I48" t="str">
-        <x:v>Targets + lanes</x:v>
-      </x:c>
-      <x:c r="J48" t="str">
-        <x:v>Vine spread/cut jackpots</x:v>
-      </x:c>
-      <x:c r="K48" t="str">
-        <x:v>Spreading hazard</x:v>
-      </x:c>
-      <x:c r="L48" t="str">
-        <x:v>Goals or spread limit / ball end</x:v>
-      </x:c>
-      <x:c r="M48" t="str">
-        <x:v>Spreading-vine/hold-shot candidate.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B49" t="str">
-        <x:v>Dimensional Finale</x:v>
-      </x:c>
-      <x:c r="C49" t="str">
-        <x:v>master_technician</x:v>
-      </x:c>
-      <x:c r="D49" t="str">
-        <x:v>Master Technician</x:v>
-      </x:c>
-      <x:c r="E49" t="str">
-        <x:v>Implemented repurpose / needs polish</x:v>
-      </x:c>
-      <x:c r="F49" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G49" t="str">
-        <x:v>Build-and-cash</x:v>
-      </x:c>
-      <x:c r="H49" t="str">
-        <x:v>Spinner value</x:v>
-      </x:c>
-      <x:c r="I49" t="str">
-        <x:v>Drops + spinner</x:v>
-      </x:c>
-      <x:c r="J49" t="str">
-        <x:v>Drops determine spinner value</x:v>
-      </x:c>
-      <x:c r="K49" t="str">
-        <x:v>Shot choice / cashout timing</x:v>
-      </x:c>
-      <x:c r="L49" t="str">
-        <x:v>Goals completed / ball end</x:v>
-      </x:c>
-      <x:c r="M49" t="str">
-        <x:v>Repurposed Meteor homage; chapter's spinner-value role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B50" t="str">
-        <x:v>Dimensional Finale</x:v>
-      </x:c>
-      <x:c r="C50" t="str">
-        <x:v>micro_men</x:v>
-      </x:c>
-      <x:c r="D50" t="str">
-        <x:v>Micro-Men</x:v>
-      </x:c>
-      <x:c r="E50" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F50" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G50" t="str">
-        <x:v>Precision / small targets</x:v>
-      </x:c>
-      <x:c r="H50" t="str">
-        <x:v>Multiplier</x:v>
-      </x:c>
-      <x:c r="I50" t="str">
-        <x:v>Small/quick shots</x:v>
-      </x:c>
-      <x:c r="J50" t="str">
-        <x:v>Micro multiplier/Super</x:v>
-      </x:c>
-      <x:c r="K50" t="str">
-        <x:v>Precision pressure</x:v>
-      </x:c>
-      <x:c r="L50" t="str">
-        <x:v>Goals completed / ball end</x:v>
-      </x:c>
-      <x:c r="M50" t="str">
-        <x:v>Good precision role for finale.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B51" t="str">
-        <x:v>Dimensional Finale</x:v>
-      </x:c>
-      <x:c r="C51" t="str">
-        <x:v>grand_emperor</x:v>
-      </x:c>
-      <x:c r="D51" t="str">
-        <x:v>Grand Emperor</x:v>
-      </x:c>
-      <x:c r="E51" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
-      </x:c>
-      <x:c r="F51" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G51" t="str">
-        <x:v>Finale / endurance</x:v>
-      </x:c>
-      <x:c r="H51" t="str">
-        <x:v>Whole playfield</x:v>
-      </x:c>
-      <x:c r="I51" t="str">
-        <x:v>Whole playfield</x:v>
-      </x:c>
-      <x:c r="J51" t="str">
-        <x:v>Grand Super / chapter synthesis</x:v>
-      </x:c>
-      <x:c r="K51" t="str">
-        <x:v>Escalating final pressure</x:v>
-      </x:c>
-      <x:c r="L51" t="str">
-        <x:v>Goals completed / ball end</x:v>
-      </x:c>
-      <x:c r="M51" t="str">
-        <x:v>Should combine prior chapter skills without becoming a generic checklist.</x:v>
+      <x:c r="M56" s="31" t="str">
+        <x:v>World War I aircraft and paralysis technology create the final chapter's aerial-war role.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2695,17 +2903,17 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="56" t="str">
-        <x:v>Mode</x:v>
-      </x:c>
-      <x:c r="B1" s="56" t="str">
-        <x:v>Removed Player Vars</x:v>
-      </x:c>
-      <x:c r="C1" s="56" t="str">
-        <x:v>Persistent/Shared Vars Kept</x:v>
-      </x:c>
-      <x:c r="D1" s="56" t="str">
-        <x:v>Notes</x:v>
+      <x:c r="A1" s="59" t="str">
+        <x:v>Area</x:v>
+      </x:c>
+      <x:c r="B1" s="59" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="C1" s="59" t="str">
+        <x:v>Variables</x:v>
+      </x:c>
+      <x:c r="D1" s="59" t="str">
+        <x:v>Reason</x:v>
       </x:c>
       <x:c r="E1" s="56"/>
       <x:c r="F1" s="56"/>
@@ -2731,17 +2939,17 @@
       <x:c r="Z1" s="56"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="14" t="str">
-        <x:v>Diana</x:v>
-      </x:c>
-      <x:c r="B2" s="14" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C2" s="14" t="str">
-        <x:v>diana_state; active_mode_* summary counters</x:v>
-      </x:c>
-      <x:c r="D2" s="14" t="str">
-        <x:v>Temporary arrows, phase, timer, targets, hit counters, Safety Net use, and end bonus moved into Python.</x:v>
+      <x:c r="A2" s="31" t="str">
+        <x:v>Danger Lurks villains</x:v>
+      </x:c>
+      <x:c r="B2" s="31" t="str">
+        <x:v>Keep</x:v>
+      </x:c>
+      <x:c r="C2" s="31" t="str">
+        <x:v>harley_clivendon_state, conquistador_state, spider_slayer_state, metal_eating_monster_state, fiddler_state</x:v>
+      </x:c>
+      <x:c r="D2" s="31" t="str">
+        <x:v>All five persistent progression states are required.</x:v>
       </x:c>
       <x:c r="E2" s="14"/>
       <x:c r="F2" s="14"/>
@@ -2767,17 +2975,17 @@
       <x:c r="Z2" s="14"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
-        <x:v>Super Swami</x:v>
-      </x:c>
-      <x:c r="B3" s="14" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="14" t="str">
-        <x:v>super_swami_state; super_swami_bonus; active_mode_*</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="str">
-        <x:v>Restored count, countdown, and next value moved into Python.</x:v>
+      <x:c r="A3" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
+      </x:c>
+      <x:c r="B3" s="31" t="str">
+        <x:v>Keep</x:v>
+      </x:c>
+      <x:c r="C3" s="31" t="str">
+        <x:v>the_web_tightens_state</x:v>
+      </x:c>
+      <x:c r="D3" s="31" t="str">
+        <x:v>Persistent mini-wizard completion state is required.</x:v>
       </x:c>
       <x:c r="E3" s="14"/>
       <x:c r="F3" s="14"/>
@@ -2803,17 +3011,17 @@
       <x:c r="Z3" s="14"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="14" t="str">
-        <x:v>Fifth Dimension Curse</x:v>
-      </x:c>
-      <x:c r="B4" s="14" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="14" t="str">
-        <x:v>fifth_dimension_curse_state; shared mini-wizard/active_mode counters</x:v>
-      </x:c>
-      <x:c r="D4" s="14" t="str">
-        <x:v>Zones, jackpots, target progress, add-a-ball state, and local Case File bonus moved into Python.</x:v>
+      <x:c r="A4" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
+      </x:c>
+      <x:c r="B4" s="31" t="str">
+        <x:v>Remove</x:v>
+      </x:c>
+      <x:c r="C4" s="31" t="str">
+        <x:v>the_web_tightens_case_file_bonus</x:v>
+      </x:c>
+      <x:c r="D4" s="31" t="str">
+        <x:v>Duplicates shared mini_wizard_case_file_bonus and a Python instance attribute.</x:v>
       </x:c>
       <x:c r="E4" s="14"/>
       <x:c r="F4" s="14"/>
@@ -2839,17 +3047,17 @@
       <x:c r="Z4" s="14"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14" t="str">
-        <x:v>Fakir</x:v>
-      </x:c>
-      <x:c r="B5" s="14" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:v>fakir_state; active_mode_*</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="str">
-        <x:v>Correct/incorrect counters and obsolete round/value variables removed from global player vars.</x:v>
+      <x:c r="A5" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
+      </x:c>
+      <x:c r="B5" s="31" t="str">
+        <x:v>Remove</x:v>
+      </x:c>
+      <x:c r="C5" s="31" t="str">
+        <x:v>the_web_tightens_jackpot_value</x:v>
+      </x:c>
+      <x:c r="D5" s="31" t="str">
+        <x:v>Computed from BASE_JACKPOT plus the shared case-file bonus; it does not need persistence or Godot export.</x:v>
       </x:c>
       <x:c r="E5" s="14"/>
       <x:c r="F5" s="14"/>
@@ -2874,6 +3082,34 @@
       <x:c r="Y5" s="14"/>
       <x:c r="Z5" s="14"/>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="31" t="str">
+        <x:v>Chapter 11 selection</x:v>
+      </x:c>
+      <x:c r="B6" s="31" t="str">
+        <x:v>Keep</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="str">
+        <x:v>chapter_11_unlocked, chapter_11_collected</x:v>
+      </x:c>
+      <x:c r="D6" s="31" t="str">
+        <x:v>Required by chapter-selection progression and display.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="31" t="str">
+        <x:v>Fiddler bonus</x:v>
+      </x:c>
+      <x:c r="B7" s="31" t="str">
+        <x:v>Keep</x:v>
+      </x:c>
+      <x:c r="C7" s="31" t="str">
+        <x:v>fiddler_bonus</x:v>
+      </x:c>
+      <x:c r="D7" s="31" t="str">
+        <x:v>Persistent end-of-ball Chapter 5 bonus bank.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2884,19 +3120,19 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="59" t="str">
         <x:v>Chapter</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
+      <x:c r="B1" s="59" t="str">
         <x:v>Villains Coded</x:v>
       </x:c>
-      <x:c r="C1" s="56" t="str">
+      <x:c r="C1" s="59" t="str">
         <x:v>Villains Remaining</x:v>
       </x:c>
-      <x:c r="D1" s="56" t="str">
+      <x:c r="D1" s="59" t="str">
         <x:v>Mini-Wizard</x:v>
       </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="E1" s="59" t="str">
         <x:v>Wizard Status</x:v>
       </x:c>
       <x:c r="F1" s="56"/>
@@ -2922,19 +3158,19 @@
       <x:c r="Z1" s="56"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="14" t="str">
+      <x:c r="A2" s="31" t="str">
         <x:v>Classic Rogues</x:v>
       </x:c>
-      <x:c r="B2" s="14" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C2" s="14" t="n">
+      <x:c r="C2" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="str">
+      <x:c r="D2" s="31" t="str">
         <x:v>Sinister Surge</x:v>
       </x:c>
-      <x:c r="E2" s="14" t="str">
+      <x:c r="E2" s="31" t="str">
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F2" s="14"/>
@@ -2960,19 +3196,19 @@
       <x:c r="Z2" s="14"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="A3" s="31" t="str">
         <x:v>Masked Masterminds</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="n">
+      <x:c r="C3" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D3" s="14" t="str">
+      <x:c r="D3" s="31" t="str">
         <x:v>Mastermind Trap</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="str">
+      <x:c r="E3" s="31" t="str">
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F3" s="14"/>
@@ -2998,19 +3234,19 @@
       <x:c r="Z3" s="14"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="14" t="str">
+      <x:c r="A4" s="31" t="str">
         <x:v>Trubble's Monsters</x:v>
       </x:c>
-      <x:c r="B4" s="14" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C4" s="14" t="n">
+      <x:c r="C4" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" s="14" t="str">
+      <x:c r="D4" s="31" t="str">
         <x:v>Trubble Unleashed</x:v>
       </x:c>
-      <x:c r="E4" s="14" t="str">
+      <x:c r="E4" s="31" t="str">
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F4" s="14"/>
@@ -3036,19 +3272,19 @@
       <x:c r="Z4" s="14"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14" t="str">
+      <x:c r="A5" s="31" t="str">
         <x:v>Crime Wave</x:v>
       </x:c>
-      <x:c r="B5" s="14" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C5" s="14" t="n">
+      <x:c r="C5" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D5" s="14" t="str">
-        <x:v>The Plotter - Master Plan</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="str">
+      <x:c r="D5" s="31" t="str">
+        <x:v>Crime Wave</x:v>
+      </x:c>
+      <x:c r="E5" s="31" t="str">
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F5" s="14"/>
@@ -3074,20 +3310,20 @@
       <x:c r="Z5" s="14"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="14" t="str">
-        <x:v>Mystic Menace</x:v>
-      </x:c>
-      <x:c r="B6" s="14" t="n">
+      <x:c r="A6" s="31" t="str">
+        <x:v>Danger Lurks</x:v>
+      </x:c>
+      <x:c r="B6" s="31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C6" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>Fifth Dimension Curse</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+      <x:c r="D6" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
+      </x:c>
+      <x:c r="E6" s="31" t="str">
+        <x:v>Working placeholder — full design needed</x:v>
       </x:c>
       <x:c r="F6" s="14"/>
       <x:c r="G6" s="14"/>
@@ -3112,20 +3348,20 @@
       <x:c r="Z6" s="14"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="14" t="str">
-        <x:v>Mad Science</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="n">
+      <x:c r="A7" s="31" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="B7" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="n">
+      <x:c r="C7" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="str">
-        <x:v>Mad Science Meltdown</x:v>
-      </x:c>
-      <x:c r="E7" s="14" t="str">
-        <x:v>Placeholder/simple — full design needed</x:v>
+      <x:c r="D7" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
+      </x:c>
+      <x:c r="E7" s="31" t="str">
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F7" s="14"/>
       <x:c r="G7" s="14"/>
@@ -3150,20 +3386,20 @@
       <x:c r="Z7" s="14"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="14" t="str">
-        <x:v>Elemental Chaos</x:v>
-      </x:c>
-      <x:c r="B8" s="14" t="n">
+      <x:c r="A8" s="31" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="B8" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="str">
-        <x:v>Nature Strikes Back</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="str">
-        <x:v>Placeholder/simple</x:v>
+      <x:c r="D8" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
+      </x:c>
+      <x:c r="E8" s="31" t="str">
+        <x:v>Placeholder/simple — full design needed</x:v>
       </x:c>
       <x:c r="F8" s="14"/>
       <x:c r="G8" s="14"/>
@@ -3188,20 +3424,20 @@
       <x:c r="Z8" s="14"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="14" t="str">
-        <x:v>Lost Worlds</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="n">
+      <x:c r="A9" s="31" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="B9" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="n">
+      <x:c r="C9" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="str">
-        <x:v>Invasion from Everywhere</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="str">
-        <x:v>Placeholder/simple</x:v>
+      <x:c r="D9" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
+      </x:c>
+      <x:c r="E9" s="31" t="str">
+        <x:v>Placeholder/simple — full design needed</x:v>
       </x:c>
       <x:c r="F9" s="14"/>
       <x:c r="G9" s="14"/>
@@ -3226,20 +3462,20 @@
       <x:c r="Z9" s="14"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="14" t="str">
-        <x:v>Savage Oddities</x:v>
-      </x:c>
-      <x:c r="B10" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="14" t="str">
-        <x:v>Who Is the Real Villain?</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="str">
-        <x:v>Placeholder/simple</x:v>
+      <x:c r="A10" s="31" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="B10" s="31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
+      </x:c>
+      <x:c r="E10" s="31" t="str">
+        <x:v>Placeholder/simple — full design needed</x:v>
       </x:c>
       <x:c r="F10" s="14"/>
       <x:c r="G10" s="14"/>
@@ -3264,20 +3500,20 @@
       <x:c r="Z10" s="14"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="14" t="str">
-        <x:v>Dimensional Finale</x:v>
-      </x:c>
-      <x:c r="B11" s="14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="14" t="str">
-        <x:v>Time-Tossed Showdown</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="str">
-        <x:v>Placeholder/simple</x:v>
+      <x:c r="A11" s="31" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="B11" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C11" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
+      </x:c>
+      <x:c r="E11" s="31" t="str">
+        <x:v>Placeholder/simple — full design needed</x:v>
       </x:c>
       <x:c r="F11" s="14"/>
       <x:c r="G11" s="14"/>
@@ -3300,6 +3536,23 @@
       <x:c r="X11" s="14"/>
       <x:c r="Y11" s="14"/>
       <x:c r="Z11" s="14"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="B12" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
+      </x:c>
+      <x:c r="E12" s="31" t="str">
+        <x:v>Placeholder/simple — full design needed</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3848,22 +4101,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="31" t="str">
-        <x:v>kingpin</x:v>
+        <x:v>master_plan</x:v>
       </x:c>
       <x:c r="F17" s="31" t="str">
-        <x:v>Kingpin</x:v>
+        <x:v>The Plotter</x:v>
       </x:c>
       <x:c r="G17" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented / simplified</x:v>
       </x:c>
       <x:c r="H17" s="31" t="str">
-        <x:v>Regular Crime Wave villain; area clears and Daily Bugle jackpots.</x:v>
+        <x:v>Pops build information. Two information plus a spinner hit lights one saucer. Collect three scheme jackpots, then shoot the Daily Bugle VUK for the Master Plan Super.</x:v>
       </x:c>
       <x:c r="I17" s="31" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>crime_wave</x:v>
       </x:c>
       <x:c r="J17" s="31" t="str">
-        <x:v>The Plotter - Master Plan</x:v>
+        <x:v>Crime Wave</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -3880,10 +4133,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E18" s="31" t="str">
-        <x:v>human_flies</x:v>
+        <x:v>fly_brothers</x:v>
       </x:c>
       <x:c r="F18" s="31" t="str">
-        <x:v>Human Flies</x:v>
+        <x:v>Fly Brothers</x:v>
       </x:c>
       <x:c r="G18" s="31" t="str">
         <x:v>Implemented / recent gate update</x:v>
@@ -3892,10 +4145,10 @@
         <x:v>Gate opens for upper-target access and closes when upper access is no longer needed.</x:v>
       </x:c>
       <x:c r="I18" s="31" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>crime_wave</x:v>
       </x:c>
       <x:c r="J18" s="31" t="str">
-        <x:v>The Plotter - Master Plan</x:v>
+        <x:v>Crime Wave</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3924,10 +4177,10 @@
         <x:v>Right bank reveals Phantom location; 5 rounds / More Jackpots extra round.</x:v>
       </x:c>
       <x:c r="I19" s="31" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>crime_wave</x:v>
       </x:c>
       <x:c r="J19" s="31" t="str">
-        <x:v>The Plotter - Master Plan</x:v>
+        <x:v>Crime Wave</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -3947,19 +4200,19 @@
         <x:v>enforcers</x:v>
       </x:c>
       <x:c r="F20" s="31" t="str">
-        <x:v>Enforcers / Ox</x:v>
+        <x:v>The Enforcers</x:v>
       </x:c>
       <x:c r="G20" s="31" t="str">
         <x:v>Implemented / needs light-color polish</x:v>
       </x:c>
       <x:c r="H20" s="31" t="str">
-        <x:v>Crime zones light upper-target jackpots; OX Super at center web.</x:v>
+        <x:v>Cowboy and Ox control three crime zones; zone clears light upper-target jackpots and build the OX Super at center web.</x:v>
       </x:c>
       <x:c r="I20" s="31" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>crime_wave</x:v>
       </x:c>
       <x:c r="J20" s="31" t="str">
-        <x:v>The Plotter - Master Plan</x:v>
+        <x:v>Crime Wave</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -3976,22 +4229,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E21" s="31" t="str">
-        <x:v>diamond_smugglers</x:v>
+        <x:v>doctor_cool</x:v>
       </x:c>
       <x:c r="F21" s="31" t="str">
-        <x:v>Diamond Smugglers</x:v>
+        <x:v>Doctor Cool</x:v>
       </x:c>
       <x:c r="G21" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H21" s="31" t="str">
-        <x:v>Drops/star bank diamond_bonus; saucer chase uses STAR freeze.</x:v>
+        <x:v>Drops build frozen-diamond value; completing the right 5-bank starts a moving saucer shipment chase. STAR freezes the chase and lights all three saucers briefly. Existing diamond_bonus bank is retained.</x:v>
       </x:c>
       <x:c r="I21" s="31" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>crime_wave</x:v>
       </x:c>
       <x:c r="J21" s="31" t="str">
-        <x:v>The Plotter - Master Plan</x:v>
+        <x:v>Crime Wave</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -3999,7 +4252,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B22" s="31" t="str">
-        <x:v>Mystic Menace</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C22" s="31" t="n">
         <x:v>1</x:v>
@@ -4008,22 +4261,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E22" s="31" t="str">
-        <x:v>pardo</x:v>
+        <x:v>harley_clivendon</x:v>
       </x:c>
       <x:c r="F22" s="31" t="str">
-        <x:v>Pardo</x:v>
+        <x:v>Harley Clivendon</x:v>
       </x:c>
       <x:c r="G22" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H22" s="31" t="str">
-        <x:v>Hypnosis Reel: spinner reveals true shot among 3 choices; 5 correct shots defeat Pardo; 7 wrong choices lets him escape.</x:v>
+        <x:v>The One-Eyed Idol / Fountain of Terror antagonist. Placeholder scoring is active; full design should use hypnosis, the idol, and hidden-scheme reveals.</x:v>
       </x:c>
       <x:c r="I22" s="31" t="str">
-        <x:v>fifth_dimension_curse</x:v>
+        <x:v>the_web_tightens</x:v>
       </x:c>
       <x:c r="J22" s="31" t="str">
-        <x:v>Fifth Dimension Curse</x:v>
+        <x:v>The Web Tightens</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4031,7 +4284,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B23" s="31" t="str">
-        <x:v>Mystic Menace</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C23" s="31" t="n">
         <x:v>2</x:v>
@@ -4040,22 +4293,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E23" s="31" t="str">
-        <x:v>fakir</x:v>
+        <x:v>conquistador</x:v>
       </x:c>
       <x:c r="F23" s="31" t="str">
-        <x:v>The Fakir</x:v>
+        <x:v>The Conquistador</x:v>
       </x:c>
       <x:c r="G23" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H23" s="31" t="str">
-        <x:v>2-ball Ruby Heist: saucers reveal upper rubies; spinners build value; 3 Ruby JPs light Super; continues until multiball ends.</x:v>
+        <x:v>Fountain of Terror antagonist. Placeholder scoring is active; full design should use the hidden fort, Fountain of Youth, and pursuit through the ruins.</x:v>
       </x:c>
       <x:c r="I23" s="31" t="str">
-        <x:v>fifth_dimension_curse</x:v>
+        <x:v>the_web_tightens</x:v>
       </x:c>
       <x:c r="J23" s="31" t="str">
-        <x:v>Fifth Dimension Curse</x:v>
+        <x:v>The Web Tightens</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4063,7 +4316,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B24" s="31" t="str">
-        <x:v>Mystic Menace</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C24" s="31" t="n">
         <x:v>3</x:v>
@@ -4072,22 +4325,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="E24" s="31" t="str">
-        <x:v>scarlet_sorcerer</x:v>
+        <x:v>spider_slayer</x:v>
       </x:c>
       <x:c r="F24" s="31" t="str">
-        <x:v>Scarlet Sorcerer</x:v>
+        <x:v>Spider-Slayer</x:v>
       </x:c>
       <x:c r="G24" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H24" s="31" t="str">
-        <x:v>Four unique demon shots appear one every 4 seconds and never relight. Demon JPs score 200K–350K; after four demons the gate opens for a 20-second 1M VUK Scepter Super. Case files add an optional fifth demon, larger values, 30 seconds, ball save, or timed Shot Assist.</x:v>
+        <x:v>Jameson-operated tracking robot. Placeholder scoring is active; full design should feature a moving hunt, capture pressure, and destroying the Slayer.</x:v>
       </x:c>
       <x:c r="I24" s="31" t="str">
-        <x:v>fifth_dimension_curse</x:v>
+        <x:v>the_web_tightens</x:v>
       </x:c>
       <x:c r="J24" s="31" t="str">
-        <x:v>Fifth Dimension Curse</x:v>
+        <x:v>The Web Tightens</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4095,7 +4348,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B25" s="31" t="str">
-        <x:v>Mystic Menace</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C25" s="31" t="n">
         <x:v>4</x:v>
@@ -4104,22 +4357,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="E25" s="31" t="str">
-        <x:v>super_swami</x:v>
+        <x:v>metal_eating_monster</x:v>
       </x:c>
       <x:c r="F25" s="31" t="str">
-        <x:v>Super Swami</x:v>
+        <x:v>Metal-Eating Monster</x:v>
       </x:c>
       <x:c r="G25" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H25" s="31" t="str">
-        <x:v>Restore six coordinate-based GI regions before the 40-second timer expires. First-time restoration values rise 100K–350K; Bigger starts at 200K, More Time gives 50 seconds, More Jackpots adds a 500K VUK Blackout Jackpot, Safety Net starts ball save, and Shot Assist spots an extra region.</x:v>
+        <x:v>Giant robot from Diet of Destruction. Placeholder scoring is active; full design should use consumed playfield areas, magnetic attacks, furnace heat, and the river finish.</x:v>
       </x:c>
       <x:c r="I25" s="31" t="str">
-        <x:v>fifth_dimension_curse</x:v>
+        <x:v>the_web_tightens</x:v>
       </x:c>
       <x:c r="J25" s="31" t="str">
-        <x:v>Fifth Dimension Curse</x:v>
+        <x:v>The Web Tightens</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4127,7 +4380,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B26" s="31" t="str">
-        <x:v>Mystic Menace</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C26" s="31" t="n">
         <x:v>5</x:v>
@@ -4136,22 +4389,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="E26" s="31" t="str">
-        <x:v>infinata</x:v>
+        <x:v>fiddler</x:v>
       </x:c>
       <x:c r="F26" s="31" t="str">
-        <x:v>Infinata</x:v>
+        <x:v>Fiddler</x:v>
       </x:c>
       <x:c r="G26" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H26" s="31" t="str">
-        <x:v>One green creature area lights at a time from pops, left drops, right drops, webs, and upper targets. Complete three to light all saucers for a 20-second 1M Super. More Jackpots adds a fourth optional area, Bigger raises values, More Time gives 30 seconds, Safety Net adds ball save, and Shot Assist awards the first two areas.</x:v>
+        <x:v>Fiddler on the Loose sound-and-ransom antagonist. Placeholder scoring is active. Persistent fiddler_bonus is wired into end-of-ball bonus and summary display; the full design will define musical sequences and how ransom is banked.</x:v>
       </x:c>
       <x:c r="I26" s="31" t="str">
-        <x:v>fifth_dimension_curse</x:v>
+        <x:v>the_web_tightens</x:v>
       </x:c>
       <x:c r="J26" s="31" t="str">
-        <x:v>Fifth Dimension Curse</x:v>
+        <x:v>The Web Tightens</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4159,7 +4412,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B27" s="31" t="str">
-        <x:v>Mad Science</x:v>
+        <x:v>Mystic Menace</x:v>
       </x:c>
       <x:c r="C27" s="31" t="n">
         <x:v>1</x:v>
@@ -4168,22 +4421,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E27" s="31" t="str">
-        <x:v>noah_boddy</x:v>
+        <x:v>pardo</x:v>
       </x:c>
       <x:c r="F27" s="31" t="str">
-        <x:v>Dr. Noah Boddy</x:v>
+        <x:v>Pardo</x:v>
       </x:c>
       <x:c r="G27" s="31" t="str">
-        <x:v>Implemented repurpose / needs polish</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Repurposed Mole Man concept; invisible/reveal/secret-shot mechanics.</x:v>
+        <x:v>Hypnosis Reel: spinner reveals true shot among 3 choices; 5 correct shots defeat Pardo; 7 wrong choices lets him escape.</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
-        <x:v>mad_science_meltdown</x:v>
+        <x:v>fifth_dimension_curse</x:v>
       </x:c>
       <x:c r="J27" s="31" t="str">
-        <x:v>Mad Science Meltdown</x:v>
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4191,7 +4444,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B28" s="31" t="str">
-        <x:v>Mad Science</x:v>
+        <x:v>Mystic Menace</x:v>
       </x:c>
       <x:c r="C28" s="31" t="n">
         <x:v>2</x:v>
@@ -4200,22 +4453,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E28" s="31" t="str">
-        <x:v>dr_magneto</x:v>
+        <x:v>fakir</x:v>
       </x:c>
       <x:c r="F28" s="31" t="str">
-        <x:v>Dr. Magneto</x:v>
+        <x:v>The Fantastic Fakir</x:v>
       </x:c>
       <x:c r="G28" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H28" s="31" t="str">
-        <x:v>Rooftop magnetic sweep: upper entrance resets both banks; each upper spin scores 50K and knocks down the next left-to-right target for another 50K. After seven steps only right drop 5 remains for a timed 1M Super. More Jackpots stages left drop 1 for a 500K Magnetic Flux Super.</x:v>
+        <x:v>2-ball Ruby Heist: saucers reveal upper rubies; spinners build value; 3 Ruby JPs light Super; continues until multiball ends.</x:v>
       </x:c>
       <x:c r="I28" s="31" t="str">
-        <x:v>mad_science_meltdown</x:v>
+        <x:v>fifth_dimension_curse</x:v>
       </x:c>
       <x:c r="J28" s="31" t="str">
-        <x:v>Mad Science Meltdown</x:v>
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -4223,7 +4476,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B29" s="31" t="str">
-        <x:v>Mad Science</x:v>
+        <x:v>Mystic Menace</x:v>
       </x:c>
       <x:c r="C29" s="31" t="n">
         <x:v>3</x:v>
@@ -4232,22 +4485,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E29" s="31" t="str">
-        <x:v>professor_pretoris</x:v>
+        <x:v>scarlet_sorcerer</x:v>
       </x:c>
       <x:c r="F29" s="31" t="str">
-        <x:v>Professor Pretoris</x:v>
+        <x:v>Kotep — The Scarlet Sorcerer</x:v>
       </x:c>
       <x:c r="G29" s="31" t="str">
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H29" s="31" t="str">
-        <x:v>Reactor Flood: GI starts red in eight horizontal bands. Each web-spinner hit turns the next band blue from bottom to top for 100K. After eight bands, center web lights for a 20-second 1M Super; More Jackpots adds a 10-second left-web Overflow Super.</x:v>
+        <x:v>Four unique demon shots appear one every 4 seconds and never relight. Demon JPs score 200K–350K; after four demons the gate opens for a 20-second 1M VUK Scepter Super. Case files add an optional fifth demon, larger values, 30 seconds, ball save, or timed Shot Assist.</x:v>
       </x:c>
       <x:c r="I29" s="31" t="str">
-        <x:v>mad_science_meltdown</x:v>
+        <x:v>fifth_dimension_curse</x:v>
       </x:c>
       <x:c r="J29" s="31" t="str">
-        <x:v>Mad Science Meltdown</x:v>
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4255,7 +4508,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B30" s="31" t="str">
-        <x:v>Mad Science</x:v>
+        <x:v>Mystic Menace</x:v>
       </x:c>
       <x:c r="C30" s="31" t="n">
         <x:v>4</x:v>
@@ -4264,22 +4517,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E30" s="31" t="str">
-        <x:v>doctor_dumpty</x:v>
+        <x:v>super_swami</x:v>
       </x:c>
       <x:c r="F30" s="31" t="str">
-        <x:v>Doctor Dumpty</x:v>
+        <x:v>Super Swami</x:v>
       </x:c>
       <x:c r="G30" s="31" t="str">
-        <x:v>Implemented repurpose / needs polish</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H30" s="31" t="str">
-        <x:v>Repurposed Blackwell; fragile puzzle / precision concept.</x:v>
+        <x:v>Restore six coordinate-based GI regions before the 40-second timer expires. First-time restoration values rise 100K–350K; Bigger starts at 200K, More Time gives 50 seconds, More Jackpots adds a 500K VUK Blackout Jackpot, Safety Net starts ball save, and Shot Assist spots an extra region.</x:v>
       </x:c>
       <x:c r="I30" s="31" t="str">
-        <x:v>mad_science_meltdown</x:v>
+        <x:v>fifth_dimension_curse</x:v>
       </x:c>
       <x:c r="J30" s="31" t="str">
-        <x:v>Mad Science Meltdown</x:v>
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4287,7 +4540,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B31" s="31" t="str">
-        <x:v>Mad Science</x:v>
+        <x:v>Mystic Menace</x:v>
       </x:c>
       <x:c r="C31" s="31" t="n">
         <x:v>5</x:v>
@@ -4296,22 +4549,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E31" s="31" t="str">
-        <x:v>dr_von_schlick</x:v>
+        <x:v>infinata</x:v>
       </x:c>
       <x:c r="F31" s="31" t="str">
-        <x:v>Dr. Von Schlick</x:v>
+        <x:v>Infinata</x:v>
       </x:c>
       <x:c r="G31" s="31" t="str">
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H31" s="31" t="str">
-        <x:v>Oil Pellet Chase: red GI and one green shot sweep left web, left drops, left pop, center web, right pop, and right drops, reversing every 4 seconds. Five pellets open the gate and light a timed VUK Super; the held-ball finish floods eight GI bands blue before awarding 1M.</x:v>
+        <x:v>One green creature area lights at a time from pops, left drops, right drops, webs, and upper targets. Complete three to light all saucers for a 20-second 1M Super. More Jackpots adds a fourth optional area, Bigger raises values, More Time gives 30 seconds, Safety Net adds ball save, and Shot Assist awards the first two areas.</x:v>
       </x:c>
       <x:c r="I31" s="31" t="str">
-        <x:v>mad_science_meltdown</x:v>
+        <x:v>fifth_dimension_curse</x:v>
       </x:c>
       <x:c r="J31" s="31" t="str">
-        <x:v>Mad Science Meltdown</x:v>
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4319,7 +4572,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B32" s="31" t="str">
-        <x:v>Elemental Chaos</x:v>
+        <x:v>Mad Science</x:v>
       </x:c>
       <x:c r="C32" s="31" t="n">
         <x:v>1</x:v>
@@ -4328,22 +4581,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="E32" s="31" t="str">
-        <x:v>radiation_specialist</x:v>
+        <x:v>noah_boddy</x:v>
       </x:c>
       <x:c r="F32" s="31" t="str">
-        <x:v>Radiation Specialist</x:v>
+        <x:v>Dr. Noah Boddy</x:v>
       </x:c>
       <x:c r="G32" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented repurpose / needs polish</x:v>
       </x:c>
       <x:c r="H32" s="31" t="str">
-        <x:v>Chapter 7 banked bonus variable is radiation_bonus.</x:v>
+        <x:v>Repurposed Mole Man concept; invisible/reveal/secret-shot mechanics.</x:v>
       </x:c>
       <x:c r="I32" s="31" t="str">
-        <x:v>nature_strikes_back</x:v>
+        <x:v>mad_science_meltdown</x:v>
       </x:c>
       <x:c r="J32" s="31" t="str">
-        <x:v>Nature Strikes Back</x:v>
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4351,7 +4604,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B33" s="31" t="str">
-        <x:v>Elemental Chaos</x:v>
+        <x:v>Mad Science</x:v>
       </x:c>
       <x:c r="C33" s="31" t="n">
         <x:v>2</x:v>
@@ -4360,22 +4613,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="E33" s="31" t="str">
-        <x:v>dr_zap</x:v>
+        <x:v>dr_magneto</x:v>
       </x:c>
       <x:c r="F33" s="31" t="str">
-        <x:v>Dr. Zap</x:v>
+        <x:v>Dr. Magneto</x:v>
       </x:c>
       <x:c r="G33" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H33" s="31" t="str">
-        <x:v>Needs full Elemental Chaos design.</x:v>
+        <x:v>Rooftop magnetic sweep: upper entrance resets both banks; each upper spin scores 50K and knocks down the next left-to-right target for another 50K. After seven steps only right drop 5 remains for a timed 1M Super. More Jackpots stages left drop 1 for a 500K Magnetic Flux Super.</x:v>
       </x:c>
       <x:c r="I33" s="31" t="str">
-        <x:v>nature_strikes_back</x:v>
+        <x:v>mad_science_meltdown</x:v>
       </x:c>
       <x:c r="J33" s="31" t="str">
-        <x:v>Nature Strikes Back</x:v>
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4383,7 +4636,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B34" s="31" t="str">
-        <x:v>Elemental Chaos</x:v>
+        <x:v>Mad Science</x:v>
       </x:c>
       <x:c r="C34" s="31" t="n">
         <x:v>3</x:v>
@@ -4392,22 +4645,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="E34" s="31" t="str">
-        <x:v>doctor_cool</x:v>
+        <x:v>professor_pretoris</x:v>
       </x:c>
       <x:c r="F34" s="31" t="str">
-        <x:v>Doctor Cool</x:v>
+        <x:v>Professor Pretoris</x:v>
       </x:c>
       <x:c r="G34" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H34" s="31" t="str">
-        <x:v>Needs full Elemental Chaos design.</x:v>
+        <x:v>Reactor Flood: GI starts red in eight horizontal bands. Each web-spinner hit turns the next band blue from bottom to top for 100K. After eight bands, center web lights for a 20-second 1M Super; More Jackpots adds a 10-second left-web Overflow Super.</x:v>
       </x:c>
       <x:c r="I34" s="31" t="str">
-        <x:v>nature_strikes_back</x:v>
+        <x:v>mad_science_meltdown</x:v>
       </x:c>
       <x:c r="J34" s="31" t="str">
-        <x:v>Nature Strikes Back</x:v>
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4415,7 +4668,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B35" s="31" t="str">
-        <x:v>Elemental Chaos</x:v>
+        <x:v>Mad Science</x:v>
       </x:c>
       <x:c r="C35" s="31" t="n">
         <x:v>4</x:v>
@@ -4424,22 +4677,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E35" s="31" t="str">
-        <x:v>snowman</x:v>
+        <x:v>doctor_dumpty</x:v>
       </x:c>
       <x:c r="F35" s="31" t="str">
-        <x:v>The Snowman</x:v>
+        <x:v>Doctor Dumpty</x:v>
       </x:c>
       <x:c r="G35" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented repurpose / needs polish</x:v>
       </x:c>
       <x:c r="H35" s="31" t="str">
-        <x:v>Needs full Elemental Chaos design.</x:v>
+        <x:v>Repurposed Blackwell; fragile puzzle / precision concept.</x:v>
       </x:c>
       <x:c r="I35" s="31" t="str">
-        <x:v>nature_strikes_back</x:v>
+        <x:v>mad_science_meltdown</x:v>
       </x:c>
       <x:c r="J35" s="31" t="str">
-        <x:v>Nature Strikes Back</x:v>
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4447,7 +4700,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B36" s="31" t="str">
-        <x:v>Elemental Chaos</x:v>
+        <x:v>Mad Science</x:v>
       </x:c>
       <x:c r="C36" s="31" t="n">
         <x:v>5</x:v>
@@ -4456,22 +4709,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E36" s="31" t="str">
-        <x:v>ice_monster</x:v>
+        <x:v>dr_von_schlick</x:v>
       </x:c>
       <x:c r="F36" s="31" t="str">
-        <x:v>The Ice Monster</x:v>
+        <x:v>Dr. Von Schlick</x:v>
       </x:c>
       <x:c r="G36" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H36" s="31" t="str">
-        <x:v>Needs full Elemental Chaos design.</x:v>
+        <x:v>Oil Pellet Chase: red GI and one green shot sweep left web, left drops, left pop, center web, right pop, and right drops, reversing every 4 seconds. Five pellets open the gate and light a timed VUK Super; the held-ball finish floods eight GI bands blue before awarding 1M.</x:v>
       </x:c>
       <x:c r="I36" s="31" t="str">
-        <x:v>nature_strikes_back</x:v>
+        <x:v>mad_science_meltdown</x:v>
       </x:c>
       <x:c r="J36" s="31" t="str">
-        <x:v>Nature Strikes Back</x:v>
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4479,7 +4732,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B37" s="31" t="str">
-        <x:v>Lost Worlds</x:v>
+        <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="C37" s="31" t="n">
         <x:v>1</x:v>
@@ -4488,22 +4741,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="E37" s="31" t="str">
-        <x:v>dr_manta</x:v>
+        <x:v>clive_blotto</x:v>
       </x:c>
       <x:c r="F37" s="31" t="str">
-        <x:v>Dr. Manta</x:v>
+        <x:v>Clive and Blotto</x:v>
       </x:c>
       <x:c r="G37" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H37" s="31" t="str">
-        <x:v>Needs full Lost Worlds design.</x:v>
+        <x:v>Former Radiation Specialist placeholder retained for later redesign. Clive creates the shape-changing tar creature Blotto with the Spirit Scope; Chapter 7 bank is now blotto_bonus.</x:v>
       </x:c>
       <x:c r="I37" s="31" t="str">
-        <x:v>invasion_from_everywhere</x:v>
+        <x:v>nature_strikes_back</x:v>
       </x:c>
       <x:c r="J37" s="31" t="str">
-        <x:v>Invasion from Everywhere</x:v>
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4511,7 +4764,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B38" s="31" t="str">
-        <x:v>Lost Worlds</x:v>
+        <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="C38" s="31" t="n">
         <x:v>2</x:v>
@@ -4520,22 +4773,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E38" s="31" t="str">
-        <x:v>doctor_atlantean</x:v>
+        <x:v>dr_zap</x:v>
       </x:c>
       <x:c r="F38" s="31" t="str">
-        <x:v>Doctor Atlantean</x:v>
+        <x:v>Doctor Zapp</x:v>
       </x:c>
       <x:c r="G38" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H38" s="31" t="str">
-        <x:v>Needs full Lost Worlds design.</x:v>
+        <x:v>Electrical/weather slot. Full rules still need design around Zapp stealing and activating Irving Caldwell's invention.</x:v>
       </x:c>
       <x:c r="I38" s="31" t="str">
-        <x:v>invasion_from_everywhere</x:v>
+        <x:v>nature_strikes_back</x:v>
       </x:c>
       <x:c r="J38" s="31" t="str">
-        <x:v>Invasion from Everywhere</x:v>
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4543,7 +4796,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B39" s="31" t="str">
-        <x:v>Lost Worlds</x:v>
+        <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="C39" s="31" t="n">
         <x:v>3</x:v>
@@ -4552,22 +4805,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E39" s="31" t="str">
-        <x:v>sky_master</x:v>
+        <x:v>voltan_boomer</x:v>
       </x:c>
       <x:c r="F39" s="31" t="str">
-        <x:v>Sky Master</x:v>
+        <x:v>Voltan and Boomer</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Needs full Lost Worlds design.</x:v>
+        <x:v>Former elemental freeze placeholder retained for later redesign. Thunder Rumble story pair; robberies are hidden inside violent storms and thunderbolt attacks.</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
-        <x:v>invasion_from_everywhere</x:v>
+        <x:v>nature_strikes_back</x:v>
       </x:c>
       <x:c r="J39" s="31" t="str">
-        <x:v>Invasion from Everywhere</x:v>
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4575,7 +4828,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B40" s="31" t="str">
-        <x:v>Lost Worlds</x:v>
+        <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="C40" s="31" t="n">
         <x:v>4</x:v>
@@ -4584,22 +4837,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="E40" s="31" t="str">
-        <x:v>plutonians</x:v>
+        <x:v>snowman</x:v>
       </x:c>
       <x:c r="F40" s="31" t="str">
-        <x:v>The Plutonians</x:v>
+        <x:v>The Snowman</x:v>
       </x:c>
       <x:c r="G40" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H40" s="31" t="str">
-        <x:v>Chapter 8 banked bonus variable is plutonians_bonus.</x:v>
+        <x:v>Snow/weather slot. Living snow creature grows with snowfall and is defeated by draining its electrical charge.</x:v>
       </x:c>
       <x:c r="I40" s="31" t="str">
-        <x:v>invasion_from_everywhere</x:v>
+        <x:v>nature_strikes_back</x:v>
       </x:c>
       <x:c r="J40" s="31" t="str">
-        <x:v>Invasion from Everywhere</x:v>
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4607,7 +4860,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B41" s="31" t="str">
-        <x:v>Lost Worlds</x:v>
+        <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="C41" s="31" t="n">
         <x:v>5</x:v>
@@ -4616,22 +4869,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E41" s="31" t="str">
-        <x:v>antarcticans</x:v>
+        <x:v>plutonians</x:v>
       </x:c>
       <x:c r="F41" s="31" t="str">
-        <x:v>The Antarcticans</x:v>
+        <x:v>The Plutonians</x:v>
       </x:c>
       <x:c r="G41" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>Needs full Lost Worlds design.</x:v>
+        <x:v>Former Ice Monster placeholder retained under the canonical Plutonians identity. Ice-themed encounter should ultimately resolve by helping repair their escape rather than treating them as purely evil.</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
-        <x:v>invasion_from_everywhere</x:v>
+        <x:v>nature_strikes_back</x:v>
       </x:c>
       <x:c r="J41" s="31" t="str">
-        <x:v>Invasion from Everywhere</x:v>
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4639,7 +4892,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B42" s="31" t="str">
-        <x:v>Savage Oddities</x:v>
+        <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="C42" s="31" t="n">
         <x:v>1</x:v>
@@ -4648,22 +4901,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="E42" s="31" t="str">
-        <x:v>charles_cameo</x:v>
+        <x:v>dr_manta</x:v>
       </x:c>
       <x:c r="F42" s="31" t="str">
-        <x:v>Charles Cameo</x:v>
+        <x:v>Dr. Manta</x:v>
       </x:c>
       <x:c r="G42" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H42" s="31" t="str">
-        <x:v>Needs full Savage Oddities design.</x:v>
+        <x:v>Phantom from the Depths of Time villain. Dr. Manta rules the hidden city and uses robotic creatures to freeze and enslave its people.</x:v>
       </x:c>
       <x:c r="I42" s="31" t="str">
-        <x:v>who_is_the_real_villain</x:v>
+        <x:v>invasion_from_everywhere</x:v>
       </x:c>
       <x:c r="J42" s="31" t="str">
-        <x:v>Who Is the Real Villain?</x:v>
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4671,7 +4924,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B43" s="31" t="str">
-        <x:v>Savage Oddities</x:v>
+        <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="C43" s="31" t="n">
         <x:v>2</x:v>
@@ -4680,22 +4933,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="E43" s="31" t="str">
-        <x:v>brutus</x:v>
+        <x:v>igor</x:v>
       </x:c>
       <x:c r="F43" s="31" t="str">
-        <x:v>Brutus</x:v>
+        <x:v>Igor</x:v>
       </x:c>
       <x:c r="G43" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H43" s="31" t="str">
-        <x:v>Needs full Savage Oddities design.</x:v>
+        <x:v>Dr. Manta's assistant from the same episode. Moved from Chapter 9 and corrected from Eigor.</x:v>
       </x:c>
       <x:c r="I43" s="31" t="str">
-        <x:v>who_is_the_real_villain</x:v>
+        <x:v>invasion_from_everywhere</x:v>
       </x:c>
       <x:c r="J43" s="31" t="str">
-        <x:v>Who Is the Real Villain?</x:v>
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4703,7 +4956,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B44" s="31" t="str">
-        <x:v>Savage Oddities</x:v>
+        <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="C44" s="31" t="n">
         <x:v>3</x:v>
@@ -4712,22 +4965,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="E44" s="31" t="str">
-        <x:v>eigor</x:v>
+        <x:v>doctor_atlantean</x:v>
       </x:c>
       <x:c r="F44" s="31" t="str">
-        <x:v>Eigor</x:v>
+        <x:v>Doctor Atlantean</x:v>
       </x:c>
       <x:c r="G44" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H44" s="31" t="str">
-        <x:v>Needs full Savage Oddities design.</x:v>
+        <x:v>Atlantean invasion from Up from Nowhere; attempts to dome Manhattan and sink it beneath the sea.</x:v>
       </x:c>
       <x:c r="I44" s="31" t="str">
-        <x:v>who_is_the_real_villain</x:v>
+        <x:v>invasion_from_everywhere</x:v>
       </x:c>
       <x:c r="J44" s="31" t="str">
-        <x:v>Who Is the Real Villain?</x:v>
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4735,7 +4988,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B45" s="31" t="str">
-        <x:v>Savage Oddities</x:v>
+        <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="C45" s="31" t="n">
         <x:v>4</x:v>
@@ -4744,22 +4997,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E45" s="31" t="str">
-        <x:v>the_fly</x:v>
+        <x:v>devargas</x:v>
       </x:c>
       <x:c r="F45" s="31" t="str">
-        <x:v>The Fly</x:v>
+        <x:v>DeVargas</x:v>
       </x:c>
       <x:c r="G45" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H45" s="31" t="str">
-        <x:v>Rooftop Swarm: saucers open roof gate; upper entrance starts 10/15-flip roof attempt; 3 upper targets score JPs/Super boosted by remaining flips.</x:v>
+        <x:v>Ruler of the hidden Cloud City of Gold. Former Chapter 8 open placeholder retained for later episode-based design.</x:v>
       </x:c>
       <x:c r="I45" s="31" t="str">
-        <x:v>who_is_the_real_villain</x:v>
+        <x:v>invasion_from_everywhere</x:v>
       </x:c>
       <x:c r="J45" s="31" t="str">
-        <x:v>Who Is the Real Villain?</x:v>
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4767,7 +5020,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B46" s="31" t="str">
-        <x:v>Savage Oddities</x:v>
+        <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="C46" s="31" t="n">
         <x:v>5</x:v>
@@ -4776,22 +5029,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E46" s="31" t="str">
-        <x:v>swamp_reptiles</x:v>
+        <x:v>molemen</x:v>
       </x:c>
       <x:c r="F46" s="31" t="str">
-        <x:v>Swamp Reptiles</x:v>
+        <x:v>Molemen</x:v>
       </x:c>
       <x:c r="G46" s="31" t="str">
-        <x:v>Implemented repurpose / needs polish</x:v>
+        <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Repurposed Reptilla; real code retained under new name; swamp_bonus bank.</x:v>
+        <x:v>Underground-world mode associated with Mugs Reilly and the Molemen. Compact live name remains Molemen.</x:v>
       </x:c>
       <x:c r="I46" s="31" t="str">
-        <x:v>who_is_the_real_villain</x:v>
+        <x:v>invasion_from_everywhere</x:v>
       </x:c>
       <x:c r="J46" s="31" t="str">
-        <x:v>Who Is the Real Villain?</x:v>
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -4799,7 +5052,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="31" t="str">
-        <x:v>Dimensional Finale</x:v>
+        <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="C47" s="31" t="n">
         <x:v>1</x:v>
@@ -4808,22 +5061,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E47" s="31" t="str">
-        <x:v>phantom_from_depths_of_time</x:v>
+        <x:v>charles_cameo</x:v>
       </x:c>
       <x:c r="F47" s="31" t="str">
-        <x:v>Phantom from the Depths of Time</x:v>
+        <x:v>Charles Cameo</x:v>
       </x:c>
       <x:c r="G47" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H47" s="31" t="str">
-        <x:v>Needs full Dimensional Finale design.</x:v>
+        <x:v>Identity and disguise mode from Double Identity; remains grouped with Brutus.</x:v>
       </x:c>
       <x:c r="I47" s="31" t="str">
-        <x:v>time_tossed_showdown</x:v>
+        <x:v>who_is_the_real_villain</x:v>
       </x:c>
       <x:c r="J47" s="31" t="str">
-        <x:v>Time-Tossed Showdown</x:v>
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -4831,7 +5084,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B48" s="31" t="str">
-        <x:v>Dimensional Finale</x:v>
+        <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="C48" s="31" t="n">
         <x:v>2</x:v>
@@ -4840,22 +5093,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="E48" s="31" t="str">
-        <x:v>master_vine</x:v>
+        <x:v>brutus</x:v>
       </x:c>
       <x:c r="F48" s="31" t="str">
-        <x:v>Master Vine</x:v>
+        <x:v>Brutus</x:v>
       </x:c>
       <x:c r="G48" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H48" s="31" t="str">
-        <x:v>Needs full Dimensional Finale design.</x:v>
+        <x:v>Charles Cameo's bodyguard from Double Identity; direct physical/bashing role.</x:v>
       </x:c>
       <x:c r="I48" s="31" t="str">
-        <x:v>time_tossed_showdown</x:v>
+        <x:v>who_is_the_real_villain</x:v>
       </x:c>
       <x:c r="J48" s="31" t="str">
-        <x:v>Time-Tossed Showdown</x:v>
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -4863,7 +5116,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B49" s="31" t="str">
-        <x:v>Dimensional Finale</x:v>
+        <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="C49" s="31" t="n">
         <x:v>3</x:v>
@@ -4872,22 +5125,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E49" s="31" t="str">
-        <x:v>master_technician</x:v>
+        <x:v>desperado</x:v>
       </x:c>
       <x:c r="F49" s="31" t="str">
-        <x:v>Master Technician</x:v>
+        <x:v>Desperado</x:v>
       </x:c>
       <x:c r="G49" s="31" t="str">
-        <x:v>Implemented repurpose / needs polish</x:v>
+        <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H49" s="31" t="str">
-        <x:v>Repurposed Meteor homage: drops determine spinner value; technician_bonus bank.</x:v>
+        <x:v>Former Skymaster placeholder retained for redesign. Hypnotic cowboy robber rides a flying mechanical horse.</x:v>
       </x:c>
       <x:c r="I49" s="31" t="str">
-        <x:v>time_tossed_showdown</x:v>
+        <x:v>who_is_the_real_villain</x:v>
       </x:c>
       <x:c r="J49" s="31" t="str">
-        <x:v>Time-Tossed Showdown</x:v>
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -4895,7 +5148,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B50" s="31" t="str">
-        <x:v>Dimensional Finale</x:v>
+        <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="C50" s="31" t="n">
         <x:v>4</x:v>
@@ -4904,22 +5157,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E50" s="31" t="str">
-        <x:v>micro_men</x:v>
+        <x:v>skymaster</x:v>
       </x:c>
       <x:c r="F50" s="31" t="str">
-        <x:v>Micro-Men</x:v>
+        <x:v>Skymaster</x:v>
       </x:c>
       <x:c r="G50" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H50" s="31" t="str">
-        <x:v>Needs full Dimensional Finale design.</x:v>
+        <x:v>Former The Fly Rooftop Swarm rules rethemed as a limited-flip assault on Skymaster's blimp. Saucers open access; three upper targets score Jackpots and a remaining-flips Super.</x:v>
       </x:c>
       <x:c r="I50" s="31" t="str">
-        <x:v>time_tossed_showdown</x:v>
+        <x:v>who_is_the_real_villain</x:v>
       </x:c>
       <x:c r="J50" s="31" t="str">
-        <x:v>Time-Tossed Showdown</x:v>
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -4927,7 +5180,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B51" s="31" t="str">
-        <x:v>Dimensional Finale</x:v>
+        <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="C51" s="31" t="n">
         <x:v>5</x:v>
@@ -4936,21 +5189,181 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E51" s="31" t="str">
-        <x:v>grand_emperor</x:v>
+        <x:v>swamp_reptiles</x:v>
       </x:c>
       <x:c r="F51" s="31" t="str">
-        <x:v>Grand Emperor</x:v>
+        <x:v>Swamp Reptiles</x:v>
       </x:c>
       <x:c r="G51" s="31" t="str">
+        <x:v>Implemented repurpose / needs polish</x:v>
+      </x:c>
+      <x:c r="H51" s="31" t="str">
+        <x:v>Repurposed Reptilla; real code retained under new name; swamp_bonus bank.</x:v>
+      </x:c>
+      <x:c r="I51" s="31" t="str">
+        <x:v>who_is_the_real_villain</x:v>
+      </x:c>
+      <x:c r="J51" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B52" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C52" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D52" s="31" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E52" s="31" t="str">
+        <x:v>sir_galahad</x:v>
+      </x:c>
+      <x:c r="F52" s="31" t="str">
+        <x:v>Sir Galahad</x:v>
+      </x:c>
+      <x:c r="G52" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
-      <x:c r="H51" s="31" t="str">
-        <x:v>Needs full Dimensional Finale design.</x:v>
-      </x:c>
-      <x:c r="I51" s="31" t="str">
+      <x:c r="H52" s="31" t="str">
+        <x:v>Knight Must Fall medieval time-displacement slot. Placeholder rules retained until the full Sir Galahad mode is designed.</x:v>
+      </x:c>
+      <x:c r="I52" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
       </x:c>
-      <x:c r="J51" s="31" t="str">
+      <x:c r="J52" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B53" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C53" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D53" s="31" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E53" s="31" t="str">
+        <x:v>master_vine</x:v>
+      </x:c>
+      <x:c r="F53" s="31" t="str">
+        <x:v>Master Vine</x:v>
+      </x:c>
+      <x:c r="G53" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="H53" s="31" t="str">
+        <x:v>Prehistoric Forbidden City and spreading-vine story from Vine. Full episode-based design still needed.</x:v>
+      </x:c>
+      <x:c r="I53" s="31" t="str">
+        <x:v>time_tossed_showdown</x:v>
+      </x:c>
+      <x:c r="J53" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B54" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C54" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D54" s="31" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E54" s="31" t="str">
+        <x:v>master_technician</x:v>
+      </x:c>
+      <x:c r="F54" s="31" t="str">
+        <x:v>Master Technician</x:v>
+      </x:c>
+      <x:c r="G54" s="31" t="str">
+        <x:v>Implemented repurpose / needs polish</x:v>
+      </x:c>
+      <x:c r="H54" s="31" t="str">
+        <x:v>Working drop-built spinner-value mode retained. Theme draws from Swing City and Manhattan being lifted into the sky.</x:v>
+      </x:c>
+      <x:c r="I54" s="31" t="str">
+        <x:v>time_tossed_showdown</x:v>
+      </x:c>
+      <x:c r="J54" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B55" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C55" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D55" s="31" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E55" s="31" t="str">
+        <x:v>spider_men</x:v>
+      </x:c>
+      <x:c r="F55" s="31" t="str">
+        <x:v>The Spider-Men</x:v>
+      </x:c>
+      <x:c r="G55" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="H55" s="31" t="str">
+        <x:v>Alien Spider-Men from Home. Placeholder rules retained; final design should focus on identifying the real Spider-Man and resolving the encounter.</x:v>
+      </x:c>
+      <x:c r="I55" s="31" t="str">
+        <x:v>time_tossed_showdown</x:v>
+      </x:c>
+      <x:c r="J55" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B56" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C56" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D56" s="31" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E56" s="31" t="str">
+        <x:v>von_rantenraven</x:v>
+      </x:c>
+      <x:c r="F56" s="31" t="str">
+        <x:v>Baron Von Rantenraven</x:v>
+      </x:c>
+      <x:c r="G56" s="31" t="str">
+        <x:v>Placeholder/simple active mode</x:v>
+      </x:c>
+      <x:c r="H56" s="31" t="str">
+        <x:v>Sky Harbor's World War I aerial invasion and paralysis technology. Placeholder rules retained until full design.</x:v>
+      </x:c>
+      <x:c r="I56" s="31" t="str">
+        <x:v>time_tossed_showdown</x:v>
+      </x:c>
+      <x:c r="J56" s="31" t="str">
         <x:v>Time-Tossed Showdown</x:v>
       </x:c>
     </x:row>
@@ -5080,19 +5493,19 @@
         <x:v>Crime Wave</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>crime_wave</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
-        <x:v>The Plotter - Master Plan</x:v>
+        <x:v>Crime Wave</x:v>
       </x:c>
       <x:c r="E5" s="31" t="str">
-        <x:v>start_mode_master_plan</x:v>
+        <x:v>start_mode_crime_wave</x:v>
       </x:c>
       <x:c r="F5" s="31" t="str">
         <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G5" s="31" t="str">
-        <x:v>Implemented; headlines/schemes/Daily Bugle super flow present.</x:v>
+        <x:v>Implemented 3-ball multiball. Five timed villain areas: Plotter/pops, Fly Brothers/upper targets, Fifth Avenue Phantom/right bank, Enforcers/left bank, Doctor Cool/saucers. Gate opens at 3+ lit areas and closes at 1 or 0. Upper exits collect jackpots based on currently lit areas. Saucers hold for 15 seconds.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5100,22 +5513,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="31" t="str">
-        <x:v>Mystic Menace</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C6" s="31" t="str">
-        <x:v>fifth_dimension_curse</x:v>
+        <x:v>the_web_tightens</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
-        <x:v>Fifth Dimension Curse</x:v>
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="E6" s="31" t="str">
-        <x:v>start_mode_fifth_dimension_curse</x:v>
+        <x:v>start_mode_the_web_tightens</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
         <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Implemented / needs playtest. Starts 3-ball multiball. Six GI zones stay bright 5s, flicker 3s, then dim independently. VUK jackpots score 500K–1.75M plus the chapter Case File bonus without clearing zones. Upper targets score 100K + 25K per active zone, pulse purple when unhit, turn solid when hit, flash three times on completion, and can award up to three add-a-balls after 3+ zone jackpots. Ends when down to one ball.</x:v>
+        <x:v>Working placeholder mini-wizard. Temporary jackpot and Case File values remain in Python/shared mini-wizard variables; no mode-specific display variables are exported to Godot.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5123,22 +5536,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="31" t="str">
-        <x:v>Mad Science</x:v>
+        <x:v>Mystic Menace</x:v>
       </x:c>
       <x:c r="C7" s="31" t="str">
-        <x:v>mad_science_meltdown</x:v>
+        <x:v>fifth_dimension_curse</x:v>
       </x:c>
       <x:c r="D7" s="31" t="str">
-        <x:v>Mad Science Meltdown</x:v>
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="E7" s="31" t="str">
-        <x:v>start_mode_mad_science_meltdown</x:v>
+        <x:v>start_mode_fifth_dimension_curse</x:v>
       </x:c>
       <x:c r="F7" s="31" t="str">
         <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G7" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Implemented / needs playtest. Starts 3-ball multiball. Six GI zones stay bright 5s, flicker 3s, then dim independently. VUK jackpots score 500K–1.75M plus the chapter Case File bonus without clearing zones. Upper targets score 100K + 25K per active zone, pulse purple when unhit, turn solid when hit, flash three times on completion, and can award up to three add-a-balls after 3+ zone jackpots. Ends when down to one ball.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -5146,16 +5559,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="31" t="str">
-        <x:v>Elemental Chaos</x:v>
+        <x:v>Mad Science</x:v>
       </x:c>
       <x:c r="C8" s="31" t="str">
-        <x:v>nature_strikes_back</x:v>
+        <x:v>mad_science_meltdown</x:v>
       </x:c>
       <x:c r="D8" s="31" t="str">
-        <x:v>Nature Strikes Back</x:v>
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="E8" s="31" t="str">
-        <x:v>start_mode_nature_strikes_back</x:v>
+        <x:v>start_mode_mad_science_meltdown</x:v>
       </x:c>
       <x:c r="F8" s="31" t="str">
         <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
@@ -5169,16 +5582,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="31" t="str">
-        <x:v>Lost Worlds</x:v>
+        <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="C9" s="31" t="str">
-        <x:v>invasion_from_everywhere</x:v>
+        <x:v>nature_strikes_back</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
-        <x:v>Invasion from Everywhere</x:v>
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="E9" s="31" t="str">
-        <x:v>start_mode_invasion_from_everywhere</x:v>
+        <x:v>start_mode_nature_strikes_back</x:v>
       </x:c>
       <x:c r="F9" s="31" t="str">
         <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
@@ -5192,16 +5605,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="31" t="str">
-        <x:v>Savage Oddities</x:v>
+        <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="C10" s="31" t="str">
-        <x:v>who_is_the_real_villain</x:v>
+        <x:v>invasion_from_everywhere</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
-        <x:v>Who Is the Real Villain?</x:v>
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="E10" s="31" t="str">
-        <x:v>start_mode_who_is_the_real_villain</x:v>
+        <x:v>start_mode_invasion_from_everywhere</x:v>
       </x:c>
       <x:c r="F10" s="31" t="str">
         <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
@@ -5215,16 +5628,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="31" t="str">
-        <x:v>Dimensional Finale</x:v>
+        <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="C11" s="31" t="str">
-        <x:v>time_tossed_showdown</x:v>
+        <x:v>who_is_the_real_villain</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
-        <x:v>Time-Tossed Showdown</x:v>
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="E11" s="31" t="str">
-        <x:v>start_mode_time_tossed_showdown</x:v>
+        <x:v>start_mode_who_is_the_real_villain</x:v>
       </x:c>
       <x:c r="F11" s="31" t="str">
         <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
@@ -5234,26 +5647,49 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="31" t="str">
+      <x:c r="A12" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C12" s="31" t="str">
+        <x:v>time_tossed_showdown</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
+      </x:c>
+      <x:c r="E12" s="31" t="str">
+        <x:v>start_mode_time_tossed_showdown</x:v>
+      </x:c>
+      <x:c r="F12" s="31" t="str">
+        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+      </x:c>
+      <x:c r="G12" s="31" t="str">
+        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="31" t="str">
         <x:v>Final</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="str">
+      <x:c r="B13" s="31" t="str">
         <x:v>After chapters</x:v>
       </x:c>
-      <x:c r="C12" s="31" t="str">
+      <x:c r="C13" s="31" t="str">
         <x:v>final_showdown</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="str">
-        <x:v>Final Showdown</x:v>
-      </x:c>
-      <x:c r="E12" s="31" t="str">
+      <x:c r="D13" s="31" t="str">
+        <x:v>Kingpin</x:v>
+      </x:c>
+      <x:c r="E13" s="31" t="str">
         <x:v>start_mode_final_showdown</x:v>
       </x:c>
-      <x:c r="F12" s="31" t="str">
-        <x:v>Separate final wizard; Kingpin remains a regular Chapter 4 villain.</x:v>
-      </x:c>
-      <x:c r="G12" s="31" t="str">
-        <x:v>Implemented structurally; playtest/polish later.</x:v>
+      <x:c r="F13" s="31" t="str">
+        <x:v>Separate final wizard after all 11 chapter wizards.</x:v>
+      </x:c>
+      <x:c r="G13" s="31" t="str">
+        <x:v>Existing Final Showdown structure is now reserved for the Kingpin finale and will be rethemed in a later design pass.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5335,7 +5771,7 @@
         <x:v>master_plan</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>The Plotter - Master Plan</x:v>
+        <x:v>Plotter's Master Plan</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
         <x:v>Foswell rumor/headline economy repurposed as Chapter 4 wizard.</x:v>
@@ -5349,10 +5785,10 @@
         <x:v>fakir</x:v>
       </x:c>
       <x:c r="C6" s="31" t="str">
-        <x:v>The Fakir</x:v>
+        <x:v>The Fantastic Fakir</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
-        <x:v>Old Miss Trubble puzzle gameplay repurposed into Fakir.</x:v>
+        <x:v>Old Ms. Trubble puzzle gameplay repurposed into The Fantastic Fakir's Ruby Heist.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5388,27 +5824,27 @@
         <x:v>fly_twins</x:v>
       </x:c>
       <x:c r="B9" s="31" t="str">
-        <x:v>human_flies</x:v>
+        <x:v>fly_brothers</x:v>
       </x:c>
       <x:c r="C9" s="31" t="str">
-        <x:v>Human Flies</x:v>
+        <x:v>Fly Brothers</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
-        <x:v>Human Flies / Fly Brothers key and display standardized.</x:v>
+        <x:v>Human Flies renamed to Fly Brothers; internal mode key, events, player variables, display text, and widget standardized.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="31" t="str">
-        <x:v>fiddler</x:v>
+        <x:v>diamond_smugglers</x:v>
       </x:c>
       <x:c r="B10" s="31" t="str">
-        <x:v>diamond_smugglers</x:v>
+        <x:v>doctor_cool</x:v>
       </x:c>
       <x:c r="C10" s="31" t="str">
-        <x:v>Diamond Smugglers</x:v>
+        <x:v>Doctor Cool</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
-        <x:v>Old temporary alias removed; consistent Crime Wave slot.</x:v>
+        <x:v>Diamond Smugglers ruleset repurposed for Doctor Cool: drops build frozen diamonds, the 5-bank starts a moving shipment chase, and STAR freezes all saucers.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5423,6 +5859,286 @@
       </x:c>
       <x:c r="D11" s="31" t="str">
         <x:v>Old wizard alias replaced by explicit Trubble Unleashed key.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="31" t="str">
+        <x:v>radiation_specialist</x:v>
+      </x:c>
+      <x:c r="B12" s="31" t="str">
+        <x:v>clive_blotto</x:v>
+      </x:c>
+      <x:c r="C12" s="31" t="str">
+        <x:v>Clive and Blotto</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="str">
+        <x:v>Radiation Specialist duplicate removed; placeholder mechanics and Chapter 8 bonus bank preserved for later Blotto redesign.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="31" t="str">
+        <x:v>elemental_freeze_placeholder</x:v>
+      </x:c>
+      <x:c r="B13" s="31" t="str">
+        <x:v>voltan_boomer</x:v>
+      </x:c>
+      <x:c r="C13" s="31" t="str">
+        <x:v>Voltan and Boomer</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="str">
+        <x:v>Neutral Elemental placeholder assigned to the Thunder Rumble story pair.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="31" t="str">
+        <x:v>ice_monster</x:v>
+      </x:c>
+      <x:c r="B14" s="31" t="str">
+        <x:v>plutonians</x:v>
+      </x:c>
+      <x:c r="C14" s="31" t="str">
+        <x:v>The Plutonians</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="str">
+        <x:v>Ice Monster renamed to the canonical Plutonians identity.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="31" t="str">
+        <x:v>eigor</x:v>
+      </x:c>
+      <x:c r="B15" s="31" t="str">
+        <x:v>igor</x:v>
+      </x:c>
+      <x:c r="C15" s="31" t="str">
+        <x:v>Igor</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="str">
+        <x:v>Spelling corrected and mode grouped with Dr. Manta in Chapter 9 beside Dr. Manta.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="31" t="str">
+        <x:v>lost_worlds_replacement</x:v>
+      </x:c>
+      <x:c r="B16" s="31" t="str">
+        <x:v>devargas</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="str">
+        <x:v>DeVargas</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="str">
+        <x:v>Former Lost Worlds open placeholder assigned to DeVargas of the Cloud City of Gold.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="31" t="str">
+        <x:v>antarcticans</x:v>
+      </x:c>
+      <x:c r="B17" s="31" t="str">
+        <x:v>molemen</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="str">
+        <x:v>Molemen</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="str">
+        <x:v>Unverified Antarcticans identity replaced by Molemen; placeholder gameplay retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="31" t="str">
+        <x:v>sky_master</x:v>
+      </x:c>
+      <x:c r="B18" s="31" t="str">
+        <x:v>desperado</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="str">
+        <x:v>Desperado</x:v>
+      </x:c>
+      <x:c r="D18" s="31" t="str">
+        <x:v>Original Skymaster placeholder mechanics preserved for future Desperado redesign.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="31" t="str">
+        <x:v>the_fly</x:v>
+      </x:c>
+      <x:c r="B19" s="31" t="str">
+        <x:v>skymaster</x:v>
+      </x:c>
+      <x:c r="C19" s="31" t="str">
+        <x:v>Skymaster</x:v>
+      </x:c>
+      <x:c r="D19" s="31" t="str">
+        <x:v>Working limited-flip Rooftop Swarm mechanics rethemed as an assault on Skymaster's blimp.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="31" t="str">
+        <x:v>mugs_reilly_and_molemen</x:v>
+      </x:c>
+      <x:c r="B20" s="31" t="str">
+        <x:v>molemen</x:v>
+      </x:c>
+      <x:c r="C20" s="31" t="str">
+        <x:v>Molemen</x:v>
+      </x:c>
+      <x:c r="D20" s="31" t="str">
+        <x:v>Compact widget and mode name; Mugs Reilly can appear on selection, intro, and summary screens.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="31" t="str">
+        <x:v>phantom_from_depths_of_time</x:v>
+      </x:c>
+      <x:c r="B21" s="31" t="str">
+        <x:v>sir_galahad</x:v>
+      </x:c>
+      <x:c r="C21" s="31" t="str">
+        <x:v>Sir Galahad</x:v>
+      </x:c>
+      <x:c r="D21" s="31" t="str">
+        <x:v>Episode-title placeholder replaced by the actual Knight Must Fall antagonist; generic placeholder mechanics retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="31" t="str">
+        <x:v>micro_men</x:v>
+      </x:c>
+      <x:c r="B22" s="31" t="str">
+        <x:v>spider_men</x:v>
+      </x:c>
+      <x:c r="C22" s="31" t="str">
+        <x:v>The Spider-Men</x:v>
+      </x:c>
+      <x:c r="D22" s="31" t="str">
+        <x:v>Unverified Micro-Men placeholder replaced by the alien Spider-Men from Home.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="31" t="str">
+        <x:v>grand_emperor</x:v>
+      </x:c>
+      <x:c r="B23" s="31" t="str">
+        <x:v>von_rantenraven</x:v>
+      </x:c>
+      <x:c r="C23" s="31" t="str">
+        <x:v>Baron Von Rantenraven</x:v>
+      </x:c>
+      <x:c r="D23" s="31" t="str">
+        <x:v>Unverified Grand Emperor placeholder replaced by the Sky Harbor antagonist.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="14" t="str">
+        <x:v>new_chapter_slot</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="str">
+        <x:v>harley_clivendon</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="str">
+        <x:v>Harley Clivendon</x:v>
+      </x:c>
+      <x:c r="D24" s="14" t="str">
+        <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="14" t="str">
+        <x:v>new_chapter_slot</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="str">
+        <x:v>conquistador</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="str">
+        <x:v>The Conquistador</x:v>
+      </x:c>
+      <x:c r="D25" s="14" t="str">
+        <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="14" t="str">
+        <x:v>new_chapter_slot</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="str">
+        <x:v>spider_slayer</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="str">
+        <x:v>Spider-Slayer</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="str">
+        <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="14" t="str">
+        <x:v>new_chapter_slot</x:v>
+      </x:c>
+      <x:c r="B27" s="14" t="str">
+        <x:v>metal_eating_monster</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="str">
+        <x:v>Metal-Eating Monster</x:v>
+      </x:c>
+      <x:c r="D27" s="14" t="str">
+        <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="14" t="str">
+        <x:v>new_chapter_slot</x:v>
+      </x:c>
+      <x:c r="B28" s="14" t="str">
+        <x:v>fiddler</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="str">
+        <x:v>Fiddler</x:v>
+      </x:c>
+      <x:c r="D28" s="14" t="str">
+        <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="14" t="str">
+        <x:v>kingpin_regular_slot</x:v>
+      </x:c>
+      <x:c r="B29" s="14" t="str">
+        <x:v>master_plan</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="str">
+        <x:v>The Plotter</x:v>
+      </x:c>
+      <x:c r="D29" s="14" t="str">
+        <x:v>Kingpin leaves the Chapter 4 villain roster. The former Plotter's Master Plan wizard is simplified into The Plotter regular villain mode.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="14" t="str">
+        <x:v>master_plan_wizard</x:v>
+      </x:c>
+      <x:c r="B30" s="14" t="str">
+        <x:v>crime_wave</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="str">
+        <x:v>Crime Wave</x:v>
+      </x:c>
+      <x:c r="D30" s="14" t="str">
+        <x:v>New Chapter 4 multiball wizard uses five timed villain areas and upper-exit jackpots.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="14" t="str">
+        <x:v>final_showdown</x:v>
+      </x:c>
+      <x:c r="B31" s="14" t="str">
+        <x:v>final_showdown</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="str">
+        <x:v>Kingpin</x:v>
+      </x:c>
+      <x:c r="D31" s="14" t="str">
+        <x:v>The existing final-wizard structure is reserved for a future Kingpin retheme.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5458,16 +6174,16 @@
       <x:c r="E1" s="40" t="str">
         <x:v>Number of Balls</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="F1" s="31" t="str">
         <x:v>How It Plays / Starts</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="G1" s="31" t="str">
         <x:v>How It Ends</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="H1" s="31" t="str">
         <x:v>Current Rule Snapshot</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="I1" s="31" t="str">
         <x:v>Presentation Status</x:v>
       </x:c>
     </x:row>
@@ -5487,13 +6203,13 @@
       <x:c r="E2" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F2" t="str">
+      <x:c r="F2" s="31" t="str">
         <x:v>Build Rage from pops, then use B/qualified shots to cash in Rhino jackpots.</x:v>
       </x:c>
-      <x:c r="G2" t="str">
+      <x:c r="G2" s="31" t="str">
         <x:v>Ends when the Rhino jackpot sequence/objectives are completed; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H2" t="str">
+      <x:c r="H2" s="31" t="str">
         <x:v>Pops build Rage; B rollover/qualified shots award jackpots; staged values grow through the mode.</x:v>
       </x:c>
       <x:c r="I2" s="31" t="str">
@@ -5516,13 +6232,13 @@
       <x:c r="E3" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F3" t="str">
+      <x:c r="F3" s="31" t="str">
         <x:v>Shoot the moving/right-bank Sandman target progression as it advances across the bank.</x:v>
       </x:c>
-      <x:c r="G3" t="str">
+      <x:c r="G3" s="31" t="str">
         <x:v>Ends when the required right-bank progression cycles are completed; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H3" t="str">
+      <x:c r="H3" s="31" t="str">
         <x:v>Moving right-bank target progression; jackpot lockout prevents repeated same-state awards.</x:v>
       </x:c>
       <x:c r="I3" s="31" t="str">
@@ -5545,13 +6261,13 @@
       <x:c r="E4" s="31" t="str">
         <x:v>1; add-a-ball possible</x:v>
       </x:c>
-      <x:c r="F4" t="str">
+      <x:c r="F4" s="31" t="str">
         <x:v>Get to the upper playfield; use upper targets/spinner to build and collect Vulture values.</x:v>
       </x:c>
-      <x:c r="G4" t="str">
+      <x:c r="G4" s="31" t="str">
         <x:v>Ends when upper-playfield Vulture objectives complete; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H4" t="str">
+      <x:c r="H4" s="31" t="str">
         <x:v>Upper playfield/spinner mode; spinner builds/scales scoring and can qualify add-a-ball; banks vulture_bonus.</x:v>
       </x:c>
       <x:c r="I4" s="31" t="str">
@@ -5574,13 +6290,13 @@
       <x:c r="E5" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F5" t="str">
+      <x:c r="F5" s="31" t="str">
         <x:v>Hit STAR to create serum, then deliver it to the required web shot before value drains.</x:v>
       </x:c>
-      <x:c r="G5" t="str">
+      <x:c r="G5" s="31" t="str">
         <x:v>Ends when serum deliveries are completed; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H5" t="str">
+      <x:c r="H5" s="31" t="str">
         <x:v>STAR creates serum; web shots deliver it. Case files add bigger value, slower decay, follow-up jackpots, one serum-save, and first-delivery flexibility.</x:v>
       </x:c>
       <x:c r="I5" s="31" t="str">
@@ -5603,13 +6319,13 @@
       <x:c r="E6" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F6" t="str">
+      <x:c r="F6" s="31" t="str">
         <x:v>Follow the travelling spark shot sequence; collected shots build toward the final Super.</x:v>
       </x:c>
-      <x:c r="G6" t="str">
+      <x:c r="G6" s="31" t="str">
         <x:v>Ends when the final Super Jackpot is collected; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H6" t="str">
+      <x:c r="H6" s="31" t="str">
         <x:v>Travelling spark selects shots; collected shots build toward a final Super Jackpot.</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
@@ -5632,13 +6348,13 @@
       <x:c r="E7" s="31" t="str">
         <x:v>2-ball MB</x:v>
       </x:c>
-      <x:c r="F7" t="str">
+      <x:c r="F7" s="31" t="str">
         <x:v>Chaos multiball: chase solid/flashing windows and saucer/shot opportunities.</x:v>
       </x:c>
-      <x:c r="G7" t="str">
+      <x:c r="G7" s="31" t="str">
         <x:v>Ends when multiball ends, or when Goblin objectives complete if reached first.</x:v>
       </x:c>
-      <x:c r="H7" t="str">
+      <x:c r="H7" s="31" t="str">
         <x:v>Chaos multiball; windows alternate between solid/flashing scoring; banks goblin_bonus.</x:v>
       </x:c>
       <x:c r="I7" s="31" t="str">
@@ -5661,13 +6377,13 @@
       <x:c r="E8" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F8" t="str">
+      <x:c r="F8" s="31" t="str">
         <x:v>Use rollovers/left bank to lock arms, then shoot web jackpots while avoiding freed arms.</x:v>
       </x:c>
-      <x:c r="G8" t="str">
+      <x:c r="G8" s="31" t="str">
         <x:v>Ends when Doc Ock is defeated by completing required jackpot/breakout objectives; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H8" t="str">
+      <x:c r="H8" s="31" t="str">
         <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpots; spinner boosts multiplier.</x:v>
       </x:c>
       <x:c r="I8" s="31" t="str">
@@ -5690,13 +6406,13 @@
       <x:c r="E9" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F9" t="str">
+      <x:c r="F9" s="31" t="str">
         <x:v>Use clues to identify the hidden Super while wrong shots reduce value.</x:v>
       </x:c>
-      <x:c r="G9" t="str">
+      <x:c r="G9" s="31" t="str">
         <x:v>Ends when the hidden Super/clue sequence is solved; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H9" t="str">
+      <x:c r="H9" s="31" t="str">
         <x:v>Hidden Super/clue mode; wrong shots score smaller and reduce value; clues narrow the target.</x:v>
       </x:c>
       <x:c r="I9" s="31" t="str">
@@ -5719,13 +6435,13 @@
       <x:c r="E10" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F10" t="str">
+      <x:c r="F10" s="31" t="str">
         <x:v>Spinner builds Venom; upper exits stage timed drop-bank attack shots.</x:v>
       </x:c>
-      <x:c r="G10" t="str">
+      <x:c r="G10" s="31" t="str">
         <x:v>Ends when the staged Scorpion attacks are completed/resolved; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H10" t="str">
+      <x:c r="H10" s="31" t="str">
         <x:v>Spinner builds Venom; upper exit stages timed drop-bank attack shots.</x:v>
       </x:c>
       <x:c r="I10" s="31" t="str">
@@ -5748,13 +6464,13 @@
       <x:c r="E11" s="31" t="str">
         <x:v>2-ball MB</x:v>
       </x:c>
-      <x:c r="F11" t="str">
+      <x:c r="F11" s="31" t="str">
         <x:v>Build heat in left/right/pops areas; maxed areas light saucer jackpots.</x:v>
       </x:c>
-      <x:c r="G11" t="str">
+      <x:c r="G11" s="31" t="str">
         <x:v>Ends when Parafino multiball ends, or when objectives complete if reached first.</x:v>
       </x:c>
-      <x:c r="H11" t="str">
+      <x:c r="H11" s="31" t="str">
         <x:v>Heat-area multiball; left/right/pops build heat; maxed areas light saucer jackpots and add-a-ball opportunities.</x:v>
       </x:c>
       <x:c r="I11" s="31" t="str">
@@ -5777,13 +6493,13 @@
       <x:c r="E12" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F12" t="str">
+      <x:c r="F12" s="31" t="str">
         <x:v>Upper targets light saucers; matching saucer collects stronger 2X jackpots while timer is active.</x:v>
       </x:c>
-      <x:c r="G12" t="str">
+      <x:c r="G12" s="31" t="str">
         <x:v>Ends after 3 saucer jackpots, timer expiry, ball end, or mode completion state.</x:v>
       </x:c>
-      <x:c r="H12" t="str">
+      <x:c r="H12" s="31" t="str">
         <x:v>Upper targets light saucers; matching saucer scores 2X; timer resets on key upper/spinner/saucer activity.</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
@@ -5806,13 +6522,13 @@
       <x:c r="E13" s="31" t="str">
         <x:v>2-ball MB; add-a-ball to 3</x:v>
       </x:c>
-      <x:c r="F13" t="str">
+      <x:c r="F13" s="31" t="str">
         <x:v>Eruption multiball: spinner builds Vulcan JP, right drops collect, upper target set can add a ball.</x:v>
       </x:c>
-      <x:c r="G13" t="str">
+      <x:c r="G13" s="31" t="str">
         <x:v>Ends when down to 1 ball with no spinner activity for the timeout, or on ball end.</x:v>
       </x:c>
-      <x:c r="H13" t="str">
+      <x:c r="H13" s="31" t="str">
         <x:v>Eruption multiball; spinner builds Vulcan JP; right drops collect; upper target set can award add-a-ball/eruption bonus.</x:v>
       </x:c>
       <x:c r="I13" s="31" t="str">
@@ -5835,13 +6551,13 @@
       <x:c r="E14" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F14" t="str">
+      <x:c r="F14" s="31" t="str">
         <x:v>Use post/upper-lower transitions to stage and collect timed arrow shots.</x:v>
       </x:c>
-      <x:c r="G14" t="str">
+      <x:c r="G14" s="31" t="str">
         <x:v>Ends when timed arrow/post-release objectives complete; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H14" t="str">
+      <x:c r="H14" s="31" t="str">
         <x:v>Post-release timed arrow shot flow; upper/lower transitions stage target opportunities.</x:v>
       </x:c>
       <x:c r="I14" s="31" t="str">
@@ -5864,13 +6580,13 @@
       <x:c r="E15" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F15" t="str">
+      <x:c r="F15" s="31" t="str">
         <x:v>Limited-flips mode: drops add flips, then center-web Eye collects based on remaining flips.</x:v>
       </x:c>
-      <x:c r="G15" t="str">
+      <x:c r="G15" s="31" t="str">
         <x:v>Ends when the Eye jackpot is collected, flips run out, or ball ends.</x:v>
       </x:c>
-      <x:c r="H15" t="str">
+      <x:c r="H15" s="31" t="str">
         <x:v>Limited-flips mode; drop targets add flips; center-web Eye jackpot value depends on remaining flips.</x:v>
       </x:c>
       <x:c r="I15" s="31" t="str">
@@ -5893,13 +6609,13 @@
       <x:c r="E16" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F16" t="str">
+      <x:c r="F16" s="31" t="str">
         <x:v>Drops build jackpot and open the roof/post final phase.</x:v>
       </x:c>
-      <x:c r="G16" t="str">
+      <x:c r="G16" s="31" t="str">
         <x:v>Ends when final rubber/target jackpot phase resolves; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H16" t="str">
+      <x:c r="H16" s="31" t="str">
         <x:v>Drops build jackpot; roof/post phase creates the final rubber/target jackpot opportunity.</x:v>
       </x:c>
       <x:c r="I16" s="31" t="str">
@@ -5914,25 +6630,25 @@
         <x:v>Crime Wave</x:v>
       </x:c>
       <x:c r="C17" s="31" t="str">
-        <x:v>kingpin</x:v>
+        <x:v>master_plan</x:v>
       </x:c>
       <x:c r="D17" s="31" t="str">
-        <x:v>Kingpin</x:v>
+        <x:v>The Plotter</x:v>
       </x:c>
       <x:c r="E17" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F17" t="str">
-        <x:v>Clear crime areas to qualify Daily Bugle jackpots.</x:v>
-      </x:c>
-      <x:c r="G17" t="str">
-        <x:v>Ends when required areas/jackpots are cleared; otherwise stops on ball end.</x:v>
-      </x:c>
-      <x:c r="H17" t="str">
-        <x:v>Area clears qualify Daily Bugle jackpots; active/inactive areas score different values.</x:v>
+      <x:c r="F17" s="31" t="str">
+        <x:v>Hit pops to build information. Spend two information with a spinner hit to light one saucer.</x:v>
+      </x:c>
+      <x:c r="G17" s="31" t="str">
+        <x:v>Collect three lit saucers, then shoot the Daily Bugle VUK for the Master Plan Super. Otherwise ends on ball end.</x:v>
+      </x:c>
+      <x:c r="H17" s="31" t="str">
+        <x:v>Each lit saucer scores a scheme jackpot. Three schemes open the roof and light the final VUK Super.</x:v>
       </x:c>
       <x:c r="I17" s="31" t="str">
-        <x:v>Good: timer/multiball status and state-change messaging are present.</x:v>
+        <x:v>Simplified regular villain mode; uses shared active-mode variables rather than many Plotter-specific player variables.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -5943,21 +6659,21 @@
         <x:v>Crime Wave</x:v>
       </x:c>
       <x:c r="C18" s="31" t="str">
-        <x:v>human_flies</x:v>
+        <x:v>fly_brothers</x:v>
       </x:c>
       <x:c r="D18" s="31" t="str">
-        <x:v>Human Flies</x:v>
+        <x:v>Fly Brothers</x:v>
       </x:c>
       <x:c r="E18" s="31" t="str">
         <x:v>2-ball MB</x:v>
       </x:c>
-      <x:c r="F18" t="str">
+      <x:c r="F18" s="31" t="str">
         <x:v>Multiball: upper targets light saucers, spinner builds jackpot, saucers collect scaled values.</x:v>
       </x:c>
-      <x:c r="G18" t="str">
-        <x:v>Ends when Human Flies multiball ends, or when objectives complete if reached first.</x:v>
-      </x:c>
-      <x:c r="H18" t="str">
+      <x:c r="G18" s="31" t="str">
+        <x:v>Ends when Fly Brothers multiball ends, or when objectives complete if reached first.</x:v>
+      </x:c>
+      <x:c r="H18" s="31" t="str">
         <x:v>Upper targets light saucers; spinner builds jackpot value; saucer collects scale by number of lit brothers/targets.</x:v>
       </x:c>
       <x:c r="I18" s="31" t="str">
@@ -5980,13 +6696,13 @@
       <x:c r="E19" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F19" t="str">
+      <x:c r="F19" s="31" t="str">
         <x:v>Right bank reveals the Phantom location; shoot the revealed location before the window closes.</x:v>
       </x:c>
-      <x:c r="G19" t="str">
+      <x:c r="G19" s="31" t="str">
         <x:v>Ends after the Phantom reveal rounds are completed, or when reveal/assist rules resolve; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H19" t="str">
+      <x:c r="H19" s="31" t="str">
         <x:v>Right bank reveals the Phantom location; later reveals give more time but lower value.</x:v>
       </x:c>
       <x:c r="I19" s="31" t="str">
@@ -6004,18 +6720,18 @@
         <x:v>enforcers</x:v>
       </x:c>
       <x:c r="D20" s="31" t="str">
-        <x:v>Enforcers / Ox</x:v>
+        <x:v>The Enforcers</x:v>
       </x:c>
       <x:c r="E20" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F20" t="str">
+      <x:c r="F20" s="31" t="str">
         <x:v>Complete crime zones to light upper-target jackpots and build the OX Super.</x:v>
       </x:c>
-      <x:c r="G20" t="str">
+      <x:c r="G20" s="31" t="str">
         <x:v>Ends after Enforcer zones and OX Super are completed; otherwise stops on ball end.</x:v>
       </x:c>
-      <x:c r="H20" t="str">
+      <x:c r="H20" s="31" t="str">
         <x:v>Crime zones light upper-target jackpots; collected jackpots build the OX Super at center web.</x:v>
       </x:c>
       <x:c r="I20" s="31" t="str">
@@ -6030,25 +6746,25 @@
         <x:v>Crime Wave</x:v>
       </x:c>
       <x:c r="C21" s="31" t="str">
-        <x:v>diamond_smugglers</x:v>
+        <x:v>doctor_cool</x:v>
       </x:c>
       <x:c r="D21" s="31" t="str">
-        <x:v>Diamond Smugglers</x:v>
+        <x:v>Doctor Cool</x:v>
       </x:c>
       <x:c r="E21" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F21" t="str">
-        <x:v>Use drops/star to bank diamond_bonus; saucer chase uses STAR freeze to lock diamond state.</x:v>
-      </x:c>
-      <x:c r="G21" t="str">
-        <x:v>Ends when diamond objectives are collected/completed; otherwise stops on ball end.</x:v>
-      </x:c>
-      <x:c r="H21" t="str">
-        <x:v>Drops/star bank diamond_bonus; saucer chase uses STAR freeze to lock the current diamond state.</x:v>
+      <x:c r="F21" s="31" t="str">
+        <x:v>Build frozen-diamond value with both drop banks; complete the right 5-bank to start the moving shipment chase.</x:v>
+      </x:c>
+      <x:c r="G21" s="31" t="str">
+        <x:v>Collect the lit saucer for each shipment. Complete three shipments, or four with More Jackpots; otherwise stops on ball end.</x:v>
+      </x:c>
+      <x:c r="H21" s="31" t="str">
+        <x:v>Drops raise the frozen-diamond jackpot and bank diamond_bonus. STAR freezes the chase and lights all three saucers for 10 seconds, or 15 with More Time.</x:v>
       </x:c>
       <x:c r="I21" s="31" t="str">
-        <x:v>Improved: persistent drop-hit, shipment, and active chase status.</x:v>
+        <x:v>Bigger Jackpots raises base and drop additions; Safety Net starts ball save; Shot Assist makes the first wrong saucer count.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -6056,28 +6772,28 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B22" s="31" t="str">
-        <x:v>Mystic Menace</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C22" s="31" t="str">
-        <x:v>pardo</x:v>
+        <x:v>harley_clivendon</x:v>
       </x:c>
       <x:c r="D22" s="31" t="str">
-        <x:v>Pardo</x:v>
+        <x:v>Harley Clivendon</x:v>
       </x:c>
       <x:c r="E22" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F22" t="str">
-        <x:v>Spinner reveals the true shot among 3 lit hypnosis choices; correct shots score jackpots.</x:v>
-      </x:c>
-      <x:c r="G22" t="str">
-        <x:v>Ends after 5 correct shots, 7 wrong shots, or ball end.</x:v>
-      </x:c>
-      <x:c r="H22" t="str">
-        <x:v>Hypnosis Reel: spinner reveals the true shot among 3 lit choices; correct shots score jackpots, wrong shots add mistakes.</x:v>
+      <x:c r="F22" s="31" t="str">
+        <x:v>Placeholder framework for hypnosis / reveal with hidden-shot control, using Spinner, targets, and changing shots.</x:v>
+      </x:c>
+      <x:c r="G22" s="31" t="str">
+        <x:v>Ends when goals completed / ball end.</x:v>
+      </x:c>
+      <x:c r="H22" s="31" t="str">
+        <x:v>Idol and scheme jackpots. Shot confusion / reveal windows.</x:v>
       </x:c>
       <x:c r="I22" s="31" t="str">
-        <x:v>Improved: persistent correct-shot and mistake-limit progress.</x:v>
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -6085,207 +6801,207 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B23" s="31" t="str">
-        <x:v>Mystic Menace</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C23" s="31" t="str">
-        <x:v>fakir</x:v>
+        <x:v>conquistador</x:v>
       </x:c>
       <x:c r="D23" s="31" t="str">
-        <x:v>The Fakir</x:v>
+        <x:v>The Conquistador</x:v>
       </x:c>
       <x:c r="E23" s="31" t="str">
-        <x:v>2-ball MB</x:v>
-      </x:c>
-      <x:c r="F23" t="str">
-        <x:v>Ruby Heist multiball: saucers reveal upper rubies; spinners build Ruby/Super value.</x:v>
-      </x:c>
-      <x:c r="G23" t="str">
-        <x:v>Ends when Fakir multiball ends.</x:v>
-      </x:c>
-      <x:c r="H23" t="str">
-        <x:v>Ruby Heist: saucers reveal upper rubies; spinners build value; 3 Ruby JPs qualify Super; post-Super rubies continue until multiball ends.</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F23" s="31" t="str">
+        <x:v>Placeholder framework for treasure hunt / pursuit with risk-reward path, using Fort, saucer, upper, and escape shots.</x:v>
+      </x:c>
+      <x:c r="G23" s="31" t="str">
+        <x:v>Ends when goals completed / ball end.</x:v>
+      </x:c>
+      <x:c r="H23" s="31" t="str">
+        <x:v>Fountain jackpots. Route and timer pressure.</x:v>
       </x:c>
       <x:c r="I23" s="31" t="str">
-        <x:v>Improved: persistent Ruby progress, reveal objective, and Super-lit status.</x:v>
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="31" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B24" s="31" t="str">
-        <x:v>Mad Science</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C24" s="31" t="str">
-        <x:v>noah_boddy</x:v>
+        <x:v>spider_slayer</x:v>
       </x:c>
       <x:c r="D24" s="31" t="str">
-        <x:v>Dr. Noah Boddy</x:v>
+        <x:v>Spider-Slayer</x:v>
       </x:c>
       <x:c r="E24" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F24" t="str">
-        <x:v>Reveal and solve secret-shot objectives using the invisible/reveal mechanic.</x:v>
-      </x:c>
-      <x:c r="G24" t="str">
-        <x:v>Ends when secret/reveal objectives are solved; otherwise stops on ball end.</x:v>
-      </x:c>
-      <x:c r="H24" t="str">
-        <x:v>Invisible/reveal/secret-shot mechanics repurposed from the Mole Man concept.</x:v>
+      <x:c r="F24" s="31" t="str">
+        <x:v>Placeholder framework for machine pursuit with tracking target, using Moving playfield shots.</x:v>
+      </x:c>
+      <x:c r="G24" s="31" t="str">
+        <x:v>Ends when slayer destroyed / ball end.</x:v>
+      </x:c>
+      <x:c r="H24" s="31" t="str">
+        <x:v>Escape and destruction jackpots. Capture pressure.</x:v>
       </x:c>
       <x:c r="I24" s="31" t="str">
-        <x:v>Good: reveal/hurry-up status and state-change messaging are present.</x:v>
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="31" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B25" s="31" t="str">
-        <x:v>Mad Science</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C25" s="31" t="str">
-        <x:v>doctor_dumpty</x:v>
+        <x:v>metal_eating_monster</x:v>
       </x:c>
       <x:c r="D25" s="31" t="str">
-        <x:v>Doctor Dumpty</x:v>
+        <x:v>Metal-Eating Monster</x:v>
       </x:c>
       <x:c r="E25" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F25" t="str">
-        <x:v>Fragile precision/puzzle shots require controlled progress without breaking the setup.</x:v>
-      </x:c>
-      <x:c r="G25" t="str">
-        <x:v>Ends when fragile puzzle objectives are completed; otherwise stops on ball end.</x:v>
-      </x:c>
-      <x:c r="H25" t="str">
-        <x:v>Precision puzzle mode repurposed from Blackwell-style fragile/controlled-shot mechanics.</x:v>
+      <x:c r="F25" s="31" t="str">
+        <x:v>Placeholder framework for area consumption with restore disabled areas, using Whole playfield and river finish.</x:v>
+      </x:c>
+      <x:c r="G25" s="31" t="str">
+        <x:v>Ends when robot stopped / ball end.</x:v>
+      </x:c>
+      <x:c r="H25" s="31" t="str">
+        <x:v>Destruction jackpots. Shrinking safe playfield.</x:v>
       </x:c>
       <x:c r="I25" s="31" t="str">
-        <x:v>Good: active countdown/status and state-change messaging are present.</x:v>
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="31" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B26" s="31" t="str">
-        <x:v>Savage Oddities</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C26" s="31" t="str">
-        <x:v>swamp_reptiles</x:v>
+        <x:v>fiddler</x:v>
       </x:c>
       <x:c r="D26" s="31" t="str">
-        <x:v>Swamp Reptiles</x:v>
+        <x:v>Fiddler</x:v>
       </x:c>
       <x:c r="E26" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F26" t="str">
-        <x:v>Play the retained Reptilla-style shot flow under the Swamp Reptiles identity.</x:v>
-      </x:c>
-      <x:c r="G26" t="str">
-        <x:v>Ends when retained Reptilla-style objectives complete; otherwise stops on ball end.</x:v>
-      </x:c>
-      <x:c r="H26" t="str">
-        <x:v>Repurposed Reptilla implementation; swamp_bonus bank preserved under new mode identity.</x:v>
+      <x:c r="F26" s="31" t="str">
+        <x:v>Placeholder framework for music / sequence with pitch and ransom build, using Spinner plus ordered shots.</x:v>
+      </x:c>
+      <x:c r="G26" s="31" t="str">
+        <x:v>Ends when violin silenced / ball end.</x:v>
+      </x:c>
+      <x:c r="H26" s="31" t="str">
+        <x:v>Sound-wave jackpots. Sequence and timer pressure.</x:v>
       </x:c>
       <x:c r="I26" s="31" t="str">
-        <x:v>Improved: persistent Rampage, lit-jackpot, collected-jackpot, and Super status.</x:v>
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B27" t="str">
-        <x:v>Savage Oddities</x:v>
-      </x:c>
-      <x:c r="C27" t="str">
-        <x:v>the_fly</x:v>
-      </x:c>
-      <x:c r="D27" t="str">
-        <x:v>The Fly</x:v>
-      </x:c>
-      <x:c r="E27" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F27" t="str">
-        <x:v>Saucers open gate; upper entrance starts a limited-flip roof attempt on the 3 upper targets.</x:v>
-      </x:c>
-      <x:c r="G27" t="str">
-        <x:v>Ends after 3 roof clears, or stops on ball end.</x:v>
-      </x:c>
-      <x:c r="H27" t="str">
-        <x:v>Rooftop Swarm: saucers open gate; upper entrance starts limited-flip roof attempt; first two targets are JPs and third is Super boosted by remaining flips.</x:v>
+      <x:c r="A27" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B27" s="31" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="C27" s="31" t="str">
+        <x:v>pardo</x:v>
+      </x:c>
+      <x:c r="D27" s="31" t="str">
+        <x:v>Pardo</x:v>
+      </x:c>
+      <x:c r="E27" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F27" s="31" t="str">
+        <x:v>Spinner reveals the true shot among 3 lit hypnosis choices; correct shots score jackpots.</x:v>
+      </x:c>
+      <x:c r="G27" s="31" t="str">
+        <x:v>Ends after 5 correct shots, 7 wrong shots, or ball end.</x:v>
+      </x:c>
+      <x:c r="H27" s="31" t="str">
+        <x:v>Hypnosis Reel: spinner reveals the true shot among 3 lit choices; correct shots score jackpots, wrong shots add mistakes.</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
-        <x:v>Improved: persistent gate state, roof targets, flips, and roof-clear progress.</x:v>
+        <x:v>Improved: persistent correct-shot and mistake-limit progress.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B28" t="str">
-        <x:v>Dimensional Finale</x:v>
-      </x:c>
-      <x:c r="C28" t="str">
-        <x:v>master_technician</x:v>
-      </x:c>
-      <x:c r="D28" t="str">
-        <x:v>Master Technician</x:v>
-      </x:c>
-      <x:c r="E28" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F28" t="str">
-        <x:v>Drops determine spinner value; spinner/shot flow cashes in Technician scoring.</x:v>
-      </x:c>
-      <x:c r="G28" t="str">
-        <x:v>Ends when Technician objectives are cleared; otherwise stops on ball end.</x:v>
-      </x:c>
-      <x:c r="H28" t="str">
-        <x:v>Repurposed Meteor homage: drops determine spinner value; technician_bonus bank.</x:v>
+      <x:c r="A28" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B28" s="31" t="str">
+        <x:v>Mystic Menace</x:v>
+      </x:c>
+      <x:c r="C28" s="31" t="str">
+        <x:v>fakir</x:v>
+      </x:c>
+      <x:c r="D28" s="31" t="str">
+        <x:v>The Fantastic Fakir</x:v>
+      </x:c>
+      <x:c r="E28" s="31" t="str">
+        <x:v>2-ball MB</x:v>
+      </x:c>
+      <x:c r="F28" s="31" t="str">
+        <x:v>Ruby Heist multiball: saucers reveal upper rubies; spinners build Ruby/Super value.</x:v>
+      </x:c>
+      <x:c r="G28" s="31" t="str">
+        <x:v>Ends when Fakir multiball ends.</x:v>
+      </x:c>
+      <x:c r="H28" s="31" t="str">
+        <x:v>Ruby Heist: saucers reveal upper rubies; spinners build value; 3 Ruby JPs qualify Super; post-Super rubies continue until multiball ends.</x:v>
       </x:c>
       <x:c r="I28" s="31" t="str">
-        <x:v>Improved: persistent left/right drop progress and live spinner value.</x:v>
+        <x:v>Improved: persistent Ruby progress, reveal objective, and Super-lit status.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B29" t="str">
+      <x:c r="A29" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B29" s="31" t="str">
         <x:v>Mystic Menace</x:v>
       </x:c>
-      <x:c r="C29" t="str">
+      <x:c r="C29" s="31" t="str">
         <x:v>scarlet_sorcerer</x:v>
       </x:c>
-      <x:c r="D29" t="str">
-        <x:v>Scarlet Sorcerer</x:v>
-      </x:c>
-      <x:c r="E29" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F29" t="str">
+      <x:c r="D29" s="31" t="str">
+        <x:v>Kotep — The Scarlet Sorcerer</x:v>
+      </x:c>
+      <x:c r="E29" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F29" s="31" t="str">
         <x:v>Destroy four unique demon shots that appear over time; shots never relight.</x:v>
       </x:c>
-      <x:c r="G29" t="str">
+      <x:c r="G29" s="31" t="str">
         <x:v>After four demons, collect the timed VUK Scepter Super. Ends on Super, timer expiry, or ball end.</x:v>
       </x:c>
-      <x:c r="H29" t="str">
+      <x:c r="H29" s="31" t="str">
         <x:v>Demon JPs 200K–350K; 20-second 1M Super. Bigger gives 300K–450K and 1.5M.</x:v>
       </x:c>
-      <x:c r="I29" t="str">
+      <x:c r="I29" s="31" t="str">
         <x:v>More Jackpots adds optional 500K fifth demon; More Time 30s; Safety Net ball save; Shot Assist introduces and destroys the next scheduled demon.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="31" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B30" s="31" t="str">
         <x:v>Mystic Menace</x:v>
@@ -6314,7 +7030,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="31" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B31" s="31" t="str">
         <x:v>Mystic Menace</x:v>
@@ -6342,102 +7058,729 @@
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B32" t="str">
+      <x:c r="A32" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B32" s="31" t="str">
         <x:v>Mad Science</x:v>
       </x:c>
-      <x:c r="C32" t="str">
+      <x:c r="C32" s="31" t="str">
+        <x:v>noah_boddy</x:v>
+      </x:c>
+      <x:c r="D32" s="31" t="str">
+        <x:v>Dr. Noah Boddy</x:v>
+      </x:c>
+      <x:c r="E32" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F32" s="31" t="str">
+        <x:v>Reveal and solve secret-shot objectives using the invisible/reveal mechanic.</x:v>
+      </x:c>
+      <x:c r="G32" s="31" t="str">
+        <x:v>Ends when secret/reveal objectives are solved; otherwise stops on ball end.</x:v>
+      </x:c>
+      <x:c r="H32" s="31" t="str">
+        <x:v>Invisible/reveal/secret-shot mechanics repurposed from the Mole Man concept.</x:v>
+      </x:c>
+      <x:c r="I32" s="31" t="str">
+        <x:v>Good: reveal/hurry-up status and state-change messaging are present.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B33" s="31" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="C33" s="31" t="str">
         <x:v>dr_magneto</x:v>
       </x:c>
-      <x:c r="D32" t="str">
+      <x:c r="D33" s="31" t="str">
         <x:v>Dr. Magneto</x:v>
       </x:c>
-      <x:c r="E32" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F32" t="str">
+      <x:c r="E33" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F33" s="31" t="str">
         <x:v>Reach the roof and spin through left drops 1–3 then right drops 1–4, leaving right drop 5 standing.</x:v>
       </x:c>
-      <x:c r="G32" t="str">
+      <x:c r="G33" s="31" t="str">
         <x:v>Hit right drop 5 within 20 seconds. Early rooftop exit before staging resets both banks.</x:v>
       </x:c>
-      <x:c r="H32" t="str">
+      <x:c r="H33" s="31" t="str">
         <x:v>Each spin 50K plus 50K per staged drop; main Super 1M or 1.5M with Bigger.</x:v>
       </x:c>
-      <x:c r="I32" t="str">
+      <x:c r="I33" s="31" t="str">
         <x:v>More Jackpots stages left drop 1 for a 500K Flux Super; More Time 30s; Safety Net at main Super; first spin drops two targets with Shot Assist.</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
-      <x:c r="A33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B33" t="str">
+    <x:row r="34">
+      <x:c r="A34" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B34" s="31" t="str">
         <x:v>Mad Science</x:v>
       </x:c>
-      <x:c r="C33" t="str">
+      <x:c r="C34" s="31" t="str">
         <x:v>professor_pretoris</x:v>
       </x:c>
-      <x:c r="D33" t="str">
+      <x:c r="D34" s="31" t="str">
         <x:v>Professor Pretoris</x:v>
       </x:c>
-      <x:c r="E33" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F33" t="str">
+      <x:c r="E34" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F34" s="31" t="str">
         <x:v>All GI starts red; eight horizontal bands flood blue bottom-to-top, one per web-spinner hit.</x:v>
       </x:c>
-      <x:c r="G33" t="str">
+      <x:c r="G34" s="31" t="str">
         <x:v>After all eight are blue, hit center web within 20 seconds. Ends on Super, timer expiry, or ball end.</x:v>
       </x:c>
-      <x:c r="H33" t="str">
+      <x:c r="H34" s="31" t="str">
         <x:v>Each converted band 100K. Main Super 1M or 1.5M with Bigger.</x:v>
       </x:c>
-      <x:c r="I33" t="str">
+      <x:c r="I34" s="31" t="str">
         <x:v>More Jackpots adds a 10-second 500K left-web Overflow Super; More Time 30s; Safety Net at Super; first spin floods two bands with Shot Assist.</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B34" t="str">
+    <x:row r="35">
+      <x:c r="A35" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B35" s="31" t="str">
         <x:v>Mad Science</x:v>
       </x:c>
-      <x:c r="C34" t="str">
+      <x:c r="C35" s="31" t="str">
+        <x:v>doctor_dumpty</x:v>
+      </x:c>
+      <x:c r="D35" s="31" t="str">
+        <x:v>Doctor Dumpty</x:v>
+      </x:c>
+      <x:c r="E35" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F35" s="31" t="str">
+        <x:v>Fragile precision/puzzle shots require controlled progress without breaking the setup.</x:v>
+      </x:c>
+      <x:c r="G35" s="31" t="str">
+        <x:v>Ends when fragile puzzle objectives are completed; otherwise stops on ball end.</x:v>
+      </x:c>
+      <x:c r="H35" s="31" t="str">
+        <x:v>Precision puzzle mode repurposed from Blackwell-style fragile/controlled-shot mechanics.</x:v>
+      </x:c>
+      <x:c r="I35" s="31" t="str">
+        <x:v>Good: active countdown/status and state-change messaging are present.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B36" s="31" t="str">
+        <x:v>Mad Science</x:v>
+      </x:c>
+      <x:c r="C36" s="31" t="str">
         <x:v>dr_von_schlick</x:v>
       </x:c>
-      <x:c r="D34" t="str">
+      <x:c r="D36" s="31" t="str">
         <x:v>Dr. Von Schlick</x:v>
       </x:c>
-      <x:c r="E34" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F34" t="str">
+      <x:c r="E36" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F36" s="31" t="str">
         <x:v>Follow one green moving shot across left web, left drops, left pop, center web, right pop, and right drops, reversing every 4 seconds.</x:v>
       </x:c>
-      <x:c r="G34" t="str">
+      <x:c r="G36" s="31" t="str">
         <x:v>Five pellets open the gate and light the VUK for 20 seconds. VUK starts the held-ball eight-band blue flood and awards 1M at completion.</x:v>
       </x:c>
-      <x:c r="H34" t="str">
+      <x:c r="H36" s="31" t="str">
         <x:v>Pellets 100K or 150K with Bigger. Wrong shots score only normal game points.</x:v>
       </x:c>
-      <x:c r="I34" t="str">
+      <x:c r="I36" s="31" t="str">
         <x:v>More Jackpots allows two optional pellets after qualification; More Time 30s; Safety Net at Super; Shot Assist makes first pellet count twice. Daily Bugle A+B cannot open the gate.</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="31"/>
-      <x:c r="B35" s="31"/>
-      <x:c r="C35" s="31"/>
-      <x:c r="D35" s="31"/>
-      <x:c r="E35" s="31"/>
-      <x:c r="F35" s="31"/>
-      <x:c r="G35" s="31"/>
-      <x:c r="H35" s="31"/>
-      <x:c r="I35" s="31"/>
+    <x:row r="37">
+      <x:c r="A37" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B37" s="31" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="C37" s="31" t="str">
+        <x:v>clive_blotto</x:v>
+      </x:c>
+      <x:c r="D37" s="31" t="str">
+        <x:v>Clive and Blotto</x:v>
+      </x:c>
+      <x:c r="E37" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F37" s="31" t="str">
+        <x:v>Placeholder framework for containment / spreading hazard with banked bonus, using Whole playfield / containment shots.</x:v>
+      </x:c>
+      <x:c r="G37" s="31" t="str">
+        <x:v>Ends when goals completed / ball end.</x:v>
+      </x:c>
+      <x:c r="H37" s="31" t="str">
+        <x:v>blotto_bonus bank. Blotto spreads and changes shape.</x:v>
+      </x:c>
+      <x:c r="I37" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B38" s="31" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="C38" s="31" t="str">
+        <x:v>dr_zap</x:v>
+      </x:c>
+      <x:c r="D38" s="31" t="str">
+        <x:v>Doctor Zapp</x:v>
+      </x:c>
+      <x:c r="E38" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F38" s="31" t="str">
+        <x:v>Placeholder framework for electrical machine / timed with invention control, using Spinner + lit shots.</x:v>
+      </x:c>
+      <x:c r="G38" s="31" t="str">
+        <x:v>Ends when sequence complete / timer / ball end.</x:v>
+      </x:c>
+      <x:c r="H38" s="31" t="str">
+        <x:v>Zapp/Super value. Overload timing.</x:v>
+      </x:c>
+      <x:c r="I38" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B39" s="31" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="C39" s="31" t="str">
+        <x:v>voltan_boomer</x:v>
+      </x:c>
+      <x:c r="D39" s="31" t="str">
+        <x:v>Voltan and Boomer</x:v>
+      </x:c>
+      <x:c r="E39" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F39" s="31" t="str">
+        <x:v>Placeholder framework for storm timing / robbery with thunder windows, using Storm shots + target groups.</x:v>
+      </x:c>
+      <x:c r="G39" s="31" t="str">
+        <x:v>Ends when goals completed / ball end.</x:v>
+      </x:c>
+      <x:c r="H39" s="31" t="str">
+        <x:v>Thunder/robbery jackpots. Short storm windows.</x:v>
+      </x:c>
+      <x:c r="I39" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B40" s="31" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="C40" s="31" t="str">
+        <x:v>snowman</x:v>
+      </x:c>
+      <x:c r="D40" s="31" t="str">
+        <x:v>The Snowman</x:v>
+      </x:c>
+      <x:c r="E40" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F40" s="31" t="str">
+        <x:v>Placeholder framework for endurance / melt with area control, using Pops / lanes / shots.</x:v>
+      </x:c>
+      <x:c r="G40" s="31" t="str">
+        <x:v>Ends when goals or timer / ball end.</x:v>
+      </x:c>
+      <x:c r="H40" s="31" t="str">
+        <x:v>Snowballing value. Escalating snowfall.</x:v>
+      </x:c>
+      <x:c r="I40" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B41" s="31" t="str">
+        <x:v>Elemental Chaos</x:v>
+      </x:c>
+      <x:c r="C41" s="31" t="str">
+        <x:v>plutonians</x:v>
+      </x:c>
+      <x:c r="D41" s="31" t="str">
+        <x:v>The Plutonians</x:v>
+      </x:c>
+      <x:c r="E41" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F41" s="31" t="str">
+        <x:v>Placeholder framework for ice rescue / repair with survival / recovery, using Whole playfield.</x:v>
+      </x:c>
+      <x:c r="G41" s="31" t="str">
+        <x:v>Ends when goals completed / ball end.</x:v>
+      </x:c>
+      <x:c r="H41" s="31" t="str">
+        <x:v>Frozen jackpots / repair value. Frozen shots and escape repairs.</x:v>
+      </x:c>
+      <x:c r="I41" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B42" s="31" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="C42" s="31" t="str">
+        <x:v>dr_manta</x:v>
+      </x:c>
+      <x:c r="D42" s="31" t="str">
+        <x:v>Dr. Manta</x:v>
+      </x:c>
+      <x:c r="E42" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F42" s="31" t="str">
+        <x:v>Placeholder framework for hidden-city control with trap / freeze, using Saucers + robotic-creature shots.</x:v>
+      </x:c>
+      <x:c r="G42" s="31" t="str">
+        <x:v>Ends when goals or timer / ball end.</x:v>
+      </x:c>
+      <x:c r="H42" s="31" t="str">
+        <x:v>Frozen-city jackpots. Held ball / trap pressure.</x:v>
+      </x:c>
+      <x:c r="I42" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B43" s="31" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="C43" s="31" t="str">
+        <x:v>igor</x:v>
+      </x:c>
+      <x:c r="D43" s="31" t="str">
+        <x:v>Igor</x:v>
+      </x:c>
+      <x:c r="E43" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F43" s="31" t="str">
+        <x:v>Placeholder framework for assistant / defenses with sequence / precision, using Castle and defense shots.</x:v>
+      </x:c>
+      <x:c r="G43" s="31" t="str">
+        <x:v>Ends when sequence complete / ball end.</x:v>
+      </x:c>
+      <x:c r="H43" s="31" t="str">
+        <x:v>Assistant combo / Super. Ordered-shot pressure.</x:v>
+      </x:c>
+      <x:c r="I43" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B44" s="31" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="C44" s="31" t="str">
+        <x:v>doctor_atlantean</x:v>
+      </x:c>
+      <x:c r="D44" s="31" t="str">
+        <x:v>Doctor Atlantean</x:v>
+      </x:c>
+      <x:c r="E44" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F44" s="31" t="str">
+        <x:v>Placeholder framework for underwater invasion with area control, using Upper/lower Atlantean shots.</x:v>
+      </x:c>
+      <x:c r="G44" s="31" t="str">
+        <x:v>Ends when goals completed / ball end.</x:v>
+      </x:c>
+      <x:c r="H44" s="31" t="str">
+        <x:v>Relic/kingdom jackpots. Dome and sinking pressure.</x:v>
+      </x:c>
+      <x:c r="I44" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B45" s="31" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="C45" s="31" t="str">
+        <x:v>devargas</x:v>
+      </x:c>
+      <x:c r="D45" s="31" t="str">
+        <x:v>DeVargas</x:v>
+      </x:c>
+      <x:c r="E45" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F45" s="31" t="str">
+        <x:v>Placeholder framework for hidden city / gold with build-and-cash, using Cloud City and golden-defense shots.</x:v>
+      </x:c>
+      <x:c r="G45" s="31" t="str">
+        <x:v>Ends when goals completed / ball end.</x:v>
+      </x:c>
+      <x:c r="H45" s="31" t="str">
+        <x:v>devargas_bonus bank. Golden eagle / city defenses.</x:v>
+      </x:c>
+      <x:c r="I45" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B46" s="31" t="str">
+        <x:v>Lost Worlds</x:v>
+      </x:c>
+      <x:c r="C46" s="31" t="str">
+        <x:v>molemen</x:v>
+      </x:c>
+      <x:c r="D46" s="31" t="str">
+        <x:v>Molemen</x:v>
+      </x:c>
+      <x:c r="E46" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F46" s="31" t="str">
+        <x:v>Placeholder framework for underground invasion with area / survival, using Drops, tunnels, lower playfield.</x:v>
+      </x:c>
+      <x:c r="G46" s="31" t="str">
+        <x:v>Ends when goals or timer / ball end.</x:v>
+      </x:c>
+      <x:c r="H46" s="31" t="str">
+        <x:v>Underground jackpots. Escalating underground pressure.</x:v>
+      </x:c>
+      <x:c r="I46" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B47" s="31" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="C47" s="31" t="str">
+        <x:v>charles_cameo</x:v>
+      </x:c>
+      <x:c r="D47" s="31" t="str">
+        <x:v>Charles Cameo</x:v>
+      </x:c>
+      <x:c r="E47" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F47" s="31" t="str">
+        <x:v>Placeholder framework for disguise / identity with mystery / reveal, using Changing shots.</x:v>
+      </x:c>
+      <x:c r="G47" s="31" t="str">
+        <x:v>Ends when goals or mistake limit / ball end.</x:v>
+      </x:c>
+      <x:c r="H47" s="31" t="str">
+        <x:v>Impostor jackpots. Wrong identity penalty.</x:v>
+      </x:c>
+      <x:c r="I47" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B48" s="31" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="C48" s="31" t="str">
+        <x:v>brutus</x:v>
+      </x:c>
+      <x:c r="D48" s="31" t="str">
+        <x:v>Brutus</x:v>
+      </x:c>
+      <x:c r="E48" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F48" s="31" t="str">
+        <x:v>Placeholder framework for strength / bash with build-and-cash, using Drops / targets.</x:v>
+      </x:c>
+      <x:c r="G48" s="31" t="str">
+        <x:v>Ends when goals completed / ball end.</x:v>
+      </x:c>
+      <x:c r="H48" s="31" t="str">
+        <x:v>Bash jackpot build. Shot volume / bank resets.</x:v>
+      </x:c>
+      <x:c r="I48" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B49" s="31" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="C49" s="31" t="str">
+        <x:v>desperado</x:v>
+      </x:c>
+      <x:c r="D49" s="31" t="str">
+        <x:v>Desperado</x:v>
+      </x:c>
+      <x:c r="E49" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F49" s="31" t="str">
+        <x:v>Placeholder framework for hypnosis / escape with moving or timed shots, using Playfield chase + upper escape.</x:v>
+      </x:c>
+      <x:c r="G49" s="31" t="str">
+        <x:v>Ends when goals or timer / ball end.</x:v>
+      </x:c>
+      <x:c r="H49" s="31" t="str">
+        <x:v>Desperado jackpots. Flying-horse escape pressure.</x:v>
+      </x:c>
+      <x:c r="I49" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B50" s="31" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="C50" s="31" t="str">
+        <x:v>skymaster</x:v>
+      </x:c>
+      <x:c r="D50" s="31" t="str">
+        <x:v>Skymaster</x:v>
+      </x:c>
+      <x:c r="E50" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F50" s="31" t="str">
+        <x:v>Saucers open gate; upper entrance starts a limited-flip roof attempt on the 3 upper targets.</x:v>
+      </x:c>
+      <x:c r="G50" s="31" t="str">
+        <x:v>Ends after 3 roof clears, or stops on ball end.</x:v>
+      </x:c>
+      <x:c r="H50" s="31" t="str">
+        <x:v>Rooftop Swarm: saucers open gate; upper entrance starts limited-flip roof attempt; first two targets are JPs and third is Super boosted by remaining flips.</x:v>
+      </x:c>
+      <x:c r="I50" s="31" t="str">
+        <x:v>Improved: persistent gate state, roof targets, flips, and roof-clear progress.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B51" s="31" t="str">
+        <x:v>Savage Oddities</x:v>
+      </x:c>
+      <x:c r="C51" s="31" t="str">
+        <x:v>swamp_reptiles</x:v>
+      </x:c>
+      <x:c r="D51" s="31" t="str">
+        <x:v>Swamp Reptiles</x:v>
+      </x:c>
+      <x:c r="E51" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F51" s="31" t="str">
+        <x:v>Play the retained Reptilla-style shot flow under the Swamp Reptiles identity.</x:v>
+      </x:c>
+      <x:c r="G51" s="31" t="str">
+        <x:v>Ends when retained Reptilla-style objectives complete; otherwise stops on ball end.</x:v>
+      </x:c>
+      <x:c r="H51" s="31" t="str">
+        <x:v>Repurposed Reptilla implementation; swamp_bonus bank preserved under new mode identity.</x:v>
+      </x:c>
+      <x:c r="I51" s="31" t="str">
+        <x:v>Improved: persistent Rampage, lit-jackpot, collected-jackpot, and Super status.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B52" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C52" s="31" t="str">
+        <x:v>sir_galahad</x:v>
+      </x:c>
+      <x:c r="D52" s="31" t="str">
+        <x:v>Sir Galahad</x:v>
+      </x:c>
+      <x:c r="E52" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F52" s="31" t="str">
+        <x:v>Placeholder framework for medieval time shift with timed duel / sequence, using Changing knight and castle shots.</x:v>
+      </x:c>
+      <x:c r="G52" s="31" t="str">
+        <x:v>Ends when goals or timer / ball end.</x:v>
+      </x:c>
+      <x:c r="H52" s="31" t="str">
+        <x:v>Duel jackpots. Short combat windows.</x:v>
+      </x:c>
+      <x:c r="I52" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B53" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C53" s="31" t="str">
+        <x:v>master_vine</x:v>
+      </x:c>
+      <x:c r="D53" s="31" t="str">
+        <x:v>Master Vine</x:v>
+      </x:c>
+      <x:c r="E53" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F53" s="31" t="str">
+        <x:v>Placeholder framework for spreading control with hold / lock shots, using Targets + lanes.</x:v>
+      </x:c>
+      <x:c r="G53" s="31" t="str">
+        <x:v>Ends when goals or spread limit / ball end.</x:v>
+      </x:c>
+      <x:c r="H53" s="31" t="str">
+        <x:v>Vine spread/cut jackpots. Spreading hazard.</x:v>
+      </x:c>
+      <x:c r="I53" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B54" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C54" s="31" t="str">
+        <x:v>master_technician</x:v>
+      </x:c>
+      <x:c r="D54" s="31" t="str">
+        <x:v>Master Technician</x:v>
+      </x:c>
+      <x:c r="E54" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F54" s="31" t="str">
+        <x:v>Drops determine spinner value; spinner/shot flow cashes in Technician scoring.</x:v>
+      </x:c>
+      <x:c r="G54" s="31" t="str">
+        <x:v>Ends when Technician objectives are cleared; otherwise stops on ball end.</x:v>
+      </x:c>
+      <x:c r="H54" s="31" t="str">
+        <x:v>Repurposed Meteor homage: drops determine spinner value; technician_bonus bank.</x:v>
+      </x:c>
+      <x:c r="I54" s="31" t="str">
+        <x:v>Improved: persistent left/right drop progress and live spinner value.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B55" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C55" s="31" t="str">
+        <x:v>spider_men</x:v>
+      </x:c>
+      <x:c r="D55" s="31" t="str">
+        <x:v>The Spider-Men</x:v>
+      </x:c>
+      <x:c r="E55" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F55" s="31" t="str">
+        <x:v>Placeholder framework for identity / alien doubles with mystery / precision, using Changing Spider-Man shots.</x:v>
+      </x:c>
+      <x:c r="G55" s="31" t="str">
+        <x:v>Ends when goals or mistake limit / ball end.</x:v>
+      </x:c>
+      <x:c r="H55" s="31" t="str">
+        <x:v>Identity jackpots / Super. Wrong-identity pressure.</x:v>
+      </x:c>
+      <x:c r="I55" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B56" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C56" s="31" t="str">
+        <x:v>von_rantenraven</x:v>
+      </x:c>
+      <x:c r="D56" s="31" t="str">
+        <x:v>Baron Von Rantenraven</x:v>
+      </x:c>
+      <x:c r="E56" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F56" s="31" t="str">
+        <x:v>Placeholder framework for aerial invasion with whole-playfield assault, using Air-raid, paralysis, and upper shots.</x:v>
+      </x:c>
+      <x:c r="G56" s="31" t="str">
+        <x:v>Ends when goals completed / ball end.</x:v>
+      </x:c>
+      <x:c r="H56" s="31" t="str">
+        <x:v>Sky Harbor jackpots. Escalating invasion pressure.</x:v>
+      </x:c>
+      <x:c r="I56" s="31" t="str">
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6466,89 +7809,100 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="31" t="str">
-        <x:v>Progression event convention</x:v>
+        <x:v>Campaign structure</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>&lt;mode_key&gt;_mode_complete</x:v>
+        <x:v>11 chapters / 55 villains / 11 mini-wizards</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
-        <x:v>Single event means mode is done for progression; no _resolved and no meaningful failed branch.</x:v>
+        <x:v>Danger Lurks is Chapter 5. Final Showdown qualifies only after the Chapter 11 wizard is completed.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="31" t="str">
-        <x:v>Durable state values</x:v>
+        <x:v>Progression event convention</x:v>
       </x:c>
       <x:c r="B3" s="31" t="str">
-        <x:v>0 / 1 / 2</x:v>
+        <x:v>&lt;mode_key&gt;_mode_complete</x:v>
       </x:c>
       <x:c r="C3" s="31" t="str">
-        <x:v>0 = not played, 1 = playing, 2 = completed. Per-mode _state vars remain.</x:v>
+        <x:v>Single event means mode is done for progression; no _resolved and no meaningful failed branch.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="31" t="str">
-        <x:v>Generic counter convention</x:v>
+        <x:v>Durable state values</x:v>
       </x:c>
       <x:c r="B4" s="31" t="str">
-        <x:v>active_mode_points / active_mode_hits / active_mode_major_hits</x:v>
+        <x:v>0 / 1 / 2</x:v>
       </x:c>
       <x:c r="C4" s="31" t="str">
-        <x:v>Avoid reintroducing per-mode generic counters unless the stat is truly mode-specific.</x:v>
+        <x:v>0 = not played, 1 = playing, 2 = completed. Per-mode _state vars remain.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="31" t="str">
-        <x:v>Wizard case files</x:v>
+        <x:v>Generic counter convention</x:v>
       </x:c>
       <x:c r="B5" s="31" t="str">
-        <x:v>0–25 chapter total</x:v>
+        <x:v>active_mode_points / active_mode_hits / active_mode_major_hits</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>Wizard values use collected chapter case files; active case-file powers are locked out during wizards.</x:v>
+        <x:v>Avoid reintroducing per-mode generic counters unless the stat is truly mode-specific.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="31" t="str">
-        <x:v>Case-file/Daily Bugle widget</x:v>
+        <x:v>Wizard case files</x:v>
       </x:c>
       <x:c r="B6" s="31" t="str">
-        <x:v>x/5 case files + x/25 wizard prep + Daily/Bugle A/B status</x:v>
+        <x:v>0–25 chapter total</x:v>
       </x:c>
       <x:c r="C6" s="31" t="str">
-        <x:v>Recent patch added safer defaults and widget refresh events; still needs machine/UI verification.</x:v>
+        <x:v>Wizard values use collected chapter case files; active case-file powers are locked out during wizards.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="31" t="str">
-        <x:v>Bonus mode</x:v>
+        <x:v>Case-file/Daily Bugle widget</x:v>
       </x:c>
       <x:c r="B7" s="31" t="str">
-        <x:v>Custom wait-queue sequence</x:v>
+        <x:v>x/5 case files + x/25 wizard prep + Daily/Bugle A/B status</x:v>
       </x:c>
       <x:c r="C7" s="31" t="str">
-        <x:v>Regular bonus buckets are multiplied; mode bonus banks list separately and carry over. Held Bonus is consumed unless earned again.</x:v>
+        <x:v>Recent patch added safer defaults and widget refresh events; still needs machine/UI verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="31" t="str">
-        <x:v>Chapter select rescue</x:v>
+        <x:v>Bonus mode</x:v>
       </x:c>
       <x:c r="B8" s="31" t="str">
-        <x:v>chapter_select_ball_save</x:v>
+        <x:v>Custom wait-queue sequence</x:v>
       </x:c>
       <x:c r="C8" s="31" t="str">
-        <x:v>Wizard completion uses controlled drain/ball-save rescue to reach shooter lane without ending the ball normally.</x:v>
+        <x:v>Regular bonus buckets are multiplied; mode bonus banks list separately and carry over. Held Bonus is consumed unless earned again.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="31" t="str">
+        <x:v>Chapter select rescue</x:v>
+      </x:c>
+      <x:c r="B9" s="31" t="str">
+        <x:v>chapter_select_ball_save</x:v>
+      </x:c>
+      <x:c r="C9" s="31" t="str">
+        <x:v>Wizard completion uses controlled drain/ball-save rescue to reach shooter lane without ending the ball normally; chapter selection supports Chapters 1–11.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
         <x:v>Wizard rooftop gate</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B10" s="14" t="str">
         <x:v>The physical rooftop gate is explicitly closed at game start. When chapter_mini_wizard_ready becomes true, villain_progression immediately pulses rooftop_diverter_open; a drop-target hit is not required and qualifying drops are ignored while the wizard is ready.</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C10" s="14" t="str">
         <x:v>Implemented 2026-07-23</x:v>
       </x:c>
     </x:row>
@@ -6568,16 +7922,16 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="49" t="str">
+      <x:c r="A1" s="53" t="str">
         <x:v>Priority</x:v>
       </x:c>
-      <x:c r="B1" s="49" t="str">
+      <x:c r="B1" s="53" t="str">
         <x:v>Todo</x:v>
       </x:c>
-      <x:c r="C1" s="49" t="str">
+      <x:c r="C1" s="53" t="str">
         <x:v>Details</x:v>
       </x:c>
-      <x:c r="D1" s="49" t="str">
+      <x:c r="D1" s="53" t="str">
         <x:v>Status</x:v>
       </x:c>
     </x:row>
@@ -6746,7 +8100,7 @@
         <x:v>Update docs for chapter select, wizard transitions, bonus, lighting, ball save, mode behavior.</x:v>
       </x:c>
       <x:c r="D13" s="45" t="str">
-        <x:v>In progress — workbook refreshed through wizard gate behavior on 2026-07-23</x:v>
+        <x:v>In progress — all tracker sheets reconciled to 11 chapters on 2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="38" customHeight="1">
@@ -6754,10 +8108,10 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="B14" s="45" t="str">
-        <x:v>Chapter 5–10 wizard design</x:v>
+        <x:v>Chapter 5 and 7–11 wizard design</x:v>
       </x:c>
       <x:c r="C14" s="45" t="str">
-        <x:v>Replace placeholder/simple wizard shells when ready.</x:v>
+        <x:v>Fully design The Web Tightens and replace the placeholder/simple wizard shells for Mad Science Meltdown through Time-Tossed Showdown.</x:v>
       </x:c>
       <x:c r="D14" s="45" t="str">
         <x:v>Future</x:v>
@@ -6768,56 +8122,62 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="B15" s="45" t="str">
-        <x:v>Chapter 5–10 bonus banks</x:v>
+        <x:v>Chapter 5–11 bonus banks</x:v>
       </x:c>
       <x:c r="C15" s="45" t="str">
-        <x:v>Implement later banked bonus modes using current naming: super_swami, dumpty, radiation, plutonians, swamp, technician.</x:v>
+        <x:v>Fiddler Ransom is structurally wired. Implement earning rules for fiddler_bonus and later banks: super_swami_bonus, dumpty_bonus, blotto_bonus, devargas_bonus, swamp_bonus, and technician_bonus.</x:v>
       </x:c>
       <x:c r="D15" s="45" t="str">
         <x:v>Future</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="str">
+      <x:c r="A16" s="14" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="B16" t="str">
+      <x:c r="B16" s="14" t="str">
         <x:v>Mystery instant villain qualification</x:v>
       </x:c>
-      <x:c r="C16" t="str">
+      <x:c r="C16" s="14" t="str">
         <x:v>Mystery award fully qualifies all three villain-start saucers only when no villain/wizard/start flow is active and an unplayed chapter villain remains. Uses sm_objective_spotted on the voice bus.</x:v>
       </x:c>
-      <x:c r="D16" t="str">
+      <x:c r="D16" s="14" t="str">
         <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
+      <x:c r="A17" s="14" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="B17" t="str">
+      <x:c r="B17" s="14" t="str">
         <x:v>Mystery immediate next villain</x:v>
       </x:c>
-      <x:c r="C17" t="str">
+      <x:c r="C17" s="14" t="str">
         <x:v>Mystery award shows STARTING NEXT VILLAIN plus the villain name, plays sm_objective_spotted on the voice bus, waits 2 seconds, then starts the first unplayed villain.</x:v>
       </x:c>
-      <x:c r="D17" t="str">
+      <x:c r="D17" s="14" t="str">
         <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="str">
+      <x:c r="A18" s="14" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="B18" t="str">
+      <x:c r="B18" s="14" t="str">
         <x:v>Villain music transition-track cleanup</x:v>
       </x:c>
-      <x:c r="C18" t="str">
-        <x:v>Reassigned Trubble Unleashed to motorcycle_circus; Fifth Avenue Phantom to waiting; Master Plan to fbi; Ice Monster to the_shadows; Nature Strikes Back to don_and_dewey. Selection/intro/summary tracks remain unchanged.</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
+      <x:c r="C18" s="14" t="str">
+        <x:v>Reassigned Trubble Unleashed to motorcycle_circus; Fifth Avenue Phantom to waiting; Master Plan to fbi; The Plutonians to the_shadows; Nature Strikes Back to don_and_dewey. Selection/intro/summary tracks remain unchanged.</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="str">
         <x:v>Implemented - needs test</x:v>
       </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="14"/>
+      <x:c r="B19" s="14"/>
+      <x:c r="C19" s="14"/>
+      <x:c r="D19" s="14"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -6851,13 +8211,13 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="31" t="str">
-        <x:v>Current codebase</x:v>
+        <x:v>Current full codebase</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>/mnt/data/asm67_2026_07_14_2pm.zip</x:v>
+        <x:v>/mnt/data/ASM67_2026_07_24_1pm.zip</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
-        <x:v>Source of truth for this workbook update.</x:v>
+        <x:v>Current source-of-truth full ZIP supplied by the user.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6868,40 +8228,73 @@
         <x:v>docs/spiderman_1967_50_villain_chapter_plan.xlsx</x:v>
       </x:c>
       <x:c r="C3" s="31" t="str">
-        <x:v>Workbook updated in docs folder.</x:v>
+        <x:v>Stable tracker filename retained for Git friendliness.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="31" t="str">
-        <x:v>Episode list</x:v>
+        <x:v>Chapter 5 patch</x:v>
       </x:c>
       <x:c r="B4" s="31" t="str">
-        <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
+        <x:v>/mnt/data/ASM67_2026_07_24_danger_lurks_chapter5_changed_files_only.zip</x:v>
       </x:c>
       <x:c r="C4" s="31" t="str">
-        <x:v>General episode/source reference.</x:v>
+        <x:v>Adds Danger Lurks, shifts later chapters, and adds The Web Tightens.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="31" t="str">
-        <x:v>Project note</x:v>
+        <x:v>Fiddler bonus patch</x:v>
       </x:c>
       <x:c r="B5" s="31" t="str">
-        <x:v>ASM67 project memory and current chat todo list</x:v>
+        <x:v>/mnt/data/ASM67_2026_07_24_fiddler_persistent_bonus_changed_files_only.zip</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>Used for settled design decisions and current work status not fully represented in code comments.</x:v>
+        <x:v>Adds the persistent fiddler_bonus structure.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>Recent patch</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
-        <x:v>/mnt/data/ASM67_2026_07_14_2pm_the_fly_rooftop_swarm_changed_files_only.zip</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>The Fly Rooftop Swarm coded; spreadsheet also retains Pardo/Lizard updates.</x:v>
+      <x:c r="A6" s="14" t="str">
+        <x:v>Player-variable cleanup</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>/mnt/data/ASM67_2026_07_24_the_web_tightens_player_vars_cleanup_changed_files_only.zip</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>Removes redundant wizard-specific display variables.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>Episode list</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>https://en.wikipedia.org/wiki/List_of_Spider-Man_(1967_TV_series)_episodes</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>General episode reference.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>Project notes</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>ASM67 project memory and current design decisions</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>Used for settled roster, mechanics, and workflow decisions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>Tracker audit</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>All sheets reconciled to 11 chapters and 55 villains.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7022,19 +8415,19 @@
         <x:v>Crime Wave</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>Diamond Smugglers</x:v>
+        <x:v>Doctor Cool</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
-        <x:v>diamond_smugglers</x:v>
+        <x:v>doctor_cool</x:v>
       </x:c>
       <x:c r="E5" s="31" t="str">
         <x:v>diamond_bonus</x:v>
       </x:c>
       <x:c r="F5" s="31" t="str">
-        <x:v>DIAMOND SMUGGLERS</x:v>
+        <x:v>FROZEN DIAMONDS</x:v>
       </x:c>
       <x:c r="G5" s="31" t="str">
-        <x:v>Implemented bank; drops +25K, STAR +100K.</x:v>
+        <x:v>Implemented bank retained from Diamond Smugglers; drops +25K and STAR +100K.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -7042,22 +8435,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="31" t="str">
-        <x:v>Mystic Menace</x:v>
+        <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C6" s="31" t="str">
-        <x:v>Super Swami</x:v>
+        <x:v>Fiddler</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
-        <x:v>super_swami</x:v>
+        <x:v>fiddler</x:v>
       </x:c>
       <x:c r="E6" s="31" t="str">
-        <x:v>super_swami_bonus</x:v>
+        <x:v>fiddler_bonus</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
-        <x:v>SUPER SWAMI</x:v>
+        <x:v>FIDDLER RANSOM</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Planned/declared; replaces earlier mystic_bonus proposal.</x:v>
+        <x:v>Persistent Chapter 5 bonus bank. Initialized for every player, included in the custom and end-of-ball bonus systems, cleared after collection unless held, and shown on Fiddler's summary. The full mode will define how ransom is earned.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -7065,22 +8458,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="31" t="str">
-        <x:v>Mad Science</x:v>
+        <x:v>Mystic Menace</x:v>
       </x:c>
       <x:c r="C7" s="31" t="str">
-        <x:v>Doctor Dumpty</x:v>
+        <x:v>Super Swami</x:v>
       </x:c>
       <x:c r="D7" s="31" t="str">
-        <x:v>doctor_dumpty</x:v>
+        <x:v>super_swami</x:v>
       </x:c>
       <x:c r="E7" s="31" t="str">
-        <x:v>dumpty_bonus</x:v>
+        <x:v>super_swami_bonus</x:v>
       </x:c>
       <x:c r="F7" s="31" t="str">
-        <x:v>DUMPTY DEVICES</x:v>
+        <x:v>SUPER SWAMI</x:v>
       </x:c>
       <x:c r="G7" s="31" t="str">
-        <x:v>Planned/declared Chapter 6 bank.</x:v>
+        <x:v>Planned/declared; replaces earlier mystic_bonus proposal.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -7088,19 +8481,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="31" t="str">
-        <x:v>Elemental Chaos</x:v>
+        <x:v>Mad Science</x:v>
       </x:c>
       <x:c r="C8" s="31" t="str">
-        <x:v>Radiation Specialist</x:v>
+        <x:v>Doctor Dumpty</x:v>
       </x:c>
       <x:c r="D8" s="31" t="str">
-        <x:v>radiation_specialist</x:v>
+        <x:v>doctor_dumpty</x:v>
       </x:c>
       <x:c r="E8" s="31" t="str">
-        <x:v>radiation_bonus</x:v>
+        <x:v>dumpty_bonus</x:v>
       </x:c>
       <x:c r="F8" s="31" t="str">
-        <x:v>RADIATION RAMPAGE</x:v>
+        <x:v>DUMPTY DEVICES</x:v>
       </x:c>
       <x:c r="G8" s="31" t="str">
         <x:v>Planned/declared Chapter 7 bank.</x:v>
@@ -7111,22 +8504,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="31" t="str">
-        <x:v>Lost Worlds</x:v>
+        <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="C9" s="31" t="str">
-        <x:v>The Plutonians</x:v>
+        <x:v>Clive and Blotto</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
-        <x:v>plutonians</x:v>
+        <x:v>clive_blotto</x:v>
       </x:c>
       <x:c r="E9" s="31" t="str">
-        <x:v>plutonians_bonus</x:v>
+        <x:v>blotto_bonus</x:v>
       </x:c>
       <x:c r="F9" s="31" t="str">
-        <x:v>THE PLUTONIANS</x:v>
+        <x:v>BLOTTO RAMPAGE</x:v>
       </x:c>
       <x:c r="G9" s="31" t="str">
-        <x:v>Planned/declared; plural variable name is current standard.</x:v>
+        <x:v>Former Radiation Specialist bank renamed for the Chapter 8 replacement identity.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -7134,22 +8527,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="31" t="str">
-        <x:v>Savage Oddities</x:v>
+        <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="C10" s="31" t="str">
-        <x:v>Swamp Reptiles</x:v>
+        <x:v>DeVargas</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
-        <x:v>swamp_reptiles</x:v>
+        <x:v>devargas</x:v>
       </x:c>
       <x:c r="E10" s="31" t="str">
-        <x:v>swamp_bonus</x:v>
+        <x:v>devargas_bonus</x:v>
       </x:c>
       <x:c r="F10" s="31" t="str">
-        <x:v>SWAMP REPTILES</x:v>
+        <x:v>DEVARGAS GOLD</x:v>
       </x:c>
       <x:c r="G10" s="31" t="str">
-        <x:v>Planned/declared Chapter 9 bank.</x:v>
+        <x:v>Former Chapter 9 placeholder bonus bank reassigned to DeVargas; scoring rules will be finalized during design.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -7157,22 +8550,45 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="31" t="str">
-        <x:v>Dimensional Finale</x:v>
+        <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="C11" s="31" t="str">
-        <x:v>Master Technician</x:v>
+        <x:v>Swamp Reptiles</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
-        <x:v>master_technician</x:v>
+        <x:v>swamp_reptiles</x:v>
       </x:c>
       <x:c r="E11" s="31" t="str">
-        <x:v>technician_bonus</x:v>
+        <x:v>swamp_bonus</x:v>
       </x:c>
       <x:c r="F11" s="31" t="str">
-        <x:v>TECHNICIAN TRAP</x:v>
+        <x:v>SWAMP REPTILES</x:v>
       </x:c>
       <x:c r="G11" s="31" t="str">
         <x:v>Planned/declared Chapter 10 bank.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="31" t="str">
+        <x:v>Dimensional Finale</x:v>
+      </x:c>
+      <x:c r="C12" s="31" t="str">
+        <x:v>Master Technician</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="str">
+        <x:v>master_technician</x:v>
+      </x:c>
+      <x:c r="E12" s="31" t="str">
+        <x:v>technician_bonus</x:v>
+      </x:c>
+      <x:c r="F12" s="31" t="str">
+        <x:v>TECHNICIAN TRAP</x:v>
+      </x:c>
+      <x:c r="G12" s="31" t="str">
+        <x:v>Planned/declared Chapter 11 bank.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rede25178088c4ca3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R7cc381b0348e4468"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Re537ee9272804efd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R8c14b1da4ffd47a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Ra6f0daa3e4104cab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R4feab012ba7a4482"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R6afeb09425a54dc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R596f224eacad48cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R770924cc95584171"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R812db085eae3427e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rcd15c5b004ef49c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R45c5630ab4ed4acc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra6803f97761d43d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R22331c687d20434b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R31e13f2883844e11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Ra19af468d046437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rd01261f17d5844f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rf2d597d84d8c4ab4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rb082b0577f1344b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R306814ab4f384907"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R2379fff1deb34de5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R44c0c7bb76f74ed7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R2ae373dbd14d4644"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R3ec3d50a4a97455c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -585,6 +585,30 @@
       <x:c r="D8" s="14"/>
       <x:c r="E8" s="14"/>
     </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>Consistency cleanup</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>Removed 14 obsolete exported player variables, replaced the Kingpin carousel panel with The Plotter, and added Crime Wave bookends.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>Stale asset cleanup</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>Removed the unloaded regular Kingpin mode, old The Fly mode, and three unused widgets. Final Showdown remains the internal key for the Kingpin finale.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>Desperado implementation</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>Former Kingpin limited-shot right-bank pursuit has been converted to Desperado without restoring the old Kingpin player-variable payload.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
@@ -2579,31 +2603,31 @@
         <x:v>Desperado</x:v>
       </x:c>
       <x:c r="E49" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented repurpose / needs playtest</x:v>
       </x:c>
       <x:c r="F49" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G49" s="31" t="str">
-        <x:v>Hypnosis / escape</x:v>
+        <x:v>Timed pursuit</x:v>
       </x:c>
       <x:c r="H49" s="31" t="str">
-        <x:v>Moving or timed shots</x:v>
+        <x:v>Limited shots per round</x:v>
       </x:c>
       <x:c r="I49" s="31" t="str">
-        <x:v>Playfield chase + upper escape</x:v>
+        <x:v>Right 5-bank + left bank</x:v>
       </x:c>
       <x:c r="J49" s="31" t="str">
-        <x:v>Desperado jackpots</x:v>
+        <x:v>Unique target values and optional showdown jackpot</x:v>
       </x:c>
       <x:c r="K49" s="31" t="str">
-        <x:v>Flying-horse escape pressure</x:v>
+        <x:v>Escalating shot allowance / 60-second timer</x:v>
       </x:c>
       <x:c r="L49" s="31" t="str">
-        <x:v>Goals or timer / ball end</x:v>
+        <x:v>Five unique targets or timer / ball end</x:v>
       </x:c>
       <x:c r="M49" s="31" t="str">
-        <x:v>Oddball western villain; full episode-based design pending.</x:v>
+        <x:v>Former Kingpin rules fit Desperado as a shooting-gallery pursuit; all temporary round state remains in Python.</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -2910,7 +2934,7 @@
         <x:v>Decision</x:v>
       </x:c>
       <x:c r="C1" s="59" t="str">
-        <x:v>Variables</x:v>
+        <x:v>Variables / Files</x:v>
       </x:c>
       <x:c r="D1" s="59" t="str">
         <x:v>Reason</x:v>
@@ -3018,10 +3042,10 @@
         <x:v>Remove</x:v>
       </x:c>
       <x:c r="C4" s="31" t="str">
-        <x:v>the_web_tightens_case_file_bonus</x:v>
+        <x:v>the_web_tightens_case_file_bonus, the_web_tightens_jackpot_value</x:v>
       </x:c>
       <x:c r="D4" s="31" t="str">
-        <x:v>Duplicates shared mini_wizard_case_file_bonus and a Python instance attribute.</x:v>
+        <x:v>Temporary values belong in Python/shared mini-wizard variables.</x:v>
       </x:c>
       <x:c r="E4" s="14"/>
       <x:c r="F4" s="14"/>
@@ -3048,16 +3072,16 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="31" t="str">
-        <x:v>The Web Tightens</x:v>
+        <x:v>Chapter 11 selection</x:v>
       </x:c>
       <x:c r="B5" s="31" t="str">
-        <x:v>Remove</x:v>
+        <x:v>Keep</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>the_web_tightens_jackpot_value</x:v>
+        <x:v>chapter_11_unlocked, chapter_11_collected</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
-        <x:v>Computed from BASE_JACKPOT plus the shared case-file bonus; it does not need persistence or Godot export.</x:v>
+        <x:v>Required by chapter-selection progression and display.</x:v>
       </x:c>
       <x:c r="E5" s="14"/>
       <x:c r="F5" s="14"/>
@@ -3084,30 +3108,100 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="31" t="str">
-        <x:v>Chapter 11 selection</x:v>
+        <x:v>Fiddler bonus</x:v>
       </x:c>
       <x:c r="B6" s="31" t="str">
         <x:v>Keep</x:v>
       </x:c>
       <x:c r="C6" s="31" t="str">
-        <x:v>chapter_11_unlocked, chapter_11_collected</x:v>
+        <x:v>fiddler_bonus</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
-        <x:v>Required by chapter-selection progression and display.</x:v>
+        <x:v>Persistent end-of-ball Chapter 5 bonus bank.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="31" t="str">
-        <x:v>Fiddler bonus</x:v>
+        <x:v>Crime Wave</x:v>
       </x:c>
       <x:c r="B7" s="31" t="str">
         <x:v>Keep</x:v>
       </x:c>
       <x:c r="C7" s="31" t="str">
-        <x:v>fiddler_bonus</x:v>
+        <x:v>crime_wave_state</x:v>
       </x:c>
       <x:c r="D7" s="31" t="str">
-        <x:v>Persistent end-of-ball Chapter 5 bonus bank.</x:v>
+        <x:v>Only persistent state required for the Chapter 4 wizard.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="31" t="str">
+        <x:v>Crime Wave legacy</x:v>
+      </x:c>
+      <x:c r="B8" s="31" t="str">
+        <x:v>Remove</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="str">
+        <x:v>crime_wave_crackdown_state, crime_wave_crackdown_case_file_bonus</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="str">
+        <x:v>Obsolete predecessor variables; no active code or widget uses them.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="31" t="str">
+        <x:v>Kingpin regular mode</x:v>
+      </x:c>
+      <x:c r="B9" s="31" t="str">
+        <x:v>Remove</x:v>
+      </x:c>
+      <x:c r="C9" s="31" t="str">
+        <x:v>kingpin_state plus 11 kingpin_* runtime variables</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="str">
+        <x:v>Kingpin is now the final wizard identity; the old regular mode is unloaded and removed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="31" t="str">
+        <x:v>Stale modes</x:v>
+      </x:c>
+      <x:c r="B10" s="31" t="str">
+        <x:v>Delete</x:v>
+      </x:c>
+      <x:c r="C10" s="31" t="str">
+        <x:v>modes/kingpin, modes/the_fly</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="str">
+        <x:v>Replaced by final_showdown/Kingpin and skymaster respectively.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="31" t="str">
+        <x:v>Stale widgets</x:v>
+      </x:c>
+      <x:c r="B11" s="31" t="str">
+        <x:v>Delete</x:v>
+      </x:c>
+      <x:c r="C11" s="31" t="str">
+        <x:v>widgets/kingpin.tscn, widgets/crime_wave_crackdown.tscn, widgets/crime_wave_mini.tscn</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="str">
+        <x:v>No active config references these widgets.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>Desperado repurpose</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>Keep minimal</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>desperado_state plus active_mode_points / active_mode_hits / active_mode_major_hits</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>Former Kingpin round, timer, target, and extra-round variables remain Python-only and are not exported to Godot.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3504,10 +3598,10 @@
         <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="B11" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C11" s="31" t="n">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="31" t="n">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
         <x:v>Who Is the Real Villain?</x:v>
@@ -5131,10 +5225,10 @@
         <x:v>Desperado</x:v>
       </x:c>
       <x:c r="G49" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented repurpose / needs playtest</x:v>
       </x:c>
       <x:c r="H49" s="31" t="str">
-        <x:v>Former Skymaster placeholder retained for redesign. Hypnotic cowboy robber rides a flying mechanical horse.</x:v>
+        <x:v>Former Kingpin limited-shot pursuit repurposed for Desperado. Complete all five unique right-bank targets in escalating rounds before the timer expires; left-bank completion adds time. More Jackpots adds a final showdown jackpot.</x:v>
       </x:c>
       <x:c r="I49" s="31" t="str">
         <x:v>who_is_the_real_villain</x:v>
@@ -6138,7 +6232,21 @@
         <x:v>Kingpin</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>The existing final-wizard structure is reserved for a future Kingpin retheme.</x:v>
+        <x:v>The final_showdown mechanics remain under the stable internal key; visible bookends now identify the finale as Kingpin.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="14" t="str">
+        <x:v>kingpin_regular_gameplay</x:v>
+      </x:c>
+      <x:c r="B32" s="14" t="str">
+        <x:v>desperado</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="str">
+        <x:v>Desperado</x:v>
+      </x:c>
+      <x:c r="D32" s="14" t="str">
+        <x:v>Former Kingpin timed right-bank pursuit repurposed as a single-ball Desperado shooting-gallery mode. Old Kingpin-specific player variables were not restored.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7567,16 +7675,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F49" s="31" t="str">
-        <x:v>Placeholder framework for hypnosis / escape with moving or timed shots, using Playfield chase + upper escape.</x:v>
+        <x:v>Complete unique targets on the right 5-bank. Round 1 allows one shot before Desperado escapes and resets the bank; each later round allows one more shot.</x:v>
       </x:c>
       <x:c r="G49" s="31" t="str">
-        <x:v>Ends when goals or timer / ball end.</x:v>
+        <x:v>Capture all five unique targets before time expires. More Jackpots adds one final right-bank showdown jackpot.</x:v>
       </x:c>
       <x:c r="H49" s="31" t="str">
-        <x:v>Desperado jackpots. Flying-horse escape pressure.</x:v>
+        <x:v>60-second timer, or 70 with More Time. Left-bank completion adds 10 seconds. New targets score 200K; repeats 50K. Bigger raises them to 250K and 75K.</x:v>
       </x:c>
       <x:c r="I49" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented repurpose. Uses only desperado_state plus shared active-mode variables; round, timer, and target state stay in Python.</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -8027,7 +8135,7 @@
         <x:v>Visual polish / images</x:v>
       </x:c>
       <x:c r="C8" s="45" t="str">
-        <x:v>Replace placeholder villain/mode images and verify paths.</x:v>
+        <x:v>Replace placeholder villain/mode images and verify paths. The Plotter carousel currently reuses the former Kingpin image until dedicated art is supplied.</x:v>
       </x:c>
       <x:c r="D8" s="45" t="str">
         <x:v>Open</x:v>
@@ -8100,7 +8208,7 @@
         <x:v>Update docs for chapter select, wizard transitions, bonus, lighting, ball save, mode behavior.</x:v>
       </x:c>
       <x:c r="D13" s="45" t="str">
-        <x:v>In progress — all tracker sheets reconciled to 11 chapters on 2026-07-24</x:v>
+        <x:v>In progress — 3pm consistency cleanup documented on 2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="38" customHeight="1">
@@ -8214,7 +8322,7 @@
         <x:v>Current full codebase</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>/mnt/data/ASM67_2026_07_24_1pm.zip</x:v>
+        <x:v>/mnt/data/ASM67_2026_07_24_3pm.zip</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
         <x:v>Current source-of-truth full ZIP supplied by the user.</x:v>
@@ -8288,13 +8396,13 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>Tracker audit</x:v>
+        <x:v>Consistency cleanup</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>All sheets reconciled to 11 chapters and 55 villains.</x:v>
+        <x:v>Case Files, progression, player variables, bookends, carousel mappings, and stale mode/widget assets audited against the 3pm baseline.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra6803f97761d43d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R22331c687d20434b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R31e13f2883844e11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Ra19af468d046437e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rd01261f17d5844f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rf2d597d84d8c4ab4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rb082b0577f1344b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R306814ab4f384907"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R2379fff1deb34de5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R44c0c7bb76f74ed7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R2ae373dbd14d4644"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R3ec3d50a4a97455c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R04e3d1e6fa584d11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R69eb3e7fd30747b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R614a07bd342f45d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rba3465fd01b94c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R2fd9ba0368b144bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Red605d3b5f3c47c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Redd49342b6a54b3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R95f075ca6288413c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rea52b0ff5ce446e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R1effcb5080b14d8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Re40639a7fdc24e72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Re98a3b705f56420d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2808,7 +2808,7 @@
         <x:v>Master Technician</x:v>
       </x:c>
       <x:c r="E54" s="31" t="str">
-        <x:v>Implemented repurpose / needs polish</x:v>
+        <x:v>Implemented</x:v>
       </x:c>
       <x:c r="F54" s="31" t="str">
         <x:v>1</x:v>
@@ -2817,22 +2817,22 @@
         <x:v>Build-and-cash</x:v>
       </x:c>
       <x:c r="H54" s="31" t="str">
-        <x:v>Spinner value</x:v>
+        <x:v>Persistent eight-drop spinner build</x:v>
       </x:c>
       <x:c r="I54" s="31" t="str">
-        <x:v>Drops + spinner</x:v>
+        <x:v>All drops + spinner + saucers + lower inlanes</x:v>
       </x:c>
       <x:c r="J54" s="31" t="str">
-        <x:v>Drops determine spinner value</x:v>
+        <x:v>Spinner 50K–400K from down targets</x:v>
       </x:c>
       <x:c r="K54" s="31" t="str">
-        <x:v>Shot choice / cashout timing</x:v>
+        <x:v>Inlanes advance a random target; saucer resets left bank</x:v>
       </x:c>
       <x:c r="L54" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>All eight drops down / ball end</x:v>
       </x:c>
       <x:c r="M54" s="31" t="str">
-        <x:v>Working Meteor-style mechanic retained; Manhattan-lifting story provides the final-chapter scale.</x:v>
+        <x:v>Inlanes are helpful but risky because an inlane can knock down the final target and end the mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -5385,10 +5385,10 @@
         <x:v>Master Technician</x:v>
       </x:c>
       <x:c r="G54" s="31" t="str">
-        <x:v>Implemented repurpose / needs polish</x:v>
+        <x:v>Implemented</x:v>
       </x:c>
       <x:c r="H54" s="31" t="str">
-        <x:v>Working drop-built spinner-value mode retained. Theme draws from Swing City and Manhattan being lifted into the sky.</x:v>
+        <x:v>All eight drop targets build the web-spinner value. Spinner scores 50K plus 50K per down target, capped at 400K. Drops stay down; any saucer resets only the left three-bank. Either lower inlane knocks down one random standing target. Mode completes when all eight drops are down.</x:v>
       </x:c>
       <x:c r="I54" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -7820,16 +7820,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F54" s="31" t="str">
-        <x:v>Drops determine spinner value; spinner/shot flow cashes in Technician scoring.</x:v>
+        <x:v>All eight drops remain down and build the spinner from 50K to 400K. Either lower inlane knocks down one random standing target; any saucer resets only the left three-bank.</x:v>
       </x:c>
       <x:c r="G54" s="31" t="str">
-        <x:v>Ends when Technician objectives are cleared; otherwise stops on ball end.</x:v>
+        <x:v>Ends when all eight drop targets are down, including when an inlane knocks down the final target; otherwise stops on ball end.</x:v>
       </x:c>
       <x:c r="H54" s="31" t="str">
-        <x:v>Repurposed Meteor homage: drops determine spinner value; technician_bonus bank.</x:v>
+        <x:v>Spinner scores 50K + 50K per down target. Drop hits, including inlane-assisted drops, score 25K.</x:v>
       </x:c>
       <x:c r="I54" s="31" t="str">
-        <x:v>Improved: persistent left/right drop progress and live spinner value.</x:v>
+        <x:v>Implemented: no automatic completed-bank reset; inlanes advance one standing target; saucers reset the left three-bank while preserving right-bank progress.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R04e3d1e6fa584d11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R69eb3e7fd30747b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R614a07bd342f45d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rba3465fd01b94c82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R2fd9ba0368b144bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Red605d3b5f3c47c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Redd49342b6a54b3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R95f075ca6288413c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rea52b0ff5ce446e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R1effcb5080b14d8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Re40639a7fdc24e72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Re98a3b705f56420d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6ca8417204fb45d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rf986420369ed4797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R8e092e99f9884e44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R8f2b057238e0450d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R30622a5ddfcb4e19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R13dd3dfd28ae4dc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R414cd4bad3e445c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rc98826fb100e448b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R7a16e4a525fd40b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra6db289cb6054c8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rd29a597d063a4ae5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Racfd6f000099463e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1086,31 +1086,31 @@
         <x:v>Cerberus</x:v>
       </x:c>
       <x:c r="E12" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented</x:v>
       </x:c>
       <x:c r="F12" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>Timed matching</x:v>
+        <x:v>Timed risk/reward</x:v>
       </x:c>
       <x:c r="H12" s="31" t="str">
-        <x:v>Saucer control</x:v>
+        <x:v>Build multiple 3X saucers</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
-        <x:v>Upper targets + saucers</x:v>
+        <x:v>Upper targets + saucers + spinner</x:v>
       </x:c>
       <x:c r="J12" s="31" t="str">
-        <x:v>Matching saucer 2X jackpots</x:v>
+        <x:v>1X or 3X growing jackpots</x:v>
       </x:c>
       <x:c r="K12" s="31" t="str">
-        <x:v>Timer expiry</x:v>
+        <x:v>Stay upstairs to build 3X before collecting</x:v>
       </x:c>
       <x:c r="L12" s="31" t="str">
-        <x:v>3 saucer JPs / timer / ball end</x:v>
+        <x:v>16s timer expiry / ball end</x:v>
       </x:c>
       <x:c r="M12" s="31" t="str">
-        <x:v>Timer/matching role.</x:v>
+        <x:v>Open-ended scoring loop; gate closes on target qualification and opens after each jackpot collect.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2808,7 +2808,7 @@
         <x:v>Master Technician</x:v>
       </x:c>
       <x:c r="E54" s="31" t="str">
-        <x:v>Implemented</x:v>
+        <x:v>Implemented repurpose / needs polish</x:v>
       </x:c>
       <x:c r="F54" s="31" t="str">
         <x:v>1</x:v>
@@ -2817,22 +2817,22 @@
         <x:v>Build-and-cash</x:v>
       </x:c>
       <x:c r="H54" s="31" t="str">
-        <x:v>Persistent eight-drop spinner build</x:v>
+        <x:v>Spinner value</x:v>
       </x:c>
       <x:c r="I54" s="31" t="str">
-        <x:v>All drops + spinner + saucers + lower inlanes</x:v>
+        <x:v>Drops + spinner</x:v>
       </x:c>
       <x:c r="J54" s="31" t="str">
-        <x:v>Spinner 50K–400K from down targets</x:v>
+        <x:v>Drops determine spinner value</x:v>
       </x:c>
       <x:c r="K54" s="31" t="str">
-        <x:v>Inlanes advance a random target; saucer resets left bank</x:v>
+        <x:v>Shot choice / cashout timing</x:v>
       </x:c>
       <x:c r="L54" s="31" t="str">
-        <x:v>All eight drops down / ball end</x:v>
+        <x:v>Goals completed / ball end</x:v>
       </x:c>
       <x:c r="M54" s="31" t="str">
-        <x:v>Inlanes are helpful but risky because an inlane can knock down the final target and end the mode.</x:v>
+        <x:v>Working Meteor-style mechanic retained; Manhattan-lifting story provides the final-chapter scale.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -4041,10 +4041,10 @@
         <x:v>Cerberus</x:v>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented</x:v>
       </x:c>
       <x:c r="H12" s="31" t="str">
-        <x:v>Upper targets light saucers; matching saucer scores 2X; timer reset flow needs testing.</x:v>
+        <x:v>Any upper target lights all three saucers and upgrades its matching saucer to 3X. Multiple targets can build all three to 3X. A jackpot collect opens the gate, leaves other saucers lit at 1X, and normally turns off the collected saucer. More Jackpots relights the collected saucer at 1X.</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
         <x:v>trubble_unleashed</x:v>
@@ -5385,10 +5385,10 @@
         <x:v>Master Technician</x:v>
       </x:c>
       <x:c r="G54" s="31" t="str">
-        <x:v>Implemented</x:v>
+        <x:v>Implemented repurpose / needs polish</x:v>
       </x:c>
       <x:c r="H54" s="31" t="str">
-        <x:v>All eight drop targets build the web-spinner value. Spinner scores 50K plus 50K per down target, capped at 400K. Drops stay down; any saucer resets only the left three-bank. Either lower inlane knocks down one random standing target. Mode completes when all eight drops are down.</x:v>
+        <x:v>Working drop-built spinner-value mode retained. Theme draws from Swing City and Manhattan being lifted into the sky.</x:v>
       </x:c>
       <x:c r="I54" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -6602,16 +6602,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F12" s="31" t="str">
-        <x:v>Upper targets light saucers; matching saucer collects stronger 2X jackpots while timer is active.</x:v>
+        <x:v>Upper targets light all three saucers and upgrade matching saucers to 3X. Multiple 3X saucers can be built before collecting. A collect opens the gate and resets all remaining lit saucers to 1X.</x:v>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>Ends after 3 saucer jackpots, timer expiry, ball end, or mode completion state.</x:v>
+        <x:v>No fixed defeat count. Ends when the 16-second timer expires or on ball end; More Time uses 20 seconds.</x:v>
       </x:c>
       <x:c r="H12" s="31" t="str">
-        <x:v>Upper targets light saucers; matching saucer scores 2X; timer resets on key upper/spinner/saucer activity.</x:v>
+        <x:v>Spinner builds the jackpot from 100K by 10K per spin to 500K. Bigger Jackpots uses 150K, +15K, and a 750K cap. Timer starts on the first jackpot and resets on upper targets or any saucer hit, but not spinner.</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
-        <x:v>Improved: persistent upper-target/saucer guidance and 3-jackpot progress.</x:v>
+        <x:v>More Jackpots relights the collected saucer at 1X. Shot Assist awards the best lit jackpot. Safety Net remains the standard 10-second ball save.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -7820,16 +7820,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F54" s="31" t="str">
-        <x:v>All eight drops remain down and build the spinner from 50K to 400K. Either lower inlane knocks down one random standing target; any saucer resets only the left three-bank.</x:v>
+        <x:v>Drops determine spinner value; spinner/shot flow cashes in Technician scoring.</x:v>
       </x:c>
       <x:c r="G54" s="31" t="str">
-        <x:v>Ends when all eight drop targets are down, including when an inlane knocks down the final target; otherwise stops on ball end.</x:v>
+        <x:v>Ends when Technician objectives are cleared; otherwise stops on ball end.</x:v>
       </x:c>
       <x:c r="H54" s="31" t="str">
-        <x:v>Spinner scores 50K + 50K per down target. Drop hits, including inlane-assisted drops, score 25K.</x:v>
+        <x:v>Repurposed Meteor homage: drops determine spinner value; technician_bonus bank.</x:v>
       </x:c>
       <x:c r="I54" s="31" t="str">
-        <x:v>Implemented: no automatic completed-bank reset; inlanes advance one standing target; saucers reset the left three-bank while preserving right-bank progress.</x:v>
+        <x:v>Improved: persistent left/right drop progress and live spinner value.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6ca8417204fb45d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rf986420369ed4797"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R8e092e99f9884e44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R8f2b057238e0450d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R30622a5ddfcb4e19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R13dd3dfd28ae4dc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R414cd4bad3e445c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rc98826fb100e448b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R7a16e4a525fd40b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra6db289cb6054c8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rd29a597d063a4ae5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Racfd6f000099463e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R01254c0549ce422c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rbc1a240a15c94f0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rca40d037aec248aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R616539b9e4fa4b28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rdc3e6f02e8a14b9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R0efa83d169ef483b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R19e6546044d242d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rd2ed67af87f141e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rba398a8eca5c49fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R7e7bfc981c8648a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R58e3c8c4dc124a23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R5be75df09b8d4f3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1086,31 +1086,31 @@
         <x:v>Cerberus</x:v>
       </x:c>
       <x:c r="E12" s="31" t="str">
-        <x:v>Implemented</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="F12" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>Timed risk/reward</x:v>
+        <x:v>Timed matching</x:v>
       </x:c>
       <x:c r="H12" s="31" t="str">
-        <x:v>Build multiple 3X saucers</x:v>
+        <x:v>Saucer control</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
-        <x:v>Upper targets + saucers + spinner</x:v>
+        <x:v>Upper targets + saucers</x:v>
       </x:c>
       <x:c r="J12" s="31" t="str">
-        <x:v>1X or 3X growing jackpots</x:v>
+        <x:v>Matching saucer 2X jackpots</x:v>
       </x:c>
       <x:c r="K12" s="31" t="str">
-        <x:v>Stay upstairs to build 3X before collecting</x:v>
+        <x:v>Timer expiry</x:v>
       </x:c>
       <x:c r="L12" s="31" t="str">
-        <x:v>16s timer expiry / ball end</x:v>
+        <x:v>3 saucer JPs / timer / ball end</x:v>
       </x:c>
       <x:c r="M12" s="31" t="str">
-        <x:v>Open-ended scoring loop; gate closes on target qualification and opens after each jackpot collect.</x:v>
+        <x:v>Timer/matching role.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1701,7 +1701,7 @@
         <x:v>Pardo</x:v>
       </x:c>
       <x:c r="E27" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented</x:v>
       </x:c>
       <x:c r="F27" s="31" t="str">
         <x:v>1</x:v>
@@ -1710,22 +1710,22 @@
         <x:v>Mystery / reveal</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Mistake limit</x:v>
+        <x:v>Spinner-controlled reveal</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
-        <x:v>Spinner + 3 lit choices</x:v>
+        <x:v>Webs + upper targets + drop banks + separate pops</x:v>
       </x:c>
       <x:c r="J27" s="31" t="str">
-        <x:v>Correct-shot jackpots</x:v>
+        <x:v>Growing correct-shot jackpots</x:v>
       </x:c>
       <x:c r="K27" s="31" t="str">
-        <x:v>Wrong-shot mistakes</x:v>
+        <x:v>Memorize flashing green among solid red choices</x:v>
       </x:c>
       <x:c r="L27" s="31" t="str">
         <x:v>5 correct / 7 wrong / ball end</x:v>
       </x:c>
       <x:c r="M27" s="31" t="str">
-        <x:v>Mystic chapter reveal/mistake-limit role.</x:v>
+        <x:v>Both spinners reveal only; dynamic 250ms flash cadence follows the configured reveal duration.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1865,7 +1865,7 @@
         <x:v>Infinata</x:v>
       </x:c>
       <x:c r="E31" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Implemented</x:v>
       </x:c>
       <x:c r="F31" s="31" t="str">
         <x:v>1</x:v>
@@ -1874,22 +1874,22 @@
         <x:v>Sequential area completion</x:v>
       </x:c>
       <x:c r="H31" s="31" t="str">
-        <x:v>Green corruption areas</x:v>
+        <x:v>Distinct grouped/unique-shot areas</x:v>
       </x:c>
       <x:c r="I31" s="31" t="str">
-        <x:v>Pops, drops, webs, upper targets, saucers</x:v>
+        <x:v>Drops, two pops, two webs, upper targets, saucers</x:v>
       </x:c>
       <x:c r="J31" s="31" t="str">
-        <x:v>Rising areas + timed saucer Super</x:v>
+        <x:v>Rising area awards + timed saucer Super</x:v>
       </x:c>
       <x:c r="K31" s="31" t="str">
-        <x:v>One area at a time; 20s Super</x:v>
+        <x:v>One area at a time with clear progress lighting</x:v>
       </x:c>
       <x:c r="L31" s="31" t="str">
-        <x:v>Super / timer / ball end</x:v>
+        <x:v>Super collect / timer / ball end</x:v>
       </x:c>
       <x:c r="M31" s="31" t="str">
-        <x:v>Three required areas; optional fourth with More Jackpots.</x:v>
+        <x:v>Drop banks and upper targets need one hit; pops and webs require both unique switches.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4041,10 +4041,10 @@
         <x:v>Cerberus</x:v>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>Implemented</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H12" s="31" t="str">
-        <x:v>Any upper target lights all three saucers and upgrades its matching saucer to 3X. Multiple targets can build all three to 3X. A jackpot collect opens the gate, leaves other saucers lit at 1X, and normally turns off the collected saucer. More Jackpots relights the collected saucer at 1X.</x:v>
+        <x:v>Upper targets light saucers; matching saucer scores 2X; timer reset flow needs testing.</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
         <x:v>trubble_unleashed</x:v>
@@ -4521,10 +4521,10 @@
         <x:v>Pardo</x:v>
       </x:c>
       <x:c r="G27" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Hypnosis Reel: spinner reveals true shot among 3 choices; 5 correct shots defeat Pardo; 7 wrong choices lets him escape.</x:v>
+        <x:v>Hypnosis Reel: three choices are selected from webs, upper targets, drop banks, and separate left/right pops. Either spinner reveals the answer. The correct shot flashes green every 250ms for 2 seconds, or 4 seconds with More Time; wrong choices remain solid red.</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -4649,10 +4649,10 @@
         <x:v>Infinata</x:v>
       </x:c>
       <x:c r="G31" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Implemented</x:v>
       </x:c>
       <x:c r="H31" s="31" t="str">
-        <x:v>One green creature area lights at a time from pops, left drops, right drops, webs, and upper targets. Complete three to light all saucers for a 20-second 1M Super. More Jackpots adds a fourth optional area, Bigger raises values, More Time gives 30 seconds, Safety Net adds ball save, and Shot Assist awards the first two areas.</x:v>
+        <x:v>One area lights at a time. Left or right drops require any one drop; pops require one unique hit on each of the two pops; webs require both unique web targets; upper targets act as one grouped shot and require any one hit. Complete three areas to light all saucers for the timed Super. More Jackpots adds a fourth optional area.</x:v>
       </x:c>
       <x:c r="I31" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -6602,16 +6602,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F12" s="31" t="str">
-        <x:v>Upper targets light all three saucers and upgrade matching saucers to 3X. Multiple 3X saucers can be built before collecting. A collect opens the gate and resets all remaining lit saucers to 1X.</x:v>
+        <x:v>Upper targets light saucers; matching saucer collects stronger 2X jackpots while timer is active.</x:v>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>No fixed defeat count. Ends when the 16-second timer expires or on ball end; More Time uses 20 seconds.</x:v>
+        <x:v>Ends after 3 saucer jackpots, timer expiry, ball end, or mode completion state.</x:v>
       </x:c>
       <x:c r="H12" s="31" t="str">
-        <x:v>Spinner builds the jackpot from 100K by 10K per spin to 500K. Bigger Jackpots uses 150K, +15K, and a 750K cap. Timer starts on the first jackpot and resets on upper targets or any saucer hit, but not spinner.</x:v>
+        <x:v>Upper targets light saucers; matching saucer scores 2X; timer resets on key upper/spinner/saucer activity.</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
-        <x:v>More Jackpots relights the collected saucer at 1X. Shot Assist awards the best lit jackpot. Safety Net remains the standard 10-second ball save.</x:v>
+        <x:v>Improved: persistent upper-target/saucer guidance and 3-jackpot progress.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -7037,16 +7037,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F27" s="31" t="str">
-        <x:v>Spinner reveals the true shot among 3 lit hypnosis choices; correct shots score jackpots.</x:v>
+        <x:v>Three hidden choices are selected from two webs, three upper targets, two drop banks, and separate left/right pops. Both spinners are reveal-only.</x:v>
       </x:c>
       <x:c r="G27" s="31" t="str">
-        <x:v>Ends after 5 correct shots, 7 wrong shots, or ball end.</x:v>
+        <x:v>Ends after 5 correct shots, 7 wrong shots, or ball end. More Jackpots raises the goal to 7 correct shots.</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Hypnosis Reel: spinner reveals the true shot among 3 lit choices; correct shots score jackpots, wrong shots add mistakes.</x:v>
+        <x:v>Correct reveal flashes green every 250ms for 2 seconds; More Time uses 4 seconds. Wrong choices remain solid red. GI is A0A0F0. Correct jackpots begin at 100K and grow by 50K.</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
-        <x:v>Improved: persistent correct-shot and mistake-limit progress.</x:v>
+        <x:v>Bigger Jackpots uses 150K and +75K; Safety Net adds 10-second ball save; Shot Assist makes all first-round choices correct. Song 53.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -7153,16 +7153,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F31" s="31" t="str">
-        <x:v>Clear one green creature area at a time from pops, drops, webs, and upper targets.</x:v>
+        <x:v>Clear one area at a time: any one left drop, any one right drop, both unique pops, both unique web targets, or any one upper target.</x:v>
       </x:c>
       <x:c r="G31" s="31" t="str">
         <x:v>After three areas, all saucers light for a timed Super. Ends on collect, timer expiry, or ball end.</x:v>
       </x:c>
       <x:c r="H31" s="31" t="str">
-        <x:v>Area awards 200K, 300K, 400K; Super 1M. Bigger increases values; More Time makes the Super 30s.</x:v>
+        <x:v>Area awards 200K, 300K, and 400K; Super 1M. Unhit pop/web shots flash green, completed shots hold at 75% green, and contrasting GI is purple.</x:v>
       </x:c>
       <x:c r="I31" s="31" t="str">
-        <x:v>More Jackpots adds an optional fourth area during the Super; Safety Net ball save; Shot Assist awards the active and next areas.</x:v>
+        <x:v>More Jackpots adds an optional fourth area during the Super; Bigger raises values; More Time gives 30 seconds; Safety Net adds ball save; Shot Assist awards the active and next areas.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R01254c0549ce422c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rbc1a240a15c94f0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rca40d037aec248aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R616539b9e4fa4b28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rdc3e6f02e8a14b9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R0efa83d169ef483b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R19e6546044d242d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rd2ed67af87f141e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rba398a8eca5c49fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R7e7bfc981c8648a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R58e3c8c4dc124a23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R5be75df09b8d4f3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra6c4f751a02b403f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R6d6192d1032e4f2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rdead96553b124e9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R201219a82b6348b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rb961595fb93c45ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R10686a42f107414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Re9ce9734ca1d476b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rcf9faa26705c49d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R7a9fe29fe7e54ecd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R3a1d1c3d7c7e4f8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Ra902c99495c24a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R82ad39d061fe418e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1168,31 +1168,31 @@
         <x:v>Diana</x:v>
       </x:c>
       <x:c r="E14" s="31" t="str">
-        <x:v>Implemented / needs light-color polish</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="F14" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="31" t="str">
-        <x:v>Timed shot</x:v>
+        <x:v>Timed precision</x:v>
       </x:c>
       <x:c r="H14" s="31" t="str">
-        <x:v>Post release</x:v>
+        <x:v>Limited arrows</x:v>
       </x:c>
       <x:c r="I14" s="31" t="str">
-        <x:v>Upper/lower transition + right bank</x:v>
+        <x:v>Upper playfield + right bank</x:v>
       </x:c>
       <x:c r="J14" s="31" t="str">
-        <x:v>Timed arrow jackpot</x:v>
+        <x:v>Three staged right-bank Hunts</x:v>
       </x:c>
       <x:c r="K14" s="31" t="str">
-        <x:v>Short shot window</x:v>
+        <x:v>First-hit timed windows</x:v>
       </x:c>
       <x:c r="L14" s="31" t="str">
-        <x:v>Timed objectives / ball end</x:v>
+        <x:v>Three Hunts complete / arrows depleted / ball end</x:v>
       </x:c>
       <x:c r="M14" s="31" t="str">
-        <x:v>Timed precision role.</x:v>
+        <x:v>Limited-resource precision role with a clear red-GI Hunt state.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1701,7 +1701,7 @@
         <x:v>Pardo</x:v>
       </x:c>
       <x:c r="E27" s="31" t="str">
-        <x:v>Implemented</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="F27" s="31" t="str">
         <x:v>1</x:v>
@@ -1710,22 +1710,22 @@
         <x:v>Mystery / reveal</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Spinner-controlled reveal</x:v>
+        <x:v>Mistake limit</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
-        <x:v>Webs + upper targets + drop banks + separate pops</x:v>
+        <x:v>Spinner + 3 lit choices</x:v>
       </x:c>
       <x:c r="J27" s="31" t="str">
-        <x:v>Growing correct-shot jackpots</x:v>
+        <x:v>Correct-shot jackpots</x:v>
       </x:c>
       <x:c r="K27" s="31" t="str">
-        <x:v>Memorize flashing green among solid red choices</x:v>
+        <x:v>Wrong-shot mistakes</x:v>
       </x:c>
       <x:c r="L27" s="31" t="str">
         <x:v>5 correct / 7 wrong / ball end</x:v>
       </x:c>
       <x:c r="M27" s="31" t="str">
-        <x:v>Both spinners reveal only; dynamic 250ms flash cadence follows the configured reveal duration.</x:v>
+        <x:v>Mystic chapter reveal/mistake-limit role.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1865,7 +1865,7 @@
         <x:v>Infinata</x:v>
       </x:c>
       <x:c r="E31" s="31" t="str">
-        <x:v>Implemented</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F31" s="31" t="str">
         <x:v>1</x:v>
@@ -1874,22 +1874,22 @@
         <x:v>Sequential area completion</x:v>
       </x:c>
       <x:c r="H31" s="31" t="str">
-        <x:v>Distinct grouped/unique-shot areas</x:v>
+        <x:v>Green corruption areas</x:v>
       </x:c>
       <x:c r="I31" s="31" t="str">
-        <x:v>Drops, two pops, two webs, upper targets, saucers</x:v>
+        <x:v>Pops, drops, webs, upper targets, saucers</x:v>
       </x:c>
       <x:c r="J31" s="31" t="str">
-        <x:v>Rising area awards + timed saucer Super</x:v>
+        <x:v>Rising areas + timed saucer Super</x:v>
       </x:c>
       <x:c r="K31" s="31" t="str">
-        <x:v>One area at a time with clear progress lighting</x:v>
+        <x:v>One area at a time; 20s Super</x:v>
       </x:c>
       <x:c r="L31" s="31" t="str">
-        <x:v>Super collect / timer / ball end</x:v>
+        <x:v>Super / timer / ball end</x:v>
       </x:c>
       <x:c r="M31" s="31" t="str">
-        <x:v>Drop banks and upper targets need one hit; pops and webs require both unique switches.</x:v>
+        <x:v>Three required areas; optional fourth with More Jackpots.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4105,10 +4105,10 @@
         <x:v>Diana</x:v>
       </x:c>
       <x:c r="G14" s="31" t="str">
-        <x:v>Implemented / needs light-color polish</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H14" s="31" t="str">
-        <x:v>Post-release timed arrow shot; right-bank color cleanup remains on todo.</x:v>
+        <x:v>Three limited-arrow Hunts. Upper entry stages green right-bank targets and red GI; either upper exit prompts the shot, and the first right-bank drop or rubber hit starts a 12s/18s timer.</x:v>
       </x:c>
       <x:c r="I14" s="31" t="str">
         <x:v>trubble_unleashed</x:v>
@@ -4521,10 +4521,10 @@
         <x:v>Pardo</x:v>
       </x:c>
       <x:c r="G27" s="31" t="str">
-        <x:v>Implemented</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Hypnosis Reel: three choices are selected from webs, upper targets, drop banks, and separate left/right pops. Either spinner reveals the answer. The correct shot flashes green every 250ms for 2 seconds, or 4 seconds with More Time; wrong choices remain solid red.</x:v>
+        <x:v>Hypnosis Reel: spinner reveals true shot among 3 choices; 5 correct shots defeat Pardo; 7 wrong choices lets him escape.</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -4649,10 +4649,10 @@
         <x:v>Infinata</x:v>
       </x:c>
       <x:c r="G31" s="31" t="str">
-        <x:v>Implemented</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H31" s="31" t="str">
-        <x:v>One area lights at a time. Left or right drops require any one drop; pops require one unique hit on each of the two pops; webs require both unique web targets; upper targets act as one grouped shot and require any one hit. Complete three areas to light all saucers for the timed Super. More Jackpots adds a fourth optional area.</x:v>
+        <x:v>One green creature area lights at a time from pops, left drops, right drops, webs, and upper targets. Complete three to light all saucers for a 20-second 1M Super. More Jackpots adds a fourth optional area, Bigger raises values, More Time gives 30 seconds, Safety Net adds ball save, and Shot Assist awards the first two areas.</x:v>
       </x:c>
       <x:c r="I31" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -6660,16 +6660,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="31" t="str">
-        <x:v>Use post/upper-lower transitions to stage and collect timed arrow shots.</x:v>
+        <x:v>Enter the upper playfield to stage each Hunt, then exit and hit the right drops. The first staged drop or right rubber hit starts the timer.</x:v>
       </x:c>
       <x:c r="G14" s="31" t="str">
-        <x:v>Ends when timed arrow/post-release objectives complete; otherwise stops on ball end.</x:v>
+        <x:v>Each Hunt ends when all staged targets are down or its timer expires. Hunt 3 immediately completes the mode and awards 50K per remaining arrow; ball end also stops it.</x:v>
       </x:c>
       <x:c r="H14" s="31" t="str">
-        <x:v>Post-release timed arrow shot flow; upper/lower transitions stage target opportunities.</x:v>
+        <x:v>Three Hunts: targets 1/3/5, then 2/4, then 3. Timers are 12s or 18s with More Time. Red GI marks the Hunt; staged inserts stay green.</x:v>
       </x:c>
       <x:c r="I14" s="31" t="str">
-        <x:v>Good: arrows/time status and state-change messaging are present.</x:v>
+        <x:v>Arrows/time status, exit instruction, first-hit timer start, rubber arrow award, Hunt completion, and helper behavior are implemented.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -7037,16 +7037,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F27" s="31" t="str">
-        <x:v>Three hidden choices are selected from two webs, three upper targets, two drop banks, and separate left/right pops. Both spinners are reveal-only.</x:v>
+        <x:v>Spinner reveals the true shot among 3 lit hypnosis choices; correct shots score jackpots.</x:v>
       </x:c>
       <x:c r="G27" s="31" t="str">
-        <x:v>Ends after 5 correct shots, 7 wrong shots, or ball end. More Jackpots raises the goal to 7 correct shots.</x:v>
+        <x:v>Ends after 5 correct shots, 7 wrong shots, or ball end.</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Correct reveal flashes green every 250ms for 2 seconds; More Time uses 4 seconds. Wrong choices remain solid red. GI is A0A0F0. Correct jackpots begin at 100K and grow by 50K.</x:v>
+        <x:v>Hypnosis Reel: spinner reveals the true shot among 3 lit choices; correct shots score jackpots, wrong shots add mistakes.</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
-        <x:v>Bigger Jackpots uses 150K and +75K; Safety Net adds 10-second ball save; Shot Assist makes all first-round choices correct. Song 53.</x:v>
+        <x:v>Improved: persistent correct-shot and mistake-limit progress.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -7153,16 +7153,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F31" s="31" t="str">
-        <x:v>Clear one area at a time: any one left drop, any one right drop, both unique pops, both unique web targets, or any one upper target.</x:v>
+        <x:v>Clear one green creature area at a time from pops, drops, webs, and upper targets.</x:v>
       </x:c>
       <x:c r="G31" s="31" t="str">
         <x:v>After three areas, all saucers light for a timed Super. Ends on collect, timer expiry, or ball end.</x:v>
       </x:c>
       <x:c r="H31" s="31" t="str">
-        <x:v>Area awards 200K, 300K, and 400K; Super 1M. Unhit pop/web shots flash green, completed shots hold at 75% green, and contrasting GI is purple.</x:v>
+        <x:v>Area awards 200K, 300K, 400K; Super 1M. Bigger increases values; More Time makes the Super 30s.</x:v>
       </x:c>
       <x:c r="I31" s="31" t="str">
-        <x:v>More Jackpots adds an optional fourth area during the Super; Bigger raises values; More Time gives 30 seconds; Safety Net adds ball save; Shot Assist awards the active and next areas.</x:v>
+        <x:v>More Jackpots adds an optional fourth area during the Super; Safety Net ball save; Shot Assist awards the active and next areas.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra6c4f751a02b403f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R6d6192d1032e4f2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rdead96553b124e9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R201219a82b6348b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rb961595fb93c45ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R10686a42f107414e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Re9ce9734ca1d476b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rcf9faa26705c49d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R7a9fe29fe7e54ecd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R3a1d1c3d7c7e4f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Ra902c99495c24a13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R82ad39d061fe418e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6c326ebadb174bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R3ef5d28ef34247ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R07930ee8c8404b52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R87766ebafed84e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R660d9c7e45944dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R1515e333b4c349a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rcd8553725c8545c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Re55a3788d83f4527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rf2effe6e344f48b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rd6e0c240b8ee4cc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R3ca6e4c7bf404ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R5aebb5260e644729"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -770,19 +770,19 @@
         <x:v>Spinner build</x:v>
       </x:c>
       <x:c r="I4" s="31" t="str">
-        <x:v>Upper playfield + spinner</x:v>
+        <x:v>Upper targets + spinner</x:v>
       </x:c>
       <x:c r="J4" s="31" t="str">
-        <x:v>Spinner-scaled value / add-a-ball</x:v>
+        <x:v>Stage-combined spinner scoring</x:v>
       </x:c>
       <x:c r="K4" s="31" t="str">
-        <x:v>Upper control</x:v>
+        <x:v>Target decay and 40s clock</x:v>
       </x:c>
       <x:c r="L4" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>40s expiry, then multiball end if active, or ball end</x:v>
       </x:c>
       <x:c r="M4" s="31" t="str">
-        <x:v>Upper-playfield/spinner role for the chapter.</x:v>
+        <x:v>High-value rooftop control mode with one rare two-ball upper multiplier and automatic all-red add-a-ball.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3788,7 +3788,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H4" s="31" t="str">
-        <x:v>Upper playfield/spinner mode; banks vulture_bonus; first 10 music assignment retained.</x:v>
+        <x:v>40-second rooftop spinner mode. Targets advance green/yellow/red, decay after 4s or 6s with More Time, and score 50K. Spinner uses 10K/25K/50K stages; Bigger doubles them. All red awards one add-a-ball.</x:v>
       </x:c>
       <x:c r="I4" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -6370,16 +6370,16 @@
         <x:v>1; add-a-ball possible</x:v>
       </x:c>
       <x:c r="F4" s="31" t="str">
-        <x:v>Get to the upper playfield; use upper targets/spinner to build and collect Vulture values.</x:v>
+        <x:v>Enter the upper playfield to start the 40-second timer. Build the three targets through green, yellow, and red, then spin for the combined stage value.</x:v>
       </x:c>
       <x:c r="G4" s="31" t="str">
-        <x:v>Ends when upper-playfield Vulture objectives complete; otherwise stops on ball end.</x:v>
+        <x:v>At 40 seconds, the mode ends unless Vulture add-a-ball multiball is active; in that case it continues until multiball ends. Ball end also stops it.</x:v>
       </x:c>
       <x:c r="H4" s="31" t="str">
-        <x:v>Upper playfield/spinner mode; spinner builds/scales scoring and can qualify add-a-ball; banks vulture_bonus.</x:v>
+        <x:v>Target hits score 50K. Spinner stages are 10K/25K/50K, doubled by Bigger and doubled again with two upper balls. More Jackpots adds 100K per spin at all red. More Time slows decay from 4s to 6s.</x:v>
       </x:c>
       <x:c r="I4" s="31" t="str">
-        <x:v>Improved: roof-access guidance before the live rooftop timer.</x:v>
+        <x:v>Gate opens for the mode. GI is yellow below and 4080F0 blue on upper entry, returning yellow on either upper exit or middle-right A. Shot Assist advances all three targets on the first target hit.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6c326ebadb174bc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R3ef5d28ef34247ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R07930ee8c8404b52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R87766ebafed84e34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R660d9c7e45944dd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R1515e333b4c349a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rcd8553725c8545c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Re55a3788d83f4527"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rf2effe6e344f48b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rd6e0c240b8ee4cc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R3ca6e4c7bf404ab7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R5aebb5260e644729"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb57dd7176d1844b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R3b9f8dd6eb584b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R6c000c7ef90546fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rb198eaeef9cb43da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rc55ba0eb5baa4e2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rd5fdc10967c94a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R83ed3047353e464f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R75e22921a9d94e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R34104275936f4565"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R9821ed6bbdd84fb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Ra1d7f332b9364acd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R6742dd39e4984248"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -770,19 +770,19 @@
         <x:v>Spinner build</x:v>
       </x:c>
       <x:c r="I4" s="31" t="str">
-        <x:v>Upper targets + spinner</x:v>
+        <x:v>Upper playfield + spinner</x:v>
       </x:c>
       <x:c r="J4" s="31" t="str">
-        <x:v>Stage-combined spinner scoring</x:v>
+        <x:v>Spinner-scaled value / add-a-ball</x:v>
       </x:c>
       <x:c r="K4" s="31" t="str">
-        <x:v>Target decay and 40s clock</x:v>
+        <x:v>Upper control</x:v>
       </x:c>
       <x:c r="L4" s="31" t="str">
-        <x:v>40s expiry, then multiball end if active, or ball end</x:v>
+        <x:v>Goals completed / ball end</x:v>
       </x:c>
       <x:c r="M4" s="31" t="str">
-        <x:v>High-value rooftop control mode with one rare two-ball upper multiplier and automatic all-red add-a-ball.</x:v>
+        <x:v>Upper-playfield/spinner role for the chapter.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -849,22 +849,22 @@
         <x:v>Sequence</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
-        <x:v>Travelling shot</x:v>
+        <x:v>Travelling timed shot</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
         <x:v>Whole playfield</x:v>
       </x:c>
       <x:c r="J6" s="31" t="str">
-        <x:v>Final Super Jackpot</x:v>
+        <x:v>Resetting decaying spark jackpots</x:v>
       </x:c>
       <x:c r="K6" s="31" t="str">
-        <x:v>Sequence completion</x:v>
+        <x:v>5s windows and final 10s Super</x:v>
       </x:c>
       <x:c r="L6" s="31" t="str">
-        <x:v>Final Super collected / ball end</x:v>
+        <x:v>Super collected, Super missed, or ball end</x:v>
       </x:c>
       <x:c r="M6" s="31" t="str">
-        <x:v>Sequence/follow-the-shot role.</x:v>
+        <x:v>Clear travelling-shot mode with reliable helper behavior; every move restores full value before decay resumes.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3788,7 +3788,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H4" s="31" t="str">
-        <x:v>40-second rooftop spinner mode. Targets advance green/yellow/red, decay after 4s or 6s with More Time, and score 50K. Spinner uses 10K/25K/50K stages; Bigger doubles them. All red awards one add-a-ball.</x:v>
+        <x:v>Upper playfield/spinner mode; banks vulture_bonus; first 10 music assignment retained.</x:v>
       </x:c>
       <x:c r="I4" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -3852,7 +3852,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
-        <x:v>Travelling spark and final Super Jackpot; final-shot/callout delay considered OK.</x:v>
+        <x:v>Travelling 5-second spark shots reset to maximum value whenever they move, then decay once per second. More Time halves decay, Shot Assist holds the first spark for 8 seconds, More Jackpots grants one extra normal collect, and the final 10-second Super countdown/status is retained.</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -6370,16 +6370,16 @@
         <x:v>1; add-a-ball possible</x:v>
       </x:c>
       <x:c r="F4" s="31" t="str">
-        <x:v>Enter the upper playfield to start the 40-second timer. Build the three targets through green, yellow, and red, then spin for the combined stage value.</x:v>
+        <x:v>Get to the upper playfield; use upper targets/spinner to build and collect Vulture values.</x:v>
       </x:c>
       <x:c r="G4" s="31" t="str">
-        <x:v>At 40 seconds, the mode ends unless Vulture add-a-ball multiball is active; in that case it continues until multiball ends. Ball end also stops it.</x:v>
+        <x:v>Ends when upper-playfield Vulture objectives complete; otherwise stops on ball end.</x:v>
       </x:c>
       <x:c r="H4" s="31" t="str">
-        <x:v>Target hits score 50K. Spinner stages are 10K/25K/50K, doubled by Bigger and doubled again with two upper balls. More Jackpots adds 100K per spin at all red. More Time slows decay from 4s to 6s.</x:v>
+        <x:v>Upper playfield/spinner mode; spinner builds/scales scoring and can qualify add-a-ball; banks vulture_bonus.</x:v>
       </x:c>
       <x:c r="I4" s="31" t="str">
-        <x:v>Gate opens for the mode. GI is yellow below and 4080F0 blue on upper entry, returning yellow on either upper exit or middle-right A. Shot Assist advances all three targets on the first target hit.</x:v>
+        <x:v>Improved: roof-access guidance before the live rooftop timer.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6428,16 +6428,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
-        <x:v>Follow the travelling spark shot sequence; collected shots build toward the final Super.</x:v>
+        <x:v>Follow the travelling spark across eight shot groups. Each new spark starts at maximum value and then decays once per second until hit or moved.</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Ends when the final Super Jackpot is collected; otherwise stops on ball end.</x:v>
+        <x:v>Collected groups are removed until one final shot remains for the 10-second Super Jackpot. Collecting the Super completes the mode; missing it or ball end stops it.</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
-        <x:v>Travelling spark selects shots; collected shots build toward a final Super Jackpot.</x:v>
+        <x:v>Normal sparks start at 250K, or 300K with Bigger, and fall 10K per second to 50K. More Time halves the drain rate. More Jackpots returns the first collected group to the pool for one extra normal jackpot. Shot Assist makes the first spark last 8 seconds.</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
-        <x:v>Improved: spark progress shown between timed shot windows.</x:v>
+        <x:v>Existing Electro light timing is retained. The Super uses the existing SUPER SURGE LIT countdown plus persistent SUPER SPARK status. Gate routing follows upper shots, and saucers use delayed clearing.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb57dd7176d1844b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R3b9f8dd6eb584b63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R6c000c7ef90546fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rb198eaeef9cb43da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rc55ba0eb5baa4e2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rd5fdc10967c94a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R83ed3047353e464f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R75e22921a9d94e34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R34104275936f4565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R9821ed6bbdd84fb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Ra1d7f332b9364acd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R6742dd39e4984248"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcb761e2c040d47c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Ra451be1887814581"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R45a46a7ffb9146c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R78a4f06c27ae4c47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R0aa8c446b5dd4f40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R6a702c60eb174b55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R55f831a98be448d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rd499acd3c3174512"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rfe17aea740d94751"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rcc59ebb472354b5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rdcc5727a886d42f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rd4f7adb540c14175"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2970,7 +2970,7 @@
         <x:v>Keep</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
-        <x:v>harley_clivendon_state, conquistador_state, spider_slayer_state, metal_eating_monster_state, fiddler_state</x:v>
+        <x:v>harley_clivendon_state, conquistador_state, spider_slayer_state, metal_eating_robot_state, fiddler_state</x:v>
       </x:c>
       <x:c r="D2" s="31" t="str">
         <x:v>All five persistent progression states are required.</x:v>
@@ -3788,7 +3788,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H4" s="31" t="str">
-        <x:v>Upper playfield/spinner mode; banks vulture_bonus; first 10 music assignment retained.</x:v>
+        <x:v>Upper playfield/spinner mode; banks vulture_bonus; first 10 music assignment ...</x:v>
       </x:c>
       <x:c r="I4" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -3820,7 +3820,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H5" s="31" t="str">
-        <x:v>Serum at STAR; deliver to web shots. Case files now enhance the loop: Bigger value, slower decay, follow-up jackpots, first expired serum saved, first delivery either web.</x:v>
+        <x:v>Serum at STAR; deliver to web shots. Case files now enhance the loop: Bigger ...</x:v>
       </x:c>
       <x:c r="I5" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -3852,7 +3852,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
-        <x:v>Travelling 5-second spark shots reset to maximum value whenever they move, then decay once per second. More Time halves decay, Shot Assist holds the first spark for 8 seconds, More Jackpots grants one extra normal collect, and the final 10-second Super countdown/status is retained.</x:v>
+        <x:v>Travelling 5-second spark shots reset to maximum value whenever they move, th...</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -3916,7 +3916,7 @@
         <x:v>Implemented / recent rule update</x:v>
       </x:c>
       <x:c r="H8" s="31" t="str">
-        <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpot; spinner boosts multiplier.</x:v>
+        <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpot; ...</x:v>
       </x:c>
       <x:c r="I8" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -3948,7 +3948,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H9" s="31" t="str">
-        <x:v>Hidden Super/clue mode; wrong shots lower value; first 10 music assignment retained.</x:v>
+        <x:v>Hidden Super/clue mode; wrong shots lower value; first 10 music assignment re...</x:v>
       </x:c>
       <x:c r="I9" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -4044,7 +4044,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H12" s="31" t="str">
-        <x:v>Upper targets light saucers; matching saucer scores 2X; timer reset flow needs testing.</x:v>
+        <x:v>Upper targets light saucers; matching saucer scores 2X; timer reset flow need...</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
         <x:v>trubble_unleashed</x:v>
@@ -4108,7 +4108,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H14" s="31" t="str">
-        <x:v>Three limited-arrow Hunts. Upper entry stages green right-bank targets and red GI; either upper exit prompts the shot, and the first right-bank drop or rubber hit starts a 12s/18s timer.</x:v>
+        <x:v>Three limited-arrow Hunts. Upper entry stages green right-bank targets and re...</x:v>
       </x:c>
       <x:c r="I14" s="31" t="str">
         <x:v>trubble_unleashed</x:v>
@@ -4195,7 +4195,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="31" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>plotter</x:v>
       </x:c>
       <x:c r="F17" s="31" t="str">
         <x:v>The Plotter</x:v>
@@ -4204,7 +4204,7 @@
         <x:v>Implemented / simplified</x:v>
       </x:c>
       <x:c r="H17" s="31" t="str">
-        <x:v>Pops build information. Two information plus a spinner hit lights one saucer. Collect three scheme jackpots, then shoot the Daily Bugle VUK for the Master Plan Super.</x:v>
+        <x:v>Pops build information. Two information plus a spinner hit lights one saucer....</x:v>
       </x:c>
       <x:c r="I17" s="31" t="str">
         <x:v>crime_wave</x:v>
@@ -4227,16 +4227,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E18" s="31" t="str">
-        <x:v>fly_brothers</x:v>
+        <x:v>fly_twins</x:v>
       </x:c>
       <x:c r="F18" s="31" t="str">
-        <x:v>Fly Brothers</x:v>
+        <x:v>The Fly Twins</x:v>
       </x:c>
       <x:c r="G18" s="31" t="str">
         <x:v>Implemented / recent gate update</x:v>
       </x:c>
       <x:c r="H18" s="31" t="str">
-        <x:v>Gate opens for upper-target access and closes when upper access is no longer needed.</x:v>
+        <x:v>Gate opens for upper-target access and closes when upper access is no longer ...</x:v>
       </x:c>
       <x:c r="I18" s="31" t="str">
         <x:v>crime_wave</x:v>
@@ -4262,7 +4262,7 @@
         <x:v>fifth_avenue_phantom</x:v>
       </x:c>
       <x:c r="F19" s="31" t="str">
-        <x:v>Fifth Avenue Phantom</x:v>
+        <x:v>The Fifth Avenue Phantom</x:v>
       </x:c>
       <x:c r="G19" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
@@ -4300,7 +4300,7 @@
         <x:v>Implemented / needs light-color polish</x:v>
       </x:c>
       <x:c r="H20" s="31" t="str">
-        <x:v>Cowboy and Ox control three crime zones; zone clears light upper-target jackpots and build the OX Super at center web.</x:v>
+        <x:v>Cowboy and Ox control three crime zones; zone clears light upper-target jackp...</x:v>
       </x:c>
       <x:c r="I20" s="31" t="str">
         <x:v>crime_wave</x:v>
@@ -4332,7 +4332,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H21" s="31" t="str">
-        <x:v>Drops build frozen-diamond value; completing the right 5-bank starts a moving saucer shipment chase. STAR freezes the chase and lights all three saucers briefly. Existing diamond_bonus bank is retained.</x:v>
+        <x:v>Drops build frozen-diamond value; completing the right 5-bank starts a moving...</x:v>
       </x:c>
       <x:c r="I21" s="31" t="str">
         <x:v>crime_wave</x:v>
@@ -4364,7 +4364,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H22" s="31" t="str">
-        <x:v>The One-Eyed Idol / Fountain of Terror antagonist. Placeholder scoring is active; full design should use hypnosis, the idol, and hidden-scheme reveals.</x:v>
+        <x:v>The One-Eyed Idol / Fountain of Terror antagonist. Placeholder scoring is act...</x:v>
       </x:c>
       <x:c r="I22" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -4396,7 +4396,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H23" s="31" t="str">
-        <x:v>Fountain of Terror antagonist. Placeholder scoring is active; full design should use the hidden fort, Fountain of Youth, and pursuit through the ruins.</x:v>
+        <x:v>Fountain of Terror antagonist. Placeholder scoring is active; full design sho...</x:v>
       </x:c>
       <x:c r="I23" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -4428,7 +4428,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H24" s="31" t="str">
-        <x:v>Jameson-operated tracking robot. Placeholder scoring is active; full design should feature a moving hunt, capture pressure, and destroying the Slayer.</x:v>
+        <x:v>Jameson-operated tracking robot. Placeholder scoring is active; full design s...</x:v>
       </x:c>
       <x:c r="I24" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -4451,16 +4451,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="E25" s="31" t="str">
-        <x:v>metal_eating_monster</x:v>
+        <x:v>metal_eating_robot</x:v>
       </x:c>
       <x:c r="F25" s="31" t="str">
-        <x:v>Metal-Eating Monster</x:v>
+        <x:v>Metal-Eating Robot</x:v>
       </x:c>
       <x:c r="G25" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H25" s="31" t="str">
-        <x:v>Giant robot from Diet of Destruction. Placeholder scoring is active; full design should use consumed playfield areas, magnetic attacks, furnace heat, and the river finish.</x:v>
+        <x:v>Giant robot from Diet of Destruction. Placeholder scoring is active; full des...</x:v>
       </x:c>
       <x:c r="I25" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -4492,7 +4492,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H26" s="31" t="str">
-        <x:v>Fiddler on the Loose sound-and-ransom antagonist. Placeholder scoring is active. Persistent fiddler_bonus is wired into end-of-ball bonus and summary display; the full design will define musical sequences and how ransom is banked.</x:v>
+        <x:v>Fiddler on the Loose sound-and-ransom antagonist. Placeholder scoring is acti...</x:v>
       </x:c>
       <x:c r="I26" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -4524,7 +4524,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Hypnosis Reel: spinner reveals true shot among 3 choices; 5 correct shots defeat Pardo; 7 wrong choices lets him escape.</x:v>
+        <x:v>Hypnosis Reel: spinner reveals true shot among 3 choices; 5 correct shots def...</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -4556,7 +4556,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H28" s="31" t="str">
-        <x:v>2-ball Ruby Heist: saucers reveal upper rubies; spinners build value; 3 Ruby JPs light Super; continues until multiball ends.</x:v>
+        <x:v>2-ball Ruby Heist: saucers reveal upper rubies; spinners build value; 3 Ruby ...</x:v>
       </x:c>
       <x:c r="I28" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -4579,16 +4579,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E29" s="31" t="str">
-        <x:v>scarlet_sorcerer</x:v>
+        <x:v>kotep</x:v>
       </x:c>
       <x:c r="F29" s="31" t="str">
-        <x:v>Kotep — The Scarlet Sorcerer</x:v>
+        <x:v>Kotep</x:v>
       </x:c>
       <x:c r="G29" s="31" t="str">
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H29" s="31" t="str">
-        <x:v>Four unique demon shots appear one every 4 seconds and never relight. Demon JPs score 200K–350K; after four demons the gate opens for a 20-second 1M VUK Scepter Super. Case files add an optional fifth demon, larger values, 30 seconds, ball save, or timed Shot Assist.</x:v>
+        <x:v>Four unique demon shots appear one every 4 seconds and never relight. Demon J...</x:v>
       </x:c>
       <x:c r="I29" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -4620,7 +4620,7 @@
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H30" s="31" t="str">
-        <x:v>Restore six coordinate-based GI regions before the 40-second timer expires. First-time restoration values rise 100K–350K; Bigger starts at 200K, More Time gives 50 seconds, More Jackpots adds a 500K VUK Blackout Jackpot, Safety Net starts ball save, and Shot Assist spots an extra region.</x:v>
+        <x:v>Restore six coordinate-based GI regions before the 40-second timer expires. F...</x:v>
       </x:c>
       <x:c r="I30" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -4652,7 +4652,7 @@
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H31" s="31" t="str">
-        <x:v>One green creature area lights at a time from pops, left drops, right drops, webs, and upper targets. Complete three to light all saucers for a 20-second 1M Super. More Jackpots adds a fourth optional area, Bigger raises values, More Time gives 30 seconds, Safety Net adds ball save, and Shot Assist awards the first two areas.</x:v>
+        <x:v>One green creature area lights at a time from pops, left drops, right drops, ...</x:v>
       </x:c>
       <x:c r="I31" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -4716,7 +4716,7 @@
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H33" s="31" t="str">
-        <x:v>Rooftop magnetic sweep: upper entrance resets both banks; each upper spin scores 50K and knocks down the next left-to-right target for another 50K. After seven steps only right drop 5 remains for a timed 1M Super. More Jackpots stages left drop 1 for a 500K Magnetic Flux Super.</x:v>
+        <x:v>Rooftop magnetic sweep: upper entrance resets both banks; each upper spin sco...</x:v>
       </x:c>
       <x:c r="I33" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -4739,16 +4739,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="E34" s="31" t="str">
-        <x:v>professor_pretoris</x:v>
+        <x:v>professor_pretorius</x:v>
       </x:c>
       <x:c r="F34" s="31" t="str">
-        <x:v>Professor Pretoris</x:v>
+        <x:v>Professor Pretorius</x:v>
       </x:c>
       <x:c r="G34" s="31" t="str">
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H34" s="31" t="str">
-        <x:v>Reactor Flood: GI starts red in eight horizontal bands. Each web-spinner hit turns the next band blue from bottom to top for 100K. After eight bands, center web lights for a 20-second 1M Super; More Jackpots adds a 10-second left-web Overflow Super.</x:v>
+        <x:v>Reactor Flood: GI starts red in eight horizontal bands. Each web-spinner hit ...</x:v>
       </x:c>
       <x:c r="I34" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -4812,7 +4812,7 @@
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H36" s="31" t="str">
-        <x:v>Oil Pellet Chase: red GI and one green shot sweep left web, left drops, left pop, center web, right pop, and right drops, reversing every 4 seconds. Five pellets open the gate and light a timed VUK Super; the held-ball finish floods eight GI bands blue before awarding 1M.</x:v>
+        <x:v>Oil Pellet Chase: red GI and one green shot sweep left web, left drops, left ...</x:v>
       </x:c>
       <x:c r="I36" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -4844,7 +4844,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H37" s="31" t="str">
-        <x:v>Former Radiation Specialist placeholder retained for later redesign. Clive creates the shape-changing tar creature Blotto with the Spirit Scope; Chapter 7 bank is now blotto_bonus.</x:v>
+        <x:v>Former Radiation Specialist placeholder retained for later redesign. Clive cr...</x:v>
       </x:c>
       <x:c r="I37" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4867,16 +4867,16 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E38" s="31" t="str">
-        <x:v>dr_zap</x:v>
+        <x:v>dr_zapp</x:v>
       </x:c>
       <x:c r="F38" s="31" t="str">
-        <x:v>Doctor Zapp</x:v>
+        <x:v>Doctor Zappp</x:v>
       </x:c>
       <x:c r="G38" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H38" s="31" t="str">
-        <x:v>Electrical/weather slot. Full rules still need design around Zapp stealing and activating Irving Caldwell's invention.</x:v>
+        <x:v>Electrical/weather slot. Full rules still need design around Zapp stealing an...</x:v>
       </x:c>
       <x:c r="I38" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4899,16 +4899,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E39" s="31" t="str">
-        <x:v>voltan_boomer</x:v>
+        <x:v>bolton_boomer</x:v>
       </x:c>
       <x:c r="F39" s="31" t="str">
-        <x:v>Voltan and Boomer</x:v>
+        <x:v>Bolton and Boomer</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Former elemental freeze placeholder retained for later redesign. Thunder Rumble story pair; robberies are hidden inside violent storms and thunderbolt attacks.</x:v>
+        <x:v>Former elemental freeze placeholder retained for later redesign. Thunder Rumb...</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4940,7 +4940,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H40" s="31" t="str">
-        <x:v>Snow/weather slot. Living snow creature grows with snowfall and is defeated by draining its electrical charge.</x:v>
+        <x:v>Snow/weather slot. Living snow creature grows with snowfall and is defeated b...</x:v>
       </x:c>
       <x:c r="I40" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4972,7 +4972,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>Former Ice Monster placeholder retained under the canonical Plutonians identity. Ice-themed encounter should ultimately resolve by helping repair their escape rather than treating them as purely evil.</x:v>
+        <x:v>Former Ice Monster placeholder retained under the canonical Plutonians identi...</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -5004,7 +5004,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H42" s="31" t="str">
-        <x:v>Phantom from the Depths of Time villain. Dr. Manta rules the hidden city and uses robotic creatures to freeze and enslave its people.</x:v>
+        <x:v>Phantom from the Depths of Time villain. Dr. Manta rules the hidden city and ...</x:v>
       </x:c>
       <x:c r="I42" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -5036,7 +5036,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H43" s="31" t="str">
-        <x:v>Dr. Manta's assistant from the same episode. Moved from Chapter 9 and corrected from Eigor.</x:v>
+        <x:v>Dr. Manta's assistant from the same episode. Moved from Chapter 9 and correct...</x:v>
       </x:c>
       <x:c r="I43" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -5068,7 +5068,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H44" s="31" t="str">
-        <x:v>Atlantean invasion from Up from Nowhere; attempts to dome Manhattan and sink it beneath the sea.</x:v>
+        <x:v>Atlantean invasion from Up from Nowhere; attempts to dome Manhattan and sink ...</x:v>
       </x:c>
       <x:c r="I44" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -5100,7 +5100,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H45" s="31" t="str">
-        <x:v>Ruler of the hidden Cloud City of Gold. Former Chapter 8 open placeholder retained for later episode-based design.</x:v>
+        <x:v>Ruler of the hidden Cloud City of Gold. Former Chapter 8 open placeholder ret...</x:v>
       </x:c>
       <x:c r="I45" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -5126,13 +5126,13 @@
         <x:v>molemen</x:v>
       </x:c>
       <x:c r="F46" s="31" t="str">
-        <x:v>Molemen</x:v>
+        <x:v>The Molemen</x:v>
       </x:c>
       <x:c r="G46" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Underground-world mode associated with Mugs Reilly and the Molemen. Compact live name remains Molemen.</x:v>
+        <x:v>Underground-world mode associated with Mugs Reilly and the Molemen. Compact l...</x:v>
       </x:c>
       <x:c r="I46" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -5228,7 +5228,7 @@
         <x:v>Implemented repurpose / needs playtest</x:v>
       </x:c>
       <x:c r="H49" s="31" t="str">
-        <x:v>Former Kingpin limited-shot pursuit repurposed for Desperado. Complete all five unique right-bank targets in escalating rounds before the timer expires; left-bank completion adds time. More Jackpots adds a final showdown jackpot.</x:v>
+        <x:v>Former Kingpin limited-shot pursuit repurposed for Desperado. Complete all fi...</x:v>
       </x:c>
       <x:c r="I49" s="31" t="str">
         <x:v>who_is_the_real_villain</x:v>
@@ -5260,7 +5260,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H50" s="31" t="str">
-        <x:v>Former The Fly Rooftop Swarm rules rethemed as a limited-flip assault on Skymaster's blimp. Saucers open access; three upper targets score Jackpots and a remaining-flips Super.</x:v>
+        <x:v>Former The Fly Rooftop Swarm rules rethemed as a limited-flip assault on Skym...</x:v>
       </x:c>
       <x:c r="I50" s="31" t="str">
         <x:v>who_is_the_real_villain</x:v>
@@ -5283,10 +5283,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E51" s="31" t="str">
-        <x:v>swamp_reptiles</x:v>
+        <x:v>conners_reptiles</x:v>
       </x:c>
       <x:c r="F51" s="31" t="str">
-        <x:v>Swamp Reptiles</x:v>
+        <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="G51" s="31" t="str">
         <x:v>Implemented repurpose / needs polish</x:v>
@@ -5324,7 +5324,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H52" s="31" t="str">
-        <x:v>Knight Must Fall medieval time-displacement slot. Placeholder rules retained until the full Sir Galahad mode is designed.</x:v>
+        <x:v>Knight Must Fall medieval time-displacement slot. Placeholder rules retained ...</x:v>
       </x:c>
       <x:c r="I52" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -5356,7 +5356,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H53" s="31" t="str">
-        <x:v>Prehistoric Forbidden City and spreading-vine story from Vine. Full episode-based design still needed.</x:v>
+        <x:v>Prehistoric Forbidden City and spreading-vine story from Vine. Full episode-b...</x:v>
       </x:c>
       <x:c r="I53" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -5388,7 +5388,7 @@
         <x:v>Implemented repurpose / needs polish</x:v>
       </x:c>
       <x:c r="H54" s="31" t="str">
-        <x:v>Working drop-built spinner-value mode retained. Theme draws from Swing City and Manhattan being lifted into the sky.</x:v>
+        <x:v>Working drop-built spinner-value mode retained. Theme draws from Swing City a...</x:v>
       </x:c>
       <x:c r="I54" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -5420,7 +5420,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H55" s="31" t="str">
-        <x:v>Alien Spider-Men from Home. Placeholder rules retained; final design should focus on identifying the real Spider-Man and resolving the encounter.</x:v>
+        <x:v>Alien Spider-Men from Home. Placeholder rules retained; final design should f...</x:v>
       </x:c>
       <x:c r="I55" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -5452,7 +5452,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H56" s="31" t="str">
-        <x:v>Sky Harbor's World War I aerial invasion and paralysis technology. Placeholder rules retained until full design.</x:v>
+        <x:v>Sky Harbor's World War I aerial invasion and paralysis technology. Placeholde...</x:v>
       </x:c>
       <x:c r="I56" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -5599,7 +5599,7 @@
         <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G5" s="31" t="str">
-        <x:v>Implemented 3-ball multiball. Five timed villain areas: Plotter/pops, Fly Brothers/upper targets, Fifth Avenue Phantom/right bank, Enforcers/left bank, Doctor Cool/saucers. Gate opens at 3+ lit areas and closes at 1 or 0. Upper exits collect jackpots based on currently lit areas. Saucers hold for 15 seconds.</x:v>
+        <x:v>Implemented 3-ball multiball. Five timed villain areas: Plotter/pops, The Fly Twins/upper targets, Fifth Avenue Phantom/right bank, Enforcers/left bank, Doctor Cool/saucers. Gate opens at 3+ lit areas and closes at 1 or 0. Upper exits collect jackpots based on currently lit areas. Saucers hold for 15 seconds.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5820,13 +5820,13 @@
         <x:v>reptilla</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>swamp_reptiles</x:v>
+        <x:v>conners_reptiles</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
-        <x:v>Swamp Reptiles</x:v>
+        <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="D2" s="31" t="str">
-        <x:v>Reptilla code repurposed; active key is swamp_reptiles.</x:v>
+        <x:v>Reptilla code repurposed; active key is conners_reptiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -5862,10 +5862,10 @@
         <x:v>frederick_foswell</x:v>
       </x:c>
       <x:c r="B5" s="31" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>plotter</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>Plotter's Master Plan</x:v>
+        <x:v>Plotter's The Plotter</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
         <x:v>Foswell rumor/headline economy repurposed as Chapter 4 wizard.</x:v>
@@ -5918,13 +5918,13 @@
         <x:v>fly_twins</x:v>
       </x:c>
       <x:c r="B9" s="31" t="str">
-        <x:v>fly_brothers</x:v>
+        <x:v>fly_twins</x:v>
       </x:c>
       <x:c r="C9" s="31" t="str">
-        <x:v>Fly Brothers</x:v>
+        <x:v>The Fly Twins</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
-        <x:v>Human Flies renamed to Fly Brothers; internal mode key, events, player variables, display text, and widget standardized.</x:v>
+        <x:v>Human Flies renamed to The Fly Twins; internal mode key, events, player variables, display text, and widget standardized.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5974,10 +5974,10 @@
         <x:v>elemental_freeze_placeholder</x:v>
       </x:c>
       <x:c r="B13" s="31" t="str">
-        <x:v>voltan_boomer</x:v>
+        <x:v>bolton_boomer</x:v>
       </x:c>
       <x:c r="C13" s="31" t="str">
-        <x:v>Voltan and Boomer</x:v>
+        <x:v>Bolton and Boomer</x:v>
       </x:c>
       <x:c r="D13" s="31" t="str">
         <x:v>Neutral Elemental placeholder assigned to the Thunder Rumble story pair.</x:v>
@@ -6033,7 +6033,7 @@
         <x:v>molemen</x:v>
       </x:c>
       <x:c r="C17" s="31" t="str">
-        <x:v>Molemen</x:v>
+        <x:v>The Molemen</x:v>
       </x:c>
       <x:c r="D17" s="31" t="str">
         <x:v>Unverified Antarcticans identity replaced by Molemen; placeholder gameplay retained.</x:v>
@@ -6075,7 +6075,7 @@
         <x:v>molemen</x:v>
       </x:c>
       <x:c r="C20" s="31" t="str">
-        <x:v>Molemen</x:v>
+        <x:v>The Molemen</x:v>
       </x:c>
       <x:c r="D20" s="31" t="str">
         <x:v>Compact widget and mode name; Mugs Reilly can appear on selection, intro, and summary screens.</x:v>
@@ -6170,10 +6170,10 @@
         <x:v>new_chapter_slot</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>metal_eating_monster</x:v>
+        <x:v>metal_eating_robot</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>Metal-Eating Monster</x:v>
+        <x:v>Metal-Eating Robot</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
         <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
@@ -6198,18 +6198,18 @@
         <x:v>kingpin_regular_slot</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>plotter</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
         <x:v>The Plotter</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>Kingpin leaves the Chapter 4 villain roster. The former Plotter's Master Plan wizard is simplified into The Plotter regular villain mode.</x:v>
+        <x:v>Kingpin leaves the Chapter 4 villain roster. The former Plotter's The Plotter wizard is simplified into The Plotter regular villain mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="14" t="str">
-        <x:v>master_plan_wizard</x:v>
+        <x:v>plotter_wizard</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
         <x:v>crime_wave</x:v>
@@ -8051,7 +8051,7 @@
         <x:v>Playtest first 4 wizards</x:v>
       </x:c>
       <x:c r="C2" s="45" t="str">
-        <x:v>Sinister Surge, Mastermind Trap, Trubble Unleashed, Master Plan.</x:v>
+        <x:v>Sinister Surge, Mastermind Trap, Trubble Unleashed, The Plotter.</x:v>
       </x:c>
       <x:c r="D2" s="45" t="str">
         <x:v>Open</x:v>
@@ -8149,7 +8149,7 @@
         <x:v>Light color cleanup</x:v>
       </x:c>
       <x:c r="C9" s="45" t="str">
-        <x:v>Centaur, Diana, Enforcers, Swamp Reptiles; especially tinted right 5-bank/GI colors.</x:v>
+        <x:v>Centaur, Diana, Enforcers, Conner's Reptiles; especially tinted right 5-bank/GI colors.</x:v>
       </x:c>
       <x:c r="D9" s="45" t="str">
         <x:v>Open</x:v>
@@ -8275,7 +8275,7 @@
         <x:v>Villain music transition-track cleanup</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>Reassigned Trubble Unleashed to motorcycle_circus; Fifth Avenue Phantom to waiting; Master Plan to fbi; The Plutonians to the_shadows; Nature Strikes Back to don_and_dewey. Selection/intro/summary tracks remain unchanged.</x:v>
+        <x:v>Reassigned Trubble Unleashed to motorcycle_circus; Fifth Avenue Phantom to waiting; The Plotter to fbi; The Plutonians to the_shadows; Nature Strikes Back to don_and_dewey. Selection/intro/summary tracks remain unchanged.</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
         <x:v>Implemented - needs test</x:v>
@@ -8661,10 +8661,10 @@
         <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="C11" s="31" t="str">
-        <x:v>Swamp Reptiles</x:v>
+        <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
-        <x:v>swamp_reptiles</x:v>
+        <x:v>conners_reptiles</x:v>
       </x:c>
       <x:c r="E11" s="31" t="str">
         <x:v>swamp_bonus</x:v>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcb761e2c040d47c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Ra451be1887814581"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R45a46a7ffb9146c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R78a4f06c27ae4c47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R0aa8c446b5dd4f40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R6a702c60eb174b55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R55f831a98be448d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rd499acd3c3174512"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rfe17aea740d94751"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rcc59ebb472354b5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rdcc5727a886d42f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rd4f7adb540c14175"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rce0cf0a05c5f4903"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R5f0578cbbc53499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rf998a3df37bf412a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rbeef99dddf2440d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R41907c7259fd4377"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R2ad7effe9b804abe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Ra9e9b582a4554095"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R459d18fb35a24cd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R0315e3460aef484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R06f15aada58240ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rb1e24ccd98ab4175"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R8fc1bb6a940f4f18"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1054,22 +1054,22 @@
         <x:v>Multiball</x:v>
       </x:c>
       <x:c r="H11" s="31" t="str">
-        <x:v>Area control</x:v>
+        <x:v>Independent area building</x:v>
       </x:c>
       <x:c r="I11" s="31" t="str">
-        <x:v>Left/right/pops + saucers</x:v>
+        <x:v>Left drops + pops + right drops + saucers</x:v>
       </x:c>
       <x:c r="J11" s="31" t="str">
-        <x:v>Heat-area saucer jackpots</x:v>
+        <x:v>Area-scaled saucer jackpots and one add-a-ball per area</x:v>
       </x:c>
       <x:c r="K11" s="31" t="str">
-        <x:v>MB drain / area maxing</x:v>
+        <x:v>Holding value for a larger collect risks multiball ending before cashout</x:v>
       </x:c>
       <x:c r="L11" s="31" t="str">
-        <x:v>MB end or goals completed</x:v>
+        <x:v>Multiball returns to one ball</x:v>
       </x:c>
       <x:c r="M11" s="31" t="str">
-        <x:v>Second MB, but area-control identity keeps it different from Goblin.</x:v>
+        <x:v>Three simultaneous build-and-cash lanes create clear strategic choices. More Jackpots preserves one extra collect, while the 20-hit cap prevents runaway values.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4012,7 +4012,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H11" s="31" t="str">
-        <x:v>2-ball heat-area multiball; saucer eject delay considered OK.</x:v>
+        <x:v>2-ball multiball. Left drops, pops, and right drops independently build lit saucer jackpots at 100K x hits, or 150K x hits with Bigger, capped at 20 hits.</x:v>
       </x:c>
       <x:c r="I11" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -6573,16 +6573,16 @@
         <x:v>2-ball MB</x:v>
       </x:c>
       <x:c r="F11" s="31" t="str">
-        <x:v>Build heat in left/right/pops areas; maxed areas light saucer jackpots.</x:v>
+        <x:v>Every qualifying left-drop, pop, or right-drop hit scores 5K, increases that area's hit count, and lights the matching saucer jackpot. Number inserts show add-a-ball readiness.</x:v>
       </x:c>
       <x:c r="G11" s="31" t="str">
-        <x:v>Ends when Parafino multiball ends, or when objectives complete if reached first.</x:v>
+        <x:v>Ends immediately when multiball returns to one ball. Pending ejects and delayed messages are cancelled during teardown, then the normal summary begins.</x:v>
       </x:c>
       <x:c r="H11" s="31" t="str">
-        <x:v>Heat-area multiball; left/right/pops build heat; maxed areas light saucer jackpots and add-a-ball opportunities.</x:v>
+        <x:v>Jackpot value is 100K x area hits, or 150K x hits with Bigger, capped at 20 hits. Collecting resets that area's count. More Jackpots preserves the same jackpot once for an extra collect while still resetting the count.</x:v>
       </x:c>
       <x:c r="I11" s="31" t="str">
-        <x:v>Improved: persistent lit-saucer and collected-jackpot totals.</x:v>
+        <x:v>More Time qualifies add-a-ball at 2 hits instead of 3. Shot Assist doubles the first hit in each area. Safety Net adds a 10-second save after the opening multiball save. Status shows LEFT/POPS/RIGHT hit counts.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rce0cf0a05c5f4903"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R5f0578cbbc53499d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rf998a3df37bf412a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rbeef99dddf2440d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R41907c7259fd4377"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R2ad7effe9b804abe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Ra9e9b582a4554095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R459d18fb35a24cd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R0315e3460aef484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R06f15aada58240ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rb1e24ccd98ab4175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R8fc1bb6a940f4f18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re5eeccb22c544815"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rbacb49e094ac437c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R6be1ce2c9aae4440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R33af766c3a1d4a53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R937d63d1e6c44a2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R2452211aaaa24920"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R7b8f901a293c408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R3a7edccfcad3401f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rfb5592a7d5b84126"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rf107d082d8714668"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R87c965ec73bb4ecb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rb49dfc0ca6304193"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1054,22 +1054,22 @@
         <x:v>Multiball</x:v>
       </x:c>
       <x:c r="H11" s="31" t="str">
-        <x:v>Independent area building</x:v>
+        <x:v>Area control</x:v>
       </x:c>
       <x:c r="I11" s="31" t="str">
-        <x:v>Left drops + pops + right drops + saucers</x:v>
+        <x:v>Left/right/pops + saucers</x:v>
       </x:c>
       <x:c r="J11" s="31" t="str">
-        <x:v>Area-scaled saucer jackpots and one add-a-ball per area</x:v>
+        <x:v>Heat-area saucer jackpots</x:v>
       </x:c>
       <x:c r="K11" s="31" t="str">
-        <x:v>Holding value for a larger collect risks multiball ending before cashout</x:v>
+        <x:v>MB drain / area maxing</x:v>
       </x:c>
       <x:c r="L11" s="31" t="str">
-        <x:v>Multiball returns to one ball</x:v>
+        <x:v>MB end or goals completed</x:v>
       </x:c>
       <x:c r="M11" s="31" t="str">
-        <x:v>Three simultaneous build-and-cash lanes create clear strategic choices. More Jackpots preserves one extra collect, while the 20-hit cap prevents runaway values.</x:v>
+        <x:v>Second MB, but area-control identity keeps it different from Goblin.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1537,31 +1537,31 @@
         <x:v>The Conquistador</x:v>
       </x:c>
       <x:c r="E23" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="F23" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="31" t="str">
-        <x:v>Treasure hunt / pursuit</x:v>
+        <x:v>Timed pursuit</x:v>
       </x:c>
       <x:c r="H23" s="31" t="str">
-        <x:v>Risk-reward path</x:v>
+        <x:v>Build-and-cash</x:v>
       </x:c>
       <x:c r="I23" s="31" t="str">
-        <x:v>Fort, saucer, upper, and escape shots</x:v>
+        <x:v>Left bank + upper spinner + upper targets + center web</x:v>
       </x:c>
       <x:c r="J23" s="31" t="str">
-        <x:v>Fountain jackpots</x:v>
+        <x:v>Uncapped Fountain Jackpot and stage Speed Bonuses</x:v>
       </x:c>
       <x:c r="K23" s="31" t="str">
-        <x:v>Route and timer pressure</x:v>
+        <x:v>Fast completion earns speed value, while extra upper-target hits increase the jackpot</x:v>
       </x:c>
       <x:c r="L23" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>Either main timer expires, or Fountain sequence resolves</x:v>
       </x:c>
       <x:c r="M23" s="31" t="str">
-        <x:v>Hidden fort and Fountain of Youth provide the chapter's exploration role.</x:v>
+        <x:v>Distinct two-stage route: timed gate opening, untimed Fountain search, then timed cashout with an optional second sip.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1578,31 +1578,31 @@
         <x:v>Spider-Slayer</x:v>
       </x:c>
       <x:c r="E24" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="F24" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="31" t="str">
-        <x:v>Machine pursuit</x:v>
+        <x:v>Expanding shot hunt</x:v>
       </x:c>
       <x:c r="H24" s="31" t="str">
-        <x:v>Tracking target</x:v>
+        <x:v>Persistent lit-shot growth</x:v>
       </x:c>
       <x:c r="I24" s="31" t="str">
-        <x:v>Moving playfield shots</x:v>
+        <x:v>Ten lower-playfield categories + Daily Bugle VUK finish</x:v>
       </x:c>
       <x:c r="J24" s="31" t="str">
-        <x:v>Escape and destruction jackpots</x:v>
+        <x:v>50K lit shots and a 2M decaying Slayer Jackpot</x:v>
       </x:c>
       <x:c r="K24" s="31" t="str">
-        <x:v>Capture pressure</x:v>
+        <x:v>Fast 15-shot completion preserves more jackpot value</x:v>
       </x:c>
       <x:c r="L24" s="31" t="str">
-        <x:v>Slayer destroyed / ball end</x:v>
+        <x:v>Daily Bugle jackpot collected / ball end</x:v>
       </x:c>
       <x:c r="M24" s="31" t="str">
-        <x:v>Jameson-operated robot provides a clear mechanical hunt.</x:v>
+        <x:v>Hunt Time measures first-to-fifteenth successful shot; jackpot value alone communicates the final urgency.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4012,7 +4012,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H11" s="31" t="str">
-        <x:v>2-ball multiball. Left drops, pops, and right drops independently build lit saucer jackpots at 100K x hits, or 150K x hits with Bigger, capped at 20 hits.</x:v>
+        <x:v>2-ball heat-area multiball; saucer eject delay considered OK.</x:v>
       </x:c>
       <x:c r="I11" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -4393,10 +4393,10 @@
         <x:v>The Conquistador</x:v>
       </x:c>
       <x:c r="G23" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H23" s="31" t="str">
-        <x:v>Fountain of Terror antagonist. Placeholder scoring is active; full design sho...</x:v>
+        <x:v>Find the Fountain: complete the left bank under timer, make three upper-spinner spins, build the uncapped Fountain Jackpot with upper targets, then collect at center web.</x:v>
       </x:c>
       <x:c r="I23" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -4425,10 +4425,10 @@
         <x:v>Spider-Slayer</x:v>
       </x:c>
       <x:c r="G24" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H24" s="31" t="str">
-        <x:v>Jameson-operated tracking robot. Placeholder scoring is active; full design s...</x:v>
+        <x:v>Expanding 15-hit hunt: one random category starts lit, every successful lit shot scores and adds another persistent lit category. The fifteenth hit opens the Daily Bugle VUK for a decaying Slayer Jackpot.</x:v>
       </x:c>
       <x:c r="I24" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -6573,16 +6573,16 @@
         <x:v>2-ball MB</x:v>
       </x:c>
       <x:c r="F11" s="31" t="str">
-        <x:v>Every qualifying left-drop, pop, or right-drop hit scores 5K, increases that area's hit count, and lights the matching saucer jackpot. Number inserts show add-a-ball readiness.</x:v>
+        <x:v>Build heat in left/right/pops areas; maxed areas light saucer jackpots.</x:v>
       </x:c>
       <x:c r="G11" s="31" t="str">
-        <x:v>Ends immediately when multiball returns to one ball. Pending ejects and delayed messages are cancelled during teardown, then the normal summary begins.</x:v>
+        <x:v>Ends when Parafino multiball ends, or when objectives complete if reached first.</x:v>
       </x:c>
       <x:c r="H11" s="31" t="str">
-        <x:v>Jackpot value is 100K x area hits, or 150K x hits with Bigger, capped at 20 hits. Collecting resets that area's count. More Jackpots preserves the same jackpot once for an extra collect while still resetting the count.</x:v>
+        <x:v>Heat-area multiball; left/right/pops build heat; maxed areas light saucer jackpots and add-a-ball opportunities.</x:v>
       </x:c>
       <x:c r="I11" s="31" t="str">
-        <x:v>More Time qualifies add-a-ball at 2 hits instead of 3. Shot Assist doubles the first hit in each area. Safety Net adds a 10-second save after the opening multiball save. Status shows LEFT/POPS/RIGHT hit counts.</x:v>
+        <x:v>Improved: persistent lit-saucer and collected-jackpot totals.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -6921,16 +6921,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F23" s="31" t="str">
-        <x:v>Placeholder framework for treasure hunt / pursuit with risk-reward path, using Fort, saucer, upper, and escape shots.</x:v>
+        <x:v>Complete the left drop bank before time expires to open the rooftop gate. Make three upper-spinner spins to light center web, then collect the Fountain Jackpot before the second timer expires.</x:v>
       </x:c>
       <x:c r="G23" s="31" t="str">
-        <x:v>Ends when goals completed / ball end.</x:v>
+        <x:v>Fails with FOUNTAIN NOT FOUND if either main timer expires. With More Jackpots, a missed 10-second second-sip window ends with WASTED YOUTH.</x:v>
       </x:c>
       <x:c r="H23" s="31" t="str">
-        <x:v>Fountain jackpots. Route and timer pressure.</x:v>
+        <x:v>Left drops and spinner spins score 50K each. Fountain Jackpot is 300K + 100K per upper-target hit with no cap. Bigger changes this to 400K + 150K per hit. Speed Bonus is 50K per second remaining on each completed timed phase.</x:v>
       </x:c>
       <x:c r="I23" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>More Time gives 30-second main timers. More Jackpots relights center web after a two-second jackpot message for a 10-second same-value second collect. Safety Net starts at Fountain readiness. Shot Assist doubles the first upper-target build hit.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -6950,16 +6950,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F24" s="31" t="str">
-        <x:v>Placeholder framework for machine pursuit with tracking target, using Moving playfield shots.</x:v>
+        <x:v>One random shot category starts lit. Each successful lit shot scores 50K and adds another persistent lit category. Hunt Time runs from the first successful hit through the fifteenth, then all build shots shut off and the Daily Bugle VUK lights.</x:v>
       </x:c>
       <x:c r="G24" s="31" t="str">
-        <x:v>Ends when slayer destroyed / ball end.</x:v>
+        <x:v>Completes when the Daily Bugle VUK collects the Slayer Jackpot. A drain before collection ends with SLAYER ESCAPED.</x:v>
       </x:c>
       <x:c r="H24" s="31" t="str">
-        <x:v>Escape and destruction jackpots. Capture pressure.</x:v>
+        <x:v>Successful lit shots score 50K; Bigger raises them to 75K. Slayer Jackpot starts at 2M, or 2.5M with Bigger, and decays to a 100K minimum.</x:v>
       </x:c>
       <x:c r="I24" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>More Jackpots freezes the full jackpot for 10 seconds. More Time halves decay to 50K/sec. Safety Net starts a 10-second save when the VUK lights. Shot Assist makes the first hit add two new categories.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re5eeccb22c544815"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rbacb49e094ac437c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R6be1ce2c9aae4440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R33af766c3a1d4a53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R937d63d1e6c44a2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R2452211aaaa24920"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R7b8f901a293c408b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R3a7edccfcad3401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rfb5592a7d5b84126"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rf107d082d8714668"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R87c965ec73bb4ecb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rb49dfc0ca6304193"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5bcfb0e819454765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Ra8ad3347d55242a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R953a369e5a9c4c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rb24acf4a88fd40bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R780a5f75bcc5482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rcdcdb7bc95424418"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rb920285ad83f422b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R5431a94423ac46e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rf00e596749264f13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rf439ed759efa438c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R7cabd38e08c04be6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R16545caf0f5d45cc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -542,7 +542,7 @@
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Danger Lurks has five playable placeholder villain modes, Fiddler Ransom is wired as its persistent bonus, and The Web Tightens is a working placeholder mini-wizard.</x:v>
+        <x:v>Danger Lurks is now complete with five substantive villain modes: Harley Clivendon, The Conquistador, Spider-Slayer, Metal-Eating Monster, and Fiddler. Across all chapters, 39 of 55 regular villain modes have substantive implementations; 16 still need major rules work.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -700,7 +700,7 @@
         <x:v>Goals completed / ball end</x:v>
       </x:c>
       <x:c r="M2" s="31" t="str">
-        <x:v>Chapter 1 build-and-cash anchor; good contrast with Lizard urgency and Electro sequence.</x:v>
+        <x:v>Chapter 1 build-and-cash anchor; contrasts with Sandman precision, Electro sequence, and Goblin multiball.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -793,10 +793,10 @@
         <x:v>Classic Rogues</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>lizard</x:v>
+        <x:v>electro</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
-        <x:v>Lizard</x:v>
+        <x:v>Electro</x:v>
       </x:c>
       <x:c r="E5" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
@@ -805,25 +805,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="31" t="str">
-        <x:v>Timed delivery</x:v>
+        <x:v>Sequence</x:v>
       </x:c>
       <x:c r="H5" s="31" t="str">
-        <x:v>Draining value</x:v>
+        <x:v>Travelling timed shot</x:v>
       </x:c>
       <x:c r="I5" s="31" t="str">
-        <x:v>STAR + web shots</x:v>
+        <x:v>Whole playfield</x:v>
       </x:c>
       <x:c r="J5" s="31" t="str">
-        <x:v>Draining serum value</x:v>
+        <x:v>Resetting decaying spark jackpots</x:v>
       </x:c>
       <x:c r="K5" s="31" t="str">
-        <x:v>Value drain / shot routing</x:v>
+        <x:v>5s windows and final 10s Super</x:v>
       </x:c>
       <x:c r="L5" s="31" t="str">
-        <x:v>Deliveries completed / ball end</x:v>
+        <x:v>Super collected, Super missed, or ball end</x:v>
       </x:c>
       <x:c r="M5" s="31" t="str">
-        <x:v>Urgency mode; case files now support the core loop instead of bypassing it.</x:v>
+        <x:v>Clear travelling-shot mode with reliable helper behavior; every move restores full value before decay resumes.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -834,37 +834,37 @@
         <x:v>Classic Rogues</x:v>
       </x:c>
       <x:c r="C6" s="31" t="str">
-        <x:v>electro</x:v>
+        <x:v>goblin</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
-        <x:v>Electro</x:v>
+        <x:v>Green Goblin</x:v>
       </x:c>
       <x:c r="E6" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>2-ball MB</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Sequence</x:v>
+        <x:v>Multiball</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
-        <x:v>Travelling timed shot</x:v>
+        <x:v>Chaos windows</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
-        <x:v>Whole playfield</x:v>
+        <x:v>Whole playfield + saucers</x:v>
       </x:c>
       <x:c r="J6" s="31" t="str">
-        <x:v>Resetting decaying spark jackpots</x:v>
+        <x:v>Windowed jackpots / banked bonus</x:v>
       </x:c>
       <x:c r="K6" s="31" t="str">
-        <x:v>5s windows and final 10s Super</x:v>
+        <x:v>Multiball drain / timing windows</x:v>
       </x:c>
       <x:c r="L6" s="31" t="str">
-        <x:v>Super collected, Super missed, or ball end</x:v>
+        <x:v>MB end or goals completed</x:v>
       </x:c>
       <x:c r="M6" s="31" t="str">
-        <x:v>Clear travelling-shot mode with reliable helper behavior; every move restores full value before decay resumes.</x:v>
+        <x:v>Chapter 1 multiball role; adds an early MB and breaks up the chapter's single-ball progression.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -875,37 +875,37 @@
         <x:v>Masked Masterminds</x:v>
       </x:c>
       <x:c r="C7" s="31" t="str">
-        <x:v>goblin</x:v>
+        <x:v>doc_ock</x:v>
       </x:c>
       <x:c r="D7" s="31" t="str">
-        <x:v>Green Goblin</x:v>
+        <x:v>Doctor Octopus</x:v>
       </x:c>
       <x:c r="E7" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented / recent rule update</x:v>
       </x:c>
       <x:c r="F7" s="31" t="str">
-        <x:v>2-ball MB</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="31" t="str">
-        <x:v>Multiball</x:v>
+        <x:v>Control / lock state</x:v>
       </x:c>
       <x:c r="H7" s="31" t="str">
-        <x:v>Chaos windows</x:v>
+        <x:v>Build-and-cash</x:v>
       </x:c>
       <x:c r="I7" s="31" t="str">
-        <x:v>Whole playfield + saucers</x:v>
+        <x:v>Rollovers + left bank + webs</x:v>
       </x:c>
       <x:c r="J7" s="31" t="str">
-        <x:v>Windowed jackpots / banked bonus</x:v>
+        <x:v>Arm locks and web jackpots</x:v>
       </x:c>
       <x:c r="K7" s="31" t="str">
-        <x:v>Multiball drain / timing windows</x:v>
+        <x:v>Arms can be freed / state pressure</x:v>
       </x:c>
       <x:c r="L7" s="31" t="str">
-        <x:v>MB end or goals completed</x:v>
+        <x:v>Goals completed / ball end</x:v>
       </x:c>
       <x:c r="M7" s="31" t="str">
-        <x:v>Chaotic MB role; distinct from Parafino because scoring windows are unstable.</x:v>
+        <x:v>State-management mode; good strategic contrast.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -916,37 +916,37 @@
         <x:v>Masked Masterminds</x:v>
       </x:c>
       <x:c r="C8" s="31" t="str">
-        <x:v>doc_ock</x:v>
+        <x:v>mysterio</x:v>
       </x:c>
       <x:c r="D8" s="31" t="str">
-        <x:v>Doctor Octopus</x:v>
+        <x:v>Mysterio</x:v>
       </x:c>
       <x:c r="E8" s="31" t="str">
-        <x:v>Implemented / recent rule update</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="F8" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="31" t="str">
-        <x:v>Control / lock state</x:v>
+        <x:v>Mystery / reveal</x:v>
       </x:c>
       <x:c r="H8" s="31" t="str">
-        <x:v>Build-and-cash</x:v>
+        <x:v>Clue logic</x:v>
       </x:c>
       <x:c r="I8" s="31" t="str">
-        <x:v>Rollovers + left bank + webs</x:v>
+        <x:v>Whole playfield</x:v>
       </x:c>
       <x:c r="J8" s="31" t="str">
-        <x:v>Arm locks and web jackpots</x:v>
+        <x:v>Hidden Super</x:v>
       </x:c>
       <x:c r="K8" s="31" t="str">
-        <x:v>Arms can be freed / state pressure</x:v>
+        <x:v>Wrong-shot penalty</x:v>
       </x:c>
       <x:c r="L8" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>Hidden Super solved / ball end</x:v>
       </x:c>
       <x:c r="M8" s="31" t="str">
-        <x:v>State-management mode; good strategic contrast.</x:v>
+        <x:v>Mystery role for the chapter.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -957,10 +957,10 @@
         <x:v>Masked Masterminds</x:v>
       </x:c>
       <x:c r="C9" s="31" t="str">
-        <x:v>mysterio</x:v>
+        <x:v>scorpion</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
-        <x:v>Mysterio</x:v>
+        <x:v>Scorpion</x:v>
       </x:c>
       <x:c r="E9" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
@@ -969,25 +969,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="31" t="str">
-        <x:v>Mystery / reveal</x:v>
+        <x:v>Timed attack</x:v>
       </x:c>
       <x:c r="H9" s="31" t="str">
-        <x:v>Clue logic</x:v>
+        <x:v>Spinner build</x:v>
       </x:c>
       <x:c r="I9" s="31" t="str">
-        <x:v>Whole playfield</x:v>
+        <x:v>Spinner + drop banks</x:v>
       </x:c>
       <x:c r="J9" s="31" t="str">
-        <x:v>Hidden Super</x:v>
+        <x:v>Venom build into staged attacks</x:v>
       </x:c>
       <x:c r="K9" s="31" t="str">
-        <x:v>Wrong-shot penalty</x:v>
+        <x:v>Timed staged shot</x:v>
       </x:c>
       <x:c r="L9" s="31" t="str">
-        <x:v>Hidden Super solved / ball end</x:v>
+        <x:v>Attack sequence complete / ball end</x:v>
       </x:c>
       <x:c r="M9" s="31" t="str">
-        <x:v>Mystery role for the chapter.</x:v>
+        <x:v>Urgency/drop attack role.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -998,10 +998,10 @@
         <x:v>Masked Masterminds</x:v>
       </x:c>
       <x:c r="C10" s="31" t="str">
-        <x:v>scorpion</x:v>
+        <x:v>lizard</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
-        <x:v>Scorpion</x:v>
+        <x:v>Lizard</x:v>
       </x:c>
       <x:c r="E10" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
@@ -1010,25 +1010,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="31" t="str">
-        <x:v>Timed attack</x:v>
+        <x:v>Timed delivery</x:v>
       </x:c>
       <x:c r="H10" s="31" t="str">
-        <x:v>Spinner build</x:v>
+        <x:v>Draining value</x:v>
       </x:c>
       <x:c r="I10" s="31" t="str">
-        <x:v>Spinner + drop banks</x:v>
+        <x:v>STAR + web shots</x:v>
       </x:c>
       <x:c r="J10" s="31" t="str">
-        <x:v>Venom build into staged attacks</x:v>
+        <x:v>Draining serum value</x:v>
       </x:c>
       <x:c r="K10" s="31" t="str">
-        <x:v>Timed staged shot</x:v>
+        <x:v>Value drain / shot routing</x:v>
       </x:c>
       <x:c r="L10" s="31" t="str">
-        <x:v>Attack sequence complete / ball end</x:v>
+        <x:v>Deliveries completed / ball end</x:v>
       </x:c>
       <x:c r="M10" s="31" t="str">
-        <x:v>Urgency/drop attack role.</x:v>
+        <x:v>Chapter 2 timed-delivery role; adds urgency and value decay without duplicating Parafino's multiball.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1069,7 +1069,7 @@
         <x:v>MB end or goals completed</x:v>
       </x:c>
       <x:c r="M11" s="31" t="str">
-        <x:v>Second MB, but area-control identity keeps it different from Goblin.</x:v>
+        <x:v>Chapter 2 multiball role; area-control and lit-saucer add-a-ball give it a distinct identity.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1496,31 +1496,31 @@
         <x:v>Harley Clivendon</x:v>
       </x:c>
       <x:c r="E22" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="F22" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>2-ball MB</x:v>
       </x:c>
       <x:c r="G22" s="31" t="str">
-        <x:v>Hypnosis / reveal</x:v>
+        <x:v>Multiball</x:v>
       </x:c>
       <x:c r="H22" s="31" t="str">
-        <x:v>Hidden-shot control</x:v>
+        <x:v>Area control / lock-and-cash</x:v>
       </x:c>
       <x:c r="I22" s="31" t="str">
-        <x:v>Spinner, targets, and changing shots</x:v>
+        <x:v>Whole playfield + saucers + VUK</x:v>
       </x:c>
       <x:c r="J22" s="31" t="str">
-        <x:v>Idol and scheme jackpots</x:v>
+        <x:v>Area-built VUK jackpot</x:v>
       </x:c>
       <x:c r="K22" s="31" t="str">
-        <x:v>Shot confusion / reveal windows</x:v>
+        <x:v>Multiball control and parallel area progress</x:v>
       </x:c>
       <x:c r="L22" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>Objectives complete / multiball end / ball end</x:v>
       </x:c>
       <x:c r="M22" s="31" t="str">
-        <x:v>Two-episode antagonist gives the chapter its hypnosis and hidden-scheme role.</x:v>
+        <x:v>Chapter 5 multiball role; controlled area-building contrasts with Conquistador's route and Spider-Slayer's expanding hunt.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1613,37 +1613,37 @@
         <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C25" s="31" t="str">
-        <x:v>metal_eating_monster</x:v>
+        <x:v>metal_eating_robot</x:v>
       </x:c>
       <x:c r="D25" s="31" t="str">
         <x:v>Metal-Eating Monster</x:v>
       </x:c>
       <x:c r="E25" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F25" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="31" t="str">
-        <x:v>Area consumption</x:v>
+        <x:v>Overlapping zone rescue</x:v>
       </x:c>
       <x:c r="H25" s="31" t="str">
-        <x:v>Restore disabled areas</x:v>
+        <x:v>Independent timers / escalating pressure</x:v>
       </x:c>
       <x:c r="I25" s="31" t="str">
-        <x:v>Whole playfield and river finish</x:v>
+        <x:v>Eight whole-playfield zones</x:v>
       </x:c>
       <x:c r="J25" s="31" t="str">
-        <x:v>Destruction jackpots</x:v>
+        <x:v>250K zone saves; one half-value repeat per saved zone with More Jackpots</x:v>
       </x:c>
       <x:c r="K25" s="31" t="str">
-        <x:v>Shrinking safe playfield</x:v>
+        <x:v>New attacks every 5s; saves accelerate the next attack to 2s</x:v>
       </x:c>
       <x:c r="L25" s="31" t="str">
-        <x:v>Robot stopped / ball end</x:v>
+        <x:v>4+ saved and no active attacks / 3 destroyed / ball end</x:v>
       </x:c>
       <x:c r="M25" s="31" t="str">
-        <x:v>Giant robot creates a distinctive city-destruction mode.</x:v>
+        <x:v>Chapter 5 reversible-pressure role. Unlike Harley's accumulating area-control multiball, this is a single-ball rescue race with up to three overlapping independent deadlines.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1660,31 +1660,31 @@
         <x:v>Fiddler</x:v>
       </x:c>
       <x:c r="E26" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F26" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G26" s="31" t="str">
-        <x:v>Music / sequence</x:v>
+        <x:v>Memory sequence</x:v>
       </x:c>
       <x:c r="H26" s="31" t="str">
-        <x:v>Pitch and ransom build</x:v>
+        <x:v>Audio-visual Simon Says</x:v>
       </x:c>
       <x:c r="I26" s="31" t="str">
-        <x:v>Spinner plus ordered shots</x:v>
+        <x:v>Left web + bank rubbers + center web</x:v>
       </x:c>
       <x:c r="J26" s="31" t="str">
-        <x:v>Sound-wave jackpots</x:v>
+        <x:v>Incrementing correct-note jackpots</x:v>
       </x:c>
       <x:c r="K26" s="31" t="str">
-        <x:v>Sequence and timer pressure</x:v>
+        <x:v>Instant failure on wrong note</x:v>
       </x:c>
       <x:c r="L26" s="31" t="str">
-        <x:v>Violin silenced / ball end</x:v>
+        <x:v>3 rounds / optional 4th / wrong note / ball end</x:v>
       </x:c>
       <x:c r="M26" s="31" t="str">
-        <x:v>Sound-based rules give the chapter a strong audiovisual identity. Persistent fiddler_bonus / FIDDLER RANSOM bank is now structurally implemented.</x:v>
+        <x:v>Completes Chapter 5 with a memory-and-precision identity unlike Harley multiball, Conquistador routing, Spider-Slayer hunting, or Metal Monster rescue pressure.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2111,31 +2111,31 @@
         <x:v>Clive and Blotto</x:v>
       </x:c>
       <x:c r="E37" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="F37" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G37" s="31" t="str">
-        <x:v>Containment / spreading hazard</x:v>
+        <x:v>Meter management</x:v>
       </x:c>
       <x:c r="H37" s="31" t="str">
-        <x:v>Banked bonus</x:v>
+        <x:v>Spreading area cleanup</x:v>
       </x:c>
       <x:c r="I37" s="31" t="str">
-        <x:v>Whole playfield / containment shots</x:v>
+        <x:v>Spinner + whole-playfield areas</x:v>
       </x:c>
       <x:c r="J37" s="31" t="str">
-        <x:v>blotto_bonus bank</x:v>
+        <x:v>Clear infected areas while draining meter</x:v>
       </x:c>
       <x:c r="K37" s="31" t="str">
-        <x:v>Blotto spreads and changes shape</x:v>
+        <x:v>Meter rises every 2 seconds</x:v>
       </x:c>
       <x:c r="L37" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>No infected areas and meter 0 / ball end</x:v>
       </x:c>
       <x:c r="M37" s="31" t="str">
-        <x:v>Tar/sludge element; full mode design pending.</x:v>
+        <x:v>Distinct tug-of-war mode; not another timed rescue or simple spinner build.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2644,31 +2644,31 @@
         <x:v>Skymaster</x:v>
       </x:c>
       <x:c r="E50" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Temporary placeholder / redesign required</x:v>
       </x:c>
       <x:c r="F50" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G50" s="31" t="str">
-        <x:v>Limited flips</x:v>
+        <x:v>Generic placeholder</x:v>
       </x:c>
       <x:c r="H50" s="31" t="str">
-        <x:v>Blimp assault</x:v>
+        <x:v>Temporary hit count</x:v>
       </x:c>
       <x:c r="I50" s="31" t="str">
-        <x:v>Saucers + upper targets</x:v>
+        <x:v>Whole playfield</x:v>
       </x:c>
       <x:c r="J50" s="31" t="str">
-        <x:v>Flips-left Super</x:v>
+        <x:v>Temporary placeholder scoring</x:v>
       </x:c>
       <x:c r="K50" s="31" t="str">
-        <x:v>Flip limit</x:v>
+        <x:v>No final distinct pressure model</x:v>
       </x:c>
       <x:c r="L50" s="31" t="str">
-        <x:v>3 roof clears / ball end</x:v>
+        <x:v>Temporary goal / ball end</x:v>
       </x:c>
       <x:c r="M50" s="31" t="str">
-        <x:v>The Fly's working limited-flip rules rethemed as an attack on Skymaster's blimp.</x:v>
+        <x:v>Do not count as a completed limited-flip mode. Current code explicitly marks Skymaster as temporary and awaiting a distinct non-rooftop redesign.</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -2890,31 +2890,31 @@
         <x:v>Baron Von Rantenraven</x:v>
       </x:c>
       <x:c r="E56" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F56" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G56" s="31" t="str">
-        <x:v>Aerial invasion</x:v>
+        <x:v>Limited flips</x:v>
       </x:c>
       <x:c r="H56" s="31" t="str">
-        <x:v>Whole-playfield assault</x:v>
+        <x:v>Upper-playfield precision</x:v>
       </x:c>
       <x:c r="I56" s="31" t="str">
-        <x:v>Air-raid, paralysis, and upper shots</x:v>
+        <x:v>Saucers + upper entrance + 3 roof targets</x:v>
       </x:c>
       <x:c r="J56" s="31" t="str">
-        <x:v>Sky Harbor jackpots</x:v>
+        <x:v>Unique-target jackpots and remaining-flips Super</x:v>
       </x:c>
       <x:c r="K56" s="31" t="str">
-        <x:v>Escalating invasion pressure</x:v>
+        <x:v>10-flip resource</x:v>
       </x:c>
       <x:c r="L56" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>3 unique roof targets / flips exhausted / ball end</x:v>
       </x:c>
       <x:c r="M56" s="31" t="str">
-        <x:v>World War I aircraft and paralysis technology create the final chapter's aerial-war role.</x:v>
+        <x:v>Sky Harbor gives Chapter 11 a true limited-resource precision mode and should be counted as substantively implemented.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3408,10 +3408,10 @@
         <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="B6" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="n">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="C6" s="31" t="n">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
         <x:v>The Web Tightens</x:v>
@@ -3598,10 +3598,10 @@
         <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="B11" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C11" s="31" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="31" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
         <x:v>Who Is the Real Villain?</x:v>
@@ -3636,10 +3636,10 @@
         <x:v>Dimensional Finale</x:v>
       </x:c>
       <x:c r="B12" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="31" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D12" s="31" t="str">
         <x:v>Time-Tossed Showdown</x:v>
@@ -3811,16 +3811,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E5" s="31" t="str">
-        <x:v>lizard</x:v>
+        <x:v>electro</x:v>
       </x:c>
       <x:c r="F5" s="31" t="str">
-        <x:v>Lizard</x:v>
+        <x:v>Electro</x:v>
       </x:c>
       <x:c r="G5" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H5" s="31" t="str">
-        <x:v>Serum at STAR; deliver to web shots. Case files now enhance the loop: Bigger ...</x:v>
+        <x:v>Travelling 5-second spark shots reset to maximum value whenever they move, th...</x:v>
       </x:c>
       <x:c r="I5" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -3843,16 +3843,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="31" t="str">
-        <x:v>electro</x:v>
+        <x:v>goblin</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
-        <x:v>Electro</x:v>
+        <x:v>Green Goblin</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
-        <x:v>Travelling 5-second spark shots reset to maximum value whenever they move, th...</x:v>
+        <x:v>Chaos multiball; banks goblin_bonus; first 10 music assignment retained.</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -3875,16 +3875,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E7" s="31" t="str">
-        <x:v>goblin</x:v>
+        <x:v>doc_ock</x:v>
       </x:c>
       <x:c r="F7" s="31" t="str">
-        <x:v>Green Goblin</x:v>
+        <x:v>Doctor Octopus</x:v>
       </x:c>
       <x:c r="G7" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented / recent rule update</x:v>
       </x:c>
       <x:c r="H7" s="31" t="str">
-        <x:v>Chaos multiball; banks goblin_bonus; first 10 music assignment retained.</x:v>
+        <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpot; ...</x:v>
       </x:c>
       <x:c r="I7" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -3907,16 +3907,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="31" t="str">
-        <x:v>doc_ock</x:v>
+        <x:v>mysterio</x:v>
       </x:c>
       <x:c r="F8" s="31" t="str">
-        <x:v>Doctor Octopus</x:v>
+        <x:v>Mysterio</x:v>
       </x:c>
       <x:c r="G8" s="31" t="str">
-        <x:v>Implemented / recent rule update</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H8" s="31" t="str">
-        <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpot; ...</x:v>
+        <x:v>Hidden Super/clue mode; wrong shots lower value; first 10 music assignment re...</x:v>
       </x:c>
       <x:c r="I8" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -3939,16 +3939,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E9" s="31" t="str">
-        <x:v>mysterio</x:v>
+        <x:v>scorpion</x:v>
       </x:c>
       <x:c r="F9" s="31" t="str">
-        <x:v>Mysterio</x:v>
+        <x:v>Scorpion</x:v>
       </x:c>
       <x:c r="G9" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H9" s="31" t="str">
-        <x:v>Hidden Super/clue mode; wrong shots lower value; first 10 music assignment re...</x:v>
+        <x:v>Spinner builds Venom; upper exit stages timed drop attack.</x:v>
       </x:c>
       <x:c r="I9" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -3971,16 +3971,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E10" s="31" t="str">
-        <x:v>scorpion</x:v>
+        <x:v>lizard</x:v>
       </x:c>
       <x:c r="F10" s="31" t="str">
-        <x:v>Scorpion</x:v>
+        <x:v>Lizard</x:v>
       </x:c>
       <x:c r="G10" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H10" s="31" t="str">
-        <x:v>Spinner builds Venom; upper exit stages timed drop attack.</x:v>
+        <x:v>Serum at STAR; deliver to web shots. Case files now enhance the loop: Bigger ...</x:v>
       </x:c>
       <x:c r="I10" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -4361,10 +4361,10 @@
         <x:v>Harley Clivendon</x:v>
       </x:c>
       <x:c r="G22" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H22" s="31" t="str">
-        <x:v>The One-Eyed Idol / Fountain of Terror antagonist. Placeholder scoring is act...</x:v>
+        <x:v>Custom 2-ball area-control multiball. A saucer holds a ball while independent playfield areas are lit; enough lit areas qualify the VUK jackpot, whose value reflects area progress.</x:v>
       </x:c>
       <x:c r="I22" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -4454,13 +4454,13 @@
         <x:v>metal_eating_robot</x:v>
       </x:c>
       <x:c r="F25" s="31" t="str">
-        <x:v>Metal-Eating Robot</x:v>
+        <x:v>Metal-Eating Monster</x:v>
       </x:c>
       <x:c r="G25" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H25" s="31" t="str">
-        <x:v>Giant robot from Diet of Destruction. Placeholder scoring is active; full des...</x:v>
+        <x:v>Eight-zone rescue mode. A new safe zone comes under attack every 5 seconds; each attack has an independent 12-second timer. Hits save zones, save reactions bring the next attack in 2 seconds, four saves stop new attacks, and three destroyed zones end the mode.</x:v>
       </x:c>
       <x:c r="I25" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -4489,10 +4489,10 @@
         <x:v>Fiddler</x:v>
       </x:c>
       <x:c r="G26" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H26" s="31" t="str">
-        <x:v>Fiddler on the Loose sound-and-ransom antagonist. Placeholder scoring is acti...</x:v>
+        <x:v>Simon Says violin mode. Three normal rounds use one, two, and three unique notes; More Jackpots adds a four-note round. Each note flashes for 2 seconds with a fixed audio event, then stays solid for ordered player input. One wrong note ends the mode.</x:v>
       </x:c>
       <x:c r="I26" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -4841,10 +4841,10 @@
         <x:v>Clive and Blotto</x:v>
       </x:c>
       <x:c r="G37" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="H37" s="31" t="str">
-        <x:v>Former Radiation Specialist placeholder retained for later redesign. Clive cr...</x:v>
+        <x:v>Blotto Meter starts at 3/4 and gains 1 every 2 seconds. Spinner hits lower it and pause growth for 2 seconds. When full, one clean area becomes Blotto'd; any hit in that area clears it. Win with no Blotto'd areas and meter at 0.</x:v>
       </x:c>
       <x:c r="I37" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4870,13 +4870,13 @@
         <x:v>dr_zapp</x:v>
       </x:c>
       <x:c r="F38" s="31" t="str">
-        <x:v>Doctor Zappp</x:v>
+        <x:v>Doctor Zapp</x:v>
       </x:c>
       <x:c r="G38" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="H38" s="31" t="str">
-        <x:v>Electrical/weather slot. Full rules still need design around Zapp stealing an...</x:v>
+        <x:v>Knock down one target from each lower bank to open roof access. Upper spinner camera flashes defeat Zapp at 25 flashes; each lit upper helper target adds +1 flash per spin. Drops score 100K, helpers 50K, flashes 50K.</x:v>
       </x:c>
       <x:c r="I38" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4905,10 +4905,10 @@
         <x:v>Bolton and Boomer</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Former elemental freeze placeholder retained for later redesign. Thunder Rumb...</x:v>
+        <x:v>Repeating 2-ball multiball loop: hit a random lit target, lock one ball in any saucer, then shoot the VUK Super. First Super is untimed; later Supers run 20 seconds and reset the loop if missed.</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -5257,10 +5257,10 @@
         <x:v>Skymaster</x:v>
       </x:c>
       <x:c r="G50" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Temporary placeholder / redesign required</x:v>
       </x:c>
       <x:c r="H50" s="31" t="str">
-        <x:v>Former The Fly Rooftop Swarm rules rethemed as a limited-flip assault on Skym...</x:v>
+        <x:v>Current Python explicitly identifies this as a temporary Skymaster placeholder pending a distinct non-rooftop redesign; generic hit-count gameplay should not be treated as complete.</x:v>
       </x:c>
       <x:c r="I50" s="31" t="str">
         <x:v>who_is_the_real_villain</x:v>
@@ -5449,10 +5449,10 @@
         <x:v>Baron Von Rantenraven</x:v>
       </x:c>
       <x:c r="G56" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H56" s="31" t="str">
-        <x:v>Sky Harbor's World War I aerial invasion and paralysis technology. Placeholde...</x:v>
+        <x:v>Sky Harbor limited-flips rooftop assault: saucers open roof access; upper entry starts a 10-flip attempt; three unique upper targets lead to a remaining-flips Super, with repeat-target scoring and case-file support.</x:v>
       </x:c>
       <x:c r="I56" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -6064,7 +6064,7 @@
         <x:v>Skymaster</x:v>
       </x:c>
       <x:c r="D19" s="31" t="str">
-        <x:v>Working limited-flip Rooftop Swarm mechanics rethemed as an assault on Skymaster's blimp.</x:v>
+        <x:v>Current mode is explicitly a temporary placeholder pending a distinct non-rooftop Skymaster redesign; do not treat former rooftop rules as final.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -6120,7 +6120,7 @@
         <x:v>Baron Von Rantenraven</x:v>
       </x:c>
       <x:c r="D23" s="31" t="str">
-        <x:v>Unverified Grand Emperor placeholder replaced by the Sky Harbor antagonist.</x:v>
+        <x:v>Former identity slot now contains the implemented Sky Harbor 10-flip rooftop precision assault.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -6134,7 +6134,7 @@
         <x:v>Harley Clivendon</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
+        <x:v>Originally introduced as a Chapter 5 placeholder; now has a custom 2-ball area-control multiball implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -6148,7 +6148,7 @@
         <x:v>The Conquistador</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
+        <x:v>Originally introduced as a Chapter 5 placeholder; now has the custom Find the Fountain timed route and jackpot implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -6162,7 +6162,7 @@
         <x:v>Spider-Slayer</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
+        <x:v>Originally introduced as a Chapter 5 placeholder; now has the expanding 15-hit hunt and decaying Daily Bugle jackpot implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -6173,10 +6173,10 @@
         <x:v>metal_eating_robot</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>Metal-Eating Robot</x:v>
+        <x:v>Metal-Eating Monster</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
+        <x:v>Originally introduced as a Chapter 5 placeholder; now implemented as an eight-zone overlapping rescue mode with independent destruction timers.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -6190,7 +6190,7 @@
         <x:v>Fiddler</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
+        <x:v>Originally introduced as a Chapter 5 placeholder; now implemented as a three-stage Simon Says light-and-violin sequence mode with an optional four-note encore.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -6390,25 +6390,25 @@
         <x:v>Classic Rogues</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>lizard</x:v>
+        <x:v>electro</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
-        <x:v>Lizard</x:v>
+        <x:v>Electro</x:v>
       </x:c>
       <x:c r="E5" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="31" t="str">
-        <x:v>Hit STAR to create serum, then deliver it to the required web shot before value drains.</x:v>
+        <x:v>Follow the travelling spark across eight shot groups. Each new spark starts at maximum value and then decays once per second until hit or moved.</x:v>
       </x:c>
       <x:c r="G5" s="31" t="str">
-        <x:v>Ends when serum deliveries are completed; otherwise stops on ball end.</x:v>
+        <x:v>Collected groups are removed until one final shot remains for the 10-second Super Jackpot. Collecting the Super completes the mode; missing it or ball end stops it.</x:v>
       </x:c>
       <x:c r="H5" s="31" t="str">
-        <x:v>STAR creates serum; web shots deliver it. Case files add bigger value, slower decay, follow-up jackpots, one serum-save, and first-delivery flexibility.</x:v>
+        <x:v>Normal sparks start at 250K, or 300K with Bigger, and fall 10K per second to 50K. More Time halves the drain rate. More Jackpots returns the first collected group to the pool for one extra normal jackpot. Shot Assist makes the first spark last 8 seconds.</x:v>
       </x:c>
       <x:c r="I5" s="31" t="str">
-        <x:v>Improved: live serum objective/delivery progress between countdowns.</x:v>
+        <x:v>Existing Electro light timing is retained. The Super uses the existing SUPER SURGE LIT countdown plus persistent SUPER SPARK status. Gate routing follows upper shots, and saucers use delayed clearing.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6419,25 +6419,25 @@
         <x:v>Classic Rogues</x:v>
       </x:c>
       <x:c r="C6" s="31" t="str">
-        <x:v>electro</x:v>
+        <x:v>goblin</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
-        <x:v>Electro</x:v>
+        <x:v>Green Goblin</x:v>
       </x:c>
       <x:c r="E6" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>2-ball MB</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
-        <x:v>Follow the travelling spark across eight shot groups. Each new spark starts at maximum value and then decays once per second until hit or moved.</x:v>
+        <x:v>Chaos multiball: chase solid/flashing windows and saucer/shot opportunities.</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Collected groups are removed until one final shot remains for the 10-second Super Jackpot. Collecting the Super completes the mode; missing it or ball end stops it.</x:v>
+        <x:v>Ends when multiball ends, or when Goblin objectives complete if reached first.</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
-        <x:v>Normal sparks start at 250K, or 300K with Bigger, and fall 10K per second to 50K. More Time halves the drain rate. More Jackpots returns the first collected group to the pool for one extra normal jackpot. Shot Assist makes the first spark last 8 seconds.</x:v>
+        <x:v>Chaos multiball; windows alternate between solid/flashing scoring; banks goblin_bonus.</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
-        <x:v>Existing Electro light timing is retained. The Super uses the existing SUPER SURGE LIT countdown plus persistent SUPER SPARK status. Gate routing follows upper shots, and saucers use delayed clearing.</x:v>
+        <x:v>Improved: persistent flashing/solid shot counts and stabilized bank status.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6448,25 +6448,25 @@
         <x:v>Masked Masterminds</x:v>
       </x:c>
       <x:c r="C7" s="31" t="str">
-        <x:v>goblin</x:v>
+        <x:v>doc_ock</x:v>
       </x:c>
       <x:c r="D7" s="31" t="str">
-        <x:v>Green Goblin</x:v>
+        <x:v>Doctor Octopus</x:v>
       </x:c>
       <x:c r="E7" s="31" t="str">
-        <x:v>2-ball MB</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="31" t="str">
-        <x:v>Chaos multiball: chase solid/flashing windows and saucer/shot opportunities.</x:v>
+        <x:v>Use rollovers/left bank to lock arms, then shoot web jackpots while avoiding freed arms.</x:v>
       </x:c>
       <x:c r="G7" s="31" t="str">
-        <x:v>Ends when multiball ends, or when Goblin objectives complete if reached first.</x:v>
+        <x:v>Ends when Doc Ock is defeated by completing required jackpot/breakout objectives; otherwise stops on ball end.</x:v>
       </x:c>
       <x:c r="H7" s="31" t="str">
-        <x:v>Chaos multiball; windows alternate between solid/flashing scoring; banks goblin_bonus.</x:v>
+        <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpots; spinner boosts multiplier.</x:v>
       </x:c>
       <x:c r="I7" s="31" t="str">
-        <x:v>Improved: persistent flashing/solid shot counts and stabilized bank status.</x:v>
+        <x:v>Improved: persistent arm-lock, web-jackpot, and breakout progress.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -6477,25 +6477,25 @@
         <x:v>Masked Masterminds</x:v>
       </x:c>
       <x:c r="C8" s="31" t="str">
-        <x:v>doc_ock</x:v>
+        <x:v>mysterio</x:v>
       </x:c>
       <x:c r="D8" s="31" t="str">
-        <x:v>Doctor Octopus</x:v>
+        <x:v>Mysterio</x:v>
       </x:c>
       <x:c r="E8" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F8" s="31" t="str">
-        <x:v>Use rollovers/left bank to lock arms, then shoot web jackpots while avoiding freed arms.</x:v>
+        <x:v>Use clues to identify the hidden Super while wrong shots reduce value.</x:v>
       </x:c>
       <x:c r="G8" s="31" t="str">
-        <x:v>Ends when Doc Ock is defeated by completing required jackpot/breakout objectives; otherwise stops on ball end.</x:v>
+        <x:v>Ends when the hidden Super/clue sequence is solved; otherwise stops on ball end.</x:v>
       </x:c>
       <x:c r="H8" s="31" t="str">
-        <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpots; spinner boosts multiplier.</x:v>
+        <x:v>Hidden Super/clue mode; wrong shots score smaller and reduce value; clues narrow the target.</x:v>
       </x:c>
       <x:c r="I8" s="31" t="str">
-        <x:v>Improved: persistent arm-lock, web-jackpot, and breakout progress.</x:v>
+        <x:v>Improved: persistent remaining-shot count and current Super value.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6506,25 +6506,25 @@
         <x:v>Masked Masterminds</x:v>
       </x:c>
       <x:c r="C9" s="31" t="str">
-        <x:v>mysterio</x:v>
+        <x:v>scorpion</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
-        <x:v>Mysterio</x:v>
+        <x:v>Scorpion</x:v>
       </x:c>
       <x:c r="E9" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="31" t="str">
-        <x:v>Use clues to identify the hidden Super while wrong shots reduce value.</x:v>
+        <x:v>Spinner builds Venom; upper exits stage timed drop-bank attack shots.</x:v>
       </x:c>
       <x:c r="G9" s="31" t="str">
-        <x:v>Ends when the hidden Super/clue sequence is solved; otherwise stops on ball end.</x:v>
+        <x:v>Ends when the staged Scorpion attacks are completed/resolved; otherwise stops on ball end.</x:v>
       </x:c>
       <x:c r="H9" s="31" t="str">
-        <x:v>Hidden Super/clue mode; wrong shots score smaller and reduce value; clues narrow the target.</x:v>
+        <x:v>Spinner builds Venom; upper exit stages timed drop-bank attack shots.</x:v>
       </x:c>
       <x:c r="I9" s="31" t="str">
-        <x:v>Improved: persistent remaining-shot count and current Super value.</x:v>
+        <x:v>Improved: persistent Venom build, attempt count, exit choice, and staged target status.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6535,25 +6535,25 @@
         <x:v>Masked Masterminds</x:v>
       </x:c>
       <x:c r="C10" s="31" t="str">
-        <x:v>scorpion</x:v>
+        <x:v>lizard</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
-        <x:v>Scorpion</x:v>
+        <x:v>Lizard</x:v>
       </x:c>
       <x:c r="E10" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="31" t="str">
-        <x:v>Spinner builds Venom; upper exits stage timed drop-bank attack shots.</x:v>
+        <x:v>Hit STAR to create serum, then deliver it to the required web shot before value drains.</x:v>
       </x:c>
       <x:c r="G10" s="31" t="str">
-        <x:v>Ends when the staged Scorpion attacks are completed/resolved; otherwise stops on ball end.</x:v>
+        <x:v>Ends when serum deliveries are completed; otherwise stops on ball end.</x:v>
       </x:c>
       <x:c r="H10" s="31" t="str">
-        <x:v>Spinner builds Venom; upper exit stages timed drop-bank attack shots.</x:v>
+        <x:v>STAR creates serum; web shots deliver it. Case files add bigger value, slower decay, follow-up jackpots, one serum-save, and first-delivery flexibility.</x:v>
       </x:c>
       <x:c r="I10" s="31" t="str">
-        <x:v>Improved: persistent Venom build, attempt count, exit choice, and staged target status.</x:v>
+        <x:v>Improved: live serum objective/delivery progress between countdowns.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6889,19 +6889,19 @@
         <x:v>Harley Clivendon</x:v>
       </x:c>
       <x:c r="E22" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>2-ball MB</x:v>
       </x:c>
       <x:c r="F22" s="31" t="str">
-        <x:v>Placeholder framework for hypnosis / reveal with hidden-shot control, using Spinner, targets, and changing shots.</x:v>
+        <x:v>A saucer holds one ball while the player lights independent areas around the playfield. Lighting enough areas qualifies a VUK jackpot.</x:v>
       </x:c>
       <x:c r="G22" s="31" t="str">
-        <x:v>Ends when goals completed / ball end.</x:v>
+        <x:v>Continues through multiball and ends when its objectives are completed, multiball ends, or the ball ends.</x:v>
       </x:c>
       <x:c r="H22" s="31" t="str">
-        <x:v>Idol and scheme jackpots. Shot confusion / reveal windows.</x:v>
+        <x:v>Custom area-control multiball. Jackpot value is based on lit-area progress; collecting at the VUK releases the held ball.</x:v>
       </x:c>
       <x:c r="I22" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented; needs on-machine playtest and presentation polish.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -6970,7 +6970,7 @@
         <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C25" s="31" t="str">
-        <x:v>metal_eating_monster</x:v>
+        <x:v>metal_eating_robot</x:v>
       </x:c>
       <x:c r="D25" s="31" t="str">
         <x:v>Metal-Eating Monster</x:v>
@@ -6979,16 +6979,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F25" s="31" t="str">
-        <x:v>Placeholder framework for area consumption with restore disabled areas, using Whole playfield and river finish.</x:v>
+        <x:v>One of eight safe zones is attacked every 5 seconds. Each attacked zone flickers and runs its own 12-second destruction timer; hitting any switch in that zone saves it.</x:v>
       </x:c>
       <x:c r="G25" s="31" t="str">
-        <x:v>Ends when robot stopped / ball end.</x:v>
+        <x:v>Win after at least four zones are saved and all attacks already in progress are resolved. Lose immediately when three zones are destroyed.</x:v>
       </x:c>
       <x:c r="H25" s="31" t="str">
-        <x:v>Destruction jackpots. Shrinking safe playfield.</x:v>
+        <x:v>Saving a zone scores 250K and resets the next-attack delay to 2 seconds. More Time gives 16-second zone timers; Bigger gives 400K saves; More Jackpots relights each saved zone once for half value; Safety Net is the standard ball save; Shot Assist automatically saves the first zone that reaches 2 seconds.</x:v>
       </x:c>
       <x:c r="I25" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented with eight physical zone groups and native-lens attack/save lighting; needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -7008,16 +7008,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F26" s="31" t="str">
-        <x:v>Placeholder framework for music / sequence with pitch and ransom build, using Spinner plus ordered shots.</x:v>
+        <x:v>Watch a one-, two-, then three-note light-and-violin pattern using Left Web, Left Bank rubber, Center Web, and Right Bank rubber. Repeat each pattern in order.</x:v>
       </x:c>
       <x:c r="G26" s="31" t="str">
-        <x:v>Ends when violin silenced / ball end.</x:v>
+        <x:v>Completes after Round 3, or Round 4 with More Jackpots. Any wrong note ends the mode unless the one-use Shot Assist awards the expected note.</x:v>
       </x:c>
       <x:c r="H26" s="31" t="str">
-        <x:v>Sound-wave jackpots. Sequence and timer pressure.</x:v>
+        <x:v>Patterns flash one note at a time for 2 seconds, then all pending notes remain solid. The pattern repeats after 14 seconds, or 8 with More Time. Correct-note scoring is 100K; 200K/300K; 400K/500K/600K; and 700K/800K/900K/1M in the optional fourth round. Bigger adds 100K to every note; Safety Net is the standard ball save.</x:v>
       </x:c>
       <x:c r="I26" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented with fixed note events play_note_1 through play_note_4 and play_bad_note, temporary existing-SFX mappings, GI 60F060, and forced-down drop banks.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -7327,16 +7327,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F37" s="31" t="str">
-        <x:v>Placeholder framework for containment / spreading hazard with banked bonus, using Whole playfield / containment shots.</x:v>
+        <x:v>Manage a 0-4 Blotto Meter that starts at 3 and rises every 2 seconds. Spinner hits reduce it and pause growth for 2 seconds.</x:v>
       </x:c>
       <x:c r="G37" s="31" t="str">
-        <x:v>Ends when goals completed / ball end.</x:v>
+        <x:v>Whenever the meter fills, a clean area becomes Blotto'd. Hit any switch in an infected area to clear it. Defeat Clive when no areas are infected and the meter is 0.</x:v>
       </x:c>
       <x:c r="H37" s="31" t="str">
-        <x:v>blotto_bonus bank. Blotto spreads and changes shape.</x:v>
+        <x:v>Approved design only; exact area map, scoring, timers, and case-file effects remain open.</x:v>
       </x:c>
       <x:c r="I37" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Generic placeholder code remains; short design notes added.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -7704,16 +7704,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F50" s="31" t="str">
-        <x:v>Saucers open gate; upper entrance starts a limited-flip roof attempt on the 3 upper targets.</x:v>
+        <x:v>Temporary generic hit-count implementation pending a distinct Skymaster redesign.</x:v>
       </x:c>
       <x:c r="G50" s="31" t="str">
-        <x:v>Ends after 3 roof clears, or stops on ball end.</x:v>
+        <x:v>Ends when the temporary placeholder goal is reached or on ball end.</x:v>
       </x:c>
       <x:c r="H50" s="31" t="str">
-        <x:v>Rooftop Swarm: saucers open gate; upper entrance starts limited-flip roof attempt; first two targets are JPs and third is Super boosted by remaining flips.</x:v>
+        <x:v>The current Python file explicitly labels this a temporary placeholder; the former rooftop limited-flip identity should not be documented as final.</x:v>
       </x:c>
       <x:c r="I50" s="31" t="str">
-        <x:v>Improved: persistent gate state, roof targets, flips, and roof-clear progress.</x:v>
+        <x:v>Temporary placeholder; major design and implementation work required.</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -7878,16 +7878,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F56" s="31" t="str">
-        <x:v>Placeholder framework for aerial invasion with whole-playfield assault, using Air-raid, paralysis, and upper shots.</x:v>
+        <x:v>Shoot a saucer to open roof access. Entering the upper playfield starts a 10-flip Sky Harbor assault on the three unique upper targets.</x:v>
       </x:c>
       <x:c r="G56" s="31" t="str">
-        <x:v>Ends when goals completed / ball end.</x:v>
+        <x:v>Completes when all three unique roof targets are hit and the Super is awarded; otherwise ends when the flip resource is exhausted or on ball end.</x:v>
       </x:c>
       <x:c r="H56" s="31" t="str">
-        <x:v>Sky Harbor jackpots. Escalating invasion pressure.</x:v>
+        <x:v>First two unique targets award jackpots; the third awards a Super boosted by remaining flips. Repeated completed targets score 250K; case-file helpers are supported.</x:v>
       </x:c>
       <x:c r="I56" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented; needs playtest and presentation polish.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8471,10 +8471,10 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="31" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="31" t="str">
-        <x:v>Masked Masterminds</x:v>
+        <x:v>Classic Rogues</x:v>
       </x:c>
       <x:c r="C3" s="31" t="str">
         <x:v>Green Goblin</x:v>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5bcfb0e819454765"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Ra8ad3347d55242a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R953a369e5a9c4c10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rb24acf4a88fd40bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R780a5f75bcc5482a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rcdcdb7bc95424418"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rb920285ad83f422b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R5431a94423ac46e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rf00e596749264f13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rf439ed759efa438c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R7cabd38e08c04be6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R16545caf0f5d45cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R7f96e0747418451d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rd17e314a0f1a485f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R11bf06edac054298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R0292b6f28d7d40a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R821590f75ddd4a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R534a2e6bdef84080"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rab0d5af679524bfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rcaaa7336794b4737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R5811ccbaf9994751"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rcfe5970c980a40f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R94dfc1f74f9d414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rd887ada7f9154491"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2234,31 +2234,31 @@
         <x:v>The Snowman</x:v>
       </x:c>
       <x:c r="E40" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="F40" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G40" s="31" t="str">
-        <x:v>Endurance / melt</x:v>
+        <x:v>Timed two-shot combo</x:v>
       </x:c>
       <x:c r="H40" s="31" t="str">
-        <x:v>Area control</x:v>
+        <x:v>Spinner bonus window</x:v>
       </x:c>
       <x:c r="I40" s="31" t="str">
-        <x:v>Pops / lanes / shots</x:v>
+        <x:v>Left web + center web + spinner</x:v>
       </x:c>
       <x:c r="J40" s="31" t="str">
-        <x:v>Snowballing value</x:v>
+        <x:v>100K/250K setup and unlimited 100K zaps</x:v>
       </x:c>
       <x:c r="K40" s="31" t="str">
-        <x:v>Escalating snowfall</x:v>
+        <x:v>16-second connection window</x:v>
       </x:c>
       <x:c r="L40" s="31" t="str">
-        <x:v>Goals or timer / ball end</x:v>
+        <x:v>8-second spinner window / ball end</x:v>
       </x:c>
       <x:c r="M40" s="31" t="str">
-        <x:v>Build heat or drain electricity before the Snowman grows.</x:v>
+        <x:v>Compact single-phase combo mode; distinct from Chapter 8 meter management, rooftop flash building, and multiball.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2275,31 +2275,31 @@
         <x:v>The Plutonians</x:v>
       </x:c>
       <x:c r="E41" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="F41" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G41" s="31" t="str">
-        <x:v>Ice rescue / repair</x:v>
+        <x:v>Freeze/thaw area control</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>Survival / recovery</x:v>
+        <x:v>Temporary shutdown window</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
-        <x:v>Whole playfield</x:v>
+        <x:v>Six zones + upper targets</x:v>
       </x:c>
       <x:c r="J41" s="31" t="str">
-        <x:v>Frozen jackpots / repair value</x:v>
+        <x:v>Thaw all six zones simultaneously</x:v>
       </x:c>
       <x:c r="K41" s="31" t="str">
-        <x:v>Frozen shots and escape repairs</x:v>
+        <x:v>One thawed zone refreezes every 12 seconds</x:v>
       </x:c>
       <x:c r="L41" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>All six thawed / ball end</x:v>
       </x:c>
       <x:c r="M41" s="31" t="str">
-        <x:v>Canonical identity replaces Ice Monster; story should end by helping them return home.</x:v>
+        <x:v>Reversible six-zone control mode; upper playfield disables the threat rather than serving as the main scoring objective.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4937,10 +4937,10 @@
         <x:v>The Snowman</x:v>
       </x:c>
       <x:c r="G40" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="H40" s="31" t="str">
-        <x:v>Snow/weather slot. Living snow creature grows with snowfall and is defeated b...</x:v>
+        <x:v>Hit either web target for 100K, then hit the opposite web target within 16 seconds for 250K to connect the copper wire. The first spinner spin defeats the Snowman, scores 100K, and starts an 8-second unlimited 100K-per-spin bonus window.</x:v>
       </x:c>
       <x:c r="I40" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4969,10 +4969,10 @@
         <x:v>The Plutonians</x:v>
       </x:c>
       <x:c r="G41" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>Former Ice Monster placeholder retained under the canonical Plutonians identi...</x:v>
+        <x:v>All six zones start frozen and the roof-access gate starts open. Any upper target disables the freeze ray for 12 seconds so zones can be thawed. Once the ray reactivates, one thawed zone freezes every 12 seconds. Thaw all six simultaneously to repair the Space Warp Control.</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -7414,16 +7414,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F40" s="31" t="str">
-        <x:v>Placeholder framework for endurance / melt with area control, using Pops / lanes / shots.</x:v>
+        <x:v>Hit either web target, then hit the opposite web target within 16 seconds to complete the copper-wire connection.</x:v>
       </x:c>
       <x:c r="G40" s="31" t="str">
-        <x:v>Ends when goals or timer / ball end.</x:v>
+        <x:v>The first spinner spin defeats the Snowman and starts an 8-second scoring window; the mode ends when that window expires.</x:v>
       </x:c>
       <x:c r="H40" s="31" t="str">
-        <x:v>Snowballing value. Escalating snowfall.</x:v>
+        <x:v>First web scores 100K, second web scores 250K, and every spinner spin scores 100K. Zaps are unlimited during the 8-second bonus window.</x:v>
       </x:c>
       <x:c r="I40" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Generic placeholder code remains; approved design notes added.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -7443,16 +7443,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F41" s="31" t="str">
-        <x:v>Placeholder framework for ice rescue / repair with survival / recovery, using Whole playfield.</x:v>
+        <x:v>All six zones begin frozen. The gate starts open, and any upper target disables the freeze ray for 12 seconds so zones can be thawed.</x:v>
       </x:c>
       <x:c r="G41" s="31" t="str">
-        <x:v>Ends when goals completed / ball end.</x:v>
+        <x:v>Thaw all six zones at the same time to repair the Space Warp Control and send the Plutonians home.</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>Frozen jackpots / repair value. Frozen shots and escape repairs.</x:v>
+        <x:v>Whenever the freeze ray is active, one thawed zone freezes again every 12 seconds. Upper-target hits create the temporary thawing window.</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Generic placeholder code remains; approved design notes added.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R7f96e0747418451d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rd17e314a0f1a485f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R11bf06edac054298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R0292b6f28d7d40a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R821590f75ddd4a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R534a2e6bdef84080"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rab0d5af679524bfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rcaaa7336794b4737"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R5811ccbaf9994751"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rcfe5970c980a40f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R94dfc1f74f9d414d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rd887ada7f9154491"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd4ee69aa57b649bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rfa1b174e5d604aca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R5a0e67be978b4df5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R405479383c3a4497"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R36ab54b8902141d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rcf494a83fd334c58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Re8b3b78c4b244033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R5195aab1fe7a4f19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R626411b7f12445c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra8d8867feeb24988"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rb36f1d6c64bf4bdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rb839177efb374fec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2275,31 +2275,31 @@
         <x:v>The Plutonians</x:v>
       </x:c>
       <x:c r="E41" s="31" t="str">
-        <x:v>Placeholder / design approved</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F41" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G41" s="31" t="str">
-        <x:v>Freeze/thaw area control</x:v>
+        <x:v>Reversible area control</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>Temporary shutdown window</x:v>
+        <x:v>Freeze Ray blocking</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
-        <x:v>Six zones + upper targets</x:v>
+        <x:v>Six Super Swami areas + upper targets</x:v>
       </x:c>
       <x:c r="J41" s="31" t="str">
-        <x:v>Thaw all six zones simultaneously</x:v>
+        <x:v>100K thaws; 50K targets; 1M completion</x:v>
       </x:c>
       <x:c r="K41" s="31" t="str">
-        <x:v>One thawed zone refreezes every 12 seconds</x:v>
+        <x:v>12s firing cycle; 20s/25s block</x:v>
       </x:c>
       <x:c r="L41" s="31" t="str">
         <x:v>All six thawed / ball end</x:v>
       </x:c>
       <x:c r="M41" s="31" t="str">
-        <x:v>Reversible six-zone control mode; upper playfield disables the threat rather than serving as the main scoring objective.</x:v>
+        <x:v>Areas can thaw while the ray is active; upper-target timing prevents random refreezes and More Jackpots rewards repeat roof entrances.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -3522,10 +3522,10 @@
         <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="B9" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="31" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
         <x:v>Nature Strikes Back</x:v>
@@ -4873,10 +4873,10 @@
         <x:v>Doctor Zapp</x:v>
       </x:c>
       <x:c r="G38" s="31" t="str">
-        <x:v>Placeholder / design approved</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H38" s="31" t="str">
-        <x:v>Knock down one target from each lower bank to open roof access. Upper spinner camera flashes defeat Zapp at 25 flashes; each lit upper helper target adds +1 flash per spin. Drops score 100K, helpers 50K, flashes 50K.</x:v>
+        <x:v>One hit from each lower bank opens rooftop access for the rest of the mode. Spinner spins score 50K and add 1 camera flash plus +1 for each unique upper target collected. Upper targets score 50K and permanently improve flashes per spin. Reach 25 flashes to defeat Zapp. Bigger raises bank hits to 150K and targets/spins to 75K. Safety Net gives 10s save at start; More Time gives a 15s save on first roof entry; Shot Assist awards and scores another upper target; More Jackpots adds a 10s points-only spinner window before the 6s upper-flipper lockout.</x:v>
       </x:c>
       <x:c r="I38" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4937,10 +4937,10 @@
         <x:v>The Snowman</x:v>
       </x:c>
       <x:c r="G40" s="31" t="str">
-        <x:v>Placeholder / design approved</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H40" s="31" t="str">
-        <x:v>Hit either web target for 100K, then hit the opposite web target within 16 seconds for 250K to connect the copper wire. The first spinner spin defeats the Snowman, scores 100K, and starts an 8-second unlimited 100K-per-spin bonus window.</x:v>
+        <x:v>Either web starts for 100K (150K Bigger). The opposite web must be hit within 16 seconds (20 with More Time) for 250K (350K Bigger). Re-hitting the starting web scores 25K and resets the timer; with Shot Assist it completes the wire. The first spinner spin defeats Snowman and starts a 10-second bonus-spin window (16 with More Time). Spins score 100K or 150K with Bigger; More Jackpots adds 25K to each next spin. Safety Net starts a 10-second save when the spinner lights.</x:v>
       </x:c>
       <x:c r="I40" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4969,10 +4969,10 @@
         <x:v>The Plutonians</x:v>
       </x:c>
       <x:c r="G41" s="31" t="str">
-        <x:v>Placeholder / design approved</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>All six zones start frozen and the roof-access gate starts open. Any upper target disables the freeze ray for 12 seconds so zones can be thawed. Once the ray reactivates, one thawed zone freezes every 12 seconds. Thaw all six simultaneously to repair the Space Warp Control.</x:v>
+        <x:v>All six Super Swami areas start frozen; one hit thaws a frozen area at any time for 100K. The active Freeze Ray fires every 12 seconds and randomly refreezes one thawed area. Any upper target scores 50K and blocks/resets the ray for 20 seconds (25 with More Time). Thaw all six simultaneously for a 1M Space Warp Control award and a 2-second normal-scoring victory hold. Bigger raises thaws to 150K, targets to 75K and completion to 1.5M. Safety Net gives a 10s save; Shot Assist spots and scores a second first thaw; More Jackpots gives one 500K upper-target jackpot per roof entrance.</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -7443,16 +7443,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F41" s="31" t="str">
-        <x:v>All six zones begin frozen. The gate starts open, and any upper target disables the freeze ray for 12 seconds so zones can be thawed.</x:v>
+        <x:v>All six established bottom/middle/upper left/right areas begin frozen. One qualifying switch hit thaws a frozen area at any time. Upper targets block or reset the Freeze Ray.</x:v>
       </x:c>
       <x:c r="G41" s="31" t="str">
-        <x:v>Thaw all six zones at the same time to repair the Space Warp Control and send the Plutonians home.</x:v>
+        <x:v>The active ray randomly refreezes one thawed area every 12 seconds. Block duration is 20 seconds, or 25 with More Time. Thaw all six simultaneously to stop the ray and repair the Space Warp Control.</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>Whenever the freeze ray is active, one thawed zone freezes again every 12 seconds. Upper-target hits create the temporary thawing window.</x:v>
+        <x:v>Thaws 100K, upper targets 50K, completion 1M. Bigger raises these to 150K/75K/1.5M. More Jackpots awards 500K/750K once per upper entrance.</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
-        <x:v>Generic placeholder code remains; approved design notes added.</x:v>
+        <x:v>Implemented at medium complexity with visible FREEZE IN / FREEZE BLOCKED timer, blue frozen-area indicators, yellow thawed-area indicators, one-use Shot Assist, and two-second victory hold.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd4ee69aa57b649bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rfa1b174e5d604aca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R5a0e67be978b4df5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R405479383c3a4497"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R36ab54b8902141d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rcf494a83fd334c58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Re8b3b78c4b244033"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R5195aab1fe7a4f19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R626411b7f12445c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra8d8867feeb24988"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rb36f1d6c64bf4bdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rb839177efb374fec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8c9ac1bae96f467e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Re0b7035d0de14af7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rf338a4d073684f3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R15fec5f0beed4256"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rbc105a3589544a1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rc2fdabc887494dc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rf6b8b5922d614b4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rb0d84d2113f14f65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R96f2dc95b5194bd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R1cc642fb0dce4502"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R8c35f1000fdb4c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R7cadfc90ee2b4902"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2193,31 +2193,31 @@
         <x:v>Voltan and Boomer</x:v>
       </x:c>
       <x:c r="E39" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F39" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
-        <x:v>Storm timing / robbery</x:v>
+        <x:v>Repeating two-ball multiball</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Thunder windows</x:v>
+        <x:v>Target / capture / VUK Super loop</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
-        <x:v>Storm shots + target groups</x:v>
+        <x:v>Random lower target + any saucer + VUK</x:v>
       </x:c>
       <x:c r="J39" s="31" t="str">
-        <x:v>Thunder/robbery jackpots</x:v>
+        <x:v>100K target; 100K capture; 500K Super</x:v>
       </x:c>
       <x:c r="K39" s="31" t="str">
-        <x:v>Short storm windows</x:v>
+        <x:v>15s opening save; 20s later Supers</x:v>
       </x:c>
       <x:c r="L39" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>Multiball end</x:v>
       </x:c>
       <x:c r="M39" s="31" t="str">
-        <x:v>Thunder Rumble pair kept together; full design pending.</x:v>
+        <x:v>First saucer remains held; a second saucer ball ejects after one second. Gate and staggered releases control each repeat.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2275,31 +2275,31 @@
         <x:v>The Plutonians</x:v>
       </x:c>
       <x:c r="E41" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="F41" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G41" s="31" t="str">
-        <x:v>Reversible area control</x:v>
+        <x:v>Freeze/thaw area control</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>Freeze Ray blocking</x:v>
+        <x:v>Temporary shutdown window</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
-        <x:v>Six Super Swami areas + upper targets</x:v>
+        <x:v>Six zones + upper targets</x:v>
       </x:c>
       <x:c r="J41" s="31" t="str">
-        <x:v>100K thaws; 50K targets; 1M completion</x:v>
+        <x:v>Thaw all six zones simultaneously</x:v>
       </x:c>
       <x:c r="K41" s="31" t="str">
-        <x:v>12s firing cycle; 20s/25s block</x:v>
+        <x:v>One thawed zone refreezes every 12 seconds</x:v>
       </x:c>
       <x:c r="L41" s="31" t="str">
         <x:v>All six thawed / ball end</x:v>
       </x:c>
       <x:c r="M41" s="31" t="str">
-        <x:v>Areas can thaw while the ray is active; upper-target timing prevents random refreezes and More Jackpots rewards repeat roof entrances.</x:v>
+        <x:v>Reversible six-zone control mode; upper playfield disables the threat rather than serving as the main scoring objective.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -3522,10 +3522,10 @@
         <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="B9" s="31" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C9" s="31" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
         <x:v>Nature Strikes Back</x:v>
@@ -4841,10 +4841,10 @@
         <x:v>Clive and Blotto</x:v>
       </x:c>
       <x:c r="G37" s="31" t="str">
-        <x:v>Placeholder / design approved</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H37" s="31" t="str">
-        <x:v>Blotto Meter starts at 3/4 and gains 1 every 2 seconds. Spinner hits lower it and pause growth for 2 seconds. When full, one clean area becomes Blotto'd; any hit in that area clears it. Win with no Blotto'd areas and meter at 0.</x:v>
+        <x:v>Blotto Meter starts at 3/4 and grows every 3 seconds (4 with More Time). At meter 4, every growth expiry infects one random clean six-zone area. Either spinner scores 25K, lowers the meter by 1, cancels growth, and starts a 2-second pause; Shot Assist makes the first spin lower it by 2. One hit clears an infected area for 100K (150K Bigger). More Jackpots raises every next clear by 25K to a 500K cap. Win when meter is 0 and no areas are infected; completion awards 1M. Safety Net gives a 10-second save.</x:v>
       </x:c>
       <x:c r="I37" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4905,10 +4905,10 @@
         <x:v>Bolton and Boomer</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
-        <x:v>Placeholder / design approved</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Repeating 2-ball multiball loop: hit a random lit target, lock one ball in any saucer, then shoot the VUK Super. First Super is untimed; later Supers run 20 seconds and reset the loop if missed.</x:v>
+        <x:v>Two-ball multiball loop: hit a random lit target for 100K, capture the first ball in any saucer for 100K, then shoot the VUK for a 500K Super. First Super is untimed; later Supers last 20 seconds. Gate closes on collect or timeout. VUK kicks after 2 seconds and held saucer 2 seconds later. Bigger is 150K/150K/750K; More Time gives 30s; Safety Net gives 25s opening save; Shot Assist spots the first timed Super at 10 seconds; More Jackpots grows Supers by 100K to 1.5M. Mode ends when multiball ends.</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -7385,16 +7385,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F39" s="31" t="str">
-        <x:v>Placeholder framework for storm timing / robbery with thunder windows, using Storm shots + target groups.</x:v>
+        <x:v>Start a two-ball multiball. Hit one random lit target, then capture the first ball in any saucer. The gate opens and the VUK lights for the Super.</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
-        <x:v>Ends when goals completed / ball end.</x:v>
+        <x:v>First Super is untimed. Later Supers use a 20-second timer. On collect, the VUK kicks after two seconds and the held saucer two seconds later. On timeout, release the saucer after two seconds and restart. Mode ends when multiball ends.</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Thunder/robbery jackpots. Short storm windows.</x:v>
+        <x:v>Target 100K, saucer capture 100K, Super 500K. Bigger raises these to 150K/150K/750K. More Jackpots adds 100K to each next Super, capped at 1.5M.</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented at medium complexity. Safety Net extends the opening save to 25 seconds, More Time gives 30-second timed Supers, and Shot Assist auto-awards the first timed Super at 10 seconds.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -7443,16 +7443,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F41" s="31" t="str">
-        <x:v>All six established bottom/middle/upper left/right areas begin frozen. One qualifying switch hit thaws a frozen area at any time. Upper targets block or reset the Freeze Ray.</x:v>
+        <x:v>All six zones begin frozen. The gate starts open, and any upper target disables the freeze ray for 12 seconds so zones can be thawed.</x:v>
       </x:c>
       <x:c r="G41" s="31" t="str">
-        <x:v>The active ray randomly refreezes one thawed area every 12 seconds. Block duration is 20 seconds, or 25 with More Time. Thaw all six simultaneously to stop the ray and repair the Space Warp Control.</x:v>
+        <x:v>Thaw all six zones at the same time to repair the Space Warp Control and send the Plutonians home.</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>Thaws 100K, upper targets 50K, completion 1M. Bigger raises these to 150K/75K/1.5M. More Jackpots awards 500K/750K once per upper entrance.</x:v>
+        <x:v>Whenever the freeze ray is active, one thawed zone freezes again every 12 seconds. Upper-target hits create the temporary thawing window.</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
-        <x:v>Implemented at medium complexity with visible FREEZE IN / FREEZE BLOCKED timer, blue frozen-area indicators, yellow thawed-area indicators, one-use Shot Assist, and two-second victory hold.</x:v>
+        <x:v>Generic placeholder code remains; approved design notes added.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8c9ac1bae96f467e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Re0b7035d0de14af7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rf338a4d073684f3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R15fec5f0beed4256"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rbc105a3589544a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rc2fdabc887494dc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rf6b8b5922d614b4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rb0d84d2113f14f65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R96f2dc95b5194bd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R1cc642fb0dce4502"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R8c35f1000fdb4c2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R7cadfc90ee2b4902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rfc0f6f02acfe4636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R84a5705ca1dc4315"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R0e7b93b814424ee7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rf0c8de35033244cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rcde15e560cf14fc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R0379c40e7e5d439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R1d6b9f17a06f4c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rbdee35dda6724e90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rdd11dce3560741c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R131961e5bbfc42e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rd9a632052a0f4d4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R2b12cd9566ee4410"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -542,7 +542,7 @@
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Danger Lurks is now complete with five substantive villain modes: Harley Clivendon, The Conquistador, Spider-Slayer, Metal-Eating Monster, and Fiddler. Across all chapters, 39 of 55 regular villain modes have substantive implementations; 16 still need major rules work.</x:v>
+        <x:v>Danger Lurks is complete with five substantive villain modes. Elemental Chaos now has Clive and Blotto implemented, with Doctor Zapp, Bolton and Boomer, The Snowman, and The Plutonians designed but still awaiting implementation. Across all chapters, 40 of 55 regular villain modes have substantive implementations.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -2111,7 +2111,7 @@
         <x:v>Clive and Blotto</x:v>
       </x:c>
       <x:c r="E37" s="31" t="str">
-        <x:v>Placeholder / design approved</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F37" s="31" t="str">
         <x:v>1</x:v>
@@ -2123,19 +2123,19 @@
         <x:v>Spreading area cleanup</x:v>
       </x:c>
       <x:c r="I37" s="31" t="str">
-        <x:v>Spinner + whole-playfield areas</x:v>
+        <x:v>Two spinners + six whole-playfield areas</x:v>
       </x:c>
       <x:c r="J37" s="31" t="str">
-        <x:v>Clear infected areas while draining meter</x:v>
+        <x:v>25K meter drains, 150K clears, 1M final</x:v>
       </x:c>
       <x:c r="K37" s="31" t="str">
-        <x:v>Meter rises every 2 seconds</x:v>
+        <x:v>Meter rises every 2s; six infected areas is failure</x:v>
       </x:c>
       <x:c r="L37" s="31" t="str">
-        <x:v>No infected areas and meter 0 / ball end</x:v>
+        <x:v>Meter 0 and no infected areas / six infected / ball end</x:v>
       </x:c>
       <x:c r="M37" s="31" t="str">
-        <x:v>Distinct tug-of-war mode; not another timed rescue or simple spinner build.</x:v>
+        <x:v>Chapter 8 tug-of-war mode. Unlike Metal Monster's timed rescues, infection persists until cleared while spinner control manages the global pressure meter.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2193,31 +2193,31 @@
         <x:v>Voltan and Boomer</x:v>
       </x:c>
       <x:c r="E39" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="F39" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
-        <x:v>Repeating two-ball multiball</x:v>
+        <x:v>Storm timing / robbery</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Target / capture / VUK Super loop</x:v>
+        <x:v>Thunder windows</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
-        <x:v>Random lower target + any saucer + VUK</x:v>
+        <x:v>Storm shots + target groups</x:v>
       </x:c>
       <x:c r="J39" s="31" t="str">
-        <x:v>100K target; 100K capture; 500K Super</x:v>
+        <x:v>Thunder/robbery jackpots</x:v>
       </x:c>
       <x:c r="K39" s="31" t="str">
-        <x:v>15s opening save; 20s later Supers</x:v>
+        <x:v>Short storm windows</x:v>
       </x:c>
       <x:c r="L39" s="31" t="str">
-        <x:v>Multiball end</x:v>
+        <x:v>Goals completed / ball end</x:v>
       </x:c>
       <x:c r="M39" s="31" t="str">
-        <x:v>First saucer remains held; a second saucer ball ejects after one second. Gate and staggered releases control each repeat.</x:v>
+        <x:v>Thunder Rumble pair kept together; full design pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3522,10 +3522,10 @@
         <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="B9" s="31" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
         <x:v>Nature Strikes Back</x:v>
@@ -4844,7 +4844,7 @@
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H37" s="31" t="str">
-        <x:v>Blotto Meter starts at 3/4 and grows every 3 seconds (4 with More Time). At meter 4, every growth expiry infects one random clean six-zone area. Either spinner scores 25K, lowers the meter by 1, cancels growth, and starts a 2-second pause; Shot Assist makes the first spin lower it by 2. One hit clears an infected area for 100K (150K Bigger). More Jackpots raises every next clear by 25K to a 500K cap. Win when meter is 0 and no areas are infected; completion awards 1M. Safety Net gives a 10-second save.</x:v>
+        <x:v>Spirit-Scope Containment: six playfield areas can become infected. The meter starts at 75%, rises 25% every 2 seconds, and resets after infecting a clean area. Either spinner lowers it 25% and pauses growth for 2 seconds. Clear infected areas and reach 0% with none infected.</x:v>
       </x:c>
       <x:c r="I37" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4873,10 +4873,10 @@
         <x:v>Doctor Zapp</x:v>
       </x:c>
       <x:c r="G38" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="H38" s="31" t="str">
-        <x:v>One hit from each lower bank opens rooftop access for the rest of the mode. Spinner spins score 50K and add 1 camera flash plus +1 for each unique upper target collected. Upper targets score 50K and permanently improve flashes per spin. Reach 25 flashes to defeat Zapp. Bigger raises bank hits to 150K and targets/spins to 75K. Safety Net gives 10s save at start; More Time gives a 15s save on first roof entry; Shot Assist awards and scores another upper target; More Jackpots adds a 10s points-only spinner window before the 6s upper-flipper lockout.</x:v>
+        <x:v>Knock down one target from each lower bank to open roof access. Upper spinner camera flashes defeat Zapp at 25 flashes; each lit upper helper target adds +1 flash per spin. Drops score 100K, helpers 50K, flashes 50K.</x:v>
       </x:c>
       <x:c r="I38" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4905,10 +4905,10 @@
         <x:v>Bolton and Boomer</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Two-ball multiball loop: hit a random lit target for 100K, capture the first ball in any saucer for 100K, then shoot the VUK for a 500K Super. First Super is untimed; later Supers last 20 seconds. Gate closes on collect or timeout. VUK kicks after 2 seconds and held saucer 2 seconds later. Bigger is 150K/150K/750K; More Time gives 30s; Safety Net gives 25s opening save; Shot Assist spots the first timed Super at 10 seconds; More Jackpots grows Supers by 100K to 1.5M. Mode ends when multiball ends.</x:v>
+        <x:v>Repeating 2-ball multiball loop: hit a random lit target, lock one ball in any saucer, then shoot the VUK Super. First Super is untimed; later Supers run 20 seconds and reset the loop if missed.</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4937,10 +4937,10 @@
         <x:v>The Snowman</x:v>
       </x:c>
       <x:c r="G40" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="H40" s="31" t="str">
-        <x:v>Either web starts for 100K (150K Bigger). The opposite web must be hit within 16 seconds (20 with More Time) for 250K (350K Bigger). Re-hitting the starting web scores 25K and resets the timer; with Shot Assist it completes the wire. The first spinner spin defeats Snowman and starts a 10-second bonus-spin window (16 with More Time). Spins score 100K or 150K with Bigger; More Jackpots adds 25K to each next spin. Safety Net starts a 10-second save when the spinner lights.</x:v>
+        <x:v>Hit either web target for 100K, then hit the opposite web target within 16 seconds for 250K to connect the copper wire. The first spinner spin defeats the Snowman, scores 100K, and starts an 8-second unlimited 100K-per-spin bonus window.</x:v>
       </x:c>
       <x:c r="I40" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4969,10 +4969,10 @@
         <x:v>The Plutonians</x:v>
       </x:c>
       <x:c r="G41" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Placeholder / design approved</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>All six Super Swami areas start frozen; one hit thaws a frozen area at any time for 100K. The active Freeze Ray fires every 12 seconds and randomly refreezes one thawed area. Any upper target scores 50K and blocks/resets the ray for 20 seconds (25 with More Time). Thaw all six simultaneously for a 1M Space Warp Control award and a 2-second normal-scoring victory hold. Bigger raises thaws to 150K, targets to 75K and completion to 1.5M. Safety Net gives a 10s save; Shot Assist spots and scores a second first thaw; More Jackpots gives one 500K upper-target jackpot per roof entrance.</x:v>
+        <x:v>All six zones start frozen and the roof-access gate starts open. Any upper target disables the freeze ray for 12 seconds so zones can be thawed. Once the ray reactivates, one thawed zone freezes every 12 seconds. Thaw all six simultaneously to repair the Space Warp Control.</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -5966,7 +5966,7 @@
         <x:v>Clive and Blotto</x:v>
       </x:c>
       <x:c r="D12" s="31" t="str">
-        <x:v>Radiation Specialist duplicate removed; placeholder mechanics and Chapter 8 bonus bank preserved for later Blotto redesign.</x:v>
+        <x:v>Former generic placeholder replaced by the implemented Spirit-Scope Containment meter-and-infected-area mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -7327,16 +7327,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F37" s="31" t="str">
-        <x:v>Manage a 0-4 Blotto Meter that starts at 3 and rises every 2 seconds. Spinner hits reduce it and pause growth for 2 seconds.</x:v>
+        <x:v>The Blotto Meter starts at 75% and rises 25% every 2 seconds. Either spinner lowers it 25%, scores 25K, and pauses growth for 2 seconds. At 100%, one of six clean playfield areas becomes infected.</x:v>
       </x:c>
       <x:c r="G37" s="31" t="str">
-        <x:v>Whenever the meter fills, a clean area becomes Blotto'd. Hit any switch in an infected area to clear it. Defeat Clive when no areas are infected and the meter is 0.</x:v>
+        <x:v>Hit any switch in an infected area to clear it. Win when the meter is 0% and no areas are infected; lose if all six areas are infected simultaneously.</x:v>
       </x:c>
       <x:c r="H37" s="31" t="str">
-        <x:v>Approved design only; exact area map, scoring, timers, and case-file effects remain open.</x:v>
+        <x:v>Area clears score 150K and the final Spirit-Scope Jackpot is 1M. More Time changes growth to 3 seconds; Bigger pays 40K/225K/1.5M; More Jackpots adds one 250K first-clear jackpot per area; Safety Net gives a 10-second ball save; Shot Assist clears a second infected area once.</x:v>
       </x:c>
       <x:c r="I37" s="31" t="str">
-        <x:v>Generic placeholder code remains; short design notes added.</x:v>
+        <x:v>Implemented with the six Super Swami area mappings, purple infected-area GI, meter urgency lighting, shared messages, and summary stats.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -7385,16 +7385,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F39" s="31" t="str">
-        <x:v>Start a two-ball multiball. Hit one random lit target, then capture the first ball in any saucer. The gate opens and the VUK lights for the Super.</x:v>
+        <x:v>Placeholder framework for storm timing / robbery with thunder windows, using Storm shots + target groups.</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
-        <x:v>First Super is untimed. Later Supers use a 20-second timer. On collect, the VUK kicks after two seconds and the held saucer two seconds later. On timeout, release the saucer after two seconds and restart. Mode ends when multiball ends.</x:v>
+        <x:v>Ends when goals completed / ball end.</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Target 100K, saucer capture 100K, Super 500K. Bigger raises these to 150K/150K/750K. More Jackpots adds 100K to each next Super, capped at 1.5M.</x:v>
+        <x:v>Thunder/robbery jackpots. Short storm windows.</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
-        <x:v>Implemented at medium complexity. Safety Net extends the opening save to 25 seconds, More Time gives 30-second timed Supers, and Shot Assist auto-awards the first timed Super at 10 seconds.</x:v>
+        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8c9ac1bae96f467e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Re0b7035d0de14af7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rf338a4d073684f3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R15fec5f0beed4256"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rbc105a3589544a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rc2fdabc887494dc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rf6b8b5922d614b4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rb0d84d2113f14f65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R96f2dc95b5194bd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R1cc642fb0dce4502"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R8c35f1000fdb4c2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R7cadfc90ee2b4902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R65c7a67dc1ae4dba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Read5618c118c4cf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Redb88fac26a6457a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R602ac6bfb19c41e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rd1c28f5961304fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R771a94b657124050"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R838b41ae257c4d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Ra5e2ca0f8e5b45fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R103d509409464d38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Re9c830ca355d4064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R87e7188aa49b4c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Raf904bbde2ec40ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2480,31 +2480,31 @@
         <x:v>Molemen</x:v>
       </x:c>
       <x:c r="E46" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F46" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G46" s="31" t="str">
-        <x:v>Underground invasion</x:v>
+        <x:v>Repeating two-ball multiball</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Area / survival</x:v>
+        <x:v>Three-area saucer jackpot build</x:v>
       </x:c>
       <x:c r="I46" s="31" t="str">
-        <x:v>Drops, tunnels, lower playfield</x:v>
+        <x:v>Left pop + center web + right pop + three saucers</x:v>
       </x:c>
       <x:c r="J46" s="31" t="str">
-        <x:v>Underground jackpots</x:v>
+        <x:v>50K/100K area hits; 250K x balls jackpots</x:v>
       </x:c>
       <x:c r="K46" s="31" t="str">
-        <x:v>Escalating underground pressure</x:v>
+        <x:v>15s opening save; 5s one-ball grace</x:v>
       </x:c>
       <x:c r="L46" s="31" t="str">
-        <x:v>Goals or timer / ball end</x:v>
+        <x:v>One-ball grace expiry / ball end</x:v>
       </x:c>
       <x:c r="M46" s="31" t="str">
-        <x:v>Compact mode name; Mugs Reilly can appear in intro and summaries.</x:v>
+        <x:v>Gate closed throughout; each saucer has one once-per-mode add-a-ball and area progress resets after jackpot.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -3560,10 +3560,10 @@
         <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="B10" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="31" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
         <x:v>Invasion from Everywhere</x:v>
@@ -5129,10 +5129,10 @@
         <x:v>The Molemen</x:v>
       </x:c>
       <x:c r="G46" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Underground-world mode associated with Mugs Reilly and the Molemen. Compact l...</x:v>
+        <x:v>Two-ball multiball with three matched areas: left pop to Saucer 1, center web to Saucer 2, and right pop to Saucer 3. One hit lights that saucer jackpot. Pop areas need 3 hits for their once-per-mode add-a-ball (2 with More Jackpots); center web needs 1. Jackpots score 250K x balls in play, or 300K x balls with Bigger. Pops score 50K/75K and center web 100K/150K. Shot Assist makes the left web always count as center web. Gate stays closed. Mode ends after a 5-second one-ball grace, or 10 seconds with More Time. Opening save is 15 seconds, or 25 with Safety Net.</x:v>
       </x:c>
       <x:c r="I46" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -7588,16 +7588,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F46" s="31" t="str">
-        <x:v>Placeholder framework for underground invasion with area / survival, using Drops, tunnels, lower playfield.</x:v>
+        <x:v>Start a two-ball multiball. Build three matched areas: left pop to Saucer 1, center web to Saucer 2, and right pop to Saucer 3. One hit lights the matching saucer.</x:v>
       </x:c>
       <x:c r="G46" s="31" t="str">
-        <x:v>Ends when goals or timer / ball end.</x:v>
+        <x:v>Collect lit saucer jackpots repeatedly. Pop areas need 3 hits for add-a-ball, or 2 with More Jackpots; center web needs 1. Each saucer can add a ball only once. End after the one-ball grace period.</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Underground jackpots. Escalating underground pressure.</x:v>
+        <x:v>Pop hits 50K, center web 100K, and jackpots 250K times balls in play. Bigger raises these to 75K, 150K, and 300K times balls.</x:v>
       </x:c>
       <x:c r="I46" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented at medium complexity. Gate remains closed. Safety Net extends the opening save to 25 seconds, More Time extends grace to 10 seconds, and Shot Assist makes the left web always count as center web.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,18 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0689e904d5ff48ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rccb6b37421474cfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R72f780dea59e4f4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R78077cae36ec4db9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R524312a8e4ed402f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Re6064498c2174a47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rc1d72e82af614645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Re13f02e8309f4adf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Ree8dd6649a844779"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rc64532a5eeaf4f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rb0d01bc622d64135"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R488963cebe844f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8681d20a12c54d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R1f64d79bd9344cbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rdd10dcc57a9e44fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R77881bc7750e40be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rb017133334ef40e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Raafefa16eefb4d4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R62ea8e3523a5400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R9891d68e1da54bcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rd8727351b67448d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R1b900bb4a95242c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rd21a5303022146d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R7c0f7bc9041e4ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R29a08e63619a4995"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="9">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -75,8 +76,19 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F4E78"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -118,15 +130,51 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="5">
     <x:border/>
     <x:border/>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFA6A6A6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="60">
+  <x:cellXfs count="81">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -263,6 +311,57 @@
     <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -371,9 +470,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2146,37 +2245,37 @@
         <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="C38" s="31" t="str">
-        <x:v>dr_zap</x:v>
+        <x:v>dr_zapp</x:v>
       </x:c>
       <x:c r="D38" s="31" t="str">
         <x:v>Doctor Zapp</x:v>
       </x:c>
       <x:c r="E38" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F38" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G38" s="31" t="str">
-        <x:v>Electrical machine / timed</x:v>
+        <x:v>Qualification / spinner attack</x:v>
       </x:c>
       <x:c r="H38" s="31" t="str">
-        <x:v>Invention control</x:v>
+        <x:v>Upper-target multiplier</x:v>
       </x:c>
       <x:c r="I38" s="31" t="str">
-        <x:v>Spinner + lit shots</x:v>
+        <x:v>Lower banks + rooftop spinner/targets</x:v>
       </x:c>
       <x:c r="J38" s="31" t="str">
-        <x:v>Zapp/Super value</x:v>
+        <x:v>100K drops; 50K helpers/flashes</x:v>
       </x:c>
       <x:c r="K38" s="31" t="str">
-        <x:v>Overload timing</x:v>
+        <x:v>Must qualify roof access and build flashes under active play</x:v>
       </x:c>
       <x:c r="L38" s="31" t="str">
-        <x:v>Sequence complete / timer / ball end</x:v>
+        <x:v>25 flashes / ball end</x:v>
       </x:c>
       <x:c r="M38" s="31" t="str">
-        <x:v>Must stay distinct from Electro by focusing on Caldwell's stolen invention.</x:v>
+        <x:v>Distinct from Electro: fixed rooftop camera-flash objective with helper targets rather than a travelling playfield spark.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2187,37 +2286,37 @@
         <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="C39" s="31" t="str">
-        <x:v>voltan_boomer</x:v>
+        <x:v>bolton_boomer</x:v>
       </x:c>
       <x:c r="D39" s="31" t="str">
-        <x:v>Voltan and Boomer</x:v>
+        <x:v>Bolton and Boomer</x:v>
       </x:c>
       <x:c r="E39" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F39" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
-        <x:v>Storm timing / robbery</x:v>
+        <x:v>Capture-loop multiball</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Thunder windows</x:v>
+        <x:v>Timed Super Jackpot</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
-        <x:v>Storm shots + target groups</x:v>
+        <x:v>Random target + saucers + VUK</x:v>
       </x:c>
       <x:c r="J39" s="31" t="str">
-        <x:v>Thunder/robbery jackpots</x:v>
+        <x:v>Capture-loop jackpots and escalating Supers</x:v>
       </x:c>
       <x:c r="K39" s="31" t="str">
-        <x:v>Short storm windows</x:v>
+        <x:v>One ball is captured while the other must reach the VUK; later Supers are timed</x:v>
       </x:c>
       <x:c r="L39" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>Super sequence complete / multiball end</x:v>
       </x:c>
       <x:c r="M39" s="31" t="str">
-        <x:v>Thunder Rumble pair kept together; full design pending.</x:v>
+        <x:v>Repeating target-capture-release loop; unlike Dr. Manta, both balls participate in a conventional ongoing multiball.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2316,31 +2415,31 @@
         <x:v>Dr. Manta</x:v>
       </x:c>
       <x:c r="E42" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F42" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>2 staged / 1 active</x:v>
       </x:c>
       <x:c r="G42" s="31" t="str">
-        <x:v>Hidden-city control</x:v>
+        <x:v>Relay / staged ball control</x:v>
       </x:c>
       <x:c r="H42" s="31" t="str">
-        <x:v>Trap / freeze</x:v>
+        <x:v>Timed jackpot build-and-cash</x:v>
       </x:c>
       <x:c r="I42" s="31" t="str">
-        <x:v>Saucers + robotic-creature shots</x:v>
+        <x:v>VUK, three saucers, both spinners, upper targets</x:v>
       </x:c>
       <x:c r="J42" s="31" t="str">
-        <x:v>Frozen-city jackpots</x:v>
+        <x:v>100K VUK; 150K saucer; 100K starting JP; +50K/spin to 1M; repeated upper-target collections</x:v>
       </x:c>
       <x:c r="K42" s="31" t="str">
-        <x:v>Held ball / trap pressure</x:v>
+        <x:v>Second ball must reach a saucer; active attack ball may leave the roof; all flippers disable at timeout</x:v>
       </x:c>
       <x:c r="L42" s="31" t="str">
-        <x:v>Goals or timer / ball end</x:v>
+        <x:v>Attack timer expires and active ball reaches trough / early second-ball loss</x:v>
       </x:c>
       <x:c r="M42" s="31" t="str">
-        <x:v>Main Phantom from the Depths of Time villain.</x:v>
+        <x:v>Mechanically distinct from Molemen: never conventional free two-ball play after setup. One ball is always held while the other performs the objective.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2477,34 +2576,34 @@
         <x:v>molemen</x:v>
       </x:c>
       <x:c r="D46" s="31" t="str">
-        <x:v>Molemen</x:v>
+        <x:v>The Molemen</x:v>
       </x:c>
       <x:c r="E46" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F46" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G46" s="31" t="str">
-        <x:v>Underground invasion</x:v>
+        <x:v>Area-control multiball</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Area / survival</x:v>
+        <x:v>Saucer jackpots / add-a-ball</x:v>
       </x:c>
       <x:c r="I46" s="31" t="str">
-        <x:v>Drops, tunnels, lower playfield</x:v>
+        <x:v>Left pop, center web, right pop + three saucers</x:v>
       </x:c>
       <x:c r="J46" s="31" t="str">
-        <x:v>Underground jackpots</x:v>
+        <x:v>50K pops; 100K center; 250K per ball saucer jackpots</x:v>
       </x:c>
       <x:c r="K46" s="31" t="str">
-        <x:v>Escalating underground pressure</x:v>
+        <x:v>Jackpot value depends on balls in play; each area offers one add-a-ball; short one-ball grace</x:v>
       </x:c>
       <x:c r="L46" s="31" t="str">
-        <x:v>Goals or timer / ball end</x:v>
+        <x:v>One-ball grace expires / ball end</x:v>
       </x:c>
       <x:c r="M46" s="31" t="str">
-        <x:v>Compact mode name; Mugs Reilly can appear in intro and summaries.</x:v>
+        <x:v>Chapter 9's conventional area-control multiball. It contrasts with Dr. Manta's staged relay, where one ball is always deliberately held.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -3522,10 +3621,10 @@
         <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="B9" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C9" s="31" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
         <x:v>Nature Strikes Back</x:v>
@@ -3560,10 +3659,10 @@
         <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="B10" s="31" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C10" s="31" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
         <x:v>Invasion from Everywhere</x:v>
@@ -3649,6 +3748,1217 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="56" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="63" t="str">
+        <x:v>ASM67 Music Inventory — Rebalanced Coded Assignments</x:v>
+      </x:c>
+      <x:c r="B1" s="63"/>
+      <x:c r="C1" s="63"/>
+      <x:c r="D1" s="63"/>
+      <x:c r="E1" s="63"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="67" t="str">
+        <x:v>Source of truth: ASM67_2026_08_06_1am plus this music patch. villain_bookends.py is canonical for villain/wizard gameplay music.</x:v>
+      </x:c>
+      <x:c r="B2" s="67"/>
+      <x:c r="C2" s="67"/>
+      <x:c r="D2" s="67"/>
+      <x:c r="E2" s="67"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="67" t="str">
+        <x:v>Rule: every villain/wizard gameplay song has at most two uses. maintheme, loop*, and intro_* tracks do not soundtrack villain/wizard gameplay; shared transition/core uses may remain.</x:v>
+      </x:c>
+      <x:c r="B3" s="67"/>
+      <x:c r="C3" s="67"/>
+      <x:c r="D3" s="67"/>
+      <x:c r="E3" s="67"/>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="72" t="str">
+        <x:v>Song #</x:v>
+      </x:c>
+      <x:c r="B5" s="72" t="str">
+        <x:v>Configured Asset</x:v>
+      </x:c>
+      <x:c r="C5" s="72" t="str">
+        <x:v>Effective Uses</x:v>
+      </x:c>
+      <x:c r="D5" s="72" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="E5" s="72" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" s="74" t="str">
+        <x:v>prowl_car</x:v>
+      </x:c>
+      <x:c r="C6" s="74" t="str">
+        <x:v>Main play random pool</x:v>
+      </x:c>
+      <x:c r="D6" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="74" t="str"/>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B7" s="74" t="str">
+        <x:v>panic_patrol</x:v>
+      </x:c>
+      <x:c r="C7" s="74" t="str">
+        <x:v>Main play random pool</x:v>
+      </x:c>
+      <x:c r="D7" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="74" t="str"/>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="73" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="74" t="str">
+        <x:v>rat_race</x:v>
+      </x:c>
+      <x:c r="C8" s="74" t="str">
+        <x:v>Cyclops; Kingpin / Final Showdown</x:v>
+      </x:c>
+      <x:c r="D8" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E8" s="74" t="str"/>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="73" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="74" t="str">
+        <x:v>ticking</x:v>
+      </x:c>
+      <x:c r="C9" s="74" t="str">
+        <x:v>Green Lizard</x:v>
+      </x:c>
+      <x:c r="D9" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="74" t="str"/>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="73" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="74" t="str">
+        <x:v>start_loop</x:v>
+      </x:c>
+      <x:c r="C10" s="74" t="str">
+        <x:v>Ball start / skill-shot lead-in</x:v>
+      </x:c>
+      <x:c r="D10" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="74" t="str"/>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="73" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B11" s="74" t="str">
+        <x:v>maintheme_no_lyrics</x:v>
+      </x:c>
+      <x:c r="C11" s="74" t="str">
+        <x:v>Bonus; High Score</x:v>
+      </x:c>
+      <x:c r="D11" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E11" s="74" t="str">
+        <x:v>Protected main-theme variant; no villain/wizard gameplay use.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="73" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="74" t="str">
+        <x:v>dash_to_safety</x:v>
+      </x:c>
+      <x:c r="C12" s="74" t="str">
+        <x:v>Green Goblin</x:v>
+      </x:c>
+      <x:c r="D12" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="74" t="str"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="73" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="74" t="str">
+        <x:v>cloak</x:v>
+      </x:c>
+      <x:c r="C13" s="74" t="str">
+        <x:v>Sandman; Dr. Von Schlick</x:v>
+      </x:c>
+      <x:c r="D13" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E13" s="74" t="str"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="73" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="74" t="str">
+        <x:v>fright</x:v>
+      </x:c>
+      <x:c r="C14" s="74" t="str">
+        <x:v>Skymaster; main play random pool</x:v>
+      </x:c>
+      <x:c r="D14" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E14" s="74" t="str"/>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="73" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" s="74" t="str">
+        <x:v>fromthebird</x:v>
+      </x:c>
+      <x:c r="C15" s="74" t="str">
+        <x:v>Vulture</x:v>
+      </x:c>
+      <x:c r="D15" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="74" t="str"/>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="77" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="78" t="str">
+        <x:v>intro_loop_2</x:v>
+      </x:c>
+      <x:c r="C16" s="78" t="str"/>
+      <x:c r="D16" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="78" t="str">
+        <x:v>Protected intro_* track; no villain/wizard gameplay use.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="77" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B17" s="78" t="str">
+        <x:v>intro_mild</x:v>
+      </x:c>
+      <x:c r="C17" s="78" t="str"/>
+      <x:c r="D17" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="78" t="str">
+        <x:v>Protected intro_* track; no villain/wizard gameplay use.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="77" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B18" s="78" t="str">
+        <x:v>loopy1</x:v>
+      </x:c>
+      <x:c r="C18" s="78" t="str"/>
+      <x:c r="D18" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="78" t="str">
+        <x:v>Protected loop* track; no villain/wizard gameplay use.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A19" s="77" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B19" s="78" t="str">
+        <x:v>loopystart</x:v>
+      </x:c>
+      <x:c r="C19" s="78" t="str">
+        <x:v>All villain/wizard bookend intros</x:v>
+      </x:c>
+      <x:c r="D19" s="77" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="78" t="str">
+        <x:v>Protected loop* track retained only as shared transition/intro music, not gameplay.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="77" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B20" s="78" t="str">
+        <x:v>loop_123</x:v>
+      </x:c>
+      <x:c r="C20" s="78" t="str"/>
+      <x:c r="D20" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="78" t="str">
+        <x:v>Protected loop* track; no villain/wizard gameplay use.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="77" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B21" s="78" t="str">
+        <x:v>loop_123456</x:v>
+      </x:c>
+      <x:c r="C21" s="78" t="str">
+        <x:v>Main play random pool</x:v>
+      </x:c>
+      <x:c r="D21" s="77" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="78" t="str">
+        <x:v>Protected loop* track retained outside villain/wizard gameplay.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="73" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B22" s="74" t="str">
+        <x:v>maintheme</x:v>
+      </x:c>
+      <x:c r="C22" s="74" t="str">
+        <x:v>Attract</x:v>
+      </x:c>
+      <x:c r="D22" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="74" t="str">
+        <x:v>Protected main theme retained outside villain/wizard gameplay.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B23" s="74" t="str">
+        <x:v>paroxism</x:v>
+      </x:c>
+      <x:c r="C23" s="74" t="str">
+        <x:v>Doctor Octopus</x:v>
+      </x:c>
+      <x:c r="D23" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" s="74" t="str"/>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B24" s="74" t="str">
+        <x:v>shakeandstone</x:v>
+      </x:c>
+      <x:c r="C24" s="74" t="str">
+        <x:v>Parafino; Vulcan</x:v>
+      </x:c>
+      <x:c r="D24" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E24" s="74" t="str"/>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B25" s="74" t="str">
+        <x:v>somethings_up</x:v>
+      </x:c>
+      <x:c r="C25" s="74" t="str">
+        <x:v>Chapter Select; Villain Select</x:v>
+      </x:c>
+      <x:c r="D25" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E25" s="74" t="str"/>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="73" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B26" s="74" t="str">
+        <x:v>spider_intro_strong</x:v>
+      </x:c>
+      <x:c r="C26" s="74" t="str">
+        <x:v>All villain/wizard bookend summaries</x:v>
+      </x:c>
+      <x:c r="D26" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="74" t="str">
+        <x:v>Shared summary context.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="73" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B27" s="74" t="str">
+        <x:v>street_beat</x:v>
+      </x:c>
+      <x:c r="C27" s="74" t="str">
+        <x:v>Rhino Bash</x:v>
+      </x:c>
+      <x:c r="D27" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="74" t="str"/>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="73" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B28" s="74" t="str">
+        <x:v>tautwalk</x:v>
+      </x:c>
+      <x:c r="C28" s="74" t="str">
+        <x:v>Electro; Time Showdown</x:v>
+      </x:c>
+      <x:c r="D28" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E28" s="74" t="str"/>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="73" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B29" s="74" t="str">
+        <x:v>twilight_guitar</x:v>
+      </x:c>
+      <x:c r="C29" s="74" t="str">
+        <x:v>Mysterio; Infinata</x:v>
+      </x:c>
+      <x:c r="D29" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E29" s="74" t="str"/>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="73" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B30" s="74" t="str">
+        <x:v>waiting</x:v>
+      </x:c>
+      <x:c r="C30" s="74" t="str">
+        <x:v>Scorpion; 5th Ave Phantom</x:v>
+      </x:c>
+      <x:c r="D30" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E30" s="74" t="str"/>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="77" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B31" s="78" t="str">
+        <x:v>intro_mild</x:v>
+      </x:c>
+      <x:c r="C31" s="78" t="str"/>
+      <x:c r="D31" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E31" s="78" t="str">
+        <x:v>Protected intro_* duplicate; unused.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="73" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B32" s="74" t="str">
+        <x:v>dash_to_safety_2</x:v>
+      </x:c>
+      <x:c r="C32" s="74" t="str">
+        <x:v>Dr. Magneto; The Spider-Men</x:v>
+      </x:c>
+      <x:c r="D32" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E32" s="74" t="str"/>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="73" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B33" s="74" t="str">
+        <x:v>dash_to_safety_3</x:v>
+      </x:c>
+      <x:c r="C33" s="74" t="str">
+        <x:v>Professor Pretorius; Charles Cameo</x:v>
+      </x:c>
+      <x:c r="D33" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E33" s="74" t="str"/>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="73" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B34" s="74" t="str">
+        <x:v>anji</x:v>
+      </x:c>
+      <x:c r="C34" s="74" t="str">
+        <x:v>Cerberus</x:v>
+      </x:c>
+      <x:c r="D34" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E34" s="74" t="str"/>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" s="73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B35" s="74" t="str">
+        <x:v>besame_mucho</x:v>
+      </x:c>
+      <x:c r="C35" s="74" t="str">
+        <x:v>Diana</x:v>
+      </x:c>
+      <x:c r="D35" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E35" s="74" t="str"/>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" s="73" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B36" s="74" t="str">
+        <x:v>blood_and_black_lace</x:v>
+      </x:c>
+      <x:c r="C36" s="74" t="str">
+        <x:v>Centaur Charge</x:v>
+      </x:c>
+      <x:c r="D36" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E36" s="74" t="str"/>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="73" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B37" s="74" t="str">
+        <x:v>danube_incident</x:v>
+      </x:c>
+      <x:c r="C37" s="74" t="str">
+        <x:v>The Fly Twins</x:v>
+      </x:c>
+      <x:c r="D37" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E37" s="74" t="str"/>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
+      <x:c r="A38" s="73" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B38" s="74" t="str">
+        <x:v>happy_go_lively</x:v>
+      </x:c>
+      <x:c r="C38" s="74" t="str">
+        <x:v>The Enforcers</x:v>
+      </x:c>
+      <x:c r="D38" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E38" s="74" t="str"/>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" s="73" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B39" s="74" t="str">
+        <x:v>la_buritta</x:v>
+      </x:c>
+      <x:c r="C39" s="74" t="str">
+        <x:v>The Fantastic Fakir</x:v>
+      </x:c>
+      <x:c r="D39" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E39" s="74" t="str"/>
+    </x:row>
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
+      <x:c r="A40" s="73" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B40" s="74" t="str">
+        <x:v>spooky</x:v>
+      </x:c>
+      <x:c r="C40" s="74" t="str">
+        <x:v>Kotep; Super Swami</x:v>
+      </x:c>
+      <x:c r="D40" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E40" s="74" t="str"/>
+    </x:row>
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
+      <x:c r="A41" s="73" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B41" s="74" t="str">
+        <x:v>sunflower</x:v>
+      </x:c>
+      <x:c r="C41" s="74" t="str">
+        <x:v>Dr. Noah Boddy</x:v>
+      </x:c>
+      <x:c r="D41" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E41" s="74" t="str"/>
+    </x:row>
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
+      <x:c r="A42" s="73" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B42" s="74" t="str">
+        <x:v>the_enchanted_sea</x:v>
+      </x:c>
+      <x:c r="C42" s="74" t="str">
+        <x:v>Doctor Dumpty; Doctor Atlantean</x:v>
+      </x:c>
+      <x:c r="D42" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E42" s="74" t="str"/>
+    </x:row>
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
+      <x:c r="A43" s="73" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B43" s="74" t="str">
+        <x:v>the_hearse</x:v>
+      </x:c>
+      <x:c r="C43" s="74" t="str">
+        <x:v>Doctor Zapp; The Web Tightens</x:v>
+      </x:c>
+      <x:c r="D43" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E43" s="74" t="str"/>
+    </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
+      <x:c r="A44" s="73" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B44" s="74" t="str">
+        <x:v>the_ox</x:v>
+      </x:c>
+      <x:c r="C44" s="74" t="str">
+        <x:v>The Snowman</x:v>
+      </x:c>
+      <x:c r="D44" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E44" s="74" t="str"/>
+    </x:row>
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
+      <x:c r="A45" s="73" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B45" s="74" t="str">
+        <x:v>yegelle_tezeta</x:v>
+      </x:c>
+      <x:c r="C45" s="74" t="str">
+        <x:v>Dr. Manta</x:v>
+      </x:c>
+      <x:c r="D45" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E45" s="74" t="str"/>
+    </x:row>
+    <x:row r="46" ht="15" hidden="0" customHeight="1">
+      <x:c r="A46" s="73" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B46" s="74" t="str">
+        <x:v>action_line</x:v>
+      </x:c>
+      <x:c r="C46" s="74" t="str">
+        <x:v>Desperado; The Plotter</x:v>
+      </x:c>
+      <x:c r="D46" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E46" s="74" t="str"/>
+    </x:row>
+    <x:row r="47" ht="15" hidden="0" customHeight="1">
+      <x:c r="A47" s="73" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B47" s="74" t="str">
+        <x:v>the_shadows</x:v>
+      </x:c>
+      <x:c r="C47" s="74" t="str">
+        <x:v>The Plutonians; The Molemen</x:v>
+      </x:c>
+      <x:c r="D47" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E47" s="74" t="str"/>
+    </x:row>
+    <x:row r="48" ht="15" hidden="0" customHeight="1">
+      <x:c r="A48" s="73" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B48" s="74" t="str">
+        <x:v>fbi</x:v>
+      </x:c>
+      <x:c r="C48" s="74" t="str">
+        <x:v>Igor; Crime Wave</x:v>
+      </x:c>
+      <x:c r="D48" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E48" s="74" t="str"/>
+    </x:row>
+    <x:row r="49" ht="15" hidden="0" customHeight="1">
+      <x:c r="A49" s="73" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B49" s="74" t="str">
+        <x:v>don_and_dewey</x:v>
+      </x:c>
+      <x:c r="C49" s="74" t="str">
+        <x:v>Conner's Reptiles; Nature Strikes Back</x:v>
+      </x:c>
+      <x:c r="D49" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E49" s="74" t="str"/>
+    </x:row>
+    <x:row r="50" ht="15" hidden="0" customHeight="1">
+      <x:c r="A50" s="73" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B50" s="74" t="str">
+        <x:v>beat_girl</x:v>
+      </x:c>
+      <x:c r="C50" s="74" t="str">
+        <x:v>Master Technician</x:v>
+      </x:c>
+      <x:c r="D50" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E50" s="74" t="str"/>
+    </x:row>
+    <x:row r="51" ht="15" hidden="0" customHeight="1">
+      <x:c r="A51" s="73" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B51" s="74" t="str">
+        <x:v>aztec</x:v>
+      </x:c>
+      <x:c r="C51" s="74" t="str">
+        <x:v>Baron Von Rantenraven</x:v>
+      </x:c>
+      <x:c r="D51" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E51" s="74" t="str"/>
+    </x:row>
+    <x:row r="52" ht="15" hidden="0" customHeight="1">
+      <x:c r="A52" s="73" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B52" s="74" t="str">
+        <x:v>motorcycle_circus</x:v>
+      </x:c>
+      <x:c r="C52" s="74" t="str">
+        <x:v>Mastermind Trap; Trubble Unleashed</x:v>
+      </x:c>
+      <x:c r="D52" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E52" s="74" t="str"/>
+    </x:row>
+    <x:row r="53" ht="15" hidden="0" customHeight="1">
+      <x:c r="A53" s="73" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B53" s="74" t="str">
+        <x:v>peace_pipe</x:v>
+      </x:c>
+      <x:c r="C53" s="74" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
+      </x:c>
+      <x:c r="D53" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E53" s="74" t="str"/>
+    </x:row>
+    <x:row r="54" ht="15" hidden="0" customHeight="1">
+      <x:c r="A54" s="73" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B54" s="74" t="str">
+        <x:v>tall_cool_one</x:v>
+      </x:c>
+      <x:c r="C54" s="74" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
+      </x:c>
+      <x:c r="D54" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E54" s="74" t="str"/>
+    </x:row>
+    <x:row r="55" ht="15" hidden="0" customHeight="1">
+      <x:c r="A55" s="73" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B55" s="74" t="str">
+        <x:v>clasical_gas</x:v>
+      </x:c>
+      <x:c r="C55" s="74" t="str">
+        <x:v>Fiddler; Sinister Surge</x:v>
+      </x:c>
+      <x:c r="D55" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E55" s="74" t="str"/>
+    </x:row>
+    <x:row r="56" ht="15" hidden="0" customHeight="1">
+      <x:c r="A56" s="73" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B56" s="74" t="str">
+        <x:v>sleepwalk</x:v>
+      </x:c>
+      <x:c r="C56" s="74" t="str">
+        <x:v>Harley Clivendon</x:v>
+      </x:c>
+      <x:c r="D56" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E56" s="74" t="str"/>
+    </x:row>
+    <x:row r="57" ht="15" hidden="0" customHeight="1">
+      <x:c r="A57" s="73" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B57" s="74" t="str">
+        <x:v>topsy</x:v>
+      </x:c>
+      <x:c r="C57" s="74" t="str">
+        <x:v>Devargas; Brutus</x:v>
+      </x:c>
+      <x:c r="D57" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E57" s="74" t="str"/>
+    </x:row>
+    <x:row r="58" ht="15" hidden="0" customHeight="1">
+      <x:c r="A58" s="73" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B58" s="74" t="str">
+        <x:v>moon_godess</x:v>
+      </x:c>
+      <x:c r="C58" s="74" t="str">
+        <x:v>Pardo; Master Vine</x:v>
+      </x:c>
+      <x:c r="D58" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E58" s="74" t="str"/>
+    </x:row>
+    <x:row r="59" ht="15" hidden="0" customHeight="1">
+      <x:c r="A59" s="73" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B59" s="74" t="str">
+        <x:v>conquistador</x:v>
+      </x:c>
+      <x:c r="C59" s="74" t="str">
+        <x:v>The Conquistador</x:v>
+      </x:c>
+      <x:c r="D59" s="73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E59" s="74" t="str"/>
+    </x:row>
+    <x:row r="60" ht="15" hidden="0" customHeight="1">
+      <x:c r="A60" s="73" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B60" s="74" t="str">
+        <x:v>death_have_no_mercy</x:v>
+      </x:c>
+      <x:c r="C60" s="74" t="str">
+        <x:v>Spider-Slayer; Lost World Invasion</x:v>
+      </x:c>
+      <x:c r="D60" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E60" s="74" t="str">
+        <x:v>New track now integrated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="15" hidden="0" customHeight="1">
+      <x:c r="A61" s="73" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B61" s="74" t="str">
+        <x:v>diamond_head</x:v>
+      </x:c>
+      <x:c r="C61" s="74" t="str">
+        <x:v>Doctor Cool; Mad Science Meltdown</x:v>
+      </x:c>
+      <x:c r="D61" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E61" s="74" t="str">
+        <x:v>New track now integrated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="15" hidden="0" customHeight="1">
+      <x:c r="A62" s="73" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B62" s="74" t="str">
+        <x:v>washington_square</x:v>
+      </x:c>
+      <x:c r="C62" s="74" t="str">
+        <x:v>Clive and Blotto; Sir Galahad</x:v>
+      </x:c>
+      <x:c r="D62" s="73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E62" s="74" t="str">
+        <x:v>New track now integrated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="15" hidden="0" customHeight="1">
+      <x:c r="A63" s="75" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B63" s="76" t="str">
+        <x:v>bongo_rock</x:v>
+      </x:c>
+      <x:c r="C63" s="76" t="str">
+        <x:v>Metal Monster; Bolton and Boomer</x:v>
+      </x:c>
+      <x:c r="D63" s="75" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E63" s="76" t="str">
+        <x:v>New track now integrated.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="15" hidden="0" customHeight="1">
+      <x:c r="A66" s="68" t="str">
+        <x:v>Wizard Music Source Audit</x:v>
+      </x:c>
+      <x:c r="B66" s="68"/>
+      <x:c r="C66" s="68"/>
+      <x:c r="D66" s="68"/>
+      <x:c r="E66" s="68"/>
+    </x:row>
+    <x:row r="67" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A67" s="80" t="str">
+        <x:v>Wizard</x:v>
+      </x:c>
+      <x:c r="B67" s="80" t="str">
+        <x:v>Canonical Song</x:v>
+      </x:c>
+      <x:c r="C67" s="80" t="str">
+        <x:v>Mode Config Override</x:v>
+      </x:c>
+      <x:c r="D67" s="80" t="str">
+        <x:v>Effective Song</x:v>
+      </x:c>
+      <x:c r="E67" s="80" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A68" s="14" t="str">
+        <x:v>Sinister Surge</x:v>
+      </x:c>
+      <x:c r="B68" s="14" t="str">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C68" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D68" s="14" t="str">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E68" s="14" t="str">
+        <x:v>Bookend assignment remains active.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A69" s="14" t="str">
+        <x:v>Mastermind Trap</x:v>
+      </x:c>
+      <x:c r="B69" s="14" t="str">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C69" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D69" s="14" t="str">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E69" s="14" t="str">
+        <x:v>Bookend assignment remains active.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A70" s="14" t="str">
+        <x:v>Trubble Unleashed</x:v>
+      </x:c>
+      <x:c r="B70" s="14" t="str">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C70" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D70" s="14" t="str">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E70" s="14" t="str">
+        <x:v>Bookend assignment remains active.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A71" s="14" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
+      </x:c>
+      <x:c r="B71" s="14" t="str">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C71" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D71" s="14" t="str">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E71" s="14" t="str">
+        <x:v>Bookend assignment remains active.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A72" s="14" t="str">
+        <x:v>Final Showdown / Kingpin</x:v>
+      </x:c>
+      <x:c r="B72" s="14" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C72" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D72" s="14" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E72" s="14" t="str">
+        <x:v>Bookend assignment remains active.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="15" hidden="0" customHeight="1">
+      <x:c r="A74" s="68" t="str">
+        <x:v>Protected Track Family Audit</x:v>
+      </x:c>
+      <x:c r="B74" s="68"/>
+      <x:c r="C74" s="68"/>
+      <x:c r="D74" s="68"/>
+      <x:c r="E74" s="68"/>
+    </x:row>
+    <x:row r="75" ht="15" hidden="0" customHeight="1">
+      <x:c r="A75" s="80" t="str">
+        <x:v>Family</x:v>
+      </x:c>
+      <x:c r="B75" s="80" t="str">
+        <x:v>Song / Asset</x:v>
+      </x:c>
+      <x:c r="C75" s="80" t="str">
+        <x:v>Villain/Wizard Gameplay</x:v>
+      </x:c>
+      <x:c r="D75" s="80" t="str">
+        <x:v>Flag</x:v>
+      </x:c>
+      <x:c r="E75" s="80" t="str">
+        <x:v>Allowed non-gameplay use</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="15" hidden="0" customHeight="1">
+      <x:c r="A76" s="14" t="str">
+        <x:v>intro_*</x:v>
+      </x:c>
+      <x:c r="B76" s="14" t="str">
+        <x:v>11 — intro_loop_2</x:v>
+      </x:c>
+      <x:c r="C76" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D76" s="14" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E76" s="14" t="str">
+        <x:v>None currently</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="15" hidden="0" customHeight="1">
+      <x:c r="A77" s="14" t="str">
+        <x:v>intro_*</x:v>
+      </x:c>
+      <x:c r="B77" s="14" t="str">
+        <x:v>12 / 26 — intro_mild</x:v>
+      </x:c>
+      <x:c r="C77" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D77" s="14" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E77" s="14" t="str">
+        <x:v>None currently</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="15" hidden="0" customHeight="1">
+      <x:c r="A78" s="14" t="str">
+        <x:v>loop*</x:v>
+      </x:c>
+      <x:c r="B78" s="14" t="str">
+        <x:v>13 — loopy1</x:v>
+      </x:c>
+      <x:c r="C78" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D78" s="14" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E78" s="14" t="str">
+        <x:v>None currently</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="15" hidden="0" customHeight="1">
+      <x:c r="A79" s="14" t="str">
+        <x:v>loop*</x:v>
+      </x:c>
+      <x:c r="B79" s="14" t="str">
+        <x:v>14 — loopystart</x:v>
+      </x:c>
+      <x:c r="C79" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D79" s="14" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E79" s="14" t="str">
+        <x:v>Shared bookend intro transition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="15" hidden="0" customHeight="1">
+      <x:c r="A80" s="14" t="str">
+        <x:v>loop*</x:v>
+      </x:c>
+      <x:c r="B80" s="14" t="str">
+        <x:v>15 — loop_123</x:v>
+      </x:c>
+      <x:c r="C80" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D80" s="14" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E80" s="14" t="str">
+        <x:v>None currently</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="15" hidden="0" customHeight="1">
+      <x:c r="A81" s="14" t="str">
+        <x:v>loop*</x:v>
+      </x:c>
+      <x:c r="B81" s="14" t="str">
+        <x:v>16 — loop_123456</x:v>
+      </x:c>
+      <x:c r="C81" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D81" s="14" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E81" s="14" t="str">
+        <x:v>Main-play random pool</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="15" hidden="0" customHeight="1">
+      <x:c r="A82" s="14" t="str">
+        <x:v>maintheme</x:v>
+      </x:c>
+      <x:c r="B82" s="14" t="str">
+        <x:v>17 — maintheme</x:v>
+      </x:c>
+      <x:c r="C82" s="14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D82" s="14" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E82" s="14" t="str">
+        <x:v>Attract</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A3:E3"/>
+    <x:mergeCell ref="A66:E66"/>
+    <x:mergeCell ref="A74:E74"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -4873,10 +6183,10 @@
         <x:v>Doctor Zapp</x:v>
       </x:c>
       <x:c r="G38" s="31" t="str">
-        <x:v>Placeholder / design approved</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H38" s="31" t="str">
-        <x:v>Knock down one target from each lower bank to open roof access. Upper spinner camera flashes defeat Zapp at 25 flashes; each lit upper helper target adds +1 flash per spin. Drops score 100K, helpers 50K, flashes 50K.</x:v>
+        <x:v>Camera Flash mode: qualify both lower banks, then use the rooftop spinner and unique upper-target boosts to reach 25 flashes. More Jackpots adds a 10-second bonus-spin window.</x:v>
       </x:c>
       <x:c r="I38" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -4905,10 +6215,10 @@
         <x:v>Bolton and Boomer</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
-        <x:v>Placeholder / design approved</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Repeating 2-ball multiball loop: hit a random lit target, lock one ball in any saucer, then shoot the VUK Super. First Super is untimed; later Supers run 20 seconds and reset the loop if missed.</x:v>
+        <x:v>Repeating 2-ball capture loop: hit a random lit target, lock one ball in any saucer, then shoot the VUK Super. The first Super is untimed; later Supers are timed.</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -5001,10 +6311,10 @@
         <x:v>Dr. Manta</x:v>
       </x:c>
       <x:c r="G42" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H42" s="31" t="str">
-        <x:v>Phantom from the Depths of Time villain. Dr. Manta rules the hidden city and ...</x:v>
+        <x:v>VUK-to-saucer relay: hold Ball 1 in the VUK, serve Ball 2 with a 10-second save, then lock it in any saucer. Kick Ball 1 to the rooftop for a 20-second attack. Either spinner raises the 100K jackpot by 50K per spin to a 1M cap; upper targets collect without resetting. At timeout all flippers disable until the active ball reaches the trough, then the held saucer ball is released.</x:v>
       </x:c>
       <x:c r="I42" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -5129,10 +6439,10 @@
         <x:v>The Molemen</x:v>
       </x:c>
       <x:c r="G46" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Underground-world mode associated with Mugs Reilly and the Molemen. Compact l...</x:v>
+        <x:v>Two-ball area-control multiball. Left pop lights Saucer 1, center web lights Saucer 2, and right pop lights Saucer 3. Lit saucers award 250K per ball in play, reset their area, and can award one add-a-ball per area. A 5-second one-ball grace delays mode end.</x:v>
       </x:c>
       <x:c r="I46" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -7347,7 +8657,7 @@
         <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="C38" s="31" t="str">
-        <x:v>dr_zap</x:v>
+        <x:v>dr_zapp</x:v>
       </x:c>
       <x:c r="D38" s="31" t="str">
         <x:v>Doctor Zapp</x:v>
@@ -7356,16 +8666,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F38" s="31" t="str">
-        <x:v>Placeholder framework for electrical machine / timed with invention control, using Spinner + lit shots.</x:v>
+        <x:v>Knock down one target from each lower bank to open roof access. Upper-spinner flashes defeat Zapp, while unique upper targets increase the flashes awarded per spin.</x:v>
       </x:c>
       <x:c r="G38" s="31" t="str">
-        <x:v>Ends when sequence complete / timer / ball end.</x:v>
+        <x:v>Complete 25 camera flashes; otherwise stop at ball end.</x:v>
       </x:c>
       <x:c r="H38" s="31" t="str">
-        <x:v>Zapp/Super value. Overload timing.</x:v>
+        <x:v>Drops score 100K, upper helpers score 50K, and each flash scores 50K. More Jackpots adds a timed bonus-spin window after completion.</x:v>
       </x:c>
       <x:c r="I38" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented with custom code, YAML, widget, lighting, status and summary variables; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -7376,25 +8686,25 @@
         <x:v>Elemental Chaos</x:v>
       </x:c>
       <x:c r="C39" s="31" t="str">
-        <x:v>voltan_boomer</x:v>
+        <x:v>bolton_boomer</x:v>
       </x:c>
       <x:c r="D39" s="31" t="str">
-        <x:v>Voltan and Boomer</x:v>
+        <x:v>Bolton and Boomer</x:v>
       </x:c>
       <x:c r="E39" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F39" s="31" t="str">
-        <x:v>Placeholder framework for storm timing / robbery with thunder windows, using Storm shots + target groups.</x:v>
+        <x:v>Hit a random lit target, capture one ball in any saucer, then shoot the VUK Super. After the release, repeat the loop.</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
-        <x:v>Ends when goals completed / ball end.</x:v>
+        <x:v>Complete the required Super sequence or end when multiball returns to one ball / ball end.</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Thunder/robbery jackpots. Short storm windows.</x:v>
+        <x:v>The first VUK Super is persistent. Later Super opportunities are timed and reset the capture loop when missed.</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented with custom code, YAML, widget, capture handling, status and summary variables; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -7469,19 +8779,19 @@
         <x:v>Dr. Manta</x:v>
       </x:c>
       <x:c r="E42" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>2 staged / 1 active</x:v>
       </x:c>
       <x:c r="F42" s="31" t="str">
-        <x:v>Placeholder framework for hidden-city control with trap / freeze, using Saucers + robotic-creature shots.</x:v>
+        <x:v>Shoot the VUK for 100K to hold Ball 1 and serve Ball 2 with a 10-second save. Lock Ball 2 in any saucer for 150K; it remains held while Ball 1 is kicked to the rooftop.</x:v>
       </x:c>
       <x:c r="G42" s="31" t="str">
-        <x:v>Ends when goals or timer / ball end.</x:v>
+        <x:v>After the 20-second attack expires, all flippers disable. When the active ball reaches the trough, the mode ends, the saucer ball releases, and normal single-ball play resumes. Losing Ball 2 before a saucer lock also ends the mode and releases the VUK ball.</x:v>
       </x:c>
       <x:c r="H42" s="31" t="str">
-        <x:v>Frozen-city jackpots. Held ball / trap pressure.</x:v>
+        <x:v>Jackpot starts at 100K. Either spinner adds 50K per spin, capped at 1M. Any upper target collects the current value without resetting it. More Time = 28s; Safety Net = 25s save; Bigger = 150K VUK / 200K saucer / 200K starting JP; More Jackpots = 75K per spin; Shot Assist makes the upper target corresponding to the occupied saucer worth 3X once.</x:v>
       </x:c>
       <x:c r="I42" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented with phase lighting, live timer/value/jackpot status, one-time mapped 3X indication, timeout blackout, and summary variables; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -7582,22 +8892,22 @@
         <x:v>molemen</x:v>
       </x:c>
       <x:c r="D46" s="31" t="str">
-        <x:v>Molemen</x:v>
+        <x:v>The Molemen</x:v>
       </x:c>
       <x:c r="E46" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F46" s="31" t="str">
-        <x:v>Placeholder framework for underground invasion with area / survival, using Drops, tunnels, lower playfield.</x:v>
+        <x:v>Two-ball multiball. Left pop, center web and right pop independently light Saucer 1, 2 and 3. The rooftop gate remains closed.</x:v>
       </x:c>
       <x:c r="G46" s="31" t="str">
-        <x:v>Ends when goals or timer / ball end.</x:v>
+        <x:v>When play drops to one ball, a 5-second grace begins before the mode ends; More Time increases it to 10 seconds. Mode also stops at ball end.</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Underground jackpots. Escalating underground pressure.</x:v>
+        <x:v>Pop hits score 50K and center web scores 100K. A lit saucer awards 250K multiplied by balls in play and resets that area. Each area can qualify add-a-ball once: 3 left-pop hits, 1 center-web hit, or 3 right-pop hits.</x:v>
       </x:c>
       <x:c r="I46" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented with three mapped areas, saucer jackpot/add-a-ball shows, custom widget, Case Files, grace handling and summary variables; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -8272,20 +9582,42 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>Villain music transition-track cleanup</x:v>
+        <x:v>Villain/wizard music rebalance</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>Reassigned Trubble Unleashed to motorcycle_circus; Fifth Avenue Phantom to waiting; The Plotter to fbi; The Plutonians to the_shadows; Nature Strikes Back to don_and_dewey. Selection/intro/summary tracks remain unchanged.</x:v>
+        <x:v>Rebalanced all villain/wizard gameplay songs to a maximum of two uses. Removed maintheme / loop* / intro_* gameplay assignments. Songs 55-58 are integrated. Wizard mode-level play_song overrides were removed so villain_bookends.py is the canonical assignment source.</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
         <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="14"/>
-      <x:c r="B19" s="14"/>
-      <x:c r="C19" s="14"/>
-      <x:c r="D19" s="14"/>
+      <x:c r="A19" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="str">
+        <x:v>Playtest Dr. Manta relay</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str">
+        <x:v>Verify VUK hold, second-ball serve/save, saucer hold, VUK rooftop eject, both spinner increments, mapped one-time 3X target, all-flipper timeout, trough handoff, saucer release, and early second-ball-loss cleanup.</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="str">
+        <x:v>Implemented - needs test</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Playtest The Molemen</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Verify two-ball start, closed rooftop gate, three area-to-saucer mappings, per-ball jackpot values, one-use add-a-ball per area, saucer reset/eject timing, one-ball grace, Case Files, widget and cleanup.</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>Implemented - needs test</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -8322,10 +9654,10 @@
         <x:v>Current full codebase</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>/mnt/data/ASM67_2026_07_24_3pm.zip</x:v>
+        <x:v>ASM67_2026_08_06_1am.zip</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
-        <x:v>Current source-of-truth full ZIP supplied by the user.</x:v>
+        <x:v>Source-of-truth full ZIP supplied by the user; music rebalance applied 2026-08-06.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8681d20a12c54d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R1f64d79bd9344cbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rdd10dcc57a9e44fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R77881bc7750e40be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rb017133334ef40e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Raafefa16eefb4d4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R62ea8e3523a5400a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R9891d68e1da54bcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rd8727351b67448d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R1b900bb4a95242c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rd21a5303022146d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R7c0f7bc9041e4ac9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R29a08e63619a4995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4c38b157dbf146fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R783292e8935a4290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R5f0d583591da4774"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rddc19c9a102142a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R745bffc6793742c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R0caf176a8bfd4dee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R9c19d7245b484241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R910d30c9a6c54d98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rf34fad48a17649f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rfd802361e734457b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rbca53a62db924596"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R4bbfadff598e42a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Reaab671bc7dc43ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -708,6 +708,17 @@
         <x:v>Former Kingpin limited-shot right-bank pursuit has been converted to Desperado without restoring the old Kingpin player-variable payload.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A12" s="14" t="str">
+        <x:v>Player-var cleanup</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>August 8 batch reduces declared player vars from 356 to 292 and moves temporary runtime state for seven modes into Python. Bookend summary contracts were corrected at the same time.</x:v>
+      </x:c>
+      <x:c r="C12" s="14"/>
+      <x:c r="D12" s="14"/>
+      <x:c r="E12" s="14"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
@@ -3024,8 +3035,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="68" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="59" t="str">
         <x:v>Area</x:v>
       </x:c>
@@ -3061,7 +3078,7 @@
       <x:c r="Y1" s="56"/>
       <x:c r="Z1" s="56"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A2" s="31" t="str">
         <x:v>Danger Lurks villains</x:v>
       </x:c>
@@ -3097,7 +3114,7 @@
       <x:c r="Y2" s="14"/>
       <x:c r="Z2" s="14"/>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="31" t="str">
         <x:v>The Web Tightens</x:v>
       </x:c>
@@ -3133,7 +3150,7 @@
       <x:c r="Y3" s="14"/>
       <x:c r="Z3" s="14"/>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="31" t="str">
         <x:v>The Web Tightens</x:v>
       </x:c>
@@ -3169,7 +3186,7 @@
       <x:c r="Y4" s="14"/>
       <x:c r="Z4" s="14"/>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="31" t="str">
         <x:v>Chapter 11 selection</x:v>
       </x:c>
@@ -3205,7 +3222,7 @@
       <x:c r="Y5" s="14"/>
       <x:c r="Z5" s="14"/>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="31" t="str">
         <x:v>Fiddler bonus</x:v>
       </x:c>
@@ -3219,7 +3236,7 @@
         <x:v>Persistent end-of-ball Chapter 5 bonus bank.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="31" t="str">
         <x:v>Crime Wave</x:v>
       </x:c>
@@ -3233,7 +3250,7 @@
         <x:v>Only persistent state required for the Chapter 4 wizard.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A8" s="31" t="str">
         <x:v>Crime Wave legacy</x:v>
       </x:c>
@@ -3247,7 +3264,7 @@
         <x:v>Obsolete predecessor variables; no active code or widget uses them.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="31" t="str">
         <x:v>Kingpin regular mode</x:v>
       </x:c>
@@ -3261,7 +3278,7 @@
         <x:v>Kingpin is now the final wizard identity; the old regular mode is unloaded and removed.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="31" t="str">
         <x:v>Stale modes</x:v>
       </x:c>
@@ -3275,7 +3292,7 @@
         <x:v>Replaced by final_showdown/Kingpin and skymaster respectively.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="31" t="str">
         <x:v>Stale widgets</x:v>
       </x:c>
@@ -3289,7 +3306,7 @@
         <x:v>No active config references these widgets.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A12" s="14" t="str">
         <x:v>Desperado repurpose</x:v>
       </x:c>
@@ -3301,6 +3318,132 @@
       </x:c>
       <x:c r="D12" s="14" t="str">
         <x:v>Former Kingpin round, timer, target, and extra-round variables remain Python-only and are not exported to Godot.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A13" s="14" t="str">
+        <x:v>August 8 cleanup batch</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>config/player_vars.yaml: 356 -&gt; 292 declarations</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>Net removal of 64 declarations; temporary mode-run state moved to Python while durable progression and shared summary data remain player state.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A14" s="14" t="str">
+        <x:v>Sinister Surge</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
+        <x:v>Mode-local</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str">
+        <x:v>~24 sinister_surge_* working/case-file variables</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>Area progress, A/B, lit/ready flags, values and target counters now live in the mode runtime dictionary; *_state and shared summary counters persist.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A15" s="14" t="str">
+        <x:v>Final Showdown</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>Mode-local</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>final_showdown_* live area/shot/jackpot working state</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="str">
+        <x:v>Working state now lives in the mode runtime dictionary; only final_showdown_state plus shared summary counters persist.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A16" s="14" t="str">
+        <x:v>Fly Twins</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="str">
+        <x:v>Mode-local</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="str">
+        <x:v>15 temporary fly_twins_* declarations removed</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="str">
+        <x:v>Round telemetry, lit saucers, multiplier, spinner/target state and Shot Assist are Python-local. Only state plus two bookend stats remain.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A17" s="14" t="str">
+        <x:v>Molemen</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="str">
+        <x:v>Mode-local</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="str">
+        <x:v>13 temporary molemen_* declarations removed</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="str">
+        <x:v>Area hits/lights/add-a-ball readiness are held in a local area_state structure. Opening ball-save timing stays a player variable because MPF YAML reads it.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A18" s="14" t="str">
+        <x:v>Trubble Unleashed</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="str">
+        <x:v>Mode-local</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str">
+        <x:v>7 temporary trubble_unleashed_* declarations removed</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="str">
+        <x:v>Timer, staged targets, add-a-ball readiness, lit saucers and live value stay on the mode; only two bookend stats and progression/shared vars persist.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A19" s="14" t="str">
+        <x:v>Dr. Manta</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="str">
+        <x:v>Mode-local</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str">
+        <x:v>7 temporary dr_manta_* declarations removed</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="str">
+        <x:v>Phase, timer, held saucer, jackpot and Shot Assist telemetry are Python-local. Second-ball-save seconds remains for the current_player YAML timing expression.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A20" s="14" t="str">
+        <x:v>Fifth Avenue Phantom</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="str">
+        <x:v>Mode-local</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="str">
+        <x:v>Stopped dynamic creation of phase/location/timer/reveal/Shot Assist vars</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="str">
+        <x:v>Runtime telemetry remains on the Python mode. Only progression and the two explicit summary stats are player variables.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A21" s="14" t="str">
+        <x:v>Bookend summary contracts</x:v>
+      </x:c>
+      <x:c r="B21" s="14" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="str">
+        <x:v>Diana, Mysterio, Fly Twins, Super Swami, Sinister Surge, Trubble Unleashed, Fifth Dimension Curse, Final Showdown</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="str">
+        <x:v>Removed references to missing or incorrect summary variables; summaries now read counters that the corresponding gameplay modes actually populate.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3350,7 +3493,7 @@
       <x:c r="Y1" s="56"/>
       <x:c r="Z1" s="56"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A2" s="31" t="str">
         <x:v>Classic Rogues</x:v>
       </x:c>
@@ -3364,7 +3507,7 @@
         <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="E2" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Coded / needs machine playtest</x:v>
       </x:c>
       <x:c r="F2" s="14"/>
       <x:c r="G2" s="14"/>
@@ -6820,7 +6963,7 @@
         <x:v>Implementation Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A2" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -6840,7 +6983,7 @@
         <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G2" s="31" t="str">
-        <x:v>Implemented; needs continued playtest/polish.</x:v>
+        <x:v>Coded; needs on-machine playtest. Chapter 1 callbacks: Rhino 6 pops; Sandman flashing right-bank drop moves every 4s; Vulture 1 upper target + 3 upper-spinner spins in any order; Electro both webs with 20s for the second shot and reset on timeout; Green Goblin any saucer holds 4s, then hit 2 of 4 areas (left web, center web, left bank, right bank; any drop counts its bank). One ball may rest in a saucer for 20s outside Goblin. Existing stage Jackpot, A+B add-a-ball, and Victory Laps structure retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9616,6 +9759,20 @@
         <x:v>Verify two-ball start, closed rooftop gate, three area-to-saucer mappings, per-ball jackpot values, one-use add-a-ball per area, saucer reset/eject timing, one-ball grace, Case Files, widget and cleanup.</x:v>
       </x:c>
       <x:c r="D20" t="str">
+        <x:v>Implemented - needs test</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A21" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="B21" s="14" t="str">
+        <x:v>Playtest player-var cleanup batch</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="str">
+        <x:v>Regression-test Sinister Surge, Final Showdown, Fly Twins, Molemen, Fifth Avenue Phantom, Trubble Unleashed and Dr. Manta; verify end-of-mode summary stats after mode stop.</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="str">
         <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
@@ -9649,15 +9806,15 @@
         <x:v>Use</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A2" s="31" t="str">
         <x:v>Current full codebase</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>ASM67_2026_08_06_1am.zip</x:v>
+        <x:v>ASM67_2026_08_08_1pm.zip</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
-        <x:v>Source-of-truth full ZIP supplied by the user; music rebalance applied 2026-08-06.</x:v>
+        <x:v>Source-of-truth full ZIP supplied by the user; August 8 player-variable cleanup applied to this baseline.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9735,6 +9892,17 @@
       </x:c>
       <x:c r="C9" s="14" t="str">
         <x:v>Case Files, progression, player variables, bookends, carousel mappings, and stale mode/widget assets audited against the 3pm baseline.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A10" s="14" t="str">
+        <x:v>Player-variable cleanup</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>2026-08-08</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>Seven-mode runtime-state refactor plus villain_bookends summary-contract repair; declared player vars reduced from 356 to 292.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4c38b157dbf146fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R783292e8935a4290"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R5f0d583591da4774"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rddc19c9a102142a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R745bffc6793742c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R0caf176a8bfd4dee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R9c19d7245b484241"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R910d30c9a6c54d98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rf34fad48a17649f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rfd802361e734457b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rbca53a62db924596"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R4bbfadff598e42a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Reaab671bc7dc43ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rca5e754bde204830"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R117af33d254d41d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Ra940ec267d704892"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R3e956232603e4ec9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rf7625bf8b37845cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R2154a5dd1f8b4363"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R0a24d08e67884cbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R8730d09b2ac243df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rc667405220c844a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R169e46b7324f47e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R75aeb8813f6c42af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R5082a3152e9b4c3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R1866e9dccf4744c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -636,12 +636,12 @@
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A5" s="10" t="str">
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Danger Lurks is complete with five substantive villain modes. Elemental Chaos now has Clive and Blotto implemented, with Doctor Zapp, Bolton and Boomer, The Snowman, and The Plutonians designed but still awaiting implementation. Across all chapters, 40 of 55 regular villain modes have substantive implementations.</x:v>
+        <x:v>Danger Lurks is complete with five substantive villain modes. Elemental Chaos is also complete with five substantively coded villain modes; all five now need on-machine playtesting/polish. Across all chapters, 46 of 55 regular villain modes have substantive implementations.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -707,17 +707,6 @@
       <x:c r="B11" s="14" t="str">
         <x:v>Former Kingpin limited-shot right-bank pursuit has been converted to Desperado without restoring the old Kingpin player-variable payload.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A12" s="14" t="str">
-        <x:v>Player-var cleanup</x:v>
-      </x:c>
-      <x:c r="B12" s="14" t="str">
-        <x:v>August 8 batch reduces declared player vars from 356 to 292 and moves temporary runtime state for seven modes into Python. Bookend summary contracts were corrected at the same time.</x:v>
-      </x:c>
-      <x:c r="C12" s="14"/>
-      <x:c r="D12" s="14"/>
-      <x:c r="E12" s="14"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3035,14 +3024,8 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="68" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1">
       <x:c r="A1" s="59" t="str">
         <x:v>Area</x:v>
       </x:c>
@@ -3078,7 +3061,7 @@
       <x:c r="Y1" s="56"/>
       <x:c r="Z1" s="56"/>
     </x:row>
-    <x:row r="2" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="2">
       <x:c r="A2" s="31" t="str">
         <x:v>Danger Lurks villains</x:v>
       </x:c>
@@ -3114,7 +3097,7 @@
       <x:c r="Y2" s="14"/>
       <x:c r="Z2" s="14"/>
     </x:row>
-    <x:row r="3" ht="15" hidden="0" customHeight="1">
+    <x:row r="3">
       <x:c r="A3" s="31" t="str">
         <x:v>The Web Tightens</x:v>
       </x:c>
@@ -3150,7 +3133,7 @@
       <x:c r="Y3" s="14"/>
       <x:c r="Z3" s="14"/>
     </x:row>
-    <x:row r="4" ht="15" hidden="0" customHeight="1">
+    <x:row r="4">
       <x:c r="A4" s="31" t="str">
         <x:v>The Web Tightens</x:v>
       </x:c>
@@ -3186,7 +3169,7 @@
       <x:c r="Y4" s="14"/>
       <x:c r="Z4" s="14"/>
     </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
+    <x:row r="5">
       <x:c r="A5" s="31" t="str">
         <x:v>Chapter 11 selection</x:v>
       </x:c>
@@ -3222,7 +3205,7 @@
       <x:c r="Y5" s="14"/>
       <x:c r="Z5" s="14"/>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
+    <x:row r="6">
       <x:c r="A6" s="31" t="str">
         <x:v>Fiddler bonus</x:v>
       </x:c>
@@ -3236,7 +3219,7 @@
         <x:v>Persistent end-of-ball Chapter 5 bonus bank.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
+    <x:row r="7">
       <x:c r="A7" s="31" t="str">
         <x:v>Crime Wave</x:v>
       </x:c>
@@ -3250,7 +3233,7 @@
         <x:v>Only persistent state required for the Chapter 4 wizard.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="8">
       <x:c r="A8" s="31" t="str">
         <x:v>Crime Wave legacy</x:v>
       </x:c>
@@ -3264,7 +3247,7 @@
         <x:v>Obsolete predecessor variables; no active code or widget uses them.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
+    <x:row r="9">
       <x:c r="A9" s="31" t="str">
         <x:v>Kingpin regular mode</x:v>
       </x:c>
@@ -3278,7 +3261,7 @@
         <x:v>Kingpin is now the final wizard identity; the old regular mode is unloaded and removed.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
+    <x:row r="10">
       <x:c r="A10" s="31" t="str">
         <x:v>Stale modes</x:v>
       </x:c>
@@ -3292,7 +3275,7 @@
         <x:v>Replaced by final_showdown/Kingpin and skymaster respectively.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="11">
       <x:c r="A11" s="31" t="str">
         <x:v>Stale widgets</x:v>
       </x:c>
@@ -3306,7 +3289,7 @@
         <x:v>No active config references these widgets.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="12">
       <x:c r="A12" s="14" t="str">
         <x:v>Desperado repurpose</x:v>
       </x:c>
@@ -3318,132 +3301,6 @@
       </x:c>
       <x:c r="D12" s="14" t="str">
         <x:v>Former Kingpin round, timer, target, and extra-round variables remain Python-only and are not exported to Godot.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A13" s="14" t="str">
-        <x:v>August 8 cleanup batch</x:v>
-      </x:c>
-      <x:c r="B13" s="14" t="str">
-        <x:v>Implemented</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="str">
-        <x:v>config/player_vars.yaml: 356 -&gt; 292 declarations</x:v>
-      </x:c>
-      <x:c r="D13" s="14" t="str">
-        <x:v>Net removal of 64 declarations; temporary mode-run state moved to Python while durable progression and shared summary data remain player state.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A14" s="14" t="str">
-        <x:v>Sinister Surge</x:v>
-      </x:c>
-      <x:c r="B14" s="14" t="str">
-        <x:v>Mode-local</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="str">
-        <x:v>~24 sinister_surge_* working/case-file variables</x:v>
-      </x:c>
-      <x:c r="D14" s="14" t="str">
-        <x:v>Area progress, A/B, lit/ready flags, values and target counters now live in the mode runtime dictionary; *_state and shared summary counters persist.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A15" s="14" t="str">
-        <x:v>Final Showdown</x:v>
-      </x:c>
-      <x:c r="B15" s="14" t="str">
-        <x:v>Mode-local</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="str">
-        <x:v>final_showdown_* live area/shot/jackpot working state</x:v>
-      </x:c>
-      <x:c r="D15" s="14" t="str">
-        <x:v>Working state now lives in the mode runtime dictionary; only final_showdown_state plus shared summary counters persist.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A16" s="14" t="str">
-        <x:v>Fly Twins</x:v>
-      </x:c>
-      <x:c r="B16" s="14" t="str">
-        <x:v>Mode-local</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="str">
-        <x:v>15 temporary fly_twins_* declarations removed</x:v>
-      </x:c>
-      <x:c r="D16" s="14" t="str">
-        <x:v>Round telemetry, lit saucers, multiplier, spinner/target state and Shot Assist are Python-local. Only state plus two bookend stats remain.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A17" s="14" t="str">
-        <x:v>Molemen</x:v>
-      </x:c>
-      <x:c r="B17" s="14" t="str">
-        <x:v>Mode-local</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="str">
-        <x:v>13 temporary molemen_* declarations removed</x:v>
-      </x:c>
-      <x:c r="D17" s="14" t="str">
-        <x:v>Area hits/lights/add-a-ball readiness are held in a local area_state structure. Opening ball-save timing stays a player variable because MPF YAML reads it.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A18" s="14" t="str">
-        <x:v>Trubble Unleashed</x:v>
-      </x:c>
-      <x:c r="B18" s="14" t="str">
-        <x:v>Mode-local</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="str">
-        <x:v>7 temporary trubble_unleashed_* declarations removed</x:v>
-      </x:c>
-      <x:c r="D18" s="14" t="str">
-        <x:v>Timer, staged targets, add-a-ball readiness, lit saucers and live value stay on the mode; only two bookend stats and progression/shared vars persist.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A19" s="14" t="str">
-        <x:v>Dr. Manta</x:v>
-      </x:c>
-      <x:c r="B19" s="14" t="str">
-        <x:v>Mode-local</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="str">
-        <x:v>7 temporary dr_manta_* declarations removed</x:v>
-      </x:c>
-      <x:c r="D19" s="14" t="str">
-        <x:v>Phase, timer, held saucer, jackpot and Shot Assist telemetry are Python-local. Second-ball-save seconds remains for the current_player YAML timing expression.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A20" s="14" t="str">
-        <x:v>Fifth Avenue Phantom</x:v>
-      </x:c>
-      <x:c r="B20" s="14" t="str">
-        <x:v>Mode-local</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="str">
-        <x:v>Stopped dynamic creation of phase/location/timer/reveal/Shot Assist vars</x:v>
-      </x:c>
-      <x:c r="D20" s="14" t="str">
-        <x:v>Runtime telemetry remains on the Python mode. Only progression and the two explicit summary stats are player variables.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A21" s="14" t="str">
-        <x:v>Bookend summary contracts</x:v>
-      </x:c>
-      <x:c r="B21" s="14" t="str">
-        <x:v>Fixed</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="str">
-        <x:v>Diana, Mysterio, Fly Twins, Super Swami, Sinister Surge, Trubble Unleashed, Fifth Dimension Curse, Final Showdown</x:v>
-      </x:c>
-      <x:c r="D21" s="14" t="str">
-        <x:v>Removed references to missing or incorrect summary variables; summaries now read counters that the corresponding gameplay modes actually populate.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3493,7 +3350,7 @@
       <x:c r="Y1" s="56"/>
       <x:c r="Z1" s="56"/>
     </x:row>
-    <x:row r="2" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="2">
       <x:c r="A2" s="31" t="str">
         <x:v>Classic Rogues</x:v>
       </x:c>
@@ -3507,7 +3364,7 @@
         <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="E2" s="31" t="str">
-        <x:v>Coded / needs machine playtest</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F2" s="14"/>
       <x:c r="G2" s="14"/>
@@ -3917,7 +3774,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="67" t="str">
-        <x:v>Source of truth: ASM67_2026_08_06_1am plus this music patch. villain_bookends.py is canonical for villain/wizard gameplay music.</x:v>
+        <x:v>Source of truth: ASM67_2026_08_08_7pm. villain_bookends.py is canonical for villain/wizard gameplay music.</x:v>
       </x:c>
       <x:c r="B2" s="67"/>
       <x:c r="C2" s="67"/>
@@ -5433,7 +5290,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H10" s="31" t="str">
-        <x:v>Serum at STAR; deliver to web shots. Case files now enhance the loop: Bigger ...</x:v>
+        <x:v>Serum at STAR; deliver to left web. A/B flash yellow while available and go solid when collected; A+B during active serum adds 500K, restarts the timer, and plays a GI celebration. Successful delivery plays a 2-second white/green web-target show before the next serum (or More Jackpots follow-up) begins. Timer expiry fades GI to off over 2 seconds; the next serum or final completion waits until the fade finishes.</x:v>
       </x:c>
       <x:c r="I10" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -6963,7 +6820,7 @@
         <x:v>Implementation Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="2">
       <x:c r="A2" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -6983,7 +6840,7 @@
         <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G2" s="31" t="str">
-        <x:v>Coded; needs on-machine playtest. Chapter 1 callbacks: Rhino 6 pops; Sandman flashing right-bank drop moves every 4s; Vulture 1 upper target + 3 upper-spinner spins in any order; Electro both webs with 20s for the second shot and reset on timeout; Green Goblin any saucer holds 4s, then hit 2 of 4 areas (left web, center web, left bank, right bank; any drop counts its bank). One ball may rest in a saucer for 20s outside Goblin. Existing stage Jackpot, A+B add-a-ball, and Victory Laps structure retained.</x:v>
+        <x:v>Implemented; needs continued playtest/polish.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -8003,7 +7860,7 @@
         <x:v>Ends when serum deliveries are completed; otherwise stops on ball end.</x:v>
       </x:c>
       <x:c r="H10" s="31" t="str">
-        <x:v>STAR creates serum; web shots deliver it. Case files add bigger value, slower decay, follow-up jackpots, one serum-save, and first-delivery flexibility.</x:v>
+        <x:v>STAR creates serum; left web delivers it. A+B adds 500,000 to an active serum and restarts the delivery timer; A/B inserts flash yellow while available, go solid yellow when collected, and completion plays a short GI celebration. Case files add bigger value, slower decay, follow-up jackpots, one serum-save, and Shot Assist delivery flexibility.</x:v>
       </x:c>
       <x:c r="I10" s="31" t="str">
         <x:v>Improved: live serum objective/delivery progress between countdowns.</x:v>
@@ -9504,7 +9361,7 @@
         <x:v>Playtest first 4 wizards</x:v>
       </x:c>
       <x:c r="C2" s="45" t="str">
-        <x:v>Sinister Surge, Mastermind Trap, Trubble Unleashed, The Plotter.</x:v>
+        <x:v>Sinister Surge, Mastermind Trap, Trubble Unleashed, Crime Wave.</x:v>
       </x:c>
       <x:c r="D2" s="45" t="str">
         <x:v>Open</x:v>
@@ -9588,7 +9445,7 @@
         <x:v>Visual polish / images</x:v>
       </x:c>
       <x:c r="C8" s="45" t="str">
-        <x:v>Replace placeholder villain/mode images and verify paths. The Plotter carousel currently reuses the former Kingpin image until dedicated art is supplied.</x:v>
+        <x:v>Replace placeholder villain/mode images and verify paths. Crime Wave carousel currently reuses the former Kingpin image until dedicated art is supplied.</x:v>
       </x:c>
       <x:c r="D8" s="45" t="str">
         <x:v>Open</x:v>
@@ -9759,20 +9616,6 @@
         <x:v>Verify two-ball start, closed rooftop gate, three area-to-saucer mappings, per-ball jackpot values, one-use add-a-ball per area, saucer reset/eject timing, one-ball grace, Case Files, widget and cleanup.</x:v>
       </x:c>
       <x:c r="D20" t="str">
-        <x:v>Implemented - needs test</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A21" s="14" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="B21" s="14" t="str">
-        <x:v>Playtest player-var cleanup batch</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="str">
-        <x:v>Regression-test Sinister Surge, Final Showdown, Fly Twins, Molemen, Fifth Avenue Phantom, Trubble Unleashed and Dr. Manta; verify end-of-mode summary stats after mode stop.</x:v>
-      </x:c>
-      <x:c r="D21" s="14" t="str">
         <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
@@ -9806,15 +9649,15 @@
         <x:v>Use</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="2">
       <x:c r="A2" s="31" t="str">
         <x:v>Current full codebase</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>ASM67_2026_08_08_1pm.zip</x:v>
+        <x:v>ASM67_2026_08_08_7pm.zip</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
-        <x:v>Source-of-truth full ZIP supplied by the user; August 8 player-variable cleanup applied to this baseline.</x:v>
+        <x:v>Current source-of-truth full ZIP supplied by the user; includes the music rebalance and subsequent August 8 work.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9892,17 +9735,6 @@
       </x:c>
       <x:c r="C9" s="14" t="str">
         <x:v>Case Files, progression, player variables, bookends, carousel mappings, and stale mode/widget assets audited against the 3pm baseline.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="39.599998474121094" hidden="0" customHeight="1">
-      <x:c r="A10" s="14" t="str">
-        <x:v>Player-variable cleanup</x:v>
-      </x:c>
-      <x:c r="B10" s="14" t="str">
-        <x:v>2026-08-08</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="str">
-        <x:v>Seven-mode runtime-state refactor plus villain_bookends summary-contract repair; declared player vars reduced from 356 to 292.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rca5e754bde204830"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R117af33d254d41d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Ra940ec267d704892"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R3e956232603e4ec9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rf7625bf8b37845cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R2154a5dd1f8b4363"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R0a24d08e67884cbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R8730d09b2ac243df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rc667405220c844a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R169e46b7324f47e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R75aeb8813f6c42af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R5082a3152e9b4c3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R1866e9dccf4744c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9fa97cf385f84943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rd01de714164f49d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R91a919fd5b984ea7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R96421597f6124fb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R456997dd73b14d76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R57266ba5a25d4e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R8645733a76914854"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Re6c4aef855a5481a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R5cac0ed2416a4bf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rcda42f69e0cb4ad3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R16eaeca5e33147b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R9bba26e56d174446"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R7b2efa29bf404011"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1171,7 +1171,7 @@
         <x:v>Chapter 2 multiball role; area-control and lit-saucer add-a-ball give it a distinct identity.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A12" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1185,7 +1185,7 @@
         <x:v>Cerberus</x:v>
       </x:c>
       <x:c r="E12" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented / needs machine playtest</x:v>
       </x:c>
       <x:c r="F12" s="31" t="str">
         <x:v>1</x:v>
@@ -1200,19 +1200,19 @@
         <x:v>Upper targets + saucers</x:v>
       </x:c>
       <x:c r="J12" s="31" t="str">
-        <x:v>Matching saucer 2X jackpots</x:v>
+        <x:v>Matching saucer 3X jackpots; per-saucer retained repeat with More Jackpots</x:v>
       </x:c>
       <x:c r="K12" s="31" t="str">
-        <x:v>Timer expiry</x:v>
+        <x:v>16s timer after first jackpot; upper target/spinner/saucer resets</x:v>
       </x:c>
       <x:c r="L12" s="31" t="str">
-        <x:v>3 saucer JPs / timer / ball end</x:v>
+        <x:v>Timer expiry / ball end; 3 jackpots is display-only</x:v>
       </x:c>
       <x:c r="M12" s="31" t="str">
-        <x:v>Timer/matching role.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>Timed matching role. CERBERUS DEFEATED is a 2-second presentation after the third jackpot; progression only requires that the mode has been played.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A13" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1226,31 +1226,31 @@
         <x:v>Vulcan</x:v>
       </x:c>
       <x:c r="E13" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented / needs machine playtest</x:v>
       </x:c>
       <x:c r="F13" s="31" t="str">
-        <x:v>2-ball MB; add-a-ball to 3</x:v>
+        <x:v>2-ball MB; repeatable add-a-ball to 3</x:v>
       </x:c>
       <x:c r="G13" s="31" t="str">
         <x:v>Multiball</x:v>
       </x:c>
       <x:c r="H13" s="31" t="str">
-        <x:v>Spinner build</x:v>
+        <x:v>Drop-bank cash / roof reset</x:v>
       </x:c>
       <x:c r="I13" s="31" t="str">
-        <x:v>Spinner + right drops + upper targets</x:v>
+        <x:v>Right bank + upper entry/targets; left bank with More Jackpots</x:v>
       </x:c>
       <x:c r="J13" s="31" t="str">
-        <x:v>Built Vulcan JP / eruption bonus</x:v>
+        <x:v>100K/150K Jackpot; +25K per upper hit to 1M; full Jackpot banks to vulcan_bonus</x:v>
       </x:c>
       <x:c r="K13" s="31" t="str">
-        <x:v>MB drain + inactivity timeout</x:v>
+        <x:v>Multiball drain; exhausted banks wait for upper entry</x:v>
       </x:c>
       <x:c r="L13" s="31" t="str">
-        <x:v>MB/inactivity end</x:v>
+        <x:v>Multiball reaches 1 ball / ball end</x:v>
       </x:c>
       <x:c r="M13" s="31" t="str">
-        <x:v>Chapter MB role; strongly physical.</x:v>
+        <x:v>Chapter multiball role. Upper playfield replenishes the drop-bank cashout loop; repeatable Add-a-Ball rewards bank completion without a separate single-ball phase.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1294,7 +1294,7 @@
         <x:v>Limited-resource precision role with a clear red-GI Hunt state.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="316.79998779296875" hidden="0" customHeight="1">
       <x:c r="A15" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1308,10 +1308,10 @@
         <x:v>Cyclops</x:v>
       </x:c>
       <x:c r="E15" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented / needs machine playtest</x:v>
       </x:c>
       <x:c r="F15" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>1-ball limited flips; timed second Eye with More Jackpots</x:v>
       </x:c>
       <x:c r="G15" s="31" t="str">
         <x:v>Limited flips</x:v>
@@ -1320,19 +1320,19 @@
         <x:v>Build-to-cash</x:v>
       </x:c>
       <x:c r="I15" s="31" t="str">
-        <x:v>Drops + center web</x:v>
+        <x:v>Drops + rubbers + center web</x:v>
       </x:c>
       <x:c r="J15" s="31" t="str">
-        <x:v>Eye value from flips remaining</x:v>
+        <x:v>Eye = 100K x remaining flips (150K Bigger), cap 2M</x:v>
       </x:c>
       <x:c r="K15" s="31" t="str">
-        <x:v>Flip limit</x:v>
+        <x:v>Flip budget; second Eye has a 20s timer</x:v>
       </x:c>
       <x:c r="L15" s="31" t="str">
-        <x:v>Eye collected / flips out / ball end</x:v>
+        <x:v>Final Eye / flips out / second-Eye timeout / ball end</x:v>
       </x:c>
       <x:c r="M15" s="31" t="str">
-        <x:v>Limited-resource role.</x:v>
+        <x:v>Limited-resource role: drops (+3) and rubbers (+1) replenish an uncapped flip supply, but every flipper press spends one. More Jackpots converts the cashout into a second timed accuracy test.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -5331,7 +5331,7 @@
         <x:v>Mastermind Trap</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A12" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -5351,10 +5351,10 @@
         <x:v>Cerberus</x:v>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented / needs machine playtest</x:v>
       </x:c>
       <x:c r="H12" s="31" t="str">
-        <x:v>Upper targets light saucers; matching saucer scores 2X; timer reset flow need...</x:v>
+        <x:v>Any upper target lights all saucers; its matching saucer is 3X. First jackpot starts the 16s timer; upper targets, upper spinner, and all saucer hits reset it. More Jackpots lets each saucer remain lit once after its first collection at the same state/multiplier. Shot Assist consumes one collection only. Third jackpot shows CERBERUS DEFEATED for 2s but play continues; playing the mode satisfies progression.</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
         <x:v>trubble_unleashed</x:v>
@@ -5363,7 +5363,7 @@
         <x:v>Trubble Unleashed</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A13" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -5383,10 +5383,10 @@
         <x:v>Vulcan</x:v>
       </x:c>
       <x:c r="G13" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented / needs machine playtest</x:v>
       </x:c>
       <x:c r="H13" s="31" t="str">
-        <x:v>Eruption multiball; spinner/right-drop scoring; upper set ramps vulcan_bonus.</x:v>
+        <x:v>2-ball Eruption multiball; right drops score a 100K Jackpot (150K Bigger) and upper-target hits add 25K to a 1M cap. Upper entry resets any down Jackpot banks. Bank completion qualifies repeatable Add-a-Ball at any upper target, capped at 3 balls. More Jackpots adds the left 3-bank. Upper-left exit holds the post 8s (12s More Time). Safety Net gives a 20s opening save; Shot Assist adds two right drops on the first right-drop hit. Every Jackpot adds its full value to vulcan_bonus.</x:v>
       </x:c>
       <x:c r="I13" s="31" t="str">
         <x:v>trubble_unleashed</x:v>
@@ -5427,7 +5427,7 @@
         <x:v>Trubble Unleashed</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A15" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -5447,10 +5447,10 @@
         <x:v>Cyclops</x:v>
       </x:c>
       <x:c r="G15" s="31" t="str">
-        <x:v>Implemented / needs playtest polish</x:v>
+        <x:v>Implemented / needs machine playtest</x:v>
       </x:c>
       <x:c r="H15" s="31" t="str">
-        <x:v>Limited flips; drops add flips; center-web Eye jackpot.</x:v>
+        <x:v>Limited flips: start 20 (30 More Time); drops add +3 and rubbers +1; banks reset immediately. Center-web Eye scores 100K x remaining flips (150K Bigger), capped at 2M. More Jackpots adds a second Eye after a 2s hold, then a 20s window; expiry shows EYE SEE YOU for 2s. Safety Net is a 10s ball save. Shot Assist makes the first drop hit knock down two additional right-bank targets, +3 flips each. Final Eye or 0 flips holds its message 2s before summary.</x:v>
       </x:c>
       <x:c r="I15" s="31" t="str">
         <x:v>trubble_unleashed</x:v>
@@ -7895,7 +7895,7 @@
         <x:v>Improved: persistent lit-saucer and collected-jackpot totals.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A12" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -7912,19 +7912,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F12" s="31" t="str">
-        <x:v>Upper targets light saucers; matching saucer collects stronger 2X jackpots while timer is active.</x:v>
+        <x:v>Hit upper targets to light all three saucers; the matching upper target makes its corresponding saucer a 3X jackpot. The upper spinner builds jackpot value.</x:v>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>Ends after 3 saucer jackpots, timer expiry, ball end, or mode completion state.</x:v>
+        <x:v>Timer expiry or ball end ends active play. Three jackpots only shows a 2-second CERBERUS DEFEATED message; it does not end the mode or gate progression.</x:v>
       </x:c>
       <x:c r="H12" s="31" t="str">
-        <x:v>Upper targets light saucers; matching saucer scores 2X; timer resets on key upper/spinner/saucer activity.</x:v>
+        <x:v>First jackpot starts a 16s timer (20s More Time). Upper targets, upper spinner, and any saucer hit reset it. After a collect the gate opens and other lit saucers return to 1X. More Jackpots gives each saucer one retained first collection at the same multiplier; Shot Assist is one use and consumes one collection on the awarded saucer.</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
-        <x:v>Improved: persistent upper-target/saucer guidance and 3-jackpot progress.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>Reviewed/corrected; needs machine playtest. Orange GI retained; red saucer-hole and green 1/2/3 insert lighting remains lens-appropriate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="805.2000122070312" hidden="0" customHeight="1">
       <x:c r="A13" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -7938,19 +7938,19 @@
         <x:v>Vulcan</x:v>
       </x:c>
       <x:c r="E13" s="31" t="str">
-        <x:v>2-ball MB; add-a-ball to 3</x:v>
+        <x:v>2-ball MB; repeatable add-a-ball to 3</x:v>
       </x:c>
       <x:c r="F13" s="31" t="str">
-        <x:v>Eruption multiball: spinner builds Vulcan JP, right drops collect, upper target set can add a ball.</x:v>
+        <x:v>Start 2-ball multiball with the roof gate open. Right drops are Jackpots; upper targets build their value. Reaching the upper playfield resets any down targets in the active Jackpot banks.</x:v>
       </x:c>
       <x:c r="G13" s="31" t="str">
-        <x:v>Ends when down to 1 ball with no spinner activity for the timeout, or on ball end.</x:v>
+        <x:v>Ends when the main multiball reaches one ball, or on ball end. There is no Cooling Timer or single-ball continuation.</x:v>
       </x:c>
       <x:c r="H13" s="31" t="str">
-        <x:v>Eruption multiball; spinner builds Vulcan JP; right drops collect; upper target set can award add-a-ball/eruption bonus.</x:v>
+        <x:v>Jackpot starts 100K (150K Bigger), +25K per upper-target hit, capped at 1M. Completing an active bank qualifies one non-stacking Add-a-Ball; upper targets flash green until collected below the 3-ball cap. More Jackpots enables the left bank. Both banks reset only on upper entry. More Time makes the upper-left post hold 12s instead of 8s; Safety Net extends the opening save from 10s to 20s; Shot Assist awards two extra right drops on the first right-drop hit. Each Jackpot banks its full value to vulcan_bonus.</x:v>
       </x:c>
       <x:c r="I13" s="31" t="str">
-        <x:v>Good: active countdown/status and state-change messaging are present.</x:v>
+        <x:v>Reviewed/redesigned; needs machine playtest. Active bank GI pulses green and goes dark when exhausted; upper targets pulse purple normally and flash green for Add-a-Ball Ready.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -7982,7 +7982,7 @@
         <x:v>Arrows/time status, exit instruction, first-hit timer start, rubber arrow award, Hunt completion, and helper behavior are implemented.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A15" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -7996,19 +7996,19 @@
         <x:v>Cyclops</x:v>
       </x:c>
       <x:c r="E15" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>1-ball limited flips; timed second Eye with More Jackpots</x:v>
       </x:c>
       <x:c r="F15" s="31" t="str">
-        <x:v>Limited-flips mode: drops add flips, then center-web Eye collects based on remaining flips.</x:v>
+        <x:v>Start with 20 flips. Each flipper press spends 1; drops add 3; rubbers add 1; completed banks reset immediately. Center-web Eye is continuously indicated by a four-light white chase.</x:v>
       </x:c>
       <x:c r="G15" s="31" t="str">
-        <x:v>Ends when the Eye jackpot is collected, flips run out, or ball ends.</x:v>
+        <x:v>Ends after the final Eye Jackpot, at 0 flips, on second-Eye timeout, or on ball end. Final/failed presentations hold for 2s before summary.</x:v>
       </x:c>
       <x:c r="H15" s="31" t="str">
-        <x:v>Limited-flips mode; drop targets add flips; center-web Eye jackpot value depends on remaining flips.</x:v>
+        <x:v>Eye = remaining flips x 100K, cap 2M. Bigger = 150K x flips, same cap. More Time starts at 30 flips. More Jackpots: first Eye -&gt; 2s hold -&gt; second Eye for 20s, with no flip reset; drops/rubbers keep adding flips. Safety Net = 10s ball save. Shot Assist = first drop hit plus two additional right-bank drops, all worth +3 flips.</x:v>
       </x:c>
       <x:c r="I15" s="31" t="str">
-        <x:v>Good: flips-left status and state-change messaging are present.</x:v>
+        <x:v>Reviewed/redesigned; needs machine playtest. Overall GI D08080; both bank GI sections pulse purple. Eye chase: l_mid_multibonus -&gt; l_advance_multiplier -&gt; l_special -&gt; l_mid_web_target, white at 250ms per step.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -9824,7 +9824,7 @@
         <x:v>Implemented bank; carries over and is not multiplied by regular bonus X.</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A4" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -9844,7 +9844,7 @@
         <x:v>VULCAN ERUPTION</x:v>
       </x:c>
       <x:c r="G4" s="31" t="str">
-        <x:v>Implemented bank; upper-target set starts at 75K and increases by 25K per completion.</x:v>
+        <x:v>Each collected Vulcan Jackpot adds its full scored value to the bank. Jackpot begins at 100K (150K with Bigger Jackpots), gains 25K per upper-target hit, and caps at 1M.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9fa97cf385f84943"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rd01de714164f49d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R91a919fd5b984ea7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R96421597f6124fb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R456997dd73b14d76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R57266ba5a25d4e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R8645733a76914854"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Re6c4aef855a5481a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R5cac0ed2416a4bf9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rcda42f69e0cb4ad3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R16eaeca5e33147b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R9bba26e56d174446"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R7b2efa29bf404011"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R85094b2b0a814997"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R0bd66f6208b049d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rb5a58462b8b146bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R683b5f907cfe47c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R14b4fed8df564495"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R569fdb9193cd49ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Ra303c6a62cac4f7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R472c6034192345d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rde44b263af4945e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra93b51163b914f69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rc2cdb73837a3470a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R6a1e75fbdd524021"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R497c1d1684d646b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -641,7 +641,7 @@
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Danger Lurks is complete with five substantive villain modes. Elemental Chaos is also complete with five substantively coded villain modes; all five now need on-machine playtesting/polish. Across all chapters, 46 of 55 regular villain modes have substantive implementations.</x:v>
+        <x:v>Lost Worlds now has three substantively coded villain modes after Igor's finalized precision-defense implementation. Across all chapters, 47 of 55 regular villain modes have substantive implementations.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -2456,31 +2456,31 @@
         <x:v>Igor</x:v>
       </x:c>
       <x:c r="E43" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F43" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G43" s="31" t="str">
-        <x:v>Assistant / defenses</x:v>
+        <x:v>Precision / defense avoidance</x:v>
       </x:c>
       <x:c r="H43" s="31" t="str">
-        <x:v>Sequence / precision</x:v>
+        <x:v>Endless authored shot-set score attack</x:v>
       </x:c>
       <x:c r="I43" s="31" t="str">
-        <x:v>Castle and defense shots</x:v>
+        <x:v>Right and left banks, pops, center/left web, main spinner, upper targets</x:v>
       </x:c>
       <x:c r="J43" s="31" t="str">
-        <x:v>Assistant combo / Super</x:v>
+        <x:v>Growing Jackpots; 25K bad shots</x:v>
       </x:c>
       <x:c r="K43" s="31" t="str">
-        <x:v>Ordered-shot pressure</x:v>
+        <x:v>Read one flashing-green good shot against nearby solid-red defenses</x:v>
       </x:c>
       <x:c r="L43" s="31" t="str">
-        <x:v>Sequence complete / ball end</x:v>
+        <x:v>Fifth bad shot (seventh with More Jackpots) or ball drain; no timer or victory</x:v>
       </x:c>
       <x:c r="M43" s="31" t="str">
-        <x:v>Shares Dr. Manta's episode and remains in the same chapter.</x:v>
+        <x:v>Distinct Chapter 9 single-ball precision role; upper set alone opens gate.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -3659,10 +3659,10 @@
         <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="B10" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C10" s="31" t="n">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="31" t="n">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
         <x:v>Invasion from Everywhere</x:v>
@@ -6343,10 +6343,10 @@
         <x:v>Igor</x:v>
       </x:c>
       <x:c r="G43" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H43" s="31" t="str">
-        <x:v>Dr. Manta's assistant from the same episode. Moved from Chapter 9 and correct...</x:v>
+        <x:v>Endless one-ball precision score attack using five authored shot sets. One shot flashes green for the current Jackpot while nearby defense shots hold red. Any good or bad shot randomly selects a different set. Jackpots start at 100K and grow by 25K; bad shots score 25K. The fifth bad shot ends the mode, or seventh with More Jackpots. There is no timer or victory condition. The upper-target set alone opens the rooftop gate.</x:v>
       </x:c>
       <x:c r="I43" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -8811,16 +8811,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F43" s="31" t="str">
-        <x:v>Placeholder framework for assistant / defenses with sequence / precision, using Castle and defense shots.</x:v>
+        <x:v>Five authored sets: right bank good / pops bad; center web good / pops bad; upper-center good / upper sides bad; main spinner good / left web and right bank bad; left bank good / left web, spinner, and pops bad. Good flashes green, bad holds red, neutral is unlit. Any scored shot selects a random different set.</x:v>
       </x:c>
       <x:c r="G43" s="31" t="str">
-        <x:v>Ends when sequence complete / ball end.</x:v>
+        <x:v>No timer and no victory condition. Ball drain ends play. Otherwise the fifth bad shot ends the mode after a 2-second IGOR'S DEFENSES WIN message; More Jackpots changes the limit to seven.</x:v>
       </x:c>
       <x:c r="H43" s="31" t="str">
-        <x:v>Assistant combo / Super. Ordered-shot pressure.</x:v>
+        <x:v>Good shots award a 100K Jackpot growing by 25K; Bigger grows by 50K. Bad shots score 25K. Safety Net = 10-second opening save; More Time = 20-second opening save; Shot Assist converts the first bad shot into the current Jackpot.</x:v>
       </x:c>
       <x:c r="I43" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented with authored no-repeat set selection, dynamic gate control, drop-bank GI indication, status display, 2-second ending hold, Case Files, and summary values; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R85094b2b0a814997"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R0bd66f6208b049d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rb5a58462b8b146bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R683b5f907cfe47c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R14b4fed8df564495"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R569fdb9193cd49ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Ra303c6a62cac4f7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R472c6034192345d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rde44b263af4945e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra93b51163b914f69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rc2cdb73837a3470a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R6a1e75fbdd524021"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R497c1d1684d646b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9ec085794ff74e3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R5da44a6a857a4123"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R53f2dd4528d04e30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rf51f67c90bb8492d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R6cc673f61cac4227"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rae8956caea5e4030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R28b5f6d5cece45d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rfb34438123714351"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R083e91fa970342fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R4ad8720095ef4d73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R9142b16c57fe4fac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R987d69c443df43c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R40dfbfb4768e45b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -641,7 +641,7 @@
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Lost Worlds now has three substantively coded villain modes after Igor's finalized precision-defense implementation. Across all chapters, 47 of 55 regular villain modes have substantive implementations.</x:v>
+        <x:v>Lost Worlds now has four substantively coded villain modes after Doctor Atlantean's finalized water-level control-panel implementation. Across all chapters, 48 of 55 regular villain modes have substantive implementations.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -2497,31 +2497,31 @@
         <x:v>Doctor Atlantean</x:v>
       </x:c>
       <x:c r="E44" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F44" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G44" s="31" t="str">
-        <x:v>Underwater invasion</x:v>
+        <x:v>Water-level tug-of-war</x:v>
       </x:c>
       <x:c r="H44" s="31" t="str">
-        <x:v>Area control</x:v>
+        <x:v>Rooftop control-panel sequence</x:v>
       </x:c>
       <x:c r="I44" s="31" t="str">
-        <x:v>Upper/lower Atlantean shots</x:v>
+        <x:v>Three upper targets, upper spinner, both upper exits</x:v>
       </x:c>
       <x:c r="J44" s="31" t="str">
-        <x:v>Relic/kingdom jackpots</x:v>
+        <x:v>100K lit targets; 25K unlit targets/exits; 10K spins; optional 100K spinner Jackpot</x:v>
       </x:c>
       <x:c r="K44" s="31" t="str">
-        <x:v>Dome and sinking pressure</x:v>
+        <x:v>20-second inactivity/danger countdown; exits reverse target progress</x:v>
       </x:c>
       <x:c r="L44" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>Water level 0 victory / level-8 timer expiry / ball drain</x:v>
       </x:c>
       <x:c r="M44" s="31" t="str">
-        <x:v>Atlantean lost-world objective role.</x:v>
+        <x:v>Distinct Chapter 9 vertical-depth struggle: targets raise Manhattan while rooftop exits and inactivity sink it.</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -3659,10 +3659,10 @@
         <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="B10" s="31" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C10" s="31" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
         <x:v>Invasion from Everywhere</x:v>
@@ -6375,10 +6375,10 @@
         <x:v>Doctor Atlantean</x:v>
       </x:c>
       <x:c r="G44" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H44" s="31" t="str">
-        <x:v>Atlantean invasion from Up from Nowhere; attempts to dome Manhattan and sink ...</x:v>
+        <x:v>Manhattan starts at water level 6 after a four-second bottom-up GI sinking animation. Pulsing green upper targets each score 100K and lower one of eight water levels; upper exits score 25K and raise one level. Target/spinner activity resets the 20-second water timer. Reach level 0 to win; a full timeout at level 8 loses.</x:v>
       </x:c>
       <x:c r="I44" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -8840,16 +8840,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F44" s="31" t="str">
-        <x:v>Placeholder framework for underwater invasion with area control, using Upper/lower Atlantean shots.</x:v>
+        <x:v>After a four-second six-band sinking animation, all three upper control-panel targets pulse green. A lit target lowers the water one level and goes dark; all three relight after a completed set.</x:v>
       </x:c>
       <x:c r="G44" s="31" t="str">
-        <x:v>Ends when goals completed / ball end.</x:v>
+        <x:v>Reach water level 0 to raise Manhattan and win. Either upper exit raises the water one level. Below level 8, timer expiry raises it one level; at level 8, timer expiry ends the mode. Ball drain also stops play.</x:v>
       </x:c>
       <x:c r="H44" s="31" t="str">
-        <x:v>Relic/kingdom jackpots. Dome and sinking pressure.</x:v>
+        <x:v>Water range 0-8; starts at 6. Lit targets score 100K (125K Bigger), unlit targets and exits 25K, upper spinner 10K. More Time = 30-second timers; Safety Net = 10-second save; More Jackpots lights the next spin for 100K after each target set; Shot Assist converts the first unlit target.</x:v>
       </x:c>
       <x:c r="I44" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented with eight-band orange/blue GI water display, four-second opening sink, pulsing target cycle, upper-activity timer resets, persistent roof access, Case Files, status, and summary values; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="45">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9ec085794ff74e3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R5da44a6a857a4123"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R53f2dd4528d04e30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rf51f67c90bb8492d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R6cc673f61cac4227"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rae8956caea5e4030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R28b5f6d5cece45d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rfb34438123714351"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R083e91fa970342fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R4ad8720095ef4d73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R9142b16c57fe4fac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R987d69c443df43c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R40dfbfb4768e45b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R731cd3474cdf476d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R9bc4323bfc824a67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rf4c1c38b9c334bd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R88405f39824a4e51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R4889701d817c4935"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R72a00705d1b543b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rf99c0f85273f4456"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R2c164f25791f459f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R3fb5cc911d704d7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rde2f166846ed4d20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rbf49ac58fb2f4ac4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R910ed777c2a04183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R1968b18c06f24510"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -641,7 +641,7 @@
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Lost Worlds now has four substantively coded villain modes after Doctor Atlantean's finalized water-level control-panel implementation. Across all chapters, 48 of 55 regular villain modes have substantive implementations.</x:v>
+        <x:v>The Spider-Men now has a substantive Homeworld Ray alignment implementation. Across all chapters, 49 of 55 regular villain modes have substantive implementations.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -2948,31 +2948,31 @@
         <x:v>The Spider-Men</x:v>
       </x:c>
       <x:c r="E55" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F55" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G55" s="31" t="str">
-        <x:v>Identity / alien doubles</x:v>
+        <x:v>Pattern completion</x:v>
       </x:c>
       <x:c r="H55" s="31" t="str">
-        <x:v>Mystery / precision</x:v>
+        <x:v>Flipper rotation + timer</x:v>
       </x:c>
       <x:c r="I55" s="31" t="str">
-        <x:v>Changing Spider-Man shots</x:v>
+        <x:v>3 saucers + Star + A/B; optional center web</x:v>
       </x:c>
       <x:c r="J55" s="31" t="str">
-        <x:v>Identity jackpots / Super</x:v>
+        <x:v>100K/150K alignment JPs; sixth 2X; 25K Fine Adjustments; 500K Super</x:v>
       </x:c>
       <x:c r="K55" s="31" t="str">
-        <x:v>Wrong-identity pressure</x:v>
+        <x:v>40s/60s proton countdown after first Jackpot</x:v>
       </x:c>
       <x:c r="L55" s="31" t="str">
-        <x:v>Goals or mistake limit / ball end</x:v>
+        <x:v>6 aligned / proton timeout / ball end</x:v>
       </x:c>
       <x:c r="M55" s="31" t="str">
-        <x:v>Home episode role; should resolve the alien encounter rather than treat them as conventional villains.</x:v>
+        <x:v>Home is treated as a rescue/cooperation story: align the Homeworld Ray and send the Spider-Men home rather than defeating them.</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -3735,10 +3735,10 @@
         <x:v>Dimensional Finale</x:v>
       </x:c>
       <x:c r="B12" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C12" s="31" t="n">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="31" t="n">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="D12" s="31" t="str">
         <x:v>Time-Tossed Showdown</x:v>
@@ -6727,10 +6727,10 @@
         <x:v>The Spider-Men</x:v>
       </x:c>
       <x:c r="G55" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H55" s="31" t="str">
-        <x:v>Alien Spider-Men from Home. Placeholder rules retained; final design should f...</x:v>
+        <x:v>Align six flipper-rotated skill-shot positions before the 40s proton timer expires (60s with More Time). Pulsing positions score 100K/150K and turn solid red; the sixth is double. Solid hits score 25K Fine Adjustments. More Jackpots adds a 10s, 500K center-web Super. Gate remains closed; GI builds from 303000 to FFFF00.</x:v>
       </x:c>
       <x:c r="I55" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -7416,7 +7416,7 @@
         <x:v>The Spider-Men</x:v>
       </x:c>
       <x:c r="D22" s="31" t="str">
-        <x:v>Unverified Micro-Men placeholder replaced by the alien Spider-Men from Home.</x:v>
+        <x:v>Unverified Micro-Men placeholder replaced by the alien Spider-Men from Home; now implemented as the six-position Homeworld Ray alignment mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -9159,16 +9159,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F55" s="31" t="str">
-        <x:v>Placeholder framework for identity / alien doubles with mystery / precision, using Changing Spider-Man shots.</x:v>
+        <x:v>All six skill-shot positions pulse red. Flippers rotate the complete/incomplete pattern; hitting a pulsing position locks it solid.</x:v>
       </x:c>
       <x:c r="G55" s="31" t="str">
-        <x:v>Ends when goals or mistake limit / ball end.</x:v>
+        <x:v>First Jackpot starts a 40s timer (60s with More Time). Six alignments complete the mode, or start the optional 10s center-web Super; proton timeout fails and ball end stops play.</x:v>
       </x:c>
       <x:c r="H55" s="31" t="str">
-        <x:v>Identity jackpots / Super. Wrong-identity pressure.</x:v>
+        <x:v>Alignment Jackpots are 100K (150K Bigger), sixth is 2X, solid-position Fine Adjustments are 25K, and the More Jackpots Super is a fixed 500K.</x:v>
       </x:c>
       <x:c r="I55" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented; needs on-machine playtest. Red six-shot pattern, progressive yellow GI, closed rooftop gate, summary stats, and all five Case Files are coded.</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -9654,10 +9654,10 @@
         <x:v>Current full codebase</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>ASM67_2026_08_08_7pm.zip</x:v>
+        <x:v>GitHub main 085f99beabe055906d2feb2d06824e67fbd7845b</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
-        <x:v>Current source-of-truth full ZIP supplied by the user; includes the music rebalance and subsequent August 8 work.</x:v>
+        <x:v>Current source-of-truth repository revision requested by the user; includes Doctor Atlantean and is the base for The Spider-Men implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R731cd3474cdf476d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R9bc4323bfc824a67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rf4c1c38b9c334bd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R88405f39824a4e51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R4889701d817c4935"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R72a00705d1b543b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rf99c0f85273f4456"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R2c164f25791f459f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R3fb5cc911d704d7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rde2f166846ed4d20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rbf49ac58fb2f4ac4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R910ed777c2a04183"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R1968b18c06f24510"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc01410c64c6d4ab0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R6b67fa302e3c470e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R5928455558fd42cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R81ffc9af1a614765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R8363abc8bb84441b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R9e3b6c4369a74503"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R4765ea4f7fbd4cd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rb717ef613b654830"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rbf2a8540c80b45a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R0f5b6b3dccc9410f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rfd90de6df6e14c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R9fb033af3a0345a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R100e89a10ee74929"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -641,7 +641,7 @@
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>The Spider-Men now has a substantive Homeworld Ray alignment implementation. Across all chapters, 49 of 55 regular villain modes have substantive implementations.</x:v>
+        <x:v>DeVargas now has a substantive City of Gold score-attack implementation. Across all chapters, 50 of 55 regular villain modes have substantive implementations.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -2538,31 +2538,31 @@
         <x:v>DeVargas</x:v>
       </x:c>
       <x:c r="E45" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F45" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G45" s="31" t="str">
-        <x:v>Hidden city / gold</x:v>
+        <x:v>Timed score attack / bonus collection</x:v>
       </x:c>
       <x:c r="H45" s="31" t="str">
-        <x:v>Build-and-cash</x:v>
+        <x:v>Twenty independently expiring gold opportunities (25 with More Jackpots)</x:v>
       </x:c>
       <x:c r="I45" s="31" t="str">
-        <x:v>Cloud City and golden-defense shots</x:v>
+        <x:v>Two webs, two pops, two banks, four A/B rollovers, grouped upper targets, main spinner, upper spinner</x:v>
       </x:c>
       <x:c r="J45" s="31" t="str">
-        <x:v>devargas_bonus bank</x:v>
+        <x:v>150K/125K/100K by phase; Bigger Jackpots awards 200K/175K/150K; full value banks as DEVARGAS GOLD</x:v>
       </x:c>
       <x:c r="K45" s="31" t="str">
-        <x:v>Golden eagle / city defenses</x:v>
+        <x:v>New selection every 8 seconds or on a hit; phases accelerate from slow to medium to fast; first expiry can be assisted</x:v>
       </x:c>
       <x:c r="L45" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>All opportunities resolve or ball drains; no failure state</x:v>
       </x:c>
       <x:c r="M45" s="31" t="str">
-        <x:v>Cloud City of Gold gives Chapter 8 its hidden-mountain kingdom role.</x:v>
+        <x:v>Distinct Chapter 9 pure score attack; needs machine playtest for overlap readability, pulse speeds, gate timing and bank-rubber coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -3659,10 +3659,10 @@
         <x:v>Lost Worlds</x:v>
       </x:c>
       <x:c r="B10" s="31" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C10" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
         <x:v>Invasion from Everywhere</x:v>
@@ -6407,10 +6407,10 @@
         <x:v>DeVargas</x:v>
       </x:c>
       <x:c r="G45" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H45" s="31" t="str">
-        <x:v>Ruler of the hidden Cloud City of Gold. Former Chapter 8 open placeholder ret...</x:v>
+        <x:v>City of Gold pure score attack. Twenty timed opportunities (25 with More Jackpots) cycle through 13 repeatable shot groups. Gold scores 150K/125K/100K by pulse phase, or 200K/175K/150K with Bigger Jackpots, and banks in full as devargas_bonus. More Time changes the phases from 4s/3s/3s to 5s/4s/4s while the selection interval stays 8s.</x:v>
       </x:c>
       <x:c r="I45" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -8869,17 +8869,18 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F45" s="31" t="str">
-        <x:v>Placeholder framework for hidden city / gold with build-and-cash, using Cloud City and golden-defense shots.</x:v>
+        <x:v>20 timed gold opportunities from 13 repeatable shot groups; new shot every 8s or immediately after a collection</x:v>
       </x:c>
       <x:c r="G45" s="31" t="str">
-        <x:v>Ends when goals completed / ball end.</x:v>
+        <x:v>Opportunity 20 resolves or ball drains</x:v>
       </x:c>
       <x:c r="H45" s="31" t="str">
-        <x:v>devargas_bonus bank. Golden eagle / city defenses.</x:v>
+        <x:v>150K/125K/100K by phase and full-value DEVARGAS GOLD banking. More JP: 25 opportunities; Bigger: 200K/175K/150K; More Time: 5s/4s/4s; Safety: 10s save; Assist: first expiry auto-collects.</x:v>
       </x:c>
       <x:c r="I45" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
-      </x:c>
+        <x:v>Implemented with 13 independent pulsing shot shows, full-value DEVARGAS GOLD banking, upper-shot gate ownership, neutral device ejects, Case Files, status and summary values; needs on-machine playtest.</x:v>
+      </x:c>
+      <x:c r="J45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="31" t="n">
@@ -9543,7 +9544,7 @@
         <x:v>Chapter 5–11 bonus banks</x:v>
       </x:c>
       <x:c r="C15" s="45" t="str">
-        <x:v>Fiddler Ransom is structurally wired. Implement earning rules for fiddler_bonus and later banks: super_swami_bonus, dumpty_bonus, blotto_bonus, devargas_bonus, swamp_bonus, and technician_bonus.</x:v>
+        <x:v>Fiddler Ransom is structurally wired and DeVargas Gold now has its full earning rule. Implement earning rules for fiddler_bonus and later banks: super_swami_bonus, dumpty_bonus, blotto_bonus, swamp_bonus, and technician_bonus.</x:v>
       </x:c>
       <x:c r="D15" s="45" t="str">
         <x:v>Future</x:v>
@@ -9654,10 +9655,10 @@
         <x:v>Current full codebase</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>GitHub main 085f99beabe055906d2feb2d06824e67fbd7845b</x:v>
+        <x:v>GitHub main fedcfdbe74bd756b1a2a81b7df8a7cc64f8fac0d</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
-        <x:v>Current source-of-truth repository revision requested by the user; includes Doctor Atlantean and is the base for The Spider-Men implementation.</x:v>
+        <x:v>Current source-of-truth repository revision requested by the user; includes The Spider-Men and is the base for the DeVargas City of Gold implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9982,7 +9983,7 @@
         <x:v>DEVARGAS GOLD</x:v>
       </x:c>
       <x:c r="G10" s="31" t="str">
-        <x:v>Former Chapter 9 placeholder bonus bank reassigned to DeVargas; scoring rules will be finalized during design.</x:v>
+        <x:v>Implemented. Every timed gold award scores immediately and adds its full 150K/125K/100K value (200K/175K/150K with Bigger Jackpots) to devargas_bonus.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc01410c64c6d4ab0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R6b67fa302e3c470e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R5928455558fd42cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R81ffc9af1a614765"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R8363abc8bb84441b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R9e3b6c4369a74503"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R4765ea4f7fbd4cd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rb717ef613b654830"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rbf2a8540c80b45a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R0f5b6b3dccc9410f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rfd90de6df6e14c57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R9fb033af3a0345a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R100e89a10ee74929"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rdedbf4a71980492f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R578158f454934092"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Re977032c79d44d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R60cd800bce1f4ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R1183d6e005b14021"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R31497bd91a0b46c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R565931a00a4146ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rd8c6351e2cc9401f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R5bc902304d5e468f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R2b62bdd69d314dd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rf5130248ffad48a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Ra09f3f4ccf074cbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R362303a6caa840c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1610,7 +1610,7 @@
         <x:v>Whole playfield + saucers + VUK</x:v>
       </x:c>
       <x:c r="J22" s="31" t="str">
-        <x:v>Area-built VUK jackpot</x:v>
+        <x:v>Area-built repeatable VUK jackpots; each full value also banks as HARLEY JACKPOTS</x:v>
       </x:c>
       <x:c r="K22" s="31" t="str">
         <x:v>Multiball control and parallel area progress</x:v>
@@ -2020,7 +2020,7 @@
         <x:v>Hidden/revealed shots + saucers</x:v>
       </x:c>
       <x:c r="J32" s="31" t="str">
-        <x:v>Secret-shot jackpots</x:v>
+        <x:v>Secret-shot Jackpot plus uncapped upper-spinner build; each 25K/50K effective increment banks as INVISIBLE FORTUNE</x:v>
       </x:c>
       <x:c r="K32" s="31" t="str">
         <x:v>Hidden info / wrong routing</x:v>
@@ -3207,16 +3207,16 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="31" t="str">
-        <x:v>Fiddler bonus</x:v>
+        <x:v>Open-ended chapter bonuses</x:v>
       </x:c>
       <x:c r="B6" s="31" t="str">
         <x:v>Keep</x:v>
       </x:c>
       <x:c r="C6" s="31" t="str">
-        <x:v>fiddler_bonus</x:v>
+        <x:v>harley_bonus, noah_boddy_bonus</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
-        <x:v>Persistent end-of-ball Chapter 5 bonus bank.</x:v>
+        <x:v>Persistent end-of-ball banks owned by Harley Clivendon's repeatable VUK loop and Noah Boddy's uncapped upper-spinner build.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5674,7 +5674,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H22" s="31" t="str">
-        <x:v>Custom 2-ball area-control multiball. A saucer holds a ball while independent playfield areas are lit; enough lit areas qualify the VUK jackpot, whose value reflects area progress.</x:v>
+        <x:v>Custom 2-ball area-control multiball. A saucer holds a ball while independent playfield areas are lit; enough lit areas qualify a repeatable VUK jackpot. Every VUK jackpot also adds its full value to the persistent harley_bonus bank shown as HARLEY JACKPOTS.</x:v>
       </x:c>
       <x:c r="I22" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -5994,7 +5994,7 @@
         <x:v>Implemented repurpose / needs polish</x:v>
       </x:c>
       <x:c r="H32" s="31" t="str">
-        <x:v>Repurposed Mole Man concept; invisible/reveal/secret-shot mechanics.</x:v>
+        <x:v>Invisible-target search. Upper targets eliminate false lower drops while the upper spinner builds the Secret Jackpot. Each spinner hit also banks the effective 25K increase, or 50K with Bigger Jackpots, in persistent noah_boddy_bonus as INVISIBLE FORTUNE.</x:v>
       </x:c>
       <x:c r="I32" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -8208,10 +8208,10 @@
         <x:v>Continues through multiball and ends when its objectives are completed, multiball ends, or the ball ends.</x:v>
       </x:c>
       <x:c r="H22" s="31" t="str">
-        <x:v>Custom area-control multiball. Jackpot value is based on lit-area progress; collecting at the VUK releases the held ball.</x:v>
+        <x:v>Area hits score 50K. Repeatable VUK Jackpots are worth 100K per lit area, or 150K with Bigger, and add their full value to persistent HARLEY JACKPOTS.</x:v>
       </x:c>
       <x:c r="I22" s="31" t="str">
-        <x:v>Implemented; needs on-machine playtest and presentation polish.</x:v>
+        <x:v>Implemented with repeatable lock-area-VUK rounds, full-value harley_bonus banking, Case Files, status, and summary values; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -8492,16 +8492,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F32" s="31" t="str">
-        <x:v>Reveal and solve secret-shot objectives using the invisible/reveal mechanic.</x:v>
+        <x:v>Reach the roof, use upper targets to eliminate false lower drops, and spin to build the Secret Jackpot before collecting the revealed target.</x:v>
       </x:c>
       <x:c r="G32" s="31" t="str">
-        <x:v>Ends when secret/reveal objectives are solved; otherwise stops on ball end.</x:v>
+        <x:v>Completes on the Secret Jackpot; fails if its hurry-up expires. An early roof exit or premature lower drop collapses the search and requires another roof trip.</x:v>
       </x:c>
       <x:c r="H32" s="31" t="str">
-        <x:v>Invisible/reveal/secret-shot mechanics repurposed from the Mole Man concept.</x:v>
+        <x:v>Upper targets score 25K, or 75K with More Jackpots. Each upper spin increases the displayed Jackpot by 25K, or effectively 50K with Bigger, and banks that increment as persistent INVISIBLE FORTUNE.</x:v>
       </x:c>
       <x:c r="I32" s="31" t="str">
-        <x:v>Good: reveal/hurry-up status and state-change messaging are present.</x:v>
+        <x:v>Implemented with reveal cycles, uncapped spinner building, noah_boddy_bonus banking, hurry-up, Case Files, status, and summary values; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -9544,7 +9544,7 @@
         <x:v>Chapter 5–11 bonus banks</x:v>
       </x:c>
       <x:c r="C15" s="45" t="str">
-        <x:v>Fiddler Ransom is structurally wired and DeVargas Gold now has its full earning rule. Implement earning rules for fiddler_bonus and later banks: super_swami_bonus, dumpty_bonus, blotto_bonus, swamp_bonus, and technician_bonus.</x:v>
+        <x:v>Harley Jackpots, Super Swami, Blotto Rampage, DeVargas Gold, and Invisible Fortune have earning rules. Implement the remaining later banks: swamp_bonus and technician_bonus.</x:v>
       </x:c>
       <x:c r="D15" s="45" t="str">
         <x:v>Future</x:v>
@@ -9685,13 +9685,13 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="31" t="str">
-        <x:v>Fiddler bonus patch</x:v>
+        <x:v>Persistent bonus history</x:v>
       </x:c>
       <x:c r="B5" s="31" t="str">
         <x:v>/mnt/data/ASM67_2026_07_24_fiddler_persistent_bonus_changed_files_only.zip</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>Adds the persistent fiddler_bonus structure.</x:v>
+        <x:v>Originally added the Chapter 5 bank structure; current code reassigns it to Harley Clivendon and assigns Chapter 7 to Dr. Noah Boddy.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -9879,19 +9879,19 @@
         <x:v>Danger Lurks</x:v>
       </x:c>
       <x:c r="C6" s="31" t="str">
-        <x:v>Fiddler</x:v>
+        <x:v>Harley Clivendon</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
-        <x:v>fiddler</x:v>
+        <x:v>harley_clivendon</x:v>
       </x:c>
       <x:c r="E6" s="31" t="str">
-        <x:v>fiddler_bonus</x:v>
+        <x:v>harley_bonus</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
-        <x:v>FIDDLER RANSOM</x:v>
+        <x:v>HARLEY JACKPOTS</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Persistent Chapter 5 bonus bank. Initialized for every player, included in the custom and end-of-ball bonus systems, cleared after collection unless held, and shown on Fiddler's summary. The full mode will define how ransom is earned.</x:v>
+        <x:v>Implemented. Every repeatable VUK jackpot adds its full 100K-per-area value (150K per area with Bigger Jackpots) to harley_bonus.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -9925,19 +9925,19 @@
         <x:v>Mad Science</x:v>
       </x:c>
       <x:c r="C8" s="31" t="str">
-        <x:v>Doctor Dumpty</x:v>
+        <x:v>Dr. Noah Boddy</x:v>
       </x:c>
       <x:c r="D8" s="31" t="str">
-        <x:v>doctor_dumpty</x:v>
+        <x:v>noah_boddy</x:v>
       </x:c>
       <x:c r="E8" s="31" t="str">
-        <x:v>dumpty_bonus</x:v>
+        <x:v>noah_boddy_bonus</x:v>
       </x:c>
       <x:c r="F8" s="31" t="str">
-        <x:v>DUMPTY DEVICES</x:v>
+        <x:v>INVISIBLE FORTUNE</x:v>
       </x:c>
       <x:c r="G8" s="31" t="str">
-        <x:v>Planned/declared Chapter 7 bank.</x:v>
+        <x:v>Implemented. Every upper-spinner hit banks the effective Jackpot increase: 25K normally or 50K with Bigger Jackpots.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rdedbf4a71980492f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R578158f454934092"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Re977032c79d44d05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R60cd800bce1f4ab1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R1183d6e005b14021"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R31497bd91a0b46c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R565931a00a4146ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rd8c6351e2cc9401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R5bc902304d5e468f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R2b62bdd69d314dd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rf5130248ffad48a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Ra09f3f4ccf074cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R362303a6caa840c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R89478c6a8b334739"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rd087a143a2354182"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Re80caf44a5ca4fc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R3fe94cd96c724e80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R67e293e479004dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R84d3f3c3d7b24130"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rdbf1cde324584222"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R494a48112e8e415e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rde54e281408c45b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra050cc5400964f28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R8264d12bd31947e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Ra5016399d8774e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R96dd4bb742b34acf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -641,7 +641,7 @@
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>DeVargas now has a substantive City of Gold score-attack implementation. Across all chapters, 50 of 55 regular villain modes have substantive implementations.</x:v>
+        <x:v>Across all chapters, 50 of 55 regular villains have substantive implementations; five remain placeholders. Mini-wizards: 2 approved/coded, 3 functional but provisional, and 6 placeholder shells. The generic Final Showdown framework exists, but its dedicated Kingpin design/retheme remains unfinished.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -3311,8 +3311,15 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="59" t="str">
         <x:v>Chapter</x:v>
       </x:c>
@@ -3350,7 +3357,7 @@
       <x:c r="Y1" s="56"/>
       <x:c r="Z1" s="56"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="31" t="str">
         <x:v>Classic Rogues</x:v>
       </x:c>
@@ -3364,7 +3371,7 @@
         <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="E2" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Approved/coded — needs playtest</x:v>
       </x:c>
       <x:c r="F2" s="14"/>
       <x:c r="G2" s="14"/>
@@ -3388,7 +3395,7 @@
       <x:c r="Y2" s="14"/>
       <x:c r="Z2" s="14"/>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="31" t="str">
         <x:v>Masked Masterminds</x:v>
       </x:c>
@@ -3402,7 +3409,7 @@
         <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="E3" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Functional provisional — design approval required</x:v>
       </x:c>
       <x:c r="F3" s="14"/>
       <x:c r="G3" s="14"/>
@@ -3426,7 +3433,7 @@
       <x:c r="Y3" s="14"/>
       <x:c r="Z3" s="14"/>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="31" t="str">
         <x:v>Trubble's Monsters</x:v>
       </x:c>
@@ -3440,7 +3447,7 @@
         <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="E4" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Approved/coded — needs playtest</x:v>
       </x:c>
       <x:c r="F4" s="14"/>
       <x:c r="G4" s="14"/>
@@ -3464,7 +3471,7 @@
       <x:c r="Y4" s="14"/>
       <x:c r="Z4" s="14"/>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="31" t="str">
         <x:v>Crime Wave</x:v>
       </x:c>
@@ -3478,7 +3485,7 @@
         <x:v>Crime Wave</x:v>
       </x:c>
       <x:c r="E5" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Functional provisional — design approval required</x:v>
       </x:c>
       <x:c r="F5" s="14"/>
       <x:c r="G5" s="14"/>
@@ -3502,7 +3509,7 @@
       <x:c r="Y5" s="14"/>
       <x:c r="Z5" s="14"/>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="31" t="str">
         <x:v>Danger Lurks</x:v>
       </x:c>
@@ -3516,7 +3523,7 @@
         <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="E6" s="31" t="str">
-        <x:v>Working placeholder — full design needed</x:v>
+        <x:v>Placeholder shell — full design/coding required</x:v>
       </x:c>
       <x:c r="F6" s="14"/>
       <x:c r="G6" s="14"/>
@@ -3540,7 +3547,7 @@
       <x:c r="Y6" s="14"/>
       <x:c r="Z6" s="14"/>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="31" t="str">
         <x:v>Mystic Menace</x:v>
       </x:c>
@@ -3554,7 +3561,7 @@
         <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="E7" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Functional provisional — design approval required</x:v>
       </x:c>
       <x:c r="F7" s="14"/>
       <x:c r="G7" s="14"/>
@@ -3578,7 +3585,7 @@
       <x:c r="Y7" s="14"/>
       <x:c r="Z7" s="14"/>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="31" t="str">
         <x:v>Mad Science</x:v>
       </x:c>
@@ -3592,7 +3599,7 @@
         <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="E8" s="31" t="str">
-        <x:v>Placeholder/simple — full design needed</x:v>
+        <x:v>Placeholder shell — full design/coding required</x:v>
       </x:c>
       <x:c r="F8" s="14"/>
       <x:c r="G8" s="14"/>
@@ -3616,7 +3623,7 @@
       <x:c r="Y8" s="14"/>
       <x:c r="Z8" s="14"/>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="31" t="str">
         <x:v>Elemental Chaos</x:v>
       </x:c>
@@ -3630,7 +3637,7 @@
         <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="E9" s="31" t="str">
-        <x:v>Placeholder/simple — full design needed</x:v>
+        <x:v>Placeholder shell — full design/coding required</x:v>
       </x:c>
       <x:c r="F9" s="14"/>
       <x:c r="G9" s="14"/>
@@ -3654,7 +3661,7 @@
       <x:c r="Y9" s="14"/>
       <x:c r="Z9" s="14"/>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="31" t="str">
         <x:v>Lost Worlds</x:v>
       </x:c>
@@ -3668,7 +3675,7 @@
         <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="E10" s="31" t="str">
-        <x:v>Placeholder/simple — full design needed</x:v>
+        <x:v>Placeholder shell — full design/coding required</x:v>
       </x:c>
       <x:c r="F10" s="14"/>
       <x:c r="G10" s="14"/>
@@ -3692,7 +3699,7 @@
       <x:c r="Y10" s="14"/>
       <x:c r="Z10" s="14"/>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="31" t="str">
         <x:v>Savage Oddities</x:v>
       </x:c>
@@ -3706,7 +3713,7 @@
         <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="E11" s="31" t="str">
-        <x:v>Placeholder/simple — full design needed</x:v>
+        <x:v>Placeholder shell — full design/coding required</x:v>
       </x:c>
       <x:c r="F11" s="14"/>
       <x:c r="G11" s="14"/>
@@ -3730,7 +3737,7 @@
       <x:c r="Y11" s="14"/>
       <x:c r="Z11" s="14"/>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="31" t="str">
         <x:v>Dimensional Finale</x:v>
       </x:c>
@@ -3744,7 +3751,7 @@
         <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="E12" s="31" t="str">
-        <x:v>Placeholder/simple — full design needed</x:v>
+        <x:v>Placeholder shell — full design/coding required</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6814,7 +6821,7 @@
         <x:v>Start Event</x:v>
       </x:c>
       <x:c r="F1" s="40" t="str">
-        <x:v>Case-File / Value Rule</x:v>
+        <x:v>Chapter Case File Jackpot Bonus</x:v>
       </x:c>
       <x:c r="G1" s="40" t="str">
         <x:v>Implementation Notes</x:v>
@@ -6837,10 +6844,10 @@
         <x:v>start_mode_sinister_surge</x:v>
       </x:c>
       <x:c r="F2" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G2" s="31" t="str">
-        <x:v>Implemented; needs continued playtest/polish.</x:v>
+        <x:v>Approved/coded; needs machine playtest and polish.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6860,10 +6867,10 @@
         <x:v>start_mode_mastermind_trap</x:v>
       </x:c>
       <x:c r="F3" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G3" s="31" t="str">
-        <x:v>Implemented; trap objectives and multiball scoring present.</x:v>
+        <x:v>Functional provisional implementation; design review and approval still required.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6883,10 +6890,10 @@
         <x:v>start_mode_trubble_unleashed</x:v>
       </x:c>
       <x:c r="F4" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G4" s="31" t="str">
-        <x:v>Implemented; staged drops, saucers, VUK add-a-ball and multiball flow present.</x:v>
+        <x:v>Approved/coded; needs machine playtest and polish.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6906,10 +6913,10 @@
         <x:v>start_mode_crime_wave</x:v>
       </x:c>
       <x:c r="F5" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G5" s="31" t="str">
-        <x:v>Implemented 3-ball multiball. Five timed villain areas: Plotter/pops, The Fly Twins/upper targets, Fifth Avenue Phantom/right bank, Enforcers/left bank, Doctor Cool/saucers. Gate opens at 3+ lit areas and closes at 1 or 0. Upper exits collect jackpots based on currently lit areas. Saucers hold for 15 seconds.</x:v>
+        <x:v>Functional provisional implementation; design review and approval still required.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6929,10 +6936,10 @@
         <x:v>start_mode_the_web_tightens</x:v>
       </x:c>
       <x:c r="F6" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Working placeholder mini-wizard. Temporary jackpot and Case File values remain in Python/shared mini-wizard variables; no mode-specific display variables are exported to Godot.</x:v>
+        <x:v>Explicit placeholder shell; full design and coding required.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6952,10 +6959,10 @@
         <x:v>start_mode_fifth_dimension_curse</x:v>
       </x:c>
       <x:c r="F7" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G7" s="31" t="str">
-        <x:v>Implemented / needs playtest. Starts 3-ball multiball. Six GI zones stay bright 5s, flicker 3s, then dim independently. VUK jackpots score 500K–1.75M plus the chapter Case File bonus without clearing zones. Upper targets score 100K + 25K per active zone, pulse purple when unhit, turn solid when hit, flash three times on completion, and can award up to three add-a-balls after 3+ zone jackpots. Ends when down to one ball.</x:v>
+        <x:v>Functional provisional implementation; design review and approval still required.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -6975,10 +6982,10 @@
         <x:v>start_mode_mad_science_meltdown</x:v>
       </x:c>
       <x:c r="F8" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G8" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Explicit placeholder shell; full design and coding required.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6998,10 +7005,10 @@
         <x:v>start_mode_nature_strikes_back</x:v>
       </x:c>
       <x:c r="F9" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G9" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Explicit placeholder shell; full design and coding required.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -7021,10 +7028,10 @@
         <x:v>start_mode_invasion_from_everywhere</x:v>
       </x:c>
       <x:c r="F10" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G10" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Explicit placeholder shell; full design and coding required.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -7044,10 +7051,10 @@
         <x:v>start_mode_who_is_the_real_villain</x:v>
       </x:c>
       <x:c r="F11" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G11" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Explicit placeholder shell; full design and coding required.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -7067,10 +7074,10 @@
         <x:v>start_mode_time_tossed_showdown</x:v>
       </x:c>
       <x:c r="F12" s="31" t="str">
-        <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
+        <x:v>No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>Placeholder/simple wizard; needs full design.</x:v>
+        <x:v>Explicit placeholder shell; full design and coding required.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -7093,7 +7100,7 @@
         <x:v>Separate final wizard after all 11 chapter wizards.</x:v>
       </x:c>
       <x:c r="G13" s="31" t="str">
-        <x:v>Existing Final Showdown structure is now reserved for the Kingpin finale and will be rethemed in a later design pass.</x:v>
+        <x:v>Working generic framework; dedicated Kingpin design/retheme remains unfinished.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8048,7 +8055,7 @@
         <x:v>Crime Wave</x:v>
       </x:c>
       <x:c r="C17" s="31" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>plotter</x:v>
       </x:c>
       <x:c r="D17" s="31" t="str">
         <x:v>The Plotter</x:v>
@@ -8077,10 +8084,10 @@
         <x:v>Crime Wave</x:v>
       </x:c>
       <x:c r="C18" s="31" t="str">
-        <x:v>fly_brothers</x:v>
+        <x:v>fly_twins</x:v>
       </x:c>
       <x:c r="D18" s="31" t="str">
-        <x:v>Fly Brothers</x:v>
+        <x:v>The Fly Twins</x:v>
       </x:c>
       <x:c r="E18" s="31" t="str">
         <x:v>2-ball MB</x:v>
@@ -8109,7 +8116,7 @@
         <x:v>fifth_avenue_phantom</x:v>
       </x:c>
       <x:c r="D19" s="31" t="str">
-        <x:v>Fifth Avenue Phantom</x:v>
+        <x:v>The Fifth Avenue Phantom</x:v>
       </x:c>
       <x:c r="E19" s="31" t="str">
         <x:v>1</x:v>
@@ -8396,10 +8403,10 @@
         <x:v>Mystic Menace</x:v>
       </x:c>
       <x:c r="C29" s="31" t="str">
-        <x:v>scarlet_sorcerer</x:v>
+        <x:v>kotep</x:v>
       </x:c>
       <x:c r="D29" s="31" t="str">
-        <x:v>Kotep — The Scarlet Sorcerer</x:v>
+        <x:v>Kotep</x:v>
       </x:c>
       <x:c r="E29" s="31" t="str">
         <x:v>1</x:v>
@@ -8541,10 +8548,10 @@
         <x:v>Mad Science</x:v>
       </x:c>
       <x:c r="C34" s="31" t="str">
-        <x:v>professor_pretoris</x:v>
+        <x:v>professor_pretorius</x:v>
       </x:c>
       <x:c r="D34" s="31" t="str">
-        <x:v>Professor Pretoris</x:v>
+        <x:v>Professor Pretorius</x:v>
       </x:c>
       <x:c r="E34" s="31" t="str">
         <x:v>1</x:v>
@@ -9035,10 +9042,10 @@
         <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="C51" s="31" t="str">
-        <x:v>swamp_reptiles</x:v>
+        <x:v>conners_reptiles</x:v>
       </x:c>
       <x:c r="D51" s="31" t="str">
-        <x:v>Swamp Reptiles</x:v>
+        <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="E51" s="31" t="str">
         <x:v>1</x:v>
@@ -9359,10 +9366,10 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="B2" s="45" t="str">
-        <x:v>Playtest first 4 wizards</x:v>
+        <x:v>Playtest coded mini-wizards</x:v>
       </x:c>
       <x:c r="C2" s="45" t="str">
-        <x:v>Sinister Surge, Mastermind Trap, Trubble Unleashed, Crime Wave.</x:v>
+        <x:v>Sinister Surge and Trubble Unleashed are approved/coded. Mastermind Trap, Crime Wave, and Fifth Dimension Curse are functional but provisional and require design approval as well as playtest.</x:v>
       </x:c>
       <x:c r="D2" s="45" t="str">
         <x:v>Open</x:v>
@@ -9516,10 +9523,10 @@
         <x:v>Documentation</x:v>
       </x:c>
       <x:c r="C13" s="45" t="str">
-        <x:v>Update docs for chapter select, wizard transitions, bonus, lighting, ball save, mode behavior.</x:v>
+        <x:v>Roster, implementation status, wizard Case File rules, mode identities, and the 55-villain Case File matrix were synced to code. Open code gaps documented: Plotter Bigger Jackpots, all Master Technician Case Files, and the loaded legacy daily_bugle_rooftop_riot placeholder.</x:v>
       </x:c>
       <x:c r="D13" s="45" t="str">
-        <x:v>In progress — 3pm consistency cleanup documented on 2026-07-24</x:v>
+        <x:v>Updated 2026-08-12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="38" customHeight="1">
@@ -9527,10 +9534,10 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="B14" s="45" t="str">
-        <x:v>Chapter 5 and 7–11 wizard design</x:v>
+        <x:v>Finish mini-wizard and final-wizard designs</x:v>
       </x:c>
       <x:c r="C14" s="45" t="str">
-        <x:v>Fully design The Web Tightens and replace the placeholder/simple wizard shells for Mad Science Meltdown through Time-Tossed Showdown.</x:v>
+        <x:v>Review 3 functional/provisional mini-wizards; fully design and code 6 placeholder shells; complete the dedicated Kingpin Final Showdown design/retheme. Wizard Case Files add only 20K each to Jackpot/Super Jackpot values (max +500K).</x:v>
       </x:c>
       <x:c r="D14" s="45" t="str">
         <x:v>Future</x:v>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R89478c6a8b334739"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rd087a143a2354182"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Re80caf44a5ca4fc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R3fe94cd96c724e80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R67e293e479004dbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R84d3f3c3d7b24130"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rdbf1cde324584222"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R494a48112e8e415e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rde54e281408c45b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra050cc5400964f28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R8264d12bd31947e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Ra5016399d8774e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R96dd4bb742b34acf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R80efe1b5b2ee401c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Ra4a64596144e4923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R135498b32d194ea8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rd3247ab1cd2b45e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R8757b941ece5498e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rf1bf38ae76614282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R2dc9b2bae21e477f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R2f106d6f23d344fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R7a25dd036068475f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R4a44e84792684584"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R8632eb4ff9854c6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R381f8374976a41f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Rdaf5eb2ae6e048f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -641,7 +641,7 @@
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Across all chapters, 50 of 55 regular villains have substantive implementations; five remain placeholders. Mini-wizards: 2 approved/coded, 3 functional but provisional, and 6 placeholder shells. The generic Final Showdown framework exists, but its dedicated Kingpin design/retheme remains unfinished.</x:v>
+        <x:v>Across all chapters, 52 of 55 regular villains have substantive implementations; three remain placeholders. Mini-wizards: 2 approved/coded, 3 functional but provisional, and 6 placeholder shells. The generic Final Showdown framework exists, but its dedicated Kingpin design/retheme remains unfinished.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -3704,10 +3704,10 @@
         <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="B11" s="31" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C11" s="31" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
         <x:v>Who Is the Real Villain?</x:v>
@@ -6478,10 +6478,10 @@
         <x:v>Charles Cameo</x:v>
       </x:c>
       <x:c r="G47" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H47" s="31" t="str">
-        <x:v>Identity and disguise mode from Double Identity; remains grouped with Brutus.</x:v>
+        <x:v>Double Identity mirrored-shot mode. Complete Pops, Drops, A+B, then the two web targets for a fixed 1M Super. Source sides are random; mirrors are timed. More Jackpots inserts a left/right upper-target pair first. Drop targets and bank rubbers count without forced resets.</x:v>
       </x:c>
       <x:c r="I47" s="31" t="str">
         <x:v>who_is_the_real_villain</x:v>
@@ -6510,10 +6510,10 @@
         <x:v>Brutus</x:v>
       </x:c>
       <x:c r="G48" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H48" s="31" t="str">
-        <x:v>Charles Cameo's bodyguard from Double Identity; direct physical/bashing role.</x:v>
+        <x:v>Get Past the Bodyguard routing mode. Any right drop knocks down the other four and opens all three saucers for 15 seconds. A saucer scores one Artwork Jackpot; any left drop or timeout closes the window and resets the right bank. Three Jackpots defeat Brutus.</x:v>
       </x:c>
       <x:c r="I48" s="31" t="str">
         <x:v>who_is_the_real_villain</x:v>
@@ -8935,16 +8935,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F47" s="31" t="str">
-        <x:v>Placeholder framework for disguise / identity with mystery / reveal, using Changing shots.</x:v>
+        <x:v>Complete mirrored pairs in order: Pops, Drop Banks, A+B, then Web Super. One random side scores first and lights its opposite for a timed follow-up. More Jackpots inserts left/right upper targets first.</x:v>
       </x:c>
       <x:c r="G47" s="31" t="str">
-        <x:v>Ends when goals or mistake limit / ball end.</x:v>
+        <x:v>The opposite web target scores a fixed 1M Super and completes the mode. A drain ends the attempt. Expired mirrors restart only the current pair with completed stages preserved.</x:v>
       </x:c>
       <x:c r="H47" s="31" t="str">
-        <x:v>Impostor jackpots. Wrong identity penalty.</x:v>
+        <x:v>Source shots score 50K and ordinary mirrors 250K. Bigger: 75K/300K; Super stays 1M. More Time: 15s instead of 10s. Safety: 10s save. Assist: first expired mirror auto-collects.</x:v>
       </x:c>
       <x:c r="I47" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented with random source sides, paired lighting, drop-bank rubber support without forced resets, More Jackpots rooftop gate ownership, neutral device handling, Case Files, status, and summary values; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -8964,16 +8964,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F48" s="31" t="str">
-        <x:v>Placeholder framework for strength / bash with build-and-cash, using Drops / targets.</x:v>
+        <x:v>All five right drops start up. Hit any one for 50K; the other four drop automatically and all three saucers light for 15 seconds. A guarded saucer scores 25K. Three Artwork Jackpots defeat Brutus.</x:v>
       </x:c>
       <x:c r="G48" s="31" t="str">
-        <x:v>Ends when goals completed / ball end.</x:v>
+        <x:v>A lit saucer collects one Jackpot and resets the right bank. Any left drop or timeout ends the current window without a Jackpot and resets the bank. A drain ends the attempt; collected artwork remains counted.</x:v>
       </x:c>
       <x:c r="H48" s="31" t="str">
-        <x:v>Bash jackpot build. Shot volume / bank resets.</x:v>
+        <x:v>Artwork Jackpot 250K. More JP: fourth Jackpot required. Bigger: 400K. More Time: 20s. Safety: 10s save. Assist: drop the full right bank 2s after mode start and open the first window.</x:v>
       </x:c>
       <x:c r="I48" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented with guarded/open states, physical right-bank knockdowns protected from duplicate scoring, left-drop interruption, all-saucer guidance, timed reset flow, neutral VUK eject, Case Files, summary values, and Brutus portrait; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -9624,6 +9624,34 @@
         <x:v>Verify two-ball start, closed rooftop gate, three area-to-saucer mappings, per-ball jackpot values, one-use add-a-ball per area, saucer reset/eject timing, one-ball grace, Case Files, widget and cleanup.</x:v>
       </x:c>
       <x:c r="D20" t="str">
+        <x:v>Implemented - needs test</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Playtest Charles Cameo</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Verify random side selection; Pops, Drops/rubbers, A+B and Web Super order; 10s/15s mirror timeout restart; More Jackpots upper pair and gate close; Bigger values; Shot Assist; VUK/saucer ejects; summary and cleanup.</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>Implemented - needs test</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Playtest Brutus</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Verify all right drops start up; one player hit drops the other four only once; all saucers open for 15s/20s; guarded saucer 25K; left drop and timeout close/reset; 250K/400K Jackpots; fourth Artwork with More Jackpots; two-second Shot Assist; VUK eject, lights, summary and cleanup.</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
         <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
@@ -9662,7 +9690,7 @@
         <x:v>Current full codebase</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>GitHub main fedcfdbe74bd756b1a2a81b7df8a7cc64f8fac0d</x:v>
+        <x:v>GitHub main 60d82f30f41ce4614260b2f3ff32fea1adf9aab9</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
         <x:v>Current source-of-truth repository revision requested by the user; includes The Spider-Men and is the base for the DeVargas City of Gold implementation.</x:v>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R80efe1b5b2ee401c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Ra4a64596144e4923"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R135498b32d194ea8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rd3247ab1cd2b45e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R8757b941ece5498e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rf1bf38ae76614282"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R2dc9b2bae21e477f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R2f106d6f23d344fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R7a25dd036068475f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R4a44e84792684584"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R8632eb4ff9854c6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R381f8374976a41f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Rdaf5eb2ae6e048f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0abd9e13cb6747dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rcf4df9ee86ef4b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R05d1afcbac98418d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rd1ac42168d3b4fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R63d3fa1db7ad45df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R025efb9ee7d64c42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R052f1f1e873d4208"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R52165282e2b94de1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R3cc995bad518416e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R1d748622781e4689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R0bb45c070b3d4c11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rceec78434bb3411e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Ra988fc9bf82c4778"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2046,31 +2046,31 @@
         <x:v>Dr. Magneto</x:v>
       </x:c>
       <x:c r="E33" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Implemented redesign / needs playtest</x:v>
       </x:c>
       <x:c r="F33" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" s="31" t="str">
-        <x:v>Rooftop spinner sequence</x:v>
+        <x:v>Staged shot chain</x:v>
       </x:c>
       <x:c r="H33" s="31" t="str">
-        <x:v>Magnetic sweep</x:v>
+        <x:v>Cross-feed circuits</x:v>
       </x:c>
       <x:c r="I33" s="31" t="str">
-        <x:v>Upper spinner + both banks</x:v>
+        <x:v>Slings/inlanes + middle A/B + pops + center web/star</x:v>
       </x:c>
       <x:c r="J33" s="31" t="str">
-        <x:v>50K spin + 50K staged drop + Supers</x:v>
+        <x:v>100K/150K rollovers, 250K pops, 500K/750K Super, optional 250K star</x:v>
       </x:c>
       <x:c r="K33" s="31" t="str">
-        <x:v>Seven-stage sweep; 20s final shot</x:v>
+        <x:v>8/10-second circuit windows and a 16/20-second single-attempt Super</x:v>
       </x:c>
       <x:c r="L33" s="31" t="str">
-        <x:v>Super / timer / ball end</x:v>
+        <x:v>Center-web Super / expiry / ball end</x:v>
       </x:c>
       <x:c r="M33" s="31" t="str">
-        <x:v>Physical bank staging with retry on early roof exit.</x:v>
+        <x:v>Uses underrepresented slings, inlanes, middle rollovers, pops, star, and center web in a readable two-circuit build.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2081,37 +2081,37 @@
         <x:v>Mad Science</x:v>
       </x:c>
       <x:c r="C34" s="31" t="str">
-        <x:v>professor_pretoris</x:v>
+        <x:v>professor_pretorius</x:v>
       </x:c>
       <x:c r="D34" s="31" t="str">
-        <x:v>Professor Pretoris</x:v>
+        <x:v>Professor Pretorius</x:v>
       </x:c>
       <x:c r="E34" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Implemented redesign / needs playtest</x:v>
       </x:c>
       <x:c r="F34" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="31" t="str">
-        <x:v>Spinner build / timed final</x:v>
+        <x:v>Heat management</x:v>
       </x:c>
       <x:c r="H34" s="31" t="str">
-        <x:v>Reactor flood</x:v>
+        <x:v>Four-station build</x:v>
       </x:c>
       <x:c r="I34" s="31" t="str">
-        <x:v>Eight GI bands + webs</x:v>
+        <x:v>Both pops + both drop banks + lower spinner + VUK</x:v>
       </x:c>
       <x:c r="J34" s="31" t="str">
-        <x:v>100K bands + timed Supers</x:v>
+        <x:v>12 hits at 100K/150K, cooling at 50K, fixed 500K VUK Super</x:v>
       </x:c>
       <x:c r="K34" s="31" t="str">
-        <x:v>Eight spins; 20s center-web Super</x:v>
+        <x:v>Every progress hit raises heat; temperature 5+ starts 4/8-second overheat grace</x:v>
       </x:c>
       <x:c r="L34" s="31" t="str">
-        <x:v>Super / timer / ball end</x:v>
+        <x:v>VUK Super / overheat / ball end</x:v>
       </x:c>
       <x:c r="M34" s="31" t="str">
-        <x:v>Strong theatrical red-to-blue GI progression.</x:v>
+        <x:v>Four stations pulse while available and turn solid at three hits; GI accelerates from solid to 100ms with heat.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2743,31 +2743,31 @@
         <x:v>Skymaster</x:v>
       </x:c>
       <x:c r="E50" s="31" t="str">
-        <x:v>Temporary placeholder / redesign required</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F50" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G50" s="31" t="str">
-        <x:v>Generic placeholder</x:v>
+        <x:v>Ordered pursuit</x:v>
       </x:c>
       <x:c r="H50" s="31" t="str">
-        <x:v>Temporary hit count</x:v>
+        <x:v>Spinner-assisted sequence</x:v>
       </x:c>
       <x:c r="I50" s="31" t="str">
-        <x:v>Whole playfield</x:v>
+        <x:v>Eight lower drops + center/left webs</x:v>
       </x:c>
       <x:c r="J50" s="31" t="str">
-        <x:v>Temporary placeholder scoring</x:v>
+        <x:v>100K ordered drops; 500K web Supers</x:v>
       </x:c>
       <x:c r="K50" s="31" t="str">
-        <x:v>No final distinct pressure model</x:v>
+        <x:v>Wrong target resets its bank; 15-second one-attempt Super</x:v>
       </x:c>
       <x:c r="L50" s="31" t="str">
-        <x:v>Temporary goal / ball end</x:v>
+        <x:v>Center Super collected or timer / ball end</x:v>
       </x:c>
       <x:c r="M50" s="31" t="str">
-        <x:v>Do not count as a completed limited-flip mode. Current code explicitly marks Skymaster as temporary and awaiting a distinct non-rooftop redesign.</x:v>
+        <x:v>Distinct non-rooftop ordered-target mode. Upper spinner forces correct drops; direct hits must follow order. More Jackpots adds the left web during the same timed Super window.</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -6030,10 +6030,10 @@
         <x:v>Dr. Magneto</x:v>
       </x:c>
       <x:c r="G33" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Implemented redesign / needs playtest</x:v>
       </x:c>
       <x:c r="H33" s="31" t="str">
-        <x:v>Rooftop magnetic sweep: upper entrance resets both banks; each upper spin sco...</x:v>
+        <x:v>Cross-feed circuits: left sling/inlane lights right-side A, which lights the left pop; right sling/inlane lights left-side B, which lights the right pop. Hit flashing pops to lock them solid; both solid light the 16-second center-web Super.</x:v>
       </x:c>
       <x:c r="I33" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -6062,10 +6062,10 @@
         <x:v>Professor Pretorius</x:v>
       </x:c>
       <x:c r="G34" s="31" t="str">
-        <x:v>Implemented / needs playtest</x:v>
+        <x:v>Implemented redesign / needs playtest</x:v>
       </x:c>
       <x:c r="H34" s="31" t="str">
-        <x:v>Reactor Flood: GI starts red in eight horizontal bands. Each web-spinner hit ...</x:v>
+        <x:v>Reactor management: complete three hits at each pop and three unique hits at each drop bank while every qualifying hit raises heat. The lower spinner cools; 12 reactor hits open the gate and light the 500K VUK Super.</x:v>
       </x:c>
       <x:c r="I34" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -6574,10 +6574,10 @@
         <x:v>Skymaster</x:v>
       </x:c>
       <x:c r="G50" s="31" t="str">
-        <x:v>Temporary placeholder / redesign required</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H50" s="31" t="str">
-        <x:v>Current Python explicitly identifies this as a temporary Skymaster placeholder pending a distinct non-rooftop redesign; generic hit-count gameplay should not be treated as complete.</x:v>
+        <x:v>Complete all eight lower drops in strict left-to-right order. Each upper-spinner spin drops the next required target; the player may advance directly only by hitting that same target. A wrong direct hit resets only that bank, then restores completed targets after 200ms with 200ms staged re-drops. Correct drops score 100K. Completing all eight lights a 15s center-web Super for 500K; expiry ends the one allowed attempt.</x:v>
       </x:c>
       <x:c r="I50" s="31" t="str">
         <x:v>who_is_the_real_villain</x:v>
@@ -7381,7 +7381,7 @@
         <x:v>Skymaster</x:v>
       </x:c>
       <x:c r="D19" s="31" t="str">
-        <x:v>Current mode is explicitly a temporary placeholder pending a distinct non-rooftop Skymaster redesign; do not treat former rooftop rules as final.</x:v>
+        <x:v>Temporary placeholder replaced by the ordered eight-drop Skymaster design, repurposing the former Pretorius spinner-to-web structure with direct-hit order validation and bank restoration.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -8528,16 +8528,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F33" s="31" t="str">
-        <x:v>Reach the roof and spin through left drops 1–3 then right drops 1–4, leaving right drop 5 standing.</x:v>
+        <x:v>Left sling/inlane lights right-side A; right sling/inlane lights left-side B. A lights the left pop and B lights the right pop for 8 seconds; hitting a flashing pop locks it solid.</x:v>
       </x:c>
       <x:c r="G33" s="31" t="str">
-        <x:v>Hit right drop 5 within 20 seconds. Early rooftop exit before staging resets both banks.</x:v>
+        <x:v>Both pops solid light the center web for a 16-second Super. Collecting it defeats Magneto; expiry ends the mode unsuccessfully. Ball end also stops the mode.</x:v>
       </x:c>
       <x:c r="H33" s="31" t="str">
-        <x:v>Each spin 50K plus 50K per staged drop; main Super 1M or 1.5M with Bigger.</x:v>
+        <x:v>Lit rollover 100K; flashing pop 250K; center-web Super 500K. Bigger Jackpots changes rollover hits to 150K and the Super to 750K.</x:v>
       </x:c>
       <x:c r="I33" s="31" t="str">
-        <x:v>More Jackpots stages left drop 1 for a 500K Flux Super; More Time 30s; Safety Net at main Super; first spin drops two targets with Shot Assist.</x:v>
+        <x:v>More Jackpots lights the star for 6 seconds and 250K whenever a new objective lights. More Time gives 10-second circuits and a 20-second Super. Safety Net is a 10-second opening save. Shot Assist lights A and B on the first qualifier.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -8557,16 +8557,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F34" s="31" t="str">
-        <x:v>All GI starts red; eight horizontal bands flood blue bottom-to-top, one per web-spinner hit.</x:v>
+        <x:v>Complete three left-pop hits, three right-pop hits, three unique left drops, and the first three unique right drops. Every qualifying reactor hit raises temperature; the lower spinner cools it.</x:v>
       </x:c>
       <x:c r="G34" s="31" t="str">
-        <x:v>After all eight are blue, hit center web within 20 seconds. Ends on Super, timer expiry, or ball end.</x:v>
+        <x:v>The 12th reactor hit immediately opens the gate and lights the VUK Super. Temperature 5+ starts a 4-second grace; cooling to 4 cancels it, while expiry ends the mode. The VUK Super defeats Pretorius.</x:v>
       </x:c>
       <x:c r="H34" s="31" t="str">
-        <x:v>Each converted band 100K. Main Super 1M or 1.5M with Bigger.</x:v>
+        <x:v>Each of the 12 reactor hits scores 100K; each actual cooling spin scores 50K; the VUK Super is 500K. Bigger Jackpots makes reactor and eligible right-bank hits 150K, while the Super remains 500K.</x:v>
       </x:c>
       <x:c r="I34" s="31" t="str">
-        <x:v>More Jackpots adds a 10-second 500K left-web Overflow Super; More Time 30s; Safety Net at Super; first spin floods two bands with Shot Assist.</x:v>
+        <x:v>More Jackpots scores all five unique right drops, but only the first three add progress and heat. More Time makes overheat grace 8 seconds. Safety Net is a 10-second opening save. Shot Assist drops a random second left target with full score, progress, and heat.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -9022,16 +9022,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F50" s="31" t="str">
-        <x:v>Temporary generic hit-count implementation pending a distinct Skymaster redesign.</x:v>
+        <x:v>Complete left 1-3, then right 1-5 in order. Each upper-spinner spin drops the next target. A correct direct hit also advances. A wrong direct hit resets only that bank and restores its completed targets after 200ms, with 200ms staged re-drops.</x:v>
       </x:c>
       <x:c r="G50" s="31" t="str">
-        <x:v>Ends when the temporary placeholder goal is reached or on ball end.</x:v>
+        <x:v>After all eight drops, the center web is lit for 15s. Center Super defeats Skymaster. Expiry ends the mode unsuccessfully with no second attempt. More Jackpots also lights the left web; each web can score once.</x:v>
       </x:c>
       <x:c r="H50" s="31" t="str">
-        <x:v>The current Python file explicitly labels this a temporary placeholder; the former rooftop limited-flip identity should not be documented as final.</x:v>
+        <x:v>Correct drops 100K; center/left web Supers 500K. Bigger: 150K drops and 750K Supers. More Time: 20s. Safety: opening 10s save. Assist: first upper spin advances two drops.</x:v>
       </x:c>
       <x:c r="I50" s="31" t="str">
-        <x:v>Temporary placeholder; major design and implementation work required.</x:v>
+        <x:v>Implemented with all eight physical drop coils, programmatic-switch guards, strict direct-hit validation, 200ms bank restoration staging, target/web lighting, one-attempt timer, Case Files, status, and summary values; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -9653,6 +9653,34 @@
       </x:c>
       <x:c r="D22" t="str">
         <x:v>Implemented - needs test</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="66" customHeight="1">
+      <x:c r="A23" s="31" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="B23" s="31" t="str">
+        <x:v>Playtest Dr. Magneto and Professor Pretorius redesigns</x:v>
+      </x:c>
+      <x:c r="C23" s="31" t="str">
+        <x:v>Verify Magneto's opposite rollover/pop mapping, objective timers, star relights, Super expiry, and Case Files. Verify Pretorius station counts, assisted physical drop, heat/grace cancellation, GI rates, optional right drops, gate opening on hit 12, and VUK summary hold.</x:v>
+      </x:c>
+      <x:c r="D23" s="31" t="str">
+        <x:v>Implemented - needs test</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="31" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="B24" s="31" t="str">
+        <x:v>Add Case Files to Mystery awards</x:v>
+      </x:c>
+      <x:c r="C24" s="31" t="str">
+        <x:v>Add Case Files to the Mystery award pool after defining eligibility and duplicate/exhaustion handling.</x:v>
+      </x:c>
+      <x:c r="D24" s="31" t="str">
+        <x:v>Design note</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0abd9e13cb6747dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rcf4df9ee86ef4b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R05d1afcbac98418d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rd1ac42168d3b4fa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R63d3fa1db7ad45df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R025efb9ee7d64c42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R052f1f1e873d4208"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R52165282e2b94de1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R3cc995bad518416e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R1d748622781e4689"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R0bb45c070b3d4c11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rceec78434bb3411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Ra988fc9bf82c4778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcf7494480b8a4524"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R4b21348701334b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R1e703278d3fb4319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rafa75c4261bc4150"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rfab60616bddf4323"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R5092dc63c08c40d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Re15b1cec6e754650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rcbbf0e4f07f2457b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R0fd25d4d02bb4765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra1372841388e4c20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R84d368b5d6664c5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R3cac00ce6c604069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R79c7ed90cf67493b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -641,7 +641,7 @@
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Across all chapters, 52 of 55 regular villains have substantive implementations; three remain placeholders. Mini-wizards: 2 approved/coded, 3 functional but provisional, and 6 placeholder shells. The generic Final Showdown framework exists, but its dedicated Kingpin design/retheme remains unfinished.</x:v>
+        <x:v>Across all chapters, 54 of 55 regular villains have substantive implementations; one remains a placeholder. Mini-wizards: 2 approved/coded, 3 functional but provisional, and 6 placeholder shells. The generic Final Showdown framework exists, but its dedicated Kingpin design/retheme remains unfinished.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -2778,10 +2778,10 @@
         <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="C51" s="31" t="str">
-        <x:v>swamp_reptiles</x:v>
+        <x:v>conners_reptiles</x:v>
       </x:c>
       <x:c r="D51" s="31" t="str">
-        <x:v>Swamp Reptiles</x:v>
+        <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="E51" s="31" t="str">
         <x:v>Implemented repurpose / needs polish</x:v>
@@ -2852,7 +2852,7 @@
         <x:v>Knight Must Fall gives the finale a medieval displacement role.</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
+    <x:row r="53" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A53" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -2866,31 +2866,31 @@
         <x:v>Master Vine</x:v>
       </x:c>
       <x:c r="E53" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F53" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G53" s="31" t="str">
-        <x:v>Spreading control</x:v>
+        <x:v>Program-and-collect</x:v>
       </x:c>
       <x:c r="H53" s="31" t="str">
-        <x:v>Hold / lock shots</x:v>
+        <x:v>Upper spinner / timed waves</x:v>
       </x:c>
       <x:c r="I53" s="31" t="str">
-        <x:v>Targets + lanes</x:v>
+        <x:v>Upper spinner + 22 lower objectives</x:v>
       </x:c>
       <x:c r="J53" s="31" t="str">
-        <x:v>Vine spread/cut jackpots</x:v>
+        <x:v>25K spins; 50K/75K lower jackpots</x:v>
       </x:c>
       <x:c r="K53" s="31" t="str">
-        <x:v>Spreading hazard</x:v>
+        <x:v>30s/40s timer resets on spins; three trips upstairs</x:v>
       </x:c>
       <x:c r="L53" s="31" t="str">
-        <x:v>Goals or spread limit / ball end</x:v>
+        <x:v>Third wave timer / ball end</x:v>
       </x:c>
       <x:c r="M53" s="31" t="str">
-        <x:v>Prehistoric Forbidden City and giant-vine role.</x:v>
+        <x:v>Three-wave whole-playfield score attack. Returning upstairs clears the lower program; waves 1–2 remain collectable after expiry until return.</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -3704,10 +3704,10 @@
         <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="B11" s="31" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C11" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
         <x:v>Who Is the Real Villain?</x:v>
@@ -3742,10 +3742,10 @@
         <x:v>Dimensional Finale</x:v>
       </x:c>
       <x:c r="B12" s="31" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C12" s="31" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="31" t="str">
         <x:v>Time-Tossed Showdown</x:v>
@@ -5169,7 +5169,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
-        <x:v>Chaos multiball; banks goblin_bonus; first 10 music assignment retained.</x:v>
+        <x:v>Chaos multiball; saucers score the current Chaos Bonus immediately; no persistent end-of-ball bank; first 10 music assignment retained.</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -5201,7 +5201,7 @@
         <x:v>Implemented / recent rule update</x:v>
       </x:c>
       <x:c r="H7" s="31" t="str">
-        <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpot; ...</x:v>
+        <x:v>Rollovers lock arms; completing the left bank locks one arm and relights the web jackpot; spinner boosts the multiplier. Every collected web jackpot adds 100K to persistent doc_ock_bonus as BREAKOUT BONUS.</x:v>
       </x:c>
       <x:c r="I7" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -6650,7 +6650,7 @@
         <x:v>Time-Tossed Showdown</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
+    <x:row r="53" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A53" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -6670,10 +6670,10 @@
         <x:v>Master Vine</x:v>
       </x:c>
       <x:c r="G53" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H53" s="31" t="str">
-        <x:v>Prehistoric Forbidden City and spreading-vine story from Vine. Full episode-b...</x:v>
+        <x:v>Vine Invasion: the gate starts open. Upper entry starts one of three 30s waves, resets both banks and all lower states, and closes the gate. Each upper-spinner pulse scores 25K, resets the timer, and lights one unique available lower shot from 22 objectives. Lit shots pulse; collected shots score 50K and remain dim solid. Waves 1–2 open the gate on expiry; the third expiry ends the mode. Case Files add a three-shot first spin, 75K jackpots, 40s waves, a first-entry 10s save, and a first-jackpot assist.</x:v>
       </x:c>
       <x:c r="I53" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -7751,7 +7751,7 @@
         <x:v>Ends when multiball ends, or when Goblin objectives complete if reached first.</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
-        <x:v>Chaos multiball; windows alternate between solid/flashing scoring; banks goblin_bonus.</x:v>
+        <x:v>Chaos multiball; windows alternate between solid/flashing scoring; each valid unsafe-phase saucer scores the current Chaos Bonus immediately.</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
         <x:v>Improved: persistent flashing/solid shot counts and stabilized bank status.</x:v>
@@ -7780,7 +7780,7 @@
         <x:v>Ends when Doc Ock is defeated by completing required jackpot/breakout objectives; otherwise stops on ball end.</x:v>
       </x:c>
       <x:c r="H7" s="31" t="str">
-        <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpots; spinner boosts multiplier.</x:v>
+        <x:v>Rollovers lock arms; completing the left bank locks one arm and relights the web jackpot; spinner boosts the multiplier. Each collected web jackpot adds 100K to persistent BREAKOUT BONUS.</x:v>
       </x:c>
       <x:c r="I7" s="31" t="str">
         <x:v>Improved: persistent arm-lock, web-jackpot, and breakout progress.</x:v>
@@ -9092,7 +9092,7 @@
         <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
+    <x:row r="53" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A53" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -9109,17 +9109,18 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F53" s="31" t="str">
-        <x:v>Placeholder framework for spreading control with hold / lock shots, using Targets + lanes.</x:v>
+        <x:v>Gate starts open; upper entry starts each of three timed Vine Invasion waves. The upper spinner programs unique lower objectives and resets the timer.</x:v>
       </x:c>
       <x:c r="G53" s="31" t="str">
-        <x:v>Ends when goals or spread limit / ball end.</x:v>
+        <x:v>Waves 1–2 expire into an open-gate return phase; the third 30s/40s expiry completes the mode. Ball end also stops it.</x:v>
       </x:c>
       <x:c r="H53" s="31" t="str">
-        <x:v>Vine spread/cut jackpots. Spreading hazard.</x:v>
+        <x:v>Spinner 25K. Programmed lower shots pulse and score 50K/75K once per wave, then remain dim solid. The 22-objective pool resets on the next upper entry.</x:v>
       </x:c>
       <x:c r="I53" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
-      </x:c>
+        <x:v>Implemented: live wave/timer/lit/cleared status, hardware-aware lamps, and display naming for the shared left-bank insert.</x:v>
+      </x:c>
+      <x:c r="J53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="31" t="n">
@@ -9669,17 +9670,31 @@
         <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="42" customHeight="1">
+    <x:row r="24" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A24" s="31" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="B24" s="31" t="str">
+        <x:v>Playtest Master Vine — Vine Invasion</x:v>
+      </x:c>
+      <x:c r="C24" s="31" t="str">
+        <x:v>Verify gate open at start; upper-entry reset/close; 30s wave and spinner reset timing; 25K spins; unique 22-shot programming; pulsing-to-dim-solid lamps; shared left-bank guidance; post-expiry collections in waves 1–2; third-expiry completion; saucer/VUK handling; and all five Case Files.</x:v>
+      </x:c>
+      <x:c r="D24" s="31" t="str">
+        <x:v>Implemented - needs test</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="B24" s="31" t="str">
+      <x:c r="B25" t="str">
         <x:v>Add Case Files to Mystery awards</x:v>
       </x:c>
-      <x:c r="C24" s="31" t="str">
+      <x:c r="C25" t="str">
         <x:v>Add Case Files to the Mystery award pool after defining eligibility and duplicate/exhaustion handling.</x:v>
       </x:c>
-      <x:c r="D24" s="31" t="str">
+      <x:c r="D25" t="str">
         <x:v>Design note</x:v>
       </x:c>
     </x:row>
@@ -9867,25 +9882,25 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="31" t="str">
-        <x:v>Classic Rogues</x:v>
+        <x:v>Masked Masterminds</x:v>
       </x:c>
       <x:c r="C3" s="31" t="str">
-        <x:v>Green Goblin</x:v>
+        <x:v>Doctor Octopus</x:v>
       </x:c>
       <x:c r="D3" s="31" t="str">
-        <x:v>goblin</x:v>
+        <x:v>doc_ock</x:v>
       </x:c>
       <x:c r="E3" s="31" t="str">
-        <x:v>goblin_bonus</x:v>
+        <x:v>doc_ock_bonus</x:v>
       </x:c>
       <x:c r="F3" s="31" t="str">
-        <x:v>GOBLIN CHAOS</x:v>
+        <x:v>BREAKOUT BONUS</x:v>
       </x:c>
       <x:c r="G3" s="31" t="str">
-        <x:v>Implemented bank; carries over and is not multiplied by regular bonus X.</x:v>
+        <x:v>Implemented. Every collected web jackpot adds 100K; carries over and is not multiplied by regular bonus X.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcf7494480b8a4524"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R4b21348701334b40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R1e703278d3fb4319"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rafa75c4261bc4150"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rfab60616bddf4323"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R5092dc63c08c40d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Re15b1cec6e754650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rcbbf0e4f07f2457b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R0fd25d4d02bb4765"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra1372841388e4c20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R84d368b5d6664c5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R3cac00ce6c604069"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R79c7ed90cf67493b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Refd875fe476f46bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rfa1a92083b4a4393"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R016ccd116ee4466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R209d2eb190054ba0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rfa24ec36404a44a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R1493e018d4664e27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R460f74445a17470a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R540a8b6c70314d94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rae39970a8be349f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Re65dd910f7214d0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R6e030d978f2e4293"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R66caa01e10f1489b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Rd50d5f4811694ddb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2784,31 +2784,31 @@
         <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="E51" s="31" t="str">
-        <x:v>Implemented repurpose / needs polish</x:v>
+        <x:v>Redesigned / implemented / needs playtest</x:v>
       </x:c>
       <x:c r="F51" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G51" s="31" t="str">
-        <x:v>Banked bonus</x:v>
+        <x:v>Reveal-and-collect</x:v>
       </x:c>
       <x:c r="H51" s="31" t="str">
-        <x:v>Area hazard</x:v>
+        <x:v>Persistent bonus builder</x:v>
       </x:c>
       <x:c r="I51" s="31" t="str">
-        <x:v>Swamp shots</x:v>
+        <x:v>Pops + seven/eight revealed objectives + VUK</x:v>
       </x:c>
       <x:c r="J51" s="31" t="str">
-        <x:v>swamp_bonus bank</x:v>
+        <x:v>25K pops; +50K Swamp Bonus per counted pop; 100K/150K Jackpots; 500K Super</x:v>
       </x:c>
       <x:c r="K51" s="31" t="str">
-        <x:v>Escalating swamp pressure</x:v>
+        <x:v>Random unique objective reveals; gate held closed until final Super</x:v>
       </x:c>
       <x:c r="L51" s="31" t="str">
-        <x:v>Goals completed / ball end</x:v>
+        <x:v>All required Jackpots then VUK Super / ball end</x:v>
       </x:c>
       <x:c r="M51" s="31" t="str">
-        <x:v>Chapter bonus-bank/hazard role.</x:v>
+        <x:v>Distinct Chapter 10 bank-builder: pop action programs the playfield while all visible Jackpot shots remain available until collected.</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -6606,10 +6606,10 @@
         <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="G51" s="31" t="str">
-        <x:v>Implemented repurpose / needs polish</x:v>
+        <x:v>Redesigned / implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H51" s="31" t="str">
-        <x:v>Repurposed Reptilla; real code retained under new name; swamp_bonus bank.</x:v>
+        <x:v>Swamp Rampage: every counted pop scores 25K, banks 50K Swamp Bonus, and reveals one unique random Jackpot from upper A/B, middle A/B, both webs, and grouped saucers. Collect all seven to open the gate for an untimed 500K VUK Super; More Jackpots adds the star.</x:v>
       </x:c>
       <x:c r="I51" s="31" t="str">
         <x:v>who_is_the_real_villain</x:v>
@@ -7143,7 +7143,7 @@
         <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="D2" s="31" t="str">
-        <x:v>Reptilla code repurposed; active key is conners_reptiles.</x:v>
+        <x:v>Former Reptilla slot fully rewritten as Conner's Reptiles — Swamp Rampage.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9051,16 +9051,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F51" s="31" t="str">
-        <x:v>Play the retained Reptilla-style shot flow under the Swamp Reptiles identity.</x:v>
+        <x:v>Each counted pop scores 25K, adds 50K to persistent Swamp Bonus, and reveals one random unique Jackpot: upper A/B, middle A/B, left web, center web, or any saucer as one grouped objective. Pops continue adding bonus after all objectives are revealed.</x:v>
       </x:c>
       <x:c r="G51" s="31" t="str">
-        <x:v>Ends when retained Reptilla-style objectives complete; otherwise stops on ball end.</x:v>
+        <x:v>Collect all seven base Jackpots to open the rooftop gate and light the untimed VUK Super. More Jackpots adds the star as an eighth required objective. Only the collected VUK Super defeats the villain.</x:v>
       </x:c>
       <x:c r="H51" s="31" t="str">
-        <x:v>Repurposed Reptilla implementation; swamp_bonus bank preserved under new mode identity.</x:v>
+        <x:v>Jackpots 100K, or 150K with Bigger; VUK Super fixed at 500K. Safety Net 10s; More Time extends it to 20s. Shot Assist makes the first physical pop count twice: 50K score, +100K Swamp Bonus, and two Jackpots revealed.</x:v>
       </x:c>
       <x:c r="I51" s="31" t="str">
-        <x:v>Improved: persistent Rampage, lit-jackpot, collected-jackpot, and Super status.</x:v>
+        <x:v>Implemented rewrite. Starts in PLAYING state; only VUK Super collection posts completion. Gate is forced closed until Super, Daily Bugle VUK handling is suspended, lens-matched objective lamps pulse, and swamp_bonus is earned at 50K per counted pop.</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -9465,13 +9465,13 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="B9" s="45" t="str">
-        <x:v>Light color cleanup</x:v>
+        <x:v>Playtest Conner's Reptiles / light color cleanup</x:v>
       </x:c>
       <x:c r="C9" s="45" t="str">
-        <x:v>Centaur, Diana, Enforcers, Conner's Reptiles; especially tinted right 5-bank/GI colors.</x:v>
+        <x:v>Verify random unique reveals; upper/middle A+B, both webs, grouped saucers and optional star; 25K pop scoring; +50K persistent Swamp Bonus per counted pop before/after Super; 100K/150K Jackpots; gate lockout; untimed 500K VUK Super; 10s/20s save; double-count Shot Assist; lens-matched pulsing; VUK summary hold and cleanup.</x:v>
       </x:c>
       <x:c r="D9" s="45" t="str">
-        <x:v>Open</x:v>
+        <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="38" customHeight="1">
@@ -9549,10 +9549,10 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="B15" s="45" t="str">
-        <x:v>Chapter 5–11 bonus banks</x:v>
+        <x:v>Chapter 11 bonus bank</x:v>
       </x:c>
       <x:c r="C15" s="45" t="str">
-        <x:v>Harley Jackpots, Super Swami, Blotto Rampage, DeVargas Gold, and Invisible Fortune have earning rules. Implement the remaining later banks: swamp_bonus and technician_bonus.</x:v>
+        <x:v>swamp_bonus is implemented for Conner's Reptiles. Decide the Chapter 11 recipient and implement its remaining persistent bonus bank; technician_bonus remains the current placeholder.</x:v>
       </x:c>
       <x:c r="D15" s="45" t="str">
         <x:v>Future</x:v>
@@ -10081,10 +10081,10 @@
         <x:v>swamp_bonus</x:v>
       </x:c>
       <x:c r="F11" s="31" t="str">
-        <x:v>SWAMP REPTILES</x:v>
+        <x:v>SWAMP BONUS</x:v>
       </x:c>
       <x:c r="G11" s="31" t="str">
-        <x:v>Planned/declared Chapter 10 bank.</x:v>
+        <x:v>Implemented. Every counted pop scores 25K immediately and adds 50K to persistent swamp_bonus throughout the mode. Shot Assist makes the first physical pop count twice, adding 100K.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Refd875fe476f46bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rfa1a92083b4a4393"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R016ccd116ee4466c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R209d2eb190054ba0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rfa24ec36404a44a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R1493e018d4664e27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R460f74445a17470a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R540a8b6c70314d94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rae39970a8be349f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Re65dd910f7214d0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R6e030d978f2e4293"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R66caa01e10f1489b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Rd50d5f4811694ddb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd782d4fc07bd4c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R248836aec6994ed2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rcb600799d7994ea9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rfea0e3496a0a4bba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R252f84448fef453f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R52581515ae9c4cdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R523269f1a33a45e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R8aab6a31805d43c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R40451d582d6d4f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R91d5293a09934de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Raf6d1951c56246ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R1e104d2b8f584e96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R29f0de6a94e9419a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -641,7 +641,7 @@
         <x:v>Current focus</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Across all chapters, 54 of 55 regular villains have substantive implementations; one remains a placeholder. Mini-wizards: 2 approved/coded, 3 functional but provisional, and 6 placeholder shells. The generic Final Showdown framework exists, but its dedicated Kingpin design/retheme remains unfinished.</x:v>
+        <x:v>All 55 regular villains now have substantive implementations. Mini-wizards: 2 approved/coded, 3 functional but provisional, and 6 placeholder shells. The generic Final Showdown framework exists, but its dedicated Kingpin design/retheme remains unfinished.</x:v>
       </x:c>
       <x:c r="C5" s="14"/>
       <x:c r="D5" s="10" t="str">
@@ -2825,31 +2825,31 @@
         <x:v>Sir Galahad</x:v>
       </x:c>
       <x:c r="E52" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented — needs playtest</x:v>
       </x:c>
       <x:c r="F52" s="31" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G52" s="31" t="str">
-        <x:v>Medieval time shift</x:v>
+        <x:v>Rooftop score attack</x:v>
       </x:c>
       <x:c r="H52" s="31" t="str">
-        <x:v>Timed duel / sequence</x:v>
+        <x:v>Timed accuracy / bank choice</x:v>
       </x:c>
       <x:c r="I52" s="31" t="str">
-        <x:v>Changing knight and castle shots</x:v>
+        <x:v>Upper exits + opposite drop bank</x:v>
       </x:c>
       <x:c r="J52" s="31" t="str">
-        <x:v>Duel jackpots</x:v>
+        <x:v>100K exits; target values peak at 500K center (750K with Bigger Jackpots)</x:v>
       </x:c>
       <x:c r="K52" s="31" t="str">
-        <x:v>Short combat windows</x:v>
+        <x:v>8s target window; 12s with More Time</x:v>
       </x:c>
       <x:c r="L52" s="31" t="str">
-        <x:v>Goals or timer / ball end</x:v>
+        <x:v>Three resolved jousts; four with More Jackpots</x:v>
       </x:c>
       <x:c r="M52" s="31" t="str">
-        <x:v>Knight Must Fall gives the finale a medieval displacement role.</x:v>
+        <x:v>Gate remains open. Left exit stages right bank on post drop; right exit stages left bank on physical right inlane. Physical target, timeout, or active-window VUK starts center-out collapse.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="211.1999969482422" hidden="0" customHeight="1">
@@ -3742,10 +3742,10 @@
         <x:v>Dimensional Finale</x:v>
       </x:c>
       <x:c r="B12" s="31" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C12" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="31" t="str">
         <x:v>Time-Tossed Showdown</x:v>
@@ -6638,10 +6638,10 @@
         <x:v>Sir Galahad</x:v>
       </x:c>
       <x:c r="G52" s="31" t="str">
-        <x:v>Placeholder/simple active mode</x:v>
+        <x:v>Implemented — needs playtest</x:v>
       </x:c>
       <x:c r="H52" s="31" t="str">
-        <x:v>Knight Must Fall medieval time-displacement slot. Placeholder rules retained ...</x:v>
+        <x:v>Knight Must Fall: 3 rooftop score-attack rounds (4 with More Jackpots). Each 100K upper exit stages the opposite drop bank; an 8s/12s window begins on post drop or the physical right inlane. One physical target scores, then the bank collapses center-out in 500ms steps. VUK or timeout triggers the same no-score collapse. Gate remains open.</x:v>
       </x:c>
       <x:c r="I52" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -9077,19 +9077,19 @@
         <x:v>Sir Galahad</x:v>
       </x:c>
       <x:c r="E52" s="31" t="str">
-        <x:v>1</x:v>
+        <x:v>3 rounds; 4 with More Jackpots</x:v>
       </x:c>
       <x:c r="F52" s="31" t="str">
-        <x:v>Placeholder framework for medieval time shift with timed duel / sequence, using Changing knight and castle shots.</x:v>
+        <x:v>Take a 100K upper exit to stage the opposite bank. Left exit stages the right five-bank after the post drops; right exit stages the left three-bank after the right inlane. Hit one target during the 8s/12s window for its value, then watch the bank collapse center-out.</x:v>
       </x:c>
       <x:c r="G52" s="31" t="str">
-        <x:v>Ends when goals or timer / ball end.</x:v>
+        <x:v>Completes after the third resolved joust, or fourth with More Jackpots. Timeout and active-window VUK still resolve the round without target points.</x:v>
       </x:c>
       <x:c r="H52" s="31" t="str">
-        <x:v>Duel jackpots. Short combat windows.</x:v>
+        <x:v>Exit 100K. Left bank 100K / 500K / 100K; right bank 50K / 100K / 500K / 100K / 50K. Bigger values: 150K / 750K / 150K and 100K / 250K / 750K / 250K / 100K.</x:v>
       </x:c>
       <x:c r="I52" s="31" t="str">
-        <x:v>Placeholder widget and progression state are active; full episode-based rules and presentation remain to be designed.</x:v>
+        <x:v>Implemented with rooftop prompts, countdowns, jackpot messaging, staged knockdowns, value-tier right-bank inserts plus both GI lamps, single left insert plus GI, summary score, and Case File helpers. Needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="250.8000030517578" hidden="0" customHeight="1">
@@ -9696,6 +9696,20 @@
       </x:c>
       <x:c r="D25" t="str">
         <x:v>Design note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="84" customHeight="1">
+      <x:c r="A26" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="str">
+        <x:v>Playtest Sir Galahad — Knight Must Fall</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="str">
+        <x:v>Verify gate-open behavior; 100K exits; opposite-bank staging; post-drop/right-inlane 8s and 12s starts; normal/Bigger target values; target, timeout, and VUK center-out 500ms collapses; More Jackpots fourth round; Safety Net; Shot Assist; bank inserts/GI; prompts, summary, and cleanup.</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="str">
+        <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R102d25045e484381"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R19cd017a9f9b4c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R4a0cfb2156af4b2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R9e82ed7d730844f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R177fc03600f34871"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Re945faf14d7d4a7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R063fc991ce8f4ebf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R27c8f27d742b4d04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R06b50308df0c47dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R7aafa6d27f474a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R963cf9de55124e8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R3dfcf2f106064d2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Rff1d937392c3484f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R61aeb050a7f24a2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Ra8bb6b97086c45c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R2e6ac79506e1412c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R55d480d7b79b4c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R6d9f756896504d96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rc21eae9b2d4d4605"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R087c0e64ad80426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R40dbe8b9ae9c408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R8c11c8ca11b041d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Ra8ac9cf687454906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R44f90e5ce54f48ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R4fbc539441f94a31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R5ee91fa115cb4fb6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -681,10 +681,8 @@
           <x:t xml:space="preserve">Project status</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks is Chapter 5; former Chapters 5–10 are now Chapters 6–11.</x:t>
-        </x:is>
+      <x:c r="B2" s="14" t="str">
+        <x:v>The Web Tightens is Chapter 5; former Chapters 5–10 are now Chapters 6–11.</x:v>
       </x:c>
       <x:c r="C2" s="14" t="n"/>
       <x:c r="D2" s="14" t="inlineStr">
@@ -923,10 +921,8 @@
       <x:c r="A2" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B2" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C2" s="31" t="inlineStr">
         <x:is>
@@ -988,10 +984,8 @@
       <x:c r="A3" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B3" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B3" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C3" s="31" t="inlineStr">
         <x:is>
@@ -1053,10 +1047,8 @@
       <x:c r="A4" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B4" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C4" s="31" t="inlineStr">
         <x:is>
@@ -1118,10 +1110,8 @@
       <x:c r="A5" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B5" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C5" s="31" t="inlineStr">
         <x:is>
@@ -1183,10 +1173,8 @@
       <x:c r="A6" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B6" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C6" s="31" t="inlineStr">
         <x:is>
@@ -1248,10 +1236,8 @@
       <x:c r="A7" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B7" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C7" s="31" t="inlineStr">
         <x:is>
@@ -1313,10 +1299,8 @@
       <x:c r="A8" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B8" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C8" s="31" t="inlineStr">
         <x:is>
@@ -1378,10 +1362,8 @@
       <x:c r="A9" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B9" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C9" s="31" t="inlineStr">
         <x:is>
@@ -1443,10 +1425,8 @@
       <x:c r="A10" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B10" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C10" s="31" t="inlineStr">
         <x:is>
@@ -1508,10 +1488,8 @@
       <x:c r="A11" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B11" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C11" s="31" t="inlineStr">
         <x:is>
@@ -1573,10 +1551,8 @@
       <x:c r="A12" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B12" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C12" s="31" t="inlineStr">
         <x:is>
@@ -1638,10 +1614,8 @@
       <x:c r="A13" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B13" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C13" s="31" t="inlineStr">
         <x:is>
@@ -1703,10 +1677,8 @@
       <x:c r="A14" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B14" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C14" s="31" t="inlineStr">
         <x:is>
@@ -1768,10 +1740,8 @@
       <x:c r="A15" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B15" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B15" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C15" s="31" t="inlineStr">
         <x:is>
@@ -1833,10 +1803,8 @@
       <x:c r="A16" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B16" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C16" s="31" t="inlineStr">
         <x:is>
@@ -2201,10 +2169,8 @@
       <x:c r="A22" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B22" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C22" s="31" t="inlineStr">
         <x:is>
@@ -2266,10 +2232,8 @@
       <x:c r="A23" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B23" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B23" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C23" s="31" t="inlineStr">
         <x:is>
@@ -2331,10 +2295,8 @@
       <x:c r="A24" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B24" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C24" s="31" t="inlineStr">
         <x:is>
@@ -2396,10 +2358,8 @@
       <x:c r="A25" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B25" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C25" s="31" t="inlineStr">
         <x:is>
@@ -2461,10 +2421,8 @@
       <x:c r="A26" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B26" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C26" s="31" t="inlineStr">
         <x:is>
@@ -2526,10 +2484,8 @@
       <x:c r="A27" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B27" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B27" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C27" s="31" t="inlineStr">
         <x:is>
@@ -2591,10 +2547,8 @@
       <x:c r="A28" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B28" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C28" s="31" t="inlineStr">
         <x:is>
@@ -2656,10 +2610,8 @@
       <x:c r="A29" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B29" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B29" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C29" s="31" t="inlineStr">
         <x:is>
@@ -2721,10 +2673,8 @@
       <x:c r="A30" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B30" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B30" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C30" s="31" t="inlineStr">
         <x:is>
@@ -2786,10 +2736,8 @@
       <x:c r="A31" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B31" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B31" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C31" s="31" t="inlineStr">
         <x:is>
@@ -2851,10 +2799,8 @@
       <x:c r="A32" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B32" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B32" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C32" s="31" t="inlineStr">
         <x:is>
@@ -2916,10 +2862,8 @@
       <x:c r="A33" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B33" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B33" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C33" s="31" t="inlineStr">
         <x:is>
@@ -2981,10 +2925,8 @@
       <x:c r="A34" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B34" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B34" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C34" s="31" t="inlineStr">
         <x:is>
@@ -3046,10 +2988,8 @@
       <x:c r="A35" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B35" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B35" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C35" s="31" t="inlineStr">
         <x:is>
@@ -3111,10 +3051,8 @@
       <x:c r="A36" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B36" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C36" s="31" t="inlineStr">
         <x:is>
@@ -3176,10 +3114,8 @@
       <x:c r="A37" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B37" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B37" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C37" s="31" t="inlineStr">
         <x:is>
@@ -3241,10 +3177,8 @@
       <x:c r="A38" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B38" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B38" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C38" s="31" t="inlineStr">
         <x:is>
@@ -3306,10 +3240,8 @@
       <x:c r="A39" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B39" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B39" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C39" s="31" t="inlineStr">
         <x:is>
@@ -3371,10 +3303,8 @@
       <x:c r="A40" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B40" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B40" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C40" s="31" t="inlineStr">
         <x:is>
@@ -3436,10 +3366,8 @@
       <x:c r="A41" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B41" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B41" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C41" s="31" t="inlineStr">
         <x:is>
@@ -3501,10 +3429,8 @@
       <x:c r="A42" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B42" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C42" s="31" t="inlineStr">
         <x:is>
@@ -3566,10 +3492,8 @@
       <x:c r="A43" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B43" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B43" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C43" s="31" t="inlineStr">
         <x:is>
@@ -3631,10 +3555,8 @@
       <x:c r="A44" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B44" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B44" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C44" s="31" t="inlineStr">
         <x:is>
@@ -3696,10 +3618,8 @@
       <x:c r="A45" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B45" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B45" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C45" s="31" t="inlineStr">
         <x:is>
@@ -3761,10 +3681,8 @@
       <x:c r="A46" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B46" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C46" s="31" t="inlineStr">
         <x:is>
@@ -3826,10 +3744,8 @@
       <x:c r="A47" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B47" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B47" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C47" s="31" t="inlineStr">
         <x:is>
@@ -3891,10 +3807,8 @@
       <x:c r="A48" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B48" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B48" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C48" s="31" t="inlineStr">
         <x:is>
@@ -3956,10 +3870,8 @@
       <x:c r="A49" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B49" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B49" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C49" s="31" t="inlineStr">
         <x:is>
@@ -4021,10 +3933,8 @@
       <x:c r="A50" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B50" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B50" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C50" s="31" t="inlineStr">
         <x:is>
@@ -4086,10 +3996,8 @@
       <x:c r="A51" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B51" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B51" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C51" s="31" t="inlineStr">
         <x:is>
@@ -4151,10 +4059,8 @@
       <x:c r="A52" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B52" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B52" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C52" s="31" t="inlineStr">
         <x:is>
@@ -4216,10 +4122,8 @@
       <x:c r="A53" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B53" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B53" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C53" s="31" t="inlineStr">
         <x:is>
@@ -4281,10 +4185,8 @@
       <x:c r="A54" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B54" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C54" s="31" t="inlineStr">
         <x:is>
@@ -4346,10 +4248,8 @@
       <x:c r="A55" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B55" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B55" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C55" s="31" t="inlineStr">
         <x:is>
@@ -4411,10 +4311,8 @@
       <x:c r="A56" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B56" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B56" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C56" s="31" t="inlineStr">
         <x:is>
@@ -4526,10 +4424,8 @@
       <x:c r="Z1" s="56" t="n"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks villains</x:t>
-        </x:is>
+      <x:c r="A2" s="31" t="str">
+        <x:v>The Web Tightens villains</x:v>
       </x:c>
       <x:c r="B2" s="31" t="inlineStr">
         <x:is>
@@ -4942,10 +4838,8 @@
       <x:c r="Z1" s="56" t="n"/>
     </x:row>
     <x:row r="2" s="26" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="A2" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="B2" s="31" t="n">
         <x:v>5</x:v>
@@ -4986,10 +4880,8 @@
       <x:c r="Z2" s="14" t="n"/>
     </x:row>
     <x:row r="3" s="26" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A3" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="A3" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="B3" s="31" t="n">
         <x:v>5</x:v>
@@ -5030,10 +4922,8 @@
       <x:c r="Z3" s="14" t="n"/>
     </x:row>
     <x:row r="4" s="26" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="A4" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="B4" s="31" t="n">
         <x:v>5</x:v>
@@ -5118,10 +5008,8 @@
       <x:c r="Z5" s="14" t="n"/>
     </x:row>
     <x:row r="6" s="26" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="A6" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="B6" s="31" t="n">
         <x:v>5</x:v>
@@ -5162,10 +5050,8 @@
       <x:c r="Z6" s="14" t="n"/>
     </x:row>
     <x:row r="7" s="26" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="A7" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="B7" s="31" t="n">
         <x:v>5</x:v>
@@ -5206,10 +5092,8 @@
       <x:c r="Z7" s="14" t="n"/>
     </x:row>
     <x:row r="8" s="26" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="A8" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="B8" s="31" t="n">
         <x:v>5</x:v>
@@ -5250,10 +5134,8 @@
       <x:c r="Z8" s="14" t="n"/>
     </x:row>
     <x:row r="9" s="26" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="A9" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="B9" s="31" t="n">
         <x:v>5</x:v>
@@ -5294,10 +5176,8 @@
       <x:c r="Z9" s="14" t="n"/>
     </x:row>
     <x:row r="10" s="26" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="A10" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="B10" s="31" t="n">
         <x:v>5</x:v>
@@ -5338,10 +5218,8 @@
       <x:c r="Z10" s="14" t="n"/>
     </x:row>
     <x:row r="11" s="26" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="A11" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="B11" s="31" t="n">
         <x:v>5</x:v>
@@ -5382,10 +5260,8 @@
       <x:c r="Z11" s="14" t="n"/>
     </x:row>
     <x:row r="12" s="26" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="A12" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="B12" s="31" t="n">
         <x:v>5</x:v>
@@ -7102,10 +6978,8 @@
       <x:c r="A2" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B2" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C2" s="31" t="n">
         <x:v>1</x:v>
@@ -7148,10 +7022,8 @@
       <x:c r="A3" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B3" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B3" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C3" s="31" t="n">
         <x:v>2</x:v>
@@ -7194,10 +7066,8 @@
       <x:c r="A4" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B4" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C4" s="31" t="n">
         <x:v>3</x:v>
@@ -7240,10 +7110,8 @@
       <x:c r="A5" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B5" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C5" s="31" t="n">
         <x:v>4</x:v>
@@ -7286,10 +7154,8 @@
       <x:c r="A6" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B6" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C6" s="31" t="n">
         <x:v>5</x:v>
@@ -7332,10 +7198,8 @@
       <x:c r="A7" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B7" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C7" s="31" t="n">
         <x:v>1</x:v>
@@ -7378,10 +7242,8 @@
       <x:c r="A8" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B8" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C8" s="31" t="n">
         <x:v>2</x:v>
@@ -7424,10 +7286,8 @@
       <x:c r="A9" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B9" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C9" s="31" t="n">
         <x:v>3</x:v>
@@ -7470,10 +7330,8 @@
       <x:c r="A10" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B10" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C10" s="31" t="n">
         <x:v>4</x:v>
@@ -7516,10 +7374,8 @@
       <x:c r="A11" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B11" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C11" s="31" t="n">
         <x:v>5</x:v>
@@ -7562,10 +7418,8 @@
       <x:c r="A12" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B12" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C12" s="31" t="n">
         <x:v>1</x:v>
@@ -7608,10 +7462,8 @@
       <x:c r="A13" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B13" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C13" s="31" t="n">
         <x:v>2</x:v>
@@ -7654,10 +7506,8 @@
       <x:c r="A14" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B14" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C14" s="31" t="n">
         <x:v>3</x:v>
@@ -7700,10 +7550,8 @@
       <x:c r="A15" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B15" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B15" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C15" s="31" t="n">
         <x:v>4</x:v>
@@ -7746,10 +7594,8 @@
       <x:c r="A16" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B16" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C16" s="31" t="n">
         <x:v>5</x:v>
@@ -8018,10 +7864,8 @@
       <x:c r="A22" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B22" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C22" s="31" t="n">
         <x:v>1</x:v>
@@ -8064,10 +7908,8 @@
       <x:c r="A23" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B23" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B23" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C23" s="31" t="n">
         <x:v>2</x:v>
@@ -8110,10 +7952,8 @@
       <x:c r="A24" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B24" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C24" s="31" t="n">
         <x:v>3</x:v>
@@ -8156,10 +7996,8 @@
       <x:c r="A25" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B25" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C25" s="31" t="n">
         <x:v>4</x:v>
@@ -8202,10 +8040,8 @@
       <x:c r="A26" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B26" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C26" s="31" t="n">
         <x:v>5</x:v>
@@ -8248,10 +8084,8 @@
       <x:c r="A27" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B27" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B27" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C27" s="31" t="n">
         <x:v>1</x:v>
@@ -8294,10 +8128,8 @@
       <x:c r="A28" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B28" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C28" s="31" t="n">
         <x:v>2</x:v>
@@ -8340,10 +8172,8 @@
       <x:c r="A29" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B29" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B29" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C29" s="31" t="n">
         <x:v>3</x:v>
@@ -8386,10 +8216,8 @@
       <x:c r="A30" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B30" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B30" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C30" s="31" t="n">
         <x:v>4</x:v>
@@ -8432,10 +8260,8 @@
       <x:c r="A31" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B31" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B31" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C31" s="31" t="n">
         <x:v>5</x:v>
@@ -8478,10 +8304,8 @@
       <x:c r="A32" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B32" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B32" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C32" s="31" t="n">
         <x:v>1</x:v>
@@ -8524,10 +8348,8 @@
       <x:c r="A33" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B33" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B33" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C33" s="31" t="n">
         <x:v>2</x:v>
@@ -8570,10 +8392,8 @@
       <x:c r="A34" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B34" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B34" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C34" s="31" t="n">
         <x:v>3</x:v>
@@ -8616,10 +8436,8 @@
       <x:c r="A35" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B35" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B35" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C35" s="31" t="n">
         <x:v>4</x:v>
@@ -8662,10 +8480,8 @@
       <x:c r="A36" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B36" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C36" s="31" t="n">
         <x:v>5</x:v>
@@ -8708,10 +8524,8 @@
       <x:c r="A37" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B37" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B37" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C37" s="31" t="n">
         <x:v>1</x:v>
@@ -8754,10 +8568,8 @@
       <x:c r="A38" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B38" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B38" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C38" s="31" t="n">
         <x:v>2</x:v>
@@ -8800,10 +8612,8 @@
       <x:c r="A39" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B39" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B39" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C39" s="31" t="n">
         <x:v>3</x:v>
@@ -8846,10 +8656,8 @@
       <x:c r="A40" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B40" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B40" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C40" s="31" t="n">
         <x:v>4</x:v>
@@ -8892,10 +8700,8 @@
       <x:c r="A41" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B41" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B41" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C41" s="31" t="n">
         <x:v>5</x:v>
@@ -8938,10 +8744,8 @@
       <x:c r="A42" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B42" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C42" s="31" t="n">
         <x:v>1</x:v>
@@ -8984,10 +8788,8 @@
       <x:c r="A43" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B43" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B43" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C43" s="31" t="n">
         <x:v>2</x:v>
@@ -9030,10 +8832,8 @@
       <x:c r="A44" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B44" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B44" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C44" s="31" t="n">
         <x:v>3</x:v>
@@ -9076,10 +8876,8 @@
       <x:c r="A45" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B45" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B45" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C45" s="31" t="n">
         <x:v>4</x:v>
@@ -9122,10 +8920,8 @@
       <x:c r="A46" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B46" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C46" s="31" t="n">
         <x:v>5</x:v>
@@ -9168,10 +8964,8 @@
       <x:c r="A47" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B47" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B47" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C47" s="31" t="n">
         <x:v>1</x:v>
@@ -9214,10 +9008,8 @@
       <x:c r="A48" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B48" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B48" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C48" s="31" t="n">
         <x:v>2</x:v>
@@ -9260,10 +9052,8 @@
       <x:c r="A49" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B49" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B49" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C49" s="31" t="n">
         <x:v>3</x:v>
@@ -9306,10 +9096,8 @@
       <x:c r="A50" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B50" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B50" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C50" s="31" t="n">
         <x:v>4</x:v>
@@ -9352,10 +9140,8 @@
       <x:c r="A51" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B51" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B51" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C51" s="31" t="n">
         <x:v>5</x:v>
@@ -9398,10 +9184,8 @@
       <x:c r="A52" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B52" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B52" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C52" s="31" t="n">
         <x:v>1</x:v>
@@ -9444,10 +9228,8 @@
       <x:c r="A53" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B53" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B53" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C53" s="31" t="n">
         <x:v>2</x:v>
@@ -9490,10 +9272,8 @@
       <x:c r="A54" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B54" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C54" s="31" t="n">
         <x:v>3</x:v>
@@ -9536,10 +9316,8 @@
       <x:c r="A55" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B55" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B55" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C55" s="31" t="n">
         <x:v>4</x:v>
@@ -9582,10 +9360,8 @@
       <x:c r="A56" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B56" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B56" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C56" s="31" t="n">
         <x:v>5</x:v>
@@ -9691,10 +9467,8 @@
       <x:c r="A2" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B2" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C2" s="31" t="inlineStr">
         <x:is>
@@ -9726,10 +9500,8 @@
       <x:c r="A3" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B3" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C3" s="31" t="inlineStr">
         <x:is>
@@ -9761,10 +9533,8 @@
       <x:c r="A4" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B4" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C4" s="31" t="inlineStr">
         <x:is>
@@ -9831,10 +9601,8 @@
       <x:c r="A6" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B6" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C6" s="31" t="inlineStr">
         <x:is>
@@ -9866,10 +9634,8 @@
       <x:c r="A7" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B7" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C7" s="31" t="inlineStr">
         <x:is>
@@ -9901,10 +9667,8 @@
       <x:c r="A8" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B8" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C8" s="31" t="inlineStr">
         <x:is>
@@ -9936,10 +9700,8 @@
       <x:c r="A9" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B9" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C9" s="31" t="inlineStr">
         <x:is>
@@ -9971,10 +9733,8 @@
       <x:c r="A10" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B10" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C10" s="31" t="inlineStr">
         <x:is>
@@ -10006,10 +9766,8 @@
       <x:c r="A11" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B11" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C11" s="31" t="inlineStr">
         <x:is>
@@ -10041,10 +9799,8 @@
       <x:c r="A12" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B12" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C12" s="31" t="inlineStr">
         <x:is>
@@ -10468,10 +10224,8 @@
           <x:t xml:space="preserve">DeVargas</x:t>
         </x:is>
       </x:c>
-      <x:c r="D16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Former Lost Worlds open placeholder assigned to DeVargas of the Cloud City of Gold.</x:t>
-        </x:is>
+      <x:c r="D16" s="31" t="str">
+        <x:v>Former Invasion from Everywhere open placeholder assigned to DeVargas of the Cloud City of Gold.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -10894,10 +10648,8 @@
       <x:c r="A2" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B2" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C2" s="31" t="inlineStr">
         <x:is>
@@ -10939,10 +10691,8 @@
       <x:c r="A3" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B3" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B3" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C3" s="31" t="inlineStr">
         <x:is>
@@ -10984,10 +10734,8 @@
       <x:c r="A4" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B4" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C4" s="31" t="inlineStr">
         <x:is>
@@ -11029,10 +10777,8 @@
       <x:c r="A5" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B5" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C5" s="31" t="inlineStr">
         <x:is>
@@ -11074,10 +10820,8 @@
       <x:c r="A6" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B6" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C6" s="31" t="inlineStr">
         <x:is>
@@ -11119,10 +10863,8 @@
       <x:c r="A7" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B7" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C7" s="31" t="inlineStr">
         <x:is>
@@ -11164,10 +10906,8 @@
       <x:c r="A8" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B8" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C8" s="31" t="inlineStr">
         <x:is>
@@ -11209,10 +10949,8 @@
       <x:c r="A9" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B9" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C9" s="31" t="inlineStr">
         <x:is>
@@ -11254,10 +10992,8 @@
       <x:c r="A10" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B10" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C10" s="31" t="inlineStr">
         <x:is>
@@ -11299,10 +11035,8 @@
       <x:c r="A11" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B11" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C11" s="31" t="inlineStr">
         <x:is>
@@ -11344,10 +11078,8 @@
       <x:c r="A12" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B12" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C12" s="31" t="inlineStr">
         <x:is>
@@ -11389,10 +11121,8 @@
       <x:c r="A13" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B13" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C13" s="31" t="inlineStr">
         <x:is>
@@ -11434,10 +11164,8 @@
       <x:c r="A14" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B14" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C14" s="31" t="inlineStr">
         <x:is>
@@ -11479,10 +11207,8 @@
       <x:c r="A15" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B15" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B15" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C15" s="31" t="inlineStr">
         <x:is>
@@ -11524,10 +11250,8 @@
       <x:c r="A16" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B16" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C16" s="31" t="inlineStr">
         <x:is>
@@ -11784,10 +11508,8 @@
       <x:c r="A22" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B22" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C22" s="31" t="inlineStr">
         <x:is>
@@ -11829,10 +11551,8 @@
       <x:c r="A23" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B23" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B23" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C23" s="31" t="inlineStr">
         <x:is>
@@ -11874,10 +11594,8 @@
       <x:c r="A24" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B24" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C24" s="31" t="inlineStr">
         <x:is>
@@ -11919,10 +11637,8 @@
       <x:c r="A25" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B25" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C25" s="31" t="inlineStr">
         <x:is>
@@ -11964,10 +11680,8 @@
       <x:c r="A26" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B26" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C26" s="31" t="inlineStr">
         <x:is>
@@ -12009,10 +11723,8 @@
       <x:c r="A27" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B27" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B27" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C27" s="31" t="inlineStr">
         <x:is>
@@ -12054,10 +11766,8 @@
       <x:c r="A28" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B28" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C28" s="31" t="inlineStr">
         <x:is>
@@ -12099,10 +11809,8 @@
       <x:c r="A29" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B29" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B29" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C29" s="31" t="inlineStr">
         <x:is>
@@ -12144,10 +11852,8 @@
       <x:c r="A30" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B30" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B30" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C30" s="31" t="inlineStr">
         <x:is>
@@ -12189,10 +11895,8 @@
       <x:c r="A31" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B31" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B31" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C31" s="31" t="inlineStr">
         <x:is>
@@ -12234,10 +11938,8 @@
       <x:c r="A32" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B32" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B32" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C32" s="31" t="inlineStr">
         <x:is>
@@ -12279,10 +11981,8 @@
       <x:c r="A33" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B33" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B33" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C33" s="31" t="inlineStr">
         <x:is>
@@ -12324,10 +12024,8 @@
       <x:c r="A34" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B34" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B34" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C34" s="31" t="inlineStr">
         <x:is>
@@ -12369,10 +12067,8 @@
       <x:c r="A35" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B35" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B35" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C35" s="31" t="inlineStr">
         <x:is>
@@ -12414,10 +12110,8 @@
       <x:c r="A36" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B36" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C36" s="31" t="inlineStr">
         <x:is>
@@ -12459,10 +12153,8 @@
       <x:c r="A37" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B37" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B37" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C37" s="31" t="inlineStr">
         <x:is>
@@ -12504,10 +12196,8 @@
       <x:c r="A38" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B38" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B38" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C38" s="31" t="inlineStr">
         <x:is>
@@ -12549,10 +12239,8 @@
       <x:c r="A39" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B39" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B39" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C39" s="31" t="inlineStr">
         <x:is>
@@ -12594,10 +12282,8 @@
       <x:c r="A40" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B40" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B40" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C40" s="31" t="inlineStr">
         <x:is>
@@ -12639,10 +12325,8 @@
       <x:c r="A41" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B41" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B41" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C41" s="31" t="inlineStr">
         <x:is>
@@ -12684,10 +12368,8 @@
       <x:c r="A42" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B42" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C42" s="31" t="inlineStr">
         <x:is>
@@ -12729,10 +12411,8 @@
       <x:c r="A43" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B43" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B43" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C43" s="31" t="inlineStr">
         <x:is>
@@ -12774,10 +12454,8 @@
       <x:c r="A44" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B44" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B44" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C44" s="31" t="inlineStr">
         <x:is>
@@ -12819,10 +12497,8 @@
       <x:c r="A45" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B45" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B45" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C45" s="31" t="inlineStr">
         <x:is>
@@ -12864,10 +12540,8 @@
       <x:c r="A46" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B46" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C46" s="31" t="inlineStr">
         <x:is>
@@ -12909,10 +12583,8 @@
       <x:c r="A47" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B47" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B47" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C47" s="31" t="inlineStr">
         <x:is>
@@ -12954,10 +12626,8 @@
       <x:c r="A48" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B48" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B48" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C48" s="31" t="inlineStr">
         <x:is>
@@ -12999,10 +12669,8 @@
       <x:c r="A49" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B49" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B49" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C49" s="31" t="inlineStr">
         <x:is>
@@ -13044,10 +12712,8 @@
       <x:c r="A50" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B50" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B50" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C50" s="31" t="inlineStr">
         <x:is>
@@ -13089,10 +12755,8 @@
       <x:c r="A51" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B51" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B51" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C51" s="31" t="inlineStr">
         <x:is>
@@ -13134,10 +12798,8 @@
       <x:c r="A52" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B52" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B52" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C52" s="31" t="inlineStr">
         <x:is>
@@ -13179,10 +12841,8 @@
       <x:c r="A53" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B53" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B53" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C53" s="31" t="inlineStr">
         <x:is>
@@ -13224,10 +12884,8 @@
       <x:c r="A54" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B54" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C54" s="31" t="inlineStr">
         <x:is>
@@ -13269,10 +12927,8 @@
       <x:c r="A55" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B55" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B55" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C55" s="31" t="inlineStr">
         <x:is>
@@ -13314,10 +12970,8 @@
       <x:c r="A56" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B56" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B56" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C56" s="31" t="inlineStr">
         <x:is>
@@ -13397,10 +13051,8 @@
           <x:t xml:space="preserve">11 chapters / 55 villains / 11 mini-wizards</x:t>
         </x:is>
       </x:c>
-      <x:c r="C2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks is Chapter 5. Final Showdown qualifies only after the Chapter 11 wizard is completed.</x:t>
-        </x:is>
+      <x:c r="C2" s="31" t="str">
+        <x:v>The Web Tightens is Chapter 5. Final Showdown qualifies only after the Chapter 11 wizard is completed.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -14219,10 +13871,8 @@
           <x:t xml:space="preserve">/mnt/data/ASM67_2026_07_24_danger_lurks_chapter5_changed_files_only.zip</x:t>
         </x:is>
       </x:c>
-      <x:c r="C4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Adds Danger Lurks, shifts later chapters, and adds The Web Tightens.</x:t>
-        </x:is>
+      <x:c r="C4" s="31" t="str">
+        <x:v>Establishes Chapter 5, shifts later chapters, and adds The Web Tightens.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -14369,10 +14019,8 @@
       <x:c r="A2" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Classic Rogues</x:t>
-        </x:is>
+      <x:c r="B2" s="31" t="str">
+        <x:v>Sinister Surge</x:v>
       </x:c>
       <x:c r="C2" s="31" t="inlineStr">
         <x:is>
@@ -14404,10 +14052,8 @@
       <x:c r="A3" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Masked Masterminds</x:t>
-        </x:is>
+      <x:c r="B3" s="31" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="C3" s="31" t="inlineStr">
         <x:is>
@@ -14439,10 +14085,8 @@
       <x:c r="A4" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trubble's Monsters</x:t>
-        </x:is>
+      <x:c r="B4" s="31" t="str">
+        <x:v>Trubble Unleashed</x:v>
       </x:c>
       <x:c r="C4" s="31" t="inlineStr">
         <x:is>
@@ -14509,10 +14153,8 @@
       <x:c r="A6" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Danger Lurks</x:t>
-        </x:is>
+      <x:c r="B6" s="31" t="str">
+        <x:v>The Web Tightens</x:v>
       </x:c>
       <x:c r="C6" s="31" t="inlineStr">
         <x:is>
@@ -14544,10 +14186,8 @@
       <x:c r="A7" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic Menace</x:t>
-        </x:is>
+      <x:c r="B7" s="31" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="C7" s="31" t="inlineStr">
         <x:is>
@@ -14579,10 +14219,8 @@
       <x:c r="A8" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science</x:t>
-        </x:is>
+      <x:c r="B8" s="31" t="str">
+        <x:v>Mad Science Meltdown</x:v>
       </x:c>
       <x:c r="C8" s="31" t="inlineStr">
         <x:is>
@@ -14614,10 +14252,8 @@
       <x:c r="A9" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Elemental Chaos</x:t>
-        </x:is>
+      <x:c r="B9" s="31" t="str">
+        <x:v>Nature Strikes Back</x:v>
       </x:c>
       <x:c r="C9" s="31" t="inlineStr">
         <x:is>
@@ -14649,10 +14285,8 @@
       <x:c r="A10" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lost Worlds</x:t>
-        </x:is>
+      <x:c r="B10" s="31" t="str">
+        <x:v>Invasion from Everywhere</x:v>
       </x:c>
       <x:c r="C10" s="31" t="inlineStr">
         <x:is>
@@ -14684,10 +14318,8 @@
       <x:c r="A11" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Savage Oddities</x:t>
-        </x:is>
+      <x:c r="B11" s="31" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
       </x:c>
       <x:c r="C11" s="31" t="inlineStr">
         <x:is>
@@ -14719,10 +14351,8 @@
       <x:c r="A12" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dimensional Finale</x:t>
-        </x:is>
+      <x:c r="B12" s="31" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
       </x:c>
       <x:c r="C12" s="31" t="inlineStr">
         <x:is>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R678f3e591d6b46f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R662f1e9580614648"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R162c6f293cb040d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Raa050da44a5240c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R80ff688462a04754"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R443ce61fba524388"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rbde67bf1cb0b4073"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rbbc6ed8c953e4d88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R16e2a63bea584cf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R64a8ed2a24184204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R88a72cbe4df14f6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Re40111ad9e1943b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R378c1d334cbe46c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R67bddbb232ae47d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R4877a3ed90b3405b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R70c3d19dcd3a43ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R2d43fb56f43b49e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rf209a773235a4f1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R3c133828b3ae4f60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rb8cb30a995964527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R02d8507935694bc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R63ede562e9cc43e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rf4e244e4c0bb456d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R4e385c76c86140fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R2facd949fec84729"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R496c4833f7da46bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2490,10 +2490,8 @@
           <x:t xml:space="preserve">Fiddler</x:t>
         </x:is>
       </x:c>
-      <x:c r="E26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
+      <x:c r="E26" s="31" t="str">
+        <x:v>Implemented / recent retry-rule fix</x:v>
       </x:c>
       <x:c r="F26" s="31" t="inlineStr">
         <x:is>
@@ -2520,15 +2518,11 @@
           <x:t xml:space="preserve">Incrementing correct-note jackpots</x:t>
         </x:is>
       </x:c>
-      <x:c r="K26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Instant failure on wrong note</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3 rounds / optional 4th / wrong note / ball end</x:t>
-        </x:is>
+      <x:c r="K26" s="31" t="str">
+        <x:v>Startup and demonstration input lock prevents drop-knockdown vibration or live-ball switches from being judged before the response phase. Three mistakes are allowed per mode.</x:v>
+      </x:c>
+      <x:c r="L26" s="31" t="str">
+        <x:v>Complete Round 3 (or Round 4 with More Jackpots), or escape on the third mistake</x:v>
       </x:c>
       <x:c r="M26" s="31" t="inlineStr">
         <x:is>
@@ -3774,50 +3768,32 @@
           <x:t xml:space="preserve">The Molemen</x:t>
         </x:is>
       </x:c>
-      <x:c r="E46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Area-control multiball</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Saucer jackpots / add-a-ball</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left pop, center web, right pop + three saucers</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">50K pops; 100K center; 250K per ball saucer jackpots</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Jackpot value depends on balls in play; each area offers one add-a-ball; short one-ball grace</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">One-ball grace expires / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapter 9's conventional area-control multiball. It contrasts with Dr. Manta's staged relay, where one ball is always deliberately held.</x:t>
-        </x:is>
+      <x:c r="E46" s="31" t="str">
+        <x:v>Implemented / recent rule-device fix</x:v>
+      </x:c>
+      <x:c r="F46" s="31" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G46" s="31" t="str">
+        <x:v>Area-control multiball</x:v>
+      </x:c>
+      <x:c r="H46" s="31" t="str">
+        <x:v>Saucer jackpots / add-a-ball</x:v>
+      </x:c>
+      <x:c r="I46" s="31" t="str">
+        <x:v>Left pop, center web, right pop + three saucers</x:v>
+      </x:c>
+      <x:c r="J46" s="31" t="str">
+        <x:v>50K pops; 100K center; 250K per ball saucer jackpots</x:v>
+      </x:c>
+      <x:c r="K46" s="31" t="str">
+        <x:v>Jackpot value depends on balls in play; each area offers one add-a-ball with a 10-second shoot-again save, or 15 seconds with More Time</x:v>
+      </x:c>
+      <x:c r="L46" s="31" t="str">
+        <x:v>Molemen multiball ends / ball end</x:v>
+      </x:c>
+      <x:c r="M46" s="31" t="str">
+        <x:v>Chapter 9's conventional area-control multiball. It ends with the multiball device rather than offering an ineffective one-ball grace.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -4294,50 +4270,32 @@
           <x:t xml:space="preserve">Master Technician</x:t>
         </x:is>
       </x:c>
-      <x:c r="E54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Coded / needs machine test</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timed score attack</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Risk/reward spinner build</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Drops + spinner + inlanes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Each down target raises spinner value; stop at seven and spin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The eighth target costs 10 seconds and resets both banks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">60-second timer expires / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Meteor-style spinner build retained in a repeatable 60-second loop; all five Case Files are implemented.</x:t>
-        </x:is>
+      <x:c r="E54" s="31" t="str">
+        <x:v>Implemented / recent widget-device-lighting fix</x:v>
+      </x:c>
+      <x:c r="F54" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G54" s="31" t="str">
+        <x:v>Timed score attack</x:v>
+      </x:c>
+      <x:c r="H54" s="31" t="str">
+        <x:v>Risk/reward spinner build</x:v>
+      </x:c>
+      <x:c r="I54" s="31" t="str">
+        <x:v>Drops + spinner + inlanes</x:v>
+      </x:c>
+      <x:c r="J54" s="31" t="str">
+        <x:v>25K drops; 10K unlit spinner; repeatable 50K per down target through seven</x:v>
+      </x:c>
+      <x:c r="K54" s="31" t="str">
+        <x:v>Building seven consumes much of the timer; the earned high spinner value remains repeatable. The eighth target costs 10 seconds and resets both banks.</x:v>
+      </x:c>
+      <x:c r="L54" s="31" t="str">
+        <x:v>60-second timer expires / ball end</x:v>
+      </x:c>
+      <x:c r="M54" s="31" t="str">
+        <x:v>Meteor-style spinner build retained with corrected portrait widget, closed lower-playfield route, staggered bank resets, and defined lens-safe lighting feedback.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -8221,15 +8179,11 @@
           <x:t xml:space="preserve">Fiddler</x:t>
         </x:is>
       </x:c>
-      <x:c r="G26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Simon Says violin mode. Three normal rounds use one, two, and three unique notes; More Jackpots adds a four-note round. Each note flashes for 2 seconds with a fixed audio event, then stays solid for ordered player input. One wrong note ends the mode.</x:t>
-        </x:is>
+      <x:c r="G26" s="31" t="str">
+        <x:v>Implemented / recent retry-rule fix</x:v>
+      </x:c>
+      <x:c r="H26" s="31" t="str">
+        <x:v>Simon Says violin mode. Three normal rounds use one, two, and three unique notes; More Jackpots adds a four-note encore. Each note flashes its ordered pulse pattern four times, then stays solid. Input is locked during startup drop knockdowns, setup delays, demonstrations, and replay delays. The first two mistakes restart the current round and replay the full pattern after 1.5s; the third mistake ends the mode. Shot Assist forgives the first wrong input without consuming a mistake.</x:v>
       </x:c>
       <x:c r="I26" s="31" t="inlineStr">
         <x:is>
@@ -9133,15 +9087,11 @@
           <x:t xml:space="preserve">The Molemen</x:t>
         </x:is>
       </x:c>
-      <x:c r="G46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Two-ball area-control multiball. Left pop lights Saucer 1, center web lights Saucer 2, and right pop lights Saucer 3. Lit saucers award 250K per ball in play, reset their area, and can award one add-a-ball per area. A 5-second one-ball grace delays mode end.</x:t>
-        </x:is>
+      <x:c r="G46" s="31" t="str">
+        <x:v>Implemented / recent rule-device fix</x:v>
+      </x:c>
+      <x:c r="H46" s="31" t="str">
+        <x:v>Two-ball area-control multiball. Left pop lights Saucer 1, center web lights Saucer 2, and right pop lights Saucer 3. Lit saucers award 250K per ball in play, reset their area, and can award one add-a-ball per area. The mode now ends immediately when multiball ends. More Time extends each add-a-ball shoot-again save from 10 to 15 seconds.</x:v>
       </x:c>
       <x:c r="I46" s="31" t="inlineStr">
         <x:is>
@@ -9501,15 +9451,11 @@
           <x:t xml:space="preserve">Master Technician</x:t>
         </x:is>
       </x:c>
-      <x:c r="G54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Coded / needs machine test</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">60-second spinner/drop score attack. Drops score 25K and build spinner value by 50K each through seven down; all eight costs 10 seconds and resets both banks. All five Case Files implemented.</x:t>
-        </x:is>
+      <x:c r="G54" s="31" t="str">
+        <x:v>Implemented / recent widget-device-lighting fix</x:v>
+      </x:c>
+      <x:c r="H54" s="31" t="str">
+        <x:v>60-second spinner/drop score attack. Drops score 25K and build a repeatable spinner value by 50K each through seven down; all eight costs 10 seconds and resets both banks. Widget now uses the existing portrait, the lower-playfield route closes the rooftop gate, bank resets are staggered 300ms, and complete lens-safe lighting/feedback is defined.</x:v>
       </x:c>
       <x:c r="I54" s="31" t="inlineStr">
         <x:is>
@@ -11976,25 +11922,17 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Watch a one-, two-, then three-note light-and-violin pattern using Left Web, Left Bank rubber, Center Web, and Right Bank rubber. Repeat each pattern in order.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Completes after Round 3, or Round 4 with More Jackpots. Any wrong note ends the mode unless the one-use Shot Assist awards the expected note.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Patterns demonstrate one light at a time. Its sequence-position pulse pattern repeats four times, then the light remains solid while the next note demonstrates. Positions 1-4 take 2.4s, 3.6s, 4.8s, and 6.0s. The pattern repeats after 14 seconds, or 8 with More Time. Correct-note scoring is 100K; 200K/300K; 400K/500K/600K; and 700K/800K/900K/1M in the optional fourth round. Bigger adds 100K to every note; Safety Net is the standard ball save.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with fixed note events play_note_1 through play_note_4 mapped to violin_1 through violin_4, play_bad_note mapped to violin_bad_note, GI 60F060, and forced-down drop banks.</x:t>
-        </x:is>
+      <x:c r="F26" s="31" t="str">
+        <x:v>Watch each ordered violin pattern, then repeat it using Left Web, Left Bank rubber, Center Web, and Right Bank rubber.</x:v>
+      </x:c>
+      <x:c r="G26" s="31" t="str">
+        <x:v>Complete three rounds, or four with More Jackpots. Three mistakes during the mode allow Fiddler to escape.</x:v>
+      </x:c>
+      <x:c r="H26" s="31" t="str">
+        <x:v>Patterns contain one to four unique notes. Correct-note scoring remains 100K; 200K/300K; 400K/500K/600K; and 700K/800K/900K/1M in the optional encore.</x:v>
+      </x:c>
+      <x:c r="I26" s="31" t="str">
+        <x:v>Inputs are ignored until PLAY THE PATTERN. A non-terminal wrong note replays the complete current pattern after 1.5s. Shot Assist forgives the first wrong input and does not consume a mistake.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -12860,25 +12798,17 @@
           <x:t xml:space="preserve">2</x:t>
         </x:is>
       </x:c>
-      <x:c r="F46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Two-ball multiball. Left pop, center web and right pop independently light Saucer 1, 2 and 3. The rooftop gate remains closed.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">When play drops to one ball, a 5-second grace begins before the mode ends; More Time increases it to 10 seconds. Mode also stops at ball end.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pop hits score 50K and center web scores 100K. A lit saucer awards 250K multiplied by balls in play and resets that area. Each area can qualify add-a-ball once: 3 left-pop hits, 1 center-web hit, or 3 right-pop hits.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I46" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with three mapped areas, saucer jackpot/add-a-ball shows, custom widget, Case Files, grace handling and summary variables; needs on-machine playtest.</x:t>
-        </x:is>
+      <x:c r="F46" s="31" t="str">
+        <x:v>Two-ball multiball. Left pop, center web and right pop independently light Saucer 1, 2 and 3. The rooftop gate remains closed.</x:v>
+      </x:c>
+      <x:c r="G46" s="31" t="str">
+        <x:v>The mode ends immediately when Molemen multiball ends. Mode also stops at ball end.</x:v>
+      </x:c>
+      <x:c r="H46" s="31" t="str">
+        <x:v>Pop hits score 50K and center web scores 100K. A lit saucer awards 250K multiplied by balls in play and resets that area. Each area can qualify add-a-ball once: 3 left-pop hits, 1 center-web hit, or 3 right-pop hits. More Time extends each add-a-ball shoot-again save from 10 to 15 seconds.</x:v>
+      </x:c>
+      <x:c r="I46" s="31" t="str">
+        <x:v>Implemented with three mapped areas, saucer jackpot/add-a-ball shows, corrected two-second saucer eject requests, immediate multiball-end handling, Case Files, status and summary variables; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -13220,25 +13150,17 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">60-second spinner/drop score attack. Drops score 25K; spinner is 10K unlit and 50K per down target through seven. Inlanes knock down a standing target.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timer expiry completes the mode; ball end stops it. All eight drops down deducts 10 seconds, resets both banks, and continues.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">More JP lights both web targets for 50K at levels 1-7; Bigger builds spinner at 75K per drop; More Time starts at 75s; Safety Net cancels first penalty; Shot Assist spots up to two safe targets.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I54" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Coded and documented; messages, seven-speed spinner/bank-GI pulses, summary stats, and player-var cleanup complete. Needs machine test.</x:t>
-        </x:is>
+      <x:c r="F54" s="31" t="str">
+        <x:v>60-second spinner/drop score attack. Drops score 25K; spinner is 10K unlit and 50K per down target through seven. Inlanes knock down a standing target. The built spinner value remains repeatable and does not reset on a spinner hit.</x:v>
+      </x:c>
+      <x:c r="G54" s="31" t="str">
+        <x:v>Timer expiry completes the mode; ball end stops it. All eight drops down deducts 10 seconds, resets both banks, and continues.</x:v>
+      </x:c>
+      <x:c r="H54" s="31" t="str">
+        <x:v>More JP lights both web targets for 50K at levels 1-7; Bigger builds spinner at 75K per drop; More Time starts at 75s; Safety Net cancels first penalty; Shot Assist spots up to two safe targets.</x:v>
+      </x:c>
+      <x:c r="I54" s="31" t="str">
+        <x:v>Implemented with portrait widget, closed rooftop gate, removed legacy upper-post action, 300ms bank-reset stagger, cool-blue base GI, seven-speed white spinner/bank pulses, drop/spinner feedback, short-circuit/Safety Net reactions, summary stats, and Case Files. Needs machine test.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -13607,10 +13529,8 @@
           <x:t xml:space="preserve">Cradle/status pages</x:t>
         </x:is>
       </x:c>
-      <x:c r="C4" s="45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pages for goals, Chaos, photo/mystery, chapter/villain, extra balls, high-score context.</x:t>
-        </x:is>
+      <x:c r="C4" s="45" t="str">
+        <x:v>Shared persistent mode-status panel retained at 720 pixels to fit between the Player 3 and Player 4 score panels, with centered stacked title/value rows. Remaining pages for goals, Chaos, photo/mystery, chapter/villain, extra balls, and high-score context remain open.</x:v>
       </x:c>
       <x:c r="D4" s="45" t="inlineStr">
         <x:is>
@@ -13805,15 +13725,11 @@
           <x:t xml:space="preserve">Documentation</x:t>
         </x:is>
       </x:c>
-      <x:c r="C13" s="45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Roster, implementation status, wizard Case File rules, mode identities, and the Case File matrix are synced to code. No regular-villain Case File gaps remain. The loaded legacy daily_bugle_rooftop_riot placeholder is still documented. Master Technician, Sir Galahad, and Plotter need machine tests.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Updated 2026-08-17</x:t>
-        </x:is>
+      <x:c r="C13" s="45" t="str">
+        <x:v>Roster, implementation status, wizard Case File rules, mode identities, and the Case File matrix are synced to code. Master Technician's widget, gate, bank-reset and lighting fixes are documented; Master Technician, Sir Galahad, and Plotter still need machine tests.</x:v>
+      </x:c>
+      <x:c r="D13" s="45" t="str">
+        <x:v>Updated 2026-08-22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="26" customFormat="1" ht="38" customHeight="1">
@@ -13959,10 +13875,8 @@
           <x:t xml:space="preserve">Playtest The Molemen</x:t>
         </x:is>
       </x:c>
-      <x:c r="C20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Verify two-ball start, closed rooftop gate, three area-to-saucer mappings, per-ball jackpot values, one-use add-a-ball per area, saucer reset/eject timing, one-ball grace, Case Files, widget and cleanup.</x:t>
-        </x:is>
+      <x:c r="C20" t="str">
+        <x:v>Verify two-ball start, closed rooftop gate, three area-to-saucer mappings, per-ball jackpot values, one-use add-a-ball per area, corrected two-second saucer eject timing, immediate mode end when multiball ends, 10s/15s add-a-ball shoot-again saves, Case Files, widget and cleanup.</x:v>
       </x:c>
       <x:c r="D20" t="inlineStr">
         <x:is>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R67bddbb232ae47d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R4877a3ed90b3405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R70c3d19dcd3a43ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R2d43fb56f43b49e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rf209a773235a4f1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R3c133828b3ae4f60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rb8cb30a995964527"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R02d8507935694bc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R63ede562e9cc43e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rf4e244e4c0bb456d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R4e385c76c86140fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R2facd949fec84729"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R496c4833f7da46bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R06056c9762c24216"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rdbc49bbee93947f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rb2e98e188f494efb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rddf960bfcd8648da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R115cc720537c4758"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R02e9676371e14fe6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rebcf4e6c81914440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R39053281d4a94272"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rdbf6726fd6de4c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R216c81d4d8ea40a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rdd3a9a7690d241f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R669fcf97292d47c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Ra7d3414ead5e4086"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1515,10 +1515,8 @@
           <x:t xml:space="preserve">Parafino</x:t>
         </x:is>
       </x:c>
-      <x:c r="E11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / recent lighting fix</x:t>
-        </x:is>
+      <x:c r="E11" s="31" t="str">
+        <x:v>Implemented / recent saucer-number fix</x:v>
       </x:c>
       <x:c r="F11" s="31" t="inlineStr">
         <x:is>
@@ -1555,10 +1553,8 @@
           <x:t xml:space="preserve">Multiball end</x:t>
         </x:is>
       </x:c>
-      <x:c r="M11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapter 2 multiball role; area-control and lit-saucer add-a-ball give it a distinct identity.</x:t>
-        </x:is>
+      <x:c r="M11" s="31" t="str">
+        <x:v>Chapter 2 multiball role; area-control and lit-saucer add-a-ball give it a distinct identity. Numeric saucer IDs now reach the shared eject service correctly while retaining Parafino's 2-second release timing.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="26" customFormat="1" ht="250.8000030517578" customHeight="1">
@@ -1580,50 +1576,32 @@
           <x:t xml:space="preserve">Cerberus</x:t>
         </x:is>
       </x:c>
-      <x:c r="E12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs machine playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timed matching</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Saucer control</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Upper targets + saucers</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Matching saucer 3X jackpots; per-saucer retained repeat with More Jackpots</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">16s timer after first jackpot; upper target/spinner/saucer resets</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timer expiry / ball end; 3 jackpots is display-only</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timed matching role. CERBERUS DEFEATED is a 2-second presentation after the third jackpot; progression only requires that the mode has been played.</x:t>
-        </x:is>
+      <x:c r="E12" s="31" t="str">
+        <x:v>Implemented / recent ball-end widget lifecycle fix</x:v>
+      </x:c>
+      <x:c r="F12" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="31" t="str">
+        <x:v>Timed matching</x:v>
+      </x:c>
+      <x:c r="H12" s="31" t="str">
+        <x:v>Saucer control</x:v>
+      </x:c>
+      <x:c r="I12" s="31" t="str">
+        <x:v>Upper targets + saucers</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="str">
+        <x:v>Matching saucer 3X jackpots; per-saucer retained repeat with More Jackpots</x:v>
+      </x:c>
+      <x:c r="K12" s="31" t="str">
+        <x:v>16s timer after first jackpot; upper target/spinner/saucer resets</x:v>
+      </x:c>
+      <x:c r="L12" s="31" t="str">
+        <x:v>Timer expiry / ball end; 3 jackpots is display-only</x:v>
+      </x:c>
+      <x:c r="M12" s="31" t="str">
+        <x:v>Timed matching role. CERBERUS DEFEATED is a 2-second presentation after the third jackpot. Cerberus now tears down at ball_ending before bonus presentation; needs drain-to-bonus regression testing.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="26" customFormat="1" ht="250.8000030517578" customHeight="1">
@@ -1645,50 +1623,32 @@
           <x:t xml:space="preserve">Vulcan</x:t>
         </x:is>
       </x:c>
-      <x:c r="E13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs machine playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2-ball MB; repeatable add-a-ball to 3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Multiball</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Drop-bank cash / roof reset</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right bank + upper entry/targets; left bank with More Jackpots</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">100K/150K Jackpot; +25K per upper hit to 1M; full Jackpot banks to vulcan_bonus</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Multiball drain; exhausted banks wait for upper entry</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Multiball reaches 1 ball / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapter multiball role. Upper playfield replenishes the drop-bank cashout loop; repeatable Add-a-Ball rewards bank completion without a separate single-ball phase.</x:t>
-        </x:is>
+      <x:c r="E13" s="31" t="str">
+        <x:v>Implemented / recent left-bank behavior fix</x:v>
+      </x:c>
+      <x:c r="F13" s="31" t="str">
+        <x:v>2-ball MB; repeatable add-a-ball to 3</x:v>
+      </x:c>
+      <x:c r="G13" s="31" t="str">
+        <x:v>Multiball</x:v>
+      </x:c>
+      <x:c r="H13" s="31" t="str">
+        <x:v>Drop-bank cash / roof reset</x:v>
+      </x:c>
+      <x:c r="I13" s="31" t="str">
+        <x:v>Right bank + upper entry/targets; conditional left bank</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="str">
+        <x:v>100K/150K Jackpot; +25K per upper hit to 1M; full Jackpot banks to vulcan_bonus</x:v>
+      </x:c>
+      <x:c r="K13" s="31" t="str">
+        <x:v>Right Jackpot bank waits for upper entry. Left bank resets normally unless More Jackpots converts it to a roof-reset Jackpot bank.</x:v>
+      </x:c>
+      <x:c r="L13" s="31" t="str">
+        <x:v>Multiball reaches 1 ball / ball end</x:v>
+      </x:c>
+      <x:c r="M13" s="31" t="str">
+        <x:v>Chapter multiball role. The left bank remains a normal 2K/reset-on-completion bank by default; More Jackpots cleanly promotes it into the upper-entry replenishment loop.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2035,50 +1995,32 @@
           <x:t xml:space="preserve">Fifth Avenue Phantom</x:t>
         </x:is>
       </x:c>
-      <x:c r="E19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystery / reveal</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timed location</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right bank + revealed location</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Declining revealed-location value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reveal window / value decay</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reveal rounds completed / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reveal/urgency role.</x:t>
-        </x:is>
+      <x:c r="E19" s="31" t="str">
+        <x:v>Implemented / recent lighting and STAR reveal update</x:v>
+      </x:c>
+      <x:c r="F19" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" s="31" t="str">
+        <x:v>Mystery / reveal</x:v>
+      </x:c>
+      <x:c r="H19" s="31" t="str">
+        <x:v>Timed location</x:v>
+      </x:c>
+      <x:c r="I19" s="31" t="str">
+        <x:v>Right bank + STAR + revealed location</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="str">
+        <x:v>Declining revealed-location value; STAR preserves value</x:v>
+      </x:c>
+      <x:c r="K19" s="31" t="str">
+        <x:v>Reveal-window tradeoff: drops add more time at lower value; repeatable STAR adds 4 seconds without value loss</x:v>
+      </x:c>
+      <x:c r="L19" s="31" t="str">
+        <x:v>Reveal rounds completed / ball end</x:v>
+      </x:c>
+      <x:c r="M19" s="31" t="str">
+        <x:v>Reveal/urgency role. Right-bank GI and standing-drop flashes keep the main reveal route visible; STAR provides a difficult rooftop time-extension alternative.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2165,50 +2107,32 @@
           <x:t xml:space="preserve">Doctor Cool</x:t>
         </x:is>
       </x:c>
-      <x:c r="E21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chase / freeze</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Banked bonus</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Drops + STAR + saucers</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Frozen-diamond bank / shipment jackpot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Moving saucer chase and freeze timing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Required shipments complete / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Crime Wave risk/reward chase; Doctor Cool smuggles diamonds inside ice.</x:t>
-        </x:is>
+      <x:c r="E21" s="31" t="str">
+        <x:v>Implemented / recent STAR lighting fix</x:v>
+      </x:c>
+      <x:c r="F21" s="31" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="31" t="str">
+        <x:v>Chase / freeze</x:v>
+      </x:c>
+      <x:c r="H21" s="31" t="str">
+        <x:v>Banked bonus</x:v>
+      </x:c>
+      <x:c r="I21" s="31" t="str">
+        <x:v>Drops + STAR + saucers</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="str">
+        <x:v>Frozen-diamond bank / shipment jackpot</x:v>
+      </x:c>
+      <x:c r="K21" s="31" t="str">
+        <x:v>Moving saucer chase and freeze timing</x:v>
+      </x:c>
+      <x:c r="L21" s="31" t="str">
+        <x:v>Required shipments complete / ball end</x:v>
+      </x:c>
+      <x:c r="M21" s="31" t="str">
+        <x:v>Crime Wave risk/reward chase; Doctor Cool smuggles diamonds inside ice. STAR now flashes red continuously at 250ms on / 250ms off and clears cleanly when the mode stops.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2672,7 +2596,7 @@
         </x:is>
       </x:c>
       <x:c r="E29" s="31" t="str">
-        <x:v>Implemented / recent lighting update</x:v>
+        <x:v>Implemented / recent Scepter timer display fix</x:v>
       </x:c>
       <x:c r="F29" s="31" t="inlineStr">
         <x:is>
@@ -2703,10 +2627,8 @@
       <x:c r="L29" s="31" t="str">
         <x:v>VUK Super or scepter timeout</x:v>
       </x:c>
-      <x:c r="M29" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Optional fifth demon with More Jackpots; strong short checklist role.</x:t>
-        </x:is>
+      <x:c r="M29" s="31" t="str">
+        <x:v>Optional fifth demon with More Jackpots; persistent 20s/30s Scepter timer now shows the current VUK objective. Machine playtest pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2728,10 +2650,8 @@
           <x:t xml:space="preserve">Super Swami</x:t>
         </x:is>
       </x:c>
-      <x:c r="E30" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
+      <x:c r="E30" s="31" t="str">
+        <x:v>Implemented / recent failure-cleanup fix</x:v>
       </x:c>
       <x:c r="F30" s="31" t="inlineStr">
         <x:is>
@@ -2768,10 +2688,8 @@
           <x:t xml:space="preserve">Six restored / timer / ball end</x:t>
         </x:is>
       </x:c>
-      <x:c r="M30" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Simple region-restoration role with optional VUK Blackout Jackpot.</x:t>
-        </x:is>
+      <x:c r="M30" s="31" t="str">
+        <x:v>Simple region-restoration role with optional VUK Blackout Jackpot. Timer failure now uses the centralized summary/cleanup pipeline; machine regression test pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -3508,50 +3426,32 @@
           <x:t xml:space="preserve">Dr. Manta</x:t>
         </x:is>
       </x:c>
-      <x:c r="E42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2 staged / 1 active</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Relay / staged ball control</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timed jackpot build-and-cash</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VUK, three saucers, both spinners, upper targets</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">100K VUK; 150K saucer; 100K starting JP; +50K/spin to 1M; repeated upper-target collections</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Second ball must reach a saucer; active attack ball may leave the roof; all flippers disable at timeout</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Attack timer expires and active ball reaches trough / early second-ball loss</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mechanically distinct from Molemen: never conventional free two-ball play after setup. One ball is always held while the other performs the objective.</x:t>
-        </x:is>
+      <x:c r="E42" s="31" t="str">
+        <x:v>Implemented / recent shared saucer-summary hold fix</x:v>
+      </x:c>
+      <x:c r="F42" s="31" t="str">
+        <x:v>2 staged / 1 active</x:v>
+      </x:c>
+      <x:c r="G42" s="31" t="str">
+        <x:v>Relay / staged ball control</x:v>
+      </x:c>
+      <x:c r="H42" s="31" t="str">
+        <x:v>Timed jackpot build-and-cash</x:v>
+      </x:c>
+      <x:c r="I42" s="31" t="str">
+        <x:v>VUK, three saucers, both spinners, upper targets</x:v>
+      </x:c>
+      <x:c r="J42" s="31" t="str">
+        <x:v>100K VUK; 150K saucer; 100K starting JP; +50K/spin to 1M; repeated upper-target collections</x:v>
+      </x:c>
+      <x:c r="K42" s="31" t="str">
+        <x:v>Second ball must reach a saucer; active attack ball may leave the roof; all flippers disable at timeout</x:v>
+      </x:c>
+      <x:c r="L42" s="31" t="str">
+        <x:v>Attack timer expires and active ball reaches trough; saucer release follows summary / early second-ball loss</x:v>
+      </x:c>
+      <x:c r="M42" s="31" t="str">
+        <x:v>Mechanically distinct from Molemen: never conventional free two-ball play after setup. One ball is always held while the other performs the objective. Terminal saucer release now uses the shared post-summary cleanup path.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -3769,7 +3669,7 @@
         </x:is>
       </x:c>
       <x:c r="E46" s="31" t="str">
-        <x:v>Implemented / recent rule-device fix</x:v>
+        <x:v>Implemented / recent drop-reset and add-a-ball lighting fix</x:v>
       </x:c>
       <x:c r="F46" s="31" t="str">
         <x:v>2</x:v>
@@ -3787,13 +3687,13 @@
         <x:v>50K pops; 100K center; 250K per ball saucer jackpots</x:v>
       </x:c>
       <x:c r="K46" s="31" t="str">
-        <x:v>Jackpot value depends on balls in play; each area offers one add-a-ball with a 10-second shoot-again save, or 15 seconds with More Time</x:v>
+        <x:v>Persistent white build-zone guidance is distinct from earned-saucer guidance. Solid green 1/2/3 identifies add-a-ball readiness while red hole lamps flash. Jackpot value depends on balls in play; each area offers one add-a-ball with a 10-second shoot-again save, or 15 seconds with More Time.</x:v>
       </x:c>
       <x:c r="L46" s="31" t="str">
         <x:v>Molemen multiball ends / ball end</x:v>
       </x:c>
       <x:c r="M46" s="31" t="str">
-        <x:v>Chapter 9's conventional area-control multiball. It ends with the multiball device rather than offering an ineffective one-ball grace.</x:v>
+        <x:v>Chapter 9's conventional area-control multiball. Startup and completed-bank resets keep both physical drop banks available; needs machine playtest for reset timing and zone-light visibility.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -7489,15 +7389,11 @@
           <x:t xml:space="preserve">Parafino</x:t>
         </x:is>
       </x:c>
-      <x:c r="G11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / recent lighting fix</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2-ball heat-area multiball. Left drops, pops, and right drops light immediately as the three active target zones. Zone hits build the matching saucer jackpot; only the earned saucer lamp flashes. Target-zone guidance remains lit throughout the mode. Saucer eject delay remains 2 seconds.</x:t>
-        </x:is>
+      <x:c r="G11" s="31" t="str">
+        <x:v>Implemented / recent saucer-number fix</x:v>
+      </x:c>
+      <x:c r="H11" s="31" t="str">
+        <x:v>2-ball heat-area multiball. Left drops, pops, and right drops light immediately as the three active target zones. Zone hits build the matching saucer jackpot; only the earned saucer lamp flashes. Target-zone guidance remains lit throughout the mode. Parafino now sends numeric saucer IDs 1/2/3 to the shared eject service and preserves its 2-second eject delay.</x:v>
       </x:c>
       <x:c r="I11" s="31" t="inlineStr">
         <x:is>
@@ -7535,15 +7431,11 @@
           <x:t xml:space="preserve">Cerberus</x:t>
         </x:is>
       </x:c>
-      <x:c r="G12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs machine playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Any upper target lights all saucers; its matching saucer is 3X. First jackpot starts the 16s timer; upper targets, upper spinner, and all saucer hits reset it. More Jackpots lets each saucer remain lit once after its first collection at the same state/multiplier. Shot Assist consumes one collection only. Third jackpot shows CERBERUS DEFEATED for 2s but play continues; playing the mode satisfies progression.</x:t>
-        </x:is>
+      <x:c r="G12" s="31" t="str">
+        <x:v>Implemented / recent ball-end widget lifecycle fix</x:v>
+      </x:c>
+      <x:c r="H12" s="31" t="str">
+        <x:v>Any upper target lights all saucers; its matching saucer is 3X. First jackpot starts the 16s timer; upper targets, upper spinner, and all saucer hits reset it. More Jackpots lets each saucer remain lit once after its first collection at the same state/multiplier. Shot Assist consumes one collection only. Third jackpot shows CERBERUS DEFEATED for 2s but play continues; playing the mode satisfies progression. On a drain, Cerberus now stops at ball_ending so its timer and widget are removed before bonus starts.</x:v>
       </x:c>
       <x:c r="I12" s="31" t="inlineStr">
         <x:is>
@@ -7581,15 +7473,11 @@
           <x:t xml:space="preserve">Vulcan</x:t>
         </x:is>
       </x:c>
-      <x:c r="G13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs machine playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2-ball Eruption multiball; right drops score a 100K Jackpot (150K Bigger) and upper-target hits add 25K to a 1M cap. Upper entry resets any down Jackpot banks. Bank completion qualifies repeatable Add-a-Ball at any upper target, capped at 3 balls. More Jackpots adds the left 3-bank. Upper-left exit holds the post 8s (12s More Time). Safety Net gives a 20s opening save; Shot Assist adds two right drops on the first right-drop hit. Every Jackpot adds its full value to vulcan_bonus.</x:t>
-        </x:is>
+      <x:c r="G13" s="31" t="str">
+        <x:v>Implemented / recent left-bank behavior fix</x:v>
+      </x:c>
+      <x:c r="H13" s="31" t="str">
+        <x:v>2-ball Eruption multiball; right drops score a 100K Jackpot (150K Bigger) and upper-target hits add 25K to a 1M cap. Without More Jackpots, left drops score the regular 2K and the left bank resets immediately when completed. More Jackpots converts the left 3-bank to a second Jackpot bank that remains down until upper entry. Bank completion qualifies repeatable Add-a-Ball at an upper target, capped at 3 balls. Upper-left exit holds the post 8s (12s More Time). Safety Net gives a 20s opening save; Shot Assist adds two right drops on the first right-drop hit. Every Jackpot adds its full value to vulcan_bonus.</x:v>
       </x:c>
       <x:c r="I13" s="31" t="inlineStr">
         <x:is>
@@ -7857,15 +7745,11 @@
           <x:t xml:space="preserve">The Fifth Avenue Phantom</x:t>
         </x:is>
       </x:c>
-      <x:c r="G19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right bank reveals Phantom location; 5 rounds / More Jackpots extra round.</x:t>
-        </x:is>
+      <x:c r="G19" s="31" t="str">
+        <x:v>Implemented / recent lighting and STAR reveal update</x:v>
+      </x:c>
+      <x:c r="H19" s="31" t="str">
+        <x:v>Five-round reveal/collect mode; More Jackpots adds a sixth. Standing right drops flash green and hit drops remain solid. A right drop reveals the hidden jackpot shot and adds time; later unique drops add more time but lower its value. STAR is not a hiding location: it flashes red throughout the mode and gives a repeatable live 4-second reveal or adds 4 seconds to an active reveal without reducing value. Right-bank GI pulses continuously.</x:v>
       </x:c>
       <x:c r="I19" s="31" t="inlineStr">
         <x:is>
@@ -7949,15 +7833,11 @@
           <x:t xml:space="preserve">Doctor Cool</x:t>
         </x:is>
       </x:c>
-      <x:c r="G21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Drops build frozen-diamond value; completing the right 5-bank starts a moving...</x:t>
-        </x:is>
+      <x:c r="G21" s="31" t="str">
+        <x:v>Implemented / recent STAR lighting fix</x:v>
+      </x:c>
+      <x:c r="H21" s="31" t="str">
+        <x:v>Drops build frozen-diamond value; completing the right 5-bank starts a moving saucer shipment chase. STAR always banks 100K to diamond_bonus and now flashes red throughout Doctor Cool. During the chase, STAR freezes the cycle and lights all three saucers for 10 seconds, or 15 with More Time.</x:v>
       </x:c>
       <x:c r="I21" s="31" t="inlineStr">
         <x:is>
@@ -8310,10 +8190,10 @@
         </x:is>
       </x:c>
       <x:c r="G29" s="31" t="str">
-        <x:v>Implemented / recent lighting update</x:v>
+        <x:v>Implemented / recent Scepter timer display fix</x:v>
       </x:c>
       <x:c r="H29" s="31" t="str">
-        <x:v>Four randomly selected demons appear one at a time every 4s across two webs, two banks, and two pops. Destroying all four starts a 20s scepter phase and opens rooftop access; the VUK scores the 1M Super. Lighting uses dim dark-red background GI, independently flashing yellow active demons, and a yellow-only ramp/VUK flash during the scepter phase. The former full-playfield red/off strobe was removed. Defeat and escape now produce the correct summary outcome.</x:v>
+        <x:v>Four randomly selected demons appear one at a time every 4s across two webs, two banks, and two pops. Destroying all four starts a 20s scepter phase and opens rooftop access; the VUK scores the 1M Super. The Scepter phase now shows a persistent SCEPTER TIME status (30s with More Time), cancels the prior demon reminder, and displays SHOOT THE VUK or OPTIONAL DEMON - THEN VUK. Lighting uses dim dark-red background GI, independently flashing yellow active demons, and a yellow-only ramp/VUK flash during the scepter phase. Defeat and escape produce the correct summary outcome.</x:v>
       </x:c>
       <x:c r="I29" s="31" t="inlineStr">
         <x:is>
@@ -8351,15 +8231,11 @@
           <x:t xml:space="preserve">Super Swami</x:t>
         </x:is>
       </x:c>
-      <x:c r="G30" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H30" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Restore six coordinate-based GI regions before the 40-second timer expires. F...</x:t>
-        </x:is>
+      <x:c r="G30" s="31" t="str">
+        <x:v>Implemented / recent failure-cleanup fix</x:v>
+      </x:c>
+      <x:c r="H30" s="31" t="str">
+        <x:v>Restore six coordinate-based GI regions before the 40-second timer expires. More Jackpots adds a final VUK Blackout Jackpot. Timer failure now enters the centralized failed-summary pipeline, marks Swami played/completed for progression, and clears the villain-running lock after the summary instead of leaving the chapter display at PLAYING.</x:v>
       </x:c>
       <x:c r="I30" s="31" t="inlineStr">
         <x:is>
@@ -8903,15 +8779,11 @@
           <x:t xml:space="preserve">Dr. Manta</x:t>
         </x:is>
       </x:c>
-      <x:c r="G42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VUK-to-saucer relay: hold Ball 1 in the VUK, serve Ball 2 with a 10-second save, then lock it in any saucer. Kick Ball 1 to the rooftop for a 20-second attack. Either spinner raises the 100K jackpot by 50K per spin to a 1M cap; upper targets collect without resetting. At timeout all flippers disable until the active ball reaches the trough, then the held saucer ball is released.</x:t>
-        </x:is>
+      <x:c r="G42" s="31" t="str">
+        <x:v>Implemented / recent shared saucer-summary hold fix</x:v>
+      </x:c>
+      <x:c r="H42" s="31" t="str">
+        <x:v>VUK-to-saucer relay: hold Ball 1 in the VUK, serve Ball 2 with a 10-second save, then lock it in any saucer. Kick Ball 1 to the rooftop for a 20-second attack. Either spinner raises the 100K jackpot by 50K per spin to a 1M cap; upper targets collect without resetting. At timeout all flippers disable until the active ball reaches the trough. The locked ball remains in its saucer through the villain summary, then shared occupancy-checked cleanup releases it.</x:v>
       </x:c>
       <x:c r="I42" s="31" t="inlineStr">
         <x:is>
@@ -9088,10 +8960,10 @@
         </x:is>
       </x:c>
       <x:c r="G46" s="31" t="str">
-        <x:v>Implemented / recent rule-device fix</x:v>
+        <x:v>Implemented / recent drop-reset and add-a-ball lighting fix</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Two-ball area-control multiball. Left pop lights Saucer 1, center web lights Saucer 2, and right pop lights Saucer 3. Lit saucers award 250K per ball in play, reset their area, and can award one add-a-ball per area. The mode now ends immediately when multiball ends. More Time extends each add-a-ball shoot-again save from 10 to 15 seconds.</x:v>
+        <x:v>Two-ball area-control multiball. Left pop lights Saucer 1, center web lights Saucer 2, and right pop lights Saucer 3. Both drop banks reset at mode startup and their completed-bank events reset them again for continued play. Persistent white guidance identifies the three build zones. When an area's one-use add-a-ball is ready, its matching green 1, 2, or 3 insert stays solid while the red saucer-hole lamps flash; collection clears the numbered insert with the area. Lit saucers award 250K per ball in play. Needs machine playtest.</x:v>
       </x:c>
       <x:c r="I46" s="31" t="inlineStr">
         <x:is>
@@ -11262,10 +11134,8 @@
           <x:t xml:space="preserve">All three target zones light at mode start and remain lit. Left/right banks use their green lens colors and the pop area uses red. Each zone hit builds and lights its matching saucer jackpot; saucer lamps remain separate from target guidance. Add-a-ball qualifies from zone hit counts.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Improved: target zones now light immediately; target guidance and earned saucer-jackpot flashes use separate shows.</x:t>
-        </x:is>
+      <x:c r="I11" s="31" t="str">
+        <x:v>Improved: target zones now light immediately; target guidance and earned saucer-jackpot flashes use separate shows. Saucer release calls now pass numeric IDs 1/2/3 to the shared eject service; the existing 2-second hold remains unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="26" customFormat="1" ht="541.2000122070312" customHeight="1">
@@ -11307,10 +11177,8 @@
           <x:t xml:space="preserve">First jackpot starts a 16s timer (20s More Time). Upper targets, upper spinner, and any saucer hit reset it. After a collect the gate opens and other lit saucers return to 1X. More Jackpots gives each saucer one retained first collection at the same multiplier; Shot Assist is one use and consumes one collection on the awarded saucer.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reviewed/corrected; needs machine playtest. Orange GI retained; red saucer-hole and green 1/2/3 insert lighting remains lens-appropriate.</x:t>
-        </x:is>
+      <x:c r="I12" s="31" t="str">
+        <x:v>Reviewed/corrected; needs machine playtest. Orange GI retained; red saucer-hole and green 1/2/3 insert lighting remains lens-appropriate. Ball-drain cleanup now stops Cerberus before bonus and avoids the Crime Tracker remove/re-add race.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="26" customFormat="1" ht="805.2000122070312" customHeight="1">
@@ -11347,15 +11215,11 @@
           <x:t xml:space="preserve">Ends when the main multiball reaches one ball, or on ball end. There is no Cooling Timer or single-ball continuation.</x:t>
         </x:is>
       </x:c>
-      <x:c r="H13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Jackpot starts 100K (150K Bigger), +25K per upper-target hit, capped at 1M. Completing an active bank qualifies one non-stacking Add-a-Ball; upper targets flash green until collected below the 3-ball cap. More Jackpots enables the left bank. Both banks reset only on upper entry. More Time makes the upper-left post hold 12s instead of 8s; Safety Net extends the opening save from 10s to 20s; Shot Assist awards two extra right drops on the first right-drop hit. Each Jackpot banks its full value to vulcan_bonus.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reviewed/redesigned; needs machine playtest. Active bank GI pulses green and goes dark when exhausted; upper targets pulse purple normally and flash green for Add-a-Ball Ready.</x:t>
-        </x:is>
+      <x:c r="H13" s="31" t="str">
+        <x:v>Jackpot starts 100K (150K Bigger), +25K per upper-target hit, capped at 1M. Without More Jackpots, left drops use the normal 2K score/sound and the bank resets on completion. More Jackpots enables left-bank Jackpots; both active Jackpot banks reset only on upper entry. Completing an active Jackpot bank qualifies one non-stacking Add-a-Ball. More Time makes the upper-left post hold 12s instead of 8s; Safety Net extends the opening save from 10s to 20s; Shot Assist awards two extra right drops on the first right-drop hit. Each Jackpot banks its full value to vulcan_bonus.</x:v>
+      </x:c>
+      <x:c r="I13" s="31" t="str">
+        <x:v>Reviewed/redesigned; needs machine playtest. Active Jackpot-bank GI pulses green and goes dark when exhausted; upper targets pulse purple normally and flash green for Add-a-Ball Ready. Verify the regular left bank resets immediately without More Jackpots and waits for upper entry with More Jackpots.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -11607,25 +11471,17 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right bank reveals the Phantom location; shoot the revealed location before the window closes.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ends after the Phantom reveal rounds are completed, or when reveal/assist rules resolve; otherwise stops on ball end. When a saucer makes the terminal collect, that ball remains held until the villain summary ends.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Right bank reveals the Phantom location; later reveals give more time but lower value.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Good: reveal countdown/status and location messages are present.</x:t>
-        </x:is>
+      <x:c r="F19" s="31" t="str">
+        <x:v>Hit a right drop or STAR to reveal the hidden Phantom shot, then collect it before the window closes. STAR gives a live four-second reveal and remains repeatable.</x:v>
+      </x:c>
+      <x:c r="G19" s="31" t="str">
+        <x:v>Ends after five reveal rounds, or six with More Jackpots; otherwise stops on ball end. When a saucer makes the terminal collect, that ball remains held until the villain summary ends.</x:v>
+      </x:c>
+      <x:c r="H19" s="31" t="str">
+        <x:v>Unique right drops add time but progressively lower the jackpot. STAR adds four seconds without increasing the reveal count or lowering value.</x:v>
+      </x:c>
+      <x:c r="I19" s="31" t="str">
+        <x:v>Right-bank GI pulses throughout. Standing right-drop inserts flash green; hit drops are solid green. STAR flashes red. Revealed white-lens locations flash purple at 250ms on/off; SAUCERS flashes only the six red hole lamps, not the green number inserts. Needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -11712,10 +11568,8 @@
           <x:t xml:space="preserve">Drops raise the frozen-diamond jackpot and bank diamond_bonus. STAR freezes the chase and lights all three saucers for 10 seconds, or 15 with More Time.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bigger Jackpots raises base and drop additions; Safety Net starts ball save; Shot Assist makes the first wrong saucer count.</x:t>
-        </x:is>
+      <x:c r="I21" s="31" t="str">
+        <x:v>Bigger Jackpots raises base and drop additions; Safety Net starts ball save; Shot Assist makes the first wrong saucer count. The red-lens STAR insert now flashes red at 250ms on / 250ms off throughout the mode, including chase and freeze, and is explicitly stopped and cleared on teardown.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -12051,7 +11905,7 @@
         <x:v>Demons appear every 4s and remain active until collected. Jackpots are 200K, 250K, 300K, and 350K. Scepter phase lasts 20s and awards a 1M Super.</x:v>
       </x:c>
       <x:c r="I29" s="31" t="str">
-        <x:v>Dim 401010 background GI; active demons flash yellow every 300ms and return to dim red/off between pulses. During the scepter phase only the ramp/VUK area flashes yellow. More JP adds an independently flashing optional 500K demon.</x:v>
+        <x:v>Dim 401010 background GI; active demons flash yellow every 300ms. During the scepter phase only the ramp/VUK area flashes yellow. More JP adds an independently flashing optional 500K demon. Persistent SCEPTER TIME status and reminder cleanup require machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -12093,10 +11947,8 @@
           <x:t xml:space="preserve">40s base / 50s More Time. Area values 100K–350K, or 200K–450K with Bigger.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I30" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Restored regions remain lit. Safety Net starts ball save; Shot Assist spots one additional unrestored region.</x:t>
-        </x:is>
+      <x:c r="I30" s="31" t="str">
+        <x:v>Restored regions remain lit. Safety Net starts ball save; Shot Assist spots one additional unrestored region. Timer failure now produces the failed summary and completes progression cleanup; timeout and successful completion both need machine regression testing.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -12618,25 +12470,17 @@
           <x:t xml:space="preserve">2 staged / 1 active</x:t>
         </x:is>
       </x:c>
-      <x:c r="F42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shoot the VUK for 100K to hold Ball 1 and serve Ball 2 with a 10-second save. Lock Ball 2 in any saucer for 150K; it remains held while Ball 1 is kicked to the rooftop.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">After the 20-second attack expires, all flippers disable. When the active ball reaches the trough, the mode ends, the saucer ball releases, and normal single-ball play resumes. Losing Ball 2 before a saucer lock also ends the mode and releases the VUK ball.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Jackpot starts at 100K. Either spinner adds 50K per spin, capped at 1M. Any upper target collects the current value without resetting it. More Time = 28s; Safety Net = 25s save; Bigger = 150K VUK / 200K saucer / 200K starting JP; More Jackpots = 75K per spin; Shot Assist makes the upper target corresponding to the occupied saucer worth 3X once.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I42" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with phase lighting, live timer/value/jackpot status, one-time mapped 3X indication, timeout blackout, and summary variables; needs on-machine playtest.</x:t>
-        </x:is>
+      <x:c r="F42" s="31" t="str">
+        <x:v>Shoot the VUK for 100K to hold Ball 1 and serve Ball 2 with a 10-second save. Lock Ball 2 in any saucer for 150K; it remains held while Ball 1 is kicked to the rooftop.</x:v>
+      </x:c>
+      <x:c r="G42" s="31" t="str">
+        <x:v>After the 20-second attack expires, all flippers disable. When the active ball reaches the trough, gameplay ends but the saucer ball stays held through the villain summary. Shared occupancy-checked cleanup releases it after the summary. Losing Ball 2 before a saucer lock still ends the mode and releases the VUK ball.</x:v>
+      </x:c>
+      <x:c r="H42" s="31" t="str">
+        <x:v>Jackpot starts at 100K. Either spinner adds 50K per spin, capped at 1M. Any upper target collects the current value without resetting it. More Time = 28s; Safety Net = 25s save; Bigger = 150K VUK / 200K saucer / 200K starting JP; More Jackpots = 75K per spin; Shot Assist makes the upper target corresponding to the occupied saucer worth 3X once.</x:v>
+      </x:c>
+      <x:c r="I42" s="31" t="str">
+        <x:v>Implemented with phase lighting, live timer/value/jackpot status, one-time mapped 3X indication, timeout blackout, summary variables, and terminal saucer ownership transferred to the shared summary hold. Needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -12799,16 +12643,16 @@
         </x:is>
       </x:c>
       <x:c r="F46" s="31" t="str">
-        <x:v>Two-ball multiball. Left pop, center web and right pop independently light Saucer 1, 2 and 3. The rooftop gate remains closed.</x:v>
+        <x:v>Two-ball multiball. Both drop banks reset at startup. Persistent white guidance marks the left pop, center web and right pop, which independently light Saucer 1, 2 and 3. The rooftop gate remains closed.</x:v>
       </x:c>
       <x:c r="G46" s="31" t="str">
         <x:v>The mode ends immediately when Molemen multiball ends. Mode also stops at ball end.</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Pop hits score 50K and center web scores 100K. A lit saucer awards 250K multiplied by balls in play and resets that area. Each area can qualify add-a-ball once: 3 left-pop hits, 1 center-web hit, or 3 right-pop hits. More Time extends each add-a-ball shoot-again save from 10 to 15 seconds.</x:v>
+        <x:v>Pop hits score 50K and center web scores 100K. A lit saucer awards 250K multiplied by balls in play and resets that area. Each area can qualify add-a-ball once: 3 left-pop hits, 1 center-web hit, or 3 right-pop hits. More Jackpots lowers each pop requirement to 2. The matching green 1/2/3 insert stays solid while add-a-ball is ready. Completed left or right drop banks reset immediately.</x:v>
       </x:c>
       <x:c r="I46" s="31" t="str">
-        <x:v>Implemented with three mapped areas, saucer jackpot/add-a-ball shows, corrected two-second saucer eject requests, immediate multiball-end handling, Case Files, status and summary variables; needs on-machine playtest.</x:v>
+        <x:v>Implemented with startup and completed-bank drop resets; persistent white build-zone guidance; solid green 1/2/3 add-a-ball readiness; separately flashing red saucer-hole lamps; corrected two-second eject requests; immediate multiball-end handling; Case Files; status and summary. Needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -13507,15 +13351,11 @@
           <x:t xml:space="preserve">Bonus mode polish</x:t>
         </x:is>
       </x:c>
-      <x:c r="C3" s="45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timing/feel, bonus music, Held Bonus presentation, last-ball Hold Bonus clarity.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Polish</x:t>
-        </x:is>
+      <x:c r="C3" s="45" t="str">
+        <x:v>Timing/feel, bonus music, Held Bonus presentation, and last-ball Hold Bonus clarity. Regression-test a Cerberus drain with its timer running: gameplay widgets must be gone before bonus and no destroyed-widget update may occur.</x:v>
+      </x:c>
+      <x:c r="D3" s="45" t="str">
+        <x:v>Polish / Cerberus crash fix needs test</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="26" customFormat="1" ht="38" customHeight="1">
@@ -13549,15 +13389,11 @@
           <x:t xml:space="preserve">Daily Bugle / case-file widget verification</x:t>
         </x:is>
       </x:c>
-      <x:c r="C5" s="45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Confirm A/B Daily/Bugle status and case-file name/status text now display consistently.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Needs test</x:t>
-        </x:is>
+      <x:c r="C5" s="45" t="str">
+        <x:v>Confirm A/B Daily/Bugle status and Case File name/status text display consistently. Verify the Crime Tracker is removed at ball_ending, never reappears during bonus, returns at the next ball start, and still receives direct MPFVariable/MPFConditional updates without parent-widget recreation.</x:v>
+      </x:c>
+      <x:c r="D5" s="45" t="str">
+        <x:v>Implemented - needs regression test</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="26" customFormat="1" ht="38" customHeight="1">
@@ -13726,10 +13562,10 @@
         </x:is>
       </x:c>
       <x:c r="C13" s="45" t="str">
-        <x:v>Roster, implementation status, wizard Case File rules, mode identities, and the Case File matrix are synced to code. Master Technician's widget, gate, bank-reset and lighting fixes are documented; Master Technician, Sir Galahad, and Plotter still need machine tests.</x:v>
+        <x:v>Roster, implementation status, wizard Case File rules, mode identities, and the Case File matrix are synced to code. Recent fixes include shared saucer-summary holds, Cerberus bonus cleanup, the Chapter Select startup cover, Doctor Cool and Fifth Avenue Phantom lighting, Vulcan's conditional left-bank behavior, Kotep's persistent Scepter timer, and Super Swami's timer-failure summary cleanup. Machine-test Swami timeout and successful completion, confirming summary display, running-lock cleanup, and COMPLETED chapter state.</x:v>
       </x:c>
       <x:c r="D13" s="45" t="str">
-        <x:v>Updated 2026-08-22</x:v>
+        <x:v>Updated 2026-08-22 - Super Swami failure cleanup needs machine test</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="26" customFormat="1" ht="38" customHeight="1">
@@ -13853,15 +13689,11 @@
           <x:t xml:space="preserve">Playtest Dr. Manta relay</x:t>
         </x:is>
       </x:c>
-      <x:c r="C19" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Verify VUK hold, second-ball serve/save, saucer hold, VUK rooftop eject, both spinner increments, mapped one-time 3X target, all-flipper timeout, trough handoff, saucer release, and early second-ball-loss cleanup.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented - needs test</x:t>
-        </x:is>
+      <x:c r="C19" s="85" t="str">
+        <x:v>Verify VUK hold, second-ball serve/save, saucer hold, VUK rooftop eject, both spinner increments, mapped one-time 3X target, all-flipper timeout, trough handoff, no saucer eject during the summary, exactly one occupancy-checked release after the summary, and early second-ball-loss cleanup.</x:v>
+      </x:c>
+      <x:c r="D19" s="85" t="str">
+        <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -13876,12 +13708,10 @@
         </x:is>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>Verify two-ball start, closed rooftop gate, three area-to-saucer mappings, per-ball jackpot values, one-use add-a-ball per area, corrected two-second saucer eject timing, immediate mode end when multiball ends, 10s/15s add-a-ball shoot-again saves, Case Files, widget and cleanup.</x:v>
-      </x:c>
-      <x:c r="D20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented - needs test</x:t>
-        </x:is>
+        <x:v>Verify two-ball start, closed rooftop gate, startup reset of both drop banks, immediate reset after either bank completes, persistent white guidance for left pop / center web / right pop, matching green 1/2/3 solid while add-a-ball is ready, separately flashing red saucer-hole lamps, numbered insert clearing after collection, three area-to-saucer mappings, per-ball jackpot values, one-use add-a-ball per area, corrected two-second eject timing, immediate multiball-end behavior, Case Files, status and summary.</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>Implemented - needs test</x:v>
       </x:c>
     </x:row>
     <x:row r="21">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R06056c9762c24216"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rdbc49bbee93947f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rb2e98e188f494efb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rddf960bfcd8648da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R115cc720537c4758"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R02e9676371e14fe6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rebcf4e6c81914440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R39053281d4a94272"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rdbf6726fd6de4c40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R216c81d4d8ea40a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rdd3a9a7690d241f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R669fcf97292d47c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Ra7d3414ead5e4086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R50411f5bc54c437f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R4d0e730334b74473"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R1f99a498f48f45eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rc5d394992e9b4320"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R6b4d06736ead488f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R873e52f448be4a12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rc62a629561a14772"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rb2220c51a7684121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R84dceab1716c4a83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R77ba89d7eb944f8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R0de9c3b469e1400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R57b3f58e316140ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R04fafc65f862460d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -88,7 +88,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -145,6 +145,16 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="5">
     <x:border/>
@@ -174,7 +184,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="86">
+  <x:cellXfs count="94">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
@@ -373,6 +383,20 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -5288,15 +5312,13 @@
       <x:c r="E1" s="1" t="n"/>
     </x:row>
     <x:row r="2" s="26" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A2" s="83" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Source of truth: ASM67_2026_08_08_7pm. villain_bookends.py is canonical for villain/wizard gameplay music.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="1" t="n"/>
-      <x:c r="C2" s="1" t="n"/>
-      <x:c r="D2" s="1" t="n"/>
-      <x:c r="E2" s="1" t="n"/>
+      <x:c r="A2" s="83" t="str">
+        <x:v>Source of truth: current villain_bookends.py and music_control.yaml as of 2026-08-22. villain_bookends.py is canonical for villain/wizard gameplay music.</x:v>
+      </x:c>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
     </x:row>
     <x:row r="3" s="26" customFormat="1" ht="30" customHeight="1">
       <x:c r="A3" s="83" t="inlineStr">
@@ -5703,15 +5725,15 @@
           <x:t xml:space="preserve">shakeandstone</x:t>
         </x:is>
       </x:c>
-      <x:c r="C24" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Parafino; Vulcan</x:t>
-        </x:is>
+      <x:c r="C24" s="74" t="str">
+        <x:v>Parafino</x:v>
       </x:c>
       <x:c r="D24" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E24" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24" s="74" t="str">
+        <x:v>Vulcan reassigned to Song 64.</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A25" s="73" t="n">
@@ -5802,15 +5824,15 @@
           <x:t xml:space="preserve">twilight_guitar</x:t>
         </x:is>
       </x:c>
-      <x:c r="C29" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mysterio; Infinata</x:t>
-        </x:is>
+      <x:c r="C29" s="74" t="str">
+        <x:v>Infinata</x:v>
       </x:c>
       <x:c r="D29" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E29" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E29" s="74" t="str">
+        <x:v>Mysterio reassigned to Song 63.</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A30" s="73" t="n">
@@ -5821,15 +5843,15 @@
           <x:t xml:space="preserve">waiting</x:t>
         </x:is>
       </x:c>
-      <x:c r="C30" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Scorpion; 5th Ave Phantom</x:t>
-        </x:is>
+      <x:c r="C30" s="74" t="str">
+        <x:v>Scorpion</x:v>
       </x:c>
       <x:c r="D30" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E30" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30" s="74" t="str">
+        <x:v>5th Ave Phantom reassigned to Song 60.</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A31" s="77" t="n">
@@ -6049,15 +6071,15 @@
           <x:t xml:space="preserve">the_enchanted_sea</x:t>
         </x:is>
       </x:c>
-      <x:c r="C42" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Doctor Dumpty; Doctor Atlantean</x:t>
-        </x:is>
+      <x:c r="C42" s="74" t="str">
+        <x:v>Doctor Dumpty</x:v>
       </x:c>
       <x:c r="D42" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E42" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E42" s="74" t="str">
+        <x:v>Doctor Atlantean reassigned to Song 62.</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A43" s="73" t="n">
@@ -6125,15 +6147,15 @@
           <x:t xml:space="preserve">action_line</x:t>
         </x:is>
       </x:c>
-      <x:c r="C46" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Desperado; The Plotter</x:t>
-        </x:is>
+      <x:c r="C46" s="74" t="str">
+        <x:v>The Plotter</x:v>
       </x:c>
       <x:c r="D46" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E46" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E46" s="74" t="str">
+        <x:v>Desperado reassigned to Song 59.</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A47" s="73" t="n">
@@ -6872,6 +6894,132 @@
         <x:is>
           <x:t xml:space="preserve">Attract</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="20" customHeight="1">
+      <x:c r="A84" s="88" t="str">
+        <x:v>Newly Added Track Assignments</x:v>
+      </x:c>
+      <x:c r="B84" s="88"/>
+      <x:c r="C84" s="88"/>
+      <x:c r="D84" s="88"/>
+      <x:c r="E84" s="88"/>
+    </x:row>
+    <x:row r="85" ht="24" customHeight="1">
+      <x:c r="A85" s="91" t="str">
+        <x:v>Song #</x:v>
+      </x:c>
+      <x:c r="B85" s="91" t="str">
+        <x:v>Configured Asset</x:v>
+      </x:c>
+      <x:c r="C85" s="91" t="str">
+        <x:v>Effective Uses</x:v>
+      </x:c>
+      <x:c r="D85" s="91" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="E85" s="91" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="93" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B86" s="93" t="str">
+        <x:v>ride_into_the_sun</x:v>
+      </x:c>
+      <x:c r="C86" s="93" t="str">
+        <x:v>Desperado</x:v>
+      </x:c>
+      <x:c r="D86" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E86" s="93" t="str">
+        <x:v>New villain assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="93" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B87" s="93" t="str">
+        <x:v>foot_patter</x:v>
+      </x:c>
+      <x:c r="C87" s="93" t="str">
+        <x:v>5th Ave Phantom</x:v>
+      </x:c>
+      <x:c r="D87" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E87" s="93" t="str">
+        <x:v>New villain assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="93" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B88" s="93" t="str">
+        <x:v>wild_weekend_intro</x:v>
+      </x:c>
+      <x:c r="C88" s="93"/>
+      <x:c r="D88" s="93" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E88" s="93" t="str">
+        <x:v>Reserved for a future purpose; not assigned to villain/wizard gameplay.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="93" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B89" s="93" t="str">
+        <x:v>sheba</x:v>
+      </x:c>
+      <x:c r="C89" s="93" t="str">
+        <x:v>Doctor Atlantean</x:v>
+      </x:c>
+      <x:c r="D89" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E89" s="93" t="str">
+        <x:v>New villain assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="93" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B90" s="93" t="str">
+        <x:v>man_of_mystery</x:v>
+      </x:c>
+      <x:c r="C90" s="93" t="str">
+        <x:v>Mysterio</x:v>
+      </x:c>
+      <x:c r="D90" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E90" s="93" t="str">
+        <x:v>New villain assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="93" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B91" s="93" t="str">
+        <x:v>bombora</x:v>
+      </x:c>
+      <x:c r="C91" s="93" t="str">
+        <x:v>Vulcan</x:v>
+      </x:c>
+      <x:c r="D91" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E91" s="93" t="str">
+        <x:v>New villain assignment.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R50411f5bc54c437f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R4d0e730334b74473"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R1f99a498f48f45eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rc5d394992e9b4320"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R6b4d06736ead488f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R873e52f448be4a12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rc62a629561a14772"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rb2220c51a7684121"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R84dceab1716c4a83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R77ba89d7eb944f8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R0de9c3b469e1400e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R57b3f58e316140ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R04fafc65f862460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R984ccccbbf2c40dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Re888b0a7366f41ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R3f1d819b43354a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R4f4e292d074f480f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R8cdd87ce817a4d53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rc756458b08f94ab8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R9f5d4f2503ac4a3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Ra5464f54c5094064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R3880576f9e924761"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rbfa6f6d34dd94cb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R54add5107de24e7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rca368cc306fe4fe7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Rfc2ee590ae274dcb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -88,7 +88,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="14">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -155,6 +155,16 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="5">
     <x:border/>
@@ -184,7 +194,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="94">
+  <x:cellXfs count="98">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
@@ -399,6 +409,10 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -5313,7 +5327,7 @@
     </x:row>
     <x:row r="2" s="26" customFormat="1" ht="30" customHeight="1">
       <x:c r="A2" s="83" t="str">
-        <x:v>Source of truth: current villain_bookends.py and music_control.yaml as of 2026-08-22. villain_bookends.py is canonical for villain/wizard gameplay music.</x:v>
+        <x:v>Source of truth: current villain_bookends.py and music_control.py/yaml as of 2026-08-23. Bookends own villain/wizard music; music_control owns chapter base music.</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -5321,15 +5335,13 @@
       <x:c r="E2" s="1"/>
     </x:row>
     <x:row r="3" s="26" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A3" s="83" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rule: every villain/wizard gameplay song has at most two uses. maintheme, loop*, and intro_* tracks do not soundtrack villain/wizard gameplay; shared transition/core uses may remain.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="1" t="n"/>
-      <x:c r="C3" s="1" t="n"/>
-      <x:c r="D3" s="1" t="n"/>
-      <x:c r="E3" s="1" t="n"/>
+      <x:c r="A3" s="83" t="str">
+        <x:v>Rule: chapter base themes use longer songs. Villain/wizard songs have at most two uses; maintheme, loop*, and intro_* tracks remain outside villain/wizard gameplay.</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
     </x:row>
     <x:row r="5" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A5" s="72" t="inlineStr">
@@ -5362,39 +5374,31 @@
       <x:c r="A6" s="73" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">prowl_car</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Main play random pool</x:t>
-        </x:is>
+      <x:c r="B6" s="74" t="str">
+        <x:v>prowl_car</x:v>
+      </x:c>
+      <x:c r="C6" s="74" t="str">
+        <x:v>Chapter 1 base — Sinister Surge</x:v>
       </x:c>
       <x:c r="D6" s="73" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E6" s="74" t="str"/>
+      <x:c r="E6" s="74"/>
     </x:row>
     <x:row r="7" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A7" s="73" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">panic_patrol</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Main play random pool</x:t>
-        </x:is>
+      <x:c r="B7" s="74" t="str">
+        <x:v>panic_patrol</x:v>
+      </x:c>
+      <x:c r="C7" s="74" t="str">
+        <x:v>Chapter 2 base — Mastermind Trap</x:v>
       </x:c>
       <x:c r="D7" s="73" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E7" s="74" t="str"/>
+      <x:c r="E7" s="74"/>
     </x:row>
     <x:row r="8" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A8" s="73" t="n">
@@ -5499,39 +5503,35 @@
       <x:c r="A13" s="73" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B13" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">cloak</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sandman; Dr. Von Schlick</x:t>
-        </x:is>
+      <x:c r="B13" s="74" t="str">
+        <x:v>cloak</x:v>
+      </x:c>
+      <x:c r="C13" s="74" t="str">
+        <x:v>Dr. Von Schlick</x:v>
       </x:c>
       <x:c r="D13" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E13" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="74" t="str">
+        <x:v>Sandman reassigned to Song 80.</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A14" s="73" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B14" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">fright</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Skymaster; main play random pool</x:t>
-        </x:is>
+      <x:c r="B14" s="74" t="str">
+        <x:v>fright</x:v>
+      </x:c>
+      <x:c r="C14" s="74" t="str">
+        <x:v>Skymaster</x:v>
       </x:c>
       <x:c r="D14" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E14" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="74" t="str">
+        <x:v>Removed from the former random main-play pool.</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A15" s="73" t="n">
@@ -5655,23 +5655,15 @@
       <x:c r="A21" s="77" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B21" s="78" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">loop_123456</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C21" s="78" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Main play random pool</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="B21" s="78" t="str">
+        <x:v>loop_123456</x:v>
+      </x:c>
+      <x:c r="C21" s="78"/>
       <x:c r="D21" s="77" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E21" s="78" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Protected loop* track retained outside villain/wizard gameplay.</x:t>
-        </x:is>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="78" t="str">
+        <x:v>Protected loop* track; no longer used for main play.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" s="26" customFormat="1" ht="15" customHeight="1">
@@ -5838,77 +5830,67 @@
       <x:c r="A30" s="73" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B30" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">waiting</x:t>
-        </x:is>
+      <x:c r="B30" s="74" t="str">
+        <x:v>waiting</x:v>
       </x:c>
       <x:c r="C30" s="74" t="str">
-        <x:v>Scorpion</x:v>
+        <x:v>Chapter 6 base — Fifth Dimension Curse</x:v>
       </x:c>
       <x:c r="D30" s="73" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E30" s="74" t="str">
-        <x:v>5th Ave Phantom reassigned to Song 60.</x:v>
+        <x:v>Scorpion reassigned to Song 72.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A31" s="77" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B31" s="78" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">intro_mild</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C31" s="78" t="str"/>
+      <x:c r="B31" s="78" t="str">
+        <x:v>intro_mild_2</x:v>
+      </x:c>
+      <x:c r="C31" s="78"/>
       <x:c r="D31" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="78" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Protected intro_* duplicate; unused.</x:t>
-        </x:is>
+      <x:c r="E31" s="78" t="str">
+        <x:v>Protected intro_* track; reserved for later use.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A32" s="73" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B32" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">dash_to_safety_2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C32" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dr. Magneto; The Spider-Men</x:t>
-        </x:is>
+      <x:c r="B32" s="74" t="str">
+        <x:v>dash_to_safety_2</x:v>
+      </x:c>
+      <x:c r="C32" s="74" t="str">
+        <x:v>Dr. Magneto</x:v>
       </x:c>
       <x:c r="D32" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E32" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E32" s="74" t="str">
+        <x:v>The Spider-Men reassigned to Song 74.</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A33" s="73" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B33" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">dash_to_safety_3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C33" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Professor Pretorius; Charles Cameo</x:t>
-        </x:is>
+      <x:c r="B33" s="74" t="str">
+        <x:v>dash_to_safety_3</x:v>
+      </x:c>
+      <x:c r="C33" s="74" t="str">
+        <x:v>Professor Pretorius</x:v>
       </x:c>
       <x:c r="D33" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E33" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E33" s="74" t="str">
+        <x:v>Charles Cameo reassigned to Song 70.</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A34" s="73" t="n">
@@ -6028,20 +6010,18 @@
       <x:c r="A40" s="73" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B40" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">spooky</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C40" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Kotep; Super Swami</x:t>
-        </x:is>
+      <x:c r="B40" s="74" t="str">
+        <x:v>spooky</x:v>
+      </x:c>
+      <x:c r="C40" s="74" t="str">
+        <x:v>Kotep</x:v>
       </x:c>
       <x:c r="D40" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E40" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E40" s="74" t="str">
+        <x:v>Super Swami reassigned to Song 73.</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A41" s="73" t="n">
@@ -6351,20 +6331,18 @@
       <x:c r="A57" s="73" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B57" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">topsy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C57" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Devargas; Brutus</x:t>
-        </x:is>
+      <x:c r="B57" s="74" t="str">
+        <x:v>topsy</x:v>
+      </x:c>
+      <x:c r="C57" s="74" t="str">
+        <x:v>DeVargas</x:v>
       </x:c>
       <x:c r="D57" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E57" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E57" s="74" t="str">
+        <x:v>Brutus reassigned to Song 76.</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A58" s="73" t="n">
@@ -6740,25 +6718,17 @@
           <x:t xml:space="preserve">intro_*</x:t>
         </x:is>
       </x:c>
-      <x:c r="B77" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12 / 26 — intro_mild</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C77" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">None</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D77" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E77" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">None currently</x:t>
-        </x:is>
+      <x:c r="B77" s="85" t="str">
+        <x:v>12 — intro_mild; 26 — intro_mild_2</x:v>
+      </x:c>
+      <x:c r="C77" s="85" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D77" s="85" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="E77" s="85" t="str">
+        <x:v>Reserved for later use</x:v>
       </x:c>
     </x:row>
     <x:row r="78" s="26" customFormat="1" ht="15" customHeight="1">
@@ -6863,10 +6833,8 @@
           <x:t xml:space="preserve">OK</x:t>
         </x:is>
       </x:c>
-      <x:c r="E81" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Main-play random pool</x:t>
-        </x:is>
+      <x:c r="E81" s="85" t="str">
+        <x:v>None currently</x:v>
       </x:c>
     </x:row>
     <x:row r="82" s="26" customFormat="1" ht="15" customHeight="1">
@@ -6936,7 +6904,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E86" s="93" t="str">
-        <x:v>New villain assignment.</x:v>
+        <x:v>Villain assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -6953,7 +6921,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E87" s="93" t="str">
-        <x:v>New villain assignment.</x:v>
+        <x:v>Villain assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -6968,7 +6936,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E88" s="93" t="str">
-        <x:v>Reserved for a future purpose; not assigned to villain/wizard gameplay.</x:v>
+        <x:v>Reserved for a future purpose.</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -6985,7 +6953,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E89" s="93" t="str">
-        <x:v>New villain assignment.</x:v>
+        <x:v>Villain assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -7002,7 +6970,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E90" s="93" t="str">
-        <x:v>New villain assignment.</x:v>
+        <x:v>Villain assignment.</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -7019,7 +6987,503 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E91" s="93" t="str">
-        <x:v>New villain assignment.</x:v>
+        <x:v>Villain assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>assault_course</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>Chapter 9 base — Invasion from Everywhere</x:v>
+      </x:c>
+      <x:c r="D92" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E92" t="str">
+        <x:v>Chapter base theme.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>tropic_waters</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>Chapter 8 base — Nature Strikes Back</x:v>
+      </x:c>
+      <x:c r="D93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E93" t="str">
+        <x:v>Chapter base theme.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>sample_syndicate</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>Chapter 7 base — Mad Science Meltdown</x:v>
+      </x:c>
+      <x:c r="D94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E94" t="str">
+        <x:v>Chapter base theme.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>men_of_action</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>Chapter 5 base — The Web Tightens</x:v>
+      </x:c>
+      <x:c r="D95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E95" t="str">
+        <x:v>Chapter base theme.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>shaker_loop_1</x:v>
+      </x:c>
+      <x:c r="C96"/>
+      <x:c r="D96" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E96" t="str">
+        <x:v>Short loop; currently unassigned.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>news_views</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>Charles Cameo</x:v>
+      </x:c>
+      <x:c r="D97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E97" t="str">
+        <x:v>Short villain-mode assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>hell_raisers</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>Chapter 3 base — Trubble Unleashed</x:v>
+      </x:c>
+      <x:c r="D98" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E98" t="str">
+        <x:v>Chapter base theme.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>scorpion</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>Scorpion</x:v>
+      </x:c>
+      <x:c r="D99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>Villain assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>last_night</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>Super Swami</x:v>
+      </x:c>
+      <x:c r="D100" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E100" t="str">
+        <x:v>Replaces the duplicate use of Spooky.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>teen_beat</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>The Spider-Men</x:v>
+      </x:c>
+      <x:c r="D101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E101" t="str">
+        <x:v>Replaces the duplicate use of Dash to Safety 2.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>harlem_intro</x:v>
+      </x:c>
+      <x:c r="C102"/>
+      <x:c r="D102" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>Short intro; currently unassigned.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>bulldog</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Brutus</x:v>
+      </x:c>
+      <x:c r="D103" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>Short villain-mode assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>orinoco</x:v>
+      </x:c>
+      <x:c r="C104"/>
+      <x:c r="D104" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>Short track; currently unassigned.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>not_so_private_eye</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>Chapter 10 base — Who Is the Real Villain?</x:v>
+      </x:c>
+      <x:c r="D105" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>Chapter base theme.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>traffic_jam</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>Chapter 4 base — Crime Wave</x:v>
+      </x:c>
+      <x:c r="D106" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E106" t="str">
+        <x:v>Chapter base theme.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>sand_storm</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>Sandman</x:v>
+      </x:c>
+      <x:c r="D107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E107" t="str">
+        <x:v>Villain assignment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>let_there_be_drums</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>Chapter 11 base — Time-Tossed Showdown</x:v>
+      </x:c>
+      <x:c r="D108" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E108" t="str">
+        <x:v>Chapter base theme.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="95" t="str">
+        <x:v>Chapter Base Music</x:v>
+      </x:c>
+      <x:c r="B111" s="95"/>
+      <x:c r="C111" s="95"/>
+      <x:c r="D111" s="95"/>
+      <x:c r="E111" s="95"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="97" t="str">
+        <x:v>Chapter #</x:v>
+      </x:c>
+      <x:c r="B112" s="97" t="str">
+        <x:v>Chapter</x:v>
+      </x:c>
+      <x:c r="C112" s="97" t="str">
+        <x:v>Song #</x:v>
+      </x:c>
+      <x:c r="D112" s="97" t="str">
+        <x:v>Configured Asset</x:v>
+      </x:c>
+      <x:c r="E112" s="97" t="str">
+        <x:v>Restore Behavior</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>Sinister Surge</x:v>
+      </x:c>
+      <x:c r="C113" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D113" t="str">
+        <x:v>prowl_car</x:v>
+      </x:c>
+      <x:c r="E113" t="str">
+        <x:v>After skill shot and villain summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>Mastermind Trap</x:v>
+      </x:c>
+      <x:c r="C114" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D114" t="str">
+        <x:v>panic_patrol</x:v>
+      </x:c>
+      <x:c r="E114" t="str">
+        <x:v>After skill shot and villain summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>Trubble Unleashed</x:v>
+      </x:c>
+      <x:c r="C115" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D115" t="str">
+        <x:v>hell_raisers</x:v>
+      </x:c>
+      <x:c r="E115" t="str">
+        <x:v>After skill shot and villain summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>Crime Wave</x:v>
+      </x:c>
+      <x:c r="C116" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D116" t="str">
+        <x:v>traffic_jam</x:v>
+      </x:c>
+      <x:c r="E116" t="str">
+        <x:v>After skill shot and villain summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>The Web Tightens</x:v>
+      </x:c>
+      <x:c r="C117" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D117" t="str">
+        <x:v>men_of_action</x:v>
+      </x:c>
+      <x:c r="E117" t="str">
+        <x:v>After skill shot and villain summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>Fifth Dimension Curse</x:v>
+      </x:c>
+      <x:c r="C118" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D118" t="str">
+        <x:v>waiting</x:v>
+      </x:c>
+      <x:c r="E118" t="str">
+        <x:v>After skill shot and villain summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>Mad Science Meltdown</x:v>
+      </x:c>
+      <x:c r="C119" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D119" t="str">
+        <x:v>sample_syndicate</x:v>
+      </x:c>
+      <x:c r="E119" t="str">
+        <x:v>After skill shot and villain summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>Nature Strikes Back</x:v>
+      </x:c>
+      <x:c r="C120" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D120" t="str">
+        <x:v>tropic_waters</x:v>
+      </x:c>
+      <x:c r="E120" t="str">
+        <x:v>After skill shot and villain summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>Invasion from Everywhere</x:v>
+      </x:c>
+      <x:c r="C121" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>assault_course</x:v>
+      </x:c>
+      <x:c r="E121" t="str">
+        <x:v>After skill shot and villain summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>Who Is the Real Villain?</x:v>
+      </x:c>
+      <x:c r="C122" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D122" t="str">
+        <x:v>not_so_private_eye</x:v>
+      </x:c>
+      <x:c r="E122" t="str">
+        <x:v>After skill shot and villain summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
+      </x:c>
+      <x:c r="C123" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D123" t="str">
+        <x:v>let_there_be_drums</x:v>
+      </x:c>
+      <x:c r="E123" t="str">
+        <x:v>After skill shot and villain summary</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8250,10 +8714,10 @@
         </x:is>
       </x:c>
       <x:c r="G27" s="31" t="str">
-        <x:v>Implemented / recent rule update</x:v>
+        <x:v>Implemented / recent spinner lighting fix</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Five chances, or seven with More JP. Each chance presents three choices; spinner reveals the correct choice for 3s, or 5s with More Time. Three correct shots defeats Pardo immediately. Using all chances with fewer than three correct shots produces the escape result. Hidden choices use solid green for white/green lens compatibility; reveal flashes only the correct green choice and turns wrong choices off. Result GI flashes for 350ms, then restores.</x:v>
+        <x:v>Five chances, or seven with More JP. Each chance presents three choices; spinner reveals the correct choice for 3s, or 5s with More Time. Three correct shots defeats Pardo immediately. Using all chances with fewer than three correct shots produces the escape result. Hidden choices use solid green for white/green lens compatibility; reveal flashes only the correct green choice and turns wrong choices off. The main spinner insert flashes white while choices are hidden, turns off during the reveal, and resumes if another reveal is needed. Result GI flashes for 350ms, then restores.</x:v>
       </x:c>
       <x:c r="I27" s="31" t="inlineStr">
         <x:is>
@@ -9108,10 +9572,10 @@
         </x:is>
       </x:c>
       <x:c r="G46" s="31" t="str">
-        <x:v>Implemented / recent drop-reset and add-a-ball lighting fix</x:v>
+        <x:v>Implemented / recent target-zone pulse fix</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Two-ball area-control multiball. Left pop lights Saucer 1, center web lights Saucer 2, and right pop lights Saucer 3. Both drop banks reset at mode startup and their completed-bank events reset them again for continued play. Persistent white guidance identifies the three build zones. When an area's one-use add-a-ball is ready, its matching green 1, 2, or 3 insert stays solid while the red saucer-hole lamps flash; collection clears the numbered insert with the area. Lit saucers award 250K per ball in play. Needs machine playtest.</x:v>
+        <x:v>Two-ball area-control multiball. Left pop lights Saucer 1, center web lights Saucer 2, and right pop lights Saucer 3. Both drop banks reset at mode startup and their completed-bank events reset them again for continued play. The left-pop ring, center-web insert, and right-pop ring pulse white to identify the three build targets. When an area's one-use add-a-ball is ready, its matching green 1, 2, or 3 insert stays solid while the red saucer-hole lamps flash; collection clears the numbered insert with the area. Lit saucers award 250K per ball in play. Needs machine playtest.</x:v>
       </x:c>
       <x:c r="I46" s="31" t="inlineStr">
         <x:is>
@@ -9425,15 +9889,11 @@
           <x:t xml:space="preserve">Master Vine</x:t>
         </x:is>
       </x:c>
-      <x:c r="G53" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H53" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Vine Invasion: the gate starts open. Upper entry starts one of three 30s waves, resets both banks and all lower states, and closes the gate. Each upper-spinner pulse scores 25K, resets the timer, and lights one unique available lower shot from 22 objectives. Lit shots pulse; collected shots score 50K and remain dim solid. Waves 1–2 open the gate on expiry; the third expiry ends the mode. Case Files add a three-shot first spin, 75K jackpots, 40s waves, a first-entry 10s save, and a first-jackpot assist.</x:t>
-        </x:is>
+      <x:c r="G53" s="31" t="str">
+        <x:v>Implemented / recent route-lighting fix</x:v>
+      </x:c>
+      <x:c r="H53" s="31" t="str">
+        <x:v>Vine Invasion: the gate starts open. A five-step chase runs from the spinner insert toward the VUK while roof access is open; the left-lower and spinner GI lamps illuminate together on step 2, followed by left-upper, ramp, and top VUK-side GI. VUK capture clears the chase and changes the spinner GI to a standalone flash. Upper entry starts one of three 30s waves, resets both banks and all lower states, and closes the gate. Each spinner pulse scores 25K, resets the timer, and lights one unique lower shot from 22 objectives. Lit shots pulse; collected shots score 50K and remain dim solid. Waves 1–2 reopen the gate; the third expiry ends the mode. Case Files add a three-shot first spin, 75K jackpots, 40s waves, a first-entry 10s save, and a first-jackpot assist.</x:v>
       </x:c>
       <x:c r="I53" s="31" t="inlineStr">
         <x:is>
@@ -9472,10 +9932,10 @@
         </x:is>
       </x:c>
       <x:c r="G54" s="31" t="str">
-        <x:v>Implemented / recent widget-device-lighting fix</x:v>
+        <x:v>Implemented / recent startup fix</x:v>
       </x:c>
       <x:c r="H54" s="31" t="str">
-        <x:v>60-second spinner/drop score attack. Drops score 25K and build a repeatable spinner value by 50K each through seven down; all eight costs 10 seconds and resets both banks. Widget now uses the existing portrait, the lower-playfield route closes the rooftop gate, bank resets are staggered 300ms, and complete lens-safe lighting/feedback is defined.</x:v>
+        <x:v>60-second spinner/drop score attack. Drops score 25K and build a repeatable spinner value by 50K each through seven down; all eight costs 10 seconds and resets both banks. Startup now waits until every Python gameplay handler is registered before resetting the banks, closing the rooftop gate, and starting the timer, scoring, status display, and lighting. Widget uses the existing portrait, bank resets are staggered 300ms, and complete lens-safe lighting/feedback is defined. Needs machine playtest.</x:v>
       </x:c>
       <x:c r="I54" s="31" t="inlineStr">
         <x:is>
@@ -9559,15 +10019,11 @@
           <x:t xml:space="preserve">Baron Von Rantenraven</x:t>
         </x:is>
       </x:c>
-      <x:c r="G56" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H56" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sky Harbor limited-flips rooftop assault: saucers open roof access; upper entry starts a 10-flip attempt; three unique upper targets lead to a remaining-flips Super, with repeat-target scoring and case-file support.</x:t>
-        </x:is>
+      <x:c r="G56" s="31" t="str">
+        <x:v>Implemented / recent saucer-lighting fix</x:v>
+      </x:c>
+      <x:c r="H56" s="31" t="str">
+        <x:v>Sky Harbor: hit any saucer to open roof access, guided by the six red saucer-hole lamps rather than the green 1–2–3 inserts. Upper entry starts a limited-flip rooftop assault. Hit all three unique upper targets; the first two award jackpots and the third awards the Super Jackpot, boosted by remaining flips. Repeats score 250K, and running out of flips permits another qualification attempt.</x:v>
       </x:c>
       <x:c r="I56" s="31" t="inlineStr">
         <x:is>
@@ -12917,10 +13373,8 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F49" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Complete unique targets on the right 5-bank. Round 1 allows one shot before Desperado escapes and resets the bank; each later round allows one more shot.</x:t>
-        </x:is>
+      <x:c r="F49" s="31" t="str">
+        <x:v>60-second right-bank pursuit. Round 1 allows one hit before the bank sweeps and resets; each later round allows one additional hit, up to five. Find all five unique outlaws: new targets score 200K, repeats 50K, and the left bank adds 10 seconds. Incomplete green-lens inserts pulse bright/dim green; completed targets remain solid green across resets. Status shows round, time, unique targets, and current-round hits. The rooftop gate closes at start and unexpected VUK balls eject. Progression exclusively owns stop and summary sequencing. Case Files: More JP adds a 500K final showdown; Bigger scores 250K/75K; More Time starts at 70s; Safety Net starts a 10s save; Shot Assist spots another unique target in round 2. Coded and validated; needs on-machine playtest.</x:v>
       </x:c>
       <x:c r="G49" s="31" t="inlineStr">
         <x:is>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R984ccccbbf2c40dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Re888b0a7366f41ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R3f1d819b43354a5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R4f4e292d074f480f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R8cdd87ce817a4d53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rc756458b08f94ab8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R9f5d4f2503ac4a3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Ra5464f54c5094064"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R3880576f9e924761"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rbfa6f6d34dd94cb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R54add5107de24e7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rca368cc306fe4fe7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Rfc2ee590ae274dcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf2348dcab4f54eb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R95d575b6cb1c4ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rde21dc13a5d04b0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R165e01178f794c42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Raec3f1f81bbe4bdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R94c36a04fe1448d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R724c94eec5bd41b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R7f244f4467c54f8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rb1cd643e221b407d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R22f06ab9b7bf47c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R0890f5a3b36c4ce1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rc3461931362d4f1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Re03b628928264a2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11985,10 +11985,8 @@
           <x:t xml:space="preserve">Three Scheme Jackpots, then timed VUK Super</x:t>
         </x:is>
       </x:c>
-      <x:c r="F17" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pulse green pops to build Rumors. Spend two at the yellow lower spinner to light a red saucer. Collect three schemes, then follow yellow VUK guidance. The upper spinner is unused.</x:t>
-        </x:is>
+      <x:c r="F17" s="31" t="str">
+        <x:v>Pulse green pops to build Rumors. Spend two at the yellow lower spinner to light a red saucer. Collect three schemes, then follow the shared Master Vine route chase to the VUK. The upper spinner is unused.</x:v>
       </x:c>
       <x:c r="G17" s="31" t="inlineStr">
         <x:is>
@@ -12000,10 +11998,8 @@
           <x:t xml:space="preserve">Base: pops 25K, spinner 50K, schemes 250K, VUK 1M, Back Page 500K. Bigger: pops 50K, spinner 100K, schemes 500K; VUK and Back Page unchanged.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I17" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with amber GI, green pop guidance, yellow spinner/VUK guidance, red saucers and upper targets, one-use unlit-saucer Shot Assist, shared summary variables, and local runtime state. Needs machine playtest.</x:t>
-        </x:is>
+      <x:c r="I17" s="31" t="str">
+        <x:v>Implemented with amber GI, green pop guidance, red saucers, one-use unlit-saucer Shot Assist, shared summary variables, and the shared Master Vine route chase during the timed VUK phase. The chase stops on the VUK Super, timeout, failure, ball end, or mode stop. Needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -12305,10 +12301,8 @@
           <x:t xml:space="preserve">Successful lit shots score 50K; Bigger raises them to 75K. Slayer Jackpot starts at 2M, or 2.5M with Bigger, and decays to a 100K minimum. An unlit VUK visit uses the shared 1.5-second eject.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">More Jackpots freezes the full jackpot for 10 seconds. More Time halves decay to 50K/sec. Safety Net starts a 10-second save when the VUK lights. Shot Assist makes the first hit add two new categories.</x:t>
-        </x:is>
+      <x:c r="I24" s="31" t="str">
+        <x:v>More Jackpots freezes the full jackpot for 10 seconds. More Time halves decay to 50K/sec. Safety Net starts a 10-second save when the VUK lights. Shot Assist makes the first hit add two new categories. The shared Master Vine route chase guides the terminal VUK and clears on collect or teardown; needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -12509,7 +12503,7 @@
         <x:v>Demons appear every 4s and remain active until collected. Jackpots are 200K, 250K, 300K, and 350K. Scepter phase lasts 20s and awards a 1M Super.</x:v>
       </x:c>
       <x:c r="I29" s="31" t="str">
-        <x:v>Dim 401010 background GI; active demons flash yellow every 300ms. During the scepter phase only the ramp/VUK area flashes yellow. More JP adds an independently flashing optional 500K demon. Persistent SCEPTER TIME status and reminder cleanup require machine playtest.</x:v>
+        <x:v>Dim 401010 background GI; active demons flash yellow every 300ms. The shared Master Vine route chase guides the timed final VUK shot during the scepter phase and clears on collect, timeout, or teardown. More JP adds an independently flashing optional 500K demon. Needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -12552,7 +12546,7 @@
         </x:is>
       </x:c>
       <x:c r="I30" s="31" t="str">
-        <x:v>Restored regions remain lit. Safety Net starts ball save; Shot Assist spots one additional unrestored region. Timer failure now produces the failed summary and completes progression cleanup; timeout and successful completion both need machine regression testing.</x:v>
+        <x:v>Restored regions remain lit. With More Jackpots, the shared Master Vine route chase guides the final 500K Blackout Jackpot at the VUK and clears on collect, timeout, or teardown. Safety Net starts ball save; Shot Assist spots one additional unrestored region. Needs machine regression testing.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -12729,10 +12723,8 @@
           <x:t xml:space="preserve">Each of the 12 reactor hits scores 100K; each actual cooling spin scores 50K; the VUK Super is 500K. Bigger Jackpots makes reactor and eligible right-bank hits 150K, while the Super remains 500K.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I34" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">More Jackpots scores all five unique right drops, but only the first three add progress and heat. More Time makes overheat grace 8 seconds. Safety Net is a 10-second opening save. Shot Assist drops a random second left target with full score, progress, and heat.</x:t>
-        </x:is>
+      <x:c r="I34" s="31" t="str">
+        <x:v>More Jackpots scores all five unique right drops, but only the first three add progress and heat. More Time makes overheat grace 8 seconds. Safety Net is a 10-second opening save. Shot Assist drops a random second left target. The shared Master Vine route chase guides the terminal Reactor Super VUK and clears on collect, failure, or teardown; needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -12809,20 +12801,16 @@
           <x:t xml:space="preserve">Follow one green moving shot across left web, left drops, left pop, center web, right pop, and right drops, reversing every 4 seconds.</x:t>
         </x:is>
       </x:c>
-      <x:c r="G36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Five pellets open the gate and light the VUK for 20 seconds. VUK starts the held-ball eight-band blue flood and awards 1M at completion.</x:t>
-        </x:is>
+      <x:c r="G36" s="31" t="str">
+        <x:v>Five pellets open the gate and light the VUK for 20 seconds. A qualified VUK capture immediately cancels pending shared ejects/retries and arms the hold before the eight-band blue flood begins. The ball remains held through the four-second flood and villain summary; flood completion awards 1M.</x:v>
       </x:c>
       <x:c r="H36" s="31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Pellets 100K or 150K with Bigger. Wrong shots score only normal game points.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">More Jackpots allows two optional pellets after qualification; More Time 30s; Safety Net at Super; Shot Assist makes first pellet count twice. Daily Bugle A+B cannot open the gate.</x:t>
-        </x:is>
+      <x:c r="I36" s="31" t="str">
+        <x:v>Implemented with moving-shot lighting, Super timer, eight-band flood, status and summary variables, Case Files, immediate qualified-VUK ownership through flood and summary, and the shared Master Vine route chase while the final VUK is lit. The chase clears on capture, timeout, or teardown. Needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -13075,7 +13063,7 @@
         </x:is>
       </x:c>
       <x:c r="F42" s="31" t="str">
-        <x:v>Shoot the VUK for 100K to hold Ball 1 and serve Ball 2 with a 10-second save. Lock Ball 2 in any saucer for 150K; it remains held while Ball 1 is kicked to the rooftop.</x:v>
+        <x:v>Shoot the VUK for 100K to hold Ball 1 and serve Ball 2 with a 10-second save. At mode start and again on capture, pending shared VUK ejects/retries are cancelled so Ball 1 remains held. Lock Ball 2 in any saucer for 150K; it remains held while Ball 1 is kicked to the rooftop.</x:v>
       </x:c>
       <x:c r="G42" s="31" t="str">
         <x:v>After the 20-second attack expires, all flippers disable. When the active ball reaches the trough, gameplay ends but the saucer ball stays held through the villain summary. Shared occupancy-checked cleanup releases it after the summary. Losing Ball 2 before a saucer lock still ends the mode and releases the VUK ball.</x:v>
@@ -13084,7 +13072,7 @@
         <x:v>Jackpot starts at 100K. Either spinner adds 50K per spin, capped at 1M. Any upper target collects the current value without resetting it. More Time = 28s; Safety Net = 25s save; Bigger = 150K VUK / 200K saucer / 200K starting JP; More Jackpots = 75K per spin; Shot Assist makes the upper target corresponding to the occupied saucer worth 3X once.</x:v>
       </x:c>
       <x:c r="I42" s="31" t="str">
-        <x:v>Implemented with phase lighting, live timer/value/jackpot status, one-time mapped 3X indication, timeout blackout, summary variables, and terminal saucer ownership transferred to the shared summary hold. Needs on-machine playtest.</x:v>
+        <x:v>Implemented with phase lighting, live timer/value/jackpot status, one-time mapped 3X indication, timeout blackout, summary variables, defensive cancellation of pending shared VUK ejects/retries, and terminal saucer ownership transferred to the shared summary hold. Needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -13111,10 +13099,8 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F43" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Five authored sets: right bank good / pops bad; center web good / pops bad; upper-center good / upper sides bad; main spinner good / left web and right bank bad; left bank good / left web, spinner, and pops bad. Good flashes green, bad holds red, neutral is unlit. Any scored shot selects a random different set.</x:t>
-        </x:is>
+      <x:c r="F43" s="31" t="str">
+        <x:v>Seven authored sets: right bank good / both pops bad; right pop good / left pop and right bank bad; left bank good / spinner and right pop bad; spinner good / left web and left bank bad; left bank good / left web, spinner, and both pops bad; right pop good / both banks bad; right pop good / center web and right bank bad. Good flashes green, bad holds red, neutral is unlit. Any scored shot selects a random different set.</x:v>
       </x:c>
       <x:c r="G43" s="31" t="inlineStr">
         <x:is>
@@ -13126,10 +13112,8 @@
           <x:t xml:space="preserve">Good shots award a 100K Jackpot growing by 25K; Bigger grows by 50K. Bad shots score 25K. Safety Net = 10-second opening save; More Time = 20-second opening save; Shot Assist converts the first bad shot into the current Jackpot.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I43" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with authored no-repeat set selection, dynamic gate control, drop-bank GI indication, status display, 2-second ending hold, Case Files, and summary values; needs on-machine playtest.</x:t>
-        </x:is>
+      <x:c r="I43" s="31" t="str">
+        <x:v>Implemented with seven authored no-repeat shot sets, independently controlled left/right pop rings, drop-bank GI indication, fixed closed rooftop gate, status display, 2-second ending hold, Case Files, and summary values; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -13216,10 +13200,8 @@
           <x:t xml:space="preserve">150K/125K/100K by phase and full-value DEVARGAS GOLD banking. More JP: 25 opportunities; Bigger: 200K/175K/150K; More Time: 5s/4s/4s; Safety: 10s save; Assist: first expiry auto-collects.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I45" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with 13 independent pulsing shot shows, full-value DEVARGAS GOLD banking, upper-shot gate ownership, neutral device ejects, Case Files, status and summary values; needs on-machine playtest.</x:t>
-        </x:is>
+      <x:c r="I45" s="31" t="str">
+        <x:v>Implemented with 13 independent pulsing shot shows, player-facing collection ratings (AWESOME!/GREAT!/GOOD!), full-value DEVARGAS GOLD banking, upper-shot gate ownership, neutral device ejects, Case Files, status and summary values; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -13283,10 +13265,8 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F47" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Complete mirrored pairs in order: Pops, Drop Banks, A+B, then Web Super. One random side scores first and lights its opposite for a timed follow-up. More Jackpots inserts left/right upper targets first.</x:t>
-        </x:is>
+      <x:c r="F47" s="31" t="str">
+        <x:v>Complete mirrored pairs in order: Pops, Drop Banks, A+B, then Web Super. One random side scores first and lights its opposite for a timed follow-up. During A+B, both physical inserts for the active letter pulse together and either matching switch counts. More Jackpots inserts left/right upper targets first.</x:v>
       </x:c>
       <x:c r="G47" s="31" t="inlineStr">
         <x:is>
@@ -13298,10 +13278,8 @@
           <x:t xml:space="preserve">Source shots score 50K and ordinary mirrors 250K. Bigger: 75K/300K; Super stays 1M. More Time: 15s instead of 10s. Safety: 10s save. Assist: first expired mirror auto-collects.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I47" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with random source sides, paired lighting, drop-bank rubber support without forced resets, More Jackpots rooftop gate ownership, neutral device handling, Case Files, status, and summary values; needs on-machine playtest.</x:t>
-        </x:is>
+      <x:c r="I47" s="31" t="str">
+        <x:v>Implemented with random source sides, paired lighting, both physical A switches mapped to A and both physical B switches mapped to B, drop-bank rubber support without forced resets, More Jackpots rooftop gate ownership, neutral device handling, Case Files, status, and summary values; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -13416,10 +13394,8 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F50" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Complete left 1-3, then right 1-5 in order. Each upper-spinner spin drops the next target. A correct direct hit also advances. A wrong direct hit resets only that bank and restores its completed targets after 200ms, with 200ms staged re-drops.</x:t>
-        </x:is>
+      <x:c r="F50" s="31" t="str">
+        <x:v>Complete left 1-3, then right 1-5 in order. After the startup bank reset, the rooftop gate opens and remains open while the upper spinner is needed; each spin drops the next target. A correct direct hit also advances. A wrong direct hit resets only that bank and restores its completed targets after 200ms, with 200ms staged re-drops.</x:v>
       </x:c>
       <x:c r="G50" s="31" t="inlineStr">
         <x:is>
@@ -13431,10 +13407,8 @@
           <x:t xml:space="preserve">Correct drops 100K; center/left web Supers 500K. Bigger: 150K drops and 750K Supers. More Time: 20s. Safety: opening 10s save. Assist: first upper spin advances two drops.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I50" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with all eight physical drop coils, programmatic-switch guards, strict direct-hit validation, 200ms bank restoration staging, target/web lighting, one-attempt timer, Case Files, status, and summary values; needs on-machine playtest.</x:t>
-        </x:is>
+      <x:c r="I50" s="31" t="str">
+        <x:v>Implemented with all eight physical drop coils, programmatic-switch guards, strict direct-hit validation, 200ms bank restoration staging, explicit ordered-phase rooftop gate ownership, VUK shared eject handling, gate closure for the Web Super and mode stop, target/web lighting, one-attempt timer, Case Files, status, and summary values; needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -13476,10 +13450,8 @@
           <x:t xml:space="preserve">Jackpots 100K, or 150K with Bigger; VUK Super fixed at 500K. Safety Net 10s; More Time extends it to 20s. Shot Assist makes the first physical pop count twice: 50K score, +100K Swamp Bonus, and two Jackpots revealed.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I51" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented rewrite. Starts in PLAYING state; only VUK Super collection posts completion. Gate is forced closed until Super, Daily Bugle VUK handling is suspended, lens-matched objective lamps pulse, and swamp_bonus is earned at 50K per counted pop.</x:t>
-        </x:is>
+      <x:c r="I51" s="31" t="str">
+        <x:v>Implemented rewrite. Both complete pop-bumper lamp rings pulse green throughout the mode. Starts in PLAYING state; only VUK Super collection posts completion. Gate stays closed until Super, Daily Bugle Mystery is suspended, objectives use lens-matched pulses, and the shared Master Vine route chase guides the final VUK and clears on collect or teardown. Needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -13566,10 +13538,8 @@
           <x:t xml:space="preserve">Spinner 25K. Programmed lower shots pulse and score 50K/75K once per wave, then remain dim solid. The 22-objective pool resets on the next upper entry.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I53" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented: live wave/timer/lit/cleared status, hardware-aware lamps, and display naming for the shared left-bank insert.</x:t>
-        </x:is>
+      <x:c r="I53" s="31" t="str">
+        <x:v>Implemented with live wave/timer/lit/cleared status, hardware-aware lamps, shared left-bank naming, and an explicit VUK-route cleanup event that turns off every chase output—including the spinner GI—before the intended active-wave spinner pulse takes over. Needs on-machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -13877,10 +13847,8 @@
           <x:t xml:space="preserve">The physical rooftop gate is explicitly closed at game start. When chapter_mini_wizard_ready becomes true, villain_progression immediately pulses rooftop_diverter_open; a drop-target hit is not required and qualifying drops are ignored while the wizard is ready.</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented 2026-07-23</x:t>
-        </x:is>
+      <x:c r="C10" s="85" t="str">
+        <x:v>Implemented 2026-07-23; updated 2026-08-24 so chapter mini-wizard ready also starts the shared Master Vine VUK route chase. The chase stops as soon as the VUK starts the wizard intro. Final Showdown ready is excluded because it starts from a saucer, not the VUK.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf2348dcab4f54eb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R95d575b6cb1c4ef0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rde21dc13a5d04b0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R165e01178f794c42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Raec3f1f81bbe4bdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R94c36a04fe1448d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R724c94eec5bd41b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R7f244f4467c54f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rb1cd643e221b407d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R22f06ab9b7bf47c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R0890f5a3b36c4ce1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rc3461931362d4f1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Re03b628928264a2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc5cb7bf8e9104e4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R3239a4b192cb486a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R9720c182defc4071"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R6e700616d25c40d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R1ab261853aa64409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R500abf3dad224943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R9f0bd51e19e14d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R0dbc6b4d561b4760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R65c7acabd1d14e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rdcfd0d136d78488c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R52b11da9d41d4072"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R859e5932623f4f58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R602813543d4e4d90"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -996,15 +996,11 @@
           <x:t xml:space="preserve">Escalation</x:t>
         </x:is>
       </x:c>
-      <x:c r="I2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pops + B/qualified shots</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Growing jackpots</x:t>
-        </x:is>
+      <x:c r="I2" s="31" t="str">
+        <x:v>Pops + Smash shots + four A/B rollovers</x:v>
+      </x:c>
+      <x:c r="J2" s="31" t="str">
+        <x:v>200K–600K bases; 25K–150K Smash additions</x:v>
       </x:c>
       <x:c r="K2" s="31" t="inlineStr">
         <x:is>
@@ -1126,20 +1122,14 @@
           <x:t xml:space="preserve">Spinner build</x:t>
         </x:is>
       </x:c>
-      <x:c r="I4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Upper playfield + spinner</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spinner-scaled value / add-a-ball</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Upper control</x:t>
-        </x:is>
+      <x:c r="I4" s="31" t="str">
+        <x:v>Upper targets + upper/lower spinners</x:v>
+      </x:c>
+      <x:c r="J4" s="31" t="str">
+        <x:v>20K yellow / 50K red combined spinner values</x:v>
+      </x:c>
+      <x:c r="K4" s="31" t="str">
+        <x:v>Independent 8s target windows; all-red follow-up hit adds a ball</x:v>
       </x:c>
       <x:c r="L4" s="31" t="inlineStr">
         <x:is>
@@ -1196,15 +1186,11 @@
           <x:t xml:space="preserve">Whole playfield</x:t>
         </x:is>
       </x:c>
-      <x:c r="J5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Resetting decaying spark jackpots</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5s windows and final 10s Super</x:t>
-        </x:is>
+      <x:c r="J5" s="31" t="str">
+        <x:v>Resetting 250K-to-50K spark jackpots; 10K decay per step</x:v>
+      </x:c>
+      <x:c r="K5" s="31" t="str">
+        <x:v>Lower: 5s and 1s decay; upper: 10s and 2s decay. More Time doubles decay intervals. Final Super: 10s lower/15s upper; final saucer holds through summary.</x:v>
       </x:c>
       <x:c r="L5" s="31" t="inlineStr">
         <x:is>
@@ -1293,10 +1279,8 @@
           <x:t xml:space="preserve">Doctor Octopus</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / recent rule update</x:t>
-        </x:is>
+      <x:c r="E7" s="31" t="str">
+        <x:v>Implemented / needs lighting playtest</x:v>
       </x:c>
       <x:c r="F7" s="31" t="inlineStr">
         <x:is>
@@ -1333,10 +1317,8 @@
           <x:t xml:space="preserve">Goals completed / ball end</x:t>
         </x:is>
       </x:c>
-      <x:c r="M7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">State-management mode; good strategic contrast.</x:t>
-        </x:is>
+      <x:c r="M7" s="31" t="str">
+        <x:v>State-management mode; bright-blue rollover states and the conditional left-bank GI now make the required arm-lock shots explicit.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1358,10 +1340,8 @@
           <x:t xml:space="preserve">Mysterio</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
+      <x:c r="E8" s="31" t="str">
+        <x:v>Implemented / recent eight-shot update / needs playtest</x:v>
       </x:c>
       <x:c r="F8" s="31" t="inlineStr">
         <x:is>
@@ -1378,30 +1358,22 @@
           <x:t xml:space="preserve">Clue logic</x:t>
         </x:is>
       </x:c>
-      <x:c r="I8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Whole playfield</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hidden Super</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wrong-shot penalty</x:t>
-        </x:is>
+      <x:c r="I8" s="31" t="str">
+        <x:v>Webs + pops + both banks + saucers + upper targets; no spinners</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="str">
+        <x:v>1M hidden Super with 50K wrong-shot scoring and value deductions</x:v>
+      </x:c>
+      <x:c r="K8" s="31" t="str">
+        <x:v>First attempt cannot win; five directional clues and two false locations narrow the eight-shot field</x:v>
       </x:c>
       <x:c r="L8" s="31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hidden Super solved / ball end</x:t>
         </x:is>
       </x:c>
-      <x:c r="M8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystery role for the chapter.</x:t>
-        </x:is>
+      <x:c r="M8" s="31" t="str">
+        <x:v>Eight-shot mystery role; all incorrect attempts count in the Clue Shots summary, and terminal saucer control follows the shared post-summary release path.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1423,10 +1395,8 @@
           <x:t xml:space="preserve">Scorpion</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
+      <x:c r="E9" s="31" t="str">
+        <x:v>Implemented / recent rule update / needs playtest</x:v>
       </x:c>
       <x:c r="F9" s="31" t="inlineStr">
         <x:is>
@@ -1443,30 +1413,22 @@
           <x:t xml:space="preserve">Spinner build</x:t>
         </x:is>
       </x:c>
-      <x:c r="I9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spinner + drop banks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Venom build into staged attacks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timed staged shot</x:t>
-        </x:is>
+      <x:c r="I9" s="31" t="str">
+        <x:v>Rooftop spinner + upper exits + opposite drop banks</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="str">
+        <x:v>250K–1.5M base Sting jackpots; upper spinner adds 50K; one 200K–500K rubber consolation per attempt</x:v>
+      </x:c>
+      <x:c r="K9" s="31" t="str">
+        <x:v>Exit choice determines the staged bank; correct target or 8s/12s timeout resolves the attempt</x:v>
       </x:c>
       <x:c r="L9" s="31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Attack sequence complete / ball end</x:t>
         </x:is>
       </x:c>
-      <x:c r="M9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Urgency/drop attack role.</x:t>
-        </x:is>
+      <x:c r="M9" s="31" t="str">
+        <x:v>Upper-playfield build-and-route mode: rooftop entry enables immediate exit choice, while optional spinner time trades safety for a larger jackpot. Rubber scoring no longer consumes the staged attempt.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1528,10 +1490,8 @@
           <x:t xml:space="preserve">All attempts used / ball end</x:t>
         </x:is>
       </x:c>
-      <x:c r="M10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapter 2 timed-delivery role; adds urgency and value decay without duplicating Parafino's multiball.</x:t>
-        </x:is>
+      <x:c r="M10" s="31" t="str">
+        <x:v>Chapter 2 timed-delivery role; adds urgency and value decay without duplicating Parafino's multiball. Lighting now separates the slow yellow/red STAR-needed pulse from the teal delivery phase with brief red urgency flashes.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1554,7 +1514,7 @@
         </x:is>
       </x:c>
       <x:c r="E11" s="31" t="str">
-        <x:v>Implemented / recent saucer-number fix</x:v>
+        <x:v>Implemented / approved lighting update / needs playtest</x:v>
       </x:c>
       <x:c r="F11" s="31" t="inlineStr">
         <x:is>
@@ -1592,7 +1552,7 @@
         </x:is>
       </x:c>
       <x:c r="M11" s="31" t="str">
-        <x:v>Chapter 2 multiball role; area-control and lit-saucer add-a-ball give it a distinct identity. Numeric saucer IDs now reach the shared eject service correctly while retaining Parafino's 2-second release timing.</x:v>
+        <x:v>Chapter 2 multiball role; area-control and lit-saucer add-a-ball give it a distinct identity. All three target areas now share a synchronized red pulse using clear-lens lamps, contrasted against solid 8080F0 blue GI; gameplay, numeric saucer ejection, and 2-second release timing are unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="26" customFormat="1" ht="250.8000030517578" customHeight="1">
@@ -1615,7 +1575,7 @@
         </x:is>
       </x:c>
       <x:c r="E12" s="31" t="str">
-        <x:v>Implemented / recent ball-end widget lifecycle fix</x:v>
+        <x:v>Implemented / recent 1X-2X qualification update / needs playtest</x:v>
       </x:c>
       <x:c r="F12" s="31" t="str">
         <x:v>1</x:v>
@@ -1627,10 +1587,10 @@
         <x:v>Saucer control</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
-        <x:v>Upper targets + saucers</x:v>
+        <x:v>Left drop bank + corresponding upper targets + saucers</x:v>
       </x:c>
       <x:c r="J12" s="31" t="str">
-        <x:v>Matching saucer 3X jackpots; per-saucer retained repeat with More Jackpots</x:v>
+        <x:v>Matching saucer jackpots at 1X from lower drops or 2X from upper targets; upper spinner builds value</x:v>
       </x:c>
       <x:c r="K12" s="31" t="str">
         <x:v>16s timer after first jackpot; upper target/spinner/saucer resets</x:v>
@@ -1639,7 +1599,7 @@
         <x:v>Timer expiry / ball end; 3 jackpots is display-only</x:v>
       </x:c>
       <x:c r="M12" s="31" t="str">
-        <x:v>Timed matching role. CERBERUS DEFEATED is a 2-second presentation after the third jackpot. Cerberus now tears down at ball_ending before bonus presentation; needs drain-to-bonus regression testing.</x:v>
+        <x:v>Timed matching role with a clear risk/reward choice: collect the lower-qualified 1X or keep the gate open and route upstairs for the matching 2X. CERBERUS DEFEATED remains a 2-second presentation after the third jackpot; the active mode continues until timer expiry or ball end.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="26" customFormat="1" ht="250.8000030517578" customHeight="1">
@@ -1708,10 +1668,8 @@
           <x:t xml:space="preserve">Diana</x:t>
         </x:is>
       </x:c>
-      <x:c r="E14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
+      <x:c r="E14" s="31" t="str">
+        <x:v>Implemented / recent timer update / needs playtest</x:v>
       </x:c>
       <x:c r="F14" s="31" t="inlineStr">
         <x:is>
@@ -1738,20 +1696,16 @@
           <x:t xml:space="preserve">Three staged right-bank Hunts</x:t>
         </x:is>
       </x:c>
-      <x:c r="K14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">First-hit timed windows</x:t>
-        </x:is>
+      <x:c r="K14" s="31" t="str">
+        <x:v>First-hit 8s windows; 12s with More Time</x:v>
       </x:c>
       <x:c r="L14" s="31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Three Hunts complete / arrows depleted / ball end</x:t>
         </x:is>
       </x:c>
-      <x:c r="M14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Limited-resource precision role with a clear red-GI Hunt state.</x:t>
-        </x:is>
+      <x:c r="M14" s="31" t="str">
+        <x:v>Limited-resource precision role with a clear red-GI Hunt state. All three Hunts now use the approved 8-second first-hit window, extended to 12 seconds with More Time; scoring and arrow economy are unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="26" customFormat="1" ht="316.79998779296875" customHeight="1">
@@ -1838,50 +1792,32 @@
           <x:t xml:space="preserve">Centaur</x:t>
         </x:is>
       </x:c>
-      <x:c r="E16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs light-color polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Build-and-cash</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Roof final</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Drops + roof/post + rubber</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Built JP into final shot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Final shot pressure</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Final phase resolved / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Build-to-final role; rounds out chapter variety.</x:t>
-        </x:is>
+      <x:c r="E16" s="31" t="str">
+        <x:v>Implemented / recent More Jackpots update / needs playtest</x:v>
+      </x:c>
+      <x:c r="F16" s="31" t="str">
+        <x:v>1 ball; optional second staged finale</x:v>
+      </x:c>
+      <x:c r="G16" s="31" t="str">
+        <x:v>Build-and-cash</x:v>
+      </x:c>
+      <x:c r="H16" s="31" t="str">
+        <x:v>Roof one-shot finale</x:v>
+      </x:c>
+      <x:c r="I16" s="31" t="str">
+        <x:v>Drops + VUK/roof + upper-left exit + right rubber</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="str">
+        <x:v>25K drops; +100K JP/drop; 50K consolation; built JP cashout</x:v>
+      </x:c>
+      <x:c r="K16" s="31" t="str">
+        <x:v>6s/12s final; fixed 12s More Jackpots re-entry window</x:v>
+      </x:c>
+      <x:c r="L16" s="31" t="str">
+        <x:v>First finale resolved; optional second finale resolved/window expired; ball end</x:v>
+      </x:c>
+      <x:c r="M16" s="31" t="str">
+        <x:v>Build-to-final role. More Jackpots now repeats the full roof/post route for one second one-shot attempt instead of creating an open-ended final or left-rubber half-Jackpot.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2034,7 +1970,7 @@
         </x:is>
       </x:c>
       <x:c r="E19" s="31" t="str">
-        <x:v>Implemented / recent lighting and STAR reveal update</x:v>
+        <x:v>Implemented / recent first-reveal timing update / needs playtest</x:v>
       </x:c>
       <x:c r="F19" s="31" t="str">
         <x:v>1</x:v>
@@ -2052,13 +1988,13 @@
         <x:v>Declining revealed-location value; STAR preserves value</x:v>
       </x:c>
       <x:c r="K19" s="31" t="str">
-        <x:v>Reveal-window tradeoff: drops add more time at lower value; repeatable STAR adds 4 seconds without value loss</x:v>
+        <x:v>First reveal 8s/10s; later drops add time at lower value; repeatable STAR adds 4s without value loss</x:v>
       </x:c>
       <x:c r="L19" s="31" t="str">
         <x:v>Reveal rounds completed / ball end</x:v>
       </x:c>
       <x:c r="M19" s="31" t="str">
-        <x:v>Reveal/urgency role. Right-bank GI and standing-drop flashes keep the main reveal route visible; STAR provides a difficult rooftop time-extension alternative.</x:v>
+        <x:v>Reveal/urgency role. The first travel window is now the approved 8 seconds, or 10 with More Time; later time/value tradeoffs, STAR behavior, scoring, lighting, and ending remain unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2080,10 +2016,8 @@
           <x:t xml:space="preserve">The Enforcers</x:t>
         </x:is>
       </x:c>
-      <x:c r="E20" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs light-color polish</x:t>
-        </x:is>
+      <x:c r="E20" s="31" t="str">
+        <x:v>Implemented / recent Ox chase lighting fix / needs playtest</x:v>
       </x:c>
       <x:c r="F20" s="31" t="inlineStr">
         <x:is>
@@ -2110,20 +2044,14 @@
           <x:t xml:space="preserve">Upper target JPs build OX Super</x:t>
         </x:is>
       </x:c>
-      <x:c r="K20" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Zone completion routing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L20" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Zones + OX Super complete / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M20" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Second area mode, but should feel like team/zone buildup rather than Kingpin boss control.</x:t>
-        </x:is>
+      <x:c r="K20" s="31" t="str">
+        <x:v>Two hits light each rooftop jackpot; continued hits build 1X-5X; spinner adds 50K per spin to Ox</x:v>
+      </x:c>
+      <x:c r="L20" s="31" t="str">
+        <x:v>Three rooftop jackpots, then center-web Ox Super / ball end</x:v>
+      </x:c>
+      <x:c r="M20" s="31" t="str">
+        <x:v>Team/zone buildup role. Ox-ready lighting now uses the approved four-insert 80F0F0 chase at 300ms per step and explicitly clears l_special with the other chase inserts; gameplay and scoring are unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2146,7 +2074,7 @@
         </x:is>
       </x:c>
       <x:c r="E21" s="31" t="str">
-        <x:v>Implemented / recent STAR lighting fix</x:v>
+        <x:v>Implemented / recent 1-2-3 saucer progression fix / needs machine playtest</x:v>
       </x:c>
       <x:c r="F21" s="31" t="str">
         <x:v>1</x:v>
@@ -2164,13 +2092,13 @@
         <x:v>Frozen-diamond bank / shipment jackpot</x:v>
       </x:c>
       <x:c r="K21" s="31" t="str">
-        <x:v>Moving saucer chase and freeze timing</x:v>
+        <x:v>Right-bank completion arms first post-reset drop to expand moving window 1 -&gt; 2 -&gt; 3; STAR freezes current window 10s/15s</x:v>
       </x:c>
       <x:c r="L21" s="31" t="str">
-        <x:v>Required shipments complete / ball end</x:v>
+        <x:v>One shipment, or two with More Jackpots / ball end</x:v>
       </x:c>
       <x:c r="M21" s="31" t="str">
-        <x:v>Crime Wave risk/reward chase; Doctor Cool smuggles diamonds inside ice. STAR now flashes red continuously at 250ms on / 250ms off and clears cleanly when the mode stops.</x:v>
+        <x:v>Crime Wave risk/reward chase. Availability now grows through the approved one-, two-, and three-saucer moving windows. Only red hole lamps show valid saucers; scoring, chase speeds, Diamond Bonus, Case Files, red STAR flash, and terminal summary hold remain intact.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2192,10 +2120,8 @@
           <x:t xml:space="preserve">Harley Clivendon</x:t>
         </x:is>
       </x:c>
-      <x:c r="E22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
+      <x:c r="E22" s="31" t="str">
+        <x:v>Implemented / recent control-lighting repair / physical congestion test pending</x:v>
       </x:c>
       <x:c r="F22" s="31" t="inlineStr">
         <x:is>
@@ -2222,20 +2148,14 @@
           <x:t xml:space="preserve">Area-built repeatable VUK jackpots; each full value also banks as HARLEY JACKPOTS</x:t>
         </x:is>
       </x:c>
-      <x:c r="K22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Multiball control and parallel area progress</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Objectives complete / multiball end / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapter 5 multiball role; controlled area-building contrasts with Conquistador's route and Spider-Slayer's expanding hunt.</x:t>
-        </x:is>
+      <x:c r="K22" s="31" t="str">
+        <x:v>Controlled lock; 4 of 8 areas qualify; retained More-Jackpots areas stay dark until next lock; delayed Ball-2 autoplunge</x:v>
+      </x:c>
+      <x:c r="L22" s="31" t="str">
+        <x:v>Multiball reaches one ball / ball end</x:v>
+      </x:c>
+      <x:c r="M22" s="31" t="str">
+        <x:v>Chapter 5 controlled area-building multiball. Autoplunge, paired left-sling lamps, area-show lifecycle, held-lamp cleanup, and single-owner saucer release are repaired. Same-saucer physical congestion still requires a separately approved machine-tested strategy.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2257,10 +2177,8 @@
           <x:t xml:space="preserve">The Conquistador</x:t>
         </x:is>
       </x:c>
-      <x:c r="E23" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
+      <x:c r="E23" s="31" t="str">
+        <x:v>Implemented / single-drop Stage 1 review patch / needs machine playtest</x:v>
       </x:c>
       <x:c r="F23" s="31" t="inlineStr">
         <x:is>
@@ -2277,30 +2195,24 @@
           <x:t xml:space="preserve">Build-and-cash</x:t>
         </x:is>
       </x:c>
-      <x:c r="I23" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left bank + upper spinner + upper targets + center web</x:t>
-        </x:is>
+      <x:c r="I23" s="31" t="str">
+        <x:v>Any left 3-bank drop + upper spinner + upper targets + center web</x:v>
       </x:c>
       <x:c r="J23" s="31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Uncapped Fountain Jackpot and stage Speed Bonuses</x:t>
         </x:is>
       </x:c>
-      <x:c r="K23" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fast completion earns speed value, while extra upper-target hits increase the jackpot</x:t>
-        </x:is>
+      <x:c r="K23" s="31" t="str">
+        <x:v>First left-drop hit scores 50K, awards remaining-time speed value, resets the bank, and opens the gate; extra upper-target hits increase the Fountain Jackpot</x:v>
       </x:c>
       <x:c r="L23" s="31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Either main timer expires, or Fountain sequence resolves</x:t>
         </x:is>
       </x:c>
-      <x:c r="M23" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Distinct two-stage route: timed gate opening, untimed Fountain search, then timed cashout with an optional second sip.</x:t>
-        </x:is>
+      <x:c r="M23" s="31" t="str">
+        <x:v>Distinct two-stage route: one timed left-drop gate shot, an untimed three-spin Fountain search, then timed center-web cashout with an optional second sip. Dedicated Song 54 remains assigned.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -6380,7 +6292,9 @@
       <x:c r="D59" s="73" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E59" s="74" t="str"/>
+      <x:c r="E59" s="74" t="str">
+        <x:v>Dedicated Conquistador mode track; villain bookends uses play_song_54.</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A60" s="73" t="n">
@@ -7596,10 +7510,8 @@
           <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
         </x:is>
       </x:c>
-      <x:c r="H2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pops build Rage; B rollover jackpots; first 10 music assignment retained.</x:t>
-        </x:is>
+      <x:c r="H2" s="31" t="str">
+        <x:v>Pops build Rage; Smash shots add 25K/50K/75K/100K/150K; all four A/B rollovers collect; bases are 200K–600K, with a 700K sixth jackpot from More Jackpots.</x:v>
       </x:c>
       <x:c r="I2" s="31" t="inlineStr">
         <x:is>
@@ -7688,10 +7600,8 @@
           <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
         </x:is>
       </x:c>
-      <x:c r="H4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Upper playfield/spinner mode; banks vulture_bonus; first 10 music assignment ...</x:t>
-        </x:is>
+      <x:c r="H4" s="31" t="str">
+        <x:v>Both spinners score after rooftop entry. Upper targets pulse yellow at 20K, light red at 50K for independent 8s timers (12s More Time); hit any target while all three are red to add a ball.</x:v>
       </x:c>
       <x:c r="I4" s="31" t="inlineStr">
         <x:is>
@@ -7734,10 +7644,8 @@
           <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
         </x:is>
       </x:c>
-      <x:c r="H5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Travelling 5-second spark shots reset to maximum value whenever they move, th...</x:t>
-        </x:is>
+      <x:c r="H5" s="31" t="str">
+        <x:v>Travelling sparks use separate lower/upper timing: lower 5s (8s Shot Assist), upper spinner/targets 10s (13s Shot Assist). Value falls 10K each 1s lower or 2s upper; More Time doubles those intervals. Final Super is 10s lower or 15s upper. A final saucer Super is held through the villain summary, then kicked out.</x:v>
       </x:c>
       <x:c r="I5" s="31" t="inlineStr">
         <x:is>
@@ -7817,15 +7725,11 @@
           <x:t xml:space="preserve">Doctor Octopus</x:t>
         </x:is>
       </x:c>
-      <x:c r="G7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / recent rule update</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rollovers lock arms; completing the left bank locks one arm and relights the web jackpot; spinner boosts the multiplier. Every collected web jackpot adds 100K to persistent doc_ock_bonus as BREAKOUT BONUS.</x:t>
-        </x:is>
+      <x:c r="G7" s="31" t="str">
+        <x:v>Implemented / needs lighting playtest</x:v>
+      </x:c>
+      <x:c r="H7" s="31" t="str">
+        <x:v>Rollovers lock arms; completing the left bank locks one arm and relights the web jackpot; spinner boosts the multiplier. Every collected web jackpot adds 100K to persistent doc_ock_bonus as BREAKOUT BONUS. Free-arm lane rollovers pulse bright blue, locked-arm rollovers stay solid blue, and the left-bank GI pulses blue while any arm remains free.</x:v>
       </x:c>
       <x:c r="I7" s="31" t="inlineStr">
         <x:is>
@@ -7863,15 +7767,11 @@
           <x:t xml:space="preserve">Mysterio</x:t>
         </x:is>
       </x:c>
-      <x:c r="G8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hidden Super/clue mode; wrong shots lower value; first 10 music assignment re...</x:t>
-        </x:is>
+      <x:c r="G8" s="31" t="str">
+        <x:v>Implemented / recent eight-shot update / needs playtest</x:v>
+      </x:c>
+      <x:c r="H8" s="31" t="str">
+        <x:v>Eight-location deduction mode with no spinner shots: left/center webs, left/right pops, both drop banks, saucers, and grouped upper targets. Five locations give directional clues, two give the false-location response, and one is the hidden Super. The first attempt cannot collect the Super; every incorrect attempt counts as a Clue Shot. A saucer Super holds through summary.</x:v>
       </x:c>
       <x:c r="I8" s="31" t="inlineStr">
         <x:is>
@@ -7909,15 +7809,11 @@
           <x:t xml:space="preserve">Scorpion</x:t>
         </x:is>
       </x:c>
-      <x:c r="G9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spinner builds Venom; upper exit stages timed drop attack.</x:t>
-        </x:is>
+      <x:c r="G9" s="31" t="str">
+        <x:v>Implemented / recent rule update / needs playtest</x:v>
+      </x:c>
+      <x:c r="H9" s="31" t="str">
+        <x:v>Rooftop entry immediately enables both exits. The upper spinner adds 50K per hit to the pending Sting Jackpot; either exit stages the opposite drop bank. The correct target or timer expiry ends the attempt. One rubber consolation can score per attempt without ending it.</x:v>
       </x:c>
       <x:c r="I9" s="31" t="inlineStr">
         <x:is>
@@ -7960,10 +7856,8 @@
           <x:t xml:space="preserve">Implemented / recent rule update</x:t>
         </x:is>
       </x:c>
-      <x:c r="H10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collect serum at STAR and deliver every attempt to the left web. Two attempts are available normally; More Jackpots adds a third. Every A+B completion adds 500K to the active serum and all future serum starting values with no cap; if serum is active, it also restarts the timer. One successful delivery produces the CURED summary; zero successful deliveries produces ESCAPED. Successful delivery plays a 2-second white/green left-web show before the next serum begins. Timer expiry fades GI to off over 2 seconds before the next attempt or summary.</x:t>
-        </x:is>
+      <x:c r="H10" s="31" t="str">
+        <x:v>Collect serum at STAR and deliver every attempt to the left web. Two attempts are available normally; More Jackpots adds a third. Every A+B completion adds 500K to the active serum and all future serum starting values with no cap; if serum is active, it also restarts the timer. One successful delivery produces the CURED summary; zero successful deliveries produces ESCAPED. Successful delivery plays a 2-second white/green left-web show before the next serum begins. Timer expiry fades GI to off over 2 seconds before the next attempt or summary. Lighting update: star-needed GI slowly fades F0F040 to F02040; delivery GI holds teal 406060 with a 250ms F02040 flash every 1.5s; the active left-web insert continues flashing purple.</x:v>
       </x:c>
       <x:c r="I10" s="31" t="inlineStr">
         <x:is>
@@ -8002,10 +7896,10 @@
         </x:is>
       </x:c>
       <x:c r="G11" s="31" t="str">
-        <x:v>Implemented / recent saucer-number fix</x:v>
+        <x:v>Implemented / approved lighting update / needs playtest</x:v>
       </x:c>
       <x:c r="H11" s="31" t="str">
-        <x:v>2-ball heat-area multiball. Left drops, pops, and right drops light immediately as the three active target zones. Zone hits build the matching saucer jackpot; only the earned saucer lamp flashes. Target-zone guidance remains lit throughout the mode. Parafino now sends numeric saucer IDs 1/2/3 to the shared eject service and preserves its 2-second eject delay.</x:v>
+        <x:v>2-ball heat-area multiball. Left drops, pops, and right drops light immediately as the three active target zones. Zone hits build the matching saucer jackpot; only the earned saucer lamp flashes. The clear-lens left-bank GI, both pop rings, and clear-lens right-bank GI pulse red together at 500ms on/off while surrounding mode GI stays solid 8080F0 blue. Numeric saucer IDs 1/2/3 and the 2-second eject delay remain.</x:v>
       </x:c>
       <x:c r="I11" s="31" t="inlineStr">
         <x:is>
@@ -8044,10 +7938,10 @@
         </x:is>
       </x:c>
       <x:c r="G12" s="31" t="str">
-        <x:v>Implemented / recent ball-end widget lifecycle fix</x:v>
+        <x:v>Implemented / recent 1X-2X qualification update / needs playtest</x:v>
       </x:c>
       <x:c r="H12" s="31" t="str">
-        <x:v>Any upper target lights all saucers; its matching saucer is 3X. First jackpot starts the 16s timer; upper targets, upper spinner, and all saucer hits reset it. More Jackpots lets each saucer remain lit once after its first collection at the same state/multiplier. Shot Assist consumes one collection only. Third jackpot shows CERBERUS DEFEATED for 2s but play continues; playing the mode satisfies progression. On a drain, Cerberus now stops at ball_ending so its timer and widget are removed before bonus starts.</x:v>
+        <x:v>Each left-bank drop lights its corresponding saucer at 1X; each corresponding upper target lights or upgrades that same saucer to 2X. The lower path keeps the rooftop gate open so the player may collect 1X or pursue the 2X upgrade. The upper spinner builds jackpot value. First jackpot starts the 16s timer; upper targets, spinner, and saucer hits reset it. The third jackpot shows CERBERUS DEFEATED for 2s, but play continues until timer expiry or ball end.</x:v>
       </x:c>
       <x:c r="I12" s="31" t="inlineStr">
         <x:is>
@@ -8127,15 +8021,11 @@
           <x:t xml:space="preserve">Diana</x:t>
         </x:is>
       </x:c>
-      <x:c r="G14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Three limited-arrow Hunts. Upper entry stages green right-bank targets and re...</x:t>
-        </x:is>
+      <x:c r="G14" s="31" t="str">
+        <x:v>Implemented / recent timer update / needs playtest</x:v>
+      </x:c>
+      <x:c r="H14" s="31" t="str">
+        <x:v>Three limited-arrow Hunts. Upper entry stages green right-bank targets and red GI; either upper exit prompts the shot. The first staged drop or right-rubber hit starts an 8-second timer for every Hunt, extended to 12 seconds with More Time. Hunt targets remain 1/3/5, then 2/4, then 3. Scoring, arrow economy, helpers, and the 50K-per-remaining-arrow end bonus are unchanged.</x:v>
       </x:c>
       <x:c r="I14" s="31" t="inlineStr">
         <x:is>
@@ -8219,15 +8109,11 @@
           <x:t xml:space="preserve">Centaur</x:t>
         </x:is>
       </x:c>
-      <x:c r="G16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs light-color polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Drops build JP; roof/post final phase; 5-bank/GI color cleanup remains on todo.</x:t>
-        </x:is>
+      <x:c r="G16" s="31" t="str">
+        <x:v>Implemented / recent More Jackpots update / needs playtest</x:v>
+      </x:c>
+      <x:c r="H16" s="31" t="str">
+        <x:v>Four unique drops score 25K each and add 100K each to the Centaur Jackpot; bank rubbers score 25K. Four drops open the roof gate. Upper entry closes the gate and the upper-left exit holds the post 6s while right targets 2-4 are staged down. Each 6s final (12s More Time) is one-shot: right rubber awards the built Jackpot; target 1 or 5 awards 50K, or the Jackpot with Shot Assist. More Jackpots replaces the old left-rubber half-Jackpot: after attempt one resolves or expires, the roof gate opens for a fixed 12s re-entry window; upper-left exit restages one second one-shot finale. Bigger doubles the Jackpot; Safety Net starts the shared 10s save for each finale.</x:v>
       </x:c>
       <x:c r="I16" s="31" t="inlineStr">
         <x:is>
@@ -8358,10 +8244,10 @@
         </x:is>
       </x:c>
       <x:c r="G19" s="31" t="str">
-        <x:v>Implemented / recent lighting and STAR reveal update</x:v>
+        <x:v>Implemented / recent first-reveal timing update / needs playtest</x:v>
       </x:c>
       <x:c r="H19" s="31" t="str">
-        <x:v>Five-round reveal/collect mode; More Jackpots adds a sixth. Standing right drops flash green and hit drops remain solid. A right drop reveals the hidden jackpot shot and adds time; later unique drops add more time but lower its value. STAR is not a hiding location: it flashes red throughout the mode and gives a repeatable live 4-second reveal or adds 4 seconds to an active reveal without reducing value. Right-bank GI pulses continuously.</x:v>
+        <x:v>Five-round reveal/collect mode; More Jackpots adds a sixth. The first unique right drop now reveals the hidden location for 8s at 1M, or 10s with More Time. Later unique drops retain their approved +8/+10/+12/+14s additions and lower the normal Jackpot to 800K/600K/400K/200K; More Time adds 2s to each. STAR remains a repeatable live 4s reveal/add with no value reduction. Standing right drops flash green and hit drops remain solid; right-bank GI pulses; STAR flashes red; revealed locations flash purple; SAUCERS uses only red hole lamps.</x:v>
       </x:c>
       <x:c r="I19" s="31" t="inlineStr">
         <x:is>
@@ -8399,15 +8285,11 @@
           <x:t xml:space="preserve">The Enforcers</x:t>
         </x:is>
       </x:c>
-      <x:c r="G20" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs light-color polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H20" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cowboy and Ox control three crime zones; zone clears light upper-target jackp...</x:t>
-        </x:is>
+      <x:c r="G20" s="31" t="str">
+        <x:v>Implemented / recent Ox chase lighting fix / needs playtest</x:v>
+      </x:c>
+      <x:c r="H20" s="31" t="str">
+        <x:v>Left drops, pops, and right drops build the matching upper-target jackpots; continued zone hits build 1X-5X multipliers. Upper-spinner spins score 5K and add 50K to Ox; collected rooftop jackpots also add their awards. All three rooftop jackpots light the center-web Ox Super. Ox-ready lighting now chases l_mid_multibonus -&gt; l_advance_multiplier -&gt; l_special -&gt; l_mid_web_target at 300ms per step in 80F0F0, with all four inserts explicitly cleared on teardown.</x:v>
       </x:c>
       <x:c r="I20" s="31" t="inlineStr">
         <x:is>
@@ -8446,10 +8328,10 @@
         </x:is>
       </x:c>
       <x:c r="G21" s="31" t="str">
-        <x:v>Implemented / recent STAR lighting fix</x:v>
+        <x:v>Implemented / recent 1-2-3 saucer progression fix / needs machine playtest</x:v>
       </x:c>
       <x:c r="H21" s="31" t="str">
-        <x:v>Drops build frozen-diamond value; completing the right 5-bank starts a moving saucer shipment chase. STAR always banks 100K to diamond_bonus and now flashes red throughout Doctor Cool. During the chase, STAR freezes the cycle and lights all three saucers for 10 seconds, or 15 with More Time.</x:v>
+        <x:v>Drops build the Frozen Diamond value and bank Diamond Bonus. Any right drop starts the moving shipment chase with one available saucer. Completing/resetting the right bank arms the first following right drop to expand the moving window to two saucers, then three, capped at three. STAR freezes only the current available window for 10s, or 15s with More Time. Availability uses only the red hole lamps; green 1/2/3 inserts stay off. One shipment completes normally; More Jackpots requires two.</x:v>
       </x:c>
       <x:c r="I21" s="31" t="inlineStr">
         <x:is>
@@ -8487,15 +8369,11 @@
           <x:t xml:space="preserve">Harley Clivendon</x:t>
         </x:is>
       </x:c>
-      <x:c r="G22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Custom 2-ball area-control multiball. A saucer holds a ball while independent playfield areas are lit; enough lit areas qualify a repeatable VUK jackpot. Every VUK jackpot also adds its full value to the persistent harley_bonus bank shown as HARLEY JACKPOTS.</x:t>
-        </x:is>
+      <x:c r="G22" s="31" t="str">
+        <x:v>Implemented / recent control-lighting repair / physical congestion test pending</x:v>
+      </x:c>
+      <x:c r="H22" s="31" t="str">
+        <x:v>Controlled 2-ball area multiball: delayed autoplunge Ball 2, capture one ball in a red-hole-lit saucer, then light eight independent areas at 50K each. Four areas qualify the repeatable VUK Jackpot at 100K per area, or 150K with Bigger; the full award also banks to HARLEY JACKPOTS. The paired upper/lower left-sling GI now acts as one area. Area guidance starts only after a lock and clears between rounds; More Jackpots retains two areas internally until the next lock. Held-saucer lights and eject ownership now clean up exactly once. Occupied-saucer congestion remains an unresolved machine-test issue with no automatic rescue added.</x:v>
       </x:c>
       <x:c r="I22" s="31" t="inlineStr">
         <x:is>
@@ -8533,15 +8411,11 @@
           <x:t xml:space="preserve">The Conquistador</x:t>
         </x:is>
       </x:c>
-      <x:c r="G23" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H23" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Find the Fountain: complete the left bank under timer, make three upper-spinner spins, build the uncapped Fountain Jackpot with upper targets, then collect at center web.</x:t>
-        </x:is>
+      <x:c r="G23" s="31" t="str">
+        <x:v>Implemented / single-drop Stage 1 review patch / needs machine playtest</x:v>
+      </x:c>
+      <x:c r="H23" s="31" t="str">
+        <x:v>Find the Fountain: hit any single left 3-bank drop under the opening timer to score 50K, award the remaining-time speed bonus, reset the bank, and open the rooftop gate. Then make three upper-spinner spins, build the uncapped Fountain Jackpot with upper targets, and collect at center web. Dedicated mode music is Song 54 (conquistador).</x:v>
       </x:c>
       <x:c r="I23" s="31" t="inlineStr">
         <x:is>
@@ -10748,10 +10622,8 @@
           <x:t xml:space="preserve">Doctor Cool</x:t>
         </x:is>
       </x:c>
-      <x:c r="D10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Diamond Smugglers ruleset repurposed for Doctor Cool: drops build frozen diamonds, the 5-bank starts a moving shipment chase, and STAR freezes all saucers.</x:t>
-        </x:is>
+      <x:c r="D10" s="31" t="str">
+        <x:v>Diamond Smugglers ruleset repurposed for Doctor Cool: drops build Frozen Diamonds; a right drop starts the moving shipment chase; right-bank resets expand availability from one to two to three; STAR freezes only the current available window.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -11326,25 +11198,17 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Build Rage from pops, then use B/qualified shots to cash in Rhino jackpots.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ends when the Rhino jackpot sequence/objectives are completed; otherwise stops on ball end.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pops build Rage; B rollover/qualified shots award jackpots; staged values grow through the mode.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Improved: live Rage / Jackpots status plus state-change messages.</x:t>
-        </x:is>
+      <x:c r="F2" s="31" t="str">
+        <x:v>Build Rage from pops, build the pending jackpot with Smash shots, then collect at any of the four A/B rollovers.</x:v>
+      </x:c>
+      <x:c r="G2" s="31" t="str">
+        <x:v>Five jackpots defeat Rhino; More Jackpots requires six. A missed Berserk collect ends the mode unless Shot Assist saves it.</x:v>
+      </x:c>
+      <x:c r="H2" s="31" t="str">
+        <x:v>Base jackpots: 200K/300K/400K/500K/600K (700K sixth). Smash additions by Rage: 25K/50K/75K/100K/150K. Bigger Jackpots adds 200K to every base.</x:v>
+      </x:c>
+      <x:c r="I2" s="31" t="str">
+        <x:v>All four A/B lamps flash as jackpot collects; escalating yellow-to-red Rage GI and Berserk presentation retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -11416,25 +11280,17 @@
           <x:t xml:space="preserve">1; add-a-ball possible</x:t>
         </x:is>
       </x:c>
-      <x:c r="F4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Get to the upper playfield; use upper targets/spinner to build and collect Vulture values.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ends when upper-playfield Vulture objectives complete; otherwise stops on ball end.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Upper playfield/spinner mode; spinner builds/scales scoring and can qualify add-a-ball; banks vulture_bonus.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Improved: roof-access guidance before the live rooftop timer.</x:t>
-        </x:is>
+      <x:c r="F4" s="31" t="str">
+        <x:v>Enter the rooftop to start 40 seconds. Hit upper targets to light them red, then use either spinner to collect the combined target values.</x:v>
+      </x:c>
+      <x:c r="G4" s="31" t="str">
+        <x:v>Hit any upper target while all three are red to add a ball. The mode ends at time expiry, or after the resulting multiball ends if time has expired.</x:v>
+      </x:c>
+      <x:c r="H4" s="31" t="str">
+        <x:v>Targets start pulsing yellow at 20K and light pulsing red at 50K for separate 8s timers; More Time gives 12s. Target hits score 50K. Either spinner scores after rooftop entry. Shot Assist lights all three red.</x:v>
+      </x:c>
+      <x:c r="I4" s="31" t="str">
+        <x:v>Yellow/red pulsing target states and yellow-to-blue rooftop GI retained; individual target timers now communicate the active scoring windows.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -11461,25 +11317,17 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Follow the travelling spark across eight shot groups. Each new spark starts at maximum value and then decays once per second until hit or moved.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collected groups are removed until one final shot remains for the 10-second Super Jackpot. Collecting the Super completes the mode; missing it or ball end stops it. When a saucer makes the terminal collect, that ball remains held until the villain summary ends.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Normal sparks start at 250K, or 300K with Bigger, and fall 10K per second to 50K. More Time halves the drain rate. More Jackpots returns the first collected group to the pool for one extra normal jackpot. Shot Assist makes the first spark last 8 seconds.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Existing Electro light timing is retained. The Super uses the existing SUPER SURGE LIT countdown plus persistent SUPER SPARK status. Gate routing follows upper shots, and saucers use delayed clearing.</x:t>
-        </x:is>
+      <x:c r="F5" s="31" t="str">
+        <x:v>Follow the travelling spark across eight shot groups. Each new spark starts at maximum value. Lower sparks last 5 seconds and decay every second; upper spinner/target sparks last 10 seconds and decay every 2 seconds.</x:v>
+      </x:c>
+      <x:c r="G5" s="31" t="str">
+        <x:v>Collected groups are removed until one final shot remains. The Super lasts 10 seconds on lower shots or 15 seconds on upper shots. Collecting it completes the mode; missing it or ball end stops it. A final saucer Super stays held until the villain summary ends.</x:v>
+      </x:c>
+      <x:c r="H5" s="31" t="str">
+        <x:v>Normal sparks start at 250K, or 300K with Bigger, and fall 10K per decay step to 50K. More Time doubles decay intervals to 2s lower/4s upper. More Jackpots returns the first collected group for one extra normal jackpot. Shot Assist gives 8s lower/13s upper.</x:v>
+      </x:c>
+      <x:c r="I5" s="31" t="str">
+        <x:v>Existing Electro light timing is retained. Gate routing follows upper shots. Ordinary and unlit saucers clear after the normal delay; a final saucer Super kicks out after the summary.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -11558,10 +11406,8 @@
           <x:t xml:space="preserve">Rollovers lock arms; completing the left bank locks one arm and relights the web jackpot; spinner boosts the multiplier. Each collected web jackpot adds 100K to persistent BREAKOUT BONUS.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I7" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Improved: persistent arm-lock, web-jackpot, and breakout progress.</x:t>
-        </x:is>
+      <x:c r="I7" s="31" t="str">
+        <x:v>Persistent arm-lock, web-jackpot, and breakout progress. Free-arm lane rollovers pulse bright blue; locked-arm rollovers stay solid blue. Left-bank GI pulses slowly in blue while any arm remains free and stops when all four are locked.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -11588,25 +11434,17 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use clues to identify the hidden Super while wrong shots reduce value.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ends when the hidden Super/clue sequence is solved; otherwise stops on ball end. When a saucer makes the terminal collect, that ball remains held until the villain summary ends.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hidden Super/clue mode; wrong shots score smaller and reduce value; clues narrow the target.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Improved: persistent remaining-shot count and current Super value.</x:t>
-        </x:is>
+      <x:c r="F8" s="31" t="str">
+        <x:v>Find one hidden Super among eight non-spinner locations: left/center webs, left/right pops, both drop banks, grouped saucers, and grouped upper targets. Five locations give directional clues and two are false locations.</x:v>
+      </x:c>
+      <x:c r="G8" s="31" t="str">
+        <x:v>The first attempted shot cannot be the Super; if necessary, it moves before that attempt resolves. The hidden Super completes the mode. A saucer Super remains held until the villain summary ends.</x:v>
+      </x:c>
+      <x:c r="H8" s="31" t="str">
+        <x:v>Super starts at 1M (1.5M Bigger) with a 100K floor. Incorrect shots score 50K and reduce the Super by 100K, or 50K with More Time. More Jackpots protects the first wrong attempt. Shot Assist removes one false location. Every incorrect attempt counts as a Clue Shot in the summary.</x:v>
+      </x:c>
+      <x:c r="I8" s="31" t="str">
+        <x:v>Existing Mysterio lighting and remaining-shot/Super status stay. Neither spinner is lit or scored by the mode. Ordinary saucer attempts eject after the normal delay; a saucer Super releases after summary.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -11633,25 +11471,17 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spinner builds Venom; upper exits stage timed drop-bank attack shots.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ends when the staged Scorpion attacks are completed/resolved; otherwise stops on ball end.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spinner builds Venom; upper exit stages timed drop-bank attack shots.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I9" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Improved: persistent Venom build, attempt count, exit choice, and staged target status.</x:t>
-        </x:is>
+      <x:c r="F9" s="31" t="str">
+        <x:v>Enter the rooftop to enable both exits immediately. Spin to build the pending Sting Jackpot, then choose an exit to stage one target on the opposite drop bank.</x:v>
+      </x:c>
+      <x:c r="G9" s="31" t="str">
+        <x:v>The correct staged target collects the jackpot and ends the attempt; timer expiry also ends it. A rubber hit awards one consolation per attempt but leaves the timer and target active. Three resolved attempts defeat Scorpion; More Jackpots adds a fourth.</x:v>
+      </x:c>
+      <x:c r="H9" s="31" t="str">
+        <x:v>Base jackpots are 250K/500K/1M/1.5M; each rooftop spinner hit adds 50K. Rubber consolations are 200K/300K/400K/500K. Bigger adds 50%; More Time gives 12s instead of 8s. Shot Assist makes the first rubber consolation use the first attempt's full 250K base, without ending the attempt.</x:v>
+      </x:c>
+      <x:c r="I9" s="31" t="str">
+        <x:v>Before entry, status prompts ENTER ROOFTOP. Rooftop entry flashes both exits and the spinner while displaying the built jackpot. During a staged attack, the chosen bank target and GI flash and the persistent timer remains visible after a rubber award.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -11693,10 +11523,8 @@
           <x:t xml:space="preserve">STAR creates serum; the left web always delivers it. Every A+B completion permanently adds 500,000 to the current and future serum values for this mode, with no cap; an active serum also receives a full timer restart. Case Files add a third attempt, bigger starting value, slower decay, one expired-serum save, and Shot Assist delivery flexibility.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I10" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Improved: all deliveries use the left web; More Jackpots adds a third attempt; cumulative A+B boosts current and future serum values.</x:t>
-        </x:is>
+      <x:c r="I10" s="31" t="str">
+        <x:v>Star-needed GI slowly fades between F0F040 and F02040. Delivery GI is teal 406060 with a 250ms F02040 flash every 1.5s. The red STAR and flashing-purple left-web cues remain.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -11733,13 +11561,11 @@
           <x:t xml:space="preserve">Ends when Parafino multiball returns to one ball.</x:t>
         </x:is>
       </x:c>
-      <x:c r="H11" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">All three target zones light at mode start and remain lit. Left/right banks use their green lens colors and the pop area uses red. Each zone hit builds and lights its matching saucer jackpot; saucer lamps remain separate from target guidance. Add-a-ball qualifies from zone hit counts.</x:t>
-        </x:is>
+      <x:c r="H11" s="31" t="str">
+        <x:v>All three target zones light at mode start and remain active. Each zone hit builds and lights its matching saucer jackpot; saucer lamps remain separate from target guidance. Add-a-ball qualifies from zone hit counts. Gameplay and scoring remain unchanged.</x:v>
       </x:c>
       <x:c r="I11" s="31" t="str">
-        <x:v>Improved: target zones now light immediately; target guidance and earned saucer-jackpot flashes use separate shows. Saucer release calls now pass numeric IDs 1/2/3 to the shared eject service; the existing 2-second hold remains unchanged.</x:v>
+        <x:v>The clear-lens left-bank GI, both pop rings, and clear-lens right-bank GI pulse red together on a synchronized 500ms-on/500ms-off cycle. Green-lensed bank inserts are excluded from the red cue. Surrounding mode GI is solid 8080F0 blue. Numeric saucer ejection and the 2-second hold remain unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="26" customFormat="1" ht="541.2000122070312" customHeight="1">
@@ -11766,23 +11592,17 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hit upper targets to light all three saucers; the matching upper target makes its corresponding saucer a 3X jackpot. The upper spinner builds jackpot value.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timer expiry or ball end ends active play. Three jackpots only shows a 2-second CERBERUS DEFEATED message; it does not end the mode or gate progression.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">First jackpot starts a 16s timer (20s More Time). Upper targets, upper spinner, and any saucer hit reset it. After a collect the gate opens and other lit saucers return to 1X. More Jackpots gives each saucer one retained first collection at the same multiplier; Shot Assist is one use and consumes one collection on the awarded saucer.</x:t>
-        </x:is>
+      <x:c r="F12" s="31" t="str">
+        <x:v>Hit left-bank drops to light the corresponding saucers at 1X, or enter the rooftop and hit the corresponding upper targets to light or upgrade them to 2X. The upper spinner builds jackpot value.</x:v>
+      </x:c>
+      <x:c r="G12" s="31" t="str">
+        <x:v>Timer expiry or ball end ends active play. Three jackpots only shows a 2-second CERBERUS DEFEATED message; it does not end the mode.</x:v>
+      </x:c>
+      <x:c r="H12" s="31" t="str">
+        <x:v>First jackpot starts a 16s timer (20s More Time). Upper targets, upper spinner, and any saucer hit reset it; lower drops do not. After a collect the gate opens and other lit saucers return to 1X. More Jackpots gives each saucer one retained first collection at the same multiplier; Shot Assist is one use and consumes one collection on the awarded saucer.</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
-        <x:v>Reviewed/corrected; needs machine playtest. Orange GI retained; red saucer-hole and green 1/2/3 insert lighting remains lens-appropriate. Ball-drain cleanup now stops Cerberus before bonus and avoids the Crime Tracker remove/re-add race.</x:v>
+        <x:v>Needs machine playtest. Orange GI retained; red saucer-hole lamps show qualified jackpots and green 1/2/3 inserts show the corresponding 2X upgrades. Lower 1X qualification leaves the rooftop gate available; an upper hit closes it for the return to the lower playfield.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="26" customFormat="1" ht="805.2000122070312" customHeight="1">
@@ -11860,15 +11680,11 @@
           <x:t xml:space="preserve">Each Hunt ends when all staged targets are down or its timer expires. Hunt 3 immediately completes the mode and awards 50K per remaining arrow; ball end also stops it.</x:t>
         </x:is>
       </x:c>
-      <x:c r="H14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Three Hunts: targets 1/3/5, then 2/4, then 3. Timers are 12s or 18s with More Time. Red GI marks the Hunt; staged inserts stay green.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Arrows/time status, exit instruction, first-hit timer start, rubber arrow award, Hunt completion, and helper behavior are implemented.</x:t>
-        </x:is>
+      <x:c r="H14" s="31" t="str">
+        <x:v>Three Hunts: targets 1/3/5, then 2/4, then 3. Every Hunt uses an 8s timer, or 12s with More Time. The timer begins on the first staged drop or right-rubber hit. Red GI marks the Hunt; staged inserts stay green.</x:v>
+      </x:c>
+      <x:c r="I14" s="31" t="str">
+        <x:v>Recent timer update; needs machine playtest. Arrows/time status, exit instruction, first-hit timer start, rubber arrow award, Hunt completion, and helper behavior remain implemented.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="26" customFormat="1" ht="475.20001220703125" customHeight="1">
@@ -11935,30 +11751,20 @@
           <x:t xml:space="preserve">Centaur</x:t>
         </x:is>
       </x:c>
-      <x:c r="E16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Drops build jackpot and open the roof/post final phase.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ends when final rubber/target jackpot phase resolves; otherwise stops on ball end.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Drops build jackpot; roof/post phase creates the final rubber/target jackpot opportunity.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Good: final-phase countdown/status and state-change messaging are present.</x:t>
-        </x:is>
+      <x:c r="E16" s="31" t="str">
+        <x:v>1 ball; optional second staged finale with More Jackpots</x:v>
+      </x:c>
+      <x:c r="F16" s="31" t="str">
+        <x:v>Hit four unique drops to open the gate. Enter the rooftop, take the upper-left exit, and use the post hold to stage right targets 2-4 down for one decisive shot.</x:v>
+      </x:c>
+      <x:c r="G16" s="31" t="str">
+        <x:v>Each finale resolves on the first right rubber/outer-target result or timer expiry. More Jackpots allows one 12s rooftop re-entry and a second staged finale. Otherwise the mode ends after attempt one or on ball end.</x:v>
+      </x:c>
+      <x:c r="H16" s="31" t="str">
+        <x:v>Drops 25K and +100K Jackpot; bank rubbers 25K; right rubber collects the built Jackpot; target 1/5 awards 50K consolation. Bigger = 2X Jackpot; More Time = 12s finale; Safety Net = 10s save; Shot Assist converts target 1/5 to Jackpot.</x:v>
+      </x:c>
+      <x:c r="I16" s="31" t="str">
+        <x:v>Recent More Jackpots redesign implemented. Yellow build pulses, green rooftop route, yellow upper-left exit guidance, red right-bank GI and flashing outer inserts now communicate the route and one-shot finale. Needs machine playtest for gate/post timing and physical colors.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -12072,16 +11878,16 @@
         </x:is>
       </x:c>
       <x:c r="F19" s="31" t="str">
-        <x:v>Hit a right drop or STAR to reveal the hidden Phantom shot, then collect it before the window closes. STAR gives a live four-second reveal and remains repeatable.</x:v>
+        <x:v>Hit a right drop or STAR to reveal the hidden Phantom shot, then collect it before the window closes. The first right drop now gives 8s, or 10s with More Time. STAR remains a repeatable four-second reveal/add.</x:v>
       </x:c>
       <x:c r="G19" s="31" t="str">
         <x:v>Ends after five reveal rounds, or six with More Jackpots; otherwise stops on ball end. When a saucer makes the terminal collect, that ball remains held until the villain summary ends.</x:v>
       </x:c>
       <x:c r="H19" s="31" t="str">
-        <x:v>Unique right drops add time but progressively lower the jackpot. STAR adds four seconds without increasing the reveal count or lowering value.</x:v>
+        <x:v>First unique right drop: 8s at 1M, or 10s with More Time. Later unique drops add 8/10/12/14s and lower the normal Jackpot to 800K/600K/400K/200K; More Time adds 2s. STAR adds 4s without lowering value.</x:v>
       </x:c>
       <x:c r="I19" s="31" t="str">
-        <x:v>Right-bank GI pulses throughout. Standing right-drop inserts flash green; hit drops are solid green. STAR flashes red. Revealed white-lens locations flash purple at 250ms on/off; SAUCERS flashes only the six red hole lamps, not the green number inserts. Needs machine playtest.</x:v>
+        <x:v>Recent first-reveal timing update; needs machine playtest. Right-bank GI pulses; standing drops flash green and hit drops remain solid; STAR flashes red; revealed white-lens locations flash purple; SAUCERS flashes only the six red hole lamps.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -12108,25 +11914,17 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F20" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Complete crime zones to light upper-target jackpots and build the OX Super.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G20" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ends after Enforcer zones and OX Super are completed; otherwise stops on ball end.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H20" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Crime zones light upper-target jackpots; collected jackpots build the OX Super at center web.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Improved: persistent upper-jackpot/zone-clear progress and OX Super instruction.</x:t>
-        </x:is>
+      <x:c r="F20" s="31" t="str">
+        <x:v>Build left drops, pops, and right drops to light their matching rooftop jackpots. Continued hits build each zone's 1X-5X multiplier; the upper spinner builds Ox. Collect all three rooftop jackpots, then hit the center web target.</x:v>
+      </x:c>
+      <x:c r="G20" s="31" t="str">
+        <x:v>Ends after the center-web Ox Super is collected; otherwise stops on ball end.</x:v>
+      </x:c>
+      <x:c r="H20" s="31" t="str">
+        <x:v>Zone hits score 25K. Rooftop jackpots start at 100K, or 150K with Bigger, and use the zone multiplier. Spinner spins score 5K and add 50K to Ox; collected rooftop jackpots also add their awards.</x:v>
+      </x:c>
+      <x:c r="I20" s="31" t="str">
+        <x:v>Recent Ox chase lighting fix; needs machine playtest. Ox-ready chase order is l_mid_multibonus -&gt; l_advance_multiplier -&gt; l_special -&gt; l_mid_web_target, 300ms per step in 80F0F0. All four chase inserts are explicitly cleared when the chase or mode stops.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -12153,23 +11951,17 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Build frozen-diamond value with both drop banks; complete the right 5-bank to start the moving shipment chase.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collect the lit saucer for each shipment. Complete three shipments, or four with More Jackpots; otherwise stops on ball end. When a saucer makes the terminal collect, that ball remains held until the villain summary ends.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H21" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Drops raise the frozen-diamond jackpot and bank diamond_bonus. STAR freezes the chase and lights all three saucers for 10 seconds, or 15 with More Time.</x:t>
-        </x:is>
+      <x:c r="F21" s="31" t="str">
+        <x:v>Build the Frozen Diamond Jackpot with both drop banks. Any right drop starts a moving one-saucer shipment window. Complete/reset the right bank, then hit the first post-reset right drop to expand the moving window to two saucers; repeat to reach three.</x:v>
+      </x:c>
+      <x:c r="G21" s="31" t="str">
+        <x:v>Collect one correct saucer shipment, or two with More Jackpots; otherwise stops on ball end. A terminal saucer remains held until the villain summary ends.</x:v>
+      </x:c>
+      <x:c r="H21" s="31" t="str">
+        <x:v>Drops score 25K and bank 25K Diamond Bonus. Base Jackpot is 100K; right drops add 25K and left drops add 40K. Bigger uses 200K/+50K/+75K. Wrong saucer scores 10K. STAR banks 100K and freezes the current available window for 10s/15s.</x:v>
       </x:c>
       <x:c r="I21" s="31" t="str">
-        <x:v>Bigger Jackpots raises base and drop additions; Safety Net starts ball save; Shot Assist makes the first wrong saucer count. The red-lens STAR insert now flashes red at 250ms on / 250ms off throughout the mode, including chase and freeze, and is explicitly stopped and cleared on teardown.</x:v>
+        <x:v>Recent 1-2-3 saucer progression and red-hole-only lighting fix; needs machine playtest. Moving windows are 1; 1+2; 2+3; 3+1; then all three at maximum. STAR does not make unavailable saucers valid. Green number inserts remain off; red STAR flash and existing summary/device cleanup are preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -12196,25 +11988,17 @@
           <x:t xml:space="preserve">2-ball MB</x:t>
         </x:is>
       </x:c>
-      <x:c r="F22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A saucer holds one ball while the player lights independent areas around the playfield. Lighting enough areas qualifies a VUK jackpot.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Continues through multiball and ends when its objectives are completed, multiball ends, or the ball ends.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Area hits score 50K. Repeatable VUK Jackpots are worth 100K per lit area, or 150K with Bigger, and add their full value to persistent HARLEY JACKPOTS.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I22" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with repeatable lock-area-VUK rounds, full-value harley_bonus banking, Case Files, status, and summary values; needs on-machine playtest.</x:t>
-        </x:is>
+      <x:c r="F22" s="31" t="str">
+        <x:v>Start controlled 2-ball multiball with a delayed autoplunge. Capture one ball in any saucer, then light unique slings, pops, banks, and web areas. Four areas qualify the VUK; up to eight increase its value.</x:v>
+      </x:c>
+      <x:c r="G22" s="31" t="str">
+        <x:v>Repeat lock-build-VUK rounds until Harley multiball reaches one ball or the ball ends. The gate stays open through the delayed VUK kick and closes at upper entry or the 5-second fallback.</x:v>
+      </x:c>
+      <x:c r="H22" s="31" t="str">
+        <x:v>Saucer capture and each unique area score 50K. VUK Jackpots are 100K per lit area, or 150K with Bigger, and add their full value to persistent HARLEY JACKPOTS. More Jackpots retains two areas for the next lock.</x:v>
+      </x:c>
+      <x:c r="I22" s="31" t="str">
+        <x:v>Recent control/lighting repair; needs machine testing. Multiball now sets and clears the shared delayed-autoplunge flag; paired left-sling GI acts together; build/clear events drive area shows; held-saucer lamps stop on release; explicit ownership prevents duplicate stop-time eject requests. Physical same-saucer congestion remains unresolved and no rescue behavior was added.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -12241,10 +12025,8 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F23" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Complete the left drop bank before time expires to open the rooftop gate. Make three upper-spinner spins to light center web, then collect the Fountain Jackpot before the second timer expires.</x:t>
-        </x:is>
+      <x:c r="F23" s="31" t="str">
+        <x:v>Hit any single left 3-bank drop before time expires to open the rooftop gate. Make three upper-spinner spins to light center web, then collect the Fountain Jackpot before the second timer expires.</x:v>
       </x:c>
       <x:c r="G23" s="31" t="inlineStr">
         <x:is>
@@ -12256,10 +12038,8 @@
           <x:t xml:space="preserve">Left drops and spinner spins score 50K each. Fountain Jackpot is 300K + 100K per upper-target hit with no cap. Bigger changes this to 400K + 150K per hit. Speed Bonus is 50K per second remaining on each completed timed phase.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I23" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">More Time gives 30-second main timers. More Jackpots relights center web after a two-second jackpot message for a 10-second same-value second collect. Safety Net starts at Fountain readiness. Shot Assist doubles the first upper-target build hit.</x:t>
-        </x:is>
+      <x:c r="I23" s="31" t="str">
+        <x:v>More Time gives 30-second main timers. More Jackpots relights center web after a two-second jackpot message for a 10-second same-value second collect. Safety Net starts at Fountain readiness. Shot Assist doubles the first upper-target build hit. Stage 1 now advances on the first left-drop hit; dedicated music remains Song 54 (conquistador). Needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc5cb7bf8e9104e4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R3239a4b192cb486a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R9720c182defc4071"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R6e700616d25c40d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R1ab261853aa64409"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R500abf3dad224943"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R9f0bd51e19e14d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R0dbc6b4d561b4760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R65c7acabd1d14e15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rdcfd0d136d78488c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R52b11da9d41d4072"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R859e5932623f4f58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R602813543d4e4d90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rfabe172fa1494ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R4b4c6a7b93184ebb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rf3671c9a8a524e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Re2556a6421ae4781"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R595226a5a3124e25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R693fbe008018486a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R3c0512cb0e1746d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rdb573936551d4475"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R94911920bf114b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rdfa5ed22392541ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R8f7e6639bbb54f30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rcea3dcfaea5e40bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Re682346dab6c4412"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8591,7 +8591,7 @@
         <x:v>Implemented / recent spinner lighting fix</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Five chances, or seven with More JP. Each chance presents three choices; spinner reveals the correct choice for 3s, or 5s with More Time. Three correct shots defeats Pardo immediately. Using all chances with fewer than three correct shots produces the escape result. Hidden choices use solid green for white/green lens compatibility; reveal flashes only the correct green choice and turns wrong choices off. The main spinner insert flashes white while choices are hidden, turns off during the reveal, and resumes if another reveal is needed. Result GI flashes for 350ms, then restores.</x:v>
+        <x:v>Five chances, or seven with More JP. Each chance presents three choices selected from seven logical shot groups; the three upper targets are one shared upper-target group so they can never show conflicting good/bad states. Spinner reveals the correct choice for 4s, or 6s with More Time. Three correct shots defeats Pardo immediately. Using all chances with fewer than three correct shots produces the escape result. Hidden choices use solid green for white/green lens compatibility; reveal flashes only the correct green choice and turns wrong choices off. The main spinner insert flashes white while choices are hidden, turns off during the reveal, and resumes if another reveal is needed. Result GI flashes for 350ms, then restores.</x:v>
       </x:c>
       <x:c r="I27" s="31" t="inlineStr">
         <x:is>
@@ -12198,10 +12198,10 @@
         <x:v>Third correct shot defeats Pardo; fewer than three correct after five chances (seven with More JP) lets him escape.</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Spinner reveals the correct choice for 3 seconds (5 seconds with More Time). Correct Jackpots start at 100K and increase 50K; Bigger JP starts at 150K and increases 75K. Wrong choices score 10K and consume the chance.</x:v>
+        <x:v>Spinner reveals the correct choice for 4 seconds (6 seconds with More Time). Correct Jackpots start at 100K and increase 50K; Bigger JP starts at 150K and increases 75K. Wrong choices score 10K and consume the chance.</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
-        <x:v>Nine possible shot groups; three are selected per chance. Hidden choices are solid green across white and green lenses. Reveal flashes only the correct choice green and turns wrong choices off. Result GI restores after a 350ms green/red confirmation. Shot Assist makes all three choices correct on the first chance. Summary outcome distinguishes defeat from escape.</x:v>
+        <x:v>Seven logical shot groups; three are selected per chance. Upper-left, upper-center, and upper-right targets are one grouped choice and always share the same good/bad state. Hidden choices are solid green across white and green lenses. Reveal flashes only the correct choice green and turns wrong choices off. Result GI restores after a 350ms green/red confirmation. Shot Assist makes all three choices correct on the first chance. Summary outcome distinguishes defeat from escape.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rfabe172fa1494ec5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R4b4c6a7b93184ebb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rf3671c9a8a524e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Re2556a6421ae4781"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R595226a5a3124e25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R693fbe008018486a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R3c0512cb0e1746d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rdb573936551d4475"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R94911920bf114b63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rdfa5ed22392541ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R8f7e6639bbb54f30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rcea3dcfaea5e40bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Re682346dab6c4412"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3313b8cce8b04e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Re8ed0d31a08f43b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R6a8c58c188964097"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R1b0956c0b3c144a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R233bc989fbc64ece"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Re2ba4c1aa4ea45ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Raa17dde6de784881"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R425ad4d5b97943a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rebd86664dc724cc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R11e23c09aa034927"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R07e11370d2784538"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R9bfbccb937ac4fb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Ra81896037cee4cf2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2234,50 +2234,32 @@
           <x:t xml:space="preserve">Spider-Slayer</x:t>
         </x:is>
       </x:c>
-      <x:c r="E24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Expanding shot hunt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Persistent lit-shot growth</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ten lower-playfield categories + Daily Bugle VUK finish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">50K lit shots and a 2M decaying Slayer Jackpot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fast 15-shot completion preserves more jackpot value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Daily Bugle jackpot collected / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hunt Time measures first-to-fifteenth successful shot; jackpot value alone communicates the final urgency.</x:t>
-        </x:is>
+      <x:c r="E24" s="31" t="str">
+        <x:v>Implemented / reviewed; needs machine test</x:v>
+      </x:c>
+      <x:c r="F24" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" s="31" t="str">
+        <x:v>Expanding shot hunt</x:v>
+      </x:c>
+      <x:c r="H24" s="31" t="str">
+        <x:v>Persistent lit-shot growth with declining repeat values</x:v>
+      </x:c>
+      <x:c r="I24" s="31" t="str">
+        <x:v>Ten lower-playfield categories + Daily Bugle VUK finish</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="str">
+        <x:v>Per-category 50K/25K/10K/5K ladder; 2M timed Slayer Jackpot</x:v>
+      </x:c>
+      <x:c r="K24" s="31" t="str">
+        <x:v>15 hits open a 20-second VUK countdown; lit shots keep scoring</x:v>
+      </x:c>
+      <x:c r="L24" s="31" t="str">
+        <x:v>Jackpot collected / ball end; VUK opportunity expires and gate closes</x:v>
+      </x:c>
+      <x:c r="M24" s="31" t="str">
+        <x:v>Shot Assist counts/scores the first shot twice. All saucers share one counter and all six red hole lamps. Hunt Time is summarized only after 15 hits.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -2299,50 +2281,32 @@
           <x:t xml:space="preserve">Metal-Eating Monster</x:t>
         </x:is>
       </x:c>
-      <x:c r="E25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Overlapping zone rescue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Independent timers / escalating pressure</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Eight whole-playfield zones</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">250K zone saves; one half-value repeat per saved zone with More Jackpots</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">New attacks every 5s; saves accelerate the next attack to 2s</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4+ saved and no active attacks / 3 destroyed / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapter 5 reversible-pressure role. Unlike Harley's accumulating area-control multiball, this is a single-ball rescue race with up to three overlapping independent deadlines.</x:t>
-        </x:is>
+      <x:c r="E25" s="31" t="str">
+        <x:v>Implemented / reviewed; saved-GI fix needs machine test</x:v>
+      </x:c>
+      <x:c r="F25" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G25" s="31" t="str">
+        <x:v>Overlapping zone rescue</x:v>
+      </x:c>
+      <x:c r="H25" s="31" t="str">
+        <x:v>Independent timers / escalating pressure</x:v>
+      </x:c>
+      <x:c r="I25" s="31" t="str">
+        <x:v>Eight whole-playfield zones</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="str">
+        <x:v>250K saves; one half-value saved-zone repeat with More Jackpots</x:v>
+      </x:c>
+      <x:c r="K25" s="31" t="str">
+        <x:v>New attacks every 5s; saves accelerate the next attack to 2s</x:v>
+      </x:c>
+      <x:c r="L25" s="31" t="str">
+        <x:v>Four saved and no active attacks / three destroyed / ball end</x:v>
+      </x:c>
+      <x:c r="M25" s="31" t="str">
+        <x:v>Attacks use 100% flashing orange GI plus native inserts. Saved zones remain visible with solid inserts and 75% green GI; destroyed zones are dark.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2480,50 +2444,32 @@
           <x:t xml:space="preserve">The Fantastic Fakir</x:t>
         </x:is>
       </x:c>
-      <x:c r="E28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / recent rule update</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2-ball MB</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Multiball</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Saucer-to-roof</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Saucers + upper targets + spinners</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ruby JPs and Super</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MB drain / timing reveals</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MB end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic chapter MB role.</x:t>
-        </x:is>
+      <x:c r="E28" s="31" t="str">
+        <x:v>Implemented / reviewed; VUK chase + status fix need machine test</x:v>
+      </x:c>
+      <x:c r="F28" s="31" t="str">
+        <x:v>2-ball MB</x:v>
+      </x:c>
+      <x:c r="G28" s="31" t="str">
+        <x:v>Multiball</x:v>
+      </x:c>
+      <x:c r="H28" s="31" t="str">
+        <x:v>Saucer-to-roof Ruby hunt</x:v>
+      </x:c>
+      <x:c r="I28" s="31" t="str">
+        <x:v>Saucers + VUK route + upper targets + both spinners</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="str">
+        <x:v>Ruby Jackpots and one summed Super</x:v>
+      </x:c>
+      <x:c r="K28" s="31" t="str">
+        <x:v>10s rooftop Ruby window; 15s with More Time</x:v>
+      </x:c>
+      <x:c r="L28" s="31" t="str">
+        <x:v>Multiball returns to one ball</x:v>
+      </x:c>
+      <x:c r="M28" s="31" t="str">
+        <x:v>Shared VUK chase stops on upper entry or attempt cleanup. Corrected status output uses real Ruby/Super state instead of nonexistent legacy flags.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2546,7 +2492,7 @@
         </x:is>
       </x:c>
       <x:c r="E29" s="31" t="str">
-        <x:v>Implemented / recent Scepter timer display fix</x:v>
+        <x:v>Implemented / reviewed; Scepter wording fix needs machine test</x:v>
       </x:c>
       <x:c r="F29" s="31" t="inlineStr">
         <x:is>
@@ -2578,7 +2524,7 @@
         <x:v>VUK Super or scepter timeout</x:v>
       </x:c>
       <x:c r="M29" s="31" t="str">
-        <x:v>Optional fifth demon with More Jackpots; persistent 20s/30s Scepter timer now shows the current VUK objective. Machine playtest pending.</x:v>
+        <x:v>Optional fifth demon with More Jackpots; persistent 20s/30s Scepter timer now directs SUPER AT DAILY BUGLE, or KILL THE DEMON, COLLECT THE SUPER while that demon remains. Machine playtest pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2601,7 +2547,7 @@
         </x:is>
       </x:c>
       <x:c r="E30" s="31" t="str">
-        <x:v>Implemented / recent failure-cleanup fix</x:v>
+        <x:v>Implemented / reviewed; flicker/status/gate fix needs machine test</x:v>
       </x:c>
       <x:c r="F30" s="31" t="inlineStr">
         <x:is>
@@ -2628,18 +2574,14 @@
           <x:t xml:space="preserve">Increasing restoration awards</x:t>
         </x:is>
       </x:c>
-      <x:c r="K30" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">40s blackout / 50s More Time</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L30" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Six restored / timer / ball end</x:t>
-        </x:is>
+      <x:c r="K30" s="31" t="str">
+        <x:v>Unrestored regions flicker independently for 100ms every random 2–5s; CITY TIME remains live through the Blackout finale.</x:v>
+      </x:c>
+      <x:c r="L30" s="31" t="str">
+        <x:v>Six restored / timer / ball end</x:v>
       </x:c>
       <x:c r="M30" s="31" t="str">
-        <x:v>Simple region-restoration role with optional VUK Blackout Jackpot. Timer failure now uses the centralized summary/cleanup pipeline; machine regression test pending.</x:v>
+        <x:v>More Jackpots adds the 500K Daily Bugle Blackout Jackpot. Its shared VUK chase starts after one guarded gate-open request. Timeout and success cleanup need machine regression testing.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2726,10 +2668,8 @@
           <x:t xml:space="preserve">Dr. Noah Boddy</x:t>
         </x:is>
       </x:c>
-      <x:c r="E32" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / recent rule update</x:t>
-        </x:is>
+      <x:c r="E32" s="31" t="str">
+        <x:v>Implemented / reviewed; lifecycle + VUK chase fix needs machine test</x:v>
       </x:c>
       <x:c r="F32" s="31" t="inlineStr">
         <x:is>
@@ -2756,20 +2696,14 @@
           <x:t xml:space="preserve">Secret-shot Jackpot plus uncapped upper-spinner build; each 25K/50K effective increment banks as INVISIBLE FORTUNE</x:t>
         </x:is>
       </x:c>
-      <x:c r="K32" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hidden info / wrong routing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L32" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Secret objectives solved / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M32" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mad Science reveal role.</x:t>
-        </x:is>
+      <x:c r="K32" s="31" t="str">
+        <x:v>Persistent cross-visit reveal state; shared VUK chase guides each rooftop return and one Python gate-open event owns access.</x:v>
+      </x:c>
+      <x:c r="L32" s="31" t="str">
+        <x:v>Secret objectives solved / hurry-up missed / ball end</x:v>
+      </x:c>
+      <x:c r="M32" s="31" t="str">
+        <x:v>Both success and missed/expired failure finish at completed state 2; their player-facing messages remain distinct. Machine regression testing pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -2791,10 +2725,8 @@
           <x:t xml:space="preserve">Dr. Magneto</x:t>
         </x:is>
       </x:c>
-      <x:c r="E33" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented redesign / needs playtest</x:t>
-        </x:is>
+      <x:c r="E33" s="31" t="str">
+        <x:v>Implemented / reviewed; status + lighting fix needs machine test</x:v>
       </x:c>
       <x:c r="F33" s="31" t="inlineStr">
         <x:is>
@@ -2821,20 +2753,16 @@
           <x:t xml:space="preserve">100K/150K rollovers, 250K pops, 500K/750K Super, optional 250K star</x:t>
         </x:is>
       </x:c>
-      <x:c r="K33" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">8/10-second circuit windows and a 16/20-second single-attempt Super</x:t>
-        </x:is>
+      <x:c r="K33" s="31" t="str">
+        <x:v>8/10-second circuits; A/B and flashing pops accelerate after 4 seconds. The 16/20-second center-web chase accelerates after 8 seconds.</x:v>
       </x:c>
       <x:c r="L33" s="31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Center-web Super / expiry / ball end</x:t>
         </x:is>
       </x:c>
-      <x:c r="M33" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Uses underrepresented slings, inlanes, middle rollovers, pops, star, and center web in a readable two-circuit build.</x:t>
-        </x:is>
+      <x:c r="M33" s="31" t="str">
+        <x:v>Purple base GI; available sling/inlane areas pulse and return to GI color when done. Completed pops stay solid. Four-light white web chase and live Super status need machine testing.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -8453,15 +8381,11 @@
           <x:t xml:space="preserve">Spider-Slayer</x:t>
         </x:is>
       </x:c>
-      <x:c r="G24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest polish</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Expanding 15-hit hunt: one random category starts lit, every successful lit shot scores and adds another persistent lit category. The fifteenth hit opens the Daily Bugle VUK for a decaying Slayer Jackpot.</x:t>
-        </x:is>
+      <x:c r="G24" s="31" t="str">
+        <x:v>Implemented / reviewed; needs machine test</x:v>
+      </x:c>
+      <x:c r="H24" s="31" t="str">
+        <x:v>Expanding 15-hit hunt with per-category repeat ladders. The fifteenth hit opens a 20-second Daily Bugle VUK countdown (25 with More Time); lit categories continue scoring. Shot Assist scores/counts the first shot twice.</x:v>
       </x:c>
       <x:c r="I24" s="31" t="inlineStr">
         <x:is>
@@ -8499,15 +8423,11 @@
           <x:t xml:space="preserve">Metal-Eating Monster</x:t>
         </x:is>
       </x:c>
-      <x:c r="G25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Eight-zone rescue mode. A new safe zone comes under attack every 5 seconds; each attack has an independent 12-second timer. Hits save zones, save reactions bring the next attack in 2 seconds, four saves stop new attacks, and three destroyed zones end the mode.</x:t>
-        </x:is>
+      <x:c r="G25" s="31" t="str">
+        <x:v>Implemented / reviewed; saved-GI fix needs machine test</x:v>
+      </x:c>
+      <x:c r="H25" s="31" t="str">
+        <x:v>Eight-zone rescue: attacks begin every 5s, each has a 12s timer, saves reset the next attack to 2s, four saves stop new attacks, and three destroyed zones end the mode. Attacked zones flash native inserts plus 100% orange GI; saved zones use solid native inserts plus 75% green GI (00BF00); destroyed zones are dark.</x:v>
       </x:c>
       <x:c r="I25" s="31" t="inlineStr">
         <x:is>
@@ -8629,15 +8549,11 @@
           <x:t xml:space="preserve">The Fantastic Fakir</x:t>
         </x:is>
       </x:c>
-      <x:c r="G28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / recent rule update</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2-ball Ruby Heist: one saucer parks a ball and reveals the real Ruby at its mapped upper target; spinners build value and three Ruby Jackpots qualify the Super. A successful Ruby or Super Ruby collect holds the parked saucer ball for 2 seconds before the shared occupancy-checked eject.</x:t>
-        </x:is>
+      <x:c r="G28" s="31" t="str">
+        <x:v>Implemented / reviewed; VUK chase + status fix need machine test</x:v>
+      </x:c>
+      <x:c r="H28" s="31" t="str">
+        <x:v>2-ball Ruby Heist: one saucer parks a ball and opens the gate; the shared VUK route chase guides the live ball until upper entry, where the 10s/15s Ruby timer begins. Spinners build value, three Rubies qualify one Super, and post-Super Rubies continue until multiball ends. Status messages now use the actual Ruby/Super state.</x:v>
       </x:c>
       <x:c r="I28" s="31" t="inlineStr">
         <x:is>
@@ -8676,10 +8592,10 @@
         </x:is>
       </x:c>
       <x:c r="G29" s="31" t="str">
-        <x:v>Implemented / recent Scepter timer display fix</x:v>
+        <x:v>Implemented / reviewed; Scepter wording fix needs machine test</x:v>
       </x:c>
       <x:c r="H29" s="31" t="str">
-        <x:v>Four randomly selected demons appear one at a time every 4s across two webs, two banks, and two pops. Destroying all four starts a 20s scepter phase and opens rooftop access; the VUK scores the 1M Super. The Scepter phase now shows a persistent SCEPTER TIME status (30s with More Time), cancels the prior demon reminder, and displays SHOOT THE VUK or OPTIONAL DEMON - THEN VUK. Lighting uses dim dark-red background GI, independently flashing yellow active demons, and a yellow-only ramp/VUK flash during the scepter phase. Defeat and escape produce the correct summary outcome.</x:v>
+        <x:v>Four randomly selected demons appear one at a time every 4s across two webs, two banks, and two pops. Destroying all four starts a 20s scepter phase and opens rooftop access; the VUK scores the 1M Super. The persistent SCEPTER TIME status uses SUPER AT DAILY BUGLE normally, or KILL THE DEMON, COLLECT THE SUPER while the optional fifth demon remains. Lighting uses dim dark-red background GI, independently flashing yellow active demons, and a yellow-only ramp/VUK flash during the scepter phase. Defeat and escape produce the correct summary outcome.</x:v>
       </x:c>
       <x:c r="I29" s="31" t="inlineStr">
         <x:is>
@@ -8718,10 +8634,10 @@
         </x:is>
       </x:c>
       <x:c r="G30" s="31" t="str">
-        <x:v>Implemented / recent failure-cleanup fix</x:v>
+        <x:v>Implemented / reviewed; flicker/status/gate fix needs machine test</x:v>
       </x:c>
       <x:c r="H30" s="31" t="str">
-        <x:v>Restore six coordinate-based GI regions before the 40-second timer expires. More Jackpots adds a final VUK Blackout Jackpot. Timer failure now enters the centralized failed-summary pipeline, marks Swami played/completed for progression, and clears the villain-running lock after the summary instead of leaving the chapter display at PLAYING.</x:v>
+        <x:v>Restore six coordinate-based GI regions before the 40-second timer expires. Each unrestored 404040 region independently flickers full white for 100ms every random 2–5s; restored regions remain solid white. A persistent CITY TIME status shows seconds and restoration progress, then BLACKOUT AT DAILY BUGLE during the More Jackpots VUK finale. The finale opens the rooftop gate once and uses the shared VUK chase. Timer failure uses the corrected summary/cleanup pipeline.</x:v>
       </x:c>
       <x:c r="I30" s="31" t="inlineStr">
         <x:is>
@@ -8805,15 +8721,11 @@
           <x:t xml:space="preserve">Dr. Noah Boddy</x:t>
         </x:is>
       </x:c>
-      <x:c r="G32" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / recent rule update</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H32" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Invisible-target search. Upper targets eliminate false lower drops while the upper spinner builds the Secret Jackpot. Each spinner hit also banks the effective 25K increase, or 50K with Bigger Jackpots, in persistent noah_boddy_bonus as INVISIBLE FORTUNE. The hidden target and eliminated false locations persist across rooftop visits. Each entry resets both banks and re-drops prior eliminations; an early exit resets both banks and requires another rooftop entry to continue.</x:t>
-        </x:is>
+      <x:c r="G32" s="31" t="str">
+        <x:v>Implemented / reviewed; lifecycle + VUK chase fix needs machine test</x:v>
+      </x:c>
+      <x:c r="H32" s="31" t="str">
+        <x:v>Invisible-target search. Upper targets eliminate false lower drops while the upper spinner builds the Secret Jackpot. Hidden target and reveal progress persist across rooftop visits. Playing state is 1; both Jackpot success and missed/expired failure finish at completed state 2 with different display messages. The shared VUK chase guides each required rooftop return and stops on entry, result, or cleanup. Rooftop access is requested once from Python.</x:v>
       </x:c>
       <x:c r="I32" s="31" t="inlineStr">
         <x:is>
@@ -8851,15 +8763,11 @@
           <x:t xml:space="preserve">Dr. Magneto</x:t>
         </x:is>
       </x:c>
-      <x:c r="G33" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented redesign / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H33" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cross-feed circuits: left sling/inlane lights right-side A, which lights the left pop; right sling/inlane lights left-side B, which lights the right pop. Hit flashing pops to lock them solid; both solid light the 16-second center-web Super.</x:t>
-        </x:is>
+      <x:c r="G33" s="31" t="str">
+        <x:v>Implemented / reviewed; status + lighting fix needs machine test</x:v>
+      </x:c>
+      <x:c r="H33" s="31" t="str">
+        <x:v>Cross-feed circuits: left sling/inlane lights right-side A and the left pop; right sling/inlane lights left-side B and the right pop. Purple 6030A0 GI underlies pulsing qualifier areas. A/B and flashing pops double pulse speed after 4 seconds. Both completed pops light the center-web Super with a four-step white chase that doubles speed after 8 seconds. Persistent Super status follows the live countdown.</x:v>
       </x:c>
       <x:c r="I33" s="31" t="inlineStr">
         <x:is>
@@ -10534,10 +10442,8 @@
           <x:t xml:space="preserve">The Fantastic Fakir</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Old Ms. Trubble puzzle gameplay repurposed into The Fantastic Fakir's Ruby Heist.</x:t>
-        </x:is>
+      <x:c r="D6" s="31" t="str">
+        <x:v>Old Ms. Trubble puzzle gameplay was replaced by the reviewed Ruby Heist: saucer hold, shared VUK route chase, rooftop Ruby targets, spinner builds, one summed Super, and corrected live status messaging.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -10972,10 +10878,8 @@
           <x:t xml:space="preserve">Spider-Slayer</x:t>
         </x:is>
       </x:c>
-      <x:c r="D26" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Originally introduced as a Chapter 5 placeholder; now has the expanding 15-hit hunt and decaying Daily Bugle jackpot implementation.</x:t>
-        </x:is>
+      <x:c r="D26" s="85" t="str">
+        <x:v>Originally a Chapter 5 placeholder; now reviewed as a 15-hit expanding hunt with per-category declining repeat scores and a timed Daily Bugle VUK Jackpot.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -10994,10 +10898,8 @@
           <x:t xml:space="preserve">Metal-Eating Monster</x:t>
         </x:is>
       </x:c>
-      <x:c r="D27" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Originally introduced as a Chapter 5 placeholder; now implemented as an eight-zone overlapping rescue mode with independent destruction timers.</x:t>
-        </x:is>
+      <x:c r="D27" s="85" t="str">
+        <x:v>Originally a Chapter 5 placeholder; now reviewed as an eight-zone overlapping rescue mode. Attacked/saved/destroyed lighting is standardized to 100% flashing orange GI, 75% solid green GI, and dark respectively.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -12061,28 +11963,20 @@
           <x:t xml:space="preserve">Spider-Slayer</x:t>
         </x:is>
       </x:c>
-      <x:c r="E24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">One random shot category starts lit. Each successful lit shot scores 50K and adds another persistent lit category. Hunt Time runs from the first successful hit through the fifteenth, then all build shots shut off and the Daily Bugle VUK lights.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Completes when the Daily Bugle VUK collects the Slayer Jackpot. The winning ball remains held through the villain summary and releases when the summary finishes or is skipped. A drain before collection ends with SLAYER ESCAPED.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H24" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Successful lit shots score 50K; Bigger raises them to 75K. Slayer Jackpot starts at 2M, or 2.5M with Bigger, and decays to a 100K minimum. An unlit VUK visit uses the shared 1.5-second eject.</x:t>
-        </x:is>
+      <x:c r="E24" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F24" s="31" t="str">
+        <x:v>Hit persistent lit categories; each successful hit adds another category. Repeat values decline independently per logical category.</x:v>
+      </x:c>
+      <x:c r="G24" s="31" t="str">
+        <x:v>Slayer Jackpot collected or ball end; an expired VUK countdown closes the gate while lit-category scoring continues.</x:v>
+      </x:c>
+      <x:c r="H24" s="31" t="str">
+        <x:v>15 qualifying hits open the Daily Bugle VUK for 20 seconds (25 with More Time). Shot ladders are 50K/25K/10K/5K, or 75K/50K/25K/10K with Bigger. More Jackpots preserves the full second-hit value; Shot Assist scores/counts the first shot twice.</x:v>
       </x:c>
       <x:c r="I24" s="31" t="str">
-        <x:v>More Jackpots freezes the full jackpot for 10 seconds. More Time halves decay to 50K/sec. Safety Net starts a 10-second save when the VUK lights. Shot Assist makes the first hit add two new categories. The shared Master Vine route chase guides the terminal VUK and clears on collect or teardown; needs machine playtest.</x:v>
+        <x:v>All active categories pulse red; the saucer category uses all six red hole lamps. Summary shows collected Jackpot only and omits Hunt Time until the hunt is completed.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -12124,10 +12018,8 @@
           <x:t xml:space="preserve">Saving a zone scores 250K and resets the next-attack delay to 2 seconds. More Time gives 16-second zone timers; Bigger gives 400K saves; More Jackpots relights each saved zone once for half value; Safety Net is the standard ball save; Shot Assist automatically saves the first zone that reaches 2 seconds.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I25" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with eight physical zone groups and native-lens attack/save lighting; needs machine playtest.</x:t>
-        </x:is>
+      <x:c r="I25" s="31" t="str">
+        <x:v>Reviewed lighting: attacked zones flash native inserts and 100% orange GI every 250ms; saved zones retain solid native inserts with 75% green GI (00BF00); destroyed zones remain dark.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -12228,25 +12120,17 @@
           <x:t xml:space="preserve">2-ball MB</x:t>
         </x:is>
       </x:c>
-      <x:c r="F28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ruby Heist multiball: a saucer parks one ball and reveals an upper Ruby while the live ball reaches the roof and spinners build the Ruby/Super value. After a successful Ruby or Super collect, the parked ball remains held for 2 seconds before release.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ends when Fakir multiball ends.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ruby Heist: saucers reveal upper rubies; spinners build value; 3 Ruby JPs qualify Super; post-Super rubies continue until multiball ends.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I28" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Improved: persistent Ruby progress, reveal objective, Super-lit status, and a 2-second successful-collect saucer hold using the shared eject service.</x:t>
-        </x:is>
+      <x:c r="F28" s="31" t="str">
+        <x:v>Park a ball in a saucer, follow the VUK chase to the roof, then hit the mapped upper Ruby; spinners build the active award.</x:v>
+      </x:c>
+      <x:c r="G28" s="31" t="str">
+        <x:v>Ends when Fakir multiball returns to one ball.</x:v>
+      </x:c>
+      <x:c r="H28" s="31" t="str">
+        <x:v>Three Ruby Jackpots qualify one Super equal to their combined collected values; post-Super base Rubies continue. The rooftop timer begins only on upper entry.</x:v>
+      </x:c>
+      <x:c r="I28" s="31" t="str">
+        <x:v>Shared green VUK chase runs only while rooftop access is being sought. Live status now reports Ruby/Super state, mapped target, builds, collections, timeouts, and readiness.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -12283,7 +12167,7 @@
         <x:v>Demons appear every 4s and remain active until collected. Jackpots are 200K, 250K, 300K, and 350K. Scepter phase lasts 20s and awards a 1M Super.</x:v>
       </x:c>
       <x:c r="I29" s="31" t="str">
-        <x:v>Dim 401010 background GI; active demons flash yellow every 300ms. The shared Master Vine route chase guides the timed final VUK shot during the scepter phase and clears on collect, timeout, or teardown. More JP adds an independently flashing optional 500K demon. Needs machine playtest.</x:v>
+        <x:v>Dim 401010 background GI; active demons flash yellow every 300ms. The shared Master Vine route chase guides the timed final VUK shot during the scepter phase and clears on collect, timeout, or teardown. Status reads SUPER AT DAILY BUGLE, or KILL THE DEMON, COLLECT THE SUPER while the optional 500K demon remains. Needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -12326,7 +12210,7 @@
         </x:is>
       </x:c>
       <x:c r="I30" s="31" t="str">
-        <x:v>Restored regions remain lit. With More Jackpots, the shared Master Vine route chase guides the final 500K Blackout Jackpot at the VUK and clears on collect, timeout, or teardown. Safety Net starts ball save; Shot Assist spots one additional unrestored region. Needs machine regression testing.</x:v>
+        <x:v>Unrestored 404040 regions independently flicker full white for 100ms every random 2–5s; restored regions stay solid white. CITY TIME shows the live countdown and restored count, changing to BLACKOUT AT DAILY BUGLE for the More JP finale. The finale uses one guarded gate-open event and the shared VUK chase. Needs machine regression testing.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -12413,10 +12297,8 @@
           <x:t xml:space="preserve">Upper targets score 25K, or 75K with More Jackpots. Each upper spin increases the displayed Jackpot by 25K, or effectively 50K with Bigger, and banks that increment as persistent INVISIBLE FORTUNE.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I32" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with persistent cross-visit reveal progress, reconstructed physical drop state, uncapped spinner building, noah_boddy_bonus banking, hurry-up, Case Files, status, and summary values; needs on-machine playtest.</x:t>
-        </x:is>
+      <x:c r="I32" s="31" t="str">
+        <x:v>Persistent cross-visit reveal progress, reconstructed physical drop state, uncapped spinner building, INVISIBLE FORTUNE banking, hurry-up, Case Files, status, and summaries retained. Shared VUK chase runs only while rooftop entry is needed. Success and failure display differently but both mark completed progression. Duplicate YAML gate request removed. Needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -12458,10 +12340,8 @@
           <x:t xml:space="preserve">Lit rollover 100K; flashing pop 250K; center-web Super 500K. Bigger Jackpots changes rollover hits to 150K and the Super to 750K.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I33" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">More Jackpots lights the star for 6 seconds and 250K whenever a new objective lights. More Time gives 10-second circuits and a 20-second Super. Safety Net is a 10-second opening save. Shot Assist lights A and B on the first qualifier.</x:t>
-        </x:is>
+      <x:c r="I33" s="31" t="str">
+        <x:v>More Jackpots lights STAR for 6 seconds and 250K whenever a new objective lights. More Time gives 10-second circuits and a 20-second Super. Safety Net is a 10-second opening save. Shot Assist lights A and B on the first qualifier. Purple GI, qualifier-area pulses, 4-second objective acceleration, an 8-second-delayed center-web chase acceleration, and live Super status are implemented; needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="34">

--- a/docs/spiderman_1967_50_villain_chapter_plan.xlsx
+++ b/docs/spiderman_1967_50_villain_chapter_plan.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3313b8cce8b04e88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Re8ed0d31a08f43b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R6a8c58c188964097"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R1b0956c0b3c144a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R233bc989fbc64ece"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Re2ba4c1aa4ea45ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Raa17dde6de784881"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R425ad4d5b97943a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rebd86664dc724cc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R11e23c09aa034927"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R07e11370d2784538"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R9bfbccb937ac4fb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Ra81896037cee4cf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Reb0c41b0e535425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R24ef06a1a8a8465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R5ca34f4559584f79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R44cc960f30e444db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R7c673aebe65d4fef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R5128b519b4164f6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rc046f837cd0c43a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R16f1c3fcb54b4f9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R39c7ac30dd4f4626"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Raa02d98ccba84d04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rb49767a7b0094bea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R77d85c6c0d4c43ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R035f15c4f4544a28"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5167,7 +5167,7 @@
     </x:row>
     <x:row r="2" s="26" customFormat="1" ht="30" customHeight="1">
       <x:c r="A2" s="83" t="str">
-        <x:v>Source of truth: current villain_bookends.py and music_control.py/yaml as of 2026-08-23. Bookends own villain/wizard music; music_control owns chapter base music.</x:v>
+        <x:v>Source of truth: ASM67_2026_08_27_1am.zip — current villain_bookends.py and music_control.py/yaml. Bookends own villain/wizard music; music_control owns chapter base music.</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -5176,7 +5176,7 @@
     </x:row>
     <x:row r="3" s="26" customFormat="1" ht="30" customHeight="1">
       <x:c r="A3" s="83" t="str">
-        <x:v>Rule: chapter base themes use longer songs. Villain/wizard songs have at most two uses; maintheme, loop*, and intro_* tracks remain outside villain/wizard gameplay.</x:v>
+        <x:v>Rule: all 67 villain/wizard modes now have unique gameplay songs. maintheme, loop*, and intro_* tracks remain outside villain/wizard gameplay; Song 8 remains within its special-use limit.</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -5249,15 +5249,15 @@
           <x:t xml:space="preserve">rat_race</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cyclops; Kingpin / Final Showdown</x:t>
-        </x:is>
+      <x:c r="C8" s="74" t="str">
+        <x:v>Cyclops</x:v>
       </x:c>
       <x:c r="D8" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E8" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="74" t="str">
+        <x:v>Kingpin / Final Showdown reassigned to Song 82.</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A9" s="73" t="n">
@@ -5637,15 +5637,15 @@
           <x:t xml:space="preserve">tautwalk</x:t>
         </x:is>
       </x:c>
-      <x:c r="C28" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Electro; Time Showdown</x:t>
-        </x:is>
+      <x:c r="C28" s="74" t="str">
+        <x:v>Electro</x:v>
       </x:c>
       <x:c r="D28" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E28" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E28" s="74" t="str">
+        <x:v>Time-Tossed Showdown reassigned to Song 83.</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A29" s="73" t="n">
@@ -5910,15 +5910,15 @@
           <x:t xml:space="preserve">the_hearse</x:t>
         </x:is>
       </x:c>
-      <x:c r="C43" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Doctor Zapp; The Web Tightens</x:t>
-        </x:is>
+      <x:c r="C43" s="74" t="str">
+        <x:v>Doctor Zapp</x:v>
       </x:c>
       <x:c r="D43" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E43" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E43" s="74" t="str">
+        <x:v>The Web Tightens reassigned to Song 84.</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A44" s="73" t="n">
@@ -5986,15 +5986,15 @@
           <x:t xml:space="preserve">the_shadows</x:t>
         </x:is>
       </x:c>
-      <x:c r="C47" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The Plutonians; The Molemen</x:t>
-        </x:is>
+      <x:c r="C47" s="74" t="str">
+        <x:v>The Plutonians</x:v>
       </x:c>
       <x:c r="D47" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E47" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E47" s="74" t="str">
+        <x:v>The Molemen reassigned to Song 85.</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A48" s="73" t="n">
@@ -6005,15 +6005,15 @@
           <x:t xml:space="preserve">fbi</x:t>
         </x:is>
       </x:c>
-      <x:c r="C48" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Igor; Crime Wave</x:t>
-        </x:is>
+      <x:c r="C48" s="74" t="str">
+        <x:v>Igor</x:v>
       </x:c>
       <x:c r="D48" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E48" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E48" s="74" t="str">
+        <x:v>Crime Wave reassigned to Song 86.</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A49" s="73" t="n">
@@ -6081,15 +6081,15 @@
           <x:t xml:space="preserve">motorcycle_circus</x:t>
         </x:is>
       </x:c>
-      <x:c r="C52" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mastermind Trap; Trubble Unleashed</x:t>
-        </x:is>
+      <x:c r="C52" s="74" t="str">
+        <x:v>Mastermind Trap</x:v>
       </x:c>
       <x:c r="D52" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E52" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E52" s="74" t="str">
+        <x:v>Trubble Unleashed reassigned to Song 87.</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A53" s="73" t="n">
@@ -6138,15 +6138,15 @@
           <x:t xml:space="preserve">clasical_gas</x:t>
         </x:is>
       </x:c>
-      <x:c r="C55" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fiddler; Sinister Surge</x:t>
-        </x:is>
+      <x:c r="C55" s="74" t="str">
+        <x:v>Fiddler</x:v>
       </x:c>
       <x:c r="D55" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E55" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E55" s="74" t="str">
+        <x:v>Sinister Surge reassigned to Song 88.</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A56" s="73" t="n">
@@ -6193,15 +6193,15 @@
           <x:t xml:space="preserve">moon_godess</x:t>
         </x:is>
       </x:c>
-      <x:c r="C58" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pardo; Master Vine</x:t>
-        </x:is>
+      <x:c r="C58" s="74" t="str">
+        <x:v>Pardo</x:v>
       </x:c>
       <x:c r="D58" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E58" s="74" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E58" s="74" t="str">
+        <x:v>Master Vine reassigned to Song 89.</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" s="26" customFormat="1" ht="15" customHeight="1">
       <x:c r="A59" s="73" t="n">
@@ -6233,18 +6233,14 @@
           <x:t xml:space="preserve">death_have_no_mercy</x:t>
         </x:is>
       </x:c>
-      <x:c r="C60" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spider-Slayer; Lost World Invasion</x:t>
-        </x:is>
+      <x:c r="C60" s="74" t="str">
+        <x:v>Spider-Slayer</x:v>
       </x:c>
       <x:c r="D60" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E60" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">New track now integrated.</x:t>
-        </x:is>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E60" s="74" t="str">
+        <x:v>Invasion from Everywhere reassigned to Song 90.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" s="26" customFormat="1" ht="15" customHeight="1">
@@ -6279,18 +6275,14 @@
           <x:t xml:space="preserve">washington_square</x:t>
         </x:is>
       </x:c>
-      <x:c r="C62" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Clive and Blotto; Sir Galahad</x:t>
-        </x:is>
+      <x:c r="C62" s="74" t="str">
+        <x:v>Clive and Blotto</x:v>
       </x:c>
       <x:c r="D62" s="73" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E62" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">New track now integrated.</x:t>
-        </x:is>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E62" s="74" t="str">
+        <x:v>Sir Galahad reassigned to Song 91.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" s="26" customFormat="1" ht="15" customHeight="1">
@@ -6302,18 +6294,14 @@
           <x:t xml:space="preserve">bongo_rock</x:t>
         </x:is>
       </x:c>
-      <x:c r="C63" s="76" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Metal Monster; Bolton and Boomer</x:t>
-        </x:is>
+      <x:c r="C63" s="76" t="str">
+        <x:v>Metal Monster</x:v>
       </x:c>
       <x:c r="D63" s="75" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E63" s="76" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">New track now integrated.</x:t>
-        </x:is>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E63" s="76" t="str">
+        <x:v>Bolton and Boomer reassigned to Song 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" s="26" customFormat="1" ht="15" customHeight="1">
@@ -6360,25 +6348,17 @@
           <x:t xml:space="preserve">Sinister Surge</x:t>
         </x:is>
       </x:c>
-      <x:c r="B68" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">50</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C68" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">None</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D68" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">50</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E68" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bookend assignment remains active.</x:t>
-        </x:is>
+      <x:c r="B68" s="85" t="str">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C68" s="85" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D68" s="85" t="str">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E68" s="85" t="str">
+        <x:v>Bookend assignment updated to Fuzz.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" s="26" customFormat="1" ht="26.399999618530273" customHeight="1">
@@ -6414,25 +6394,17 @@
           <x:t xml:space="preserve">Trubble Unleashed</x:t>
         </x:is>
       </x:c>
-      <x:c r="B70" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">47</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C70" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">None</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D70" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">47</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E70" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bookend assignment remains active.</x:t>
-        </x:is>
+      <x:c r="B70" s="85" t="str">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C70" s="85" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D70" s="85" t="str">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E70" s="85" t="str">
+        <x:v>Bookend assignment updated to Mas Que Nada.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" s="26" customFormat="1" ht="39.599998474121094" customHeight="1">
@@ -6468,25 +6440,17 @@
           <x:t xml:space="preserve">Final Showdown / Kingpin</x:t>
         </x:is>
       </x:c>
-      <x:c r="B72" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C72" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">None</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D72" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E72" s="85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bookend assignment remains active.</x:t>
-        </x:is>
+      <x:c r="B72" s="85" t="str">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C72" s="85" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="D72" s="85" t="str">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E72" s="85" t="str">
+        <x:v>Bookend assignment updated to Rescue Squad.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" s="26" customFormat="1" ht="15" customHeight="1">
@@ -7326,6 +7290,219 @@
       </x:c>
       <x:c r="E123" t="str">
         <x:v>After skill shot and villain summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>Duplicate-Replacement Assignments</x:v>
+      </x:c>
+      <x:c r="B125"/>
+      <x:c r="C125"/>
+      <x:c r="D125"/>
+      <x:c r="E125"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>Song #</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>Configured Asset</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>Effective Uses</x:v>
+      </x:c>
+      <x:c r="D126" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="E126" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>rescue_squad</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>Final Showdown / Kingpin</x:v>
+      </x:c>
+      <x:c r="D127" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E127" t="str">
+        <x:v>Replaces duplicate Song 3; file rescue_squad.wav.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>galatea</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>Time-Tossed Showdown</x:v>
+      </x:c>
+      <x:c r="D128" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E128" t="str">
+        <x:v>Replaces duplicate Song 23; file galatea.wav.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>uptight</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>The Web Tightens</x:v>
+      </x:c>
+      <x:c r="D129" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E129" t="str">
+        <x:v>Replaces duplicate Song 38; file uptight.wav.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>monte_carlo</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>The Molemen</x:v>
+      </x:c>
+      <x:c r="D130" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E130" t="str">
+        <x:v>Replaces duplicate Song 42; file monte_carlo.wav.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>mersey_front</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>Crime Wave</x:v>
+      </x:c>
+      <x:c r="D131" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E131" t="str">
+        <x:v>Replaces duplicate Song 43; file mersey_front.wav.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>mas_que_nada</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>Trubble Unleashed</x:v>
+      </x:c>
+      <x:c r="D132" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E132" t="str">
+        <x:v>Replaces duplicate Song 47; file mas_que_nada.wav.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>fuzz</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>Sinister Surge</x:v>
+      </x:c>
+      <x:c r="D133" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E133" t="str">
+        <x:v>Replaces duplicate Song 50; file fuzz.wav.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>cardova</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>Master Vine</x:v>
+      </x:c>
+      <x:c r="D134" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E134" t="str">
+        <x:v>Replaces duplicate Song 53; file cardova.wav.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>birds_lament</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>Invasion from Everywhere</x:v>
+      </x:c>
+      <x:c r="D135" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E135" t="str">
+        <x:v>Replaces duplicate Song 55; file birds_lament.wav.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>come_september</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>Sir Galahad</x:v>
+      </x:c>
+      <x:c r="D136" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E136" t="str">
+        <x:v>Replaces duplicate Song 57; file come_september.wav.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>runaway</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>Bolton and Boomer</x:v>
+      </x:c>
+      <x:c r="D137" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E137" t="str">
+        <x:v>Replaces duplicate Song 58; file runaway.wav.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
